--- a/data/台股_外資雷達.xlsx
+++ b/data/台股_外資雷達.xlsx
@@ -487,31 +487,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>81760</v>
+        <v>10985</v>
       </c>
       <c r="D2" t="n">
-        <v>115575</v>
+        <v>94520</v>
       </c>
       <c r="E2" t="n">
-        <v>34496</v>
+        <v>162919</v>
       </c>
       <c r="F2" t="n">
-        <v>-5479</v>
+        <v>960</v>
       </c>
       <c r="G2" t="n">
-        <v>-34849</v>
+        <v>5424</v>
       </c>
       <c r="H2" t="n">
-        <v>-3927</v>
+        <v>-3532</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -520,49 +520,49 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10305</v>
+        <v>8196</v>
       </c>
       <c r="D3" t="n">
-        <v>89725</v>
+        <v>76309</v>
       </c>
       <c r="E3" t="n">
-        <v>146309</v>
+        <v>542316</v>
       </c>
       <c r="F3" t="n">
-        <v>1275</v>
+        <v>2110</v>
       </c>
       <c r="G3" t="n">
-        <v>5107</v>
+        <v>11694</v>
       </c>
       <c r="H3" t="n">
-        <v>-3448</v>
+        <v>-3215</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -583,37 +583,37 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-2309</v>
+        <v>26026</v>
       </c>
       <c r="D4" t="n">
-        <v>52146</v>
+        <v>40858</v>
       </c>
       <c r="E4" t="n">
-        <v>518093</v>
+        <v>-34455</v>
       </c>
       <c r="F4" t="n">
-        <v>2884</v>
+        <v>-136</v>
       </c>
       <c r="G4" t="n">
-        <v>11906</v>
+        <v>-27075</v>
       </c>
       <c r="H4" t="n">
-        <v>-4337</v>
+        <v>1310</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -622,49 +622,49 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🐌 龜速*</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>30496</v>
+        <v>-1957</v>
       </c>
       <c r="D5" t="n">
-        <v>51928</v>
+        <v>34008</v>
       </c>
       <c r="E5" t="n">
-        <v>-20874</v>
+        <v>-19149</v>
       </c>
       <c r="F5" t="n">
-        <v>-803</v>
+        <v>1326</v>
       </c>
       <c r="G5" t="n">
-        <v>-31524</v>
+        <v>7169</v>
       </c>
       <c r="H5" t="n">
-        <v>1731</v>
+        <v>-435</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -677,45 +677,45 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>🐌 龜速*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10214</v>
+        <v>45227</v>
       </c>
       <c r="D6" t="n">
-        <v>39976</v>
+        <v>28506</v>
       </c>
       <c r="E6" t="n">
-        <v>-20669</v>
+        <v>45849</v>
       </c>
       <c r="F6" t="n">
-        <v>610</v>
+        <v>-142</v>
       </c>
       <c r="G6" t="n">
-        <v>6359</v>
+        <v>-40197</v>
       </c>
       <c r="H6" t="n">
-        <v>-1075</v>
+        <v>-7784</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -724,49 +724,49 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2752</v>
+        <v>25199</v>
       </c>
       <c r="D7" t="n">
-        <v>24469</v>
+        <v>26962</v>
       </c>
       <c r="E7" t="n">
-        <v>46357</v>
+        <v>73131</v>
       </c>
       <c r="F7" t="n">
-        <v>1186</v>
+        <v>507</v>
       </c>
       <c r="G7" t="n">
-        <v>-3173</v>
+        <v>7295</v>
       </c>
       <c r="H7" t="n">
-        <v>-1154</v>
+        <v>24</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -775,11 +775,11 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -787,37 +787,37 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>41493</v>
+        <v>3157</v>
       </c>
       <c r="D8" t="n">
-        <v>20274</v>
+        <v>24329</v>
       </c>
       <c r="E8" t="n">
-        <v>57299</v>
+        <v>66867</v>
       </c>
       <c r="F8" t="n">
-        <v>-2023</v>
+        <v>1008</v>
       </c>
       <c r="G8" t="n">
-        <v>-3218</v>
+        <v>-2618</v>
       </c>
       <c r="H8" t="n">
-        <v>-4372</v>
+        <v>-1025</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -826,11 +826,11 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -838,37 +838,37 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-2329</v>
+        <v>27961</v>
       </c>
       <c r="D9" t="n">
-        <v>14518</v>
+        <v>17198</v>
       </c>
       <c r="E9" t="n">
-        <v>23734</v>
+        <v>65242</v>
       </c>
       <c r="F9" t="n">
-        <v>-18</v>
+        <v>-183</v>
       </c>
       <c r="G9" t="n">
-        <v>112</v>
+        <v>-3663</v>
       </c>
       <c r="H9" t="n">
-        <v>199</v>
+        <v>-4078</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -877,11 +877,11 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -889,37 +889,37 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19014</v>
+        <v>-1858</v>
       </c>
       <c r="D10" t="n">
-        <v>14491</v>
+        <v>14987</v>
       </c>
       <c r="E10" t="n">
-        <v>-125830</v>
+        <v>23678</v>
       </c>
       <c r="F10" t="n">
-        <v>-136</v>
+        <v>-83</v>
       </c>
       <c r="G10" t="n">
-        <v>-5355</v>
+        <v>110</v>
       </c>
       <c r="H10" t="n">
-        <v>2240</v>
+        <v>221</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -932,100 +932,100 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>16846</v>
+        <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>12763</v>
+        <v>9571</v>
       </c>
       <c r="E11" t="n">
-        <v>42662</v>
+        <v>12222</v>
       </c>
       <c r="F11" t="n">
-        <v>560</v>
+        <v>-682</v>
       </c>
       <c r="G11" t="n">
-        <v>8691</v>
+        <v>902</v>
       </c>
       <c r="H11" t="n">
-        <v>95</v>
+        <v>792</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>🚀 大買</t>
+          <t>🟢 加碼</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>603</v>
+        <v>8878</v>
       </c>
       <c r="D12" t="n">
-        <v>10236</v>
+        <v>9264</v>
       </c>
       <c r="E12" t="n">
-        <v>12345</v>
+        <v>-130743</v>
       </c>
       <c r="F12" t="n">
-        <v>-681</v>
+        <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>903</v>
+        <v>-5156</v>
       </c>
       <c r="H12" t="n">
-        <v>676</v>
+        <v>2212</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>🚀 大買</t>
+          <t>🟢 加碼</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1034,7 +1034,7 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1042,37 +1042,37 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4678</v>
+        <v>237</v>
       </c>
       <c r="D13" t="n">
-        <v>7774</v>
+        <v>6604</v>
       </c>
       <c r="E13" t="n">
-        <v>3932</v>
+        <v>13436</v>
       </c>
       <c r="F13" t="n">
-        <v>1680</v>
+        <v>-9</v>
       </c>
       <c r="G13" t="n">
-        <v>-4265</v>
+        <v>-2114</v>
       </c>
       <c r="H13" t="n">
-        <v>-404</v>
+        <v>-162</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1081,49 +1081,49 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2915</v>
+        <v>3401</v>
       </c>
       <c r="D14" t="n">
-        <v>6005</v>
+        <v>5537</v>
       </c>
       <c r="E14" t="n">
-        <v>21718</v>
+        <v>1250</v>
       </c>
       <c r="F14" t="n">
-        <v>-138</v>
+        <v>1448</v>
       </c>
       <c r="G14" t="n">
-        <v>-580</v>
+        <v>-3643</v>
       </c>
       <c r="H14" t="n">
-        <v>-705</v>
+        <v>205</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1132,15 +1132,15 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M14" t="n">
@@ -1150,31 +1150,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-177</v>
+        <v>2849</v>
       </c>
       <c r="D15" t="n">
-        <v>5389</v>
+        <v>5021</v>
       </c>
       <c r="E15" t="n">
-        <v>12121</v>
+        <v>24051</v>
       </c>
       <c r="F15" t="n">
-        <v>-11</v>
+        <v>-121</v>
       </c>
       <c r="G15" t="n">
-        <v>-2113</v>
+        <v>-580</v>
       </c>
       <c r="H15" t="n">
-        <v>-156</v>
+        <v>-299</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1183,19 +1183,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1210,22 +1210,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2350</v>
+        <v>2172</v>
       </c>
       <c r="D16" t="n">
-        <v>3426</v>
+        <v>4213</v>
       </c>
       <c r="E16" t="n">
-        <v>5838</v>
+        <v>10599</v>
       </c>
       <c r="F16" t="n">
-        <v>-2200</v>
+        <v>-2629</v>
       </c>
       <c r="G16" t="n">
-        <v>-5338</v>
+        <v>-5708</v>
       </c>
       <c r="H16" t="n">
-        <v>-121</v>
+        <v>-82</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1246,37 +1246,37 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>2808</v>
       </c>
       <c r="D17" t="n">
-        <v>3387</v>
+        <v>3717</v>
       </c>
       <c r="E17" t="n">
-        <v>12785</v>
+        <v>426</v>
       </c>
       <c r="F17" t="n">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="G17" t="n">
-        <v>665</v>
+        <v>-1495</v>
       </c>
       <c r="H17" t="n">
-        <v>-171</v>
+        <v>-249</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1285,11 +1285,11 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1312,22 +1312,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1814</v>
+        <v>1080</v>
       </c>
       <c r="D18" t="n">
-        <v>3330</v>
+        <v>3006</v>
       </c>
       <c r="E18" t="n">
-        <v>1347</v>
+        <v>1025</v>
       </c>
       <c r="F18" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="G18" t="n">
-        <v>-27</v>
+        <v>-30</v>
       </c>
       <c r="H18" t="n">
-        <v>-116</v>
+        <v>-121</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1354,31 +1354,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1253</v>
+        <v>603</v>
       </c>
       <c r="D19" t="n">
-        <v>3165</v>
+        <v>2325</v>
       </c>
       <c r="E19" t="n">
-        <v>11404</v>
+        <v>-1965</v>
       </c>
       <c r="F19" t="n">
-        <v>-5</v>
+        <v>1378</v>
       </c>
       <c r="G19" t="n">
-        <v>-21</v>
+        <v>-1265</v>
       </c>
       <c r="H19" t="n">
-        <v>116</v>
+        <v>164</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1391,11 +1391,11 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M19" t="n">
@@ -1414,22 +1414,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-865</v>
+        <v>-1699</v>
       </c>
       <c r="D20" t="n">
-        <v>2959</v>
+        <v>2317</v>
       </c>
       <c r="E20" t="n">
-        <v>9724</v>
+        <v>8711</v>
       </c>
       <c r="F20" t="n">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="G20" t="n">
-        <v>-13844</v>
+        <v>-13840</v>
       </c>
       <c r="H20" t="n">
-        <v>-174</v>
+        <v>-157</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1456,31 +1456,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1022</v>
+        <v>183</v>
       </c>
       <c r="D21" t="n">
-        <v>2910</v>
+        <v>2005</v>
       </c>
       <c r="E21" t="n">
-        <v>-783</v>
+        <v>-161</v>
       </c>
       <c r="F21" t="n">
-        <v>-301</v>
+        <v>16</v>
       </c>
       <c r="G21" t="n">
-        <v>-1493</v>
+        <v>675</v>
       </c>
       <c r="H21" t="n">
-        <v>-144</v>
+        <v>-127</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1493,49 +1493,49 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>414</v>
+        <v>556</v>
       </c>
       <c r="D22" t="n">
-        <v>2742</v>
+        <v>1791</v>
       </c>
       <c r="E22" t="n">
-        <v>7630</v>
+        <v>5705</v>
       </c>
       <c r="F22" t="n">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="G22" t="n">
-        <v>2436</v>
+        <v>-404</v>
       </c>
       <c r="H22" t="n">
-        <v>-357</v>
+        <v>-120</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>🟢 加碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1544,49 +1544,49 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>166</v>
+        <v>-134</v>
       </c>
       <c r="D23" t="n">
-        <v>2338</v>
+        <v>1535</v>
       </c>
       <c r="E23" t="n">
-        <v>-2022</v>
+        <v>5526</v>
       </c>
       <c r="F23" t="n">
-        <v>1254</v>
+        <v>-311</v>
       </c>
       <c r="G23" t="n">
-        <v>-1347</v>
+        <v>1697</v>
       </c>
       <c r="H23" t="n">
-        <v>143</v>
+        <v>-199</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>🟢 加碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1595,62 +1595,62 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>322</v>
+        <v>-316</v>
       </c>
       <c r="D24" t="n">
-        <v>2021</v>
+        <v>1492</v>
       </c>
       <c r="E24" t="n">
-        <v>116</v>
+        <v>11360</v>
       </c>
       <c r="F24" t="n">
-        <v>-85</v>
+        <v>388</v>
       </c>
       <c r="G24" t="n">
-        <v>663</v>
+        <v>992</v>
       </c>
       <c r="H24" t="n">
-        <v>-117</v>
+        <v>51</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>🟢 加碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M24" t="n">
@@ -1660,31 +1660,31 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>60</v>
+        <v>-97</v>
       </c>
       <c r="D25" t="n">
-        <v>1899</v>
+        <v>1352</v>
       </c>
       <c r="E25" t="n">
-        <v>-2892</v>
+        <v>10368</v>
       </c>
       <c r="F25" t="n">
-        <v>-445</v>
+        <v>-3</v>
       </c>
       <c r="G25" t="n">
-        <v>-2076</v>
+        <v>-21</v>
       </c>
       <c r="H25" t="n">
-        <v>239</v>
+        <v>88</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1705,58 +1705,58 @@
         </is>
       </c>
       <c r="M25" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>475</v>
+        <v>58</v>
       </c>
       <c r="D26" t="n">
-        <v>1647</v>
+        <v>1281</v>
       </c>
       <c r="E26" t="n">
-        <v>6076</v>
+        <v>-2877</v>
       </c>
       <c r="F26" t="n">
+        <v>-126</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-2135</v>
+      </c>
+      <c r="H26" t="n">
+        <v>250</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>90</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>🚀 加速器</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
         <v>5</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-432</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-107</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>97</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M26" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1771,22 +1771,22 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>178</v>
+        <v>-52</v>
       </c>
       <c r="D27" t="n">
-        <v>1604</v>
+        <v>1230</v>
       </c>
       <c r="E27" t="n">
-        <v>1492</v>
+        <v>1411</v>
       </c>
       <c r="F27" t="n">
-        <v>88</v>
+        <v>159</v>
       </c>
       <c r="G27" t="n">
-        <v>759</v>
+        <v>827</v>
       </c>
       <c r="H27" t="n">
-        <v>85</v>
+        <v>-17</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1813,31 +1813,31 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>128</v>
+        <v>3694</v>
       </c>
       <c r="D28" t="n">
-        <v>1377</v>
+        <v>990</v>
       </c>
       <c r="E28" t="n">
-        <v>2371</v>
+        <v>-2829</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>-6748</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-10076</v>
       </c>
       <c r="H28" t="n">
-        <v>-221</v>
+        <v>-0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1846,49 +1846,49 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-513</v>
+        <v>376</v>
       </c>
       <c r="D29" t="n">
-        <v>1043</v>
+        <v>716</v>
       </c>
       <c r="E29" t="n">
-        <v>2345</v>
+        <v>172</v>
       </c>
       <c r="F29" t="n">
-        <v>-425</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>-1565</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-585</v>
+        <v>2</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1897,11 +1897,11 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1909,37 +1909,37 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-731</v>
+        <v>123</v>
       </c>
       <c r="D30" t="n">
-        <v>866</v>
+        <v>501</v>
       </c>
       <c r="E30" t="n">
-        <v>4301</v>
+        <v>310</v>
       </c>
       <c r="F30" t="n">
-        <v>-3131</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>2040</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>561</v>
+        <v>-54</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1948,49 +1948,49 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>186</v>
+        <v>-162</v>
       </c>
       <c r="D31" t="n">
-        <v>710</v>
+        <v>463</v>
       </c>
       <c r="E31" t="n">
-        <v>550</v>
+        <v>899</v>
       </c>
       <c r="F31" t="n">
-        <v>-1465</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>-2863</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-42</v>
+        <v>12</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1999,40 +1999,40 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>468</v>
+        <v>-94</v>
       </c>
       <c r="D32" t="n">
-        <v>635</v>
+        <v>439</v>
       </c>
       <c r="E32" t="n">
-        <v>443</v>
+        <v>858</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -2041,7 +2041,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2054,45 +2054,45 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>278</v>
+        <v>23</v>
       </c>
       <c r="D33" t="n">
-        <v>510</v>
+        <v>399</v>
       </c>
       <c r="E33" t="n">
-        <v>-578</v>
+        <v>919</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="H33" t="n">
-        <v>-52</v>
+        <v>-2</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2101,49 +2101,49 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-129</v>
+        <v>-43</v>
       </c>
       <c r="D34" t="n">
-        <v>490</v>
+        <v>367</v>
       </c>
       <c r="E34" t="n">
-        <v>962</v>
+        <v>989</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="H34" t="n">
-        <v>11</v>
+        <v>-1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2152,15 +2152,15 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🐌 龜速*</t>
         </is>
       </c>
       <c r="M34" t="n">
@@ -2170,31 +2170,31 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D35" t="n">
-        <v>488</v>
+        <v>363</v>
       </c>
       <c r="E35" t="n">
-        <v>1036</v>
+        <v>-600</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>-249</v>
       </c>
       <c r="H35" t="n">
-        <v>-13</v>
+        <v>-34</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2207,45 +2207,45 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>68</v>
+        <v>362</v>
       </c>
       <c r="D36" t="n">
-        <v>387</v>
+        <v>360</v>
       </c>
       <c r="E36" t="n">
-        <v>-711</v>
+        <v>-471</v>
       </c>
       <c r="F36" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-249</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-32</v>
+        <v>4</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2258,45 +2258,45 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>122</v>
+        <v>-886</v>
       </c>
       <c r="D37" t="n">
-        <v>379</v>
+        <v>302</v>
       </c>
       <c r="E37" t="n">
-        <v>862</v>
+        <v>4981</v>
       </c>
       <c r="F37" t="n">
-        <v>-5</v>
+        <v>-3370</v>
       </c>
       <c r="G37" t="n">
-        <v>-7</v>
+        <v>1800</v>
       </c>
       <c r="H37" t="n">
-        <v>-0</v>
+        <v>460</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2305,49 +2305,49 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>合機</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>3883</v>
+        <v>189</v>
       </c>
       <c r="D38" t="n">
-        <v>363</v>
+        <v>301</v>
       </c>
       <c r="E38" t="n">
-        <v>-2642</v>
+        <v>2334</v>
       </c>
       <c r="F38" t="n">
-        <v>-6768</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-9192</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>52</v>
+        <v>-209</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2356,139 +2356,139 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>158</v>
+        <v>-2012</v>
       </c>
       <c r="D39" t="n">
-        <v>340</v>
+        <v>270</v>
       </c>
       <c r="E39" t="n">
-        <v>-112</v>
+        <v>-1075</v>
       </c>
       <c r="F39" t="n">
-        <v>-7</v>
+        <v>-215</v>
       </c>
       <c r="G39" t="n">
-        <v>95</v>
+        <v>-1535</v>
       </c>
       <c r="H39" t="n">
-        <v>17</v>
+        <v>-585</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>63</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>🛬 穩定</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-81</v>
+        <v>151</v>
       </c>
       <c r="D40" t="n">
-        <v>294</v>
+        <v>269</v>
       </c>
       <c r="E40" t="n">
-        <v>683</v>
+        <v>-254</v>
       </c>
       <c r="F40" t="n">
-        <v>5</v>
+        <v>-18</v>
       </c>
       <c r="G40" t="n">
-        <v>-6</v>
+        <v>63</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K40" t="n">
-        <v>94</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>🐌 龜速*</t>
-        </is>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>400</v>
+        <v>-342</v>
       </c>
       <c r="D41" t="n">
-        <v>200</v>
+        <v>244</v>
       </c>
       <c r="E41" t="n">
-        <v>541</v>
+        <v>4315</v>
       </c>
       <c r="F41" t="n">
-        <v>202</v>
+        <v>-7</v>
       </c>
       <c r="G41" t="n">
-        <v>319</v>
+        <v>-48</v>
       </c>
       <c r="H41" t="n">
-        <v>23</v>
+        <v>-55</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2497,11 +2497,11 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         </is>
       </c>
       <c r="M41" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="42">
@@ -2524,22 +2524,22 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-88</v>
+        <v>-132</v>
       </c>
       <c r="D42" t="n">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="E42" t="n">
-        <v>1803</v>
+        <v>2132</v>
       </c>
       <c r="F42" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G42" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H42" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2566,31 +2566,31 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="D43" t="n">
         <v>154</v>
       </c>
       <c r="E43" t="n">
-        <v>-447</v>
+        <v>-835</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>-283</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="H43" t="n">
-        <v>23</v>
+        <v>99</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2611,28 +2611,28 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="D44" t="n">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E44" t="n">
-        <v>-528</v>
+        <v>176</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2654,45 +2654,45 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>38</v>
+        <v>136</v>
       </c>
       <c r="D45" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="E45" t="n">
-        <v>783</v>
+        <v>1126</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>449</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>564</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2705,45 +2705,45 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M45" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-2962</v>
+        <v>25</v>
       </c>
       <c r="D46" t="n">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="E46" t="n">
-        <v>-228</v>
+        <v>770</v>
       </c>
       <c r="F46" t="n">
-        <v>3137</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>10308</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-93</v>
+        <v>-2</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2752,49 +2752,49 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D47" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E47" t="n">
-        <v>-957</v>
+        <v>167</v>
       </c>
       <c r="F47" t="n">
-        <v>-337</v>
+        <v>33</v>
       </c>
       <c r="G47" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="H47" t="n">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2803,49 +2803,49 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>方土霖</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-324</v>
+        <v>13</v>
       </c>
       <c r="D48" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E48" t="n">
-        <v>4297</v>
+        <v>45</v>
       </c>
       <c r="F48" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>-48</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-48</v>
+        <v>-3</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2854,49 +2854,49 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>方土霖</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>16</v>
+        <v>-100</v>
       </c>
       <c r="D49" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="E49" t="n">
-        <v>50</v>
+        <v>445</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>-1458</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>-1998</v>
       </c>
       <c r="H49" t="n">
-        <v>-3</v>
+        <v>-38</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2909,15 +2909,15 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -2932,13 +2932,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>-5</v>
       </c>
       <c r="D50" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>-47</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -2947,7 +2947,7 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0</v>
+        <v>-1</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2974,31 +2974,31 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-11</v>
+        <v>-581</v>
       </c>
       <c r="D51" t="n">
-        <v>30</v>
+        <v>-26</v>
       </c>
       <c r="E51" t="n">
-        <v>40</v>
+        <v>493</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>-713</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>2818</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>-155</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3007,49 +3007,49 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D52" t="n">
-        <v>-3</v>
+        <v>-71</v>
       </c>
       <c r="E52" t="n">
-        <v>137</v>
+        <v>-166</v>
       </c>
       <c r="F52" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3062,45 +3062,45 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-143</v>
+        <v>-372</v>
       </c>
       <c r="D53" t="n">
-        <v>-52</v>
+        <v>-84</v>
       </c>
       <c r="E53" t="n">
-        <v>333</v>
+        <v>1163</v>
       </c>
       <c r="F53" t="n">
-        <v>-40</v>
+        <v>80</v>
       </c>
       <c r="G53" t="n">
-        <v>-42</v>
+        <v>154</v>
       </c>
       <c r="H53" t="n">
-        <v>-14</v>
+        <v>82</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3109,19 +3109,19 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="54">
@@ -3136,13 +3136,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-93</v>
+        <v>-115</v>
       </c>
       <c r="D54" t="n">
-        <v>-70</v>
+        <v>-97</v>
       </c>
       <c r="E54" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3178,82 +3178,82 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>9</v>
+        <v>-118</v>
       </c>
       <c r="D55" t="n">
-        <v>-110</v>
+        <v>-104</v>
       </c>
       <c r="E55" t="n">
-        <v>-107</v>
+        <v>337</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>-41</v>
       </c>
       <c r="H55" t="n">
+        <v>-23</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>96</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>✈️ 高飛*</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
         <v>1</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K55" t="n">
-        <v>77</v>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M55" t="n">
-        <v>-2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>德昌</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-556</v>
+        <v>-26</v>
       </c>
       <c r="D56" t="n">
-        <v>-134</v>
+        <v>-201</v>
       </c>
       <c r="E56" t="n">
-        <v>676</v>
+        <v>-1988</v>
       </c>
       <c r="F56" t="n">
-        <v>479</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3262,49 +3262,49 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-685</v>
+        <v>-320</v>
       </c>
       <c r="D57" t="n">
-        <v>-166</v>
+        <v>-286</v>
       </c>
       <c r="E57" t="n">
-        <v>-1354</v>
+        <v>-510</v>
       </c>
       <c r="F57" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>698</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>219</v>
+        <v>-9</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3325,37 +3325,37 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-61</v>
+        <v>-33</v>
       </c>
       <c r="D58" t="n">
-        <v>-190</v>
+        <v>-290</v>
       </c>
       <c r="E58" t="n">
-        <v>-1970</v>
+        <v>-1715</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>688</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>-2196</v>
       </c>
       <c r="H58" t="n">
-        <v>-1</v>
+        <v>-67</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3364,49 +3364,49 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-396</v>
+        <v>-465</v>
       </c>
       <c r="D59" t="n">
-        <v>-206</v>
+        <v>-319</v>
       </c>
       <c r="E59" t="n">
-        <v>1617</v>
+        <v>-1904</v>
       </c>
       <c r="F59" t="n">
-        <v>91</v>
+        <v>264</v>
       </c>
       <c r="G59" t="n">
-        <v>146</v>
+        <v>572</v>
       </c>
       <c r="H59" t="n">
-        <v>78</v>
+        <v>177</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3415,49 +3415,49 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-457</v>
+        <v>118</v>
       </c>
       <c r="D60" t="n">
-        <v>-316</v>
+        <v>-390</v>
       </c>
       <c r="E60" t="n">
-        <v>1347</v>
+        <v>-1099</v>
       </c>
       <c r="F60" t="n">
-        <v>-418</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>2769</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-359</v>
+        <v>-8</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3466,49 +3466,49 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-3</v>
+        <v>539</v>
       </c>
       <c r="D61" t="n">
-        <v>-318</v>
+        <v>-460</v>
       </c>
       <c r="E61" t="n">
-        <v>-1781</v>
+        <v>-3953</v>
       </c>
       <c r="F61" t="n">
-        <v>622</v>
+        <v>155</v>
       </c>
       <c r="G61" t="n">
-        <v>-2233</v>
+        <v>195</v>
       </c>
       <c r="H61" t="n">
-        <v>-62</v>
+        <v>-21</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3517,19 +3517,19 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="62">
@@ -3544,13 +3544,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-203</v>
+        <v>-388</v>
       </c>
       <c r="D62" t="n">
-        <v>-338</v>
+        <v>-474</v>
       </c>
       <c r="E62" t="n">
-        <v>-3843</v>
+        <v>-3941</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -3586,31 +3586,31 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-89</v>
+        <v>-341</v>
       </c>
       <c r="D63" t="n">
-        <v>-471</v>
+        <v>-492</v>
       </c>
       <c r="E63" t="n">
-        <v>999</v>
+        <v>488</v>
       </c>
       <c r="F63" t="n">
-        <v>-25</v>
+        <v>288</v>
       </c>
       <c r="G63" t="n">
-        <v>-173</v>
+        <v>436</v>
       </c>
       <c r="H63" t="n">
-        <v>-45</v>
+        <v>4</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3619,49 +3619,49 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>922</v>
+        <v>-24</v>
       </c>
       <c r="D64" t="n">
-        <v>-499</v>
+        <v>-508</v>
       </c>
       <c r="E64" t="n">
-        <v>-3899</v>
+        <v>-1396</v>
       </c>
       <c r="F64" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-5</v>
+        <v>-55</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3670,40 +3670,40 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>智冠</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>110</v>
+        <v>-126</v>
       </c>
       <c r="D65" t="n">
-        <v>-501</v>
+        <v>-523</v>
       </c>
       <c r="E65" t="n">
-        <v>-722</v>
+        <v>-855</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
@@ -3712,7 +3712,7 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3721,11 +3721,11 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3733,37 +3733,37 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-150</v>
+        <v>-72</v>
       </c>
       <c r="D66" t="n">
-        <v>-535</v>
+        <v>-534</v>
       </c>
       <c r="E66" t="n">
-        <v>-773</v>
+        <v>-4201</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>-893</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>2309</v>
       </c>
       <c r="H66" t="n">
-        <v>-2</v>
+        <v>112</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3772,11 +3772,11 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3784,37 +3784,37 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-618</v>
+        <v>1662</v>
       </c>
       <c r="D67" t="n">
-        <v>-546</v>
+        <v>-542</v>
       </c>
       <c r="E67" t="n">
-        <v>-2396</v>
+        <v>-9625</v>
       </c>
       <c r="F67" t="n">
-        <v>-285</v>
+        <v>-4</v>
       </c>
       <c r="G67" t="n">
-        <v>-452</v>
+        <v>-10</v>
       </c>
       <c r="H67" t="n">
-        <v>356</v>
+        <v>578</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3823,49 +3823,49 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>554</v>
+        <v>-60</v>
       </c>
       <c r="D68" t="n">
-        <v>-567</v>
+        <v>-543</v>
       </c>
       <c r="E68" t="n">
-        <v>-3821</v>
+        <v>1045</v>
       </c>
       <c r="F68" t="n">
-        <v>-1376</v>
+        <v>-24</v>
       </c>
       <c r="G68" t="n">
-        <v>2264</v>
+        <v>-53</v>
       </c>
       <c r="H68" t="n">
-        <v>299</v>
+        <v>-33</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3878,45 +3878,45 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-670</v>
+        <v>-1078</v>
       </c>
       <c r="D69" t="n">
-        <v>-733</v>
+        <v>-592</v>
       </c>
       <c r="E69" t="n">
-        <v>2256</v>
+        <v>-495</v>
       </c>
       <c r="F69" t="n">
-        <v>-253</v>
+        <v>-37</v>
       </c>
       <c r="G69" t="n">
-        <v>-595</v>
+        <v>-360</v>
       </c>
       <c r="H69" t="n">
-        <v>-73</v>
+        <v>-259</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3925,19 +3925,19 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -3952,13 +3952,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-641</v>
+        <v>-699</v>
       </c>
       <c r="D70" t="n">
-        <v>-825</v>
+        <v>-610</v>
       </c>
       <c r="E70" t="n">
-        <v>916</v>
+        <v>741</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -3967,7 +3967,7 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-139</v>
+        <v>-164</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3994,31 +3994,31 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-525</v>
+        <v>-222</v>
       </c>
       <c r="D71" t="n">
-        <v>-922</v>
+        <v>-879</v>
       </c>
       <c r="E71" t="n">
-        <v>-1036</v>
+        <v>-7578</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>-659</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>785</v>
       </c>
       <c r="H71" t="n">
-        <v>-72</v>
+        <v>620</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -4027,49 +4027,49 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M71" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-218</v>
+        <v>87</v>
       </c>
       <c r="D72" t="n">
-        <v>-938</v>
+        <v>-950</v>
       </c>
       <c r="E72" t="n">
-        <v>-8480</v>
+        <v>1046</v>
       </c>
       <c r="F72" t="n">
-        <v>-977</v>
+        <v>-271</v>
       </c>
       <c r="G72" t="n">
-        <v>693</v>
+        <v>-448</v>
       </c>
       <c r="H72" t="n">
-        <v>590</v>
+        <v>-34</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -4078,40 +4078,40 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-331</v>
+        <v>-407</v>
       </c>
       <c r="D73" t="n">
-        <v>-1033</v>
+        <v>-1084</v>
       </c>
       <c r="E73" t="n">
-        <v>-1555</v>
+        <v>37</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -4120,7 +4120,7 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>-175</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4129,11 +4129,11 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4141,127 +4141,127 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>聯合</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-535</v>
+        <v>-370</v>
       </c>
       <c r="D74" t="n">
-        <v>-1328</v>
+        <v>-1094</v>
       </c>
       <c r="E74" t="n">
-        <v>1747</v>
+        <v>-1764</v>
       </c>
       <c r="F74" t="n">
-        <v>246</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>3151</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-104</v>
+        <v>0</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>87</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>🚀 加速器</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>324</v>
+        <v>-225</v>
       </c>
       <c r="D75" t="n">
-        <v>-1364</v>
+        <v>-1361</v>
       </c>
       <c r="E75" t="n">
-        <v>-2456</v>
+        <v>2383</v>
       </c>
       <c r="F75" t="n">
-        <v>-39</v>
+        <v>209</v>
       </c>
       <c r="G75" t="n">
-        <v>-406</v>
+        <v>2819</v>
       </c>
       <c r="H75" t="n">
-        <v>-13</v>
+        <v>39</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K75" t="n">
-        <v>71</v>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M75" t="n">
-        <v>-3</v>
-      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>勝一</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-571</v>
+        <v>238</v>
       </c>
       <c r="D76" t="n">
-        <v>-1425</v>
+        <v>-1448</v>
       </c>
       <c r="E76" t="n">
-        <v>282</v>
+        <v>-2617</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>-39</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>-262</v>
       </c>
       <c r="H76" t="n">
-        <v>-178</v>
+        <v>9</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4274,45 +4274,45 @@
         </is>
       </c>
       <c r="K76" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M76" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-1329</v>
+        <v>-4812</v>
       </c>
       <c r="D77" t="n">
-        <v>-1760</v>
+        <v>-1708</v>
       </c>
       <c r="E77" t="n">
-        <v>-471</v>
+        <v>-2285</v>
       </c>
       <c r="F77" t="n">
-        <v>-37</v>
+        <v>3874</v>
       </c>
       <c r="G77" t="n">
-        <v>-360</v>
+        <v>11028</v>
       </c>
       <c r="H77" t="n">
-        <v>-309</v>
+        <v>-111</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4329,41 +4329,41 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M77" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-166</v>
+        <v>171</v>
       </c>
       <c r="D78" t="n">
-        <v>-1778</v>
+        <v>-1712</v>
       </c>
       <c r="E78" t="n">
-        <v>-5562</v>
+        <v>-8211</v>
       </c>
       <c r="F78" t="n">
-        <v>105</v>
+        <v>-2661</v>
       </c>
       <c r="G78" t="n">
-        <v>619</v>
+        <v>-7210</v>
       </c>
       <c r="H78" t="n">
-        <v>-131</v>
+        <v>197</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4376,45 +4376,45 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-666</v>
+        <v>441</v>
       </c>
       <c r="D79" t="n">
-        <v>-1837</v>
+        <v>-1782</v>
       </c>
       <c r="E79" t="n">
-        <v>-8665</v>
+        <v>-2363</v>
       </c>
       <c r="F79" t="n">
-        <v>-2073</v>
+        <v>87</v>
       </c>
       <c r="G79" t="n">
-        <v>-6727</v>
+        <v>343</v>
       </c>
       <c r="H79" t="n">
-        <v>242</v>
+        <v>139</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4435,41 +4435,41 @@
         </is>
       </c>
       <c r="M79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>703</v>
+        <v>-290</v>
       </c>
       <c r="D80" t="n">
-        <v>-2218</v>
+        <v>-1846</v>
       </c>
       <c r="E80" t="n">
-        <v>-3305</v>
+        <v>-5561</v>
       </c>
       <c r="F80" t="n">
-        <v>89</v>
+        <v>132</v>
       </c>
       <c r="G80" t="n">
-        <v>383</v>
+        <v>707</v>
       </c>
       <c r="H80" t="n">
-        <v>140</v>
+        <v>-144</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4478,15 +4478,15 @@
         </is>
       </c>
       <c r="K80" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -4501,22 +4501,22 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-888</v>
+        <v>-117</v>
       </c>
       <c r="D81" t="n">
-        <v>-2447</v>
+        <v>-2157</v>
       </c>
       <c r="E81" t="n">
-        <v>-2541</v>
+        <v>-2389</v>
       </c>
       <c r="F81" t="n">
-        <v>1396</v>
+        <v>1060</v>
       </c>
       <c r="G81" t="n">
-        <v>1927</v>
+        <v>1898</v>
       </c>
       <c r="H81" t="n">
-        <v>-47</v>
+        <v>-52</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4543,31 +4543,31 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-1453</v>
+        <v>1754</v>
       </c>
       <c r="D82" t="n">
-        <v>-3021</v>
+        <v>-2160</v>
       </c>
       <c r="E82" t="n">
-        <v>4199</v>
+        <v>-14252</v>
       </c>
       <c r="F82" t="n">
-        <v>-229</v>
+        <v>99</v>
       </c>
       <c r="G82" t="n">
-        <v>-177</v>
+        <v>2764</v>
       </c>
       <c r="H82" t="n">
-        <v>-128</v>
+        <v>-95</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4576,49 +4576,49 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M82" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>959</v>
+        <v>-1441</v>
       </c>
       <c r="D83" t="n">
-        <v>-3145</v>
+        <v>-2992</v>
       </c>
       <c r="E83" t="n">
-        <v>-16457</v>
+        <v>542</v>
       </c>
       <c r="F83" t="n">
-        <v>174</v>
+        <v>-349</v>
       </c>
       <c r="G83" t="n">
-        <v>2691</v>
+        <v>-287</v>
       </c>
       <c r="H83" t="n">
-        <v>-58</v>
+        <v>-131</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4627,19 +4627,19 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M83" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="84">
@@ -4654,22 +4654,22 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-95</v>
+        <v>-331</v>
       </c>
       <c r="D84" t="n">
-        <v>-3147</v>
+        <v>-3136</v>
       </c>
       <c r="E84" t="n">
-        <v>-4320</v>
+        <v>-3875</v>
       </c>
       <c r="F84" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="G84" t="n">
         <v>-189</v>
       </c>
       <c r="H84" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4696,31 +4696,31 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-400</v>
+        <v>-736</v>
       </c>
       <c r="D85" t="n">
-        <v>-3245</v>
+        <v>-3157</v>
       </c>
       <c r="E85" t="n">
-        <v>-10408</v>
+        <v>-5546</v>
       </c>
       <c r="F85" t="n">
         <v>-4</v>
       </c>
       <c r="G85" t="n">
-        <v>-10</v>
+        <v>1077</v>
       </c>
       <c r="H85" t="n">
-        <v>558</v>
+        <v>2358</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4741,37 +4741,37 @@
         </is>
       </c>
       <c r="M85" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-877</v>
+        <v>-2803</v>
       </c>
       <c r="D86" t="n">
-        <v>-3600</v>
+        <v>-3292</v>
       </c>
       <c r="E86" t="n">
-        <v>-4985</v>
+        <v>-4657</v>
       </c>
       <c r="F86" t="n">
-        <v>39</v>
+        <v>-291</v>
       </c>
       <c r="G86" t="n">
-        <v>-524</v>
+        <v>-179</v>
       </c>
       <c r="H86" t="n">
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4780,100 +4780,88 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K86" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>🚀 加速器*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M86" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-16438</v>
+        <v>392</v>
       </c>
       <c r="D87" t="n">
-        <v>-3702</v>
+        <v>-3310</v>
       </c>
       <c r="E87" t="n">
-        <v>60732</v>
+        <v>-5763</v>
       </c>
       <c r="F87" t="n">
-        <v>786</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>495</v>
+        <v>-400</v>
       </c>
       <c r="H87" t="n">
-        <v>-2906</v>
+        <v>52</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
           <t>🟠 減碼</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K87" t="n">
-        <v>68</v>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M87" t="n">
-        <v>0</v>
-      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-1000</v>
+        <v>198</v>
       </c>
       <c r="D88" t="n">
-        <v>-3720</v>
+        <v>-3737</v>
       </c>
       <c r="E88" t="n">
-        <v>-5021</v>
+        <v>-7954</v>
       </c>
       <c r="F88" t="n">
-        <v>-4</v>
+        <v>392</v>
       </c>
       <c r="G88" t="n">
-        <v>1077</v>
+        <v>2398</v>
       </c>
       <c r="H88" t="n">
-        <v>2305</v>
+        <v>-595</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4882,11 +4870,11 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K88" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -4894,37 +4882,37 @@
         </is>
       </c>
       <c r="M88" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>678</v>
+        <v>-2905</v>
       </c>
       <c r="D89" t="n">
-        <v>-4012</v>
+        <v>-3971</v>
       </c>
       <c r="E89" t="n">
-        <v>-24434</v>
+        <v>-3232</v>
       </c>
       <c r="F89" t="n">
-        <v>-293</v>
+        <v>-328</v>
       </c>
       <c r="G89" t="n">
-        <v>-1444</v>
+        <v>5452</v>
       </c>
       <c r="H89" t="n">
-        <v>-74</v>
+        <v>60</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4933,49 +4921,49 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K89" t="n">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M89" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-2001</v>
+        <v>-375</v>
       </c>
       <c r="D90" t="n">
-        <v>-4071</v>
+        <v>-4301</v>
       </c>
       <c r="E90" t="n">
-        <v>-3708</v>
+        <v>-6322</v>
       </c>
       <c r="F90" t="n">
-        <v>413</v>
+        <v>-7</v>
       </c>
       <c r="G90" t="n">
-        <v>5026</v>
+        <v>-536</v>
       </c>
       <c r="H90" t="n">
-        <v>85</v>
+        <v>-10</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4992,41 +4980,41 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🚀 加速器*</t>
         </is>
       </c>
       <c r="M90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-4171</v>
+        <v>-489</v>
       </c>
       <c r="D91" t="n">
-        <v>-4201</v>
+        <v>-4629</v>
       </c>
       <c r="E91" t="n">
-        <v>-43281</v>
+        <v>-23490</v>
       </c>
       <c r="F91" t="n">
-        <v>123</v>
+        <v>-242</v>
       </c>
       <c r="G91" t="n">
-        <v>218</v>
+        <v>-1545</v>
       </c>
       <c r="H91" t="n">
-        <v>13</v>
+        <v>-238</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -5035,49 +5023,49 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K91" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M91" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-433</v>
+        <v>-5729</v>
       </c>
       <c r="D92" t="n">
-        <v>-4424</v>
+        <v>-5572</v>
       </c>
       <c r="E92" t="n">
-        <v>-7227</v>
+        <v>-38520</v>
       </c>
       <c r="F92" t="n">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="G92" t="n">
-        <v>2164</v>
+        <v>301</v>
       </c>
       <c r="H92" t="n">
-        <v>-645</v>
+        <v>46</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -5086,59 +5074,71 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K92" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>1</v>
+        <v>-335</v>
       </c>
       <c r="D93" t="n">
-        <v>-4500</v>
+        <v>-8937</v>
       </c>
       <c r="E93" t="n">
-        <v>-6178</v>
+        <v>-15199</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>-752</v>
       </c>
       <c r="G93" t="n">
-        <v>-400</v>
+        <v>2690</v>
       </c>
       <c r="H93" t="n">
-        <v>125</v>
+        <v>418</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
           <t>🟠 減碼</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>93</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>🚀 加速器</t>
+        </is>
+      </c>
+      <c r="M93" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5152,22 +5152,22 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-1918</v>
+        <v>-1986</v>
       </c>
       <c r="D94" t="n">
-        <v>-8602</v>
+        <v>-9126</v>
       </c>
       <c r="E94" t="n">
-        <v>-10921</v>
+        <v>-10960</v>
       </c>
       <c r="F94" t="n">
-        <v>-3052</v>
+        <v>-3315</v>
       </c>
       <c r="G94" t="n">
-        <v>-2684</v>
+        <v>-3071</v>
       </c>
       <c r="H94" t="n">
-        <v>-711</v>
+        <v>-637</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -5194,53 +5194,41 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-385</v>
+        <v>-611</v>
       </c>
       <c r="D95" t="n">
-        <v>-10149</v>
+        <v>-9743</v>
       </c>
       <c r="E95" t="n">
-        <v>-14537</v>
+        <v>-8989</v>
       </c>
       <c r="F95" t="n">
-        <v>-1480</v>
+        <v>-562</v>
       </c>
       <c r="G95" t="n">
-        <v>4132</v>
+        <v>3142</v>
       </c>
       <c r="H95" t="n">
-        <v>318</v>
+        <v>219</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>🔴 大賣</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K95" t="n">
-        <v>93</v>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>🚀 加速器</t>
-        </is>
-      </c>
-      <c r="M95" t="n">
-        <v>3</v>
-      </c>
+          <t>🟠 減碼</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5254,13 +5242,13 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-1819</v>
+        <v>-1759</v>
       </c>
       <c r="D96" t="n">
-        <v>-11059</v>
+        <v>-10220</v>
       </c>
       <c r="E96" t="n">
-        <v>-16042</v>
+        <v>-16716</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -5269,7 +5257,7 @@
         <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>-1</v>
+        <v>-8</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -5296,70 +5284,82 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-3767</v>
+        <v>-12414</v>
       </c>
       <c r="D97" t="n">
-        <v>-12749</v>
+        <v>-12240</v>
       </c>
       <c r="E97" t="n">
-        <v>-9308</v>
+        <v>66876</v>
       </c>
       <c r="F97" t="n">
-        <v>613</v>
+        <v>-2410</v>
       </c>
       <c r="G97" t="n">
-        <v>5574</v>
+        <v>13440</v>
       </c>
       <c r="H97" t="n">
-        <v>339</v>
+        <v>-933</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
           <t>🔴 大賣</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>64</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M97" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>長榮航太</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-6937</v>
+        <v>-724</v>
       </c>
       <c r="D98" t="n">
-        <v>-12920</v>
+        <v>-14303</v>
       </c>
       <c r="E98" t="n">
-        <v>76316</v>
+        <v>-10729</v>
       </c>
       <c r="F98" t="n">
-        <v>-1041</v>
+        <v>6</v>
       </c>
       <c r="G98" t="n">
-        <v>14277</v>
+        <v>204</v>
       </c>
       <c r="H98" t="n">
-        <v>-999</v>
+        <v>-17</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5368,19 +5368,19 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K98" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M98" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -5395,22 +5395,22 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-6955</v>
+        <v>-11935</v>
       </c>
       <c r="D99" t="n">
-        <v>-14860</v>
+        <v>-17441</v>
       </c>
       <c r="E99" t="n">
-        <v>-50375</v>
+        <v>-52736</v>
       </c>
       <c r="F99" t="n">
-        <v>-2356</v>
+        <v>-3156</v>
       </c>
       <c r="G99" t="n">
-        <v>-8243</v>
+        <v>-8934</v>
       </c>
       <c r="H99" t="n">
-        <v>-524</v>
+        <v>-48</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5437,31 +5437,31 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-667</v>
+        <v>-2534</v>
       </c>
       <c r="D100" t="n">
-        <v>-17122</v>
+        <v>-18392</v>
       </c>
       <c r="E100" t="n">
-        <v>-8816</v>
+        <v>-26136</v>
       </c>
       <c r="F100" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>203</v>
+        <v>0</v>
       </c>
       <c r="H100" t="n">
-        <v>98</v>
+        <v>-64</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -5470,70 +5470,70 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K100" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-3066</v>
+        <v>-29474</v>
       </c>
       <c r="D101" t="n">
-        <v>-18403</v>
+        <v>-18531</v>
       </c>
       <c r="E101" t="n">
-        <v>-25717</v>
+        <v>61108</v>
       </c>
       <c r="F101" t="n">
+        <v>482</v>
+      </c>
+      <c r="G101" t="n">
+        <v>781</v>
+      </c>
+      <c r="H101" t="n">
+        <v>-3610</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>🔴 大賣</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>68</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M101" t="n">
         <v>0</v>
-      </c>
-      <c r="G101" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" t="n">
-        <v>-70</v>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>🔴 大賣</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K101" t="n">
-        <v>60</v>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>🛬 穩定</t>
-        </is>
-      </c>
-      <c r="M101" t="n">
-        <v>-4</v>
       </c>
     </row>
     <row r="102">
@@ -5548,22 +5548,22 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1167</v>
+        <v>2290</v>
       </c>
       <c r="D102" t="n">
-        <v>-27012</v>
+        <v>-19450</v>
       </c>
       <c r="E102" t="n">
-        <v>-68018</v>
+        <v>-66136</v>
       </c>
       <c r="F102" t="n">
-        <v>-14</v>
+        <v>-31</v>
       </c>
       <c r="G102" t="n">
-        <v>-1902</v>
+        <v>-1993</v>
       </c>
       <c r="H102" t="n">
-        <v>-570</v>
+        <v>-643</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5590,31 +5590,31 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>10247</v>
+        <v>-5641</v>
       </c>
       <c r="D103" t="n">
-        <v>-28232</v>
+        <v>-26947</v>
       </c>
       <c r="E103" t="n">
-        <v>5745</v>
+        <v>-68039</v>
       </c>
       <c r="F103" t="n">
-        <v>2137</v>
+        <v>-672</v>
       </c>
       <c r="G103" t="n">
-        <v>-4713</v>
+        <v>-27587</v>
       </c>
       <c r="H103" t="n">
-        <v>-3679</v>
+        <v>302</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5623,15 +5623,15 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K103" t="n">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M103" t="n">
@@ -5641,31 +5641,31 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>18471</v>
+        <v>-19912</v>
       </c>
       <c r="D104" t="n">
-        <v>-43649</v>
+        <v>-35054</v>
       </c>
       <c r="E104" t="n">
-        <v>-63772</v>
+        <v>23102</v>
       </c>
       <c r="F104" t="n">
-        <v>-1279</v>
+        <v>1401</v>
       </c>
       <c r="G104" t="n">
-        <v>-26678</v>
+        <v>-1751</v>
       </c>
       <c r="H104" t="n">
-        <v>283</v>
+        <v>-2904</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5674,15 +5674,15 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K104" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M104" t="n">
@@ -5701,22 +5701,22 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-60119</v>
+        <v>-80785</v>
       </c>
       <c r="D105" t="n">
-        <v>-107604</v>
+        <v>-103789</v>
       </c>
       <c r="E105" t="n">
-        <v>127849</v>
+        <v>139111</v>
       </c>
       <c r="F105" t="n">
-        <v>7363</v>
+        <v>2879</v>
       </c>
       <c r="G105" t="n">
-        <v>19320</v>
+        <v>21134</v>
       </c>
       <c r="H105" t="n">
-        <v>-195</v>
+        <v>150</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         </is>
       </c>
       <c r="M105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5799,20 +5799,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,581 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -1,207 千股)</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>-133899</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1535342</v>
+      </c>
+      <c r="E2" t="n">
         <v>413639</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>2741874</v>
-      </c>
-      <c r="E2" t="n">
-        <v>510417</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4322741</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -5823,29 +5823,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -221 千股)</t>
+          <t>📈 20d 巨變(加碼 1,213 千股)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>185946</v>
+        <v>-334930</v>
       </c>
       <c r="D3" t="n">
-        <v>709557</v>
+        <v>-8936751</v>
       </c>
       <c r="E3" t="n">
-        <v>53328</v>
+        <v>-384885</v>
       </c>
       <c r="F3" t="n">
-        <v>930122</v>
+        <v>-10149484</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
@@ -5857,20 +5857,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠</t>
+          <t>📉 20d 巨變(減碼 -618 千股)</t>
         </is>
       </c>
       <c r="C4" t="n">
+        <v>57512</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1281306</v>
+      </c>
+      <c r="E4" t="n">
         <v>59677</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>1899349</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-44489</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1895018</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -5881,203 +5881,203 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 717 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -679 千股)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>678009</v>
+        <v>-100330</v>
       </c>
       <c r="D5" t="n">
-        <v>-4012448</v>
+        <v>30718</v>
       </c>
       <c r="E5" t="n">
-        <v>695718</v>
+        <v>185946</v>
       </c>
       <c r="F5" t="n">
-        <v>-4728977</v>
+        <v>709557</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>勤誠</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 13 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -616 千股)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>322160</v>
+        <v>-489132</v>
       </c>
       <c r="D6" t="n">
-        <v>2020859</v>
+        <v>-4628887</v>
       </c>
       <c r="E6" t="n">
-        <v>426968</v>
+        <v>678009</v>
       </c>
       <c r="F6" t="n">
-        <v>2007436</v>
+        <v>-4012448</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>亞翔</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 371 千股)</t>
+          <t>📉 20d 巨變(減碼 -16 千股)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-384885</v>
+        <v>183068</v>
       </c>
       <c r="D7" t="n">
-        <v>-10149484</v>
+        <v>2005152</v>
       </c>
       <c r="E7" t="n">
-        <v>-617478</v>
+        <v>322160</v>
       </c>
       <c r="F7" t="n">
-        <v>-10520197</v>
+        <v>2020859</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>健策</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 538 千股)</t>
+          <t>📉 20d 巨變(減碼 -13 千股)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>602507</v>
+        <v>603030</v>
       </c>
       <c r="D8" t="n">
-        <v>10235741</v>
+        <v>2324994</v>
       </c>
       <c r="E8" t="n">
-        <v>468045</v>
+        <v>166455</v>
       </c>
       <c r="F8" t="n">
-        <v>9698133</v>
+        <v>2337683</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>致茂</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -53 千股)</t>
+          <t>📉 20d 巨變(減碼 -153 千股)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-2531</v>
+        <v>-465155</v>
       </c>
       <c r="D9" t="n">
-        <v>-317898</v>
+        <v>-319191</v>
       </c>
       <c r="E9" t="n">
-        <v>221899</v>
+        <v>-685246</v>
       </c>
       <c r="F9" t="n">
-        <v>-265344</v>
+        <v>-166018</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>光聖</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -5,917 千股)</t>
+          <t>📉 20d 巨變(減碼 -665 千股)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19013989</v>
+        <v>108230</v>
       </c>
       <c r="D10" t="n">
-        <v>14491033</v>
+        <v>9571239</v>
       </c>
       <c r="E10" t="n">
-        <v>19997518</v>
+        <v>602507</v>
       </c>
       <c r="F10" t="n">
-        <v>20407548</v>
+        <v>10235741</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>雙鴻</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 678 千股)</t>
+          <t>📈 20d 巨變(加碼 28 千股)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-685246</v>
+        <v>-32920</v>
       </c>
       <c r="D11" t="n">
-        <v>-166018</v>
+        <v>-289771</v>
       </c>
       <c r="E11" t="n">
-        <v>-346033</v>
+        <v>-2531</v>
       </c>
       <c r="F11" t="n">
-        <v>-843662</v>
+        <v>-317898</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>旺矽</t>
         </is>
       </c>
     </row>
@@ -6089,20 +6089,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 624 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 125 千股)</t>
         </is>
       </c>
       <c r="C12" t="n">
+        <v>171263</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-1711576</v>
+      </c>
+      <c r="E12" t="n">
         <v>-666245</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>-1836700</v>
-      </c>
-      <c r="E12" t="n">
-        <v>-974489</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-2461126</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -6113,203 +6113,203 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -814 千股)</t>
+          <t>📉 20d 巨變(減碼 -5,227 千股)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>166455</v>
+        <v>8877774</v>
       </c>
       <c r="D13" t="n">
-        <v>2337683</v>
+        <v>9264250</v>
       </c>
       <c r="E13" t="n">
-        <v>919829</v>
+        <v>19013989</v>
       </c>
       <c r="F13" t="n">
-        <v>3151737</v>
+        <v>14491033</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -904 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,580 千股)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>474674</v>
+        <v>-11935031</v>
       </c>
       <c r="D14" t="n">
-        <v>1646848</v>
+        <v>-17440933</v>
       </c>
       <c r="E14" t="n">
-        <v>1764154</v>
+        <v>-6955457</v>
       </c>
       <c r="F14" t="n">
-        <v>2550691</v>
+        <v>-14860437</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -10,108 千股)</t>
+          <t>📈 20d 巨變(加碼 144 千股)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-6955457</v>
+        <v>555865</v>
       </c>
       <c r="D15" t="n">
-        <v>-14860437</v>
+        <v>1791270</v>
       </c>
       <c r="E15" t="n">
-        <v>3860807</v>
+        <v>474674</v>
       </c>
       <c r="F15" t="n">
-        <v>-4752440</v>
+        <v>1646848</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>帆宣</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -483 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 687 千股)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-670227</v>
+        <v>198488</v>
       </c>
       <c r="D16" t="n">
-        <v>-733375</v>
+        <v>-3737139</v>
       </c>
       <c r="E16" t="n">
-        <v>-613062</v>
+        <v>-433454</v>
       </c>
       <c r="F16" t="n">
-        <v>-250122</v>
+        <v>-4424081</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>健鼎</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 10 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -217 千股)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>137400</v>
+        <v>87218</v>
       </c>
       <c r="D17" t="n">
-        <v>89176</v>
+        <v>-950289</v>
       </c>
       <c r="E17" t="n">
-        <v>107110</v>
+        <v>-670227</v>
       </c>
       <c r="F17" t="n">
-        <v>78822</v>
+        <v>-733375</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>辛耘</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -158 千股)</t>
+          <t>📈 20d 巨變(加碼 65 千股)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-94876</v>
+        <v>111538</v>
       </c>
       <c r="D18" t="n">
-        <v>-3146856</v>
+        <v>154496</v>
       </c>
       <c r="E18" t="n">
-        <v>-883818</v>
+        <v>137400</v>
       </c>
       <c r="F18" t="n">
-        <v>-2989277</v>
+        <v>89176</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>川湖</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -2,810 千股)</t>
+          <t>📈 20d 巨變(加碼 11 千股)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-433454</v>
+        <v>-331369</v>
       </c>
       <c r="D19" t="n">
-        <v>-4424081</v>
+        <v>-3135895</v>
       </c>
       <c r="E19" t="n">
-        <v>383396</v>
+        <v>-94876</v>
       </c>
       <c r="F19" t="n">
-        <v>-1613636</v>
+        <v>-3146856</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>佳必琪</t>
         </is>
       </c>
     </row>
@@ -6321,20 +6321,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -8,878 千股)</t>
+          <t>📉 20d 巨變(減碼 -984 千股)</t>
         </is>
       </c>
       <c r="C20" t="n">
+        <v>2849155</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5020631</v>
+      </c>
+      <c r="E20" t="n">
         <v>2915041</v>
       </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
         <v>6004719</v>
-      </c>
-      <c r="E20" t="n">
-        <v>2511917</v>
-      </c>
-      <c r="F20" t="n">
-        <v>14883055</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -6345,29 +6345,29 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 595 千股)</t>
+          <t>📉 20d 巨變(減碼 -68 千股)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1022304</v>
+        <v>-289627</v>
       </c>
       <c r="D21" t="n">
-        <v>2910209</v>
+        <v>-1846112</v>
       </c>
       <c r="E21" t="n">
-        <v>798613</v>
+        <v>-166062</v>
       </c>
       <c r="F21" t="n">
-        <v>2315193</v>
+        <v>-1778232</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>崇越</t>
         </is>
       </c>
     </row>
@@ -6379,20 +6379,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -153 千股)</t>
+          <t>📈 20d 巨變(加碼 436 千股)</t>
         </is>
       </c>
       <c r="C22" t="n">
+        <v>440790</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-1782189</v>
+      </c>
+      <c r="E22" t="n">
         <v>703272</v>
       </c>
-      <c r="D22" t="n">
+      <c r="F22" t="n">
         <v>-2217971</v>
-      </c>
-      <c r="E22" t="n">
-        <v>566846</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-2065200</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -6403,116 +6403,116 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -261 千股)</t>
+          <t>📈 20d 巨變(加碼 60 千股)</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>89729</v>
+        <v>-221563</v>
       </c>
       <c r="D23" t="n">
-        <v>153609</v>
+        <v>-878585</v>
       </c>
       <c r="E23" t="n">
-        <v>432258</v>
+        <v>-217721</v>
       </c>
       <c r="F23" t="n">
-        <v>414413</v>
+        <v>-938268</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>大立光</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 160 千股)</t>
+          <t>📈 20d 巨變(加碼 807 千股)</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-217721</v>
+        <v>2807671</v>
       </c>
       <c r="D24" t="n">
-        <v>-938268</v>
+        <v>3717175</v>
       </c>
       <c r="E24" t="n">
-        <v>-460028</v>
+        <v>1022304</v>
       </c>
       <c r="F24" t="n">
-        <v>-1098182</v>
+        <v>2910209</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>中砂</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -428 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -440 千股)</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1252892</v>
+        <v>-320398</v>
       </c>
       <c r="D25" t="n">
-        <v>3164534</v>
+        <v>-286297</v>
       </c>
       <c r="E25" t="n">
-        <v>660823</v>
+        <v>89729</v>
       </c>
       <c r="F25" t="n">
-        <v>3592285</v>
+        <v>153609</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>建榮</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 12 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -1,812 千股)</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5858</v>
+        <v>-96513</v>
       </c>
       <c r="D26" t="n">
-        <v>47231</v>
+        <v>1352310</v>
       </c>
       <c r="E26" t="n">
-        <v>12780</v>
+        <v>1252892</v>
       </c>
       <c r="F26" t="n">
-        <v>35231</v>
+        <v>3164534</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>零壹</t>
         </is>
       </c>
     </row>
@@ -6524,20 +6524,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -9 千股)</t>
+          <t>📉 20d 巨變(減碼 -28 千股)</t>
         </is>
       </c>
       <c r="C27" t="n">
+        <v>25240</v>
+      </c>
+      <c r="D27" t="n">
+        <v>103239</v>
+      </c>
+      <c r="E27" t="n">
         <v>38293</v>
       </c>
-      <c r="D27" t="n">
+      <c r="F27" t="n">
         <v>131457</v>
-      </c>
-      <c r="E27" t="n">
-        <v>36584</v>
-      </c>
-      <c r="F27" t="n">
-        <v>140557</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -6548,145 +6548,145 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -208 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -23 千股)</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-525084</v>
+        <v>-5142</v>
       </c>
       <c r="D28" t="n">
-        <v>-922429</v>
+        <v>24231</v>
       </c>
       <c r="E28" t="n">
-        <v>-1019774</v>
+        <v>5858</v>
       </c>
       <c r="F28" t="n">
-        <v>-714000</v>
+        <v>47231</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>大車隊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -190 千股)</t>
+          <t>📈 20d 巨變(加碼 414 千股)</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-202994</v>
+        <v>-23630</v>
       </c>
       <c r="D29" t="n">
-        <v>-337555</v>
+        <v>-508392</v>
       </c>
       <c r="E29" t="n">
-        <v>-150994</v>
+        <v>-525084</v>
       </c>
       <c r="F29" t="n">
-        <v>-147555</v>
+        <v>-922429</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>湧德</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -577 千股)</t>
+          <t>📉 20d 巨變(減碼 -137 千股)</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-2328594</v>
+        <v>-387994</v>
       </c>
       <c r="D30" t="n">
-        <v>14518305</v>
+        <v>-474445</v>
       </c>
       <c r="E30" t="n">
-        <v>-2226169</v>
+        <v>-202994</v>
       </c>
       <c r="F30" t="n">
-        <v>15095122</v>
+        <v>-337555</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>隆大</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 354 千股)</t>
+          <t>📈 20d 巨變(加碼 469 千股)</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>400307</v>
+        <v>-1858027</v>
       </c>
       <c r="D31" t="n">
-        <v>200001</v>
+        <v>14987241</v>
       </c>
       <c r="E31" t="n">
-        <v>199616</v>
+        <v>-2328594</v>
       </c>
       <c r="F31" t="n">
-        <v>-154109</v>
+        <v>14518305</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 10,468 千股)</t>
+          <t>📉 20d 巨變(減碼 -57 千股)</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-2309475</v>
+        <v>136326</v>
       </c>
       <c r="D32" t="n">
-        <v>52146302</v>
+        <v>142991</v>
       </c>
       <c r="E32" t="n">
-        <v>10300087</v>
+        <v>400307</v>
       </c>
       <c r="F32" t="n">
-        <v>41678122</v>
+        <v>200001</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>卜蜂</t>
         </is>
       </c>
     </row>
@@ -6698,20 +6698,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -82 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,076 千股)</t>
         </is>
       </c>
       <c r="C33" t="n">
+        <v>189351</v>
+      </c>
+      <c r="D33" t="n">
+        <v>300791</v>
+      </c>
+      <c r="E33" t="n">
         <v>128011</v>
       </c>
-      <c r="D33" t="n">
+      <c r="F33" t="n">
         <v>1376580</v>
-      </c>
-      <c r="E33" t="n">
-        <v>163857</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1459035</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -6722,348 +6722,348 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 5,059 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 24,163 千股)</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1167329</v>
+        <v>8196467</v>
       </c>
       <c r="D34" t="n">
-        <v>-27012390</v>
+        <v>76309054</v>
       </c>
       <c r="E34" t="n">
-        <v>-2484187</v>
+        <v>-2309475</v>
       </c>
       <c r="F34" t="n">
-        <v>-32071263</v>
+        <v>52146302</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -27 千股)</t>
+          <t>📈 20d 巨變(加碼 7,562 千股)</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>122250</v>
+        <v>2289845</v>
       </c>
       <c r="D35" t="n">
-        <v>379221</v>
+        <v>-19450013</v>
       </c>
       <c r="E35" t="n">
-        <v>146954</v>
+        <v>1167329</v>
       </c>
       <c r="F35" t="n">
-        <v>406337</v>
+        <v>-27012390</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>寶雅*</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -251 千股)</t>
+          <t>📈 20d 巨變(加碼 20 千股)</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-323860</v>
+        <v>23077</v>
       </c>
       <c r="D36" t="n">
-        <v>63046</v>
+        <v>399190</v>
       </c>
       <c r="E36" t="n">
-        <v>-278003</v>
+        <v>122250</v>
       </c>
       <c r="F36" t="n">
-        <v>314296</v>
+        <v>379221</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>大統益</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 63 千股)</t>
+          <t>📈 20d 巨變(加碼 181 千股)</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-150071</v>
+        <v>-341652</v>
       </c>
       <c r="D37" t="n">
-        <v>-534926</v>
+        <v>244040</v>
       </c>
       <c r="E37" t="n">
-        <v>-170932</v>
+        <v>-323860</v>
       </c>
       <c r="F37" t="n">
-        <v>-597866</v>
+        <v>63046</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>豐藝</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -137 千股)</t>
+          <t>📈 20d 巨變(加碼 12 千股)</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-143295</v>
+        <v>-125845</v>
       </c>
       <c r="D38" t="n">
-        <v>-51670</v>
+        <v>-522513</v>
       </c>
       <c r="E38" t="n">
-        <v>-96345</v>
+        <v>-150071</v>
       </c>
       <c r="F38" t="n">
-        <v>85431</v>
+        <v>-534926</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>智冠</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -141 千股)</t>
+          <t>📈 20d 巨變(加碼 72 千股)</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-556359</v>
+        <v>-43361</v>
       </c>
       <c r="D39" t="n">
-        <v>-134280</v>
+        <v>366611</v>
       </c>
       <c r="E39" t="n">
-        <v>-698871</v>
+        <v>-80511</v>
       </c>
       <c r="F39" t="n">
-        <v>6727</v>
+        <v>294481</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>八方雲集</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 112 千股)</t>
+          <t>📉 20d 巨變(減碼 -53 千股)</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-80511</v>
+        <v>-118250</v>
       </c>
       <c r="D40" t="n">
-        <v>294481</v>
+        <v>-104203</v>
       </c>
       <c r="E40" t="n">
-        <v>-114479</v>
+        <v>-143295</v>
       </c>
       <c r="F40" t="n">
-        <v>182481</v>
+        <v>-51670</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>華景電</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 8,066 千股)</t>
+          <t>📉 20d 巨變(減碼 -358 千股)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>10305477</v>
+        <v>-341000</v>
       </c>
       <c r="D41" t="n">
-        <v>89724532</v>
+        <v>-491807</v>
       </c>
       <c r="E41" t="n">
-        <v>17477662</v>
+        <v>-556359</v>
       </c>
       <c r="F41" t="n">
-        <v>81658966</v>
+        <v>-134280</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>穎崴</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -6 千股)</t>
+          <t>📈 20d 巨變(加碼 4,795 千股)</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-331000</v>
+        <v>10985380</v>
       </c>
       <c r="D42" t="n">
-        <v>-1032635</v>
+        <v>94519818</v>
       </c>
       <c r="E42" t="n">
-        <v>-513000</v>
+        <v>10305477</v>
       </c>
       <c r="F42" t="n">
-        <v>-1026635</v>
+        <v>89724532</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 812 千股)</t>
+          <t>📉 20d 巨變(減碼 -62 千股)</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-176658</v>
+        <v>-370000</v>
       </c>
       <c r="D43" t="n">
-        <v>5389484</v>
+        <v>-1094333</v>
       </c>
       <c r="E43" t="n">
-        <v>-199897</v>
+        <v>-331000</v>
       </c>
       <c r="F43" t="n">
-        <v>4577392</v>
+        <v>-1032635</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>聯合</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -175 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 1,215 千股)</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>922146</v>
+        <v>237004</v>
       </c>
       <c r="D44" t="n">
-        <v>-499360</v>
+        <v>6604004</v>
       </c>
       <c r="E44" t="n">
-        <v>668304</v>
+        <v>-176658</v>
       </c>
       <c r="F44" t="n">
-        <v>-324839</v>
+        <v>5389484</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -186 千股)</t>
+          <t>📈 20d 巨變(加碼 40 千股)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>277912</v>
+        <v>539287</v>
       </c>
       <c r="D45" t="n">
-        <v>509718</v>
+        <v>-459547</v>
       </c>
       <c r="E45" t="n">
-        <v>172092</v>
+        <v>922146</v>
       </c>
       <c r="F45" t="n">
-        <v>695732</v>
+        <v>-499360</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>亞力</t>
         </is>
       </c>
     </row>
@@ -7075,20 +7075,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 50 千股)</t>
+          <t>📈 20d 巨變(加碼 111 千股)</t>
         </is>
       </c>
       <c r="C46" t="n">
+        <v>117620</v>
+      </c>
+      <c r="D46" t="n">
+        <v>-390098</v>
+      </c>
+      <c r="E46" t="n">
         <v>110379</v>
       </c>
-      <c r="D46" t="n">
+      <c r="F46" t="n">
         <v>-501339</v>
-      </c>
-      <c r="E46" t="n">
-        <v>103499</v>
-      </c>
-      <c r="F46" t="n">
-        <v>-551219</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -7099,87 +7099,87 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 691 千股)</t>
+          <t>📉 20d 巨變(減碼 -8 千股)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3883222</v>
+        <v>123187</v>
       </c>
       <c r="D47" t="n">
-        <v>362528</v>
+        <v>501327</v>
       </c>
       <c r="E47" t="n">
-        <v>3754109</v>
+        <v>277912</v>
       </c>
       <c r="F47" t="n">
-        <v>-328386</v>
+        <v>509718</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>大綜</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,629 千股)</t>
+          <t>📈 20d 巨變(加碼 628 千股)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2349962</v>
+        <v>3694404</v>
       </c>
       <c r="D48" t="n">
-        <v>3426406</v>
+        <v>990413</v>
       </c>
       <c r="E48" t="n">
-        <v>1774196</v>
+        <v>3883222</v>
       </c>
       <c r="F48" t="n">
-        <v>797686</v>
+        <v>362528</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>台燿</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,039 千股)</t>
+          <t>📈 20d 巨變(加碼 786 千股)</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-2961909</v>
+        <v>2172040</v>
       </c>
       <c r="D49" t="n">
-        <v>109850</v>
+        <v>4212847</v>
       </c>
       <c r="E49" t="n">
-        <v>-512511</v>
+        <v>2349962</v>
       </c>
       <c r="F49" t="n">
-        <v>1148880</v>
+        <v>3426406</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>立隆電</t>
         </is>
       </c>
     </row>
@@ -7191,20 +7191,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -3,053 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -1,895 千股)</t>
         </is>
       </c>
       <c r="C50" t="n">
+        <v>-316461</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1492025</v>
+      </c>
+      <c r="E50" t="n">
         <v>12359</v>
       </c>
-      <c r="D50" t="n">
+      <c r="F50" t="n">
         <v>3386702</v>
-      </c>
-      <c r="E50" t="n">
-        <v>-2523012</v>
-      </c>
-      <c r="F50" t="n">
-        <v>6439924</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -7215,377 +7215,377 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -599 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,818 千股)</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-617526</v>
+        <v>-4812156</v>
       </c>
       <c r="D51" t="n">
-        <v>-546190</v>
+        <v>-1708334</v>
       </c>
       <c r="E51" t="n">
-        <v>-749016</v>
+        <v>-2961909</v>
       </c>
       <c r="F51" t="n">
-        <v>52803</v>
+        <v>109850</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>玉晶光</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -6,710 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,746 千股)</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>18470978</v>
+        <v>-2803263</v>
       </c>
       <c r="D52" t="n">
-        <v>-43649480</v>
+        <v>-3292463</v>
       </c>
       <c r="E52" t="n">
-        <v>15777966</v>
+        <v>-617526</v>
       </c>
       <c r="F52" t="n">
-        <v>-36939548</v>
+        <v>-546190</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>世芯-KY</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -45,251 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 16,703 千股)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>41493231</v>
+        <v>-5641323</v>
       </c>
       <c r="D53" t="n">
-        <v>20273872</v>
+        <v>-26946699</v>
       </c>
       <c r="E53" t="n">
-        <v>9603953</v>
+        <v>18470978</v>
       </c>
       <c r="F53" t="n">
-        <v>65524882</v>
+        <v>-43649480</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 9 千股)</t>
+          <t>📉 20d 巨變(減碼 -3,076 千股)</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>30496334</v>
+        <v>27960674</v>
       </c>
       <c r="D54" t="n">
-        <v>51927884</v>
+        <v>17197528</v>
       </c>
       <c r="E54" t="n">
-        <v>29213823</v>
+        <v>41493231</v>
       </c>
       <c r="F54" t="n">
-        <v>51919009</v>
+        <v>20273872</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 204 千股)</t>
+          <t>📉 20d 巨變(減碼 -11,070 千股)</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1813519</v>
+        <v>26025516</v>
       </c>
       <c r="D55" t="n">
-        <v>3330020</v>
+        <v>40857502</v>
       </c>
       <c r="E55" t="n">
-        <v>946685</v>
+        <v>30496334</v>
       </c>
       <c r="F55" t="n">
-        <v>3126491</v>
+        <v>51927884</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 186 千股)</t>
+          <t>📉 20d 巨變(減碼 -642 千股)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>67521</v>
+        <v>-1699437</v>
       </c>
       <c r="D56" t="n">
-        <v>387220</v>
+        <v>2317442</v>
       </c>
       <c r="E56" t="n">
-        <v>-28148</v>
+        <v>-864969</v>
       </c>
       <c r="F56" t="n">
-        <v>200756</v>
+        <v>2959291</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>鈊象</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 390 千股)</t>
+          <t>📉 20d 巨變(減碼 -324 千股)</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-864969</v>
+        <v>1079565</v>
       </c>
       <c r="D57" t="n">
-        <v>2959291</v>
+        <v>3006460</v>
       </c>
       <c r="E57" t="n">
-        <v>-752787</v>
+        <v>1813519</v>
       </c>
       <c r="F57" t="n">
-        <v>2568888</v>
+        <v>3330020</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>士電</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 927 千股)</t>
+          <t>📉 20d 巨變(減碼 -24 千股)</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-1000103</v>
+        <v>20257</v>
       </c>
       <c r="D58" t="n">
-        <v>-3720146</v>
+        <v>362864</v>
       </c>
       <c r="E58" t="n">
-        <v>-748438</v>
+        <v>67521</v>
       </c>
       <c r="F58" t="n">
-        <v>-4647256</v>
+        <v>387220</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>達欣工</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -102 千股)</t>
+          <t>📈 20d 巨變(加碼 563 千股)</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-129339</v>
+        <v>-735694</v>
       </c>
       <c r="D59" t="n">
-        <v>490182</v>
+        <v>-3156755</v>
       </c>
       <c r="E59" t="n">
-        <v>-111650</v>
+        <v>-1000103</v>
       </c>
       <c r="F59" t="n">
-        <v>592315</v>
+        <v>-3720146</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>鉅祥</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -38 千股)</t>
+          <t>📉 20d 巨變(減碼 -27 千股)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>324099</v>
+        <v>-162311</v>
       </c>
       <c r="D60" t="n">
-        <v>-1364376</v>
+        <v>463056</v>
       </c>
       <c r="E60" t="n">
-        <v>108836</v>
+        <v>-129339</v>
       </c>
       <c r="F60" t="n">
-        <v>-1326376</v>
+        <v>490182</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>普萊德</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 28 千股)</t>
+          <t>📉 20d 巨變(減碼 -84 千股)</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-395584</v>
+        <v>237681</v>
       </c>
       <c r="D61" t="n">
-        <v>-205907</v>
+        <v>-1448320</v>
       </c>
       <c r="E61" t="n">
-        <v>-333842</v>
+        <v>324099</v>
       </c>
       <c r="F61" t="n">
-        <v>-233937</v>
+        <v>-1364376</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>勝一</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,552 千股)</t>
+          <t>📉 20d 巨變(減碼 -72 千股)</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-2000662</v>
+        <v>-59666</v>
       </c>
       <c r="D62" t="n">
-        <v>-4071005</v>
+        <v>-543061</v>
       </c>
       <c r="E62" t="n">
-        <v>-1581460</v>
+        <v>-89346</v>
       </c>
       <c r="F62" t="n">
-        <v>-5622571</v>
+        <v>-471097</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 50 千股)</t>
+          <t>📈 20d 巨變(加碼 122 千股)</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-876670</v>
+        <v>-371745</v>
       </c>
       <c r="D63" t="n">
-        <v>-3599703</v>
+        <v>-84178</v>
       </c>
       <c r="E63" t="n">
-        <v>-507222</v>
+        <v>-395584</v>
       </c>
       <c r="F63" t="n">
-        <v>-3649526</v>
+        <v>-205907</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>祥碩</t>
         </is>
       </c>
     </row>
@@ -7597,20 +7597,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -447 千股)</t>
+          <t>📈 20d 巨變(加碼 341 千股)</t>
         </is>
       </c>
       <c r="C64" t="n">
+        <v>-406723</v>
+      </c>
+      <c r="D64" t="n">
+        <v>-1083994</v>
+      </c>
+      <c r="E64" t="n">
         <v>-571217</v>
       </c>
-      <c r="D64" t="n">
+      <c r="F64" t="n">
         <v>-1424794</v>
-      </c>
-      <c r="E64" t="n">
-        <v>-565638</v>
-      </c>
-      <c r="F64" t="n">
-        <v>-978181</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -7621,754 +7621,754 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -364 千股)</t>
+          <t>📉 20d 巨變(減碼 -701 千股)</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-89346</v>
+        <v>-375023</v>
       </c>
       <c r="D65" t="n">
-        <v>-471097</v>
+        <v>-4301050</v>
       </c>
       <c r="E65" t="n">
-        <v>-114945</v>
+        <v>-876670</v>
       </c>
       <c r="F65" t="n">
-        <v>-107404</v>
+        <v>-3599703</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,303 千股)</t>
+          <t>📈 20d 巨變(加碼 100 千股)</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-731238</v>
+        <v>-2905006</v>
       </c>
       <c r="D66" t="n">
-        <v>866006</v>
+        <v>-3971344</v>
       </c>
       <c r="E66" t="n">
-        <v>-88221</v>
+        <v>-2000662</v>
       </c>
       <c r="F66" t="n">
-        <v>2168928</v>
+        <v>-4071005</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>華星光</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -148 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 33 千股)</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-1329359</v>
+        <v>-72098</v>
       </c>
       <c r="D67" t="n">
-        <v>-1759709</v>
+        <v>-533829</v>
       </c>
       <c r="E67" t="n">
-        <v>-1363305</v>
+        <v>554408</v>
       </c>
       <c r="F67" t="n">
-        <v>-1611587</v>
+        <v>-566816</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>聯亞</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,968 千股)</t>
+          <t>📉 20d 巨變(減碼 -564 千股)</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>10214227</v>
+        <v>-885577</v>
       </c>
       <c r="D68" t="n">
-        <v>39976020</v>
+        <v>302106</v>
       </c>
       <c r="E68" t="n">
-        <v>15496741</v>
+        <v>-731238</v>
       </c>
       <c r="F68" t="n">
-        <v>37008415</v>
+        <v>866006</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -79 千股)</t>
+          <t>📈 20d 巨變(加碼 1,167 千股)</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>554408</v>
+        <v>-1078273</v>
       </c>
       <c r="D69" t="n">
-        <v>-566816</v>
+        <v>-592447</v>
       </c>
       <c r="E69" t="n">
-        <v>1343193</v>
+        <v>-1329359</v>
       </c>
       <c r="F69" t="n">
-        <v>-487442</v>
+        <v>-1759709</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>宇瞻</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -44,080 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -5,968 千股)</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-60119017</v>
+        <v>-1956622</v>
       </c>
       <c r="D70" t="n">
-        <v>-107603778</v>
+        <v>34007934</v>
       </c>
       <c r="E70" t="n">
-        <v>-23602047</v>
+        <v>10214227</v>
       </c>
       <c r="F70" t="n">
-        <v>-63523914</v>
+        <v>39976020</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -12,239 千股)</t>
+          <t>📈 20d 巨變(加碼 985 千股)</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-6937120</v>
+        <v>1754411</v>
       </c>
       <c r="D71" t="n">
-        <v>-12919781</v>
+        <v>-2159820</v>
       </c>
       <c r="E71" t="n">
-        <v>-13416646</v>
+        <v>959066</v>
       </c>
       <c r="F71" t="n">
-        <v>-680897</v>
+        <v>-3144835</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 737 千股)</t>
+          <t>📈 20d 巨變(加碼 3,815 千股)</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>959066</v>
+        <v>-80785282</v>
       </c>
       <c r="D72" t="n">
-        <v>-3144835</v>
+        <v>-103788976</v>
       </c>
       <c r="E72" t="n">
-        <v>-1098737</v>
+        <v>-60119017</v>
       </c>
       <c r="F72" t="n">
-        <v>-3882056</v>
+        <v>-107603778</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,946 千股)</t>
+          <t>📈 20d 巨變(加碼 680 千股)</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-4170843</v>
+        <v>-12413589</v>
       </c>
       <c r="D73" t="n">
-        <v>-4201007</v>
+        <v>-12240223</v>
       </c>
       <c r="E73" t="n">
-        <v>-587726</v>
+        <v>-6937120</v>
       </c>
       <c r="F73" t="n">
-        <v>-1254521</v>
+        <v>-12919781</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -21 千股)</t>
+          <t>📉 20d 巨變(減碼 -11 千股)</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>9000</v>
+        <v>-26454</v>
       </c>
       <c r="D74" t="n">
-        <v>-109550</v>
+        <v>-201203</v>
       </c>
       <c r="E74" t="n">
-        <v>-5000</v>
+        <v>-60828</v>
       </c>
       <c r="F74" t="n">
-        <v>-88550</v>
+        <v>-190071</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>德昌</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 62 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,371 千股)</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>467993</v>
+        <v>-5728973</v>
       </c>
       <c r="D75" t="n">
-        <v>634546</v>
+        <v>-5572346</v>
       </c>
       <c r="E75" t="n">
-        <v>497518</v>
+        <v>-4170843</v>
       </c>
       <c r="F75" t="n">
-        <v>572146</v>
+        <v>-4201007</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 109 千股)</t>
+          <t>📈 20d 巨變(加碼 81 千股)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-60828</v>
+        <v>376060</v>
       </c>
       <c r="D76" t="n">
-        <v>-190071</v>
+        <v>715596</v>
       </c>
       <c r="E76" t="n">
-        <v>-189796</v>
+        <v>467993</v>
       </c>
       <c r="F76" t="n">
-        <v>-299023</v>
+        <v>634546</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>億泰</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 785 千股)</t>
+          <t>📈 20d 巨變(加碼 39 千股)</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-1818692</v>
+        <v>33000</v>
       </c>
       <c r="D77" t="n">
-        <v>-11058748</v>
+        <v>-70550</v>
       </c>
       <c r="E77" t="n">
-        <v>-2334015</v>
+        <v>9000</v>
       </c>
       <c r="F77" t="n">
-        <v>-11843509</v>
+        <v>-109550</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>友輝</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -21 千股)</t>
+          <t>📈 20d 巨變(加碼 838 千股)</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-1452966</v>
+        <v>-1759434</v>
       </c>
       <c r="D78" t="n">
-        <v>-3021480</v>
+        <v>-10220401</v>
       </c>
       <c r="E78" t="n">
-        <v>-1433974</v>
+        <v>-1818692</v>
       </c>
       <c r="F78" t="n">
-        <v>-3000660</v>
+        <v>-11058748</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>智易</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,105 千股)</t>
+          <t>📈 20d 巨變(加碼 29 千股)</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-513211</v>
+        <v>-1441098</v>
       </c>
       <c r="D79" t="n">
-        <v>1042911</v>
+        <v>-2992140</v>
       </c>
       <c r="E79" t="n">
-        <v>-7912</v>
+        <v>-1452966</v>
       </c>
       <c r="F79" t="n">
-        <v>-62552</v>
+        <v>-3021480</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>原相</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -13 千股)</t>
+          <t>📉 20d 巨變(減碼 -773 千股)</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-887855</v>
+        <v>-2012472</v>
       </c>
       <c r="D80" t="n">
-        <v>-2446814</v>
+        <v>270205</v>
       </c>
       <c r="E80" t="n">
-        <v>-1488563</v>
+        <v>-513211</v>
       </c>
       <c r="F80" t="n">
-        <v>-2433695</v>
+        <v>1042911</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -14,040 千股)</t>
+          <t>📈 20d 巨變(加碼 290 千股)</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-16437846</v>
+        <v>-116797</v>
       </c>
       <c r="D81" t="n">
-        <v>-3702035</v>
+        <v>-2156849</v>
       </c>
       <c r="E81" t="n">
-        <v>-8760496</v>
+        <v>-887855</v>
       </c>
       <c r="F81" t="n">
-        <v>10338271</v>
+        <v>-2446814</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>精測</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 29,968 千股)</t>
+          <t>📉 20d 巨變(減碼 -14,829 千股)</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>10246775</v>
+        <v>-29474185</v>
       </c>
       <c r="D82" t="n">
-        <v>-28231647</v>
+        <v>-18531211</v>
       </c>
       <c r="E82" t="n">
-        <v>11319063</v>
+        <v>-16437846</v>
       </c>
       <c r="F82" t="n">
-        <v>-58199679</v>
+        <v>-3702035</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -5 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -6,823 千股)</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-641485</v>
+        <v>-19911926</v>
       </c>
       <c r="D83" t="n">
-        <v>-824993</v>
+        <v>-35054452</v>
       </c>
       <c r="E83" t="n">
-        <v>-990771</v>
+        <v>10246775</v>
       </c>
       <c r="F83" t="n">
-        <v>-819771</v>
+        <v>-28231647</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 228 千股)</t>
+          <t>📈 20d 巨變(加碼 215 千股)</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>64521</v>
+        <v>-699308</v>
       </c>
       <c r="D84" t="n">
-        <v>147169</v>
+        <v>-610093</v>
       </c>
       <c r="E84" t="n">
-        <v>17521</v>
+        <v>-641485</v>
       </c>
       <c r="F84" t="n">
-        <v>-80541</v>
+        <v>-824993</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 36 千股)</t>
+          <t>📈 20d 巨變(加碼 213 千股)</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>35746</v>
+        <v>362421</v>
       </c>
       <c r="D85" t="n">
-        <v>488009</v>
+        <v>360169</v>
       </c>
       <c r="E85" t="n">
-        <v>63746</v>
+        <v>64521</v>
       </c>
       <c r="F85" t="n">
-        <v>452009</v>
+        <v>147169</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>東科-KY</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -535 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -49 千股)</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-399669</v>
+        <v>-94019</v>
       </c>
       <c r="D86" t="n">
-        <v>-3245178</v>
+        <v>439009</v>
       </c>
       <c r="E86" t="n">
-        <v>-2910038</v>
+        <v>35746</v>
       </c>
       <c r="F86" t="n">
-        <v>-2709843</v>
+        <v>488009</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,265 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 2,703 千股)</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-3066027</v>
+        <v>1661861</v>
       </c>
       <c r="D87" t="n">
-        <v>-18402957</v>
+        <v>-542475</v>
       </c>
       <c r="E87" t="n">
-        <v>-3075660</v>
+        <v>-399669</v>
       </c>
       <c r="F87" t="n">
-        <v>-17138076</v>
+        <v>-3245178</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 362 千股)</t>
+          <t>📈 20d 巨變(加碼 11 千股)</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-456573</v>
+        <v>-2533523</v>
       </c>
       <c r="D88" t="n">
-        <v>-316208</v>
+        <v>-18392310</v>
       </c>
       <c r="E88" t="n">
-        <v>-676339</v>
+        <v>-3066027</v>
       </c>
       <c r="F88" t="n">
-        <v>-677947</v>
+        <v>-18402957</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>宏捷科</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 5,881 千股)</t>
+          <t>📈 20d 巨變(加碼 290 千股)</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>16846399</v>
+        <v>-581347</v>
       </c>
       <c r="D89" t="n">
-        <v>12762927</v>
+        <v>-26443</v>
       </c>
       <c r="E89" t="n">
-        <v>18164850</v>
+        <v>-456573</v>
       </c>
       <c r="F89" t="n">
-        <v>6881877</v>
+        <v>-316208</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>研華</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -39 千股)</t>
+          <t>📈 20d 巨變(加碼 14,199 千股)</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-87942</v>
+        <v>25199166</v>
       </c>
       <c r="D90" t="n">
-        <v>168476</v>
+        <v>26962211</v>
       </c>
       <c r="E90" t="n">
-        <v>-94175</v>
+        <v>16846399</v>
       </c>
       <c r="F90" t="n">
-        <v>207576</v>
+        <v>12762927</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
@@ -8380,20 +8380,20 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 31 千股)</t>
+          <t>📈 20d 巨變(加碼 2,820 千股)</t>
         </is>
       </c>
       <c r="C91" t="n">
+        <v>-723700</v>
+      </c>
+      <c r="D91" t="n">
+        <v>-14302501</v>
+      </c>
+      <c r="E91" t="n">
         <v>-667302</v>
       </c>
-      <c r="D91" t="n">
+      <c r="F91" t="n">
         <v>-17122012</v>
-      </c>
-      <c r="E91" t="n">
-        <v>-1178298</v>
-      </c>
-      <c r="F91" t="n">
-        <v>-17152916</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -8404,174 +8404,174 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -23 千股)</t>
+          <t>📉 20d 巨變(減碼 -140 千股)</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>43226</v>
+        <v>3157335</v>
       </c>
       <c r="D92" t="n">
-        <v>-3182</v>
+        <v>24329068</v>
       </c>
       <c r="E92" t="n">
-        <v>95271</v>
+        <v>2751780</v>
       </c>
       <c r="F92" t="n">
-        <v>19866</v>
+        <v>24468891</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -23 千股)</t>
+          <t>📈 20d 巨變(加碼 99 千股)</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-11153</v>
+        <v>135934</v>
       </c>
       <c r="D93" t="n">
-        <v>29502</v>
+        <v>95526</v>
       </c>
       <c r="E93" t="n">
-        <v>-22728</v>
+        <v>43226</v>
       </c>
       <c r="F93" t="n">
-        <v>52507</v>
+        <v>-3182</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>竹陞科技</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -39 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 114 千股)</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-93269</v>
+        <v>99860</v>
       </c>
       <c r="D94" t="n">
-        <v>-70045</v>
+        <v>143635</v>
       </c>
       <c r="E94" t="n">
-        <v>-12269</v>
+        <v>-11153</v>
       </c>
       <c r="F94" t="n">
-        <v>-31045</v>
+        <v>29502</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>安碁資訊</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -18,040 千股)</t>
+          <t>📉 20d 巨變(減碼 -27 千股)</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>81759531</v>
+        <v>-115412</v>
       </c>
       <c r="D95" t="n">
-        <v>115574939</v>
+        <v>-97045</v>
       </c>
       <c r="E95" t="n">
-        <v>60610861</v>
+        <v>-93269</v>
       </c>
       <c r="F95" t="n">
-        <v>133615313</v>
+        <v>-70045</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>六方科-KY</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,429 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,237 千股)</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2751780</v>
+        <v>3401305</v>
       </c>
       <c r="D96" t="n">
-        <v>24468891</v>
+        <v>5537305</v>
       </c>
       <c r="E96" t="n">
-        <v>4283220</v>
+        <v>4677849</v>
       </c>
       <c r="F96" t="n">
-        <v>22040188</v>
+        <v>7774312</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,043 千股)</t>
+          <t>📉 20d 巨變(減碼 -87,069 千股)</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>4677849</v>
+        <v>45227120</v>
       </c>
       <c r="D97" t="n">
-        <v>7774312</v>
+        <v>28506329</v>
       </c>
       <c r="E97" t="n">
-        <v>4133229</v>
+        <v>81759531</v>
       </c>
       <c r="F97" t="n">
-        <v>9817592</v>
+        <v>115574939</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
@@ -8583,20 +8583,20 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 173 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -374 千股)</t>
         </is>
       </c>
       <c r="C98" t="n">
+        <v>-52278</v>
+      </c>
+      <c r="D98" t="n">
+        <v>1229728</v>
+      </c>
+      <c r="E98" t="n">
         <v>178278</v>
       </c>
-      <c r="D98" t="n">
+      <c r="F98" t="n">
         <v>1604115</v>
-      </c>
-      <c r="E98" t="n">
-        <v>123782</v>
-      </c>
-      <c r="F98" t="n">
-        <v>1430631</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -8612,20 +8612,20 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -510 千股)</t>
+          <t>📉 20d 巨變(減碼 -524 千股)</t>
         </is>
       </c>
       <c r="C99" t="n">
+        <v>-1985731</v>
+      </c>
+      <c r="D99" t="n">
+        <v>-9125837</v>
+      </c>
+      <c r="E99" t="n">
         <v>-1917531</v>
       </c>
-      <c r="D99" t="n">
+      <c r="F99" t="n">
         <v>-8602098</v>
-      </c>
-      <c r="E99" t="n">
-        <v>-3312027</v>
-      </c>
-      <c r="F99" t="n">
-        <v>-8092008</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -8636,116 +8636,116 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,441 千股)</t>
+          <t>📉 20d 巨變(減碼 -70 千股)</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-3766557</v>
+        <v>151301</v>
       </c>
       <c r="D100" t="n">
-        <v>-12748994</v>
+        <v>269458</v>
       </c>
       <c r="E100" t="n">
-        <v>-1674662</v>
+        <v>158382</v>
       </c>
       <c r="F100" t="n">
-        <v>-15190447</v>
+        <v>339602</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>信驊</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 363 千股)</t>
+          <t>📈 20d 巨變(加碼 3,006 千股)</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>909</v>
+        <v>-611183</v>
       </c>
       <c r="D101" t="n">
-        <v>-4500046</v>
+        <v>-9742886</v>
       </c>
       <c r="E101" t="n">
-        <v>465611</v>
+        <v>-3766557</v>
       </c>
       <c r="F101" t="n">
-        <v>-4862828</v>
+        <v>-12748994</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>金像電</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 60 千股)</t>
+          <t>📉 20d 巨變(減碼 -33 千股)</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>158382</v>
+        <v>-224865</v>
       </c>
       <c r="D102" t="n">
-        <v>339602</v>
+        <v>-1360822</v>
       </c>
       <c r="E102" t="n">
-        <v>81741</v>
+        <v>-535050</v>
       </c>
       <c r="F102" t="n">
-        <v>279756</v>
+        <v>-1328176</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>萬潤</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -888 千股)</t>
+          <t>📈 20d 巨變(加碼 1,190 千股)</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-535050</v>
+        <v>392272</v>
       </c>
       <c r="D103" t="n">
-        <v>-1328176</v>
+        <v>-3310295</v>
       </c>
       <c r="E103" t="n">
-        <v>-646292</v>
+        <v>909</v>
       </c>
       <c r="F103" t="n">
-        <v>-440577</v>
+        <v>-4500046</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>高技</t>
         </is>
       </c>
     </row>

--- a/data/台股_外資雷達.xlsx
+++ b/data/台股_外資雷達.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10985</v>
+        <v>12549</v>
       </c>
       <c r="D2" t="n">
-        <v>94520</v>
+        <v>86798</v>
       </c>
       <c r="E2" t="n">
-        <v>162919</v>
+        <v>173821</v>
       </c>
       <c r="F2" t="n">
-        <v>960</v>
+        <v>855</v>
       </c>
       <c r="G2" t="n">
-        <v>5424</v>
+        <v>6190</v>
       </c>
       <c r="H2" t="n">
-        <v>-3532</v>
+        <v>-3278</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -547,22 +547,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8196</v>
+        <v>13309</v>
       </c>
       <c r="D3" t="n">
-        <v>76309</v>
+        <v>53815</v>
       </c>
       <c r="E3" t="n">
-        <v>542316</v>
+        <v>567203</v>
       </c>
       <c r="F3" t="n">
-        <v>2110</v>
+        <v>-368</v>
       </c>
       <c r="G3" t="n">
-        <v>11694</v>
+        <v>11511</v>
       </c>
       <c r="H3" t="n">
-        <v>-3215</v>
+        <v>-4841</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -589,31 +589,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26026</v>
+        <v>36089</v>
       </c>
       <c r="D4" t="n">
-        <v>40858</v>
+        <v>40298</v>
       </c>
       <c r="E4" t="n">
-        <v>-34455</v>
+        <v>92307</v>
       </c>
       <c r="F4" t="n">
-        <v>-136</v>
+        <v>593</v>
       </c>
       <c r="G4" t="n">
-        <v>-27075</v>
+        <v>5269</v>
       </c>
       <c r="H4" t="n">
-        <v>1310</v>
+        <v>-356</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -622,49 +622,49 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>🐌 龜速*</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-1957</v>
+        <v>7662</v>
       </c>
       <c r="D5" t="n">
-        <v>34008</v>
+        <v>31195</v>
       </c>
       <c r="E5" t="n">
-        <v>-19149</v>
+        <v>-36401</v>
       </c>
       <c r="F5" t="n">
-        <v>1326</v>
+        <v>396</v>
       </c>
       <c r="G5" t="n">
-        <v>7169</v>
+        <v>-21363</v>
       </c>
       <c r="H5" t="n">
-        <v>-435</v>
+        <v>890</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -677,45 +677,45 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速*</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>45227</v>
+        <v>-1029</v>
       </c>
       <c r="D6" t="n">
-        <v>28506</v>
+        <v>28783</v>
       </c>
       <c r="E6" t="n">
-        <v>45849</v>
+        <v>-20960</v>
       </c>
       <c r="F6" t="n">
-        <v>-142</v>
+        <v>499</v>
       </c>
       <c r="G6" t="n">
-        <v>-40197</v>
+        <v>7994</v>
       </c>
       <c r="H6" t="n">
-        <v>-7784</v>
+        <v>-460</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -724,49 +724,49 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>25199</v>
+        <v>5299</v>
       </c>
       <c r="D7" t="n">
-        <v>26962</v>
+        <v>23279</v>
       </c>
       <c r="E7" t="n">
-        <v>73131</v>
+        <v>75504</v>
       </c>
       <c r="F7" t="n">
-        <v>507</v>
+        <v>1018</v>
       </c>
       <c r="G7" t="n">
-        <v>7295</v>
+        <v>-1385</v>
       </c>
       <c r="H7" t="n">
-        <v>24</v>
+        <v>-1014</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -775,11 +775,11 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -787,37 +787,37 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3157</v>
+        <v>594</v>
       </c>
       <c r="D8" t="n">
-        <v>24329</v>
+        <v>15236</v>
       </c>
       <c r="E8" t="n">
-        <v>66867</v>
+        <v>23099</v>
       </c>
       <c r="F8" t="n">
-        <v>1008</v>
+        <v>-111</v>
       </c>
       <c r="G8" t="n">
-        <v>-2618</v>
+        <v>91</v>
       </c>
       <c r="H8" t="n">
-        <v>-1025</v>
+        <v>48</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -826,11 +826,11 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -838,101 +838,101 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>27961</v>
+        <v>-156</v>
       </c>
       <c r="D9" t="n">
-        <v>17198</v>
+        <v>9445</v>
       </c>
       <c r="E9" t="n">
-        <v>65242</v>
+        <v>11819</v>
       </c>
       <c r="F9" t="n">
-        <v>-183</v>
+        <v>-681</v>
       </c>
       <c r="G9" t="n">
-        <v>-3663</v>
+        <v>903</v>
       </c>
       <c r="H9" t="n">
-        <v>-4078</v>
+        <v>762</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>🚀 大買</t>
+          <t>🟢 加碼</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-1858</v>
+        <v>1296</v>
       </c>
       <c r="D10" t="n">
-        <v>14987</v>
+        <v>6944</v>
       </c>
       <c r="E10" t="n">
-        <v>23678</v>
+        <v>14669</v>
       </c>
       <c r="F10" t="n">
-        <v>-83</v>
+        <v>-10</v>
       </c>
       <c r="G10" t="n">
-        <v>110</v>
+        <v>-1168</v>
       </c>
       <c r="H10" t="n">
-        <v>221</v>
+        <v>-165</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>🚀 大買</t>
+          <t>🟢 加碼</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>90</v>
+        <v>57</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -940,37 +940,37 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>108</v>
+        <v>1223</v>
       </c>
       <c r="D11" t="n">
-        <v>9571</v>
+        <v>5084</v>
       </c>
       <c r="E11" t="n">
-        <v>12222</v>
+        <v>1491</v>
       </c>
       <c r="F11" t="n">
-        <v>-682</v>
+        <v>634</v>
       </c>
       <c r="G11" t="n">
-        <v>902</v>
+        <v>-1881</v>
       </c>
       <c r="H11" t="n">
-        <v>792</v>
+        <v>149</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -979,49 +979,49 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8878</v>
+        <v>2842</v>
       </c>
       <c r="D12" t="n">
-        <v>9264</v>
+        <v>4486</v>
       </c>
       <c r="E12" t="n">
-        <v>-130743</v>
+        <v>11253</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>-2641</v>
       </c>
       <c r="G12" t="n">
-        <v>-5156</v>
+        <v>-6180</v>
       </c>
       <c r="H12" t="n">
-        <v>2212</v>
+        <v>-73</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1030,15 +1030,15 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -1048,31 +1048,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>237</v>
+        <v>1993</v>
       </c>
       <c r="D13" t="n">
-        <v>6604</v>
+        <v>3729</v>
       </c>
       <c r="E13" t="n">
-        <v>13436</v>
+        <v>24001</v>
       </c>
       <c r="F13" t="n">
-        <v>-9</v>
+        <v>-58</v>
       </c>
       <c r="G13" t="n">
-        <v>-2114</v>
+        <v>-580</v>
       </c>
       <c r="H13" t="n">
-        <v>-162</v>
+        <v>-362</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1081,49 +1081,49 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3401</v>
+        <v>3559</v>
       </c>
       <c r="D14" t="n">
-        <v>5537</v>
+        <v>2961</v>
       </c>
       <c r="E14" t="n">
-        <v>1250</v>
+        <v>-1861</v>
       </c>
       <c r="F14" t="n">
-        <v>1448</v>
+        <v>-4721</v>
       </c>
       <c r="G14" t="n">
-        <v>-3643</v>
+        <v>-9546</v>
       </c>
       <c r="H14" t="n">
-        <v>205</v>
+        <v>-275</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1132,49 +1132,49 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2849</v>
+        <v>-1354</v>
       </c>
       <c r="D15" t="n">
-        <v>5021</v>
+        <v>2744</v>
       </c>
       <c r="E15" t="n">
-        <v>24051</v>
+        <v>9618</v>
       </c>
       <c r="F15" t="n">
-        <v>-121</v>
+        <v>51</v>
       </c>
       <c r="G15" t="n">
-        <v>-580</v>
+        <v>-13449</v>
       </c>
       <c r="H15" t="n">
-        <v>-299</v>
+        <v>-104</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1183,15 +1183,15 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M15" t="n">
@@ -1201,31 +1201,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2172</v>
+        <v>1318</v>
       </c>
       <c r="D16" t="n">
-        <v>4213</v>
+        <v>2638</v>
       </c>
       <c r="E16" t="n">
-        <v>10599</v>
+        <v>-259</v>
       </c>
       <c r="F16" t="n">
-        <v>-2629</v>
+        <v>407</v>
       </c>
       <c r="G16" t="n">
-        <v>-5708</v>
+        <v>-1206</v>
       </c>
       <c r="H16" t="n">
-        <v>-82</v>
+        <v>-278</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1234,11 +1234,11 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1246,37 +1246,37 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2808</v>
+        <v>-15</v>
       </c>
       <c r="D17" t="n">
-        <v>3717</v>
+        <v>2173</v>
       </c>
       <c r="E17" t="n">
-        <v>426</v>
+        <v>-1848</v>
       </c>
       <c r="F17" t="n">
-        <v>117</v>
+        <v>1350</v>
       </c>
       <c r="G17" t="n">
-        <v>-1495</v>
+        <v>-1132</v>
       </c>
       <c r="H17" t="n">
-        <v>-249</v>
+        <v>140</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1303,31 +1303,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1080</v>
+        <v>272</v>
       </c>
       <c r="D18" t="n">
-        <v>3006</v>
+        <v>2052</v>
       </c>
       <c r="E18" t="n">
-        <v>1025</v>
+        <v>-395</v>
       </c>
       <c r="F18" t="n">
-        <v>30</v>
+        <v>212</v>
       </c>
       <c r="G18" t="n">
-        <v>-30</v>
+        <v>913</v>
       </c>
       <c r="H18" t="n">
-        <v>-121</v>
+        <v>-196</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1336,53 +1336,53 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>603</v>
+        <v>1176</v>
       </c>
       <c r="D19" t="n">
-        <v>2325</v>
+        <v>1876</v>
       </c>
       <c r="E19" t="n">
-        <v>-1965</v>
+        <v>6111</v>
       </c>
       <c r="F19" t="n">
-        <v>1378</v>
+        <v>39</v>
       </c>
       <c r="G19" t="n">
-        <v>-1265</v>
+        <v>26</v>
       </c>
       <c r="H19" t="n">
-        <v>164</v>
+        <v>-105</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>🟢 加碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1391,11 +1391,11 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M19" t="n">
@@ -1405,35 +1405,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-1699</v>
+        <v>283</v>
       </c>
       <c r="D20" t="n">
-        <v>2317</v>
+        <v>1751</v>
       </c>
       <c r="E20" t="n">
-        <v>8711</v>
+        <v>108</v>
       </c>
       <c r="F20" t="n">
-        <v>127</v>
+        <v>50</v>
       </c>
       <c r="G20" t="n">
-        <v>-13840</v>
+        <v>-0</v>
       </c>
       <c r="H20" t="n">
-        <v>-157</v>
+        <v>-121</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>🟢 加碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1442,49 +1442,49 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>183</v>
+        <v>126</v>
       </c>
       <c r="D21" t="n">
-        <v>2005</v>
+        <v>1340</v>
       </c>
       <c r="E21" t="n">
-        <v>-161</v>
+        <v>-2738</v>
       </c>
       <c r="F21" t="n">
-        <v>16</v>
+        <v>-339</v>
       </c>
       <c r="G21" t="n">
-        <v>675</v>
+        <v>-2319</v>
       </c>
       <c r="H21" t="n">
-        <v>-127</v>
+        <v>114</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>🟢 加碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1497,41 +1497,41 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>556</v>
+        <v>747</v>
       </c>
       <c r="D22" t="n">
-        <v>1791</v>
+        <v>1213</v>
       </c>
       <c r="E22" t="n">
-        <v>5705</v>
+        <v>4724</v>
       </c>
       <c r="F22" t="n">
-        <v>30</v>
+        <v>-702</v>
       </c>
       <c r="G22" t="n">
-        <v>-404</v>
+        <v>2032</v>
       </c>
       <c r="H22" t="n">
-        <v>-120</v>
+        <v>-250</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1544,45 +1544,45 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-134</v>
+        <v>-177</v>
       </c>
       <c r="D23" t="n">
-        <v>1535</v>
+        <v>1197</v>
       </c>
       <c r="E23" t="n">
-        <v>5526</v>
+        <v>1297</v>
       </c>
       <c r="F23" t="n">
-        <v>-311</v>
+        <v>621</v>
       </c>
       <c r="G23" t="n">
-        <v>1697</v>
+        <v>1082</v>
       </c>
       <c r="H23" t="n">
-        <v>-199</v>
+        <v>-84</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1591,49 +1591,49 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>合機</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-316</v>
+        <v>326</v>
       </c>
       <c r="D24" t="n">
-        <v>1492</v>
+        <v>1031</v>
       </c>
       <c r="E24" t="n">
-        <v>11360</v>
+        <v>2252</v>
       </c>
       <c r="F24" t="n">
-        <v>388</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>992</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>51</v>
+        <v>-53</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1642,49 +1642,49 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-97</v>
+        <v>390</v>
       </c>
       <c r="D25" t="n">
-        <v>1352</v>
+        <v>699</v>
       </c>
       <c r="E25" t="n">
-        <v>10368</v>
+        <v>202</v>
       </c>
       <c r="F25" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>-21</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>88</v>
+        <v>1</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1693,49 +1693,49 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>58</v>
+        <v>493</v>
       </c>
       <c r="D26" t="n">
-        <v>1281</v>
+        <v>514</v>
       </c>
       <c r="E26" t="n">
-        <v>-2877</v>
+        <v>-377</v>
       </c>
       <c r="F26" t="n">
-        <v>-126</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-2135</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>250</v>
+        <v>2</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1744,49 +1744,49 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-52</v>
+        <v>86</v>
       </c>
       <c r="D27" t="n">
-        <v>1230</v>
+        <v>423</v>
       </c>
       <c r="E27" t="n">
-        <v>1411</v>
+        <v>655</v>
       </c>
       <c r="F27" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>827</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-17</v>
+        <v>-29</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1795,49 +1795,49 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3694</v>
+        <v>-192</v>
       </c>
       <c r="D28" t="n">
-        <v>990</v>
+        <v>414</v>
       </c>
       <c r="E28" t="n">
-        <v>-2829</v>
+        <v>872</v>
       </c>
       <c r="F28" t="n">
-        <v>-6748</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>-10076</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0</v>
+        <v>10</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1850,36 +1850,36 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>376</v>
+        <v>-67</v>
       </c>
       <c r="D29" t="n">
-        <v>716</v>
+        <v>414</v>
       </c>
       <c r="E29" t="n">
-        <v>172</v>
+        <v>804</v>
       </c>
       <c r="F29" t="n">
         <v>0</v>
@@ -1888,7 +1888,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>-0</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1901,45 +1901,45 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>123</v>
+        <v>-4607</v>
       </c>
       <c r="D30" t="n">
-        <v>501</v>
+        <v>371</v>
       </c>
       <c r="E30" t="n">
-        <v>310</v>
+        <v>12702</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>488</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="H30" t="n">
-        <v>-54</v>
+        <v>72</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1952,45 +1952,45 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-162</v>
+        <v>1556</v>
       </c>
       <c r="D31" t="n">
-        <v>463</v>
+        <v>368</v>
       </c>
       <c r="E31" t="n">
-        <v>899</v>
+        <v>-9123</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="H31" t="n">
-        <v>12</v>
+        <v>737</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2011,37 +2011,37 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-94</v>
+        <v>-11</v>
       </c>
       <c r="D32" t="n">
-        <v>439</v>
+        <v>366</v>
       </c>
       <c r="E32" t="n">
-        <v>858</v>
+        <v>3040</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-48</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>-54</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2050,19 +2050,19 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>77</v>
+        <v>32</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="33">
@@ -2077,13 +2077,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>23</v>
+        <v>-63</v>
       </c>
       <c r="D33" t="n">
-        <v>399</v>
+        <v>349</v>
       </c>
       <c r="E33" t="n">
-        <v>919</v>
+        <v>889</v>
       </c>
       <c r="F33" t="n">
         <v>-5</v>
@@ -2128,22 +2128,22 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-43</v>
+        <v>-54</v>
       </c>
       <c r="D34" t="n">
-        <v>367</v>
+        <v>282</v>
       </c>
       <c r="E34" t="n">
-        <v>989</v>
+        <v>1227</v>
       </c>
       <c r="F34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G34" t="n">
         <v>-3</v>
       </c>
       <c r="H34" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2170,133 +2170,121 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D35" t="n">
-        <v>363</v>
+        <v>244</v>
       </c>
       <c r="E35" t="n">
-        <v>-600</v>
+        <v>-296</v>
       </c>
       <c r="F35" t="n">
-        <v>-6</v>
+        <v>-56</v>
       </c>
       <c r="G35" t="n">
-        <v>-249</v>
+        <v>82</v>
       </c>
       <c r="H35" t="n">
-        <v>-34</v>
+        <v>19</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K35" t="n">
-        <v>79</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>🛬 穩定</t>
-        </is>
-      </c>
-      <c r="M35" t="n">
-        <v>-1</v>
-      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>362</v>
+        <v>693</v>
       </c>
       <c r="D36" t="n">
-        <v>360</v>
+        <v>235</v>
       </c>
       <c r="E36" t="n">
-        <v>-471</v>
+        <v>755</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>-1126</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>-2052</v>
       </c>
       <c r="H36" t="n">
+        <v>-43</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>90</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>🚀 加速器</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
         <v>4</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
-        <v>78</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M36" t="n">
-        <v>-3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-886</v>
+        <v>145</v>
       </c>
       <c r="D37" t="n">
-        <v>302</v>
+        <v>192</v>
       </c>
       <c r="E37" t="n">
-        <v>4981</v>
+        <v>-746</v>
       </c>
       <c r="F37" t="n">
-        <v>-3370</v>
+        <v>-303</v>
       </c>
       <c r="G37" t="n">
-        <v>1800</v>
+        <v>36</v>
       </c>
       <c r="H37" t="n">
-        <v>460</v>
+        <v>61</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2305,49 +2293,49 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>189</v>
+        <v>-59</v>
       </c>
       <c r="D38" t="n">
-        <v>301</v>
+        <v>171</v>
       </c>
       <c r="E38" t="n">
-        <v>2334</v>
+        <v>2480</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="H38" t="n">
-        <v>-209</v>
+        <v>-5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2356,15 +2344,15 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M38" t="n">
@@ -2383,22 +2371,22 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-2012</v>
+        <v>-1270</v>
       </c>
       <c r="D39" t="n">
-        <v>270</v>
+        <v>167</v>
       </c>
       <c r="E39" t="n">
-        <v>-1075</v>
+        <v>2883</v>
       </c>
       <c r="F39" t="n">
-        <v>-215</v>
+        <v>-151</v>
       </c>
       <c r="G39" t="n">
-        <v>-1535</v>
+        <v>-1510</v>
       </c>
       <c r="H39" t="n">
-        <v>-585</v>
+        <v>-546</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2425,70 +2413,82 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="D40" t="n">
-        <v>269</v>
+        <v>122</v>
       </c>
       <c r="E40" t="n">
-        <v>-254</v>
+        <v>183</v>
       </c>
       <c r="F40" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>77</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>✈️ 高飛*</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-342</v>
+        <v>-39</v>
       </c>
       <c r="D41" t="n">
-        <v>244</v>
+        <v>75</v>
       </c>
       <c r="E41" t="n">
-        <v>4315</v>
+        <v>748</v>
       </c>
       <c r="F41" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-48</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-55</v>
+        <v>-2</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2497,49 +2497,49 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>32</v>
+        <v>91</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>方土霖</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-132</v>
+        <v>13</v>
       </c>
       <c r="D42" t="n">
-        <v>172</v>
+        <v>55</v>
       </c>
       <c r="E42" t="n">
-        <v>2132</v>
+        <v>50</v>
       </c>
       <c r="F42" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-6</v>
+        <v>-0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2548,11 +2548,11 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2566,31 +2566,31 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>112</v>
+        <v>-252</v>
       </c>
       <c r="D43" t="n">
-        <v>154</v>
+        <v>52</v>
       </c>
       <c r="E43" t="n">
-        <v>-835</v>
+        <v>1474</v>
       </c>
       <c r="F43" t="n">
-        <v>-283</v>
+        <v>48</v>
       </c>
       <c r="G43" t="n">
-        <v>-16</v>
+        <v>148</v>
       </c>
       <c r="H43" t="n">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2599,49 +2599,49 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M43" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>100</v>
+        <v>-16</v>
       </c>
       <c r="D44" t="n">
-        <v>144</v>
+        <v>25</v>
       </c>
       <c r="E44" t="n">
-        <v>176</v>
+        <v>-501</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>-249</v>
       </c>
       <c r="H44" t="n">
-        <v>4</v>
+        <v>-23</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2654,11 +2654,11 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M44" t="n">
@@ -2668,31 +2668,31 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>大車隊</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>136</v>
+        <v>-6</v>
       </c>
       <c r="D45" t="n">
-        <v>143</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>1126</v>
+        <v>-22</v>
       </c>
       <c r="F45" t="n">
-        <v>449</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>564</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2705,45 +2705,45 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M45" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>25</v>
+        <v>-16</v>
       </c>
       <c r="D46" t="n">
-        <v>103</v>
+        <v>-9</v>
       </c>
       <c r="E46" t="n">
-        <v>770</v>
+        <v>132</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H46" t="n">
-        <v>-2</v>
+        <v>38</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2752,49 +2752,49 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>136</v>
+        <v>18</v>
       </c>
       <c r="D47" t="n">
-        <v>96</v>
+        <v>-54</v>
       </c>
       <c r="E47" t="n">
-        <v>167</v>
+        <v>-182</v>
       </c>
       <c r="F47" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>58</v>
+        <v>-0</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2807,36 +2807,36 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>方土霖</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>13</v>
+        <v>-149</v>
       </c>
       <c r="D48" t="n">
-        <v>60</v>
+        <v>-113</v>
       </c>
       <c r="E48" t="n">
-        <v>45</v>
+        <v>-18</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2854,15 +2854,15 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M48" t="n">
@@ -2872,31 +2872,31 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-100</v>
+        <v>-1532</v>
       </c>
       <c r="D49" t="n">
-        <v>31</v>
+        <v>-122</v>
       </c>
       <c r="E49" t="n">
-        <v>445</v>
+        <v>-43</v>
       </c>
       <c r="F49" t="n">
-        <v>-1458</v>
+        <v>-37</v>
       </c>
       <c r="G49" t="n">
-        <v>-1998</v>
+        <v>-360</v>
       </c>
       <c r="H49" t="n">
-        <v>-38</v>
+        <v>-247</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2905,49 +2905,49 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-5</v>
+        <v>-199</v>
       </c>
       <c r="D50" t="n">
-        <v>24</v>
+        <v>-131</v>
       </c>
       <c r="E50" t="n">
-        <v>-47</v>
+        <v>213</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>-41</v>
       </c>
       <c r="H50" t="n">
-        <v>-1</v>
+        <v>-24</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2960,45 +2960,45 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-581</v>
+        <v>-362</v>
       </c>
       <c r="D51" t="n">
-        <v>-26</v>
+        <v>-133</v>
       </c>
       <c r="E51" t="n">
-        <v>493</v>
+        <v>-2034</v>
       </c>
       <c r="F51" t="n">
-        <v>-713</v>
+        <v>271</v>
       </c>
       <c r="G51" t="n">
-        <v>2818</v>
+        <v>560</v>
       </c>
       <c r="H51" t="n">
-        <v>-155</v>
+        <v>88</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3007,49 +3007,49 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>33</v>
+        <v>-327</v>
       </c>
       <c r="D52" t="n">
-        <v>-71</v>
+        <v>-163</v>
       </c>
       <c r="E52" t="n">
-        <v>-166</v>
+        <v>-1882</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>-1972</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3058,49 +3058,49 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>德昌</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-372</v>
+        <v>-30</v>
       </c>
       <c r="D53" t="n">
-        <v>-84</v>
+        <v>-263</v>
       </c>
       <c r="E53" t="n">
-        <v>1163</v>
+        <v>-2038</v>
       </c>
       <c r="F53" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>82</v>
+        <v>-1</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3109,15 +3109,15 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M53" t="n">
@@ -3127,22 +3127,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-115</v>
+        <v>163</v>
       </c>
       <c r="D54" t="n">
-        <v>-97</v>
+        <v>-391</v>
       </c>
       <c r="E54" t="n">
-        <v>11</v>
+        <v>-1393</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-3</v>
+        <v>-9</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3168,41 +3168,41 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M54" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-118</v>
+        <v>-278</v>
       </c>
       <c r="D55" t="n">
-        <v>-104</v>
+        <v>-475</v>
       </c>
       <c r="E55" t="n">
-        <v>337</v>
+        <v>-3854</v>
       </c>
       <c r="F55" t="n">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>-41</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-23</v>
+        <v>-96</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3215,36 +3215,36 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>智冠</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-26</v>
+        <v>-99</v>
       </c>
       <c r="D56" t="n">
-        <v>-201</v>
+        <v>-488</v>
       </c>
       <c r="E56" t="n">
-        <v>-1988</v>
+        <v>-867</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
@@ -3253,7 +3253,7 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3262,40 +3262,40 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-320</v>
+        <v>315</v>
       </c>
       <c r="D57" t="n">
-        <v>-286</v>
+        <v>-545</v>
       </c>
       <c r="E57" t="n">
-        <v>-510</v>
+        <v>-2031</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
@@ -3304,7 +3304,7 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-9</v>
+        <v>-53</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3317,45 +3317,45 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-33</v>
+        <v>-91</v>
       </c>
       <c r="D58" t="n">
-        <v>-290</v>
+        <v>-547</v>
       </c>
       <c r="E58" t="n">
-        <v>-1715</v>
+        <v>845</v>
       </c>
       <c r="F58" t="n">
-        <v>688</v>
+        <v>-21</v>
       </c>
       <c r="G58" t="n">
-        <v>-2196</v>
+        <v>-48</v>
       </c>
       <c r="H58" t="n">
-        <v>-67</v>
+        <v>-52</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3364,49 +3364,49 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-465</v>
+        <v>-204</v>
       </c>
       <c r="D59" t="n">
-        <v>-319</v>
+        <v>-615</v>
       </c>
       <c r="E59" t="n">
-        <v>-1904</v>
+        <v>554</v>
       </c>
       <c r="F59" t="n">
-        <v>264</v>
+        <v>188</v>
       </c>
       <c r="G59" t="n">
-        <v>572</v>
+        <v>530</v>
       </c>
       <c r="H59" t="n">
-        <v>177</v>
+        <v>3</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3419,45 +3419,45 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>118</v>
+        <v>498</v>
       </c>
       <c r="D60" t="n">
-        <v>-390</v>
+        <v>-621</v>
       </c>
       <c r="E60" t="n">
-        <v>-1099</v>
+        <v>-4316</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="H60" t="n">
-        <v>-8</v>
+        <v>-15</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3470,45 +3470,45 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>539</v>
+        <v>-610</v>
       </c>
       <c r="D61" t="n">
-        <v>-460</v>
+        <v>-643</v>
       </c>
       <c r="E61" t="n">
-        <v>-3953</v>
+        <v>488</v>
       </c>
       <c r="F61" t="n">
-        <v>155</v>
+        <v>450</v>
       </c>
       <c r="G61" t="n">
-        <v>195</v>
+        <v>564</v>
       </c>
       <c r="H61" t="n">
-        <v>-21</v>
+        <v>19</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3517,15 +3517,15 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M61" t="n">
@@ -3535,31 +3535,31 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-388</v>
+        <v>65</v>
       </c>
       <c r="D62" t="n">
-        <v>-474</v>
+        <v>-709</v>
       </c>
       <c r="E62" t="n">
-        <v>-3941</v>
+        <v>-4464</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>-806</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>2328</v>
       </c>
       <c r="H62" t="n">
-        <v>-96</v>
+        <v>-90</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3568,49 +3568,49 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-341</v>
+        <v>-754</v>
       </c>
       <c r="D63" t="n">
-        <v>-492</v>
+        <v>-913</v>
       </c>
       <c r="E63" t="n">
-        <v>488</v>
+        <v>803</v>
       </c>
       <c r="F63" t="n">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>436</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>4</v>
+        <v>-192</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3619,49 +3619,49 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-24</v>
+        <v>3043</v>
       </c>
       <c r="D64" t="n">
-        <v>-508</v>
+        <v>-987</v>
       </c>
       <c r="E64" t="n">
-        <v>-1396</v>
+        <v>-10648</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>-27</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>2874</v>
       </c>
       <c r="H64" t="n">
-        <v>-55</v>
+        <v>-213</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3670,11 +3670,11 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3682,37 +3682,37 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-126</v>
+        <v>1057</v>
       </c>
       <c r="D65" t="n">
-        <v>-523</v>
+        <v>-987</v>
       </c>
       <c r="E65" t="n">
-        <v>-855</v>
+        <v>10</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>-567</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>2858</v>
       </c>
       <c r="H65" t="n">
-        <v>-4</v>
+        <v>-130</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3721,15 +3721,15 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M65" t="n">
@@ -3739,31 +3739,31 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-72</v>
+        <v>-2504</v>
       </c>
       <c r="D66" t="n">
-        <v>-534</v>
+        <v>-1046</v>
       </c>
       <c r="E66" t="n">
-        <v>-4201</v>
+        <v>7536</v>
       </c>
       <c r="F66" t="n">
-        <v>-893</v>
+        <v>-3</v>
       </c>
       <c r="G66" t="n">
-        <v>2309</v>
+        <v>-21</v>
       </c>
       <c r="H66" t="n">
-        <v>112</v>
+        <v>169</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3772,15 +3772,15 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>70</v>
+        <v>97</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M66" t="n">
@@ -3790,82 +3790,70 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1662</v>
+        <v>136</v>
       </c>
       <c r="D67" t="n">
-        <v>-542</v>
+        <v>-1080</v>
       </c>
       <c r="E67" t="n">
-        <v>-9625</v>
+        <v>2381</v>
       </c>
       <c r="F67" t="n">
-        <v>-4</v>
+        <v>12</v>
       </c>
       <c r="G67" t="n">
-        <v>-10</v>
+        <v>1408</v>
       </c>
       <c r="H67" t="n">
-        <v>578</v>
+        <v>2</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K67" t="n">
-        <v>75</v>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M67" t="n">
-        <v>2</v>
-      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-60</v>
+        <v>-147</v>
       </c>
       <c r="D68" t="n">
-        <v>-543</v>
+        <v>-1105</v>
       </c>
       <c r="E68" t="n">
-        <v>1045</v>
+        <v>635</v>
       </c>
       <c r="F68" t="n">
-        <v>-24</v>
+        <v>-285</v>
       </c>
       <c r="G68" t="n">
-        <v>-53</v>
+        <v>-520</v>
       </c>
       <c r="H68" t="n">
-        <v>-33</v>
+        <v>-85</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3874,49 +3862,49 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>聯合</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-1078</v>
+        <v>-351</v>
       </c>
       <c r="D69" t="n">
-        <v>-592</v>
+        <v>-1150</v>
       </c>
       <c r="E69" t="n">
-        <v>-495</v>
+        <v>-1830</v>
       </c>
       <c r="F69" t="n">
-        <v>-37</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>-360</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-259</v>
+        <v>1</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3925,49 +3913,49 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-699</v>
+        <v>482</v>
       </c>
       <c r="D70" t="n">
-        <v>-610</v>
+        <v>-1175</v>
       </c>
       <c r="E70" t="n">
-        <v>741</v>
+        <v>-8604</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>-2896</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>-7074</v>
       </c>
       <c r="H70" t="n">
-        <v>-164</v>
+        <v>278</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3976,49 +3964,49 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K70" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M70" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-222</v>
+        <v>-2408</v>
       </c>
       <c r="D71" t="n">
-        <v>-879</v>
+        <v>-1186</v>
       </c>
       <c r="E71" t="n">
-        <v>-7578</v>
+        <v>3940</v>
       </c>
       <c r="F71" t="n">
-        <v>-659</v>
+        <v>-3380</v>
       </c>
       <c r="G71" t="n">
-        <v>785</v>
+        <v>1789</v>
       </c>
       <c r="H71" t="n">
-        <v>620</v>
+        <v>380</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -4031,7 +4019,7 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4039,37 +4027,37 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>87</v>
+        <v>208</v>
       </c>
       <c r="D72" t="n">
-        <v>-950</v>
+        <v>-1359</v>
       </c>
       <c r="E72" t="n">
-        <v>1046</v>
+        <v>-7180</v>
       </c>
       <c r="F72" t="n">
-        <v>-271</v>
+        <v>-285</v>
       </c>
       <c r="G72" t="n">
-        <v>-448</v>
+        <v>654</v>
       </c>
       <c r="H72" t="n">
-        <v>-34</v>
+        <v>396</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -4078,19 +4066,19 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="73">
@@ -4105,13 +4093,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-407</v>
+        <v>-217</v>
       </c>
       <c r="D73" t="n">
-        <v>-1084</v>
+        <v>-1386</v>
       </c>
       <c r="E73" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -4147,31 +4135,31 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-370</v>
+        <v>-4239</v>
       </c>
       <c r="D74" t="n">
-        <v>-1094</v>
+        <v>-1647</v>
       </c>
       <c r="E74" t="n">
-        <v>-1764</v>
+        <v>-1655</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>3897</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>10556</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>-317</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4180,88 +4168,100 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-225</v>
+        <v>-397</v>
       </c>
       <c r="D75" t="n">
-        <v>-1361</v>
+        <v>-1697</v>
       </c>
       <c r="E75" t="n">
-        <v>2383</v>
+        <v>-4555</v>
       </c>
       <c r="F75" t="n">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="G75" t="n">
-        <v>2819</v>
+        <v>660</v>
       </c>
       <c r="H75" t="n">
-        <v>39</v>
+        <v>-137</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>96</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>📉 減速</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>238</v>
+        <v>57</v>
       </c>
       <c r="D76" t="n">
-        <v>-1448</v>
+        <v>-1763</v>
       </c>
       <c r="E76" t="n">
-        <v>-2617</v>
+        <v>-1112</v>
       </c>
       <c r="F76" t="n">
-        <v>-39</v>
+        <v>-24</v>
       </c>
       <c r="G76" t="n">
-        <v>-262</v>
+        <v>344</v>
       </c>
       <c r="H76" t="n">
-        <v>9</v>
+        <v>122</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4270,49 +4270,49 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M76" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-4812</v>
+        <v>475</v>
       </c>
       <c r="D77" t="n">
-        <v>-1708</v>
+        <v>-1785</v>
       </c>
       <c r="E77" t="n">
-        <v>-2285</v>
+        <v>-2218</v>
       </c>
       <c r="F77" t="n">
-        <v>3874</v>
+        <v>475</v>
       </c>
       <c r="G77" t="n">
-        <v>11028</v>
+        <v>1656</v>
       </c>
       <c r="H77" t="n">
-        <v>-111</v>
+        <v>11</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4325,45 +4325,45 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M77" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>勝一</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="D78" t="n">
-        <v>-1712</v>
+        <v>-1788</v>
       </c>
       <c r="E78" t="n">
-        <v>-8211</v>
+        <v>-2921</v>
       </c>
       <c r="F78" t="n">
-        <v>-2661</v>
+        <v>-38</v>
       </c>
       <c r="G78" t="n">
-        <v>-7210</v>
+        <v>-117</v>
       </c>
       <c r="H78" t="n">
-        <v>197</v>
+        <v>-0</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4372,53 +4372,53 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>441</v>
+        <v>-2053</v>
       </c>
       <c r="D79" t="n">
-        <v>-1782</v>
+        <v>-2026</v>
       </c>
       <c r="E79" t="n">
-        <v>-2363</v>
+        <v>-1670</v>
       </c>
       <c r="F79" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>343</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>139</v>
+        <v>6</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>🟡 中性</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4427,7 +4427,7 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4435,41 +4435,41 @@
         </is>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-290</v>
+        <v>499</v>
       </c>
       <c r="D80" t="n">
-        <v>-1846</v>
+        <v>-2660</v>
       </c>
       <c r="E80" t="n">
-        <v>-5561</v>
+        <v>-9887</v>
       </c>
       <c r="F80" t="n">
-        <v>132</v>
+        <v>298</v>
       </c>
       <c r="G80" t="n">
-        <v>707</v>
+        <v>1729</v>
       </c>
       <c r="H80" t="n">
-        <v>-144</v>
+        <v>-542</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>🟡 中性</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -4478,45 +4478,45 @@
         </is>
       </c>
       <c r="K80" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-117</v>
+        <v>-1213</v>
       </c>
       <c r="D81" t="n">
-        <v>-2157</v>
+        <v>-2857</v>
       </c>
       <c r="E81" t="n">
-        <v>-2389</v>
+        <v>-1173</v>
       </c>
       <c r="F81" t="n">
-        <v>1060</v>
+        <v>-284</v>
       </c>
       <c r="G81" t="n">
-        <v>1898</v>
+        <v>-438</v>
       </c>
       <c r="H81" t="n">
-        <v>-52</v>
+        <v>-136</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4537,37 +4537,37 @@
         </is>
       </c>
       <c r="M81" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1754</v>
+        <v>-20</v>
       </c>
       <c r="D82" t="n">
-        <v>-2160</v>
+        <v>-2998</v>
       </c>
       <c r="E82" t="n">
-        <v>-14252</v>
+        <v>-3599</v>
       </c>
       <c r="F82" t="n">
-        <v>99</v>
+        <v>-5</v>
       </c>
       <c r="G82" t="n">
-        <v>2764</v>
+        <v>-189</v>
       </c>
       <c r="H82" t="n">
-        <v>-95</v>
+        <v>21</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4576,49 +4576,49 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M82" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-1441</v>
+        <v>-382</v>
       </c>
       <c r="D83" t="n">
-        <v>-2992</v>
+        <v>-3010</v>
       </c>
       <c r="E83" t="n">
-        <v>542</v>
+        <v>-5906</v>
       </c>
       <c r="F83" t="n">
-        <v>-349</v>
+        <v>56</v>
       </c>
       <c r="G83" t="n">
-        <v>-287</v>
+        <v>-433</v>
       </c>
       <c r="H83" t="n">
-        <v>-131</v>
+        <v>3</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4631,67 +4631,55 @@
         </is>
       </c>
       <c r="K83" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器*</t>
         </is>
       </c>
       <c r="M83" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-331</v>
+        <v>434</v>
       </c>
       <c r="D84" t="n">
-        <v>-3136</v>
+        <v>-3155</v>
       </c>
       <c r="E84" t="n">
-        <v>-3875</v>
+        <v>-4916</v>
       </c>
       <c r="F84" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>-189</v>
+        <v>-400</v>
       </c>
       <c r="H84" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
           <t>🟠 減碼</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K84" t="n">
-        <v>90</v>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>🚀 加速器</t>
-        </is>
-      </c>
-      <c r="M84" t="n">
-        <v>4</v>
-      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4705,22 +4693,22 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-736</v>
+        <v>-714</v>
       </c>
       <c r="D85" t="n">
-        <v>-3157</v>
+        <v>-3167</v>
       </c>
       <c r="E85" t="n">
-        <v>-5546</v>
+        <v>-4325</v>
       </c>
       <c r="F85" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="G85" t="n">
         <v>1077</v>
       </c>
       <c r="H85" t="n">
-        <v>2358</v>
+        <v>2406</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4756,22 +4744,22 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-2803</v>
+        <v>-2214</v>
       </c>
       <c r="D86" t="n">
-        <v>-3292</v>
+        <v>-3180</v>
       </c>
       <c r="E86" t="n">
-        <v>-4657</v>
+        <v>-4422</v>
       </c>
       <c r="F86" t="n">
-        <v>-291</v>
+        <v>-138</v>
       </c>
       <c r="G86" t="n">
-        <v>-179</v>
+        <v>54</v>
       </c>
       <c r="H86" t="n">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4798,70 +4786,82 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>392</v>
+        <v>5643</v>
       </c>
       <c r="D87" t="n">
-        <v>-3310</v>
+        <v>-3390</v>
       </c>
       <c r="E87" t="n">
-        <v>-5763</v>
+        <v>58585</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>-4075</v>
       </c>
       <c r="G87" t="n">
-        <v>-400</v>
+        <v>-7044</v>
       </c>
       <c r="H87" t="n">
-        <v>52</v>
+        <v>-5529</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
           <t>🟠 減碼</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>62</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M87" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>198</v>
+        <v>-562</v>
       </c>
       <c r="D88" t="n">
-        <v>-3737</v>
+        <v>-3751</v>
       </c>
       <c r="E88" t="n">
-        <v>-7954</v>
+        <v>-2645</v>
       </c>
       <c r="F88" t="n">
-        <v>392</v>
+        <v>329</v>
       </c>
       <c r="G88" t="n">
-        <v>2398</v>
+        <v>5452</v>
       </c>
       <c r="H88" t="n">
-        <v>-595</v>
+        <v>46</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4870,49 +4870,49 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K88" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-2905</v>
+        <v>-786</v>
       </c>
       <c r="D89" t="n">
-        <v>-3971</v>
+        <v>-5079</v>
       </c>
       <c r="E89" t="n">
-        <v>-3232</v>
+        <v>-22109</v>
       </c>
       <c r="F89" t="n">
-        <v>-328</v>
+        <v>-340</v>
       </c>
       <c r="G89" t="n">
-        <v>5452</v>
+        <v>-1543</v>
       </c>
       <c r="H89" t="n">
-        <v>60</v>
+        <v>-268</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4921,49 +4921,49 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K89" t="n">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M89" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-375</v>
+        <v>-44426</v>
       </c>
       <c r="D90" t="n">
-        <v>-4301</v>
+        <v>-5174</v>
       </c>
       <c r="E90" t="n">
-        <v>-6322</v>
+        <v>26260</v>
       </c>
       <c r="F90" t="n">
-        <v>-7</v>
+        <v>-6985</v>
       </c>
       <c r="G90" t="n">
-        <v>-536</v>
+        <v>-48703</v>
       </c>
       <c r="H90" t="n">
-        <v>-10</v>
+        <v>-10060</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4972,49 +4972,49 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K90" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>🚀 加速器*</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M90" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-489</v>
+        <v>-5169</v>
       </c>
       <c r="D91" t="n">
-        <v>-4629</v>
+        <v>-6017</v>
       </c>
       <c r="E91" t="n">
-        <v>-23490</v>
+        <v>-36570</v>
       </c>
       <c r="F91" t="n">
-        <v>-242</v>
+        <v>204</v>
       </c>
       <c r="G91" t="n">
-        <v>-1545</v>
+        <v>350</v>
       </c>
       <c r="H91" t="n">
-        <v>-238</v>
+        <v>124</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -5023,49 +5023,49 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K91" t="n">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M91" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-5729</v>
+        <v>-18449</v>
       </c>
       <c r="D92" t="n">
-        <v>-5572</v>
+        <v>-6368</v>
       </c>
       <c r="E92" t="n">
-        <v>-38520</v>
+        <v>-149334</v>
       </c>
       <c r="F92" t="n">
-        <v>161</v>
+        <v>905</v>
       </c>
       <c r="G92" t="n">
-        <v>301</v>
+        <v>-2565</v>
       </c>
       <c r="H92" t="n">
-        <v>46</v>
+        <v>2267</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -5074,49 +5074,49 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K92" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M92" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-335</v>
+        <v>-18026</v>
       </c>
       <c r="D93" t="n">
-        <v>-8937</v>
+        <v>-7044</v>
       </c>
       <c r="E93" t="n">
-        <v>-15199</v>
+        <v>71930</v>
       </c>
       <c r="F93" t="n">
-        <v>-752</v>
+        <v>594</v>
       </c>
       <c r="G93" t="n">
-        <v>2690</v>
+        <v>2283</v>
       </c>
       <c r="H93" t="n">
-        <v>418</v>
+        <v>-3446</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -5125,343 +5125,343 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K93" t="n">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M93" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-1986</v>
+        <v>539</v>
       </c>
       <c r="D94" t="n">
-        <v>-9126</v>
+        <v>-8797</v>
       </c>
       <c r="E94" t="n">
-        <v>-10960</v>
+        <v>-7788</v>
       </c>
       <c r="F94" t="n">
-        <v>-3315</v>
+        <v>-1248</v>
       </c>
       <c r="G94" t="n">
-        <v>-3071</v>
+        <v>2695</v>
       </c>
       <c r="H94" t="n">
-        <v>-637</v>
+        <v>-26</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
           <t>🟠 減碼</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K94" t="n">
-        <v>65</v>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>🚀 加速器</t>
-        </is>
-      </c>
-      <c r="M94" t="n">
-        <v>1</v>
-      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-611</v>
+        <v>-1217</v>
       </c>
       <c r="D95" t="n">
-        <v>-9743</v>
+        <v>-9176</v>
       </c>
       <c r="E95" t="n">
-        <v>-8989</v>
+        <v>-11123</v>
       </c>
       <c r="F95" t="n">
-        <v>-562</v>
+        <v>-2445</v>
       </c>
       <c r="G95" t="n">
-        <v>3142</v>
+        <v>-3039</v>
       </c>
       <c r="H95" t="n">
-        <v>219</v>
+        <v>-751</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
           <t>🟠 減碼</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>65</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>🚀 加速器</t>
+        </is>
+      </c>
+      <c r="M95" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>長榮航太</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-1759</v>
+        <v>-606</v>
       </c>
       <c r="D96" t="n">
-        <v>-10220</v>
+        <v>-9322</v>
       </c>
       <c r="E96" t="n">
-        <v>-16716</v>
+        <v>-11661</v>
       </c>
       <c r="F96" t="n">
+        <v>9</v>
+      </c>
+      <c r="G96" t="n">
+        <v>204</v>
+      </c>
+      <c r="H96" t="n">
+        <v>-9</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>🟠 減碼</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>79</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>✈️ 高飛*</t>
+        </is>
+      </c>
+      <c r="M96" t="n">
         <v>0</v>
-      </c>
-      <c r="G96" t="n">
-        <v>1</v>
-      </c>
-      <c r="H96" t="n">
-        <v>-8</v>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>🔴 大賣</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K96" t="n">
-        <v>78</v>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M96" t="n">
-        <v>-5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-12414</v>
+        <v>-1693</v>
       </c>
       <c r="D97" t="n">
-        <v>-12240</v>
+        <v>-9643</v>
       </c>
       <c r="E97" t="n">
-        <v>66876</v>
+        <v>-16148</v>
       </c>
       <c r="F97" t="n">
-        <v>-2410</v>
+        <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>13440</v>
+        <v>1</v>
       </c>
       <c r="H97" t="n">
-        <v>-933</v>
+        <v>8</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>🔴 大賣</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K97" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M97" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-724</v>
+        <v>-923</v>
       </c>
       <c r="D98" t="n">
-        <v>-14303</v>
+        <v>-9691</v>
       </c>
       <c r="E98" t="n">
-        <v>-10729</v>
+        <v>-16855</v>
       </c>
       <c r="F98" t="n">
-        <v>6</v>
+        <v>120</v>
       </c>
       <c r="G98" t="n">
-        <v>204</v>
+        <v>2097</v>
       </c>
       <c r="H98" t="n">
-        <v>-17</v>
+        <v>468</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>🔴 大賣</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K98" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-11935</v>
+        <v>-1601</v>
       </c>
       <c r="D99" t="n">
-        <v>-17441</v>
+        <v>-9998</v>
       </c>
       <c r="E99" t="n">
-        <v>-52736</v>
+        <v>64294</v>
       </c>
       <c r="F99" t="n">
-        <v>-3156</v>
+        <v>-2449</v>
       </c>
       <c r="G99" t="n">
-        <v>-8934</v>
+        <v>13871</v>
       </c>
       <c r="H99" t="n">
-        <v>-48</v>
+        <v>-1203</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>🔴 大賣</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K99" t="n">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M99" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>寶雅*</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-2534</v>
+        <v>3335</v>
       </c>
       <c r="D100" t="n">
-        <v>-18392</v>
+        <v>-14882</v>
       </c>
       <c r="E100" t="n">
-        <v>-26136</v>
+        <v>-64954</v>
       </c>
       <c r="F100" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>-1905</v>
       </c>
       <c r="H100" t="n">
-        <v>-64</v>
+        <v>-284</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -5470,11 +5470,11 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K100" t="n">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -5482,37 +5482,37 @@
         </is>
       </c>
       <c r="M100" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-29474</v>
+        <v>-1970</v>
       </c>
       <c r="D101" t="n">
-        <v>-18531</v>
+        <v>-18109</v>
       </c>
       <c r="E101" t="n">
-        <v>61108</v>
+        <v>-24646</v>
       </c>
       <c r="F101" t="n">
-        <v>482</v>
+        <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>781</v>
+        <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>-3610</v>
+        <v>-301</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5521,49 +5521,49 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K101" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2290</v>
+        <v>-11814</v>
       </c>
       <c r="D102" t="n">
-        <v>-19450</v>
+        <v>-18501</v>
       </c>
       <c r="E102" t="n">
-        <v>-66136</v>
+        <v>-52825</v>
       </c>
       <c r="F102" t="n">
-        <v>-31</v>
+        <v>-3225</v>
       </c>
       <c r="G102" t="n">
-        <v>-1993</v>
+        <v>-8202</v>
       </c>
       <c r="H102" t="n">
-        <v>-643</v>
+        <v>-36</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5576,7 +5576,7 @@
         </is>
       </c>
       <c r="K102" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         </is>
       </c>
       <c r="M102" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -5599,22 +5599,22 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-5641</v>
+        <v>-8379</v>
       </c>
       <c r="D103" t="n">
-        <v>-26947</v>
+        <v>-20902</v>
       </c>
       <c r="E103" t="n">
-        <v>-68039</v>
+        <v>-77636</v>
       </c>
       <c r="F103" t="n">
-        <v>-672</v>
+        <v>177</v>
       </c>
       <c r="G103" t="n">
-        <v>-27587</v>
+        <v>-26421</v>
       </c>
       <c r="H103" t="n">
-        <v>302</v>
+        <v>-521</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5650,22 +5650,22 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-19912</v>
+        <v>-17123</v>
       </c>
       <c r="D104" t="n">
-        <v>-35054</v>
+        <v>-25839</v>
       </c>
       <c r="E104" t="n">
-        <v>23102</v>
+        <v>45672</v>
       </c>
       <c r="F104" t="n">
-        <v>1401</v>
+        <v>2162</v>
       </c>
       <c r="G104" t="n">
-        <v>-1751</v>
+        <v>730</v>
       </c>
       <c r="H104" t="n">
-        <v>-2904</v>
+        <v>-3288</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5701,22 +5701,22 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-80785</v>
+        <v>-83197</v>
       </c>
       <c r="D105" t="n">
-        <v>-103789</v>
+        <v>-114098</v>
       </c>
       <c r="E105" t="n">
-        <v>139111</v>
+        <v>138942</v>
       </c>
       <c r="F105" t="n">
-        <v>2879</v>
+        <v>1158</v>
       </c>
       <c r="G105" t="n">
-        <v>21134</v>
+        <v>32267</v>
       </c>
       <c r="H105" t="n">
-        <v>150</v>
+        <v>273</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5794,348 +5794,348 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -1,207 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 204 千股)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-133899</v>
+        <v>692690</v>
       </c>
       <c r="D2" t="n">
-        <v>1535342</v>
+        <v>234850</v>
       </c>
       <c r="E2" t="n">
-        <v>413639</v>
+        <v>-100330</v>
       </c>
       <c r="F2" t="n">
-        <v>2741874</v>
+        <v>30718</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>勤誠</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,213 千股)</t>
+          <t>📉 20d 巨變(減碼 -450 千股)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-334930</v>
+        <v>-786062</v>
       </c>
       <c r="D3" t="n">
-        <v>-8936751</v>
+        <v>-5078924</v>
       </c>
       <c r="E3" t="n">
-        <v>-384885</v>
+        <v>-489132</v>
       </c>
       <c r="F3" t="n">
-        <v>-10149484</v>
+        <v>-4628887</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>亞翔</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -618 千股)</t>
+          <t>📈 20d 巨變(加碼 47 千股)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>57512</v>
+        <v>271561</v>
       </c>
       <c r="D4" t="n">
-        <v>1281306</v>
+        <v>2051842</v>
       </c>
       <c r="E4" t="n">
-        <v>59677</v>
+        <v>183068</v>
       </c>
       <c r="F4" t="n">
-        <v>1899349</v>
+        <v>2005152</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>健策</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -679 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -322 千股)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-100330</v>
+        <v>746751</v>
       </c>
       <c r="D5" t="n">
-        <v>30718</v>
+        <v>1213139</v>
       </c>
       <c r="E5" t="n">
-        <v>185946</v>
+        <v>-133899</v>
       </c>
       <c r="F5" t="n">
-        <v>709557</v>
+        <v>1535342</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>奇鋐</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -616 千股)</t>
+          <t>📈 20d 巨變(加碼 59 千股)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-489132</v>
+        <v>126216</v>
       </c>
       <c r="D6" t="n">
-        <v>-4628887</v>
+        <v>1339959</v>
       </c>
       <c r="E6" t="n">
-        <v>678009</v>
+        <v>57512</v>
       </c>
       <c r="F6" t="n">
-        <v>-4012448</v>
+        <v>1281306</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>台光電</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -16 千股)</t>
+          <t>📉 20d 巨變(減碼 -754 千股)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>183068</v>
+        <v>-923067</v>
       </c>
       <c r="D7" t="n">
-        <v>2005152</v>
+        <v>-9691049</v>
       </c>
       <c r="E7" t="n">
-        <v>322160</v>
+        <v>-334930</v>
       </c>
       <c r="F7" t="n">
-        <v>2020859</v>
+        <v>-8936751</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -13 千股)</t>
+          <t>📈 20d 巨變(加碼 186 千股)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>603030</v>
+        <v>-361990</v>
       </c>
       <c r="D8" t="n">
-        <v>2324994</v>
+        <v>-132874</v>
       </c>
       <c r="E8" t="n">
-        <v>166455</v>
+        <v>-465155</v>
       </c>
       <c r="F8" t="n">
-        <v>2337683</v>
+        <v>-319191</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>光聖</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -153 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -152 千股)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-465155</v>
+        <v>-14835</v>
       </c>
       <c r="D9" t="n">
-        <v>-319191</v>
+        <v>2173381</v>
       </c>
       <c r="E9" t="n">
-        <v>-685246</v>
+        <v>603030</v>
       </c>
       <c r="F9" t="n">
-        <v>-166018</v>
+        <v>2324994</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>致茂</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -665 千股)</t>
+          <t>📈 20d 巨變(加碼 127 千股)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>108230</v>
+        <v>-326672</v>
       </c>
       <c r="D10" t="n">
-        <v>9571239</v>
+        <v>-162990</v>
       </c>
       <c r="E10" t="n">
-        <v>602507</v>
+        <v>-32920</v>
       </c>
       <c r="F10" t="n">
-        <v>10235741</v>
+        <v>-289771</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>旺矽</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 28 千股)</t>
+          <t>📈 20d 巨變(加碼 537 千股)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-32920</v>
+        <v>482323</v>
       </c>
       <c r="D11" t="n">
-        <v>-289771</v>
+        <v>-1175019</v>
       </c>
       <c r="E11" t="n">
-        <v>-2531</v>
+        <v>171263</v>
       </c>
       <c r="F11" t="n">
-        <v>-317898</v>
+        <v>-1711576</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>智邦</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 125 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -15,633 千股)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>171263</v>
+        <v>-18448562</v>
       </c>
       <c r="D12" t="n">
-        <v>-1711576</v>
+        <v>-6368431</v>
       </c>
       <c r="E12" t="n">
-        <v>-666245</v>
+        <v>8877774</v>
       </c>
       <c r="F12" t="n">
-        <v>-1836700</v>
+        <v>9264250</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -5,227 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -126 千股)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8877774</v>
+        <v>-155839</v>
       </c>
       <c r="D13" t="n">
-        <v>9264250</v>
+        <v>9445037</v>
       </c>
       <c r="E13" t="n">
-        <v>19013989</v>
+        <v>108230</v>
       </c>
       <c r="F13" t="n">
-        <v>14491033</v>
+        <v>9571239</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>雙鴻</t>
         </is>
       </c>
     </row>
@@ -6147,20 +6147,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,580 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,060 千股)</t>
         </is>
       </c>
       <c r="C14" t="n">
+        <v>-11813898</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-18501314</v>
+      </c>
+      <c r="E14" t="n">
         <v>-11935031</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>-17440933</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-6955457</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-14860437</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -6176,20 +6176,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 144 千股)</t>
+          <t>📈 20d 巨變(加碼 84 千股)</t>
         </is>
       </c>
       <c r="C15" t="n">
+        <v>1175652</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1875536</v>
+      </c>
+      <c r="E15" t="n">
         <v>555865</v>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>1791270</v>
-      </c>
-      <c r="E15" t="n">
-        <v>474674</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1646848</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -6200,2175 +6200,2175 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 687 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -155 千股)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>198488</v>
+        <v>-147378</v>
       </c>
       <c r="D16" t="n">
-        <v>-3737139</v>
+        <v>-1105337</v>
       </c>
       <c r="E16" t="n">
-        <v>-433454</v>
+        <v>87218</v>
       </c>
       <c r="F16" t="n">
-        <v>-4424081</v>
+        <v>-950289</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>辛耘</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -217 千股)</t>
+          <t>📈 20d 巨變(加碼 1,077 千股)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>87218</v>
+        <v>499335</v>
       </c>
       <c r="D17" t="n">
-        <v>-950289</v>
+        <v>-2659816</v>
       </c>
       <c r="E17" t="n">
-        <v>-670227</v>
+        <v>198488</v>
       </c>
       <c r="F17" t="n">
-        <v>-733375</v>
+        <v>-3737139</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>健鼎</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 65 千股)</t>
+          <t>📈 20d 巨變(加碼 137 千股)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>111538</v>
+        <v>-19851</v>
       </c>
       <c r="D18" t="n">
-        <v>154496</v>
+        <v>-2998427</v>
       </c>
       <c r="E18" t="n">
-        <v>137400</v>
+        <v>-331369</v>
       </c>
       <c r="F18" t="n">
-        <v>89176</v>
+        <v>-3135895</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>佳必琪</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 11 千股)</t>
+          <t>📈 20d 巨變(加碼 38 千股)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-331369</v>
+        <v>144544</v>
       </c>
       <c r="D19" t="n">
-        <v>-3135895</v>
+        <v>192234</v>
       </c>
       <c r="E19" t="n">
-        <v>-94876</v>
+        <v>111538</v>
       </c>
       <c r="F19" t="n">
-        <v>-3146856</v>
+        <v>154496</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>川湖</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -984 千股)</t>
+          <t>📈 20d 巨變(加碼 149 千股)</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2849155</v>
+        <v>-396606</v>
       </c>
       <c r="D20" t="n">
-        <v>5020631</v>
+        <v>-1697244</v>
       </c>
       <c r="E20" t="n">
-        <v>2915041</v>
+        <v>-289627</v>
       </c>
       <c r="F20" t="n">
-        <v>6004719</v>
+        <v>-1846112</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>崇越</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -68 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,079 千股)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-289627</v>
+        <v>1317827</v>
       </c>
       <c r="D21" t="n">
-        <v>-1846112</v>
+        <v>2637838</v>
       </c>
       <c r="E21" t="n">
-        <v>-166062</v>
+        <v>2807671</v>
       </c>
       <c r="F21" t="n">
-        <v>-1778232</v>
+        <v>3717175</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>中砂</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 436 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,291 千股)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>440790</v>
+        <v>1993012</v>
       </c>
       <c r="D22" t="n">
-        <v>-1782189</v>
+        <v>3729156</v>
       </c>
       <c r="E22" t="n">
-        <v>703272</v>
+        <v>2849155</v>
       </c>
       <c r="F22" t="n">
-        <v>-2217971</v>
+        <v>5020631</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 60 千股)</t>
+          <t>📈 20d 巨變(加碼 19 千股)</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-221563</v>
+        <v>57296</v>
       </c>
       <c r="D23" t="n">
-        <v>-878585</v>
+        <v>-1763497</v>
       </c>
       <c r="E23" t="n">
-        <v>-217721</v>
+        <v>440790</v>
       </c>
       <c r="F23" t="n">
-        <v>-938268</v>
+        <v>-1782189</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>華城</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 807 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,740 千股)</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2807671</v>
+        <v>-2053206</v>
       </c>
       <c r="D24" t="n">
-        <v>3717175</v>
+        <v>-2026035</v>
       </c>
       <c r="E24" t="n">
-        <v>1022304</v>
+        <v>-320398</v>
       </c>
       <c r="F24" t="n">
-        <v>2910209</v>
+        <v>-286297</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>建榮</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -440 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -480 千股)</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-320398</v>
+        <v>208489</v>
       </c>
       <c r="D25" t="n">
-        <v>-286297</v>
+        <v>-1358574</v>
       </c>
       <c r="E25" t="n">
-        <v>89729</v>
+        <v>-221563</v>
       </c>
       <c r="F25" t="n">
-        <v>153609</v>
+        <v>-878585</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>大立光</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -1,812 千股)</t>
+          <t>📉 20d 巨變(減碼 -23 千股)</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-96513</v>
+        <v>-6000</v>
       </c>
       <c r="D26" t="n">
-        <v>1352310</v>
+        <v>1251</v>
       </c>
       <c r="E26" t="n">
-        <v>1252892</v>
+        <v>-5142</v>
       </c>
       <c r="F26" t="n">
-        <v>3164534</v>
+        <v>24231</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>大車隊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -28 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,398 千股)</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>25240</v>
+        <v>-2503564</v>
       </c>
       <c r="D27" t="n">
-        <v>103239</v>
+        <v>-1045780</v>
       </c>
       <c r="E27" t="n">
-        <v>38293</v>
+        <v>-96513</v>
       </c>
       <c r="F27" t="n">
-        <v>131457</v>
+        <v>1352310</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>零壹</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -23 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -37 千股)</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-5142</v>
+        <v>315170</v>
       </c>
       <c r="D28" t="n">
-        <v>24231</v>
+        <v>-545392</v>
       </c>
       <c r="E28" t="n">
-        <v>5858</v>
+        <v>-23630</v>
       </c>
       <c r="F28" t="n">
-        <v>47231</v>
+        <v>-508392</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>湧德</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 414 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 249 千股)</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-23630</v>
+        <v>593705</v>
       </c>
       <c r="D29" t="n">
-        <v>-508392</v>
+        <v>15235938</v>
       </c>
       <c r="E29" t="n">
-        <v>-525084</v>
+        <v>-1858027</v>
       </c>
       <c r="F29" t="n">
-        <v>-922429</v>
+        <v>14987241</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -137 千股)</t>
+          <t>📈 20d 巨變(加碼 730 千股)</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-387994</v>
+        <v>326467</v>
       </c>
       <c r="D30" t="n">
-        <v>-474445</v>
+        <v>1030818</v>
       </c>
       <c r="E30" t="n">
-        <v>-202994</v>
+        <v>189351</v>
       </c>
       <c r="F30" t="n">
-        <v>-337555</v>
+        <v>300791</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>合機</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 469 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -786 千股)</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-1858027</v>
+        <v>-610007</v>
       </c>
       <c r="D31" t="n">
-        <v>14987241</v>
+        <v>-643428</v>
       </c>
       <c r="E31" t="n">
-        <v>-2328594</v>
+        <v>136326</v>
       </c>
       <c r="F31" t="n">
-        <v>14518305</v>
+        <v>142991</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>卜蜂</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -57 千股)</t>
+          <t>📈 20d 巨變(加碼 4,568 千股)</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>136326</v>
+        <v>3334681</v>
       </c>
       <c r="D32" t="n">
-        <v>142991</v>
+        <v>-14881883</v>
       </c>
       <c r="E32" t="n">
-        <v>400307</v>
+        <v>2289845</v>
       </c>
       <c r="F32" t="n">
-        <v>200001</v>
+        <v>-19450013</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>寶雅*</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,076 千股)</t>
+          <t>📉 20d 巨變(減碼 -22,494 千股)</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>189351</v>
+        <v>13308687</v>
       </c>
       <c r="D33" t="n">
-        <v>300791</v>
+        <v>53814945</v>
       </c>
       <c r="E33" t="n">
-        <v>128011</v>
+        <v>8196467</v>
       </c>
       <c r="F33" t="n">
-        <v>1376580</v>
+        <v>76309054</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 24,163 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -51 千股)</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>8196467</v>
+        <v>-63301</v>
       </c>
       <c r="D34" t="n">
-        <v>76309054</v>
+        <v>348522</v>
       </c>
       <c r="E34" t="n">
-        <v>-2309475</v>
+        <v>23077</v>
       </c>
       <c r="F34" t="n">
-        <v>52146302</v>
+        <v>399190</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>大統益</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 7,562 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -28 千股)</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2289845</v>
+        <v>-38953</v>
       </c>
       <c r="D35" t="n">
-        <v>-19450013</v>
+        <v>75239</v>
       </c>
       <c r="E35" t="n">
-        <v>1167329</v>
+        <v>25240</v>
       </c>
       <c r="F35" t="n">
-        <v>-27012390</v>
+        <v>103239</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>崇友</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 20 千股)</t>
+          <t>📈 20d 巨變(加碼 122 千股)</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>23077</v>
+        <v>-11432</v>
       </c>
       <c r="D36" t="n">
-        <v>399190</v>
+        <v>365790</v>
       </c>
       <c r="E36" t="n">
-        <v>122250</v>
+        <v>-341652</v>
       </c>
       <c r="F36" t="n">
-        <v>379221</v>
+        <v>244040</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>豐藝</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 181 千股)</t>
+          <t>📈 20d 巨變(加碼 35 千股)</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-341652</v>
+        <v>-98786</v>
       </c>
       <c r="D37" t="n">
-        <v>244040</v>
+        <v>-487525</v>
       </c>
       <c r="E37" t="n">
-        <v>-323860</v>
+        <v>-125845</v>
       </c>
       <c r="F37" t="n">
-        <v>63046</v>
+        <v>-522513</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>智冠</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 12 千股)</t>
+          <t>📉 20d 巨變(減碼 -5 千股)</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-125845</v>
+        <v>13000</v>
       </c>
       <c r="D38" t="n">
-        <v>-522513</v>
+        <v>55000</v>
       </c>
       <c r="E38" t="n">
-        <v>-150071</v>
+        <v>13000</v>
       </c>
       <c r="F38" t="n">
-        <v>-534926</v>
+        <v>60000</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>方土霖</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 72 千股)</t>
+          <t>📉 20d 巨變(減碼 -27 千股)</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-43361</v>
+        <v>-198865</v>
       </c>
       <c r="D39" t="n">
-        <v>366611</v>
+        <v>-131163</v>
       </c>
       <c r="E39" t="n">
-        <v>-80511</v>
+        <v>-118250</v>
       </c>
       <c r="F39" t="n">
-        <v>294481</v>
+        <v>-104203</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>華景電</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -53 千股)</t>
+          <t>📉 20d 巨變(減碼 -123 千股)</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-118250</v>
+        <v>-203949</v>
       </c>
       <c r="D40" t="n">
-        <v>-104203</v>
+        <v>-615273</v>
       </c>
       <c r="E40" t="n">
-        <v>-143295</v>
+        <v>-341000</v>
       </c>
       <c r="F40" t="n">
-        <v>-51670</v>
+        <v>-491807</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>穎崴</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -358 千股)</t>
+          <t>📉 20d 巨變(減碼 -7,722 千股)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-341000</v>
+        <v>12549340</v>
       </c>
       <c r="D41" t="n">
-        <v>-491807</v>
+        <v>86797673</v>
       </c>
       <c r="E41" t="n">
-        <v>-556359</v>
+        <v>10985380</v>
       </c>
       <c r="F41" t="n">
-        <v>-134280</v>
+        <v>94519818</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 4,795 千股)</t>
+          <t>📉 20d 巨變(減碼 -84 千股)</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>10985380</v>
+        <v>-54361</v>
       </c>
       <c r="D42" t="n">
-        <v>94519818</v>
+        <v>282461</v>
       </c>
       <c r="E42" t="n">
-        <v>10305477</v>
+        <v>-43361</v>
       </c>
       <c r="F42" t="n">
-        <v>89724532</v>
+        <v>366611</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>八方雲集</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -62 千股)</t>
+          <t>📈 20d 巨變(加碼 340 千股)</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-370000</v>
+        <v>1295726</v>
       </c>
       <c r="D43" t="n">
-        <v>-1094333</v>
+        <v>6943957</v>
       </c>
       <c r="E43" t="n">
-        <v>-331000</v>
+        <v>237004</v>
       </c>
       <c r="F43" t="n">
-        <v>-1032635</v>
+        <v>6604004</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 1,215 千股)</t>
+          <t>📉 20d 巨變(減碼 -161 千股)</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>237004</v>
+        <v>497924</v>
       </c>
       <c r="D44" t="n">
-        <v>6604004</v>
+        <v>-620937</v>
       </c>
       <c r="E44" t="n">
-        <v>-176658</v>
+        <v>539287</v>
       </c>
       <c r="F44" t="n">
-        <v>5389484</v>
+        <v>-459547</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>亞力</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 40 千股)</t>
+          <t>📉 20d 巨變(減碼 -56 千股)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>539287</v>
+        <v>-351000</v>
       </c>
       <c r="D45" t="n">
-        <v>-459547</v>
+        <v>-1150333</v>
       </c>
       <c r="E45" t="n">
-        <v>922146</v>
+        <v>-370000</v>
       </c>
       <c r="F45" t="n">
-        <v>-499360</v>
+        <v>-1094333</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>聯合</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 111 千股)</t>
+          <t>📉 20d 巨變(減碼 -78 千股)</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>117620</v>
+        <v>85895</v>
       </c>
       <c r="D46" t="n">
-        <v>-390098</v>
+        <v>423169</v>
       </c>
       <c r="E46" t="n">
-        <v>110379</v>
+        <v>123187</v>
       </c>
       <c r="F46" t="n">
-        <v>-501339</v>
+        <v>501327</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>大綜</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -8 千股)</t>
+          <t>📈 20d 巨變(加碼 1,971 千股)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>123187</v>
+        <v>3558955</v>
       </c>
       <c r="D47" t="n">
-        <v>501327</v>
+        <v>2961109</v>
       </c>
       <c r="E47" t="n">
-        <v>277912</v>
+        <v>3694404</v>
       </c>
       <c r="F47" t="n">
-        <v>509718</v>
+        <v>990413</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>台燿</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 628 千股)</t>
+          <t>📈 20d 巨變(加碼 274 千股)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3694404</v>
+        <v>2841999</v>
       </c>
       <c r="D48" t="n">
-        <v>990413</v>
+        <v>4486460</v>
       </c>
       <c r="E48" t="n">
-        <v>3883222</v>
+        <v>2172040</v>
       </c>
       <c r="F48" t="n">
-        <v>362528</v>
+        <v>4212847</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>立隆電</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 786 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,121 千股)</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2172040</v>
+        <v>-4606790</v>
       </c>
       <c r="D49" t="n">
-        <v>4212847</v>
+        <v>371360</v>
       </c>
       <c r="E49" t="n">
-        <v>2349962</v>
+        <v>-316461</v>
       </c>
       <c r="F49" t="n">
-        <v>3426406</v>
+        <v>1492025</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -1,895 千股)</t>
+          <t>📈 20d 巨變(加碼 62 千股)</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-316461</v>
+        <v>-4238594</v>
       </c>
       <c r="D50" t="n">
-        <v>1492025</v>
+        <v>-1646735</v>
       </c>
       <c r="E50" t="n">
-        <v>12359</v>
+        <v>-4812156</v>
       </c>
       <c r="F50" t="n">
-        <v>3386702</v>
+        <v>-1708334</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>玉晶光</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,818 千股)</t>
+          <t>📈 20d 巨變(加碼 112 千股)</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-4812156</v>
+        <v>-2214029</v>
       </c>
       <c r="D51" t="n">
-        <v>-1708334</v>
+        <v>-3179969</v>
       </c>
       <c r="E51" t="n">
-        <v>-2961909</v>
+        <v>-2803263</v>
       </c>
       <c r="F51" t="n">
-        <v>109850</v>
+        <v>-3292463</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>世芯-KY</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,746 千股)</t>
+          <t>📉 20d 巨變(減碼 -20,587 千股)</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-2803263</v>
+        <v>5643449</v>
       </c>
       <c r="D52" t="n">
-        <v>-3292463</v>
+        <v>-3389805</v>
       </c>
       <c r="E52" t="n">
-        <v>-617526</v>
+        <v>27960674</v>
       </c>
       <c r="F52" t="n">
-        <v>-546190</v>
+        <v>17197528</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 16,703 千股)</t>
+          <t>📉 20d 巨變(減碼 -9,662 千股)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-5641323</v>
+        <v>7661571</v>
       </c>
       <c r="D53" t="n">
-        <v>-26946699</v>
+        <v>31195069</v>
       </c>
       <c r="E53" t="n">
-        <v>18470978</v>
+        <v>26025516</v>
       </c>
       <c r="F53" t="n">
-        <v>-43649480</v>
+        <v>40857502</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -3,076 千股)</t>
+          <t>📈 20d 巨變(加碼 6,045 千股)</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>27960674</v>
+        <v>-8378962</v>
       </c>
       <c r="D54" t="n">
-        <v>17197528</v>
+        <v>-20902043</v>
       </c>
       <c r="E54" t="n">
-        <v>41493231</v>
+        <v>-5641323</v>
       </c>
       <c r="F54" t="n">
-        <v>20273872</v>
+        <v>-26946699</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -11,070 千股)</t>
+          <t>📈 20d 巨變(加碼 426 千股)</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>26025516</v>
+        <v>-1353958</v>
       </c>
       <c r="D55" t="n">
-        <v>40857502</v>
+        <v>2743730</v>
       </c>
       <c r="E55" t="n">
-        <v>30496334</v>
+        <v>-1699437</v>
       </c>
       <c r="F55" t="n">
-        <v>51927884</v>
+        <v>2317442</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>鈊象</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -642 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,255 千股)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-1699437</v>
+        <v>282726</v>
       </c>
       <c r="D56" t="n">
-        <v>2317442</v>
+        <v>1751207</v>
       </c>
       <c r="E56" t="n">
-        <v>-864969</v>
+        <v>1079565</v>
       </c>
       <c r="F56" t="n">
-        <v>2959291</v>
+        <v>3006460</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>士電</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -324 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -338 千股)</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>1079565</v>
+        <v>-15672</v>
       </c>
       <c r="D57" t="n">
-        <v>3006460</v>
+        <v>24972</v>
       </c>
       <c r="E57" t="n">
-        <v>1813519</v>
+        <v>20257</v>
       </c>
       <c r="F57" t="n">
-        <v>3330020</v>
+        <v>362864</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>達欣工</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -24 千股)</t>
+          <t>📉 20d 巨變(減碼 -11 千股)</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>20257</v>
+        <v>-714104</v>
       </c>
       <c r="D58" t="n">
-        <v>362864</v>
+        <v>-3167465</v>
       </c>
       <c r="E58" t="n">
-        <v>67521</v>
+        <v>-735694</v>
       </c>
       <c r="F58" t="n">
-        <v>387220</v>
+        <v>-3156755</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>鉅祥</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 563 千股)</t>
+          <t>📉 20d 巨變(減碼 -49 千股)</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-735694</v>
+        <v>-192103</v>
       </c>
       <c r="D59" t="n">
-        <v>-3156755</v>
+        <v>413793</v>
       </c>
       <c r="E59" t="n">
-        <v>-1000103</v>
+        <v>-162311</v>
       </c>
       <c r="F59" t="n">
-        <v>-3720146</v>
+        <v>463056</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>普萊德</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -27 千股)</t>
+          <t>📉 20d 巨變(減碼 -340 千股)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-162311</v>
+        <v>183681</v>
       </c>
       <c r="D60" t="n">
-        <v>463056</v>
+        <v>-1788320</v>
       </c>
       <c r="E60" t="n">
-        <v>-129339</v>
+        <v>237681</v>
       </c>
       <c r="F60" t="n">
-        <v>490182</v>
+        <v>-1448320</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>勝一</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -84 千股)</t>
+          <t>📉 20d 巨變(減碼 -302 千股)</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>237681</v>
+        <v>-217110</v>
       </c>
       <c r="D61" t="n">
-        <v>-1448320</v>
+        <v>-1385941</v>
       </c>
       <c r="E61" t="n">
-        <v>324099</v>
+        <v>-406723</v>
       </c>
       <c r="F61" t="n">
-        <v>-1364376</v>
+        <v>-1083994</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>信立</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -72 千股)</t>
+          <t>📈 20d 巨變(加碼 136 千股)</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-59666</v>
+        <v>-251769</v>
       </c>
       <c r="D62" t="n">
-        <v>-543061</v>
+        <v>52145</v>
       </c>
       <c r="E62" t="n">
-        <v>-89346</v>
+        <v>-371745</v>
       </c>
       <c r="F62" t="n">
-        <v>-471097</v>
+        <v>-84178</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>祥碩</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 122 千股)</t>
+          <t>📈 20d 巨變(加碼 1,291 千股)</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-371745</v>
+        <v>-382481</v>
       </c>
       <c r="D63" t="n">
-        <v>-84178</v>
+        <v>-3009982</v>
       </c>
       <c r="E63" t="n">
-        <v>-395584</v>
+        <v>-375023</v>
       </c>
       <c r="F63" t="n">
-        <v>-205907</v>
+        <v>-4301050</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 341 千股)</t>
+          <t>📈 20d 巨變(加碼 220 千股)</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-406723</v>
+        <v>-562452</v>
       </c>
       <c r="D64" t="n">
-        <v>-1083994</v>
+        <v>-3750899</v>
       </c>
       <c r="E64" t="n">
-        <v>-571217</v>
+        <v>-2905006</v>
       </c>
       <c r="F64" t="n">
-        <v>-1424794</v>
+        <v>-3971344</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>華星光</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -701 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -175 千股)</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-375023</v>
+        <v>64559</v>
       </c>
       <c r="D65" t="n">
-        <v>-4301050</v>
+        <v>-708781</v>
       </c>
       <c r="E65" t="n">
-        <v>-876670</v>
+        <v>-72098</v>
       </c>
       <c r="F65" t="n">
-        <v>-3599703</v>
+        <v>-533829</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>聯亞</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 100 千股)</t>
+          <t>📈 20d 巨變(加碼 471 千股)</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-2905006</v>
+        <v>-1531836</v>
       </c>
       <c r="D66" t="n">
-        <v>-3971344</v>
+        <v>-121630</v>
       </c>
       <c r="E66" t="n">
-        <v>-2000662</v>
+        <v>-1078273</v>
       </c>
       <c r="F66" t="n">
-        <v>-4071005</v>
+        <v>-592447</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>宇瞻</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 33 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,489 千股)</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-72098</v>
+        <v>-2408322</v>
       </c>
       <c r="D67" t="n">
-        <v>-533829</v>
+        <v>-1186464</v>
       </c>
       <c r="E67" t="n">
-        <v>554408</v>
+        <v>-885577</v>
       </c>
       <c r="F67" t="n">
-        <v>-566816</v>
+        <v>302106</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -564 千股)</t>
+          <t>📉 20d 巨變(減碼 -5,225 千股)</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-885577</v>
+        <v>-1028944</v>
       </c>
       <c r="D68" t="n">
-        <v>302106</v>
+        <v>28783401</v>
       </c>
       <c r="E68" t="n">
-        <v>-731238</v>
+        <v>-1956622</v>
       </c>
       <c r="F68" t="n">
-        <v>866006</v>
+        <v>34007934</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,167 千股)</t>
+          <t>📈 20d 巨變(加碼 1,173 千股)</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-1078273</v>
+        <v>3043389</v>
       </c>
       <c r="D69" t="n">
-        <v>-592447</v>
+        <v>-986949</v>
       </c>
       <c r="E69" t="n">
-        <v>-1329359</v>
+        <v>1754411</v>
       </c>
       <c r="F69" t="n">
-        <v>-1759709</v>
+        <v>-2159820</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -5,968 千股)</t>
+          <t>📉 20d 巨變(減碼 -10,309 千股)</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-1956622</v>
+        <v>-83197181</v>
       </c>
       <c r="D70" t="n">
-        <v>34007934</v>
+        <v>-114097650</v>
       </c>
       <c r="E70" t="n">
-        <v>10214227</v>
+        <v>-80785282</v>
       </c>
       <c r="F70" t="n">
-        <v>39976020</v>
+        <v>-103788976</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 985 千股)</t>
+          <t>📉 20d 巨變(減碼 -445 千股)</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1754411</v>
+        <v>-5168732</v>
       </c>
       <c r="D71" t="n">
-        <v>-2159820</v>
+        <v>-6017077</v>
       </c>
       <c r="E71" t="n">
-        <v>959066</v>
+        <v>-5728973</v>
       </c>
       <c r="F71" t="n">
-        <v>-3144835</v>
+        <v>-5572346</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 3,815 千股)</t>
+          <t>📉 20d 巨變(減碼 -62 千股)</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-80785282</v>
+        <v>-29794</v>
       </c>
       <c r="D72" t="n">
-        <v>-103788976</v>
+        <v>-263388</v>
       </c>
       <c r="E72" t="n">
-        <v>-60119017</v>
+        <v>-26454</v>
       </c>
       <c r="F72" t="n">
-        <v>-107603778</v>
+        <v>-201203</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>德昌</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 680 千股)</t>
+          <t>📉 20d 巨變(減碼 -17 千股)</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-12413589</v>
+        <v>390024</v>
       </c>
       <c r="D73" t="n">
-        <v>-12240223</v>
+        <v>698576</v>
       </c>
       <c r="E73" t="n">
-        <v>-6937120</v>
+        <v>376060</v>
       </c>
       <c r="F73" t="n">
-        <v>-12919781</v>
+        <v>715596</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>億泰</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -11 千股)</t>
+          <t>📈 20d 巨變(加碼 2,242 千股)</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-26454</v>
+        <v>-1600522</v>
       </c>
       <c r="D74" t="n">
-        <v>-201203</v>
+        <v>-9998157</v>
       </c>
       <c r="E74" t="n">
-        <v>-60828</v>
+        <v>-12413589</v>
       </c>
       <c r="F74" t="n">
-        <v>-190071</v>
+        <v>-12240223</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,371 千股)</t>
+          <t>📈 20d 巨變(加碼 577 千股)</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-5728973</v>
+        <v>-1693434</v>
       </c>
       <c r="D75" t="n">
-        <v>-5572346</v>
+        <v>-9643401</v>
       </c>
       <c r="E75" t="n">
-        <v>-4170843</v>
+        <v>-1759434</v>
       </c>
       <c r="F75" t="n">
-        <v>-4201007</v>
+        <v>-10220401</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>智易</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 81 千股)</t>
+          <t>📉 20d 巨變(減碼 -103 千股)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>376060</v>
+        <v>-1270205</v>
       </c>
       <c r="D76" t="n">
-        <v>715596</v>
+        <v>167228</v>
       </c>
       <c r="E76" t="n">
-        <v>467993</v>
+        <v>-2012472</v>
       </c>
       <c r="F76" t="n">
-        <v>634546</v>
+        <v>270205</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 39 千股)</t>
+          <t>📈 20d 巨變(加碼 135 千股)</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>33000</v>
+        <v>-1213098</v>
       </c>
       <c r="D77" t="n">
-        <v>-70550</v>
+        <v>-2857317</v>
       </c>
       <c r="E77" t="n">
-        <v>9000</v>
+        <v>-1441098</v>
       </c>
       <c r="F77" t="n">
-        <v>-109550</v>
+        <v>-2992140</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>原相</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 838 千股)</t>
+          <t>📈 20d 巨變(加碼 11,488 千股)</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-1759434</v>
+        <v>-18026110</v>
       </c>
       <c r="D78" t="n">
-        <v>-10220401</v>
+        <v>-7043631</v>
       </c>
       <c r="E78" t="n">
-        <v>-1818692</v>
+        <v>-29474185</v>
       </c>
       <c r="F78" t="n">
-        <v>-11058748</v>
+        <v>-18531211</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 29 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 372 千股)</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-1441098</v>
+        <v>474984</v>
       </c>
       <c r="D79" t="n">
-        <v>-2992140</v>
+        <v>-1784925</v>
       </c>
       <c r="E79" t="n">
-        <v>-1452966</v>
+        <v>-116797</v>
       </c>
       <c r="F79" t="n">
-        <v>-3021480</v>
+        <v>-2156849</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>精測</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -773 千股)</t>
+          <t>📈 20d 巨變(加碼 9,216 千股)</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-2012472</v>
+        <v>-17122734</v>
       </c>
       <c r="D80" t="n">
-        <v>270205</v>
+        <v>-25838539</v>
       </c>
       <c r="E80" t="n">
-        <v>-513211</v>
+        <v>-19911926</v>
       </c>
       <c r="F80" t="n">
-        <v>1042911</v>
+        <v>-35054452</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 290 千股)</t>
+          <t>📈 20d 巨變(加碼 154 千股)</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-116797</v>
+        <v>493411</v>
       </c>
       <c r="D81" t="n">
-        <v>-2156849</v>
+        <v>514169</v>
       </c>
       <c r="E81" t="n">
-        <v>-887855</v>
+        <v>362421</v>
       </c>
       <c r="F81" t="n">
-        <v>-2446814</v>
+        <v>360169</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>東科-KY</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -14,829 千股)</t>
+          <t>📉 20d 巨變(減碼 -25 千股)</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-29474185</v>
+        <v>-67000</v>
       </c>
       <c r="D82" t="n">
-        <v>-18531211</v>
+        <v>414009</v>
       </c>
       <c r="E82" t="n">
-        <v>-16437846</v>
+        <v>-94019</v>
       </c>
       <c r="F82" t="n">
-        <v>-3702035</v>
+        <v>439009</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -6,823 千股)</t>
+          <t>📉 20d 巨變(減碼 -303 千股)</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-19911926</v>
+        <v>-754085</v>
       </c>
       <c r="D83" t="n">
-        <v>-35054452</v>
+        <v>-913379</v>
       </c>
       <c r="E83" t="n">
-        <v>10246775</v>
+        <v>-699308</v>
       </c>
       <c r="F83" t="n">
-        <v>-28231647</v>
+        <v>-610093</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 215 千股)</t>
+          <t>📈 20d 巨變(加碼 911 千股)</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-699308</v>
+        <v>1555751</v>
       </c>
       <c r="D84" t="n">
-        <v>-610093</v>
+        <v>368137</v>
       </c>
       <c r="E84" t="n">
-        <v>-641485</v>
+        <v>1661861</v>
       </c>
       <c r="F84" t="n">
-        <v>-824993</v>
+        <v>-542475</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 213 千股)</t>
+          <t>📈 20d 巨變(加碼 283 千股)</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>362421</v>
+        <v>-1970432</v>
       </c>
       <c r="D85" t="n">
-        <v>360169</v>
+        <v>-18109219</v>
       </c>
       <c r="E85" t="n">
-        <v>64521</v>
+        <v>-2533523</v>
       </c>
       <c r="F85" t="n">
-        <v>147169</v>
+        <v>-18392310</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>宏捷科</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -49 千股)</t>
+          <t>📈 20d 巨變(加碼 17 千股)</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-94019</v>
+        <v>18000</v>
       </c>
       <c r="D86" t="n">
-        <v>439009</v>
+        <v>-53550</v>
       </c>
       <c r="E86" t="n">
-        <v>35746</v>
+        <v>33000</v>
       </c>
       <c r="F86" t="n">
-        <v>488009</v>
+        <v>-70550</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>友輝</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 2,703 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -960 千股)</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1661861</v>
+        <v>1057185</v>
       </c>
       <c r="D87" t="n">
-        <v>-542475</v>
+        <v>-986890</v>
       </c>
       <c r="E87" t="n">
-        <v>-399669</v>
+        <v>-581347</v>
       </c>
       <c r="F87" t="n">
-        <v>-3245178</v>
+        <v>-26443</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>研華</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 11 千股)</t>
+          <t>📈 20d 巨變(加碼 13,336 千股)</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-2533523</v>
+        <v>36088567</v>
       </c>
       <c r="D88" t="n">
-        <v>-18392310</v>
+        <v>40297762</v>
       </c>
       <c r="E88" t="n">
-        <v>-3066027</v>
+        <v>25199166</v>
       </c>
       <c r="F88" t="n">
-        <v>-18402957</v>
+        <v>26962211</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 290 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -104 千股)</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-581347</v>
+        <v>-16098</v>
       </c>
       <c r="D89" t="n">
-        <v>-26443</v>
+        <v>-8690</v>
       </c>
       <c r="E89" t="n">
-        <v>-456573</v>
+        <v>135934</v>
       </c>
       <c r="F89" t="n">
-        <v>-316208</v>
+        <v>95526</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>竹陞科技</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 14,199 千股)</t>
+          <t>📉 20d 巨變(減碼 -22 千股)</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>25199166</v>
+        <v>74065</v>
       </c>
       <c r="D90" t="n">
-        <v>26962211</v>
+        <v>121635</v>
       </c>
       <c r="E90" t="n">
-        <v>16846399</v>
+        <v>99860</v>
       </c>
       <c r="F90" t="n">
-        <v>12762927</v>
+        <v>143635</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>安碁資訊</t>
         </is>
       </c>
     </row>
@@ -8380,20 +8380,20 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,820 千股)</t>
+          <t>📈 20d 巨變(加碼 4,981 千股)</t>
         </is>
       </c>
       <c r="C91" t="n">
+        <v>-606122</v>
+      </c>
+      <c r="D91" t="n">
+        <v>-9321751</v>
+      </c>
+      <c r="E91" t="n">
         <v>-723700</v>
       </c>
-      <c r="D91" t="n">
+      <c r="F91" t="n">
         <v>-14302501</v>
-      </c>
-      <c r="E91" t="n">
-        <v>-667302</v>
-      </c>
-      <c r="F91" t="n">
-        <v>-17122012</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -8409,20 +8409,20 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -140 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,050 千股)</t>
         </is>
       </c>
       <c r="C92" t="n">
+        <v>5298555</v>
+      </c>
+      <c r="D92" t="n">
+        <v>23278823</v>
+      </c>
+      <c r="E92" t="n">
         <v>3157335</v>
       </c>
-      <c r="D92" t="n">
+      <c r="F92" t="n">
         <v>24329068</v>
-      </c>
-      <c r="E92" t="n">
-        <v>2751780</v>
-      </c>
-      <c r="F92" t="n">
-        <v>24468891</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -8433,319 +8433,261 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 99 千股)</t>
+          <t>📉 20d 巨變(減碼 -16 千股)</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>135934</v>
+        <v>-148702</v>
       </c>
       <c r="D93" t="n">
-        <v>95526</v>
+        <v>-113045</v>
       </c>
       <c r="E93" t="n">
-        <v>43226</v>
+        <v>-115412</v>
       </c>
       <c r="F93" t="n">
-        <v>-3182</v>
+        <v>-97045</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>六方科-KY</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 114 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -33,680 千股)</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>99860</v>
+        <v>-44426223</v>
       </c>
       <c r="D94" t="n">
-        <v>143635</v>
+        <v>-5173895</v>
       </c>
       <c r="E94" t="n">
-        <v>-11153</v>
+        <v>45227120</v>
       </c>
       <c r="F94" t="n">
-        <v>29502</v>
+        <v>28506329</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -27 千股)</t>
+          <t>📉 20d 巨變(減碼 -454 千股)</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-115412</v>
+        <v>1223096</v>
       </c>
       <c r="D95" t="n">
-        <v>-97045</v>
+        <v>5083594</v>
       </c>
       <c r="E95" t="n">
-        <v>-93269</v>
+        <v>3401305</v>
       </c>
       <c r="F95" t="n">
-        <v>-70045</v>
+        <v>5537305</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,237 千股)</t>
+          <t>📉 20d 巨變(減碼 -33 千股)</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3401305</v>
+        <v>-176732</v>
       </c>
       <c r="D96" t="n">
-        <v>5537305</v>
+        <v>1197177</v>
       </c>
       <c r="E96" t="n">
-        <v>4677849</v>
+        <v>-52278</v>
       </c>
       <c r="F96" t="n">
-        <v>7774312</v>
+        <v>1229728</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>創意</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -87,069 千股)</t>
+          <t>📉 20d 巨變(減碼 -50 千股)</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>45227120</v>
+        <v>-1217245</v>
       </c>
       <c r="D97" t="n">
-        <v>28506329</v>
+        <v>-9176008</v>
       </c>
       <c r="E97" t="n">
-        <v>81759531</v>
+        <v>-1985731</v>
       </c>
       <c r="F97" t="n">
-        <v>115574939</v>
+        <v>-9125837</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>緯穎</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -374 千股)</t>
+          <t>📉 20d 巨變(減碼 -25 千股)</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-52278</v>
+        <v>90500</v>
       </c>
       <c r="D98" t="n">
-        <v>1229728</v>
+        <v>244134</v>
       </c>
       <c r="E98" t="n">
-        <v>178278</v>
+        <v>151301</v>
       </c>
       <c r="F98" t="n">
-        <v>1604115</v>
+        <v>269458</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>信驊</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -524 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 946 千股)</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-1985731</v>
+        <v>539018</v>
       </c>
       <c r="D99" t="n">
-        <v>-9125837</v>
+        <v>-8796536</v>
       </c>
       <c r="E99" t="n">
-        <v>-1917531</v>
+        <v>-611183</v>
       </c>
       <c r="F99" t="n">
-        <v>-8602098</v>
+        <v>-9742886</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>金像電</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -70 千股)</t>
+          <t>📈 20d 巨變(加碼 156 千股)</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>151301</v>
+        <v>434157</v>
       </c>
       <c r="D100" t="n">
-        <v>269458</v>
+        <v>-3154601</v>
       </c>
       <c r="E100" t="n">
-        <v>158382</v>
+        <v>392272</v>
       </c>
       <c r="F100" t="n">
-        <v>339602</v>
+        <v>-3310295</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>高技</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 3,006 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 281 千股)</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-611183</v>
+        <v>135533</v>
       </c>
       <c r="D101" t="n">
-        <v>-9742886</v>
+        <v>-1079947</v>
       </c>
       <c r="E101" t="n">
-        <v>-3766557</v>
+        <v>-224865</v>
       </c>
       <c r="F101" t="n">
-        <v>-12748994</v>
+        <v>-1360822</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>金像電</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -33 千股)</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>-224865</v>
-      </c>
-      <c r="D102" t="n">
-        <v>-1360822</v>
-      </c>
-      <c r="E102" t="n">
-        <v>-535050</v>
-      </c>
-      <c r="F102" t="n">
-        <v>-1328176</v>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
           <t>萬潤</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>5439</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 1,190 千股)</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>392272</v>
-      </c>
-      <c r="D103" t="n">
-        <v>-3310295</v>
-      </c>
-      <c r="E103" t="n">
-        <v>909</v>
-      </c>
-      <c r="F103" t="n">
-        <v>-4500046</v>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>高技</t>
         </is>
       </c>
     </row>

--- a/data/台股_外資雷達.xlsx
+++ b/data/台股_外資雷達.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12549</v>
+        <v>11960</v>
       </c>
       <c r="D2" t="n">
-        <v>86798</v>
+        <v>86253</v>
       </c>
       <c r="E2" t="n">
-        <v>173821</v>
+        <v>187103</v>
       </c>
       <c r="F2" t="n">
-        <v>855</v>
+        <v>823</v>
       </c>
       <c r="G2" t="n">
-        <v>6190</v>
+        <v>5944</v>
       </c>
       <c r="H2" t="n">
-        <v>-3278</v>
+        <v>-3428</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -538,31 +538,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13309</v>
+        <v>42107</v>
       </c>
       <c r="D3" t="n">
-        <v>53815</v>
+        <v>54138</v>
       </c>
       <c r="E3" t="n">
-        <v>567203</v>
+        <v>114504</v>
       </c>
       <c r="F3" t="n">
-        <v>-368</v>
+        <v>1165</v>
       </c>
       <c r="G3" t="n">
-        <v>11511</v>
+        <v>854</v>
       </c>
       <c r="H3" t="n">
-        <v>-4841</v>
+        <v>-208</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -571,11 +571,11 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -583,37 +583,37 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>36089</v>
+        <v>3200</v>
       </c>
       <c r="D4" t="n">
-        <v>40298</v>
+        <v>37669</v>
       </c>
       <c r="E4" t="n">
-        <v>92307</v>
+        <v>568591</v>
       </c>
       <c r="F4" t="n">
-        <v>593</v>
+        <v>2026</v>
       </c>
       <c r="G4" t="n">
-        <v>5269</v>
+        <v>15009</v>
       </c>
       <c r="H4" t="n">
-        <v>-356</v>
+        <v>-4258</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -622,11 +622,11 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -634,37 +634,37 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>7662</v>
+        <v>13080</v>
       </c>
       <c r="D5" t="n">
-        <v>31195</v>
+        <v>29017</v>
       </c>
       <c r="E5" t="n">
-        <v>-36401</v>
+        <v>-19077</v>
       </c>
       <c r="F5" t="n">
-        <v>396</v>
+        <v>575</v>
       </c>
       <c r="G5" t="n">
-        <v>-21363</v>
+        <v>8107</v>
       </c>
       <c r="H5" t="n">
-        <v>890</v>
+        <v>-140</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -677,45 +677,45 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>🐌 龜速*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-1029</v>
+        <v>420</v>
       </c>
       <c r="D6" t="n">
-        <v>28783</v>
+        <v>25735</v>
       </c>
       <c r="E6" t="n">
-        <v>-20960</v>
+        <v>-41782</v>
       </c>
       <c r="F6" t="n">
-        <v>499</v>
+        <v>98</v>
       </c>
       <c r="G6" t="n">
-        <v>7994</v>
+        <v>-18458</v>
       </c>
       <c r="H6" t="n">
-        <v>-460</v>
+        <v>1035</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -728,15 +728,15 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速*</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5299</v>
+        <v>4152</v>
       </c>
       <c r="D7" t="n">
-        <v>23279</v>
+        <v>21136</v>
       </c>
       <c r="E7" t="n">
-        <v>75504</v>
+        <v>84343</v>
       </c>
       <c r="F7" t="n">
-        <v>1018</v>
+        <v>889</v>
       </c>
       <c r="G7" t="n">
-        <v>-1385</v>
+        <v>-953</v>
       </c>
       <c r="H7" t="n">
-        <v>-1014</v>
+        <v>-944</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -802,22 +802,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>594</v>
+        <v>309</v>
       </c>
       <c r="D8" t="n">
-        <v>15236</v>
+        <v>14692</v>
       </c>
       <c r="E8" t="n">
-        <v>23099</v>
+        <v>22787</v>
       </c>
       <c r="F8" t="n">
-        <v>-111</v>
+        <v>-132</v>
       </c>
       <c r="G8" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="H8" t="n">
-        <v>48</v>
+        <v>-80</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -853,22 +853,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-156</v>
+        <v>88</v>
       </c>
       <c r="D9" t="n">
-        <v>9445</v>
+        <v>9416</v>
       </c>
       <c r="E9" t="n">
-        <v>11819</v>
+        <v>11942</v>
       </c>
       <c r="F9" t="n">
-        <v>-681</v>
+        <v>-170</v>
       </c>
       <c r="G9" t="n">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="H9" t="n">
-        <v>762</v>
+        <v>667</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -904,22 +904,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1296</v>
+        <v>1067</v>
       </c>
       <c r="D10" t="n">
-        <v>6944</v>
+        <v>6942</v>
       </c>
       <c r="E10" t="n">
-        <v>14669</v>
+        <v>12827</v>
       </c>
       <c r="F10" t="n">
-        <v>-10</v>
+        <v>48</v>
       </c>
       <c r="G10" t="n">
-        <v>-1168</v>
+        <v>-1106</v>
       </c>
       <c r="H10" t="n">
-        <v>-165</v>
+        <v>-143</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -946,31 +946,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1223</v>
+        <v>3204</v>
       </c>
       <c r="D11" t="n">
-        <v>5084</v>
+        <v>4435</v>
       </c>
       <c r="E11" t="n">
-        <v>1491</v>
+        <v>13695</v>
       </c>
       <c r="F11" t="n">
-        <v>634</v>
+        <v>-2599</v>
       </c>
       <c r="G11" t="n">
-        <v>-1881</v>
+        <v>-6166</v>
       </c>
       <c r="H11" t="n">
-        <v>149</v>
+        <v>-49</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -979,49 +979,49 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2842</v>
+        <v>-48</v>
       </c>
       <c r="D12" t="n">
-        <v>4486</v>
+        <v>4282</v>
       </c>
       <c r="E12" t="n">
-        <v>11253</v>
+        <v>1604</v>
       </c>
       <c r="F12" t="n">
-        <v>-2641</v>
+        <v>428</v>
       </c>
       <c r="G12" t="n">
-        <v>-6180</v>
+        <v>-747</v>
       </c>
       <c r="H12" t="n">
-        <v>-73</v>
+        <v>408</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1030,19 +1030,19 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1057,22 +1057,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1993</v>
+        <v>1255</v>
       </c>
       <c r="D13" t="n">
-        <v>3729</v>
+        <v>3860</v>
       </c>
       <c r="E13" t="n">
-        <v>24001</v>
+        <v>24234</v>
       </c>
       <c r="F13" t="n">
-        <v>-58</v>
+        <v>-35</v>
       </c>
       <c r="G13" t="n">
-        <v>-580</v>
+        <v>-556</v>
       </c>
       <c r="H13" t="n">
-        <v>-362</v>
+        <v>-230</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1099,31 +1099,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3559</v>
+        <v>-1223</v>
       </c>
       <c r="D14" t="n">
-        <v>2961</v>
+        <v>2667</v>
       </c>
       <c r="E14" t="n">
-        <v>-1861</v>
+        <v>9912</v>
       </c>
       <c r="F14" t="n">
-        <v>-4721</v>
+        <v>37</v>
       </c>
       <c r="G14" t="n">
-        <v>-9546</v>
+        <v>-13437</v>
       </c>
       <c r="H14" t="n">
-        <v>-275</v>
+        <v>-116</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1136,45 +1136,45 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-1354</v>
+        <v>1041</v>
       </c>
       <c r="D15" t="n">
-        <v>2744</v>
+        <v>2316</v>
       </c>
       <c r="E15" t="n">
-        <v>9618</v>
+        <v>-402</v>
       </c>
       <c r="F15" t="n">
-        <v>51</v>
+        <v>506</v>
       </c>
       <c r="G15" t="n">
-        <v>-13449</v>
+        <v>-707</v>
       </c>
       <c r="H15" t="n">
-        <v>-104</v>
+        <v>-235</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1183,49 +1183,49 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1318</v>
+        <v>-7457</v>
       </c>
       <c r="D16" t="n">
-        <v>2638</v>
+        <v>2303</v>
       </c>
       <c r="E16" t="n">
-        <v>-259</v>
+        <v>10566</v>
       </c>
       <c r="F16" t="n">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="G16" t="n">
-        <v>-1206</v>
+        <v>1389</v>
       </c>
       <c r="H16" t="n">
-        <v>-278</v>
+        <v>220</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1234,11 +1234,11 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1261,22 +1261,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-15</v>
+        <v>-529</v>
       </c>
       <c r="D17" t="n">
-        <v>2173</v>
+        <v>2048</v>
       </c>
       <c r="E17" t="n">
-        <v>-1848</v>
+        <v>-1920</v>
       </c>
       <c r="F17" t="n">
-        <v>1350</v>
+        <v>773</v>
       </c>
       <c r="G17" t="n">
-        <v>-1132</v>
+        <v>-1206</v>
       </c>
       <c r="H17" t="n">
-        <v>140</v>
+        <v>201</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1303,31 +1303,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>272</v>
+        <v>1804</v>
       </c>
       <c r="D18" t="n">
-        <v>2052</v>
+        <v>2037</v>
       </c>
       <c r="E18" t="n">
-        <v>-395</v>
+        <v>6335</v>
       </c>
       <c r="F18" t="n">
-        <v>212</v>
+        <v>37</v>
       </c>
       <c r="G18" t="n">
-        <v>913</v>
+        <v>-126</v>
       </c>
       <c r="H18" t="n">
-        <v>-196</v>
+        <v>-104</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1340,45 +1340,45 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1176</v>
+        <v>-5</v>
       </c>
       <c r="D19" t="n">
-        <v>1876</v>
+        <v>1568</v>
       </c>
       <c r="E19" t="n">
-        <v>6111</v>
+        <v>373</v>
       </c>
       <c r="F19" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G19" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>-105</v>
+        <v>-70</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1387,49 +1387,49 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>283</v>
+        <v>2803</v>
       </c>
       <c r="D20" t="n">
-        <v>1751</v>
+        <v>1167</v>
       </c>
       <c r="E20" t="n">
-        <v>108</v>
+        <v>-2366</v>
       </c>
       <c r="F20" t="n">
-        <v>50</v>
+        <v>-4130</v>
       </c>
       <c r="G20" t="n">
-        <v>-0</v>
+        <v>-9440</v>
       </c>
       <c r="H20" t="n">
-        <v>-121</v>
+        <v>-294</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1442,45 +1442,45 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>126</v>
+        <v>-9</v>
       </c>
       <c r="D21" t="n">
-        <v>1340</v>
+        <v>1080</v>
       </c>
       <c r="E21" t="n">
-        <v>-2738</v>
+        <v>-494</v>
       </c>
       <c r="F21" t="n">
-        <v>-339</v>
+        <v>452</v>
       </c>
       <c r="G21" t="n">
-        <v>-2319</v>
+        <v>626</v>
       </c>
       <c r="H21" t="n">
-        <v>114</v>
+        <v>-41</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1497,41 +1497,41 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>合機</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>747</v>
+        <v>79</v>
       </c>
       <c r="D22" t="n">
-        <v>1213</v>
+        <v>992</v>
       </c>
       <c r="E22" t="n">
-        <v>4724</v>
+        <v>2165</v>
       </c>
       <c r="F22" t="n">
-        <v>-702</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>2032</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-250</v>
+        <v>-45</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1544,45 +1544,45 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-177</v>
+        <v>1890</v>
       </c>
       <c r="D23" t="n">
-        <v>1197</v>
+        <v>917</v>
       </c>
       <c r="E23" t="n">
-        <v>1297</v>
+        <v>294</v>
       </c>
       <c r="F23" t="n">
-        <v>621</v>
+        <v>45</v>
       </c>
       <c r="G23" t="n">
-        <v>1082</v>
+        <v>1597</v>
       </c>
       <c r="H23" t="n">
-        <v>-84</v>
+        <v>-119</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1595,45 +1595,45 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>326</v>
+        <v>805</v>
       </c>
       <c r="D24" t="n">
-        <v>1031</v>
+        <v>885</v>
       </c>
       <c r="E24" t="n">
-        <v>2252</v>
+        <v>5109</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>-170</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2575</v>
       </c>
       <c r="H24" t="n">
-        <v>-53</v>
+        <v>-226</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1646,45 +1646,45 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>390</v>
+        <v>230</v>
       </c>
       <c r="D25" t="n">
-        <v>699</v>
+        <v>866</v>
       </c>
       <c r="E25" t="n">
-        <v>202</v>
+        <v>-1397</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>-181</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>318</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1693,40 +1693,40 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>493</v>
+        <v>354</v>
       </c>
       <c r="D26" t="n">
-        <v>514</v>
+        <v>752</v>
       </c>
       <c r="E26" t="n">
-        <v>-377</v>
+        <v>234</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1735,7 +1735,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1752,41 +1752,41 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>86</v>
+        <v>-263</v>
       </c>
       <c r="D27" t="n">
-        <v>423</v>
+        <v>736</v>
       </c>
       <c r="E27" t="n">
-        <v>655</v>
+        <v>855</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>605</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1231</v>
       </c>
       <c r="H27" t="n">
-        <v>-29</v>
+        <v>-110</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1795,49 +1795,49 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-192</v>
+        <v>126</v>
       </c>
       <c r="D28" t="n">
-        <v>414</v>
+        <v>735</v>
       </c>
       <c r="E28" t="n">
-        <v>872</v>
+        <v>-2878</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>-426</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-2251</v>
       </c>
       <c r="H28" t="n">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1846,49 +1846,49 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-67</v>
+        <v>-1229</v>
       </c>
       <c r="D29" t="n">
-        <v>414</v>
+        <v>558</v>
       </c>
       <c r="E29" t="n">
-        <v>804</v>
+        <v>2273</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-1285</v>
       </c>
       <c r="H29" t="n">
-        <v>-0</v>
+        <v>-561</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1897,49 +1897,49 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-4607</v>
+        <v>516</v>
       </c>
       <c r="D30" t="n">
-        <v>371</v>
+        <v>546</v>
       </c>
       <c r="E30" t="n">
-        <v>12702</v>
+        <v>-366</v>
       </c>
       <c r="F30" t="n">
-        <v>488</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>1023</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1952,45 +1952,45 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1556</v>
+        <v>184</v>
       </c>
       <c r="D31" t="n">
-        <v>368</v>
+        <v>459</v>
       </c>
       <c r="E31" t="n">
-        <v>-9123</v>
+        <v>2915</v>
       </c>
       <c r="F31" t="n">
-        <v>-4</v>
+        <v>-7</v>
       </c>
       <c r="G31" t="n">
-        <v>-10</v>
+        <v>-32</v>
       </c>
       <c r="H31" t="n">
-        <v>737</v>
+        <v>-44</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1999,49 +1999,49 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-11</v>
+        <v>-45</v>
       </c>
       <c r="D32" t="n">
-        <v>366</v>
+        <v>404</v>
       </c>
       <c r="E32" t="n">
-        <v>3040</v>
+        <v>868</v>
       </c>
       <c r="F32" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-48</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-54</v>
+        <v>9</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2050,19 +2050,19 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="33">
@@ -2077,22 +2077,22 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-63</v>
+        <v>-119</v>
       </c>
       <c r="D33" t="n">
-        <v>349</v>
+        <v>271</v>
       </c>
       <c r="E33" t="n">
-        <v>889</v>
+        <v>911</v>
       </c>
       <c r="F33" t="n">
-        <v>-5</v>
+        <v>-21</v>
       </c>
       <c r="G33" t="n">
-        <v>-7</v>
+        <v>-22</v>
       </c>
       <c r="H33" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2119,31 +2119,31 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-54</v>
+        <v>-125</v>
       </c>
       <c r="D34" t="n">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="E34" t="n">
-        <v>1227</v>
+        <v>777</v>
       </c>
       <c r="F34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2152,19 +2152,19 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>🐌 龜速*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2179,22 +2179,22 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="D35" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E35" t="n">
-        <v>-296</v>
+        <v>-348</v>
       </c>
       <c r="F35" t="n">
-        <v>-56</v>
+        <v>-61</v>
       </c>
       <c r="G35" t="n">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="H35" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2209,31 +2209,31 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>693</v>
+        <v>85</v>
       </c>
       <c r="D36" t="n">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="E36" t="n">
-        <v>755</v>
+        <v>-729</v>
       </c>
       <c r="F36" t="n">
-        <v>-1126</v>
+        <v>-100</v>
       </c>
       <c r="G36" t="n">
-        <v>-2052</v>
+        <v>-346</v>
       </c>
       <c r="H36" t="n">
-        <v>-43</v>
+        <v>68</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2254,37 +2254,37 @@
         </is>
       </c>
       <c r="M36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>145</v>
+        <v>-68</v>
       </c>
       <c r="D37" t="n">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="E37" t="n">
-        <v>-746</v>
+        <v>1249</v>
       </c>
       <c r="F37" t="n">
-        <v>-303</v>
+        <v>8</v>
       </c>
       <c r="G37" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
-        <v>61</v>
+        <v>-1</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2297,45 +2297,45 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速*</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-59</v>
+        <v>-38</v>
       </c>
       <c r="D38" t="n">
-        <v>171</v>
+        <v>202</v>
       </c>
       <c r="E38" t="n">
-        <v>2480</v>
+        <v>716</v>
       </c>
       <c r="F38" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-5</v>
+        <v>-17</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2348,45 +2348,45 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-1270</v>
+        <v>-3356</v>
       </c>
       <c r="D39" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E39" t="n">
-        <v>2883</v>
+        <v>-723</v>
       </c>
       <c r="F39" t="n">
-        <v>-151</v>
+        <v>4292</v>
       </c>
       <c r="G39" t="n">
-        <v>-1510</v>
+        <v>9452</v>
       </c>
       <c r="H39" t="n">
-        <v>-546</v>
+        <v>62</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2395,49 +2395,49 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>74</v>
+        <v>-170</v>
       </c>
       <c r="D40" t="n">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="E40" t="n">
-        <v>183</v>
+        <v>1374</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>205</v>
       </c>
       <c r="H40" t="n">
-        <v>34</v>
+        <v>136</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2446,15 +2446,15 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M40" t="n">
@@ -2464,31 +2464,31 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-39</v>
+        <v>-49</v>
       </c>
       <c r="D41" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E41" t="n">
-        <v>748</v>
+        <v>-507</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>-269</v>
       </c>
       <c r="H41" t="n">
-        <v>-2</v>
+        <v>-17</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2497,15 +2497,15 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M41" t="n">
@@ -2515,31 +2515,31 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>方土霖</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>13</v>
+        <v>159</v>
       </c>
       <c r="D42" t="n">
         <v>55</v>
       </c>
       <c r="E42" t="n">
-        <v>50</v>
+        <v>307</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>-624</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>-2069</v>
       </c>
       <c r="H42" t="n">
-        <v>-0</v>
+        <v>-68</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2552,45 +2552,45 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-252</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E43" t="n">
-        <v>1474</v>
+        <v>114</v>
       </c>
       <c r="F43" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>118</v>
+        <v>27</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2599,15 +2599,15 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M43" t="n">
@@ -2617,31 +2617,31 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>方土霖</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-16</v>
+        <v>10</v>
       </c>
       <c r="D44" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="E44" t="n">
-        <v>-501</v>
+        <v>51</v>
       </c>
       <c r="F44" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>-249</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-23</v>
+        <v>0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2650,49 +2650,49 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-6</v>
+        <v>-183</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E45" t="n">
-        <v>-22</v>
+        <v>2546</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2701,49 +2701,49 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M45" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-16</v>
+        <v>-59</v>
       </c>
       <c r="D46" t="n">
-        <v>-9</v>
+        <v>23</v>
       </c>
       <c r="E46" t="n">
-        <v>132</v>
+        <v>708</v>
       </c>
       <c r="F46" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>38</v>
+        <v>-2</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2752,40 +2752,40 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>大車隊</t>
         </is>
       </c>
       <c r="C47" t="n">
+        <v>7</v>
+      </c>
+      <c r="D47" t="n">
         <v>18</v>
       </c>
-      <c r="D47" t="n">
-        <v>-54</v>
-      </c>
       <c r="E47" t="n">
-        <v>-182</v>
+        <v>-11</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -2794,7 +2794,7 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-0</v>
+        <v>-1</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2803,49 +2803,49 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-149</v>
+        <v>-73</v>
       </c>
       <c r="D48" t="n">
-        <v>-113</v>
+        <v>-19</v>
       </c>
       <c r="E48" t="n">
-        <v>-18</v>
+        <v>90</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="H48" t="n">
-        <v>-4</v>
+        <v>41</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2866,37 +2866,37 @@
         </is>
       </c>
       <c r="M48" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-1532</v>
+        <v>5</v>
       </c>
       <c r="D49" t="n">
-        <v>-122</v>
+        <v>-68</v>
       </c>
       <c r="E49" t="n">
-        <v>-43</v>
+        <v>-204</v>
       </c>
       <c r="F49" t="n">
-        <v>-37</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>-360</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-247</v>
+        <v>-0</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -2917,37 +2917,37 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-199</v>
+        <v>-153</v>
       </c>
       <c r="D50" t="n">
-        <v>-131</v>
+        <v>-109</v>
       </c>
       <c r="E50" t="n">
-        <v>213</v>
+        <v>-36</v>
       </c>
       <c r="F50" t="n">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>-41</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-24</v>
+        <v>-4</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2956,49 +2956,49 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-362</v>
+        <v>-183</v>
       </c>
       <c r="D51" t="n">
-        <v>-133</v>
+        <v>-199</v>
       </c>
       <c r="E51" t="n">
-        <v>-2034</v>
+        <v>246</v>
       </c>
       <c r="F51" t="n">
-        <v>271</v>
+        <v>-40</v>
       </c>
       <c r="G51" t="n">
-        <v>560</v>
+        <v>-41</v>
       </c>
       <c r="H51" t="n">
-        <v>88</v>
+        <v>-25</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3015,41 +3015,41 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-327</v>
+        <v>-688</v>
       </c>
       <c r="D52" t="n">
-        <v>-163</v>
+        <v>-234</v>
       </c>
       <c r="E52" t="n">
-        <v>-1882</v>
+        <v>-4970</v>
       </c>
       <c r="F52" t="n">
-        <v>720</v>
+        <v>-599</v>
       </c>
       <c r="G52" t="n">
-        <v>-1972</v>
+        <v>1550</v>
       </c>
       <c r="H52" t="n">
-        <v>46</v>
+        <v>-66</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3058,49 +3058,49 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-30</v>
+        <v>-1599</v>
       </c>
       <c r="D53" t="n">
-        <v>-263</v>
+        <v>-281</v>
       </c>
       <c r="E53" t="n">
-        <v>-2038</v>
+        <v>-488</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>-37</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>-360</v>
       </c>
       <c r="H53" t="n">
-        <v>-1</v>
+        <v>-301</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3113,15 +3113,15 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3136,13 +3136,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>163</v>
+        <v>252</v>
       </c>
       <c r="D54" t="n">
-        <v>-391</v>
+        <v>-299</v>
       </c>
       <c r="E54" t="n">
-        <v>-1393</v>
+        <v>-1873</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-9</v>
+        <v>-25</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3178,22 +3178,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>德昌</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-278</v>
+        <v>-105</v>
       </c>
       <c r="D55" t="n">
-        <v>-475</v>
+        <v>-354</v>
       </c>
       <c r="E55" t="n">
-        <v>-3854</v>
+        <v>-2121</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3202,7 +3202,7 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-96</v>
+        <v>-1</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3211,49 +3211,49 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-99</v>
+        <v>-52</v>
       </c>
       <c r="D56" t="n">
-        <v>-488</v>
+        <v>-422</v>
       </c>
       <c r="E56" t="n">
-        <v>-867</v>
+        <v>707</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>-29</v>
       </c>
       <c r="H56" t="n">
-        <v>-5</v>
+        <v>-65</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3262,49 +3262,49 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>315</v>
+        <v>-216</v>
       </c>
       <c r="D57" t="n">
-        <v>-545</v>
+        <v>-435</v>
       </c>
       <c r="E57" t="n">
-        <v>-2031</v>
+        <v>-2066</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>341</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>-1231</v>
       </c>
       <c r="H57" t="n">
-        <v>-53</v>
+        <v>20</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3317,45 +3317,45 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>智冠</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-91</v>
+        <v>-71</v>
       </c>
       <c r="D58" t="n">
-        <v>-547</v>
+        <v>-449</v>
       </c>
       <c r="E58" t="n">
-        <v>845</v>
+        <v>-866</v>
       </c>
       <c r="F58" t="n">
-        <v>-21</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>-48</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-52</v>
+        <v>-4</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3364,49 +3364,49 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-204</v>
+        <v>-256</v>
       </c>
       <c r="D59" t="n">
-        <v>-615</v>
+        <v>-482</v>
       </c>
       <c r="E59" t="n">
-        <v>554</v>
+        <v>-3763</v>
       </c>
       <c r="F59" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>530</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>3</v>
+        <v>-94</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3419,45 +3419,45 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>498</v>
+        <v>3388</v>
       </c>
       <c r="D60" t="n">
-        <v>-621</v>
+        <v>-564</v>
       </c>
       <c r="E60" t="n">
-        <v>-4316</v>
+        <v>-9298</v>
       </c>
       <c r="F60" t="n">
-        <v>171</v>
+        <v>79</v>
       </c>
       <c r="G60" t="n">
-        <v>225</v>
+        <v>2889</v>
       </c>
       <c r="H60" t="n">
-        <v>-15</v>
+        <v>-248</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3466,49 +3466,49 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-610</v>
+        <v>-2879</v>
       </c>
       <c r="D61" t="n">
-        <v>-643</v>
+        <v>-595</v>
       </c>
       <c r="E61" t="n">
-        <v>488</v>
+        <v>7472</v>
       </c>
       <c r="F61" t="n">
-        <v>450</v>
+        <v>-3</v>
       </c>
       <c r="G61" t="n">
-        <v>564</v>
+        <v>-16</v>
       </c>
       <c r="H61" t="n">
-        <v>19</v>
+        <v>167</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3521,45 +3521,45 @@
         </is>
       </c>
       <c r="K61" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>65</v>
+        <v>-319</v>
       </c>
       <c r="D62" t="n">
-        <v>-709</v>
+        <v>-635</v>
       </c>
       <c r="E62" t="n">
-        <v>-4464</v>
+        <v>537</v>
       </c>
       <c r="F62" t="n">
-        <v>-806</v>
+        <v>27</v>
       </c>
       <c r="G62" t="n">
-        <v>2328</v>
+        <v>564</v>
       </c>
       <c r="H62" t="n">
-        <v>-90</v>
+        <v>1</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3568,40 +3568,40 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-754</v>
+        <v>283</v>
       </c>
       <c r="D63" t="n">
-        <v>-913</v>
+        <v>-686</v>
       </c>
       <c r="E63" t="n">
-        <v>803</v>
+        <v>-2842</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -3610,7 +3610,7 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-192</v>
+        <v>-53</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3619,11 +3619,11 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3631,37 +3631,37 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3043</v>
+        <v>257</v>
       </c>
       <c r="D64" t="n">
-        <v>-987</v>
+        <v>-691</v>
       </c>
       <c r="E64" t="n">
-        <v>-10648</v>
+        <v>-3693</v>
       </c>
       <c r="F64" t="n">
-        <v>-27</v>
+        <v>146</v>
       </c>
       <c r="G64" t="n">
-        <v>2874</v>
+        <v>205</v>
       </c>
       <c r="H64" t="n">
-        <v>-213</v>
+        <v>-12</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3670,49 +3670,49 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1057</v>
+        <v>2098</v>
       </c>
       <c r="D65" t="n">
-        <v>-987</v>
+        <v>-796</v>
       </c>
       <c r="E65" t="n">
-        <v>10</v>
+        <v>-10554</v>
       </c>
       <c r="F65" t="n">
-        <v>-567</v>
+        <v>-4</v>
       </c>
       <c r="G65" t="n">
-        <v>2858</v>
+        <v>-8</v>
       </c>
       <c r="H65" t="n">
-        <v>-130</v>
+        <v>591</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3721,139 +3721,151 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-2504</v>
+        <v>493</v>
       </c>
       <c r="D66" t="n">
-        <v>-1046</v>
+        <v>-847</v>
       </c>
       <c r="E66" t="n">
-        <v>7536</v>
+        <v>-6510</v>
       </c>
       <c r="F66" t="n">
+        <v>-36</v>
+      </c>
+      <c r="G66" t="n">
+        <v>231</v>
+      </c>
+      <c r="H66" t="n">
+        <v>240</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>51</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
         <v>-3</v>
-      </c>
-      <c r="G66" t="n">
-        <v>-21</v>
-      </c>
-      <c r="H66" t="n">
-        <v>169</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K66" t="n">
-        <v>97</v>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>🚀 加速器</t>
-        </is>
-      </c>
-      <c r="M66" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>136</v>
+        <v>-711</v>
       </c>
       <c r="D67" t="n">
-        <v>-1080</v>
+        <v>-941</v>
       </c>
       <c r="E67" t="n">
-        <v>2381</v>
+        <v>401</v>
       </c>
       <c r="F67" t="n">
-        <v>12</v>
+        <v>-181</v>
       </c>
       <c r="G67" t="n">
-        <v>1408</v>
+        <v>-601</v>
       </c>
       <c r="H67" t="n">
-        <v>2</v>
+        <v>-63</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>91</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>✈️ 高飛</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-147</v>
+        <v>-336</v>
       </c>
       <c r="D68" t="n">
-        <v>-1105</v>
+        <v>-1086</v>
       </c>
       <c r="E68" t="n">
-        <v>635</v>
+        <v>329</v>
       </c>
       <c r="F68" t="n">
-        <v>-285</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>-520</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-85</v>
+        <v>-227</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3862,19 +3874,19 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="69">
@@ -3889,13 +3901,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-351</v>
+        <v>-324</v>
       </c>
       <c r="D69" t="n">
-        <v>-1150</v>
+        <v>-1149</v>
       </c>
       <c r="E69" t="n">
-        <v>-1830</v>
+        <v>-1774</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -3931,31 +3943,31 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>482</v>
+        <v>305</v>
       </c>
       <c r="D70" t="n">
-        <v>-1175</v>
+        <v>-1421</v>
       </c>
       <c r="E70" t="n">
-        <v>-8604</v>
+        <v>-1019</v>
       </c>
       <c r="F70" t="n">
-        <v>-2896</v>
+        <v>-114</v>
       </c>
       <c r="G70" t="n">
-        <v>-7074</v>
+        <v>228</v>
       </c>
       <c r="H70" t="n">
-        <v>278</v>
+        <v>106</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3968,7 +3980,7 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -3976,37 +3988,37 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-2408</v>
+        <v>-246</v>
       </c>
       <c r="D71" t="n">
-        <v>-1186</v>
+        <v>-1492</v>
       </c>
       <c r="E71" t="n">
-        <v>3940</v>
+        <v>-64</v>
       </c>
       <c r="F71" t="n">
-        <v>-3380</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>1789</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>380</v>
+        <v>-178</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -4015,49 +4027,49 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>208</v>
+        <v>802</v>
       </c>
       <c r="D72" t="n">
-        <v>-1359</v>
+        <v>-1496</v>
       </c>
       <c r="E72" t="n">
-        <v>-7180</v>
+        <v>-2049</v>
       </c>
       <c r="F72" t="n">
-        <v>-285</v>
+        <v>-21</v>
       </c>
       <c r="G72" t="n">
-        <v>654</v>
+        <v>1478</v>
       </c>
       <c r="H72" t="n">
-        <v>396</v>
+        <v>9</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -4066,11 +4078,11 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4078,37 +4090,37 @@
         </is>
       </c>
       <c r="M72" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-217</v>
+        <v>-1270</v>
       </c>
       <c r="D73" t="n">
-        <v>-1386</v>
+        <v>-1515</v>
       </c>
       <c r="E73" t="n">
-        <v>57</v>
+        <v>1447</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>430</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>544</v>
       </c>
       <c r="H73" t="n">
-        <v>-175</v>
+        <v>26</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4117,49 +4129,49 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M73" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-4239</v>
+        <v>2070</v>
       </c>
       <c r="D74" t="n">
-        <v>-1647</v>
+        <v>-1568</v>
       </c>
       <c r="E74" t="n">
-        <v>-1655</v>
+        <v>-8825</v>
       </c>
       <c r="F74" t="n">
-        <v>3897</v>
+        <v>-2091</v>
       </c>
       <c r="G74" t="n">
-        <v>10556</v>
+        <v>-6723</v>
       </c>
       <c r="H74" t="n">
-        <v>-317</v>
+        <v>277</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4168,49 +4180,49 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M74" t="n">
-        <v>-5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-397</v>
+        <v>-2667</v>
       </c>
       <c r="D75" t="n">
-        <v>-1697</v>
+        <v>-1591</v>
       </c>
       <c r="E75" t="n">
-        <v>-4555</v>
+        <v>-1958</v>
       </c>
       <c r="F75" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>660</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-137</v>
+        <v>-4</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4223,96 +4235,84 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>57</v>
+        <v>-105</v>
       </c>
       <c r="D76" t="n">
-        <v>-1763</v>
+        <v>-1607</v>
       </c>
       <c r="E76" t="n">
-        <v>-1112</v>
+        <v>2693</v>
       </c>
       <c r="F76" t="n">
-        <v>-24</v>
+        <v>-358</v>
       </c>
       <c r="G76" t="n">
-        <v>344</v>
+        <v>1538</v>
       </c>
       <c r="H76" t="n">
-        <v>122</v>
+        <v>10</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K76" t="n">
-        <v>89</v>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>🚀 加速器</t>
-        </is>
-      </c>
-      <c r="M76" t="n">
-        <v>0</v>
-      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>勝一</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>475</v>
+        <v>-279</v>
       </c>
       <c r="D77" t="n">
         <v>-1785</v>
       </c>
       <c r="E77" t="n">
-        <v>-2218</v>
+        <v>-3028</v>
       </c>
       <c r="F77" t="n">
-        <v>475</v>
+        <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>1656</v>
+        <v>-4</v>
       </c>
       <c r="H77" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4325,45 +4325,45 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M77" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>184</v>
+        <v>-234</v>
       </c>
       <c r="D78" t="n">
-        <v>-1788</v>
+        <v>-1945</v>
       </c>
       <c r="E78" t="n">
-        <v>-2921</v>
+        <v>-4119</v>
       </c>
       <c r="F78" t="n">
-        <v>-38</v>
+        <v>164</v>
       </c>
       <c r="G78" t="n">
-        <v>-117</v>
+        <v>292</v>
       </c>
       <c r="H78" t="n">
-        <v>-0</v>
+        <v>-129</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4372,11 +4372,11 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4384,37 +4384,37 @@
         </is>
       </c>
       <c r="M78" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-2053</v>
+        <v>-902</v>
       </c>
       <c r="D79" t="n">
-        <v>-2026</v>
+        <v>-2859</v>
       </c>
       <c r="E79" t="n">
-        <v>-1670</v>
+        <v>-1253</v>
       </c>
       <c r="F79" t="n">
-        <v>0</v>
+        <v>-402</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>-688</v>
       </c>
       <c r="H79" t="n">
-        <v>6</v>
+        <v>-122</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4423,49 +4423,49 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K79" t="n">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M79" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>499</v>
+        <v>-2300</v>
       </c>
       <c r="D80" t="n">
-        <v>-2660</v>
+        <v>-2987</v>
       </c>
       <c r="E80" t="n">
-        <v>-9887</v>
+        <v>-4224</v>
       </c>
       <c r="F80" t="n">
-        <v>298</v>
+        <v>-221</v>
       </c>
       <c r="G80" t="n">
-        <v>1729</v>
+        <v>-34</v>
       </c>
       <c r="H80" t="n">
-        <v>-542</v>
+        <v>153</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4474,15 +4474,15 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M80" t="n">
@@ -4492,31 +4492,31 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-1213</v>
+        <v>-1135</v>
       </c>
       <c r="D81" t="n">
-        <v>-2857</v>
+        <v>-3000</v>
       </c>
       <c r="E81" t="n">
-        <v>-1173</v>
+        <v>-5678</v>
       </c>
       <c r="F81" t="n">
-        <v>-284</v>
+        <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>-438</v>
+        <v>-747</v>
       </c>
       <c r="H81" t="n">
-        <v>-136</v>
+        <v>12</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4529,15 +4529,15 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器*</t>
         </is>
       </c>
       <c r="M81" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
@@ -4552,22 +4552,22 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-20</v>
+        <v>-114</v>
       </c>
       <c r="D82" t="n">
-        <v>-2998</v>
+        <v>-3033</v>
       </c>
       <c r="E82" t="n">
-        <v>-3599</v>
+        <v>-4660</v>
       </c>
       <c r="F82" t="n">
-        <v>-5</v>
+        <v>-25</v>
       </c>
       <c r="G82" t="n">
-        <v>-189</v>
+        <v>-209</v>
       </c>
       <c r="H82" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4594,31 +4594,31 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-382</v>
+        <v>-436</v>
       </c>
       <c r="D83" t="n">
-        <v>-3010</v>
+        <v>-3041</v>
       </c>
       <c r="E83" t="n">
-        <v>-5906</v>
+        <v>-5513</v>
       </c>
       <c r="F83" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>-433</v>
+        <v>596</v>
       </c>
       <c r="H83" t="n">
-        <v>3</v>
+        <v>2385</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4631,84 +4631,96 @@
         </is>
       </c>
       <c r="K83" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>🚀 加速器*</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M83" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>434</v>
+        <v>216</v>
       </c>
       <c r="D84" t="n">
-        <v>-3155</v>
+        <v>-3228</v>
       </c>
       <c r="E84" t="n">
-        <v>-4916</v>
+        <v>-13092</v>
       </c>
       <c r="F84" t="n">
+        <v>288</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1417</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-557</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>🟠 減碼</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>90</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
         <v>0</v>
       </c>
-      <c r="G84" t="n">
-        <v>-400</v>
-      </c>
-      <c r="H84" t="n">
-        <v>42</v>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>🟠 減碼</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-714</v>
+        <v>-2969</v>
       </c>
       <c r="D85" t="n">
-        <v>-3167</v>
+        <v>-3380</v>
       </c>
       <c r="E85" t="n">
-        <v>-4325</v>
+        <v>3356</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>-2596</v>
       </c>
       <c r="G85" t="n">
-        <v>1077</v>
+        <v>-490</v>
       </c>
       <c r="H85" t="n">
-        <v>2406</v>
+        <v>337</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4717,11 +4729,11 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K85" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4729,88 +4741,76 @@
         </is>
       </c>
       <c r="M85" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-2214</v>
+        <v>282</v>
       </c>
       <c r="D86" t="n">
-        <v>-3180</v>
+        <v>-3561</v>
       </c>
       <c r="E86" t="n">
-        <v>-4422</v>
+        <v>-5741</v>
       </c>
       <c r="F86" t="n">
-        <v>-138</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>54</v>
+        <v>-400</v>
       </c>
       <c r="H86" t="n">
-        <v>143</v>
+        <v>-2</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
           <t>🟠 減碼</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K86" t="n">
-        <v>64</v>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>🚀 加速器</t>
-        </is>
-      </c>
-      <c r="M86" t="n">
-        <v>0</v>
-      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>5643</v>
+        <v>-1390</v>
       </c>
       <c r="D87" t="n">
-        <v>-3390</v>
+        <v>-3750</v>
       </c>
       <c r="E87" t="n">
-        <v>58585</v>
+        <v>-4350</v>
       </c>
       <c r="F87" t="n">
-        <v>-4075</v>
+        <v>-1661</v>
       </c>
       <c r="G87" t="n">
-        <v>-7044</v>
+        <v>5073</v>
       </c>
       <c r="H87" t="n">
-        <v>-5529</v>
+        <v>58</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4819,49 +4819,49 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M87" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-562</v>
+        <v>-232</v>
       </c>
       <c r="D88" t="n">
-        <v>-3751</v>
+        <v>-3763</v>
       </c>
       <c r="E88" t="n">
-        <v>-2645</v>
+        <v>-21062</v>
       </c>
       <c r="F88" t="n">
-        <v>329</v>
+        <v>-334</v>
       </c>
       <c r="G88" t="n">
-        <v>5452</v>
+        <v>-1374</v>
       </c>
       <c r="H88" t="n">
-        <v>46</v>
+        <v>-197</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4870,49 +4870,49 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K88" t="n">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M88" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-786</v>
+        <v>-1387</v>
       </c>
       <c r="D89" t="n">
-        <v>-5079</v>
+        <v>-5112</v>
       </c>
       <c r="E89" t="n">
-        <v>-22109</v>
+        <v>73857</v>
       </c>
       <c r="F89" t="n">
-        <v>-340</v>
+        <v>-1385</v>
       </c>
       <c r="G89" t="n">
-        <v>-1543</v>
+        <v>1608</v>
       </c>
       <c r="H89" t="n">
-        <v>-268</v>
+        <v>-2662</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4921,49 +4921,49 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K89" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-44426</v>
+        <v>-4502</v>
       </c>
       <c r="D90" t="n">
-        <v>-5174</v>
+        <v>-5945</v>
       </c>
       <c r="E90" t="n">
-        <v>26260</v>
+        <v>-34544</v>
       </c>
       <c r="F90" t="n">
-        <v>-6985</v>
+        <v>222</v>
       </c>
       <c r="G90" t="n">
-        <v>-48703</v>
+        <v>381</v>
       </c>
       <c r="H90" t="n">
-        <v>-10060</v>
+        <v>153</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4972,11 +4972,11 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K90" t="n">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -4984,37 +4984,37 @@
         </is>
       </c>
       <c r="M90" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-5169</v>
+        <v>-28172</v>
       </c>
       <c r="D91" t="n">
-        <v>-6017</v>
+        <v>-7350</v>
       </c>
       <c r="E91" t="n">
-        <v>-36570</v>
+        <v>-141307</v>
       </c>
       <c r="F91" t="n">
-        <v>204</v>
+        <v>-314</v>
       </c>
       <c r="G91" t="n">
-        <v>350</v>
+        <v>-3206</v>
       </c>
       <c r="H91" t="n">
-        <v>124</v>
+        <v>2727</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -5023,100 +5023,88 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K91" t="n">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M91" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-18449</v>
+        <v>919</v>
       </c>
       <c r="D92" t="n">
-        <v>-6368</v>
+        <v>-7611</v>
       </c>
       <c r="E92" t="n">
-        <v>-149334</v>
+        <v>-8072</v>
       </c>
       <c r="F92" t="n">
-        <v>905</v>
+        <v>-1592</v>
       </c>
       <c r="G92" t="n">
-        <v>-2565</v>
+        <v>1411</v>
       </c>
       <c r="H92" t="n">
-        <v>2267</v>
+        <v>-200</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
           <t>🟠 減碼</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K92" t="n">
-        <v>100</v>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>✈️ 高飛</t>
-        </is>
-      </c>
-      <c r="M92" t="n">
-        <v>3</v>
-      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>長榮航太</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-18026</v>
+        <v>-457</v>
       </c>
       <c r="D93" t="n">
-        <v>-7044</v>
+        <v>-7958</v>
       </c>
       <c r="E93" t="n">
-        <v>71930</v>
+        <v>-14093</v>
       </c>
       <c r="F93" t="n">
-        <v>594</v>
+        <v>-43</v>
       </c>
       <c r="G93" t="n">
-        <v>2283</v>
+        <v>164</v>
       </c>
       <c r="H93" t="n">
-        <v>-3446</v>
+        <v>-1</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -5129,11 +5117,11 @@
         </is>
       </c>
       <c r="K93" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M93" t="n">
@@ -5143,70 +5131,82 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>539</v>
+        <v>-1177</v>
       </c>
       <c r="D94" t="n">
-        <v>-8797</v>
+        <v>-8606</v>
       </c>
       <c r="E94" t="n">
-        <v>-7788</v>
+        <v>-16052</v>
       </c>
       <c r="F94" t="n">
-        <v>-1248</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>2695</v>
+        <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>-26</v>
+        <v>11</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
           <t>🟠 減碼</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>78</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>📉 減速</t>
+        </is>
+      </c>
+      <c r="M94" t="n">
+        <v>-5</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-1217</v>
+        <v>-902</v>
       </c>
       <c r="D95" t="n">
-        <v>-9176</v>
+        <v>-9453</v>
       </c>
       <c r="E95" t="n">
-        <v>-11123</v>
+        <v>-16495</v>
       </c>
       <c r="F95" t="n">
-        <v>-2445</v>
+        <v>690</v>
       </c>
       <c r="G95" t="n">
-        <v>-3039</v>
+        <v>1992</v>
       </c>
       <c r="H95" t="n">
-        <v>-751</v>
+        <v>422</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5215,11 +5215,11 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K95" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -5227,41 +5227,41 @@
         </is>
       </c>
       <c r="M95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-606</v>
+        <v>-2150</v>
       </c>
       <c r="D96" t="n">
-        <v>-9322</v>
+        <v>-10124</v>
       </c>
       <c r="E96" t="n">
-        <v>-11661</v>
+        <v>-10984</v>
       </c>
       <c r="F96" t="n">
-        <v>9</v>
+        <v>-815</v>
       </c>
       <c r="G96" t="n">
-        <v>204</v>
+        <v>-2691</v>
       </c>
       <c r="H96" t="n">
-        <v>-9</v>
+        <v>-420</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🔴 大賣</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -5270,58 +5270,58 @@
         </is>
       </c>
       <c r="K96" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-1693</v>
+        <v>-141119</v>
       </c>
       <c r="D97" t="n">
-        <v>-9643</v>
+        <v>-10166</v>
       </c>
       <c r="E97" t="n">
-        <v>-16148</v>
+        <v>-19225</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>-16382</v>
       </c>
       <c r="G97" t="n">
-        <v>1</v>
+        <v>-53708</v>
       </c>
       <c r="H97" t="n">
-        <v>8</v>
+        <v>-8282</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🔴 大賣</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K97" t="n">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -5329,92 +5329,92 @@
         </is>
       </c>
       <c r="M97" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-923</v>
+        <v>-35204</v>
       </c>
       <c r="D98" t="n">
-        <v>-9691</v>
+        <v>-12307</v>
       </c>
       <c r="E98" t="n">
-        <v>-16855</v>
+        <v>45807</v>
       </c>
       <c r="F98" t="n">
-        <v>120</v>
+        <v>-5741</v>
       </c>
       <c r="G98" t="n">
-        <v>2097</v>
+        <v>-9312</v>
       </c>
       <c r="H98" t="n">
-        <v>468</v>
+        <v>-5164</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🔴 大賣</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K98" t="n">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M98" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-1601</v>
+        <v>-1437</v>
       </c>
       <c r="D99" t="n">
-        <v>-9998</v>
+        <v>-12479</v>
       </c>
       <c r="E99" t="n">
-        <v>64294</v>
+        <v>-24597</v>
       </c>
       <c r="F99" t="n">
-        <v>-2449</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
-        <v>13871</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>-1203</v>
+        <v>-259</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🔴 大賣</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -5423,15 +5423,15 @@
         </is>
       </c>
       <c r="K99" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M99" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="100">
@@ -5446,22 +5446,22 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>3335</v>
+        <v>4101</v>
       </c>
       <c r="D100" t="n">
-        <v>-14882</v>
+        <v>-13701</v>
       </c>
       <c r="E100" t="n">
-        <v>-64954</v>
+        <v>-63728</v>
       </c>
       <c r="F100" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G100" t="n">
-        <v>-1905</v>
+        <v>-1922</v>
       </c>
       <c r="H100" t="n">
-        <v>-284</v>
+        <v>-210</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -5488,82 +5488,82 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-1970</v>
+        <v>-9228</v>
       </c>
       <c r="D101" t="n">
-        <v>-18109</v>
+        <v>-16129</v>
       </c>
       <c r="E101" t="n">
-        <v>-24646</v>
+        <v>-49487</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>-3674</v>
       </c>
       <c r="G101" t="n">
+        <v>-8639</v>
+      </c>
+      <c r="H101" t="n">
+        <v>415</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>🔴 大賣</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K101" t="n">
+        <v>100</v>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>🛬 穩定</t>
+        </is>
+      </c>
+      <c r="M101" t="n">
         <v>1</v>
-      </c>
-      <c r="H101" t="n">
-        <v>-301</v>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>🔴 大賣</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K101" t="n">
-        <v>60</v>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>🛬 穩定</t>
-        </is>
-      </c>
-      <c r="M101" t="n">
-        <v>-4</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-11814</v>
+        <v>-7896</v>
       </c>
       <c r="D102" t="n">
-        <v>-18501</v>
+        <v>-19223</v>
       </c>
       <c r="E102" t="n">
-        <v>-52825</v>
+        <v>-74740</v>
       </c>
       <c r="F102" t="n">
-        <v>-3225</v>
+        <v>1275</v>
       </c>
       <c r="G102" t="n">
-        <v>-8202</v>
+        <v>-25528</v>
       </c>
       <c r="H102" t="n">
-        <v>-36</v>
+        <v>169</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5572,49 +5572,49 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K102" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M102" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-8379</v>
+        <v>-6226</v>
       </c>
       <c r="D103" t="n">
-        <v>-20902</v>
+        <v>-20372</v>
       </c>
       <c r="E103" t="n">
-        <v>-77636</v>
+        <v>68526</v>
       </c>
       <c r="F103" t="n">
-        <v>177</v>
+        <v>2095</v>
       </c>
       <c r="G103" t="n">
-        <v>-26421</v>
+        <v>5009</v>
       </c>
       <c r="H103" t="n">
-        <v>-521</v>
+        <v>-2261</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5623,15 +5623,15 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K103" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M103" t="n">
@@ -5641,31 +5641,31 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-17123</v>
+        <v>-1867</v>
       </c>
       <c r="D104" t="n">
-        <v>-25839</v>
+        <v>-22783</v>
       </c>
       <c r="E104" t="n">
-        <v>45672</v>
+        <v>57917</v>
       </c>
       <c r="F104" t="n">
-        <v>2162</v>
+        <v>-2662</v>
       </c>
       <c r="G104" t="n">
-        <v>730</v>
+        <v>10742</v>
       </c>
       <c r="H104" t="n">
-        <v>-3288</v>
+        <v>-700</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5674,11 +5674,11 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K104" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         </is>
       </c>
       <c r="M104" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="105">
@@ -5701,22 +5701,22 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-83197</v>
+        <v>-38830</v>
       </c>
       <c r="D105" t="n">
-        <v>-114098</v>
+        <v>-108275</v>
       </c>
       <c r="E105" t="n">
-        <v>138942</v>
+        <v>145615</v>
       </c>
       <c r="F105" t="n">
-        <v>1158</v>
+        <v>64</v>
       </c>
       <c r="G105" t="n">
-        <v>32267</v>
+        <v>34105</v>
       </c>
       <c r="H105" t="n">
-        <v>273</v>
+        <v>725</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5794,58 +5794,58 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 204 千股)</t>
+          <t>📉 20d 巨變(減碼 -605 千股)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>692690</v>
+        <v>126407</v>
       </c>
       <c r="D2" t="n">
-        <v>234850</v>
+        <v>734763</v>
       </c>
       <c r="E2" t="n">
-        <v>-100330</v>
+        <v>126216</v>
       </c>
       <c r="F2" t="n">
-        <v>30718</v>
+        <v>1339959</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>台光電</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -450 千股)</t>
+          <t>📈 20d 巨變(加碼 238 千股)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-786062</v>
+        <v>-901804</v>
       </c>
       <c r="D3" t="n">
-        <v>-5078924</v>
+        <v>-9453091</v>
       </c>
       <c r="E3" t="n">
-        <v>-489132</v>
+        <v>-923067</v>
       </c>
       <c r="F3" t="n">
-        <v>-4628887</v>
+        <v>-9691049</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
@@ -5857,20 +5857,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 47 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -972 千股)</t>
         </is>
       </c>
       <c r="C4" t="n">
+        <v>-8608</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1079985</v>
+      </c>
+      <c r="E4" t="n">
         <v>271561</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>2051842</v>
-      </c>
-      <c r="E4" t="n">
-        <v>183068</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2005152</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -5881,87 +5881,87 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -322 千股)</t>
+          <t>📉 20d 巨變(減碼 -179 千股)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>746751</v>
+        <v>158831</v>
       </c>
       <c r="D5" t="n">
-        <v>1213139</v>
+        <v>55400</v>
       </c>
       <c r="E5" t="n">
-        <v>-133899</v>
+        <v>692690</v>
       </c>
       <c r="F5" t="n">
-        <v>1535342</v>
+        <v>234850</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>勤誠</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 59 千股)</t>
+          <t>📈 20d 巨變(加碼 1,316 千股)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>126216</v>
+        <v>-232115</v>
       </c>
       <c r="D6" t="n">
-        <v>1339959</v>
+        <v>-3763227</v>
       </c>
       <c r="E6" t="n">
-        <v>57512</v>
+        <v>-786062</v>
       </c>
       <c r="F6" t="n">
-        <v>1281306</v>
+        <v>-5078924</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>亞翔</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -754 千股)</t>
+          <t>📉 20d 巨變(減碼 -328 千股)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-923067</v>
+        <v>805321</v>
       </c>
       <c r="D7" t="n">
-        <v>-9691049</v>
+        <v>885199</v>
       </c>
       <c r="E7" t="n">
-        <v>-334930</v>
+        <v>746751</v>
       </c>
       <c r="F7" t="n">
-        <v>-8936751</v>
+        <v>1213139</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>奇鋐</t>
         </is>
       </c>
     </row>
@@ -5973,20 +5973,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 186 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 999 千股)</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>229699</v>
+      </c>
+      <c r="D8" t="n">
+        <v>866408</v>
+      </c>
+      <c r="E8" t="n">
         <v>-361990</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>-132874</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-465155</v>
-      </c>
-      <c r="F8" t="n">
-        <v>-319191</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -5997,290 +5997,290 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -152 千股)</t>
+          <t>📉 20d 巨變(減碼 -982 千股)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-14835</v>
+        <v>-28172058</v>
       </c>
       <c r="D9" t="n">
-        <v>2173381</v>
+        <v>-7350073</v>
       </c>
       <c r="E9" t="n">
-        <v>603030</v>
+        <v>-18448562</v>
       </c>
       <c r="F9" t="n">
-        <v>2324994</v>
+        <v>-6368431</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 127 千股)</t>
+          <t>📉 20d 巨變(減碼 -125 千股)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-326672</v>
+        <v>-529188</v>
       </c>
       <c r="D10" t="n">
-        <v>-162990</v>
+        <v>2048169</v>
       </c>
       <c r="E10" t="n">
-        <v>-32920</v>
+        <v>-14835</v>
       </c>
       <c r="F10" t="n">
-        <v>-289771</v>
+        <v>2173381</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>致茂</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 537 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -29 千股)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>482323</v>
+        <v>88450</v>
       </c>
       <c r="D11" t="n">
-        <v>-1175019</v>
+        <v>9415690</v>
       </c>
       <c r="E11" t="n">
-        <v>171263</v>
+        <v>-155839</v>
       </c>
       <c r="F11" t="n">
-        <v>-1711576</v>
+        <v>9445037</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>雙鴻</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -15,633 千股)</t>
+          <t>📉 20d 巨變(減碼 -272 千股)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-18448562</v>
+        <v>-215699</v>
       </c>
       <c r="D12" t="n">
-        <v>-6368431</v>
+        <v>-434902</v>
       </c>
       <c r="E12" t="n">
-        <v>8877774</v>
+        <v>-326672</v>
       </c>
       <c r="F12" t="n">
-        <v>9264250</v>
+        <v>-162990</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>旺矽</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -126 千股)</t>
+          <t>📉 20d 巨變(減碼 -393 千股)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-155839</v>
+        <v>2070385</v>
       </c>
       <c r="D13" t="n">
-        <v>9445037</v>
+        <v>-1568199</v>
       </c>
       <c r="E13" t="n">
-        <v>108230</v>
+        <v>482323</v>
       </c>
       <c r="F13" t="n">
-        <v>9571239</v>
+        <v>-1175019</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>智邦</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,060 千股)</t>
+          <t>📈 20d 巨變(加碼 161 千股)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-11813898</v>
+        <v>1803921</v>
       </c>
       <c r="D14" t="n">
-        <v>-18501314</v>
+        <v>2036971</v>
       </c>
       <c r="E14" t="n">
-        <v>-11935031</v>
+        <v>1175652</v>
       </c>
       <c r="F14" t="n">
-        <v>-17440933</v>
+        <v>1875536</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>帆宣</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 84 千股)</t>
+          <t>📈 20d 巨變(加碼 2,372 千股)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1175652</v>
+        <v>-9227556</v>
       </c>
       <c r="D15" t="n">
-        <v>1875536</v>
+        <v>-16128955</v>
       </c>
       <c r="E15" t="n">
-        <v>555865</v>
+        <v>-11813898</v>
       </c>
       <c r="F15" t="n">
-        <v>1791270</v>
+        <v>-18501314</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -155 千股)</t>
+          <t>📉 20d 巨變(減碼 -34 千股)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-147378</v>
+        <v>-113917</v>
       </c>
       <c r="D16" t="n">
-        <v>-1105337</v>
+        <v>-3032766</v>
       </c>
       <c r="E16" t="n">
-        <v>87218</v>
+        <v>-19851</v>
       </c>
       <c r="F16" t="n">
-        <v>-950289</v>
+        <v>-2998427</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>佳必琪</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,077 千股)</t>
+          <t>📈 20d 巨變(加碼 164 千股)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>499335</v>
+        <v>-710826</v>
       </c>
       <c r="D17" t="n">
-        <v>-2659816</v>
+        <v>-941083</v>
       </c>
       <c r="E17" t="n">
-        <v>198488</v>
+        <v>-147378</v>
       </c>
       <c r="F17" t="n">
-        <v>-3737139</v>
+        <v>-1105337</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>辛耘</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 137 千股)</t>
+          <t>📉 20d 巨變(減碼 -568 千股)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-19851</v>
+        <v>216411</v>
       </c>
       <c r="D18" t="n">
-        <v>-2998427</v>
+        <v>-3227832</v>
       </c>
       <c r="E18" t="n">
-        <v>-331369</v>
+        <v>499335</v>
       </c>
       <c r="F18" t="n">
-        <v>-3135895</v>
+        <v>-2659816</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>健鼎</t>
         </is>
       </c>
     </row>
@@ -6292,20 +6292,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 38 千股)</t>
+          <t>📈 20d 巨變(加碼 35 千股)</t>
         </is>
       </c>
       <c r="C19" t="n">
+        <v>84817</v>
+      </c>
+      <c r="D19" t="n">
+        <v>227430</v>
+      </c>
+      <c r="E19" t="n">
         <v>144544</v>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>192234</v>
-      </c>
-      <c r="E19" t="n">
-        <v>111538</v>
-      </c>
-      <c r="F19" t="n">
-        <v>154496</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -6321,20 +6321,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 149 千股)</t>
+          <t>📉 20d 巨變(減碼 -248 千股)</t>
         </is>
       </c>
       <c r="C20" t="n">
+        <v>-233788</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-1945357</v>
+      </c>
+      <c r="E20" t="n">
         <v>-396606</v>
       </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
         <v>-1697244</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-289627</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-1846112</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -6345,58 +6345,58 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,079 千股)</t>
+          <t>📈 20d 巨變(加碼 131 千股)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1317827</v>
+        <v>1254908</v>
       </c>
       <c r="D21" t="n">
-        <v>2637838</v>
+        <v>3860387</v>
       </c>
       <c r="E21" t="n">
-        <v>2807671</v>
+        <v>1993012</v>
       </c>
       <c r="F21" t="n">
-        <v>3717175</v>
+        <v>3729156</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,291 千股)</t>
+          <t>📉 20d 巨變(減碼 -322 千股)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1993012</v>
+        <v>1040996</v>
       </c>
       <c r="D22" t="n">
-        <v>3729156</v>
+        <v>2315629</v>
       </c>
       <c r="E22" t="n">
-        <v>2849155</v>
+        <v>1317827</v>
       </c>
       <c r="F22" t="n">
-        <v>5020631</v>
+        <v>2637838</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>中砂</t>
         </is>
       </c>
     </row>
@@ -6408,20 +6408,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 19 千股)</t>
+          <t>📈 20d 巨變(加碼 342 千股)</t>
         </is>
       </c>
       <c r="C23" t="n">
+        <v>305390</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-1421472</v>
+      </c>
+      <c r="E23" t="n">
         <v>57296</v>
       </c>
-      <c r="D23" t="n">
+      <c r="F23" t="n">
         <v>-1763497</v>
-      </c>
-      <c r="E23" t="n">
-        <v>440790</v>
-      </c>
-      <c r="F23" t="n">
-        <v>-1782189</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -6437,20 +6437,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,740 千股)</t>
+          <t>📈 20d 巨變(加碼 435 千股)</t>
         </is>
       </c>
       <c r="C24" t="n">
+        <v>-2667490</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-1591149</v>
+      </c>
+      <c r="E24" t="n">
         <v>-2053206</v>
       </c>
-      <c r="D24" t="n">
+      <c r="F24" t="n">
         <v>-2026035</v>
-      </c>
-      <c r="E24" t="n">
-        <v>-320398</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-286297</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -6466,20 +6466,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -480 千股)</t>
+          <t>📈 20d 巨變(加碼 511 千股)</t>
         </is>
       </c>
       <c r="C25" t="n">
+        <v>492619</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-847469</v>
+      </c>
+      <c r="E25" t="n">
         <v>208489</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
         <v>-1358574</v>
-      </c>
-      <c r="E25" t="n">
-        <v>-221563</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-878585</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -6495,20 +6495,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -23 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 17 千股)</t>
         </is>
       </c>
       <c r="C26" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D26" t="n">
+        <v>18251</v>
+      </c>
+      <c r="E26" t="n">
         <v>-6000</v>
       </c>
-      <c r="D26" t="n">
+      <c r="F26" t="n">
         <v>1251</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-5142</v>
-      </c>
-      <c r="F26" t="n">
-        <v>24231</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -6524,20 +6524,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,398 千股)</t>
+          <t>📈 20d 巨變(加碼 451 千股)</t>
         </is>
       </c>
       <c r="C27" t="n">
+        <v>-2879314</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-594821</v>
+      </c>
+      <c r="E27" t="n">
         <v>-2503564</v>
       </c>
-      <c r="D27" t="n">
+      <c r="F27" t="n">
         <v>-1045780</v>
-      </c>
-      <c r="E27" t="n">
-        <v>-96513</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1352310</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -6548,319 +6548,319 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -37 千股)</t>
+          <t>📉 20d 巨變(減碼 -53 千股)</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>315170</v>
+        <v>-58643</v>
       </c>
       <c r="D28" t="n">
-        <v>-545392</v>
+        <v>22631</v>
       </c>
       <c r="E28" t="n">
-        <v>-23630</v>
+        <v>-38953</v>
       </c>
       <c r="F28" t="n">
-        <v>-508392</v>
+        <v>75239</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>崇友</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 249 千股)</t>
+          <t>📉 20d 巨變(減碼 -141 千股)</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>593705</v>
+        <v>283170</v>
       </c>
       <c r="D29" t="n">
-        <v>15235938</v>
+        <v>-686392</v>
       </c>
       <c r="E29" t="n">
-        <v>-1858027</v>
+        <v>315170</v>
       </c>
       <c r="F29" t="n">
-        <v>14987241</v>
+        <v>-545392</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>湧德</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 730 千股)</t>
+          <t>📉 20d 巨變(減碼 -544 千股)</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>326467</v>
+        <v>308995</v>
       </c>
       <c r="D30" t="n">
-        <v>1030818</v>
+        <v>14692122</v>
       </c>
       <c r="E30" t="n">
-        <v>189351</v>
+        <v>593705</v>
       </c>
       <c r="F30" t="n">
-        <v>300791</v>
+        <v>15235938</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -786 千股)</t>
+          <t>📉 20d 巨變(減碼 -7 千股)</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-610007</v>
+        <v>-255650</v>
       </c>
       <c r="D31" t="n">
-        <v>-643428</v>
+        <v>-481844</v>
       </c>
       <c r="E31" t="n">
-        <v>136326</v>
+        <v>-277644</v>
       </c>
       <c r="F31" t="n">
-        <v>142991</v>
+        <v>-475144</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>隆大</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 4,568 千股)</t>
+          <t>📉 20d 巨變(減碼 -39 千股)</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3334681</v>
+        <v>78934</v>
       </c>
       <c r="D32" t="n">
-        <v>-14881883</v>
+        <v>991654</v>
       </c>
       <c r="E32" t="n">
-        <v>2289845</v>
+        <v>326467</v>
       </c>
       <c r="F32" t="n">
-        <v>-19450013</v>
+        <v>1030818</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>合機</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -22,494 千股)</t>
+          <t>📉 20d 巨變(減碼 -871 千股)</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>13308687</v>
+        <v>-1270466</v>
       </c>
       <c r="D33" t="n">
-        <v>53814945</v>
+        <v>-1514833</v>
       </c>
       <c r="E33" t="n">
-        <v>8196467</v>
+        <v>-610007</v>
       </c>
       <c r="F33" t="n">
-        <v>76309054</v>
+        <v>-643428</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>卜蜂</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -51 千股)</t>
+          <t>📈 20d 巨變(加碼 1,180 千股)</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-63301</v>
+        <v>4101197</v>
       </c>
       <c r="D34" t="n">
-        <v>348522</v>
+        <v>-13701406</v>
       </c>
       <c r="E34" t="n">
-        <v>23077</v>
+        <v>3334681</v>
       </c>
       <c r="F34" t="n">
-        <v>399190</v>
+        <v>-14881883</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>寶雅*</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -28 千股)</t>
+          <t>📉 20d 巨變(減碼 -16,146 千股)</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-38953</v>
+        <v>3200128</v>
       </c>
       <c r="D35" t="n">
-        <v>75239</v>
+        <v>37669057</v>
       </c>
       <c r="E35" t="n">
-        <v>25240</v>
+        <v>13308687</v>
       </c>
       <c r="F35" t="n">
-        <v>103239</v>
+        <v>53814945</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 122 千股)</t>
+          <t>📉 20d 巨變(減碼 -77 千股)</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-11432</v>
+        <v>-119118</v>
       </c>
       <c r="D36" t="n">
-        <v>365790</v>
+        <v>271407</v>
       </c>
       <c r="E36" t="n">
-        <v>-341652</v>
+        <v>-63301</v>
       </c>
       <c r="F36" t="n">
-        <v>244040</v>
+        <v>348522</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>大統益</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 35 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 93 千股)</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-98786</v>
+        <v>184014</v>
       </c>
       <c r="D37" t="n">
-        <v>-487525</v>
+        <v>458790</v>
       </c>
       <c r="E37" t="n">
-        <v>-125845</v>
+        <v>-11432</v>
       </c>
       <c r="F37" t="n">
-        <v>-522513</v>
+        <v>365790</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>豐藝</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -5 千股)</t>
+          <t>📈 20d 巨變(加碼 39 千股)</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>13000</v>
+        <v>-71173</v>
       </c>
       <c r="D38" t="n">
-        <v>55000</v>
+        <v>-448616</v>
       </c>
       <c r="E38" t="n">
-        <v>13000</v>
+        <v>-98786</v>
       </c>
       <c r="F38" t="n">
-        <v>60000</v>
+        <v>-487525</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>方土霖</t>
+          <t>智冠</t>
         </is>
       </c>
     </row>
@@ -6872,20 +6872,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -27 千股)</t>
+          <t>📉 20d 巨變(減碼 -68 千股)</t>
         </is>
       </c>
       <c r="C39" t="n">
+        <v>-182865</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-198674</v>
+      </c>
+      <c r="E39" t="n">
         <v>-198865</v>
       </c>
-      <c r="D39" t="n">
+      <c r="F39" t="n">
         <v>-131163</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-118250</v>
-      </c>
-      <c r="F39" t="n">
-        <v>-104203</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -6901,20 +6901,20 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -123 千股)</t>
+          <t>📉 20d 巨變(減碼 -20 千股)</t>
         </is>
       </c>
       <c r="C40" t="n">
+        <v>-318607</v>
+      </c>
+      <c r="D40" t="n">
+        <v>-635129</v>
+      </c>
+      <c r="E40" t="n">
         <v>-203949</v>
       </c>
-      <c r="D40" t="n">
+      <c r="F40" t="n">
         <v>-615273</v>
-      </c>
-      <c r="E40" t="n">
-        <v>-341000</v>
-      </c>
-      <c r="F40" t="n">
-        <v>-491807</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -6925,348 +6925,348 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -7,722 千股)</t>
+          <t>📉 20d 巨變(減碼 -70 千股)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>12549340</v>
+        <v>-67950</v>
       </c>
       <c r="D41" t="n">
-        <v>86797673</v>
+        <v>212461</v>
       </c>
       <c r="E41" t="n">
-        <v>10985380</v>
+        <v>-54361</v>
       </c>
       <c r="F41" t="n">
-        <v>94519818</v>
+        <v>282461</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>八方雲集</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -84 千股)</t>
+          <t>📉 20d 巨變(減碼 -545 千股)</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-54361</v>
+        <v>11959992</v>
       </c>
       <c r="D42" t="n">
-        <v>282461</v>
+        <v>86252968</v>
       </c>
       <c r="E42" t="n">
-        <v>-43361</v>
+        <v>12549340</v>
       </c>
       <c r="F42" t="n">
-        <v>366611</v>
+        <v>86797673</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 340 千股)</t>
+          <t>📉 20d 巨變(減碼 -70 千股)</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1295726</v>
+        <v>257201</v>
       </c>
       <c r="D43" t="n">
-        <v>6943957</v>
+        <v>-690754</v>
       </c>
       <c r="E43" t="n">
-        <v>237004</v>
+        <v>497924</v>
       </c>
       <c r="F43" t="n">
-        <v>6604004</v>
+        <v>-620937</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>亞力</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -161 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -222 千股)</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>497924</v>
+        <v>-37854</v>
       </c>
       <c r="D44" t="n">
-        <v>-620937</v>
+        <v>201507</v>
       </c>
       <c r="E44" t="n">
-        <v>539287</v>
+        <v>85895</v>
       </c>
       <c r="F44" t="n">
-        <v>-459547</v>
+        <v>423169</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>大綜</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -56 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,794 千股)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-351000</v>
+        <v>2802843</v>
       </c>
       <c r="D45" t="n">
-        <v>-1150333</v>
+        <v>1167165</v>
       </c>
       <c r="E45" t="n">
-        <v>-370000</v>
+        <v>3558955</v>
       </c>
       <c r="F45" t="n">
-        <v>-1094333</v>
+        <v>2961109</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>台燿</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -78 千股)</t>
+          <t>📈 20d 巨變(加碼 92 千股)</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>85895</v>
+        <v>251855</v>
       </c>
       <c r="D46" t="n">
-        <v>423169</v>
+        <v>-298921</v>
       </c>
       <c r="E46" t="n">
-        <v>123187</v>
+        <v>162920</v>
       </c>
       <c r="F46" t="n">
-        <v>501327</v>
+        <v>-390598</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>漢科</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,971 千股)</t>
+          <t>📈 20d 巨變(加碼 1,813 千股)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>3558955</v>
+        <v>-3355756</v>
       </c>
       <c r="D47" t="n">
-        <v>2961109</v>
+        <v>166137</v>
       </c>
       <c r="E47" t="n">
-        <v>3694404</v>
+        <v>-4238594</v>
       </c>
       <c r="F47" t="n">
-        <v>990413</v>
+        <v>-1646735</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>玉晶光</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 274 千股)</t>
+          <t>📈 20d 巨變(加碼 1,931 千股)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2841999</v>
+        <v>-7457376</v>
       </c>
       <c r="D48" t="n">
-        <v>4486460</v>
+        <v>2302769</v>
       </c>
       <c r="E48" t="n">
-        <v>2172040</v>
+        <v>-4606790</v>
       </c>
       <c r="F48" t="n">
-        <v>4212847</v>
+        <v>371360</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,121 千股)</t>
+          <t>📉 20d 巨變(減碼 -52 千股)</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-4606790</v>
+        <v>3203931</v>
       </c>
       <c r="D49" t="n">
-        <v>371360</v>
+        <v>4434632</v>
       </c>
       <c r="E49" t="n">
-        <v>-316461</v>
+        <v>2841999</v>
       </c>
       <c r="F49" t="n">
-        <v>1492025</v>
+        <v>4486460</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>立隆電</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 62 千股)</t>
+          <t>📈 20d 巨變(加碼 193 千股)</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-4238594</v>
+        <v>-2299614</v>
       </c>
       <c r="D50" t="n">
-        <v>-1646735</v>
+        <v>-2987077</v>
       </c>
       <c r="E50" t="n">
-        <v>-4812156</v>
+        <v>-2214029</v>
       </c>
       <c r="F50" t="n">
-        <v>-1708334</v>
+        <v>-3179969</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>世芯-KY</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 112 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -8,917 千股)</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-2214029</v>
+        <v>-35204437</v>
       </c>
       <c r="D51" t="n">
-        <v>-3179969</v>
+        <v>-12306613</v>
       </c>
       <c r="E51" t="n">
-        <v>-2803263</v>
+        <v>5643449</v>
       </c>
       <c r="F51" t="n">
-        <v>-3292463</v>
+        <v>-3389805</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -20,587 千股)</t>
+          <t>📈 20d 巨變(加碼 1,679 千股)</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5643449</v>
+        <v>-7896331</v>
       </c>
       <c r="D52" t="n">
-        <v>-3389805</v>
+        <v>-19223011</v>
       </c>
       <c r="E52" t="n">
-        <v>27960674</v>
+        <v>-8378962</v>
       </c>
       <c r="F52" t="n">
-        <v>17197528</v>
+        <v>-20902043</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
@@ -7278,20 +7278,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -9,662 千股)</t>
+          <t>📉 20d 巨變(減碼 -5,460 千股)</t>
         </is>
       </c>
       <c r="C53" t="n">
+        <v>419818</v>
+      </c>
+      <c r="D53" t="n">
+        <v>25734731</v>
+      </c>
+      <c r="E53" t="n">
         <v>7661571</v>
       </c>
-      <c r="D53" t="n">
+      <c r="F53" t="n">
         <v>31195069</v>
-      </c>
-      <c r="E53" t="n">
-        <v>26025516</v>
-      </c>
-      <c r="F53" t="n">
-        <v>40857502</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -7302,261 +7302,261 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 6,045 千股)</t>
+          <t>📉 20d 巨變(減碼 -77 千股)</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-8378962</v>
+        <v>-1223194</v>
       </c>
       <c r="D54" t="n">
-        <v>-20902043</v>
+        <v>2666974</v>
       </c>
       <c r="E54" t="n">
-        <v>-5641323</v>
+        <v>-1353958</v>
       </c>
       <c r="F54" t="n">
-        <v>-26946699</v>
+        <v>2743730</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>鈊象</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 426 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -184 千股)</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-1353958</v>
+        <v>-4564</v>
       </c>
       <c r="D55" t="n">
-        <v>2743730</v>
+        <v>1567586</v>
       </c>
       <c r="E55" t="n">
-        <v>-1699437</v>
+        <v>282726</v>
       </c>
       <c r="F55" t="n">
-        <v>2317442</v>
+        <v>1751207</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>士電</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,255 千股)</t>
+          <t>📈 20d 巨變(加碼 55 千股)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>282726</v>
+        <v>-49231</v>
       </c>
       <c r="D56" t="n">
-        <v>1751207</v>
+        <v>79725</v>
       </c>
       <c r="E56" t="n">
-        <v>1079565</v>
+        <v>-15672</v>
       </c>
       <c r="F56" t="n">
-        <v>3006460</v>
+        <v>24972</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>達欣工</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -338 千股)</t>
+          <t>📈 20d 巨變(加碼 126 千股)</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-15672</v>
+        <v>-436252</v>
       </c>
       <c r="D57" t="n">
-        <v>24972</v>
+        <v>-3041455</v>
       </c>
       <c r="E57" t="n">
-        <v>20257</v>
+        <v>-714104</v>
       </c>
       <c r="F57" t="n">
-        <v>362864</v>
+        <v>-3167465</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>鉅祥</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -11 千股)</t>
+          <t>📉 20d 巨變(減碼 -10 千股)</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-714104</v>
+        <v>-44998</v>
       </c>
       <c r="D58" t="n">
-        <v>-3167465</v>
+        <v>403653</v>
       </c>
       <c r="E58" t="n">
-        <v>-735694</v>
+        <v>-192103</v>
       </c>
       <c r="F58" t="n">
-        <v>-3156755</v>
+        <v>413793</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>普萊德</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -49 千股)</t>
+          <t>🔴 外資 5d 翻紅</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-192103</v>
+        <v>-279283</v>
       </c>
       <c r="D59" t="n">
-        <v>413793</v>
+        <v>-1785436</v>
       </c>
       <c r="E59" t="n">
-        <v>-162311</v>
+        <v>183681</v>
       </c>
       <c r="F59" t="n">
-        <v>463056</v>
+        <v>-1788320</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>勝一</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -340 千股)</t>
+          <t>📈 20d 巨變(加碼 51 千股)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>183681</v>
+        <v>-170317</v>
       </c>
       <c r="D60" t="n">
-        <v>-1788320</v>
+        <v>102700</v>
       </c>
       <c r="E60" t="n">
-        <v>237681</v>
+        <v>-251769</v>
       </c>
       <c r="F60" t="n">
-        <v>-1448320</v>
+        <v>52145</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>祥碩</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -302 千股)</t>
+          <t>📈 20d 巨變(加碼 125 千股)</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-217110</v>
+        <v>-51551</v>
       </c>
       <c r="D61" t="n">
-        <v>-1385941</v>
+        <v>-421957</v>
       </c>
       <c r="E61" t="n">
-        <v>-406723</v>
+        <v>-91090</v>
       </c>
       <c r="F61" t="n">
-        <v>-1083994</v>
+        <v>-546821</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 136 千股)</t>
+          <t>📉 20d 巨變(減碼 -106 千股)</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-251769</v>
+        <v>-245612</v>
       </c>
       <c r="D62" t="n">
-        <v>52145</v>
+        <v>-1492337</v>
       </c>
       <c r="E62" t="n">
-        <v>-371745</v>
+        <v>-217110</v>
       </c>
       <c r="F62" t="n">
-        <v>-84178</v>
+        <v>-1385941</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>信立</t>
         </is>
       </c>
     </row>
@@ -7568,20 +7568,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,291 千股)</t>
+          <t>📈 20d 巨變(加碼 10 千股)</t>
         </is>
       </c>
       <c r="C63" t="n">
+        <v>-1134938</v>
+      </c>
+      <c r="D63" t="n">
+        <v>-3000021</v>
+      </c>
+      <c r="E63" t="n">
         <v>-382481</v>
       </c>
-      <c r="D63" t="n">
+      <c r="F63" t="n">
         <v>-3009982</v>
-      </c>
-      <c r="E63" t="n">
-        <v>-375023</v>
-      </c>
-      <c r="F63" t="n">
-        <v>-4301050</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -7592,29 +7592,29 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 220 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,193 千股)</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-562452</v>
+        <v>-2969338</v>
       </c>
       <c r="D64" t="n">
-        <v>-3750899</v>
+        <v>-3379534</v>
       </c>
       <c r="E64" t="n">
-        <v>-2905006</v>
+        <v>-2408322</v>
       </c>
       <c r="F64" t="n">
-        <v>-3971344</v>
+        <v>-1186464</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
@@ -7626,20 +7626,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -175 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 475 千股)</t>
         </is>
       </c>
       <c r="C65" t="n">
+        <v>-688347</v>
+      </c>
+      <c r="D65" t="n">
+        <v>-233602</v>
+      </c>
+      <c r="E65" t="n">
         <v>64559</v>
       </c>
-      <c r="D65" t="n">
+      <c r="F65" t="n">
         <v>-708781</v>
-      </c>
-      <c r="E65" t="n">
-        <v>-72098</v>
-      </c>
-      <c r="F65" t="n">
-        <v>-533829</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -7650,87 +7650,87 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 471 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 233 千股)</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-1531836</v>
+        <v>13079639</v>
       </c>
       <c r="D66" t="n">
-        <v>-121630</v>
+        <v>29016789</v>
       </c>
       <c r="E66" t="n">
-        <v>-1078273</v>
+        <v>-1028944</v>
       </c>
       <c r="F66" t="n">
-        <v>-592447</v>
+        <v>28783401</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,489 千股)</t>
+          <t>📉 20d 巨變(減碼 -159 千股)</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-2408322</v>
+        <v>-1598741</v>
       </c>
       <c r="D67" t="n">
-        <v>-1186464</v>
+        <v>-280642</v>
       </c>
       <c r="E67" t="n">
-        <v>-885577</v>
+        <v>-1531836</v>
       </c>
       <c r="F67" t="n">
-        <v>302106</v>
+        <v>-121630</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>宇瞻</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -5,225 千股)</t>
+          <t>📈 20d 巨變(加碼 5,822 千股)</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-1028944</v>
+        <v>-38830336</v>
       </c>
       <c r="D68" t="n">
-        <v>28783401</v>
+        <v>-108275409</v>
       </c>
       <c r="E68" t="n">
-        <v>-1956622</v>
+        <v>-83197181</v>
       </c>
       <c r="F68" t="n">
-        <v>34007934</v>
+        <v>-114097650</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
@@ -7742,20 +7742,20 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,173 千股)</t>
+          <t>📈 20d 巨變(加碼 423 千股)</t>
         </is>
       </c>
       <c r="C69" t="n">
+        <v>3388449</v>
+      </c>
+      <c r="D69" t="n">
+        <v>-563808</v>
+      </c>
+      <c r="E69" t="n">
         <v>3043389</v>
       </c>
-      <c r="D69" t="n">
+      <c r="F69" t="n">
         <v>-986949</v>
-      </c>
-      <c r="E69" t="n">
-        <v>1754411</v>
-      </c>
-      <c r="F69" t="n">
-        <v>-2159820</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -7766,87 +7766,87 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -10,309 千股)</t>
+          <t>📉 20d 巨變(減碼 -12,785 千股)</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-83197181</v>
+        <v>-1867365</v>
       </c>
       <c r="D70" t="n">
-        <v>-114097650</v>
+        <v>-22783426</v>
       </c>
       <c r="E70" t="n">
-        <v>-80785282</v>
+        <v>-1600522</v>
       </c>
       <c r="F70" t="n">
-        <v>-103788976</v>
+        <v>-9998157</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -445 千股)</t>
+          <t>📉 20d 巨變(減碼 -91 千股)</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-5168732</v>
+        <v>-104949</v>
       </c>
       <c r="D71" t="n">
-        <v>-6017077</v>
+        <v>-354477</v>
       </c>
       <c r="E71" t="n">
-        <v>-5728973</v>
+        <v>-29794</v>
       </c>
       <c r="F71" t="n">
-        <v>-5572346</v>
+        <v>-263388</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>德昌</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -62 千股)</t>
+          <t>📈 20d 巨變(加碼 72 千股)</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-29794</v>
+        <v>-4501754</v>
       </c>
       <c r="D72" t="n">
-        <v>-263388</v>
+        <v>-5944830</v>
       </c>
       <c r="E72" t="n">
-        <v>-26454</v>
+        <v>-5168732</v>
       </c>
       <c r="F72" t="n">
-        <v>-201203</v>
+        <v>-6017077</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
@@ -7858,20 +7858,20 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -17 千股)</t>
+          <t>📈 20d 巨變(加碼 53 千股)</t>
         </is>
       </c>
       <c r="C73" t="n">
+        <v>354302</v>
+      </c>
+      <c r="D73" t="n">
+        <v>752006</v>
+      </c>
+      <c r="E73" t="n">
         <v>390024</v>
       </c>
-      <c r="D73" t="n">
+      <c r="F73" t="n">
         <v>698576</v>
-      </c>
-      <c r="E73" t="n">
-        <v>376060</v>
-      </c>
-      <c r="F73" t="n">
-        <v>715596</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -7882,58 +7882,58 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,242 千股)</t>
+          <t>📈 20d 巨變(加碼 1,037 千股)</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-1600522</v>
+        <v>-1176757</v>
       </c>
       <c r="D74" t="n">
-        <v>-9998157</v>
+        <v>-8606147</v>
       </c>
       <c r="E74" t="n">
-        <v>-12413589</v>
+        <v>-1693434</v>
       </c>
       <c r="F74" t="n">
-        <v>-12240223</v>
+        <v>-9643401</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>智易</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 577 千股)</t>
+          <t>📉 20d 巨變(減碼 -14 千股)</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-1693434</v>
+        <v>5000</v>
       </c>
       <c r="D75" t="n">
-        <v>-9643401</v>
+        <v>-67550</v>
       </c>
       <c r="E75" t="n">
-        <v>-1759434</v>
+        <v>18000</v>
       </c>
       <c r="F75" t="n">
-        <v>-10220401</v>
+        <v>-53550</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>友輝</t>
         </is>
       </c>
     </row>
@@ -7945,20 +7945,20 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -103 千股)</t>
+          <t>📈 20d 巨變(加碼 391 千股)</t>
         </is>
       </c>
       <c r="C76" t="n">
+        <v>-1228909</v>
+      </c>
+      <c r="D76" t="n">
+        <v>557944</v>
+      </c>
+      <c r="E76" t="n">
         <v>-1270205</v>
       </c>
-      <c r="D76" t="n">
+      <c r="F76" t="n">
         <v>167228</v>
-      </c>
-      <c r="E76" t="n">
-        <v>-2012472</v>
-      </c>
-      <c r="F76" t="n">
-        <v>270205</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -7969,87 +7969,87 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 135 千股)</t>
+          <t>📈 20d 巨變(加碼 1,932 千股)</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-1213098</v>
+        <v>-1386713</v>
       </c>
       <c r="D77" t="n">
-        <v>-2857317</v>
+        <v>-5111730</v>
       </c>
       <c r="E77" t="n">
-        <v>-1441098</v>
+        <v>-18026110</v>
       </c>
       <c r="F77" t="n">
-        <v>-2992140</v>
+        <v>-7043631</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 11,488 千股)</t>
+          <t>📈 20d 巨變(加碼 289 千股)</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-18026110</v>
+        <v>801511</v>
       </c>
       <c r="D78" t="n">
-        <v>-7043631</v>
+        <v>-1496023</v>
       </c>
       <c r="E78" t="n">
-        <v>-29474185</v>
+        <v>474984</v>
       </c>
       <c r="F78" t="n">
-        <v>-18531211</v>
+        <v>-1784925</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>精測</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 372 千股)</t>
+          <t>📉 20d 巨變(減碼 -173 千股)</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>474984</v>
+        <v>-336446</v>
       </c>
       <c r="D79" t="n">
-        <v>-1784925</v>
+        <v>-1086486</v>
       </c>
       <c r="E79" t="n">
-        <v>-116797</v>
+        <v>-754085</v>
       </c>
       <c r="F79" t="n">
-        <v>-2156849</v>
+        <v>-913379</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
     </row>
@@ -8061,20 +8061,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 9,216 千股)</t>
+          <t>📈 20d 巨變(加碼 5,467 千股)</t>
         </is>
       </c>
       <c r="C80" t="n">
+        <v>-6226405</v>
+      </c>
+      <c r="D80" t="n">
+        <v>-20371886</v>
+      </c>
+      <c r="E80" t="n">
         <v>-17122734</v>
       </c>
-      <c r="D80" t="n">
+      <c r="F80" t="n">
         <v>-25838539</v>
-      </c>
-      <c r="E80" t="n">
-        <v>-19911926</v>
-      </c>
-      <c r="F80" t="n">
-        <v>-35054452</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -8085,607 +8085,520 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 154 千股)</t>
+          <t>📉 20d 巨變(減碼 -152 千股)</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>493411</v>
+        <v>-125000</v>
       </c>
       <c r="D81" t="n">
-        <v>514169</v>
+        <v>262009</v>
       </c>
       <c r="E81" t="n">
-        <v>362421</v>
+        <v>-67000</v>
       </c>
       <c r="F81" t="n">
-        <v>360169</v>
+        <v>414009</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -25 千股)</t>
+          <t>📈 20d 巨變(加碼 31 千股)</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-67000</v>
+        <v>515624</v>
       </c>
       <c r="D82" t="n">
-        <v>414009</v>
+        <v>545524</v>
       </c>
       <c r="E82" t="n">
-        <v>-94019</v>
+        <v>493411</v>
       </c>
       <c r="F82" t="n">
-        <v>439009</v>
+        <v>514169</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>東科-KY</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -303 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,164 千股)</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-754085</v>
+        <v>2098171</v>
       </c>
       <c r="D83" t="n">
-        <v>-913379</v>
+        <v>-796018</v>
       </c>
       <c r="E83" t="n">
-        <v>-699308</v>
+        <v>1555751</v>
       </c>
       <c r="F83" t="n">
-        <v>-610093</v>
+        <v>368137</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 911 千股)</t>
+          <t>📈 20d 巨變(加碼 5,630 千股)</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>1555751</v>
+        <v>-1437432</v>
       </c>
       <c r="D84" t="n">
-        <v>368137</v>
+        <v>-12479349</v>
       </c>
       <c r="E84" t="n">
-        <v>1661861</v>
+        <v>-1970432</v>
       </c>
       <c r="F84" t="n">
-        <v>-542475</v>
+        <v>-18109219</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>宏捷科</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 283 千股)</t>
+          <t>📈 20d 巨變(加碼 1,904 千股)</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-1970432</v>
+        <v>1889863</v>
       </c>
       <c r="D85" t="n">
-        <v>-18109219</v>
+        <v>917111</v>
       </c>
       <c r="E85" t="n">
-        <v>-2533523</v>
+        <v>1057185</v>
       </c>
       <c r="F85" t="n">
-        <v>-18392310</v>
+        <v>-986890</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>研華</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 17 千股)</t>
+          <t>📈 20d 巨變(加碼 13,841 千股)</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>18000</v>
+        <v>42107380</v>
       </c>
       <c r="D86" t="n">
-        <v>-53550</v>
+        <v>54138286</v>
       </c>
       <c r="E86" t="n">
-        <v>33000</v>
+        <v>36088567</v>
       </c>
       <c r="F86" t="n">
-        <v>-70550</v>
+        <v>40297762</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -960 千股)</t>
+          <t>📉 20d 巨變(減碼 -131 千股)</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1057185</v>
+        <v>-183155</v>
       </c>
       <c r="D87" t="n">
-        <v>-986890</v>
+        <v>40309</v>
       </c>
       <c r="E87" t="n">
-        <v>-581347</v>
+        <v>-58895</v>
       </c>
       <c r="F87" t="n">
-        <v>-26443</v>
+        <v>171210</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>中保科</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 13,336 千股)</t>
+          <t>📉 20d 巨變(減碼 -10 千股)</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>36088567</v>
+        <v>-73183</v>
       </c>
       <c r="D88" t="n">
-        <v>40297762</v>
+        <v>-18842</v>
       </c>
       <c r="E88" t="n">
-        <v>25199166</v>
+        <v>-16098</v>
       </c>
       <c r="F88" t="n">
-        <v>26962211</v>
+        <v>-8690</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>竹陞科技</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -104 千股)</t>
+          <t>📉 20d 巨變(減碼 -68 千股)</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-16098</v>
+        <v>32</v>
       </c>
       <c r="D89" t="n">
-        <v>-8690</v>
+        <v>53602</v>
       </c>
       <c r="E89" t="n">
-        <v>135934</v>
+        <v>74065</v>
       </c>
       <c r="F89" t="n">
-        <v>95526</v>
+        <v>121635</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>安碁資訊</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -22 千股)</t>
+          <t>📈 20d 巨變(加碼 1,364 千股)</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>74065</v>
+        <v>-457192</v>
       </c>
       <c r="D90" t="n">
-        <v>121635</v>
+        <v>-7958076</v>
       </c>
       <c r="E90" t="n">
-        <v>99860</v>
+        <v>-606122</v>
       </c>
       <c r="F90" t="n">
-        <v>143635</v>
+        <v>-9321751</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 4,981 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,142 千股)</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-606122</v>
+        <v>4151571</v>
       </c>
       <c r="D91" t="n">
-        <v>-9321751</v>
+        <v>21136419</v>
       </c>
       <c r="E91" t="n">
-        <v>-723700</v>
+        <v>5298555</v>
       </c>
       <c r="F91" t="n">
-        <v>-14302501</v>
+        <v>23278823</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,050 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -802 千股)</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>5298555</v>
+        <v>-47834</v>
       </c>
       <c r="D92" t="n">
-        <v>23278823</v>
+        <v>4281687</v>
       </c>
       <c r="E92" t="n">
-        <v>3157335</v>
+        <v>1223096</v>
       </c>
       <c r="F92" t="n">
-        <v>24329068</v>
+        <v>5083594</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -16 千股)</t>
+          <t>📉 20d 巨變(減碼 -4,993 千股)</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-148702</v>
+        <v>-141118626</v>
       </c>
       <c r="D93" t="n">
-        <v>-113045</v>
+        <v>-10166434</v>
       </c>
       <c r="E93" t="n">
-        <v>-115412</v>
+        <v>-44426223</v>
       </c>
       <c r="F93" t="n">
-        <v>-97045</v>
+        <v>-5173895</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -33,680 千股)</t>
+          <t>📉 20d 巨變(減碼 -948 千股)</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-44426223</v>
+        <v>-2149767</v>
       </c>
       <c r="D94" t="n">
-        <v>-5173895</v>
+        <v>-10124082</v>
       </c>
       <c r="E94" t="n">
-        <v>45227120</v>
+        <v>-1217245</v>
       </c>
       <c r="F94" t="n">
-        <v>28506329</v>
+        <v>-9176008</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>緯穎</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -454 千股)</t>
+          <t>📉 20d 巨變(減碼 -462 千股)</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1223096</v>
+        <v>-263181</v>
       </c>
       <c r="D95" t="n">
-        <v>5083594</v>
+        <v>735605</v>
       </c>
       <c r="E95" t="n">
-        <v>3401305</v>
+        <v>-176732</v>
       </c>
       <c r="F95" t="n">
-        <v>5537305</v>
+        <v>1197177</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>創意</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -33 千股)</t>
+          <t>📈 20d 巨變(加碼 1,185 千股)</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-176732</v>
+        <v>919078</v>
       </c>
       <c r="D96" t="n">
-        <v>1197177</v>
+        <v>-7611331</v>
       </c>
       <c r="E96" t="n">
-        <v>-52278</v>
+        <v>539018</v>
       </c>
       <c r="F96" t="n">
-        <v>1229728</v>
+        <v>-8796536</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>金像電</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -50 千股)</t>
+          <t>📉 20d 巨變(減碼 -407 千股)</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-1217245</v>
+        <v>282495</v>
       </c>
       <c r="D97" t="n">
-        <v>-9176008</v>
+        <v>-3561387</v>
       </c>
       <c r="E97" t="n">
-        <v>-1985731</v>
+        <v>434157</v>
       </c>
       <c r="F97" t="n">
-        <v>-9125837</v>
+        <v>-3154601</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>高技</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -25 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -527 千股)</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>90500</v>
+        <v>-105293</v>
       </c>
       <c r="D98" t="n">
-        <v>244134</v>
+        <v>-1606778</v>
       </c>
       <c r="E98" t="n">
-        <v>151301</v>
+        <v>135533</v>
       </c>
       <c r="F98" t="n">
-        <v>269458</v>
+        <v>-1079947</v>
       </c>
       <c r="G98" t="inlineStr">
-        <is>
-          <t>信驊</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 946 千股)</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>539018</v>
-      </c>
-      <c r="D99" t="n">
-        <v>-8796536</v>
-      </c>
-      <c r="E99" t="n">
-        <v>-611183</v>
-      </c>
-      <c r="F99" t="n">
-        <v>-9742886</v>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>金像電</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>5439</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 156 千股)</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>434157</v>
-      </c>
-      <c r="D100" t="n">
-        <v>-3154601</v>
-      </c>
-      <c r="E100" t="n">
-        <v>392272</v>
-      </c>
-      <c r="F100" t="n">
-        <v>-3310295</v>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>高技</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 281 千股)</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>135533</v>
-      </c>
-      <c r="D101" t="n">
-        <v>-1079947</v>
-      </c>
-      <c r="E101" t="n">
-        <v>-224865</v>
-      </c>
-      <c r="F101" t="n">
-        <v>-1360822</v>
-      </c>
-      <c r="G101" t="inlineStr">
         <is>
           <t>萬潤</t>
         </is>

--- a/data/台股_外資雷達.xlsx
+++ b/data/台股_外資雷達.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11960</v>
+        <v>10963</v>
       </c>
       <c r="D2" t="n">
-        <v>86253</v>
+        <v>69855</v>
       </c>
       <c r="E2" t="n">
-        <v>187103</v>
+        <v>199536</v>
       </c>
       <c r="F2" t="n">
-        <v>823</v>
+        <v>342</v>
       </c>
       <c r="G2" t="n">
-        <v>5944</v>
+        <v>6318</v>
       </c>
       <c r="H2" t="n">
-        <v>-3428</v>
+        <v>-3492</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -547,22 +547,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>42107</v>
+        <v>43395</v>
       </c>
       <c r="D3" t="n">
-        <v>54138</v>
+        <v>61117</v>
       </c>
       <c r="E3" t="n">
-        <v>114504</v>
+        <v>130455</v>
       </c>
       <c r="F3" t="n">
-        <v>1165</v>
+        <v>-62</v>
       </c>
       <c r="G3" t="n">
-        <v>854</v>
+        <v>588</v>
       </c>
       <c r="H3" t="n">
-        <v>-208</v>
+        <v>-125</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3200</v>
+        <v>-3057</v>
       </c>
       <c r="D4" t="n">
-        <v>37669</v>
+        <v>31879</v>
       </c>
       <c r="E4" t="n">
-        <v>568591</v>
+        <v>570598</v>
       </c>
       <c r="F4" t="n">
-        <v>2026</v>
+        <v>4355</v>
       </c>
       <c r="G4" t="n">
-        <v>15009</v>
+        <v>17056</v>
       </c>
       <c r="H4" t="n">
-        <v>-4258</v>
+        <v>-2719</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -640,31 +640,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13080</v>
+        <v>-5781</v>
       </c>
       <c r="D5" t="n">
-        <v>29017</v>
+        <v>26017</v>
       </c>
       <c r="E5" t="n">
-        <v>-19077</v>
+        <v>-20838</v>
       </c>
       <c r="F5" t="n">
-        <v>575</v>
+        <v>-1329</v>
       </c>
       <c r="G5" t="n">
-        <v>8107</v>
+        <v>-16172</v>
       </c>
       <c r="H5" t="n">
-        <v>-140</v>
+        <v>1258</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -677,45 +677,45 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速*</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>420</v>
+        <v>-177</v>
       </c>
       <c r="D6" t="n">
-        <v>25735</v>
+        <v>25632</v>
       </c>
       <c r="E6" t="n">
-        <v>-41782</v>
+        <v>-20465</v>
       </c>
       <c r="F6" t="n">
-        <v>98</v>
+        <v>4344</v>
       </c>
       <c r="G6" t="n">
-        <v>-18458</v>
+        <v>12173</v>
       </c>
       <c r="H6" t="n">
-        <v>1035</v>
+        <v>752</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -728,15 +728,15 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>🐌 龜速*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4152</v>
+        <v>3420</v>
       </c>
       <c r="D7" t="n">
-        <v>21136</v>
+        <v>19387</v>
       </c>
       <c r="E7" t="n">
-        <v>84343</v>
+        <v>88457</v>
       </c>
       <c r="F7" t="n">
-        <v>889</v>
+        <v>335</v>
       </c>
       <c r="G7" t="n">
-        <v>-953</v>
+        <v>-577</v>
       </c>
       <c r="H7" t="n">
-        <v>-944</v>
+        <v>-940</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -802,22 +802,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>309</v>
+        <v>182</v>
       </c>
       <c r="D8" t="n">
         <v>14692</v>
       </c>
       <c r="E8" t="n">
-        <v>22787</v>
+        <v>22449</v>
       </c>
       <c r="F8" t="n">
-        <v>-132</v>
+        <v>-69</v>
       </c>
       <c r="G8" t="n">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="H8" t="n">
-        <v>-80</v>
+        <v>-3</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -844,82 +844,82 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>88</v>
+        <v>-64654</v>
       </c>
       <c r="D9" t="n">
-        <v>9416</v>
+        <v>12948</v>
       </c>
       <c r="E9" t="n">
-        <v>11942</v>
+        <v>9565</v>
       </c>
       <c r="F9" t="n">
-        <v>-170</v>
+        <v>-15785</v>
       </c>
       <c r="G9" t="n">
-        <v>901</v>
+        <v>-35949</v>
       </c>
       <c r="H9" t="n">
-        <v>667</v>
+        <v>-6097</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>🟢 加碼</t>
+          <t>🚀 大買</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1067</v>
+        <v>-1272</v>
       </c>
       <c r="D10" t="n">
-        <v>6942</v>
+        <v>8458</v>
       </c>
       <c r="E10" t="n">
-        <v>12827</v>
+        <v>10714</v>
       </c>
       <c r="F10" t="n">
-        <v>48</v>
+        <v>-4</v>
       </c>
       <c r="G10" t="n">
-        <v>-1106</v>
+        <v>902</v>
       </c>
       <c r="H10" t="n">
-        <v>-143</v>
+        <v>867</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -928,49 +928,49 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3204</v>
+        <v>-24297</v>
       </c>
       <c r="D11" t="n">
-        <v>4435</v>
+        <v>7949</v>
       </c>
       <c r="E11" t="n">
-        <v>13695</v>
+        <v>59718</v>
       </c>
       <c r="F11" t="n">
-        <v>-2599</v>
+        <v>-4680</v>
       </c>
       <c r="G11" t="n">
-        <v>-6166</v>
+        <v>-8869</v>
       </c>
       <c r="H11" t="n">
-        <v>-49</v>
+        <v>-3297</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -979,11 +979,11 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1006,22 +1006,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-48</v>
+        <v>1707</v>
       </c>
       <c r="D12" t="n">
-        <v>4282</v>
+        <v>5495</v>
       </c>
       <c r="E12" t="n">
-        <v>1604</v>
+        <v>5968</v>
       </c>
       <c r="F12" t="n">
-        <v>428</v>
+        <v>-233</v>
       </c>
       <c r="G12" t="n">
-        <v>-747</v>
+        <v>-184</v>
       </c>
       <c r="H12" t="n">
-        <v>408</v>
+        <v>888</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1048,31 +1048,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1255</v>
+        <v>409</v>
       </c>
       <c r="D13" t="n">
-        <v>3860</v>
+        <v>4838</v>
       </c>
       <c r="E13" t="n">
-        <v>24234</v>
+        <v>11538</v>
       </c>
       <c r="F13" t="n">
-        <v>-35</v>
+        <v>452</v>
       </c>
       <c r="G13" t="n">
-        <v>-556</v>
+        <v>-720</v>
       </c>
       <c r="H13" t="n">
-        <v>-230</v>
+        <v>-120</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1081,49 +1081,49 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-1223</v>
+        <v>6625</v>
       </c>
       <c r="D14" t="n">
-        <v>2667</v>
+        <v>4422</v>
       </c>
       <c r="E14" t="n">
-        <v>9912</v>
+        <v>-5821</v>
       </c>
       <c r="F14" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-13437</v>
+        <v>-8</v>
       </c>
       <c r="H14" t="n">
-        <v>-116</v>
+        <v>586</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1136,45 +1136,45 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1041</v>
+        <v>3365</v>
       </c>
       <c r="D15" t="n">
-        <v>2316</v>
+        <v>4397</v>
       </c>
       <c r="E15" t="n">
-        <v>-402</v>
+        <v>15894</v>
       </c>
       <c r="F15" t="n">
-        <v>506</v>
+        <v>-2613</v>
       </c>
       <c r="G15" t="n">
-        <v>-707</v>
+        <v>-6175</v>
       </c>
       <c r="H15" t="n">
-        <v>-235</v>
+        <v>-65</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1183,11 +1183,11 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1195,37 +1195,37 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-7457</v>
+        <v>333</v>
       </c>
       <c r="D16" t="n">
-        <v>2303</v>
+        <v>4347</v>
       </c>
       <c r="E16" t="n">
-        <v>10566</v>
+        <v>24405</v>
       </c>
       <c r="F16" t="n">
-        <v>420</v>
+        <v>-9</v>
       </c>
       <c r="G16" t="n">
-        <v>1389</v>
+        <v>-568</v>
       </c>
       <c r="H16" t="n">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1234,49 +1234,49 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-529</v>
+        <v>-7220</v>
       </c>
       <c r="D17" t="n">
-        <v>2048</v>
+        <v>2677</v>
       </c>
       <c r="E17" t="n">
-        <v>-1920</v>
+        <v>10653</v>
       </c>
       <c r="F17" t="n">
-        <v>773</v>
+        <v>509</v>
       </c>
       <c r="G17" t="n">
-        <v>-1206</v>
+        <v>1473</v>
       </c>
       <c r="H17" t="n">
-        <v>201</v>
+        <v>808</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1285,11 +1285,11 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1297,37 +1297,37 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1804</v>
+        <v>-1139</v>
       </c>
       <c r="D18" t="n">
-        <v>2037</v>
+        <v>2067</v>
       </c>
       <c r="E18" t="n">
-        <v>6335</v>
+        <v>10072</v>
       </c>
       <c r="F18" t="n">
-        <v>37</v>
+        <v>335</v>
       </c>
       <c r="G18" t="n">
-        <v>-126</v>
+        <v>-12624</v>
       </c>
       <c r="H18" t="n">
-        <v>-104</v>
+        <v>-122</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1336,49 +1336,49 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-5</v>
+        <v>840</v>
       </c>
       <c r="D19" t="n">
-        <v>1568</v>
+        <v>1918</v>
       </c>
       <c r="E19" t="n">
-        <v>373</v>
+        <v>6120</v>
       </c>
       <c r="F19" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G19" t="n">
-        <v>7</v>
+        <v>-260</v>
       </c>
       <c r="H19" t="n">
-        <v>-70</v>
+        <v>-20</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1387,19 +1387,19 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1414,22 +1414,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2803</v>
+        <v>1072</v>
       </c>
       <c r="D20" t="n">
-        <v>1167</v>
+        <v>1911</v>
       </c>
       <c r="E20" t="n">
-        <v>-2366</v>
+        <v>-2030</v>
       </c>
       <c r="F20" t="n">
-        <v>-4130</v>
+        <v>-1117</v>
       </c>
       <c r="G20" t="n">
-        <v>-9440</v>
+        <v>-9956</v>
       </c>
       <c r="H20" t="n">
-        <v>-294</v>
+        <v>-67</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1456,31 +1456,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-9</v>
+        <v>2306</v>
       </c>
       <c r="D21" t="n">
-        <v>1080</v>
+        <v>1819</v>
       </c>
       <c r="E21" t="n">
-        <v>-494</v>
+        <v>218</v>
       </c>
       <c r="F21" t="n">
-        <v>452</v>
+        <v>-72</v>
       </c>
       <c r="G21" t="n">
-        <v>626</v>
+        <v>876</v>
       </c>
       <c r="H21" t="n">
-        <v>-41</v>
+        <v>-215</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1489,49 +1489,49 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>79</v>
+        <v>561</v>
       </c>
       <c r="D22" t="n">
-        <v>992</v>
+        <v>1769</v>
       </c>
       <c r="E22" t="n">
-        <v>2165</v>
+        <v>-297</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>533</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="H22" t="n">
-        <v>-45</v>
+        <v>-239</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1544,45 +1544,45 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1890</v>
+        <v>-623</v>
       </c>
       <c r="D23" t="n">
-        <v>917</v>
+        <v>1705</v>
       </c>
       <c r="E23" t="n">
-        <v>294</v>
+        <v>-2122</v>
       </c>
       <c r="F23" t="n">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="G23" t="n">
-        <v>1597</v>
+        <v>-404</v>
       </c>
       <c r="H23" t="n">
-        <v>-119</v>
+        <v>165</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1591,49 +1591,49 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>805</v>
+        <v>-765</v>
       </c>
       <c r="D24" t="n">
-        <v>885</v>
+        <v>1279</v>
       </c>
       <c r="E24" t="n">
-        <v>5109</v>
+        <v>26</v>
       </c>
       <c r="F24" t="n">
-        <v>-170</v>
+        <v>27</v>
       </c>
       <c r="G24" t="n">
-        <v>2575</v>
+        <v>57</v>
       </c>
       <c r="H24" t="n">
-        <v>-226</v>
+        <v>-20</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1642,49 +1642,49 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>230</v>
+        <v>20</v>
       </c>
       <c r="D25" t="n">
-        <v>866</v>
+        <v>1231</v>
       </c>
       <c r="E25" t="n">
-        <v>-1397</v>
+        <v>-330</v>
       </c>
       <c r="F25" t="n">
-        <v>-181</v>
+        <v>340</v>
       </c>
       <c r="G25" t="n">
-        <v>318</v>
+        <v>300</v>
       </c>
       <c r="H25" t="n">
-        <v>57</v>
+        <v>-33</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1697,36 +1697,36 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>合機</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>354</v>
+        <v>34</v>
       </c>
       <c r="D26" t="n">
-        <v>752</v>
+        <v>968</v>
       </c>
       <c r="E26" t="n">
-        <v>234</v>
+        <v>1740</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -1735,7 +1735,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>-45</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1744,11 +1744,11 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1762,31 +1762,31 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-263</v>
+        <v>549</v>
       </c>
       <c r="D27" t="n">
-        <v>736</v>
+        <v>860</v>
       </c>
       <c r="E27" t="n">
-        <v>855</v>
+        <v>-1000</v>
       </c>
       <c r="F27" t="n">
-        <v>605</v>
+        <v>-70</v>
       </c>
       <c r="G27" t="n">
-        <v>1231</v>
+        <v>318</v>
       </c>
       <c r="H27" t="n">
-        <v>-110</v>
+        <v>88</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1795,49 +1795,49 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>126</v>
+        <v>-177</v>
       </c>
       <c r="D28" t="n">
-        <v>735</v>
+        <v>761</v>
       </c>
       <c r="E28" t="n">
-        <v>-2878</v>
+        <v>198</v>
       </c>
       <c r="F28" t="n">
-        <v>-426</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>-2251</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1846,49 +1846,49 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-1229</v>
+        <v>20</v>
       </c>
       <c r="D29" t="n">
-        <v>558</v>
+        <v>726</v>
       </c>
       <c r="E29" t="n">
-        <v>2273</v>
+        <v>-3145</v>
       </c>
       <c r="F29" t="n">
-        <v>171</v>
+        <v>-411</v>
       </c>
       <c r="G29" t="n">
-        <v>-1285</v>
+        <v>-2207</v>
       </c>
       <c r="H29" t="n">
-        <v>-561</v>
+        <v>40</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1897,49 +1897,49 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>516</v>
+        <v>-2514</v>
       </c>
       <c r="D30" t="n">
-        <v>546</v>
+        <v>646</v>
       </c>
       <c r="E30" t="n">
-        <v>-366</v>
+        <v>-769</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>3367</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>8714</v>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>-19</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -1960,37 +1960,37 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>184</v>
+        <v>550</v>
       </c>
       <c r="D31" t="n">
-        <v>459</v>
+        <v>639</v>
       </c>
       <c r="E31" t="n">
-        <v>2915</v>
+        <v>4613</v>
       </c>
       <c r="F31" t="n">
-        <v>-7</v>
+        <v>-95</v>
       </c>
       <c r="G31" t="n">
-        <v>-32</v>
+        <v>2121</v>
       </c>
       <c r="H31" t="n">
-        <v>-44</v>
+        <v>33</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1999,40 +1999,40 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-45</v>
+        <v>356</v>
       </c>
       <c r="D32" t="n">
-        <v>404</v>
+        <v>517</v>
       </c>
       <c r="E32" t="n">
-        <v>868</v>
+        <v>-404</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -2041,7 +2041,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2054,45 +2054,45 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-119</v>
+        <v>260</v>
       </c>
       <c r="D33" t="n">
-        <v>271</v>
+        <v>507</v>
       </c>
       <c r="E33" t="n">
-        <v>911</v>
+        <v>2822</v>
       </c>
       <c r="F33" t="n">
-        <v>-21</v>
+        <v>-2</v>
       </c>
       <c r="G33" t="n">
-        <v>-22</v>
+        <v>-34</v>
       </c>
       <c r="H33" t="n">
-        <v>2</v>
+        <v>-46</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2101,11 +2101,11 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2119,31 +2119,31 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-125</v>
+        <v>-58</v>
       </c>
       <c r="D34" t="n">
-        <v>262</v>
+        <v>419</v>
       </c>
       <c r="E34" t="n">
-        <v>777</v>
+        <v>302</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>-608</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-2294</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>-59</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2152,11 +2152,11 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2164,76 +2164,88 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>59</v>
+        <v>449</v>
       </c>
       <c r="D35" t="n">
-        <v>245</v>
+        <v>398</v>
       </c>
       <c r="E35" t="n">
-        <v>-348</v>
+        <v>2011</v>
       </c>
       <c r="F35" t="n">
-        <v>-61</v>
+        <v>57</v>
       </c>
       <c r="G35" t="n">
-        <v>59</v>
+        <v>237</v>
       </c>
       <c r="H35" t="n">
-        <v>17</v>
+        <v>-94</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>60</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>✈️ 高飛</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="D36" t="n">
-        <v>227</v>
+        <v>396</v>
       </c>
       <c r="E36" t="n">
-        <v>-729</v>
+        <v>729</v>
       </c>
       <c r="F36" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-346</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2242,49 +2254,49 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-68</v>
+        <v>-84</v>
       </c>
       <c r="D37" t="n">
-        <v>212</v>
+        <v>292</v>
       </c>
       <c r="E37" t="n">
-        <v>1249</v>
+        <v>785</v>
       </c>
       <c r="F37" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2293,49 +2305,49 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>🐌 龜速*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-38</v>
+        <v>-21</v>
       </c>
       <c r="D38" t="n">
-        <v>202</v>
+        <v>266</v>
       </c>
       <c r="E38" t="n">
-        <v>716</v>
+        <v>-751</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-306</v>
       </c>
       <c r="H38" t="n">
-        <v>-17</v>
+        <v>37</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2344,11 +2356,11 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2356,88 +2368,76 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-3356</v>
+        <v>-24</v>
       </c>
       <c r="D39" t="n">
-        <v>166</v>
+        <v>252</v>
       </c>
       <c r="E39" t="n">
-        <v>-723</v>
+        <v>-345</v>
       </c>
       <c r="F39" t="n">
-        <v>4292</v>
+        <v>42</v>
       </c>
       <c r="G39" t="n">
-        <v>9452</v>
+        <v>180</v>
       </c>
       <c r="H39" t="n">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K39" t="n">
-        <v>69</v>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M39" t="n">
-        <v>-5</v>
-      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-170</v>
+        <v>-145</v>
       </c>
       <c r="D40" t="n">
-        <v>103</v>
+        <v>163</v>
       </c>
       <c r="E40" t="n">
-        <v>1374</v>
+        <v>560</v>
       </c>
       <c r="F40" t="n">
-        <v>56</v>
+        <v>-28</v>
       </c>
       <c r="G40" t="n">
-        <v>205</v>
+        <v>-28</v>
       </c>
       <c r="H40" t="n">
-        <v>136</v>
+        <v>2</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2446,49 +2446,49 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-49</v>
+        <v>14</v>
       </c>
       <c r="D41" t="n">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="E41" t="n">
-        <v>-507</v>
+        <v>147</v>
       </c>
       <c r="F41" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-269</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-17</v>
+        <v>18</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2501,11 +2501,11 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M41" t="n">
@@ -2515,31 +2515,31 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>方土霖</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>159</v>
+        <v>9</v>
       </c>
       <c r="D42" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E42" t="n">
-        <v>307</v>
+        <v>51</v>
       </c>
       <c r="F42" t="n">
-        <v>-624</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>-2069</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-68</v>
+        <v>0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2552,36 +2552,36 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>-289</v>
       </c>
       <c r="D43" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="E43" t="n">
-        <v>114</v>
+        <v>446</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2590,7 +2590,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2603,36 +2603,36 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M43" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>方土霖</t>
+          <t>大車隊</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D44" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="E44" t="n">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2654,45 +2654,45 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-183</v>
+        <v>-41</v>
       </c>
       <c r="D45" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="E45" t="n">
-        <v>2546</v>
+        <v>-523</v>
       </c>
       <c r="F45" t="n">
-        <v>3</v>
+        <v>-34</v>
       </c>
       <c r="G45" t="n">
-        <v>39</v>
+        <v>-277</v>
       </c>
       <c r="H45" t="n">
-        <v>4</v>
+        <v>-15</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2705,15 +2705,15 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M45" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="46">
@@ -2728,13 +2728,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-59</v>
+        <v>-51</v>
       </c>
       <c r="D46" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E46" t="n">
-        <v>708</v>
+        <v>689</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2743,7 +2743,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2770,32 +2770,32 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7</v>
+        <v>-76</v>
       </c>
       <c r="D47" t="n">
-        <v>18</v>
+        <v>-3</v>
       </c>
       <c r="E47" t="n">
-        <v>-11</v>
+        <v>1115</v>
       </c>
       <c r="F47" t="n">
+        <v>10</v>
+      </c>
+      <c r="G47" t="n">
+        <v>4</v>
+      </c>
+      <c r="H47" t="n">
         <v>0</v>
       </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-1</v>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>🟡 中性</t>
@@ -2807,11 +2807,11 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速*</t>
         </is>
       </c>
       <c r="M47" t="n">
@@ -2821,31 +2821,31 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-73</v>
+        <v>34</v>
       </c>
       <c r="D48" t="n">
-        <v>-19</v>
+        <v>-62</v>
       </c>
       <c r="E48" t="n">
-        <v>90</v>
+        <v>-284</v>
       </c>
       <c r="F48" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2858,46 +2858,46 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C49" t="n">
+        <v>-184</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-84</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2057</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-101</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-55</v>
+      </c>
+      <c r="H49" t="n">
         <v>5</v>
       </c>
-      <c r="D49" t="n">
-        <v>-68</v>
-      </c>
-      <c r="E49" t="n">
-        <v>-204</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-0</v>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>🟡 中性</t>
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -2923,31 +2923,31 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-153</v>
+        <v>-283</v>
       </c>
       <c r="D50" t="n">
-        <v>-109</v>
+        <v>-108</v>
       </c>
       <c r="E50" t="n">
-        <v>-36</v>
+        <v>1219</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>591</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>1388</v>
       </c>
       <c r="H50" t="n">
-        <v>-4</v>
+        <v>-87</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2956,49 +2956,49 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-183</v>
+        <v>-90</v>
       </c>
       <c r="D51" t="n">
-        <v>-199</v>
+        <v>-110</v>
       </c>
       <c r="E51" t="n">
-        <v>246</v>
+        <v>-57</v>
       </c>
       <c r="F51" t="n">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>-41</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-25</v>
+        <v>-4</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3007,49 +3007,49 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-688</v>
+        <v>-124</v>
       </c>
       <c r="D52" t="n">
-        <v>-234</v>
+        <v>-119</v>
       </c>
       <c r="E52" t="n">
-        <v>-4970</v>
+        <v>74</v>
       </c>
       <c r="F52" t="n">
-        <v>-599</v>
+        <v>33</v>
       </c>
       <c r="G52" t="n">
-        <v>1550</v>
+        <v>48</v>
       </c>
       <c r="H52" t="n">
-        <v>-66</v>
+        <v>41</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3062,11 +3062,11 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M52" t="n">
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-1599</v>
+        <v>-953</v>
       </c>
       <c r="D53" t="n">
-        <v>-281</v>
+        <v>-120</v>
       </c>
       <c r="E53" t="n">
-        <v>-488</v>
+        <v>-13</v>
       </c>
       <c r="F53" t="n">
-        <v>-37</v>
+        <v>-1</v>
       </c>
       <c r="G53" t="n">
-        <v>-360</v>
+        <v>-361</v>
       </c>
       <c r="H53" t="n">
-        <v>-301</v>
+        <v>-160</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3127,31 +3127,31 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>252</v>
+        <v>-125</v>
       </c>
       <c r="D54" t="n">
-        <v>-299</v>
+        <v>-223</v>
       </c>
       <c r="E54" t="n">
-        <v>-1873</v>
+        <v>115</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>-41</v>
       </c>
       <c r="H54" t="n">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3160,100 +3160,100 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-105</v>
+        <v>73</v>
       </c>
       <c r="D55" t="n">
-        <v>-354</v>
+        <v>-231</v>
       </c>
       <c r="E55" t="n">
-        <v>-2121</v>
+        <v>-2203</v>
       </c>
       <c r="F55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-28</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>77</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
         <v>0</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K55" t="n">
-        <v>79</v>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>🛬 穩定</t>
-        </is>
-      </c>
-      <c r="M55" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>-52</v>
       </c>
       <c r="D56" t="n">
-        <v>-422</v>
+        <v>-246</v>
       </c>
       <c r="E56" t="n">
-        <v>707</v>
+        <v>-2081</v>
       </c>
       <c r="F56" t="n">
-        <v>6</v>
+        <v>183</v>
       </c>
       <c r="G56" t="n">
-        <v>-29</v>
+        <v>-1189</v>
       </c>
       <c r="H56" t="n">
-        <v>-65</v>
+        <v>43</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3262,49 +3262,49 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-216</v>
+        <v>3093</v>
       </c>
       <c r="D57" t="n">
-        <v>-435</v>
+        <v>-253</v>
       </c>
       <c r="E57" t="n">
-        <v>-2066</v>
+        <v>-6056</v>
       </c>
       <c r="F57" t="n">
-        <v>341</v>
+        <v>119</v>
       </c>
       <c r="G57" t="n">
-        <v>-1231</v>
+        <v>2789</v>
       </c>
       <c r="H57" t="n">
-        <v>20</v>
+        <v>-416</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3313,40 +3313,40 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>德昌</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-71</v>
+        <v>-140</v>
       </c>
       <c r="D58" t="n">
-        <v>-449</v>
+        <v>-413</v>
       </c>
       <c r="E58" t="n">
-        <v>-866</v>
+        <v>-2076</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3364,40 +3364,40 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>智冠</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-256</v>
+        <v>-58</v>
       </c>
       <c r="D59" t="n">
-        <v>-482</v>
+        <v>-458</v>
       </c>
       <c r="E59" t="n">
-        <v>-3763</v>
+        <v>-884</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -3406,7 +3406,7 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-94</v>
+        <v>-3</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3419,11 +3419,11 @@
         </is>
       </c>
       <c r="K59" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M59" t="n">
@@ -3433,31 +3433,31 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3388</v>
+        <v>-309</v>
       </c>
       <c r="D60" t="n">
-        <v>-564</v>
+        <v>-523</v>
       </c>
       <c r="E60" t="n">
-        <v>-9298</v>
+        <v>-3526</v>
       </c>
       <c r="F60" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>2889</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-248</v>
+        <v>-63</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3466,11 +3466,11 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3478,37 +3478,37 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-2879</v>
+        <v>-240</v>
       </c>
       <c r="D61" t="n">
-        <v>-595</v>
+        <v>-526</v>
       </c>
       <c r="E61" t="n">
-        <v>7472</v>
+        <v>418</v>
       </c>
       <c r="F61" t="n">
-        <v>-3</v>
+        <v>12</v>
       </c>
       <c r="G61" t="n">
-        <v>-16</v>
+        <v>-22</v>
       </c>
       <c r="H61" t="n">
-        <v>167</v>
+        <v>-46</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3517,49 +3517,49 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-319</v>
+        <v>251</v>
       </c>
       <c r="D62" t="n">
-        <v>-635</v>
+        <v>-642</v>
       </c>
       <c r="E62" t="n">
-        <v>537</v>
+        <v>-2961</v>
       </c>
       <c r="F62" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>564</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>1</v>
+        <v>-35</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3572,45 +3572,45 @@
         </is>
       </c>
       <c r="K62" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>283</v>
+        <v>530</v>
       </c>
       <c r="D63" t="n">
-        <v>-686</v>
+        <v>-731</v>
       </c>
       <c r="E63" t="n">
-        <v>-2842</v>
+        <v>-6227</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>-106</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>109</v>
       </c>
       <c r="H63" t="n">
-        <v>-53</v>
+        <v>43</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3619,49 +3619,49 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>257</v>
+        <v>-1769</v>
       </c>
       <c r="D64" t="n">
-        <v>-691</v>
+        <v>-746</v>
       </c>
       <c r="E64" t="n">
-        <v>-3693</v>
+        <v>4141</v>
       </c>
       <c r="F64" t="n">
-        <v>146</v>
+        <v>-933</v>
       </c>
       <c r="G64" t="n">
-        <v>205</v>
+        <v>-2394</v>
       </c>
       <c r="H64" t="n">
-        <v>-12</v>
+        <v>429</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3670,49 +3670,49 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2098</v>
+        <v>-2742</v>
       </c>
       <c r="D65" t="n">
-        <v>-796</v>
+        <v>-784</v>
       </c>
       <c r="E65" t="n">
-        <v>-10554</v>
+        <v>1085</v>
       </c>
       <c r="F65" t="n">
-        <v>-4</v>
+        <v>-510</v>
       </c>
       <c r="G65" t="n">
-        <v>-8</v>
+        <v>-1999</v>
       </c>
       <c r="H65" t="n">
-        <v>591</v>
+        <v>-363</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3721,49 +3721,49 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>493</v>
+        <v>-74</v>
       </c>
       <c r="D66" t="n">
-        <v>-847</v>
+        <v>-807</v>
       </c>
       <c r="E66" t="n">
-        <v>-6510</v>
+        <v>594</v>
       </c>
       <c r="F66" t="n">
-        <v>-36</v>
+        <v>-143</v>
       </c>
       <c r="G66" t="n">
-        <v>231</v>
+        <v>632</v>
       </c>
       <c r="H66" t="n">
-        <v>240</v>
+        <v>13</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3772,49 +3772,49 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M66" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-711</v>
+        <v>-170</v>
       </c>
       <c r="D67" t="n">
-        <v>-941</v>
+        <v>-876</v>
       </c>
       <c r="E67" t="n">
-        <v>401</v>
+        <v>627</v>
       </c>
       <c r="F67" t="n">
-        <v>-181</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>-601</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-63</v>
+        <v>-226</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3823,49 +3823,49 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M67" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-336</v>
+        <v>-368</v>
       </c>
       <c r="D68" t="n">
-        <v>-1086</v>
+        <v>-894</v>
       </c>
       <c r="E68" t="n">
-        <v>329</v>
+        <v>-3091</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="H68" t="n">
-        <v>-227</v>
+        <v>-62</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3878,11 +3878,11 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M68" t="n">
@@ -3892,31 +3892,31 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-324</v>
+        <v>-1623</v>
       </c>
       <c r="D69" t="n">
-        <v>-1149</v>
+        <v>-974</v>
       </c>
       <c r="E69" t="n">
-        <v>-1774</v>
+        <v>-6479</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>177</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>1992</v>
       </c>
       <c r="H69" t="n">
-        <v>1</v>
+        <v>-516</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3925,49 +3925,49 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>305</v>
+        <v>-346</v>
       </c>
       <c r="D70" t="n">
-        <v>-1421</v>
+        <v>-1119</v>
       </c>
       <c r="E70" t="n">
-        <v>-1019</v>
+        <v>1442</v>
       </c>
       <c r="F70" t="n">
-        <v>-114</v>
+        <v>-254</v>
       </c>
       <c r="G70" t="n">
-        <v>228</v>
+        <v>-482</v>
       </c>
       <c r="H70" t="n">
-        <v>106</v>
+        <v>-77</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3980,36 +3980,36 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>聯合</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-246</v>
+        <v>-208</v>
       </c>
       <c r="D71" t="n">
-        <v>-1492</v>
+        <v>-1248</v>
       </c>
       <c r="E71" t="n">
-        <v>-64</v>
+        <v>-1732</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -4018,7 +4018,7 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-178</v>
+        <v>1</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -4027,11 +4027,11 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4039,37 +4039,37 @@
         </is>
       </c>
       <c r="M71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>802</v>
+        <v>-86</v>
       </c>
       <c r="D72" t="n">
-        <v>-1496</v>
+        <v>-1262</v>
       </c>
       <c r="E72" t="n">
-        <v>-2049</v>
+        <v>-3186</v>
       </c>
       <c r="F72" t="n">
-        <v>-21</v>
+        <v>78</v>
       </c>
       <c r="G72" t="n">
-        <v>1478</v>
+        <v>202</v>
       </c>
       <c r="H72" t="n">
-        <v>9</v>
+        <v>-94</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -4078,49 +4078,49 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-1270</v>
+        <v>-125</v>
       </c>
       <c r="D73" t="n">
-        <v>-1515</v>
+        <v>-1273</v>
       </c>
       <c r="E73" t="n">
-        <v>1447</v>
+        <v>-1182</v>
       </c>
       <c r="F73" t="n">
-        <v>430</v>
+        <v>81</v>
       </c>
       <c r="G73" t="n">
-        <v>544</v>
+        <v>422</v>
       </c>
       <c r="H73" t="n">
-        <v>26</v>
+        <v>113</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4133,15 +4133,15 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M73" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4156,22 +4156,22 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2070</v>
+        <v>165</v>
       </c>
       <c r="D74" t="n">
-        <v>-1568</v>
+        <v>-1364</v>
       </c>
       <c r="E74" t="n">
-        <v>-8825</v>
+        <v>-8895</v>
       </c>
       <c r="F74" t="n">
-        <v>-2091</v>
+        <v>-1370</v>
       </c>
       <c r="G74" t="n">
-        <v>-6723</v>
+        <v>-6747</v>
       </c>
       <c r="H74" t="n">
-        <v>277</v>
+        <v>123</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4198,121 +4198,121 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-2667</v>
+        <v>330</v>
       </c>
       <c r="D75" t="n">
-        <v>-1591</v>
+        <v>-1430</v>
       </c>
       <c r="E75" t="n">
-        <v>-1958</v>
+        <v>1888</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>-314</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>1559</v>
       </c>
       <c r="H75" t="n">
-        <v>-4</v>
+        <v>-43</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K75" t="n">
-        <v>93</v>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>🚀 加速器</t>
-        </is>
-      </c>
-      <c r="M75" t="n">
-        <v>2</v>
-      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-105</v>
+        <v>767</v>
       </c>
       <c r="D76" t="n">
-        <v>-1607</v>
+        <v>-1465</v>
       </c>
       <c r="E76" t="n">
-        <v>2693</v>
+        <v>-2071</v>
       </c>
       <c r="F76" t="n">
-        <v>-358</v>
+        <v>-356</v>
       </c>
       <c r="G76" t="n">
-        <v>1538</v>
+        <v>1465</v>
       </c>
       <c r="H76" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>66</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-279</v>
+        <v>-1456</v>
       </c>
       <c r="D77" t="n">
-        <v>-1785</v>
+        <v>-1496</v>
       </c>
       <c r="E77" t="n">
-        <v>-3028</v>
+        <v>1171</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>428</v>
       </c>
       <c r="G77" t="n">
-        <v>-4</v>
+        <v>526</v>
       </c>
       <c r="H77" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4321,11 +4321,11 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -4333,37 +4333,37 @@
         </is>
       </c>
       <c r="M77" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-234</v>
+        <v>-242</v>
       </c>
       <c r="D78" t="n">
-        <v>-1945</v>
+        <v>-1587</v>
       </c>
       <c r="E78" t="n">
-        <v>-4119</v>
+        <v>51</v>
       </c>
       <c r="F78" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>292</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-129</v>
+        <v>-184</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4372,15 +4372,15 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M78" t="n">
@@ -4390,35 +4390,35 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>勝一</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-902</v>
+        <v>-398</v>
       </c>
       <c r="D79" t="n">
-        <v>-2859</v>
+        <v>-1772</v>
       </c>
       <c r="E79" t="n">
-        <v>-1253</v>
+        <v>-3368</v>
       </c>
       <c r="F79" t="n">
-        <v>-402</v>
+        <v>38</v>
       </c>
       <c r="G79" t="n">
-        <v>-688</v>
+        <v>-1</v>
       </c>
       <c r="H79" t="n">
-        <v>-122</v>
+        <v>5</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -4427,58 +4427,58 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M79" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-2300</v>
+        <v>-2819</v>
       </c>
       <c r="D80" t="n">
-        <v>-2987</v>
+        <v>-1816</v>
       </c>
       <c r="E80" t="n">
-        <v>-4224</v>
+        <v>-2295</v>
       </c>
       <c r="F80" t="n">
-        <v>-221</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>153</v>
+        <v>6</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4486,88 +4486,88 @@
         </is>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-1135</v>
+        <v>-3636</v>
       </c>
       <c r="D81" t="n">
-        <v>-3000</v>
+        <v>-1881</v>
       </c>
       <c r="E81" t="n">
-        <v>-5678</v>
+        <v>5865</v>
       </c>
       <c r="F81" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G81" t="n">
-        <v>-747</v>
+        <v>-17</v>
       </c>
       <c r="H81" t="n">
-        <v>12</v>
+        <v>148</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>🚀 加速器*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-114</v>
+        <v>-764</v>
       </c>
       <c r="D82" t="n">
-        <v>-3033</v>
+        <v>-2395</v>
       </c>
       <c r="E82" t="n">
-        <v>-4660</v>
+        <v>-5164</v>
       </c>
       <c r="F82" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>-209</v>
+        <v>115</v>
       </c>
       <c r="H82" t="n">
-        <v>34</v>
+        <v>2292</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4576,49 +4576,49 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M82" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-436</v>
+        <v>92</v>
       </c>
       <c r="D83" t="n">
-        <v>-3041</v>
+        <v>-2692</v>
       </c>
       <c r="E83" t="n">
-        <v>-5513</v>
+        <v>-5802</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="G83" t="n">
-        <v>596</v>
+        <v>-823</v>
       </c>
       <c r="H83" t="n">
-        <v>2385</v>
+        <v>7</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4631,45 +4631,45 @@
         </is>
       </c>
       <c r="K83" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器*</t>
         </is>
       </c>
       <c r="M83" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>216</v>
+        <v>-2215</v>
       </c>
       <c r="D84" t="n">
-        <v>-3228</v>
+        <v>-2862</v>
       </c>
       <c r="E84" t="n">
-        <v>-13092</v>
+        <v>-4117</v>
       </c>
       <c r="F84" t="n">
-        <v>288</v>
+        <v>-216</v>
       </c>
       <c r="G84" t="n">
-        <v>1417</v>
+        <v>-84</v>
       </c>
       <c r="H84" t="n">
-        <v>-557</v>
+        <v>114</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4678,15 +4678,15 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K84" t="n">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M84" t="n">
@@ -4696,31 +4696,31 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-2969</v>
+        <v>-815</v>
       </c>
       <c r="D85" t="n">
-        <v>-3380</v>
+        <v>-2936</v>
       </c>
       <c r="E85" t="n">
-        <v>3356</v>
+        <v>-1171</v>
       </c>
       <c r="F85" t="n">
-        <v>-2596</v>
+        <v>-325</v>
       </c>
       <c r="G85" t="n">
-        <v>-490</v>
+        <v>-764</v>
       </c>
       <c r="H85" t="n">
-        <v>337</v>
+        <v>-25</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4729,11 +4729,11 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K85" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4741,76 +4741,88 @@
         </is>
       </c>
       <c r="M85" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>282</v>
+        <v>-1724</v>
       </c>
       <c r="D86" t="n">
-        <v>-3561</v>
+        <v>-2967</v>
       </c>
       <c r="E86" t="n">
-        <v>-5741</v>
+        <v>-13881</v>
       </c>
       <c r="F86" t="n">
+        <v>784</v>
+      </c>
+      <c r="G86" t="n">
+        <v>1872</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-274</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>🟠 減碼</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>90</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
         <v>0</v>
       </c>
-      <c r="G86" t="n">
-        <v>-400</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-2</v>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>🟠 減碼</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-1390</v>
+        <v>-23</v>
       </c>
       <c r="D87" t="n">
-        <v>-3750</v>
+        <v>-3126</v>
       </c>
       <c r="E87" t="n">
-        <v>-4350</v>
+        <v>-4921</v>
       </c>
       <c r="F87" t="n">
-        <v>-1661</v>
+        <v>-34</v>
       </c>
       <c r="G87" t="n">
-        <v>5073</v>
+        <v>-217</v>
       </c>
       <c r="H87" t="n">
-        <v>58</v>
+        <v>-32</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4819,11 +4831,11 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4837,82 +4849,70 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-232</v>
+        <v>-24</v>
       </c>
       <c r="D88" t="n">
-        <v>-3763</v>
+        <v>-3414</v>
       </c>
       <c r="E88" t="n">
-        <v>-21062</v>
+        <v>-5811</v>
       </c>
       <c r="F88" t="n">
-        <v>-334</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>-1374</v>
+        <v>-400</v>
       </c>
       <c r="H88" t="n">
-        <v>-197</v>
+        <v>51</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
           <t>🟠 減碼</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K88" t="n">
-        <v>100</v>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>✈️ 高飛</t>
-        </is>
-      </c>
-      <c r="M88" t="n">
-        <v>1</v>
-      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-1387</v>
+        <v>-206</v>
       </c>
       <c r="D89" t="n">
-        <v>-5112</v>
+        <v>-3456</v>
       </c>
       <c r="E89" t="n">
-        <v>73857</v>
+        <v>-21029</v>
       </c>
       <c r="F89" t="n">
-        <v>-1385</v>
+        <v>-370</v>
       </c>
       <c r="G89" t="n">
-        <v>1608</v>
+        <v>-1521</v>
       </c>
       <c r="H89" t="n">
-        <v>-2662</v>
+        <v>-293</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4921,49 +4921,49 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K89" t="n">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-4502</v>
+        <v>692</v>
       </c>
       <c r="D90" t="n">
-        <v>-5945</v>
+        <v>-3662</v>
       </c>
       <c r="E90" t="n">
-        <v>-34544</v>
+        <v>-2639</v>
       </c>
       <c r="F90" t="n">
-        <v>222</v>
+        <v>-2360</v>
       </c>
       <c r="G90" t="n">
-        <v>381</v>
+        <v>4955</v>
       </c>
       <c r="H90" t="n">
-        <v>153</v>
+        <v>22</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4976,45 +4976,45 @@
         </is>
       </c>
       <c r="K90" t="n">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M90" t="n">
-        <v>-4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-28172</v>
+        <v>-3969</v>
       </c>
       <c r="D91" t="n">
-        <v>-7350</v>
+        <v>-4629</v>
       </c>
       <c r="E91" t="n">
-        <v>-141307</v>
+        <v>-33894</v>
       </c>
       <c r="F91" t="n">
-        <v>-314</v>
+        <v>142</v>
       </c>
       <c r="G91" t="n">
-        <v>-3206</v>
+        <v>327</v>
       </c>
       <c r="H91" t="n">
-        <v>2727</v>
+        <v>157</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -5023,19 +5023,19 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K91" t="n">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M91" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="92">
@@ -5050,22 +5050,22 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>919</v>
+        <v>1671</v>
       </c>
       <c r="D92" t="n">
-        <v>-7611</v>
+        <v>-6797</v>
       </c>
       <c r="E92" t="n">
-        <v>-8072</v>
+        <v>-8050</v>
       </c>
       <c r="F92" t="n">
-        <v>-1592</v>
+        <v>-2359</v>
       </c>
       <c r="G92" t="n">
-        <v>1411</v>
+        <v>1447</v>
       </c>
       <c r="H92" t="n">
-        <v>-200</v>
+        <v>-80</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -5089,22 +5089,22 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-457</v>
+        <v>-616</v>
       </c>
       <c r="D93" t="n">
-        <v>-7958</v>
+        <v>-7032</v>
       </c>
       <c r="E93" t="n">
-        <v>-14093</v>
+        <v>-13824</v>
       </c>
       <c r="F93" t="n">
-        <v>-43</v>
+        <v>-395</v>
       </c>
       <c r="G93" t="n">
-        <v>164</v>
+        <v>-187</v>
       </c>
       <c r="H93" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -5131,82 +5131,82 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-1177</v>
+        <v>-10101</v>
       </c>
       <c r="D94" t="n">
-        <v>-8606</v>
+        <v>-7995</v>
       </c>
       <c r="E94" t="n">
-        <v>-16052</v>
+        <v>72826</v>
       </c>
       <c r="F94" t="n">
+        <v>-466</v>
+      </c>
+      <c r="G94" t="n">
+        <v>2229</v>
+      </c>
+      <c r="H94" t="n">
+        <v>-843</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>🟠 減碼</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>68</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M94" t="n">
         <v>0</v>
-      </c>
-      <c r="G94" t="n">
-        <v>1</v>
-      </c>
-      <c r="H94" t="n">
-        <v>11</v>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>🟠 減碼</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K94" t="n">
-        <v>78</v>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M94" t="n">
-        <v>-5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-902</v>
+        <v>-1206</v>
       </c>
       <c r="D95" t="n">
-        <v>-9453</v>
+        <v>-8340</v>
       </c>
       <c r="E95" t="n">
-        <v>-16495</v>
+        <v>-16404</v>
       </c>
       <c r="F95" t="n">
-        <v>690</v>
+        <v>-1</v>
       </c>
       <c r="G95" t="n">
-        <v>1992</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>422</v>
+        <v>-66</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5215,151 +5215,151 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K95" t="n">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M95" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-2150</v>
+        <v>-34358</v>
       </c>
       <c r="D96" t="n">
-        <v>-10124</v>
+        <v>-8677</v>
       </c>
       <c r="E96" t="n">
-        <v>-10984</v>
+        <v>-137515</v>
       </c>
       <c r="F96" t="n">
-        <v>-815</v>
+        <v>56</v>
       </c>
       <c r="G96" t="n">
-        <v>-2691</v>
+        <v>-2371</v>
       </c>
       <c r="H96" t="n">
-        <v>-420</v>
+        <v>2770</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>🔴 大賣</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K96" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M96" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-141119</v>
+        <v>-1706</v>
       </c>
       <c r="D97" t="n">
-        <v>-10166</v>
+        <v>-9122</v>
       </c>
       <c r="E97" t="n">
-        <v>-19225</v>
+        <v>-16361</v>
       </c>
       <c r="F97" t="n">
-        <v>-16382</v>
+        <v>442</v>
       </c>
       <c r="G97" t="n">
-        <v>-53708</v>
+        <v>1812</v>
       </c>
       <c r="H97" t="n">
-        <v>-8282</v>
+        <v>434</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>🔴 大賣</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K97" t="n">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M97" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-35204</v>
+        <v>-2503</v>
       </c>
       <c r="D98" t="n">
-        <v>-12307</v>
+        <v>-11561</v>
       </c>
       <c r="E98" t="n">
-        <v>45807</v>
+        <v>-24636</v>
       </c>
       <c r="F98" t="n">
-        <v>-5741</v>
+        <v>-100</v>
       </c>
       <c r="G98" t="n">
-        <v>-9312</v>
+        <v>-100</v>
       </c>
       <c r="H98" t="n">
-        <v>-5164</v>
+        <v>-168</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5372,45 +5372,45 @@
         </is>
       </c>
       <c r="K98" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M98" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>寶雅*</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-1437</v>
+        <v>3018</v>
       </c>
       <c r="D99" t="n">
-        <v>-12479</v>
+        <v>-11944</v>
       </c>
       <c r="E99" t="n">
-        <v>-24597</v>
+        <v>-63473</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>-1150</v>
       </c>
       <c r="H99" t="n">
-        <v>-259</v>
+        <v>-264</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5419,11 +5419,11 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K99" t="n">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -5431,37 +5431,37 @@
         </is>
       </c>
       <c r="M99" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>4101</v>
+        <v>-11048</v>
       </c>
       <c r="D100" t="n">
-        <v>-13701</v>
+        <v>-11996</v>
       </c>
       <c r="E100" t="n">
-        <v>-63728</v>
+        <v>66252</v>
       </c>
       <c r="F100" t="n">
-        <v>44</v>
+        <v>3411</v>
       </c>
       <c r="G100" t="n">
-        <v>-1922</v>
+        <v>6591</v>
       </c>
       <c r="H100" t="n">
-        <v>-210</v>
+        <v>-3622</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -5470,49 +5470,49 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K100" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M100" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-9228</v>
+        <v>-4866</v>
       </c>
       <c r="D101" t="n">
-        <v>-16129</v>
+        <v>-13068</v>
       </c>
       <c r="E101" t="n">
-        <v>-49487</v>
+        <v>-13664</v>
       </c>
       <c r="F101" t="n">
-        <v>-3674</v>
+        <v>415</v>
       </c>
       <c r="G101" t="n">
-        <v>-8639</v>
+        <v>-2117</v>
       </c>
       <c r="H101" t="n">
-        <v>415</v>
+        <v>-1040</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5521,15 +5521,15 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K101" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M101" t="n">
@@ -5539,31 +5539,31 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-7896</v>
+        <v>-10970</v>
       </c>
       <c r="D102" t="n">
-        <v>-19223</v>
+        <v>-14657</v>
       </c>
       <c r="E102" t="n">
-        <v>-74740</v>
+        <v>-50769</v>
       </c>
       <c r="F102" t="n">
-        <v>1275</v>
+        <v>-2689</v>
       </c>
       <c r="G102" t="n">
-        <v>-25528</v>
+        <v>-8155</v>
       </c>
       <c r="H102" t="n">
-        <v>169</v>
+        <v>332</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5572,49 +5572,49 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K102" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M102" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-6226</v>
+        <v>-10907</v>
       </c>
       <c r="D103" t="n">
-        <v>-20372</v>
+        <v>-22198</v>
       </c>
       <c r="E103" t="n">
-        <v>68526</v>
+        <v>-80955</v>
       </c>
       <c r="F103" t="n">
-        <v>2095</v>
+        <v>1964</v>
       </c>
       <c r="G103" t="n">
-        <v>5009</v>
+        <v>-22119</v>
       </c>
       <c r="H103" t="n">
-        <v>-2261</v>
+        <v>1159</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5623,15 +5623,15 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K103" t="n">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M103" t="n">
@@ -5650,22 +5650,22 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-1867</v>
+        <v>-4803</v>
       </c>
       <c r="D104" t="n">
-        <v>-22783</v>
+        <v>-23126</v>
       </c>
       <c r="E104" t="n">
-        <v>57917</v>
+        <v>54850</v>
       </c>
       <c r="F104" t="n">
-        <v>-2662</v>
+        <v>-1685</v>
       </c>
       <c r="G104" t="n">
-        <v>10742</v>
+        <v>10114</v>
       </c>
       <c r="H104" t="n">
-        <v>-700</v>
+        <v>-1828</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5701,22 +5701,22 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-38830</v>
+        <v>-54905</v>
       </c>
       <c r="D105" t="n">
-        <v>-108275</v>
+        <v>-114915</v>
       </c>
       <c r="E105" t="n">
-        <v>145615</v>
+        <v>142192</v>
       </c>
       <c r="F105" t="n">
-        <v>64</v>
+        <v>3923</v>
       </c>
       <c r="G105" t="n">
-        <v>34105</v>
+        <v>35059</v>
       </c>
       <c r="H105" t="n">
-        <v>725</v>
+        <v>-88</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5794,58 +5794,58 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -605 千股)</t>
+          <t>📈 20d 巨變(加碼 331 千股)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>126407</v>
+        <v>-1705983</v>
       </c>
       <c r="D2" t="n">
-        <v>734763</v>
+        <v>-9122032</v>
       </c>
       <c r="E2" t="n">
-        <v>126216</v>
+        <v>-901804</v>
       </c>
       <c r="F2" t="n">
-        <v>1339959</v>
+        <v>-9453091</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 238 千股)</t>
+          <t>📉 20d 巨變(減碼 -8 千股)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-901804</v>
+        <v>20135</v>
       </c>
       <c r="D3" t="n">
-        <v>-9453091</v>
+        <v>726365</v>
       </c>
       <c r="E3" t="n">
-        <v>-923067</v>
+        <v>126407</v>
       </c>
       <c r="F3" t="n">
-        <v>-9691049</v>
+        <v>734763</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>台光電</t>
         </is>
       </c>
     </row>
@@ -5857,20 +5857,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -972 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 151 千股)</t>
         </is>
       </c>
       <c r="C4" t="n">
+        <v>20255</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1230832</v>
+      </c>
+      <c r="E4" t="n">
         <v>-8608</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>1079985</v>
-      </c>
-      <c r="E4" t="n">
-        <v>271561</v>
-      </c>
-      <c r="F4" t="n">
-        <v>2051842</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -5881,29 +5881,29 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -179 千股)</t>
+          <t>📉 20d 巨變(減碼 -246 千股)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>158831</v>
+        <v>549697</v>
       </c>
       <c r="D5" t="n">
-        <v>55400</v>
+        <v>639380</v>
       </c>
       <c r="E5" t="n">
-        <v>692690</v>
+        <v>805321</v>
       </c>
       <c r="F5" t="n">
-        <v>234850</v>
+        <v>885199</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>奇鋐</t>
         </is>
       </c>
     </row>
@@ -5915,20 +5915,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,316 千股)</t>
+          <t>📈 20d 巨變(加碼 307 千股)</t>
         </is>
       </c>
       <c r="C6" t="n">
+        <v>-206030</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-3455854</v>
+      </c>
+      <c r="E6" t="n">
         <v>-232115</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>-3763227</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-786062</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-5078924</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -5939,116 +5939,116 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -328 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 364 千股)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>805321</v>
+        <v>-57933</v>
       </c>
       <c r="D7" t="n">
-        <v>885199</v>
+        <v>419071</v>
       </c>
       <c r="E7" t="n">
-        <v>746751</v>
+        <v>158831</v>
       </c>
       <c r="F7" t="n">
-        <v>1213139</v>
+        <v>55400</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>勤誠</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 999 千股)</t>
+          <t>📉 20d 巨變(減碼 -343 千股)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>229699</v>
+        <v>-623168</v>
       </c>
       <c r="D8" t="n">
-        <v>866408</v>
+        <v>1705253</v>
       </c>
       <c r="E8" t="n">
-        <v>-361990</v>
+        <v>-529188</v>
       </c>
       <c r="F8" t="n">
-        <v>-132874</v>
+        <v>2048169</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>致茂</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -982 千股)</t>
+          <t>📉 20d 巨變(減碼 -7 千股)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-28172058</v>
+        <v>548930</v>
       </c>
       <c r="D9" t="n">
-        <v>-7350073</v>
+        <v>859780</v>
       </c>
       <c r="E9" t="n">
-        <v>-18448562</v>
+        <v>229699</v>
       </c>
       <c r="F9" t="n">
-        <v>-6368431</v>
+        <v>866408</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>光聖</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -125 千股)</t>
+          <t>📈 20d 巨變(加碼 189 千股)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-529188</v>
+        <v>-51764</v>
       </c>
       <c r="D10" t="n">
-        <v>2048169</v>
+        <v>-245918</v>
       </c>
       <c r="E10" t="n">
-        <v>-14835</v>
+        <v>-215699</v>
       </c>
       <c r="F10" t="n">
-        <v>2173381</v>
+        <v>-434902</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>旺矽</t>
         </is>
       </c>
     </row>
@@ -6060,20 +6060,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -29 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -958 千股)</t>
         </is>
       </c>
       <c r="C11" t="n">
+        <v>-1272477</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8457783</v>
+      </c>
+      <c r="E11" t="n">
         <v>88450</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>9415690</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-155839</v>
-      </c>
-      <c r="F11" t="n">
-        <v>9445037</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -6084,58 +6084,58 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -272 千股)</t>
+          <t>📈 20d 巨變(加碼 204 千股)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-215699</v>
+        <v>164892</v>
       </c>
       <c r="D12" t="n">
-        <v>-434902</v>
+        <v>-1364263</v>
       </c>
       <c r="E12" t="n">
-        <v>-326672</v>
+        <v>2070385</v>
       </c>
       <c r="F12" t="n">
-        <v>-162990</v>
+        <v>-1568199</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>智邦</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -393 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,326 千股)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2070385</v>
+        <v>-34357576</v>
       </c>
       <c r="D13" t="n">
-        <v>-1568199</v>
+        <v>-8676510</v>
       </c>
       <c r="E13" t="n">
-        <v>482323</v>
+        <v>-28172058</v>
       </c>
       <c r="F13" t="n">
-        <v>-1175019</v>
+        <v>-7350073</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
@@ -6147,20 +6147,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 161 千股)</t>
+          <t>📉 20d 巨變(減碼 -119 千股)</t>
         </is>
       </c>
       <c r="C14" t="n">
+        <v>839724</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1918125</v>
+      </c>
+      <c r="E14" t="n">
         <v>1803921</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>2036971</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1175652</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1875536</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -6171,29 +6171,29 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,372 千股)</t>
+          <t>📉 20d 巨變(減碼 -178 千股)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-9227556</v>
+        <v>-345554</v>
       </c>
       <c r="D15" t="n">
-        <v>-16128955</v>
+        <v>-1119118</v>
       </c>
       <c r="E15" t="n">
-        <v>-11813898</v>
+        <v>-710826</v>
       </c>
       <c r="F15" t="n">
-        <v>-18501314</v>
+        <v>-941083</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>辛耘</t>
         </is>
       </c>
     </row>
@@ -6205,20 +6205,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -34 千股)</t>
+          <t>📉 20d 巨變(減碼 -93 千股)</t>
         </is>
       </c>
       <c r="C16" t="n">
+        <v>-23253</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-3125507</v>
+      </c>
+      <c r="E16" t="n">
         <v>-113917</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
         <v>-3032766</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-19851</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-2998427</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -6229,58 +6229,58 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 164 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 261 千股)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-710826</v>
+        <v>-1723597</v>
       </c>
       <c r="D17" t="n">
-        <v>-941083</v>
+        <v>-2967191</v>
       </c>
       <c r="E17" t="n">
-        <v>-147378</v>
+        <v>216411</v>
       </c>
       <c r="F17" t="n">
-        <v>-1105337</v>
+        <v>-3227832</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>健鼎</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -568 千股)</t>
+          <t>📈 20d 巨變(加碼 1,472 千股)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>216411</v>
+        <v>-10969822</v>
       </c>
       <c r="D18" t="n">
-        <v>-3227832</v>
+        <v>-14657061</v>
       </c>
       <c r="E18" t="n">
-        <v>499335</v>
+        <v>-9227556</v>
       </c>
       <c r="F18" t="n">
-        <v>-2659816</v>
+        <v>-16128955</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
@@ -6292,20 +6292,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 35 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 39 千股)</t>
         </is>
       </c>
       <c r="C19" t="n">
+        <v>-20521</v>
+      </c>
+      <c r="D19" t="n">
+        <v>266445</v>
+      </c>
+      <c r="E19" t="n">
         <v>84817</v>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>227430</v>
-      </c>
-      <c r="E19" t="n">
-        <v>144544</v>
-      </c>
-      <c r="F19" t="n">
-        <v>192234</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -6316,174 +6316,174 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -248 千股)</t>
+          <t>📈 20d 巨變(加碼 117 千股)</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-233788</v>
+        <v>529543</v>
       </c>
       <c r="D20" t="n">
-        <v>-1945357</v>
+        <v>-730543</v>
       </c>
       <c r="E20" t="n">
-        <v>-396606</v>
+        <v>492619</v>
       </c>
       <c r="F20" t="n">
-        <v>-1697244</v>
+        <v>-847469</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>大立光</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 131 千股)</t>
+          <t>📉 20d 巨變(減碼 -224 千股)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1254908</v>
+        <v>-2819244</v>
       </c>
       <c r="D21" t="n">
-        <v>3860387</v>
+        <v>-1815520</v>
       </c>
       <c r="E21" t="n">
-        <v>1993012</v>
+        <v>-2667490</v>
       </c>
       <c r="F21" t="n">
-        <v>3729156</v>
+        <v>-1591149</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>建榮</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -322 千股)</t>
+          <t>📈 20d 巨變(加碼 486 千股)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1040996</v>
+        <v>333317</v>
       </c>
       <c r="D22" t="n">
-        <v>2315629</v>
+        <v>4346584</v>
       </c>
       <c r="E22" t="n">
-        <v>1317827</v>
+        <v>1254908</v>
       </c>
       <c r="F22" t="n">
-        <v>2637838</v>
+        <v>3860387</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 342 千股)</t>
+          <t>📈 20d 巨變(加碼 683 千股)</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>305390</v>
+        <v>-86077</v>
       </c>
       <c r="D23" t="n">
-        <v>-1421472</v>
+        <v>-1262118</v>
       </c>
       <c r="E23" t="n">
-        <v>57296</v>
+        <v>-233788</v>
       </c>
       <c r="F23" t="n">
-        <v>-1763497</v>
+        <v>-1945357</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>崇越</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 435 千股)</t>
+          <t>📉 20d 巨變(減碼 -547 千股)</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-2667490</v>
+        <v>561262</v>
       </c>
       <c r="D24" t="n">
-        <v>-1591149</v>
+        <v>1768910</v>
       </c>
       <c r="E24" t="n">
-        <v>-2053206</v>
+        <v>1040996</v>
       </c>
       <c r="F24" t="n">
-        <v>-2026035</v>
+        <v>2315629</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>中砂</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 511 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 149 千股)</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>492619</v>
+        <v>-124909</v>
       </c>
       <c r="D25" t="n">
-        <v>-847469</v>
+        <v>-1272894</v>
       </c>
       <c r="E25" t="n">
-        <v>208489</v>
+        <v>305390</v>
       </c>
       <c r="F25" t="n">
-        <v>-1358574</v>
+        <v>-1421472</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>華城</t>
         </is>
       </c>
     </row>
@@ -6495,20 +6495,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 17 千股)</t>
+          <t>📈 20d 巨變(加碼 17 千股)</t>
         </is>
       </c>
       <c r="C26" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D26" t="n">
+        <v>35251</v>
+      </c>
+      <c r="E26" t="n">
         <v>7000</v>
       </c>
-      <c r="D26" t="n">
+      <c r="F26" t="n">
         <v>18251</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-6000</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1251</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -6519,29 +6519,29 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 451 千股)</t>
+          <t>📈 20d 巨變(加碼 44 千股)</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-2879314</v>
+        <v>250917</v>
       </c>
       <c r="D27" t="n">
-        <v>-594821</v>
+        <v>-642090</v>
       </c>
       <c r="E27" t="n">
-        <v>-2503564</v>
+        <v>283170</v>
       </c>
       <c r="F27" t="n">
-        <v>-1045780</v>
+        <v>-686392</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>湧德</t>
         </is>
       </c>
     </row>
@@ -6553,20 +6553,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -53 千股)</t>
+          <t>📉 20d 巨變(減碼 -5 千股)</t>
         </is>
       </c>
       <c r="C28" t="n">
+        <v>-50643</v>
+      </c>
+      <c r="D28" t="n">
+        <v>17631</v>
+      </c>
+      <c r="E28" t="n">
         <v>-58643</v>
       </c>
-      <c r="D28" t="n">
+      <c r="F28" t="n">
         <v>22631</v>
-      </c>
-      <c r="E28" t="n">
-        <v>-38953</v>
-      </c>
-      <c r="F28" t="n">
-        <v>75239</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -6577,145 +6577,145 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -141 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,286 千股)</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>283170</v>
+        <v>-3635553</v>
       </c>
       <c r="D29" t="n">
-        <v>-686392</v>
+        <v>-1880910</v>
       </c>
       <c r="E29" t="n">
-        <v>315170</v>
+        <v>-2879314</v>
       </c>
       <c r="F29" t="n">
-        <v>-545392</v>
+        <v>-594821</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>零壹</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -544 千股)</t>
+          <t>📉 20d 巨變(減碼 -42 千股)</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>308995</v>
+        <v>-309173</v>
       </c>
       <c r="D30" t="n">
-        <v>14692122</v>
+        <v>-523367</v>
       </c>
       <c r="E30" t="n">
-        <v>593705</v>
+        <v>-255650</v>
       </c>
       <c r="F30" t="n">
-        <v>15235938</v>
+        <v>-481844</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>隆大</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -7 千股)</t>
+          <t>📉 20d 巨變(減碼 -24 千股)</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-255650</v>
+        <v>34446</v>
       </c>
       <c r="D31" t="n">
-        <v>-481844</v>
+        <v>967620</v>
       </c>
       <c r="E31" t="n">
-        <v>-277644</v>
+        <v>78934</v>
       </c>
       <c r="F31" t="n">
-        <v>-475144</v>
+        <v>991654</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>合機</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -39 千股)</t>
+          <t>📈 20d 巨變(加碼 19 千股)</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>78934</v>
+        <v>-1456004</v>
       </c>
       <c r="D32" t="n">
-        <v>991654</v>
+        <v>-1496195</v>
       </c>
       <c r="E32" t="n">
-        <v>326467</v>
+        <v>-1270466</v>
       </c>
       <c r="F32" t="n">
-        <v>1030818</v>
+        <v>-1514833</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>卜蜂</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -871 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -5,790 千股)</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-1270466</v>
+        <v>-3056869</v>
       </c>
       <c r="D33" t="n">
-        <v>-1514833</v>
+        <v>31878739</v>
       </c>
       <c r="E33" t="n">
-        <v>-610007</v>
+        <v>3200128</v>
       </c>
       <c r="F33" t="n">
-        <v>-643428</v>
+        <v>37669057</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
@@ -6727,20 +6727,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,180 千股)</t>
+          <t>📈 20d 巨變(加碼 1,758 千股)</t>
         </is>
       </c>
       <c r="C34" t="n">
+        <v>3018222</v>
+      </c>
+      <c r="D34" t="n">
+        <v>-11943903</v>
+      </c>
+      <c r="E34" t="n">
         <v>4101197</v>
       </c>
-      <c r="D34" t="n">
+      <c r="F34" t="n">
         <v>-13701406</v>
-      </c>
-      <c r="E34" t="n">
-        <v>3334681</v>
-      </c>
-      <c r="F34" t="n">
-        <v>-14881883</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -6751,58 +6751,58 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -16,146 千股)</t>
+          <t>📉 20d 巨變(減碼 -108 千股)</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3200128</v>
+        <v>-144598</v>
       </c>
       <c r="D35" t="n">
-        <v>37669057</v>
+        <v>163447</v>
       </c>
       <c r="E35" t="n">
-        <v>13308687</v>
+        <v>-119118</v>
       </c>
       <c r="F35" t="n">
-        <v>53814945</v>
+        <v>271407</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>大統益</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -77 千股)</t>
+          <t>📉 20d 巨變(減碼 -9 千股)</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-119118</v>
+        <v>-58173</v>
       </c>
       <c r="D36" t="n">
-        <v>271407</v>
+        <v>-457554</v>
       </c>
       <c r="E36" t="n">
-        <v>-63301</v>
+        <v>-71173</v>
       </c>
       <c r="F36" t="n">
-        <v>348522</v>
+        <v>-448616</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>智冠</t>
         </is>
       </c>
     </row>
@@ -6814,20 +6814,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 93 千股)</t>
+          <t>📈 20d 巨變(加碼 48 千股)</t>
         </is>
       </c>
       <c r="C37" t="n">
+        <v>260208</v>
+      </c>
+      <c r="D37" t="n">
+        <v>506790</v>
+      </c>
+      <c r="E37" t="n">
         <v>184014</v>
       </c>
-      <c r="D37" t="n">
+      <c r="F37" t="n">
         <v>458790</v>
-      </c>
-      <c r="E37" t="n">
-        <v>-11432</v>
-      </c>
-      <c r="F37" t="n">
-        <v>365790</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -6838,29 +6838,29 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 39 千股)</t>
+          <t>📉 20d 巨變(減碼 -172 千股)</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-71173</v>
+        <v>-74218</v>
       </c>
       <c r="D38" t="n">
-        <v>-448616</v>
+        <v>-807090</v>
       </c>
       <c r="E38" t="n">
-        <v>-98786</v>
+        <v>-318607</v>
       </c>
       <c r="F38" t="n">
-        <v>-487525</v>
+        <v>-635129</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>穎崴</t>
         </is>
       </c>
     </row>
@@ -6872,20 +6872,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -68 千股)</t>
+          <t>📉 20d 巨變(減碼 -25 千股)</t>
         </is>
       </c>
       <c r="C39" t="n">
+        <v>-124872</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-223418</v>
+      </c>
+      <c r="E39" t="n">
         <v>-182865</v>
       </c>
-      <c r="D39" t="n">
+      <c r="F39" t="n">
         <v>-198674</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-198865</v>
-      </c>
-      <c r="F39" t="n">
-        <v>-131163</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -6896,348 +6896,348 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -20 千股)</t>
+          <t>📉 20d 巨變(減碼 -216 千股)</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-318607</v>
+        <v>-75850</v>
       </c>
       <c r="D40" t="n">
-        <v>-635129</v>
+        <v>-3197</v>
       </c>
       <c r="E40" t="n">
-        <v>-203949</v>
+        <v>-67950</v>
       </c>
       <c r="F40" t="n">
-        <v>-615273</v>
+        <v>212461</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>八方雲集</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -70 千股)</t>
+          <t>📉 20d 巨變(減碼 -16,398 千股)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-67950</v>
+        <v>10963481</v>
       </c>
       <c r="D41" t="n">
-        <v>212461</v>
+        <v>69854759</v>
       </c>
       <c r="E41" t="n">
-        <v>-54361</v>
+        <v>11959992</v>
       </c>
       <c r="F41" t="n">
-        <v>282461</v>
+        <v>86252968</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -545 千股)</t>
+          <t>📉 20d 巨變(減碼 -99 千股)</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>11959992</v>
+        <v>-208000</v>
       </c>
       <c r="D42" t="n">
-        <v>86252968</v>
+        <v>-1248333</v>
       </c>
       <c r="E42" t="n">
-        <v>12549340</v>
+        <v>-324000</v>
       </c>
       <c r="F42" t="n">
-        <v>86797673</v>
+        <v>-1149333</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>聯合</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -70 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,105 千股)</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>257201</v>
+        <v>408831</v>
       </c>
       <c r="D43" t="n">
-        <v>-690754</v>
+        <v>4837820</v>
       </c>
       <c r="E43" t="n">
-        <v>497924</v>
+        <v>1067236</v>
       </c>
       <c r="F43" t="n">
-        <v>-620937</v>
+        <v>6942447</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -222 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -203 千股)</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-37854</v>
+        <v>-367938</v>
       </c>
       <c r="D44" t="n">
-        <v>201507</v>
+        <v>-893664</v>
       </c>
       <c r="E44" t="n">
-        <v>85895</v>
+        <v>257201</v>
       </c>
       <c r="F44" t="n">
-        <v>423169</v>
+        <v>-690754</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>亞力</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,794 千股)</t>
+          <t>📈 20d 巨變(加碼 68 千股)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2802843</v>
+        <v>73382</v>
       </c>
       <c r="D45" t="n">
-        <v>1167165</v>
+        <v>-231237</v>
       </c>
       <c r="E45" t="n">
-        <v>3558955</v>
+        <v>251855</v>
       </c>
       <c r="F45" t="n">
-        <v>2961109</v>
+        <v>-298921</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>漢科</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 92 千股)</t>
+          <t>📉 20d 巨變(減碼 -158 千股)</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>251855</v>
+        <v>-288588</v>
       </c>
       <c r="D46" t="n">
-        <v>-298921</v>
+        <v>43148</v>
       </c>
       <c r="E46" t="n">
-        <v>162920</v>
+        <v>-37854</v>
       </c>
       <c r="F46" t="n">
-        <v>-390598</v>
+        <v>201507</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>大綜</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,813 千股)</t>
+          <t>📈 20d 巨變(加碼 744 千股)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-3355756</v>
+        <v>1072224</v>
       </c>
       <c r="D47" t="n">
-        <v>166137</v>
+        <v>1910895</v>
       </c>
       <c r="E47" t="n">
-        <v>-4238594</v>
+        <v>2802843</v>
       </c>
       <c r="F47" t="n">
-        <v>-1646735</v>
+        <v>1167165</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>台燿</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,931 千股)</t>
+          <t>📉 20d 巨變(減碼 -37 千股)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-7457376</v>
+        <v>3365468</v>
       </c>
       <c r="D48" t="n">
-        <v>2302769</v>
+        <v>4397470</v>
       </c>
       <c r="E48" t="n">
-        <v>-4606790</v>
+        <v>3203931</v>
       </c>
       <c r="F48" t="n">
-        <v>371360</v>
+        <v>4434632</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>立隆電</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -52 千股)</t>
+          <t>📈 20d 巨變(加碼 374 千股)</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3203931</v>
+        <v>-7219533</v>
       </c>
       <c r="D49" t="n">
-        <v>4434632</v>
+        <v>2676611</v>
       </c>
       <c r="E49" t="n">
-        <v>2841999</v>
+        <v>-7457376</v>
       </c>
       <c r="F49" t="n">
-        <v>4486460</v>
+        <v>2302769</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 193 千股)</t>
+          <t>📈 20d 巨變(加碼 480 千股)</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-2299614</v>
+        <v>-2514008</v>
       </c>
       <c r="D50" t="n">
-        <v>-2987077</v>
+        <v>646185</v>
       </c>
       <c r="E50" t="n">
-        <v>-2214029</v>
+        <v>-3355756</v>
       </c>
       <c r="F50" t="n">
-        <v>-3179969</v>
+        <v>166137</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>玉晶光</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -8,917 千股)</t>
+          <t>📈 20d 巨變(加碼 125 千股)</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-35204437</v>
+        <v>-2214807</v>
       </c>
       <c r="D51" t="n">
-        <v>-12306613</v>
+        <v>-2861924</v>
       </c>
       <c r="E51" t="n">
-        <v>5643449</v>
+        <v>-2299614</v>
       </c>
       <c r="F51" t="n">
-        <v>-3389805</v>
+        <v>-2987077</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>世芯-KY</t>
         </is>
       </c>
     </row>
@@ -7249,20 +7249,20 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,679 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,975 千股)</t>
         </is>
       </c>
       <c r="C52" t="n">
+        <v>-10907438</v>
+      </c>
+      <c r="D52" t="n">
+        <v>-22197565</v>
+      </c>
+      <c r="E52" t="n">
         <v>-7896331</v>
       </c>
-      <c r="D52" t="n">
+      <c r="F52" t="n">
         <v>-19223011</v>
-      </c>
-      <c r="E52" t="n">
-        <v>-8378962</v>
-      </c>
-      <c r="F52" t="n">
-        <v>-20902043</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -7273,261 +7273,261 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -5,460 千股)</t>
+          <t>📈 20d 巨變(加碼 20,255 千股)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>419818</v>
+        <v>-24297060</v>
       </c>
       <c r="D53" t="n">
-        <v>25734731</v>
+        <v>7948555</v>
       </c>
       <c r="E53" t="n">
-        <v>7661571</v>
+        <v>-35204437</v>
       </c>
       <c r="F53" t="n">
-        <v>31195069</v>
+        <v>-12306613</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -77 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 283 千股)</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-1223194</v>
+        <v>-5780922</v>
       </c>
       <c r="D54" t="n">
-        <v>2666974</v>
+        <v>26017364</v>
       </c>
       <c r="E54" t="n">
-        <v>-1353958</v>
+        <v>419818</v>
       </c>
       <c r="F54" t="n">
-        <v>2743730</v>
+        <v>25734731</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -184 千股)</t>
+          <t>📉 20d 巨變(減碼 -600 千股)</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-4564</v>
+        <v>-1138518</v>
       </c>
       <c r="D55" t="n">
-        <v>1567586</v>
+        <v>2067082</v>
       </c>
       <c r="E55" t="n">
-        <v>282726</v>
+        <v>-1223194</v>
       </c>
       <c r="F55" t="n">
-        <v>1751207</v>
+        <v>2666974</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>鈊象</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 55 千股)</t>
+          <t>📉 20d 巨變(減碼 -289 千股)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-49231</v>
+        <v>-764534</v>
       </c>
       <c r="D56" t="n">
-        <v>79725</v>
+        <v>1278873</v>
       </c>
       <c r="E56" t="n">
-        <v>-15672</v>
+        <v>-4564</v>
       </c>
       <c r="F56" t="n">
-        <v>24972</v>
+        <v>1567586</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>士電</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 126 千股)</t>
+          <t>📉 20d 巨變(減碼 -59 千股)</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-436252</v>
+        <v>-40915</v>
       </c>
       <c r="D57" t="n">
-        <v>-3041455</v>
+        <v>21085</v>
       </c>
       <c r="E57" t="n">
-        <v>-714104</v>
+        <v>-49231</v>
       </c>
       <c r="F57" t="n">
-        <v>-3167465</v>
+        <v>79725</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>達欣工</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -10 千股)</t>
+          <t>📈 20d 巨變(加碼 647 千股)</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-44998</v>
+        <v>-763977</v>
       </c>
       <c r="D58" t="n">
-        <v>403653</v>
+        <v>-2394805</v>
       </c>
       <c r="E58" t="n">
-        <v>-192103</v>
+        <v>-436252</v>
       </c>
       <c r="F58" t="n">
-        <v>413793</v>
+        <v>-3041455</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>鉅祥</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -8 千股)</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-279283</v>
+        <v>16874</v>
       </c>
       <c r="D59" t="n">
-        <v>-1785436</v>
+        <v>395694</v>
       </c>
       <c r="E59" t="n">
-        <v>183681</v>
+        <v>-44998</v>
       </c>
       <c r="F59" t="n">
-        <v>-1788320</v>
+        <v>403653</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>普萊德</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 51 千股)</t>
+          <t>📉 20d 巨變(減碼 -104 千股)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-170317</v>
+        <v>-240446</v>
       </c>
       <c r="D60" t="n">
-        <v>102700</v>
+        <v>-525650</v>
       </c>
       <c r="E60" t="n">
-        <v>-251769</v>
+        <v>-51551</v>
       </c>
       <c r="F60" t="n">
-        <v>52145</v>
+        <v>-421957</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 125 千股)</t>
+          <t>📈 20d 巨變(加碼 14 千股)</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-51551</v>
+        <v>-398351</v>
       </c>
       <c r="D61" t="n">
-        <v>-421957</v>
+        <v>-1771926</v>
       </c>
       <c r="E61" t="n">
-        <v>-91090</v>
+        <v>-279283</v>
       </c>
       <c r="F61" t="n">
-        <v>-546821</v>
+        <v>-1785436</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>勝一</t>
         </is>
       </c>
     </row>
@@ -7539,20 +7539,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -106 千股)</t>
+          <t>📉 20d 巨變(減碼 -95 千股)</t>
         </is>
       </c>
       <c r="C62" t="n">
+        <v>-242464</v>
+      </c>
+      <c r="D62" t="n">
+        <v>-1586899</v>
+      </c>
+      <c r="E62" t="n">
         <v>-245612</v>
       </c>
-      <c r="D62" t="n">
+      <c r="F62" t="n">
         <v>-1492337</v>
-      </c>
-      <c r="E62" t="n">
-        <v>-217110</v>
-      </c>
-      <c r="F62" t="n">
-        <v>-1385941</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -7563,116 +7563,116 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 10 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 295 千股)</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-1134938</v>
+        <v>449305</v>
       </c>
       <c r="D63" t="n">
-        <v>-3000021</v>
+        <v>397599</v>
       </c>
       <c r="E63" t="n">
-        <v>-382481</v>
+        <v>-170317</v>
       </c>
       <c r="F63" t="n">
-        <v>-3009982</v>
+        <v>102700</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>祥碩</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,193 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 308 千股)</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-2969338</v>
+        <v>92408</v>
       </c>
       <c r="D64" t="n">
-        <v>-3379534</v>
+        <v>-2692420</v>
       </c>
       <c r="E64" t="n">
-        <v>-2408322</v>
+        <v>-1134938</v>
       </c>
       <c r="F64" t="n">
-        <v>-1186464</v>
+        <v>-3000021</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 475 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 89 千股)</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-688347</v>
+        <v>691770</v>
       </c>
       <c r="D65" t="n">
-        <v>-233602</v>
+        <v>-3661689</v>
       </c>
       <c r="E65" t="n">
-        <v>64559</v>
+        <v>-1390357</v>
       </c>
       <c r="F65" t="n">
-        <v>-708781</v>
+        <v>-3750193</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>華星光</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 233 千股)</t>
+          <t>📉 20d 巨變(減碼 -740 千股)</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>13079639</v>
+        <v>-1623268</v>
       </c>
       <c r="D66" t="n">
-        <v>29016789</v>
+        <v>-973985</v>
       </c>
       <c r="E66" t="n">
-        <v>-1028944</v>
+        <v>-688347</v>
       </c>
       <c r="F66" t="n">
-        <v>28783401</v>
+        <v>-233602</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>聯亞</t>
         </is>
       </c>
     </row>
@@ -7684,20 +7684,20 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -159 千股)</t>
+          <t>📈 20d 巨變(加碼 161 千股)</t>
         </is>
       </c>
       <c r="C67" t="n">
+        <v>-952719</v>
+      </c>
+      <c r="D67" t="n">
+        <v>-119917</v>
+      </c>
+      <c r="E67" t="n">
         <v>-1598741</v>
       </c>
-      <c r="D67" t="n">
+      <c r="F67" t="n">
         <v>-280642</v>
-      </c>
-      <c r="E67" t="n">
-        <v>-1531836</v>
-      </c>
-      <c r="F67" t="n">
-        <v>-121630</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -7708,897 +7708,984 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 5,822 千股)</t>
+          <t>📈 20d 巨變(加碼 2,634 千股)</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-38830336</v>
+        <v>-1769102</v>
       </c>
       <c r="D68" t="n">
-        <v>-108275409</v>
+        <v>-745763</v>
       </c>
       <c r="E68" t="n">
-        <v>-83197181</v>
+        <v>-2969338</v>
       </c>
       <c r="F68" t="n">
-        <v>-114097650</v>
+        <v>-3379534</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 423 千股)</t>
+          <t>📉 20d 巨變(減碼 -6,640 千股)</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3388449</v>
+        <v>-54905250</v>
       </c>
       <c r="D69" t="n">
-        <v>-563808</v>
+        <v>-114915491</v>
       </c>
       <c r="E69" t="n">
-        <v>3043389</v>
+        <v>-38830336</v>
       </c>
       <c r="F69" t="n">
-        <v>-986949</v>
+        <v>-108275409</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -12,785 千股)</t>
+          <t>📈 20d 巨變(加碼 311 千股)</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-1867365</v>
+        <v>3092866</v>
       </c>
       <c r="D70" t="n">
-        <v>-22783426</v>
+        <v>-252814</v>
       </c>
       <c r="E70" t="n">
-        <v>-1600522</v>
+        <v>3388449</v>
       </c>
       <c r="F70" t="n">
-        <v>-9998157</v>
+        <v>-563808</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -91 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -3,385 千股)</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-104949</v>
+        <v>-176747</v>
       </c>
       <c r="D71" t="n">
-        <v>-354477</v>
+        <v>25631958</v>
       </c>
       <c r="E71" t="n">
-        <v>-29794</v>
+        <v>13079639</v>
       </c>
       <c r="F71" t="n">
-        <v>-263388</v>
+        <v>29016789</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 72 千股)</t>
+          <t>📉 20d 巨變(減碼 -343 千股)</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-4501754</v>
+        <v>-4802590</v>
       </c>
       <c r="D72" t="n">
-        <v>-5944830</v>
+        <v>-23125948</v>
       </c>
       <c r="E72" t="n">
-        <v>-5168732</v>
+        <v>-1867365</v>
       </c>
       <c r="F72" t="n">
-        <v>-6017077</v>
+        <v>-22783426</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 53 千股)</t>
+          <t>📉 20d 巨變(減碼 -59 千股)</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>354302</v>
+        <v>-140115</v>
       </c>
       <c r="D73" t="n">
-        <v>752006</v>
+        <v>-413109</v>
       </c>
       <c r="E73" t="n">
-        <v>390024</v>
+        <v>-104949</v>
       </c>
       <c r="F73" t="n">
-        <v>698576</v>
+        <v>-354477</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>德昌</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,037 千股)</t>
+          <t>📈 20d 巨變(加碼 1,316 千股)</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-1176757</v>
+        <v>-3969403</v>
       </c>
       <c r="D74" t="n">
-        <v>-8606147</v>
+        <v>-4629221</v>
       </c>
       <c r="E74" t="n">
-        <v>-1693434</v>
+        <v>-4501754</v>
       </c>
       <c r="F74" t="n">
-        <v>-9643401</v>
+        <v>-5944830</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -14 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 9 千股)</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>5000</v>
+        <v>-177232</v>
       </c>
       <c r="D75" t="n">
-        <v>-67550</v>
+        <v>760966</v>
       </c>
       <c r="E75" t="n">
-        <v>18000</v>
+        <v>354302</v>
       </c>
       <c r="F75" t="n">
-        <v>-53550</v>
+        <v>752006</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>億泰</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 391 千股)</t>
+          <t>📈 20d 巨變(加碼 6 千股)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-1228909</v>
+        <v>34000</v>
       </c>
       <c r="D76" t="n">
-        <v>557944</v>
+        <v>-61550</v>
       </c>
       <c r="E76" t="n">
-        <v>-1270205</v>
+        <v>5000</v>
       </c>
       <c r="F76" t="n">
-        <v>167228</v>
+        <v>-67550</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>友輝</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,932 千股)</t>
+          <t>📈 20d 巨變(加碼 266 千股)</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-1386713</v>
+        <v>-1205919</v>
       </c>
       <c r="D77" t="n">
-        <v>-5111730</v>
+        <v>-8340490</v>
       </c>
       <c r="E77" t="n">
-        <v>-18026110</v>
+        <v>-1176757</v>
       </c>
       <c r="F77" t="n">
-        <v>-7043631</v>
+        <v>-8606147</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>智易</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 289 千股)</t>
+          <t>📉 20d 巨變(減碼 -77 千股)</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>801511</v>
+        <v>-814586</v>
       </c>
       <c r="D78" t="n">
-        <v>-1496023</v>
+        <v>-2935709</v>
       </c>
       <c r="E78" t="n">
-        <v>474984</v>
+        <v>-902167</v>
       </c>
       <c r="F78" t="n">
-        <v>-1784925</v>
+        <v>-2858946</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>原相</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -173 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,342 千股)</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-336446</v>
+        <v>-2742460</v>
       </c>
       <c r="D79" t="n">
-        <v>-1086486</v>
+        <v>-783949</v>
       </c>
       <c r="E79" t="n">
-        <v>-754085</v>
+        <v>-1228909</v>
       </c>
       <c r="F79" t="n">
-        <v>-913379</v>
+        <v>557944</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 5,467 千股)</t>
+          <t>📈 20d 巨變(加碼 31 千股)</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-6226405</v>
+        <v>767117</v>
       </c>
       <c r="D80" t="n">
-        <v>-20371886</v>
+        <v>-1464671</v>
       </c>
       <c r="E80" t="n">
-        <v>-17122734</v>
+        <v>801511</v>
       </c>
       <c r="F80" t="n">
-        <v>-25838539</v>
+        <v>-1496023</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>精測</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -152 千股)</t>
+          <t>📈 20d 巨變(加碼 8,376 千股)</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-125000</v>
+        <v>-11047969</v>
       </c>
       <c r="D81" t="n">
-        <v>262009</v>
+        <v>-11995730</v>
       </c>
       <c r="E81" t="n">
-        <v>-67000</v>
+        <v>-6226405</v>
       </c>
       <c r="F81" t="n">
-        <v>414009</v>
+        <v>-20371886</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 31 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,883 千股)</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>515624</v>
+        <v>-10100528</v>
       </c>
       <c r="D82" t="n">
-        <v>545524</v>
+        <v>-7995207</v>
       </c>
       <c r="E82" t="n">
-        <v>493411</v>
+        <v>-1386713</v>
       </c>
       <c r="F82" t="n">
-        <v>514169</v>
+        <v>-5111730</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,164 千股)</t>
+          <t>📈 20d 巨變(加碼 210 千股)</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2098171</v>
+        <v>-169583</v>
       </c>
       <c r="D83" t="n">
-        <v>-796018</v>
+        <v>-876233</v>
       </c>
       <c r="E83" t="n">
-        <v>1555751</v>
+        <v>-336446</v>
       </c>
       <c r="F83" t="n">
-        <v>368137</v>
+        <v>-1086486</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 5,630 千股)</t>
+          <t>📉 20d 巨變(減碼 -29 千股)</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-1437432</v>
+        <v>356000</v>
       </c>
       <c r="D84" t="n">
-        <v>-12479349</v>
+        <v>516524</v>
       </c>
       <c r="E84" t="n">
-        <v>-1970432</v>
+        <v>515624</v>
       </c>
       <c r="F84" t="n">
-        <v>-18109219</v>
+        <v>545524</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>東科-KY</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,904 千股)</t>
+          <t>📈 20d 巨變(加碼 30 千股)</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1889863</v>
+        <v>-84000</v>
       </c>
       <c r="D85" t="n">
-        <v>917111</v>
+        <v>292009</v>
       </c>
       <c r="E85" t="n">
-        <v>1057185</v>
+        <v>-125000</v>
       </c>
       <c r="F85" t="n">
-        <v>-986890</v>
+        <v>262009</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 13,841 千股)</t>
+          <t>📈 20d 巨變(加碼 5,218 千股)</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>42107380</v>
+        <v>6624646</v>
       </c>
       <c r="D86" t="n">
-        <v>54138286</v>
+        <v>4421604</v>
       </c>
       <c r="E86" t="n">
-        <v>36088567</v>
+        <v>2098171</v>
       </c>
       <c r="F86" t="n">
-        <v>40297762</v>
+        <v>-796018</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -131 千股)</t>
+          <t>📈 20d 巨變(加碼 6,978 千股)</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-183155</v>
+        <v>43395130</v>
       </c>
       <c r="D87" t="n">
-        <v>40309</v>
+        <v>61116687</v>
       </c>
       <c r="E87" t="n">
-        <v>-58895</v>
+        <v>42107380</v>
       </c>
       <c r="F87" t="n">
-        <v>171210</v>
+        <v>54138286</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -10 千股)</t>
+          <t>📈 20d 巨變(加碼 902 千股)</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-73183</v>
+        <v>2306190</v>
       </c>
       <c r="D88" t="n">
-        <v>-18842</v>
+        <v>1819068</v>
       </c>
       <c r="E88" t="n">
-        <v>-16098</v>
+        <v>1889863</v>
       </c>
       <c r="F88" t="n">
-        <v>-8690</v>
+        <v>917111</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>研華</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -68 千股)</t>
+          <t>📈 20d 巨變(加碼 918 千股)</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>32</v>
+        <v>-2503223</v>
       </c>
       <c r="D89" t="n">
-        <v>53602</v>
+        <v>-11561252</v>
       </c>
       <c r="E89" t="n">
-        <v>74065</v>
+        <v>-1437432</v>
       </c>
       <c r="F89" t="n">
-        <v>121635</v>
+        <v>-12479349</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>宏捷科</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,364 千股)</t>
+          <t>📉 20d 巨變(減碼 -125 千股)</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-457192</v>
+        <v>-183974</v>
       </c>
       <c r="D90" t="n">
-        <v>-7958076</v>
+        <v>-84355</v>
       </c>
       <c r="E90" t="n">
-        <v>-606122</v>
+        <v>-183155</v>
       </c>
       <c r="F90" t="n">
-        <v>-9321751</v>
+        <v>40309</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>中保科</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,142 千股)</t>
+          <t>📉 20d 巨變(減碼 -100 千股)</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>4151571</v>
+        <v>-123821</v>
       </c>
       <c r="D91" t="n">
-        <v>21136419</v>
+        <v>-118669</v>
       </c>
       <c r="E91" t="n">
-        <v>5298555</v>
+        <v>-73183</v>
       </c>
       <c r="F91" t="n">
-        <v>23278823</v>
+        <v>-18842</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>竹陞科技</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -802 千股)</t>
+          <t>📈 20d 巨變(加碼 926 千股)</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-47834</v>
+        <v>-616225</v>
       </c>
       <c r="D92" t="n">
-        <v>4281687</v>
+        <v>-7031911</v>
       </c>
       <c r="E92" t="n">
-        <v>1223096</v>
+        <v>-457192</v>
       </c>
       <c r="F92" t="n">
-        <v>5083594</v>
+        <v>-7958076</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -4,993 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,750 千股)</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-141118626</v>
+        <v>3420405</v>
       </c>
       <c r="D93" t="n">
-        <v>-10166434</v>
+        <v>19386872</v>
       </c>
       <c r="E93" t="n">
-        <v>-44426223</v>
+        <v>4151571</v>
       </c>
       <c r="F93" t="n">
-        <v>-5173895</v>
+        <v>21136419</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -948 千股)</t>
+          <t>📈 20d 巨變(加碼 23,115 千股)</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-2149767</v>
+        <v>-64654213</v>
       </c>
       <c r="D94" t="n">
-        <v>-10124082</v>
+        <v>12948485</v>
       </c>
       <c r="E94" t="n">
-        <v>-1217245</v>
+        <v>-141118626</v>
       </c>
       <c r="F94" t="n">
-        <v>-9176008</v>
+        <v>-10166434</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -462 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 1,213 千股)</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-263181</v>
+        <v>1706793</v>
       </c>
       <c r="D95" t="n">
-        <v>735605</v>
+        <v>5494945</v>
       </c>
       <c r="E95" t="n">
-        <v>-176732</v>
+        <v>-47834</v>
       </c>
       <c r="F95" t="n">
-        <v>1197177</v>
+        <v>4281687</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,185 千股)</t>
+          <t>📉 20d 巨變(減碼 -843 千股)</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>919078</v>
+        <v>-283090</v>
       </c>
       <c r="D96" t="n">
-        <v>-7611331</v>
+        <v>-107715</v>
       </c>
       <c r="E96" t="n">
-        <v>539018</v>
+        <v>-263181</v>
       </c>
       <c r="F96" t="n">
-        <v>-8796536</v>
+        <v>735605</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>創意</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -407 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,944 千股)</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>282495</v>
+        <v>-4866091</v>
       </c>
       <c r="D97" t="n">
-        <v>-3561387</v>
+        <v>-13067663</v>
       </c>
       <c r="E97" t="n">
-        <v>434157</v>
+        <v>-2149767</v>
       </c>
       <c r="F97" t="n">
-        <v>-3154601</v>
+        <v>-10124082</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>緯穎</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 815 千股)</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>1671012</v>
+      </c>
+      <c r="D98" t="n">
+        <v>-6796663</v>
+      </c>
+      <c r="E98" t="n">
+        <v>919078</v>
+      </c>
+      <c r="F98" t="n">
+        <v>-7611331</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>5274</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 6 千股)</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>-24347</v>
+      </c>
+      <c r="D99" t="n">
+        <v>251782</v>
+      </c>
+      <c r="E99" t="n">
+        <v>58845</v>
+      </c>
+      <c r="F99" t="n">
+        <v>245467</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>信驊</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>5439</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 147 千股)</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>-24336</v>
+      </c>
+      <c r="D100" t="n">
+        <v>-3414486</v>
+      </c>
+      <c r="E100" t="n">
+        <v>282495</v>
+      </c>
+      <c r="F100" t="n">
+        <v>-3561387</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>高技</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
           <t>6187</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -527 千股)</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 177 千股)</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>329662</v>
+      </c>
+      <c r="D101" t="n">
+        <v>-1429625</v>
+      </c>
+      <c r="E101" t="n">
         <v>-105293</v>
       </c>
-      <c r="D98" t="n">
+      <c r="F101" t="n">
         <v>-1606778</v>
       </c>
-      <c r="E98" t="n">
-        <v>135533</v>
-      </c>
-      <c r="F98" t="n">
-        <v>-1079947</v>
-      </c>
-      <c r="G98" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>萬潤</t>
         </is>

--- a/data/台股_外資雷達.xlsx
+++ b/data/台股_外資雷達.xlsx
@@ -487,31 +487,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10963</v>
+        <v>49524</v>
       </c>
       <c r="D2" t="n">
-        <v>69855</v>
+        <v>70895</v>
       </c>
       <c r="E2" t="n">
-        <v>199536</v>
+        <v>140499</v>
       </c>
       <c r="F2" t="n">
-        <v>342</v>
+        <v>-724</v>
       </c>
       <c r="G2" t="n">
-        <v>6318</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>-3492</v>
+        <v>-39</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -520,11 +520,11 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -538,31 +538,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>43395</v>
+        <v>10210</v>
       </c>
       <c r="D3" t="n">
-        <v>61117</v>
+        <v>62041</v>
       </c>
       <c r="E3" t="n">
-        <v>130455</v>
+        <v>200298</v>
       </c>
       <c r="F3" t="n">
-        <v>-62</v>
+        <v>378</v>
       </c>
       <c r="G3" t="n">
-        <v>588</v>
+        <v>4463</v>
       </c>
       <c r="H3" t="n">
-        <v>-125</v>
+        <v>-3181</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -571,11 +571,11 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -589,31 +589,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-3057</v>
+        <v>6121</v>
       </c>
       <c r="D4" t="n">
-        <v>31879</v>
+        <v>31972</v>
       </c>
       <c r="E4" t="n">
-        <v>570598</v>
+        <v>-15675</v>
       </c>
       <c r="F4" t="n">
-        <v>4355</v>
+        <v>8462</v>
       </c>
       <c r="G4" t="n">
-        <v>17056</v>
+        <v>14104</v>
       </c>
       <c r="H4" t="n">
-        <v>-2719</v>
+        <v>1016</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -622,15 +622,15 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -640,31 +640,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-5781</v>
+        <v>4349</v>
       </c>
       <c r="D5" t="n">
-        <v>26017</v>
+        <v>28128</v>
       </c>
       <c r="E5" t="n">
-        <v>-20838</v>
+        <v>574546</v>
       </c>
       <c r="F5" t="n">
-        <v>-1329</v>
+        <v>6970</v>
       </c>
       <c r="G5" t="n">
-        <v>-16172</v>
+        <v>20000</v>
       </c>
       <c r="H5" t="n">
-        <v>1258</v>
+        <v>-2123</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -673,49 +673,49 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>🐌 龜速*</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-177</v>
+        <v>-8088</v>
       </c>
       <c r="D6" t="n">
-        <v>25632</v>
+        <v>27410</v>
       </c>
       <c r="E6" t="n">
-        <v>-20465</v>
+        <v>-18375</v>
       </c>
       <c r="F6" t="n">
-        <v>4344</v>
+        <v>-934</v>
       </c>
       <c r="G6" t="n">
-        <v>12173</v>
+        <v>-11837</v>
       </c>
       <c r="H6" t="n">
-        <v>752</v>
+        <v>1188</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -728,15 +728,15 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速*</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3420</v>
+        <v>3556</v>
       </c>
       <c r="D7" t="n">
-        <v>19387</v>
+        <v>18161</v>
       </c>
       <c r="E7" t="n">
-        <v>88457</v>
+        <v>89038</v>
       </c>
       <c r="F7" t="n">
-        <v>335</v>
+        <v>601</v>
       </c>
       <c r="G7" t="n">
-        <v>-577</v>
+        <v>-1547</v>
       </c>
       <c r="H7" t="n">
-        <v>-940</v>
+        <v>-847</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -802,22 +802,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>182</v>
+        <v>591</v>
       </c>
       <c r="D8" t="n">
-        <v>14692</v>
+        <v>15221</v>
       </c>
       <c r="E8" t="n">
-        <v>22449</v>
+        <v>22631</v>
       </c>
       <c r="F8" t="n">
-        <v>-69</v>
+        <v>-56</v>
       </c>
       <c r="G8" t="n">
         <v>57</v>
       </c>
       <c r="H8" t="n">
-        <v>-3</v>
+        <v>80</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -844,82 +844,82 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-64654</v>
+        <v>-1530</v>
       </c>
       <c r="D9" t="n">
-        <v>12948</v>
+        <v>8380</v>
       </c>
       <c r="E9" t="n">
-        <v>9565</v>
+        <v>10593</v>
       </c>
       <c r="F9" t="n">
-        <v>-15785</v>
+        <v>-2</v>
       </c>
       <c r="G9" t="n">
-        <v>-35949</v>
+        <v>903</v>
       </c>
       <c r="H9" t="n">
-        <v>-6097</v>
+        <v>1094</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>🚀 大買</t>
+          <t>🟢 加碼</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-1272</v>
+        <v>6553</v>
       </c>
       <c r="D10" t="n">
-        <v>8458</v>
+        <v>6489</v>
       </c>
       <c r="E10" t="n">
-        <v>10714</v>
+        <v>-4307</v>
       </c>
       <c r="F10" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>902</v>
+        <v>-8</v>
       </c>
       <c r="H10" t="n">
-        <v>867</v>
+        <v>620</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -928,49 +928,49 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-24297</v>
+        <v>290</v>
       </c>
       <c r="D11" t="n">
-        <v>7949</v>
+        <v>6055</v>
       </c>
       <c r="E11" t="n">
-        <v>59718</v>
+        <v>6268</v>
       </c>
       <c r="F11" t="n">
-        <v>-4680</v>
+        <v>-251</v>
       </c>
       <c r="G11" t="n">
-        <v>-8869</v>
+        <v>1653</v>
       </c>
       <c r="H11" t="n">
-        <v>-3297</v>
+        <v>1271</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -979,49 +979,49 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1707</v>
+        <v>706</v>
       </c>
       <c r="D12" t="n">
-        <v>5495</v>
+        <v>5020</v>
       </c>
       <c r="E12" t="n">
-        <v>5968</v>
+        <v>24969</v>
       </c>
       <c r="F12" t="n">
-        <v>-233</v>
+        <v>427</v>
       </c>
       <c r="G12" t="n">
-        <v>-184</v>
+        <v>-89</v>
       </c>
       <c r="H12" t="n">
-        <v>888</v>
+        <v>41</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1030,15 +1030,15 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -1048,31 +1048,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>409</v>
+        <v>2871</v>
       </c>
       <c r="D13" t="n">
-        <v>4838</v>
+        <v>4419</v>
       </c>
       <c r="E13" t="n">
-        <v>11538</v>
+        <v>16208</v>
       </c>
       <c r="F13" t="n">
-        <v>452</v>
+        <v>-2502</v>
       </c>
       <c r="G13" t="n">
-        <v>-720</v>
+        <v>-6157</v>
       </c>
       <c r="H13" t="n">
-        <v>-120</v>
+        <v>-54</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1081,11 +1081,11 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1093,37 +1093,37 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6625</v>
+        <v>395</v>
       </c>
       <c r="D14" t="n">
-        <v>4422</v>
+        <v>3858</v>
       </c>
       <c r="E14" t="n">
-        <v>-5821</v>
+        <v>11733</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>732</v>
       </c>
       <c r="G14" t="n">
-        <v>-8</v>
+        <v>-441</v>
       </c>
       <c r="H14" t="n">
-        <v>586</v>
+        <v>-103</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1132,11 +1132,11 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1144,37 +1144,37 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3365</v>
+        <v>3521</v>
       </c>
       <c r="D15" t="n">
-        <v>4397</v>
+        <v>3803</v>
       </c>
       <c r="E15" t="n">
-        <v>15894</v>
+        <v>1506</v>
       </c>
       <c r="F15" t="n">
-        <v>-2613</v>
+        <v>-91</v>
       </c>
       <c r="G15" t="n">
-        <v>-6175</v>
+        <v>592</v>
       </c>
       <c r="H15" t="n">
-        <v>-65</v>
+        <v>-137</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1183,49 +1183,49 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>333</v>
+        <v>1970</v>
       </c>
       <c r="D16" t="n">
-        <v>4347</v>
+        <v>3359</v>
       </c>
       <c r="E16" t="n">
-        <v>24405</v>
+        <v>-926</v>
       </c>
       <c r="F16" t="n">
-        <v>-9</v>
+        <v>-5125</v>
       </c>
       <c r="G16" t="n">
-        <v>-568</v>
+        <v>-14662</v>
       </c>
       <c r="H16" t="n">
-        <v>18</v>
+        <v>956</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1234,49 +1234,49 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-7220</v>
+        <v>4077</v>
       </c>
       <c r="D17" t="n">
-        <v>2677</v>
+        <v>3253</v>
       </c>
       <c r="E17" t="n">
-        <v>10653</v>
+        <v>-4545</v>
       </c>
       <c r="F17" t="n">
-        <v>509</v>
+        <v>101</v>
       </c>
       <c r="G17" t="n">
-        <v>1473</v>
+        <v>2253</v>
       </c>
       <c r="H17" t="n">
-        <v>808</v>
+        <v>-339</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1285,19 +1285,19 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="18">
@@ -1312,22 +1312,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-1139</v>
+        <v>173</v>
       </c>
       <c r="D18" t="n">
-        <v>2067</v>
+        <v>2304</v>
       </c>
       <c r="E18" t="n">
-        <v>10072</v>
+        <v>11131</v>
       </c>
       <c r="F18" t="n">
-        <v>335</v>
+        <v>567</v>
       </c>
       <c r="G18" t="n">
-        <v>-12624</v>
+        <v>-11853</v>
       </c>
       <c r="H18" t="n">
-        <v>-122</v>
+        <v>-28</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1354,35 +1354,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>840</v>
+        <v>970</v>
       </c>
       <c r="D19" t="n">
-        <v>1918</v>
+        <v>2095</v>
       </c>
       <c r="E19" t="n">
-        <v>6120</v>
+        <v>233</v>
       </c>
       <c r="F19" t="n">
-        <v>36</v>
+        <v>587</v>
       </c>
       <c r="G19" t="n">
-        <v>-260</v>
+        <v>228</v>
       </c>
       <c r="H19" t="n">
-        <v>-20</v>
+        <v>-111</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>🟡 中性</t>
+          <t>🟢 加碼</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1391,11 +1391,11 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M19" t="n">
@@ -1405,82 +1405,82 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1072</v>
+        <v>841</v>
       </c>
       <c r="D20" t="n">
-        <v>1911</v>
+        <v>2087</v>
       </c>
       <c r="E20" t="n">
-        <v>-2030</v>
+        <v>6052</v>
       </c>
       <c r="F20" t="n">
-        <v>-1117</v>
+        <v>36</v>
       </c>
       <c r="G20" t="n">
-        <v>-9956</v>
+        <v>-353</v>
       </c>
       <c r="H20" t="n">
-        <v>-67</v>
+        <v>8</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>🟡 中性</t>
+          <t>🟢 加碼</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2306</v>
+        <v>-9</v>
       </c>
       <c r="D21" t="n">
-        <v>1819</v>
+        <v>1814</v>
       </c>
       <c r="E21" t="n">
-        <v>218</v>
+        <v>-2052</v>
       </c>
       <c r="F21" t="n">
-        <v>-72</v>
+        <v>82</v>
       </c>
       <c r="G21" t="n">
-        <v>876</v>
+        <v>-400</v>
       </c>
       <c r="H21" t="n">
-        <v>-215</v>
+        <v>198</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1489,49 +1489,49 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>561</v>
+        <v>79</v>
       </c>
       <c r="D22" t="n">
-        <v>1769</v>
+        <v>1381</v>
       </c>
       <c r="E22" t="n">
-        <v>-297</v>
+        <v>-290</v>
       </c>
       <c r="F22" t="n">
-        <v>533</v>
+        <v>273</v>
       </c>
       <c r="G22" t="n">
-        <v>-200</v>
+        <v>109</v>
       </c>
       <c r="H22" t="n">
-        <v>-239</v>
+        <v>-57</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1544,45 +1544,45 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-623</v>
+        <v>1227</v>
       </c>
       <c r="D23" t="n">
-        <v>1705</v>
+        <v>1126</v>
       </c>
       <c r="E23" t="n">
-        <v>-2122</v>
+        <v>75132</v>
       </c>
       <c r="F23" t="n">
-        <v>83</v>
+        <v>2509</v>
       </c>
       <c r="G23" t="n">
-        <v>-404</v>
+        <v>5358</v>
       </c>
       <c r="H23" t="n">
-        <v>165</v>
+        <v>-2730</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1591,11 +1591,11 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1603,37 +1603,37 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>合機</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-765</v>
+        <v>203</v>
       </c>
       <c r="D24" t="n">
-        <v>1279</v>
+        <v>1027</v>
       </c>
       <c r="E24" t="n">
-        <v>26</v>
+        <v>1883</v>
       </c>
       <c r="F24" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-20</v>
+        <v>-44</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1642,15 +1642,15 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M24" t="n">
@@ -1660,31 +1660,31 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>20</v>
+        <v>-1264</v>
       </c>
       <c r="D25" t="n">
-        <v>1231</v>
+        <v>942</v>
       </c>
       <c r="E25" t="n">
-        <v>-330</v>
+        <v>64</v>
       </c>
       <c r="F25" t="n">
-        <v>340</v>
+        <v>21</v>
       </c>
       <c r="G25" t="n">
-        <v>300</v>
+        <v>71</v>
       </c>
       <c r="H25" t="n">
-        <v>-33</v>
+        <v>13</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1693,49 +1693,49 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>34</v>
+        <v>116</v>
       </c>
       <c r="D26" t="n">
-        <v>968</v>
+        <v>885</v>
       </c>
       <c r="E26" t="n">
-        <v>1740</v>
+        <v>4459</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>-93</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2033</v>
       </c>
       <c r="H26" t="n">
-        <v>-45</v>
+        <v>95</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1748,45 +1748,45 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>549</v>
+        <v>25</v>
       </c>
       <c r="D27" t="n">
-        <v>860</v>
+        <v>762</v>
       </c>
       <c r="E27" t="n">
-        <v>-1000</v>
+        <v>327</v>
       </c>
       <c r="F27" t="n">
-        <v>-70</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>318</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1795,49 +1795,49 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-177</v>
+        <v>-6150</v>
       </c>
       <c r="D28" t="n">
-        <v>761</v>
+        <v>703</v>
       </c>
       <c r="E28" t="n">
-        <v>198</v>
+        <v>9727</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>637</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1513</v>
       </c>
       <c r="H28" t="n">
-        <v>4</v>
+        <v>1040</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1850,45 +1850,45 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>20</v>
+        <v>784</v>
       </c>
       <c r="D29" t="n">
-        <v>726</v>
+        <v>642</v>
       </c>
       <c r="E29" t="n">
-        <v>-3145</v>
+        <v>2275</v>
       </c>
       <c r="F29" t="n">
-        <v>-411</v>
+        <v>59</v>
       </c>
       <c r="G29" t="n">
-        <v>-2207</v>
+        <v>236</v>
       </c>
       <c r="H29" t="n">
-        <v>40</v>
+        <v>-63</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1897,49 +1897,49 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-2514</v>
+        <v>489</v>
       </c>
       <c r="D30" t="n">
-        <v>646</v>
+        <v>590</v>
       </c>
       <c r="E30" t="n">
-        <v>-769</v>
+        <v>3038</v>
       </c>
       <c r="F30" t="n">
-        <v>3367</v>
+        <v>-2</v>
       </c>
       <c r="G30" t="n">
-        <v>8714</v>
+        <v>-34</v>
       </c>
       <c r="H30" t="n">
-        <v>-19</v>
+        <v>-46</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1948,11 +1948,11 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -1960,37 +1960,37 @@
         </is>
       </c>
       <c r="M30" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>550</v>
+        <v>267</v>
       </c>
       <c r="D31" t="n">
-        <v>639</v>
+        <v>504</v>
       </c>
       <c r="E31" t="n">
-        <v>4613</v>
+        <v>-393</v>
       </c>
       <c r="F31" t="n">
-        <v>-95</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>2121</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1999,100 +1999,100 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>356</v>
+        <v>-214</v>
       </c>
       <c r="D32" t="n">
-        <v>517</v>
+        <v>492</v>
       </c>
       <c r="E32" t="n">
-        <v>-404</v>
+        <v>253</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>-279</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>-2295</v>
       </c>
       <c r="H32" t="n">
+        <v>-28</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>90</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>🚀 加速器</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
         <v>4</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K32" t="n">
-        <v>78</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M32" t="n">
-        <v>-3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>260</v>
+        <v>343</v>
       </c>
       <c r="D33" t="n">
-        <v>507</v>
+        <v>426</v>
       </c>
       <c r="E33" t="n">
-        <v>2822</v>
+        <v>-2870</v>
       </c>
       <c r="F33" t="n">
-        <v>-2</v>
+        <v>-1061</v>
       </c>
       <c r="G33" t="n">
-        <v>-34</v>
+        <v>-2996</v>
       </c>
       <c r="H33" t="n">
-        <v>-46</v>
+        <v>327</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2101,49 +2101,49 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-58</v>
+        <v>19</v>
       </c>
       <c r="D34" t="n">
-        <v>419</v>
+        <v>349</v>
       </c>
       <c r="E34" t="n">
-        <v>302</v>
+        <v>718</v>
       </c>
       <c r="F34" t="n">
-        <v>-608</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-2294</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-59</v>
+        <v>7</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2152,49 +2152,49 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>449</v>
+        <v>-1201</v>
       </c>
       <c r="D35" t="n">
-        <v>398</v>
+        <v>345</v>
       </c>
       <c r="E35" t="n">
-        <v>2011</v>
+        <v>2030</v>
       </c>
       <c r="F35" t="n">
-        <v>57</v>
+        <v>-469</v>
       </c>
       <c r="G35" t="n">
-        <v>237</v>
+        <v>-1989</v>
       </c>
       <c r="H35" t="n">
-        <v>-94</v>
+        <v>-295</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2207,45 +2207,45 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D36" t="n">
-        <v>396</v>
+        <v>311</v>
       </c>
       <c r="E36" t="n">
-        <v>729</v>
+        <v>-1431</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>-409</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2254,19 +2254,19 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-84</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>292</v>
+        <v>232</v>
       </c>
       <c r="E37" t="n">
-        <v>785</v>
+        <v>833</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -2332,22 +2332,22 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-21</v>
+        <v>-159</v>
       </c>
       <c r="D38" t="n">
-        <v>266</v>
+        <v>205</v>
       </c>
       <c r="E38" t="n">
-        <v>-751</v>
+        <v>-876</v>
       </c>
       <c r="F38" t="n">
-        <v>3</v>
+        <v>97</v>
       </c>
       <c r="G38" t="n">
-        <v>-306</v>
+        <v>-251</v>
       </c>
       <c r="H38" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2383,22 +2383,22 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-24</v>
+        <v>-98</v>
       </c>
       <c r="D39" t="n">
-        <v>252</v>
+        <v>168</v>
       </c>
       <c r="E39" t="n">
-        <v>-345</v>
+        <v>-380</v>
       </c>
       <c r="F39" t="n">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="G39" t="n">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="H39" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2422,22 +2422,22 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-145</v>
+        <v>-89</v>
       </c>
       <c r="D40" t="n">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E40" t="n">
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="F40" t="n">
-        <v>-28</v>
+        <v>-23</v>
       </c>
       <c r="G40" t="n">
         <v>-28</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2473,13 +2473,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D41" t="n">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="E41" t="n">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -2488,7 +2488,7 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2524,13 +2524,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D42" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E42" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -2575,13 +2575,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-289</v>
+        <v>-199</v>
       </c>
       <c r="D43" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="E43" t="n">
-        <v>446</v>
+        <v>487</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2590,7 +2590,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2626,13 +2626,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D44" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2668,31 +2668,31 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-41</v>
+        <v>-27</v>
       </c>
       <c r="D45" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E45" t="n">
-        <v>-523</v>
+        <v>707</v>
       </c>
       <c r="F45" t="n">
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>-277</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-15</v>
+        <v>-2</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2701,15 +2701,15 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M45" t="n">
@@ -2719,22 +2719,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-51</v>
+        <v>38</v>
       </c>
       <c r="D46" t="n">
-        <v>18</v>
+        <v>-49</v>
       </c>
       <c r="E46" t="n">
-        <v>689</v>
+        <v>-273</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2743,7 +2743,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-1</v>
+        <v>-0</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2752,11 +2752,11 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2764,37 +2764,37 @@
         </is>
       </c>
       <c r="M46" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-76</v>
+        <v>-65</v>
       </c>
       <c r="D47" t="n">
-        <v>-3</v>
+        <v>-53</v>
       </c>
       <c r="E47" t="n">
-        <v>1115</v>
+        <v>-479</v>
       </c>
       <c r="F47" t="n">
-        <v>10</v>
+        <v>-29</v>
       </c>
       <c r="G47" t="n">
-        <v>4</v>
+        <v>-277</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2803,15 +2803,15 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>🐌 龜速*</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M47" t="n">
@@ -2821,22 +2821,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="D48" t="n">
-        <v>-62</v>
+        <v>-59</v>
       </c>
       <c r="E48" t="n">
-        <v>-284</v>
+        <v>-2</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M48" t="n">
@@ -2872,31 +2872,31 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-184</v>
+        <v>-89</v>
       </c>
       <c r="D49" t="n">
-        <v>-84</v>
+        <v>-103</v>
       </c>
       <c r="E49" t="n">
-        <v>2057</v>
+        <v>1114</v>
       </c>
       <c r="F49" t="n">
-        <v>-101</v>
+        <v>13</v>
       </c>
       <c r="G49" t="n">
-        <v>-55</v>
+        <v>8</v>
       </c>
       <c r="H49" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2905,49 +2905,49 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🐌 龜速*</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-283</v>
+        <v>-1419</v>
       </c>
       <c r="D50" t="n">
-        <v>-108</v>
+        <v>-106</v>
       </c>
       <c r="E50" t="n">
-        <v>1219</v>
+        <v>-1630</v>
       </c>
       <c r="F50" t="n">
-        <v>591</v>
+        <v>1032</v>
       </c>
       <c r="G50" t="n">
-        <v>1388</v>
+        <v>8626</v>
       </c>
       <c r="H50" t="n">
-        <v>-87</v>
+        <v>60</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2956,49 +2956,49 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-90</v>
+        <v>93</v>
       </c>
       <c r="D51" t="n">
-        <v>-110</v>
+        <v>-120</v>
       </c>
       <c r="E51" t="n">
-        <v>-57</v>
+        <v>-2163</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H51" t="n">
-        <v>-4</v>
+        <v>-22</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3015,11 +3015,11 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3034,22 +3034,22 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-124</v>
+        <v>-126</v>
       </c>
       <c r="D52" t="n">
-        <v>-119</v>
+        <v>-127</v>
       </c>
       <c r="E52" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="F52" t="n">
         <v>33</v>
       </c>
       <c r="G52" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H52" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3076,31 +3076,31 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-953</v>
+        <v>-835</v>
       </c>
       <c r="D53" t="n">
-        <v>-120</v>
+        <v>-162</v>
       </c>
       <c r="E53" t="n">
-        <v>-13</v>
+        <v>808</v>
       </c>
       <c r="F53" t="n">
-        <v>-1</v>
+        <v>985</v>
       </c>
       <c r="G53" t="n">
-        <v>-361</v>
+        <v>1595</v>
       </c>
       <c r="H53" t="n">
-        <v>-160</v>
+        <v>-93</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3109,15 +3109,15 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M53" t="n">
@@ -3127,31 +3127,31 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-125</v>
+        <v>11</v>
       </c>
       <c r="D54" t="n">
-        <v>-223</v>
+        <v>-185</v>
       </c>
       <c r="E54" t="n">
-        <v>115</v>
+        <v>2186</v>
       </c>
       <c r="F54" t="n">
-        <v>-40</v>
+        <v>-216</v>
       </c>
       <c r="G54" t="n">
-        <v>-41</v>
+        <v>-169</v>
       </c>
       <c r="H54" t="n">
-        <v>-24</v>
+        <v>7</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3160,49 +3160,49 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M54" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>73</v>
+        <v>-34</v>
       </c>
       <c r="D55" t="n">
-        <v>-231</v>
+        <v>-229</v>
       </c>
       <c r="E55" t="n">
-        <v>-2203</v>
+        <v>94</v>
       </c>
       <c r="F55" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>-1</v>
+        <v>-41</v>
       </c>
       <c r="H55" t="n">
-        <v>-28</v>
+        <v>-21</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3211,19 +3211,19 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3238,22 +3238,22 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-52</v>
+        <v>-197</v>
       </c>
       <c r="D56" t="n">
-        <v>-246</v>
+        <v>-242</v>
       </c>
       <c r="E56" t="n">
-        <v>-2081</v>
+        <v>-2247</v>
       </c>
       <c r="F56" t="n">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="G56" t="n">
-        <v>-1189</v>
+        <v>-1349</v>
       </c>
       <c r="H56" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3280,31 +3280,31 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>智冠</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3093</v>
+        <v>-18</v>
       </c>
       <c r="D57" t="n">
-        <v>-253</v>
+        <v>-429</v>
       </c>
       <c r="E57" t="n">
-        <v>-6056</v>
+        <v>-869</v>
       </c>
       <c r="F57" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>2789</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-416</v>
+        <v>-4</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3313,19 +3313,19 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="58">
@@ -3340,13 +3340,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-140</v>
+        <v>-56</v>
       </c>
       <c r="D58" t="n">
-        <v>-413</v>
+        <v>-454</v>
       </c>
       <c r="E58" t="n">
-        <v>-2076</v>
+        <v>-2043</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -3382,82 +3382,82 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-58</v>
+        <v>499</v>
       </c>
       <c r="D59" t="n">
-        <v>-458</v>
+        <v>-497</v>
       </c>
       <c r="E59" t="n">
-        <v>-884</v>
+        <v>-6238</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>-198</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H59" t="n">
+        <v>90</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>51</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
         <v>-3</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K59" t="n">
-        <v>80</v>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M59" t="n">
-        <v>-2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-309</v>
+        <v>583</v>
       </c>
       <c r="D60" t="n">
-        <v>-523</v>
+        <v>-545</v>
       </c>
       <c r="E60" t="n">
-        <v>-3526</v>
+        <v>-8414</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>-2187</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>-7873</v>
       </c>
       <c r="H60" t="n">
-        <v>-63</v>
+        <v>190</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3470,45 +3470,45 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-240</v>
+        <v>-91</v>
       </c>
       <c r="D61" t="n">
-        <v>-526</v>
+        <v>-548</v>
       </c>
       <c r="E61" t="n">
-        <v>418</v>
+        <v>-3477</v>
       </c>
       <c r="F61" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-46</v>
+        <v>-63</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3517,40 +3517,40 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>251</v>
+        <v>128</v>
       </c>
       <c r="D62" t="n">
-        <v>-642</v>
+        <v>-622</v>
       </c>
       <c r="E62" t="n">
-        <v>-2961</v>
+        <v>867</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-35</v>
+        <v>-219</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3568,11 +3568,11 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -3580,37 +3580,37 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>530</v>
+        <v>83</v>
       </c>
       <c r="D63" t="n">
-        <v>-731</v>
+        <v>-656</v>
       </c>
       <c r="E63" t="n">
-        <v>-6227</v>
+        <v>-1165</v>
       </c>
       <c r="F63" t="n">
-        <v>-106</v>
+        <v>84</v>
       </c>
       <c r="G63" t="n">
-        <v>109</v>
+        <v>425</v>
       </c>
       <c r="H63" t="n">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3619,49 +3619,49 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-1769</v>
+        <v>219</v>
       </c>
       <c r="D64" t="n">
-        <v>-746</v>
+        <v>-657</v>
       </c>
       <c r="E64" t="n">
-        <v>4141</v>
+        <v>-3035</v>
       </c>
       <c r="F64" t="n">
-        <v>-933</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>-2394</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>429</v>
+        <v>-31</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3670,49 +3670,49 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-2742</v>
+        <v>142</v>
       </c>
       <c r="D65" t="n">
-        <v>-784</v>
+        <v>-719</v>
       </c>
       <c r="E65" t="n">
-        <v>1085</v>
+        <v>-2679</v>
       </c>
       <c r="F65" t="n">
-        <v>-510</v>
+        <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>-1999</v>
+        <v>197</v>
       </c>
       <c r="H65" t="n">
-        <v>-363</v>
+        <v>-57</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3721,11 +3721,11 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3733,37 +3733,37 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-74</v>
+        <v>-450</v>
       </c>
       <c r="D66" t="n">
-        <v>-807</v>
+        <v>-745</v>
       </c>
       <c r="E66" t="n">
-        <v>594</v>
+        <v>191</v>
       </c>
       <c r="F66" t="n">
-        <v>-143</v>
+        <v>8</v>
       </c>
       <c r="G66" t="n">
-        <v>632</v>
+        <v>-20</v>
       </c>
       <c r="H66" t="n">
-        <v>13</v>
+        <v>-35</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3772,49 +3772,49 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M66" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-170</v>
+        <v>-87</v>
       </c>
       <c r="D67" t="n">
-        <v>-876</v>
+        <v>-889</v>
       </c>
       <c r="E67" t="n">
-        <v>627</v>
+        <v>517</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>590</v>
       </c>
       <c r="H67" t="n">
-        <v>-226</v>
+        <v>17</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3823,49 +3823,49 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M67" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-368</v>
+        <v>-89</v>
       </c>
       <c r="D68" t="n">
-        <v>-894</v>
+        <v>-999</v>
       </c>
       <c r="E68" t="n">
-        <v>-3091</v>
+        <v>1503</v>
       </c>
       <c r="F68" t="n">
-        <v>-3</v>
+        <v>-229</v>
       </c>
       <c r="G68" t="n">
-        <v>198</v>
+        <v>-482</v>
       </c>
       <c r="H68" t="n">
-        <v>-62</v>
+        <v>-46</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3874,49 +3874,49 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-1623</v>
+        <v>-96</v>
       </c>
       <c r="D69" t="n">
-        <v>-974</v>
+        <v>-1089</v>
       </c>
       <c r="E69" t="n">
-        <v>-6479</v>
+        <v>-3251</v>
       </c>
       <c r="F69" t="n">
-        <v>177</v>
+        <v>-50</v>
       </c>
       <c r="G69" t="n">
-        <v>1992</v>
+        <v>88</v>
       </c>
       <c r="H69" t="n">
-        <v>-516</v>
+        <v>-74</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3925,71 +3925,59 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-346</v>
+        <v>18</v>
       </c>
       <c r="D70" t="n">
-        <v>-1119</v>
+        <v>-1243</v>
       </c>
       <c r="E70" t="n">
-        <v>1442</v>
+        <v>1562</v>
       </c>
       <c r="F70" t="n">
-        <v>-254</v>
+        <v>-111</v>
       </c>
       <c r="G70" t="n">
-        <v>-482</v>
+        <v>1637</v>
       </c>
       <c r="H70" t="n">
-        <v>-77</v>
+        <v>-32</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K70" t="n">
-        <v>91</v>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>✈️ 高飛</t>
-        </is>
-      </c>
-      <c r="M70" t="n">
-        <v>4</v>
-      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4003,13 +3991,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-208</v>
+        <v>-233</v>
       </c>
       <c r="D71" t="n">
-        <v>-1248</v>
+        <v>-1290</v>
       </c>
       <c r="E71" t="n">
-        <v>-1732</v>
+        <v>-1740</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -4018,7 +4006,7 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -4045,31 +4033,31 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-86</v>
+        <v>-969</v>
       </c>
       <c r="D72" t="n">
-        <v>-1262</v>
+        <v>-1304</v>
       </c>
       <c r="E72" t="n">
-        <v>-3186</v>
+        <v>-898</v>
       </c>
       <c r="F72" t="n">
-        <v>78</v>
+        <v>-1</v>
       </c>
       <c r="G72" t="n">
-        <v>202</v>
+        <v>-281</v>
       </c>
       <c r="H72" t="n">
-        <v>-94</v>
+        <v>-263</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -4078,49 +4066,49 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>勝一</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-125</v>
+        <v>-197</v>
       </c>
       <c r="D73" t="n">
-        <v>-1273</v>
+        <v>-1525</v>
       </c>
       <c r="E73" t="n">
-        <v>-1182</v>
+        <v>-3144</v>
       </c>
       <c r="F73" t="n">
-        <v>81</v>
+        <v>38</v>
       </c>
       <c r="G73" t="n">
-        <v>422</v>
+        <v>-1</v>
       </c>
       <c r="H73" t="n">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4129,49 +4117,49 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>165</v>
+        <v>-2150</v>
       </c>
       <c r="D74" t="n">
-        <v>-1364</v>
+        <v>-1550</v>
       </c>
       <c r="E74" t="n">
-        <v>-8895</v>
+        <v>-7189</v>
       </c>
       <c r="F74" t="n">
-        <v>-1370</v>
+        <v>410</v>
       </c>
       <c r="G74" t="n">
-        <v>-6747</v>
+        <v>1850</v>
       </c>
       <c r="H74" t="n">
-        <v>123</v>
+        <v>-338</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4180,88 +4168,100 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M74" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>330</v>
+        <v>702</v>
       </c>
       <c r="D75" t="n">
-        <v>-1430</v>
+        <v>-1558</v>
       </c>
       <c r="E75" t="n">
-        <v>1888</v>
+        <v>-2149</v>
       </c>
       <c r="F75" t="n">
-        <v>-314</v>
+        <v>-598</v>
       </c>
       <c r="G75" t="n">
-        <v>1559</v>
+        <v>1403</v>
       </c>
       <c r="H75" t="n">
-        <v>-43</v>
+        <v>31</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>66</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>767</v>
+        <v>-1540</v>
       </c>
       <c r="D76" t="n">
-        <v>-1465</v>
+        <v>-1568</v>
       </c>
       <c r="E76" t="n">
-        <v>-2071</v>
+        <v>1234</v>
       </c>
       <c r="F76" t="n">
-        <v>-356</v>
+        <v>223</v>
       </c>
       <c r="G76" t="n">
-        <v>1465</v>
+        <v>510</v>
       </c>
       <c r="H76" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4270,49 +4270,49 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M76" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-1456</v>
+        <v>-4480</v>
       </c>
       <c r="D77" t="n">
-        <v>-1496</v>
+        <v>-1599</v>
       </c>
       <c r="E77" t="n">
-        <v>1171</v>
+        <v>972</v>
       </c>
       <c r="F77" t="n">
-        <v>428</v>
+        <v>488</v>
       </c>
       <c r="G77" t="n">
-        <v>526</v>
+        <v>-1141</v>
       </c>
       <c r="H77" t="n">
-        <v>24</v>
+        <v>287</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4321,49 +4321,49 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M77" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-242</v>
+        <v>-3733</v>
       </c>
       <c r="D78" t="n">
-        <v>-1587</v>
+        <v>-1681</v>
       </c>
       <c r="E78" t="n">
-        <v>51</v>
+        <v>6276</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="H78" t="n">
-        <v>-184</v>
+        <v>57</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4372,11 +4372,11 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4384,79 +4384,79 @@
         </is>
       </c>
       <c r="M78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-398</v>
+        <v>-548</v>
       </c>
       <c r="D79" t="n">
-        <v>-1772</v>
+        <v>-1817</v>
       </c>
       <c r="E79" t="n">
-        <v>-3368</v>
+        <v>-5035</v>
       </c>
       <c r="F79" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G79" t="n">
+        <v>-226</v>
+      </c>
+      <c r="H79" t="n">
+        <v>2297</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>78</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
         <v>-1</v>
-      </c>
-      <c r="H79" t="n">
-        <v>5</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K79" t="n">
-        <v>71</v>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M79" t="n">
-        <v>-3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-2819</v>
+        <v>63</v>
       </c>
       <c r="D80" t="n">
-        <v>-1816</v>
+        <v>-1979</v>
       </c>
       <c r="E80" t="n">
-        <v>-2295</v>
+        <v>119</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -4465,7 +4465,7 @@
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>6</v>
+        <v>-188</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4474,11 +4474,11 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -4486,41 +4486,41 @@
         </is>
       </c>
       <c r="M80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-3636</v>
+        <v>-2395</v>
       </c>
       <c r="D81" t="n">
-        <v>-1881</v>
+        <v>-2270</v>
       </c>
       <c r="E81" t="n">
-        <v>5865</v>
+        <v>-2587</v>
       </c>
       <c r="F81" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>-17</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>148</v>
+        <v>2</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>🟡 中性</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4543,31 +4543,31 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-764</v>
+        <v>-225</v>
       </c>
       <c r="D82" t="n">
-        <v>-2395</v>
+        <v>-2840</v>
       </c>
       <c r="E82" t="n">
-        <v>-5164</v>
+        <v>-6332</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>-83</v>
       </c>
       <c r="G82" t="n">
-        <v>115</v>
+        <v>-820</v>
       </c>
       <c r="H82" t="n">
-        <v>2292</v>
+        <v>28</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4580,45 +4580,45 @@
         </is>
       </c>
       <c r="K82" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器*</t>
         </is>
       </c>
       <c r="M82" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>92</v>
+        <v>-1510</v>
       </c>
       <c r="D83" t="n">
-        <v>-2692</v>
+        <v>-2878</v>
       </c>
       <c r="E83" t="n">
-        <v>-5802</v>
+        <v>-14446</v>
       </c>
       <c r="F83" t="n">
-        <v>-80</v>
+        <v>757</v>
       </c>
       <c r="G83" t="n">
-        <v>-823</v>
+        <v>1256</v>
       </c>
       <c r="H83" t="n">
-        <v>7</v>
+        <v>-316</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4627,49 +4627,49 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>🚀 加速器*</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M83" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-2215</v>
+        <v>46</v>
       </c>
       <c r="D84" t="n">
-        <v>-2862</v>
+        <v>-2900</v>
       </c>
       <c r="E84" t="n">
-        <v>-4117</v>
+        <v>-4730</v>
       </c>
       <c r="F84" t="n">
-        <v>-216</v>
+        <v>-29</v>
       </c>
       <c r="G84" t="n">
-        <v>-84</v>
+        <v>-217</v>
       </c>
       <c r="H84" t="n">
-        <v>114</v>
+        <v>15</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4678,11 +4678,11 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K84" t="n">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         </is>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
@@ -4705,22 +4705,22 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-815</v>
+        <v>-843</v>
       </c>
       <c r="D85" t="n">
-        <v>-2936</v>
+        <v>-3068</v>
       </c>
       <c r="E85" t="n">
-        <v>-1171</v>
+        <v>-1485</v>
       </c>
       <c r="F85" t="n">
-        <v>-325</v>
+        <v>-303</v>
       </c>
       <c r="G85" t="n">
-        <v>-764</v>
+        <v>-1030</v>
       </c>
       <c r="H85" t="n">
-        <v>-25</v>
+        <v>-1</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4747,31 +4747,31 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-1724</v>
+        <v>-2655</v>
       </c>
       <c r="D86" t="n">
-        <v>-2967</v>
+        <v>-3311</v>
       </c>
       <c r="E86" t="n">
-        <v>-13881</v>
+        <v>-4528</v>
       </c>
       <c r="F86" t="n">
-        <v>784</v>
+        <v>-558</v>
       </c>
       <c r="G86" t="n">
-        <v>1872</v>
+        <v>-453</v>
       </c>
       <c r="H86" t="n">
-        <v>-274</v>
+        <v>108</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4780,15 +4780,15 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K86" t="n">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M86" t="n">
@@ -4798,121 +4798,121 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-23</v>
+        <v>-31</v>
       </c>
       <c r="D87" t="n">
-        <v>-3126</v>
+        <v>-3404</v>
       </c>
       <c r="E87" t="n">
-        <v>-4921</v>
+        <v>-6189</v>
       </c>
       <c r="F87" t="n">
-        <v>-34</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>-217</v>
+        <v>-400</v>
       </c>
       <c r="H87" t="n">
-        <v>-32</v>
+        <v>-4</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
           <t>🟠 減碼</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K87" t="n">
-        <v>90</v>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>🚀 加速器</t>
-        </is>
-      </c>
-      <c r="M87" t="n">
-        <v>4</v>
-      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-24</v>
+        <v>-639</v>
       </c>
       <c r="D88" t="n">
-        <v>-3414</v>
+        <v>-3656</v>
       </c>
       <c r="E88" t="n">
-        <v>-5811</v>
+        <v>-21353</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>-556</v>
       </c>
       <c r="G88" t="n">
-        <v>-400</v>
+        <v>-1452</v>
       </c>
       <c r="H88" t="n">
-        <v>51</v>
+        <v>-350</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
           <t>🟠 減碼</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>100</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>✈️ 高飛</t>
+        </is>
+      </c>
+      <c r="M88" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-206</v>
+        <v>840</v>
       </c>
       <c r="D89" t="n">
-        <v>-3456</v>
+        <v>-3673</v>
       </c>
       <c r="E89" t="n">
-        <v>-21029</v>
+        <v>-2654</v>
       </c>
       <c r="F89" t="n">
-        <v>-370</v>
+        <v>-982</v>
       </c>
       <c r="G89" t="n">
-        <v>-1521</v>
+        <v>4955</v>
       </c>
       <c r="H89" t="n">
-        <v>-293</v>
+        <v>-175</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4921,49 +4921,49 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K89" t="n">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M89" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>692</v>
+        <v>-27619</v>
       </c>
       <c r="D90" t="n">
-        <v>-3662</v>
+        <v>-4616</v>
       </c>
       <c r="E90" t="n">
-        <v>-2639</v>
+        <v>-132721</v>
       </c>
       <c r="F90" t="n">
-        <v>-2360</v>
+        <v>445</v>
       </c>
       <c r="G90" t="n">
-        <v>4955</v>
+        <v>-2830</v>
       </c>
       <c r="H90" t="n">
-        <v>22</v>
+        <v>3296</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4972,19 +4972,19 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K90" t="n">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91">
@@ -4999,22 +4999,22 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-3969</v>
+        <v>24</v>
       </c>
       <c r="D91" t="n">
-        <v>-4629</v>
+        <v>-4635</v>
       </c>
       <c r="E91" t="n">
-        <v>-33894</v>
+        <v>-33483</v>
       </c>
       <c r="F91" t="n">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="G91" t="n">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="H91" t="n">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -5041,70 +5041,82 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>長榮航太</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1671</v>
+        <v>39</v>
       </c>
       <c r="D92" t="n">
-        <v>-6797</v>
+        <v>-6244</v>
       </c>
       <c r="E92" t="n">
-        <v>-8050</v>
+        <v>-13488</v>
       </c>
       <c r="F92" t="n">
-        <v>-2359</v>
+        <v>-395</v>
       </c>
       <c r="G92" t="n">
-        <v>1447</v>
+        <v>-233</v>
       </c>
       <c r="H92" t="n">
-        <v>-80</v>
+        <v>18</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
           <t>🟠 減碼</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>79</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>✈️ 高飛*</t>
+        </is>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-616</v>
+        <v>-3219</v>
       </c>
       <c r="D93" t="n">
-        <v>-7032</v>
+        <v>-7531</v>
       </c>
       <c r="E93" t="n">
-        <v>-13824</v>
+        <v>72606</v>
       </c>
       <c r="F93" t="n">
-        <v>-395</v>
+        <v>-377</v>
       </c>
       <c r="G93" t="n">
-        <v>-187</v>
+        <v>2365</v>
       </c>
       <c r="H93" t="n">
-        <v>8</v>
+        <v>-504</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -5117,11 +5129,11 @@
         </is>
       </c>
       <c r="K93" t="n">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M93" t="n">
@@ -5131,31 +5143,31 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-10101</v>
+        <v>-558</v>
       </c>
       <c r="D94" t="n">
-        <v>-7995</v>
+        <v>-8068</v>
       </c>
       <c r="E94" t="n">
-        <v>72826</v>
+        <v>-16437</v>
       </c>
       <c r="F94" t="n">
-        <v>-466</v>
+        <v>-1</v>
       </c>
       <c r="G94" t="n">
-        <v>2229</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>-843</v>
+        <v>-64</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -5168,45 +5180,45 @@
         </is>
       </c>
       <c r="K94" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-1206</v>
+        <v>-1491</v>
       </c>
       <c r="D95" t="n">
-        <v>-8340</v>
+        <v>-8933</v>
       </c>
       <c r="E95" t="n">
-        <v>-16404</v>
+        <v>-16463</v>
       </c>
       <c r="F95" t="n">
-        <v>-1</v>
+        <v>475</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>1372</v>
       </c>
       <c r="H95" t="n">
-        <v>-66</v>
+        <v>446</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5215,151 +5227,139 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K95" t="n">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M95" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-34358</v>
+        <v>-1360</v>
       </c>
       <c r="D96" t="n">
-        <v>-8677</v>
+        <v>-9526</v>
       </c>
       <c r="E96" t="n">
-        <v>-137515</v>
+        <v>-11719</v>
       </c>
       <c r="F96" t="n">
-        <v>56</v>
+        <v>-2179</v>
       </c>
       <c r="G96" t="n">
-        <v>-2371</v>
+        <v>1586</v>
       </c>
       <c r="H96" t="n">
-        <v>2770</v>
+        <v>177</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
           <t>🟠 減碼</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K96" t="n">
-        <v>100</v>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>✈️ 高飛</t>
-        </is>
-      </c>
-      <c r="M96" t="n">
-        <v>3</v>
-      </c>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-1706</v>
+        <v>-921</v>
       </c>
       <c r="D97" t="n">
-        <v>-9122</v>
+        <v>-10612</v>
       </c>
       <c r="E97" t="n">
-        <v>-16361</v>
+        <v>-24686</v>
       </c>
       <c r="F97" t="n">
-        <v>442</v>
+        <v>-100</v>
       </c>
       <c r="G97" t="n">
-        <v>1812</v>
+        <v>-100</v>
       </c>
       <c r="H97" t="n">
-        <v>434</v>
+        <v>-154</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🔴 大賣</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K97" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M97" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-2503</v>
+        <v>-4314</v>
       </c>
       <c r="D98" t="n">
-        <v>-11561</v>
+        <v>-12896</v>
       </c>
       <c r="E98" t="n">
-        <v>-24636</v>
+        <v>-13599</v>
       </c>
       <c r="F98" t="n">
-        <v>-100</v>
+        <v>-191</v>
       </c>
       <c r="G98" t="n">
-        <v>-100</v>
+        <v>-2682</v>
       </c>
       <c r="H98" t="n">
-        <v>-168</v>
+        <v>-1071</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5368,19 +5368,19 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K98" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M98" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -5395,22 +5395,22 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>3018</v>
+        <v>-349</v>
       </c>
       <c r="D99" t="n">
-        <v>-11944</v>
+        <v>-13596</v>
       </c>
       <c r="E99" t="n">
-        <v>-63473</v>
+        <v>-67910</v>
       </c>
       <c r="F99" t="n">
-        <v>816</v>
+        <v>1491</v>
       </c>
       <c r="G99" t="n">
-        <v>-1150</v>
+        <v>-95</v>
       </c>
       <c r="H99" t="n">
-        <v>-264</v>
+        <v>-229</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5437,31 +5437,31 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-11048</v>
+        <v>-2925</v>
       </c>
       <c r="D100" t="n">
-        <v>-11996</v>
+        <v>-14834</v>
       </c>
       <c r="E100" t="n">
-        <v>66252</v>
+        <v>-51432</v>
       </c>
       <c r="F100" t="n">
-        <v>3411</v>
+        <v>-773</v>
       </c>
       <c r="G100" t="n">
-        <v>6591</v>
+        <v>-7311</v>
       </c>
       <c r="H100" t="n">
-        <v>-3622</v>
+        <v>593</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -5470,49 +5470,49 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K100" t="n">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M100" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-4866</v>
+        <v>-4067</v>
       </c>
       <c r="D101" t="n">
-        <v>-13068</v>
+        <v>-15352</v>
       </c>
       <c r="E101" t="n">
-        <v>-13664</v>
+        <v>54874</v>
       </c>
       <c r="F101" t="n">
-        <v>415</v>
+        <v>-714</v>
       </c>
       <c r="G101" t="n">
-        <v>-2117</v>
+        <v>7899</v>
       </c>
       <c r="H101" t="n">
-        <v>-1040</v>
+        <v>-1472</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5521,49 +5521,49 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K101" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M101" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-10970</v>
+        <v>-21478</v>
       </c>
       <c r="D102" t="n">
-        <v>-14657</v>
+        <v>-18020</v>
       </c>
       <c r="E102" t="n">
-        <v>-50769</v>
+        <v>60027</v>
       </c>
       <c r="F102" t="n">
-        <v>-2689</v>
+        <v>-3802</v>
       </c>
       <c r="G102" t="n">
-        <v>-8155</v>
+        <v>-9057</v>
       </c>
       <c r="H102" t="n">
-        <v>332</v>
+        <v>-3356</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5572,19 +5572,19 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K102" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
@@ -5599,22 +5599,22 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-10907</v>
+        <v>-11012</v>
       </c>
       <c r="D103" t="n">
-        <v>-22198</v>
+        <v>-19390</v>
       </c>
       <c r="E103" t="n">
-        <v>-80955</v>
+        <v>-83008</v>
       </c>
       <c r="F103" t="n">
-        <v>1964</v>
+        <v>2336</v>
       </c>
       <c r="G103" t="n">
-        <v>-22119</v>
+        <v>-21001</v>
       </c>
       <c r="H103" t="n">
-        <v>1159</v>
+        <v>1454</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5641,31 +5641,31 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-4803</v>
+        <v>-69311</v>
       </c>
       <c r="D104" t="n">
-        <v>-23126</v>
+        <v>-20433</v>
       </c>
       <c r="E104" t="n">
-        <v>54850</v>
+        <v>-681</v>
       </c>
       <c r="F104" t="n">
-        <v>-1685</v>
+        <v>-15128</v>
       </c>
       <c r="G104" t="n">
-        <v>10114</v>
+        <v>-32931</v>
       </c>
       <c r="H104" t="n">
-        <v>-1828</v>
+        <v>-4808</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5678,15 +5678,15 @@
         </is>
       </c>
       <c r="K104" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M104" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="105">
@@ -5701,22 +5701,22 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-54905</v>
+        <v>-12325</v>
       </c>
       <c r="D105" t="n">
-        <v>-114915</v>
+        <v>-100782</v>
       </c>
       <c r="E105" t="n">
-        <v>142192</v>
+        <v>151019</v>
       </c>
       <c r="F105" t="n">
-        <v>3923</v>
+        <v>5147</v>
       </c>
       <c r="G105" t="n">
-        <v>35059</v>
+        <v>36240</v>
       </c>
       <c r="H105" t="n">
-        <v>-88</v>
+        <v>734</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5794,348 +5794,348 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 331 千股)</t>
+          <t>📉 20d 巨變(減碼 -300 千股)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-1705983</v>
+        <v>343111</v>
       </c>
       <c r="D2" t="n">
-        <v>-9122032</v>
+        <v>426273</v>
       </c>
       <c r="E2" t="n">
-        <v>-901804</v>
+        <v>20135</v>
       </c>
       <c r="F2" t="n">
-        <v>-9453091</v>
+        <v>726365</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>台光電</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -8 千股)</t>
+          <t>📈 20d 巨變(加碼 246 千股)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20135</v>
+        <v>115861</v>
       </c>
       <c r="D3" t="n">
-        <v>726365</v>
+        <v>885463</v>
       </c>
       <c r="E3" t="n">
-        <v>126407</v>
+        <v>549697</v>
       </c>
       <c r="F3" t="n">
-        <v>734763</v>
+        <v>639380</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>奇鋐</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 151 千股)</t>
+          <t>📈 20d 巨變(加碼 189 千股)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20255</v>
+        <v>-1491111</v>
       </c>
       <c r="D4" t="n">
-        <v>1230832</v>
+        <v>-8932948</v>
       </c>
       <c r="E4" t="n">
-        <v>-8608</v>
+        <v>-1705983</v>
       </c>
       <c r="F4" t="n">
-        <v>1079985</v>
+        <v>-9122032</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -246 千股)</t>
+          <t>📉 20d 巨變(減碼 -200 千股)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>549697</v>
+        <v>-639297</v>
       </c>
       <c r="D5" t="n">
-        <v>639380</v>
+        <v>-3656169</v>
       </c>
       <c r="E5" t="n">
-        <v>805321</v>
+        <v>-206030</v>
       </c>
       <c r="F5" t="n">
-        <v>885199</v>
+        <v>-3455854</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>亞翔</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 307 千股)</t>
+          <t>📈 20d 巨變(加碼 73 千股)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-206030</v>
+        <v>-213601</v>
       </c>
       <c r="D6" t="n">
-        <v>-3455854</v>
+        <v>491720</v>
       </c>
       <c r="E6" t="n">
-        <v>-232115</v>
+        <v>-57933</v>
       </c>
       <c r="F6" t="n">
-        <v>-3763227</v>
+        <v>419071</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>勤誠</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 364 千股)</t>
+          <t>📈 20d 巨變(加碼 151 千股)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-57933</v>
+        <v>79052</v>
       </c>
       <c r="D7" t="n">
-        <v>419071</v>
+        <v>1381453</v>
       </c>
       <c r="E7" t="n">
-        <v>158831</v>
+        <v>20255</v>
       </c>
       <c r="F7" t="n">
-        <v>55400</v>
+        <v>1230832</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>健策</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -343 千股)</t>
+          <t>📉 20d 巨變(減碼 -548 千股)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-623168</v>
+        <v>25102</v>
       </c>
       <c r="D8" t="n">
-        <v>1705253</v>
+        <v>311470</v>
       </c>
       <c r="E8" t="n">
-        <v>-529188</v>
+        <v>548930</v>
       </c>
       <c r="F8" t="n">
-        <v>2048169</v>
+        <v>859780</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>光聖</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -7 千股)</t>
+          <t>📈 20d 巨變(加碼 4,060 千股)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>548930</v>
+        <v>-27619102</v>
       </c>
       <c r="D9" t="n">
-        <v>859780</v>
+        <v>-4616452</v>
       </c>
       <c r="E9" t="n">
-        <v>229699</v>
+        <v>-34357576</v>
       </c>
       <c r="F9" t="n">
-        <v>866408</v>
+        <v>-8676510</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 189 千股)</t>
+          <t>📉 20d 巨變(減碼 -78 千股)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-51764</v>
+        <v>-1530237</v>
       </c>
       <c r="D10" t="n">
-        <v>-245918</v>
+        <v>8379729</v>
       </c>
       <c r="E10" t="n">
-        <v>-215699</v>
+        <v>-1272477</v>
       </c>
       <c r="F10" t="n">
-        <v>-434902</v>
+        <v>8457783</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>雙鴻</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -958 千股)</t>
+          <t>📈 20d 巨變(加碼 819 千股)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-1272477</v>
+        <v>582550</v>
       </c>
       <c r="D11" t="n">
-        <v>8457783</v>
+        <v>-544788</v>
       </c>
       <c r="E11" t="n">
-        <v>88450</v>
+        <v>164892</v>
       </c>
       <c r="F11" t="n">
-        <v>9415690</v>
+        <v>-1364263</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>智邦</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 204 千股)</t>
+          <t>📈 20d 巨變(加碼 109 千股)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>164892</v>
+        <v>-9446</v>
       </c>
       <c r="D12" t="n">
-        <v>-1364263</v>
+        <v>1814324</v>
       </c>
       <c r="E12" t="n">
-        <v>2070385</v>
+        <v>-623168</v>
       </c>
       <c r="F12" t="n">
-        <v>-1568199</v>
+        <v>1705253</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>致茂</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,326 千股)</t>
+          <t>📉 20d 巨變(減碼 -177 千股)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-34357576</v>
+        <v>-2924887</v>
       </c>
       <c r="D13" t="n">
-        <v>-8676510</v>
+        <v>-14834469</v>
       </c>
       <c r="E13" t="n">
-        <v>-28172058</v>
+        <v>-10969822</v>
       </c>
       <c r="F13" t="n">
-        <v>-7350073</v>
+        <v>-14657061</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
@@ -6147,20 +6147,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -119 千股)</t>
+          <t>📈 20d 巨變(加碼 168 千股)</t>
         </is>
       </c>
       <c r="C14" t="n">
+        <v>840746</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2086615</v>
+      </c>
+      <c r="E14" t="n">
         <v>839724</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>1918125</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1803921</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2036971</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -6171,696 +6171,696 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -178 千股)</t>
+          <t>📉 20d 巨變(減碼 -62 千股)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-345554</v>
+        <v>-159131</v>
       </c>
       <c r="D15" t="n">
-        <v>-1119118</v>
+        <v>204756</v>
       </c>
       <c r="E15" t="n">
-        <v>-710826</v>
+        <v>-20521</v>
       </c>
       <c r="F15" t="n">
-        <v>-941083</v>
+        <v>266445</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>川湖</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -93 千股)</t>
+          <t>📈 20d 巨變(加碼 89 千股)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-23253</v>
+        <v>-1509760</v>
       </c>
       <c r="D16" t="n">
-        <v>-3125507</v>
+        <v>-2877872</v>
       </c>
       <c r="E16" t="n">
-        <v>-113917</v>
+        <v>-1723597</v>
       </c>
       <c r="F16" t="n">
-        <v>-3032766</v>
+        <v>-2967191</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>健鼎</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 261 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 226 千股)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-1723597</v>
+        <v>45713</v>
       </c>
       <c r="D17" t="n">
-        <v>-2967191</v>
+        <v>-2899731</v>
       </c>
       <c r="E17" t="n">
-        <v>216411</v>
+        <v>-23253</v>
       </c>
       <c r="F17" t="n">
-        <v>-3227832</v>
+        <v>-3125507</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>佳必琪</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,472 千股)</t>
+          <t>📈 20d 巨變(加碼 120 千股)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-10969822</v>
+        <v>-88754</v>
       </c>
       <c r="D18" t="n">
-        <v>-14657061</v>
+        <v>-998712</v>
       </c>
       <c r="E18" t="n">
-        <v>-9227556</v>
+        <v>-345554</v>
       </c>
       <c r="F18" t="n">
-        <v>-16128955</v>
+        <v>-1119118</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>辛耘</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 39 千股)</t>
+          <t>📈 20d 巨變(加碼 173 千股)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-20521</v>
+        <v>-95640</v>
       </c>
       <c r="D19" t="n">
-        <v>266445</v>
+        <v>-1088657</v>
       </c>
       <c r="E19" t="n">
-        <v>84817</v>
+        <v>-86077</v>
       </c>
       <c r="F19" t="n">
-        <v>227430</v>
+        <v>-1262118</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>崇越</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 117 千股)</t>
+          <t>📈 20d 巨變(加碼 674 千股)</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>529543</v>
+        <v>705718</v>
       </c>
       <c r="D20" t="n">
-        <v>-730543</v>
+        <v>5020474</v>
       </c>
       <c r="E20" t="n">
-        <v>492619</v>
+        <v>333317</v>
       </c>
       <c r="F20" t="n">
-        <v>-847469</v>
+        <v>4346584</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -224 千股)</t>
+          <t>📈 20d 巨變(加碼 326 千股)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-2819244</v>
+        <v>969972</v>
       </c>
       <c r="D21" t="n">
-        <v>-1815520</v>
+        <v>2094944</v>
       </c>
       <c r="E21" t="n">
-        <v>-2667490</v>
+        <v>561262</v>
       </c>
       <c r="F21" t="n">
-        <v>-1591149</v>
+        <v>1768910</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>中砂</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 486 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 617 千股)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>333317</v>
+        <v>82690</v>
       </c>
       <c r="D22" t="n">
-        <v>4346584</v>
+        <v>-655599</v>
       </c>
       <c r="E22" t="n">
-        <v>1254908</v>
+        <v>-124909</v>
       </c>
       <c r="F22" t="n">
-        <v>3860387</v>
+        <v>-1272894</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>華城</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 683 千股)</t>
+          <t>📉 20d 巨變(減碼 -455 千股)</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-86077</v>
+        <v>-2394722</v>
       </c>
       <c r="D23" t="n">
-        <v>-1262118</v>
+        <v>-2270298</v>
       </c>
       <c r="E23" t="n">
-        <v>-233788</v>
+        <v>-2819244</v>
       </c>
       <c r="F23" t="n">
-        <v>-1945357</v>
+        <v>-1815520</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>建榮</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -547 千股)</t>
+          <t>📈 20d 巨變(加碼 233 千股)</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>561262</v>
+        <v>499293</v>
       </c>
       <c r="D24" t="n">
-        <v>1768910</v>
+        <v>-497121</v>
       </c>
       <c r="E24" t="n">
-        <v>1040996</v>
+        <v>529543</v>
       </c>
       <c r="F24" t="n">
-        <v>2315629</v>
+        <v>-730543</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>大立光</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 149 千股)</t>
+          <t>📈 20d 巨變(加碼 200 千股)</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-124909</v>
+        <v>-3732764</v>
       </c>
       <c r="D25" t="n">
-        <v>-1272894</v>
+        <v>-1680640</v>
       </c>
       <c r="E25" t="n">
-        <v>305390</v>
+        <v>-3635553</v>
       </c>
       <c r="F25" t="n">
-        <v>-1421472</v>
+        <v>-1880910</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>零壹</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 17 千股)</t>
+          <t>📉 20d 巨變(減碼 -15 千股)</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>15000</v>
+        <v>218782</v>
       </c>
       <c r="D26" t="n">
-        <v>35251</v>
+        <v>-657400</v>
       </c>
       <c r="E26" t="n">
-        <v>7000</v>
+        <v>250917</v>
       </c>
       <c r="F26" t="n">
-        <v>18251</v>
+        <v>-642090</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>湧德</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 44 千股)</t>
+          <t>📈 20d 巨變(加碼 529 千股)</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>250917</v>
+        <v>591133</v>
       </c>
       <c r="D27" t="n">
-        <v>-642090</v>
+        <v>15220548</v>
       </c>
       <c r="E27" t="n">
-        <v>283170</v>
+        <v>182195</v>
       </c>
       <c r="F27" t="n">
-        <v>-686392</v>
+        <v>14691920</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -5 千股)</t>
+          <t>📉 20d 巨變(減碼 -24 千股)</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-50643</v>
+        <v>-91173</v>
       </c>
       <c r="D28" t="n">
-        <v>17631</v>
+        <v>-547672</v>
       </c>
       <c r="E28" t="n">
-        <v>-58643</v>
+        <v>-309173</v>
       </c>
       <c r="F28" t="n">
-        <v>22631</v>
+        <v>-523367</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>隆大</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,286 千股)</t>
+          <t>📈 20d 巨變(加碼 59 千股)</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-3635553</v>
+        <v>203303</v>
       </c>
       <c r="D29" t="n">
-        <v>-1880910</v>
+        <v>1027113</v>
       </c>
       <c r="E29" t="n">
-        <v>-2879314</v>
+        <v>34446</v>
       </c>
       <c r="F29" t="n">
-        <v>-594821</v>
+        <v>967620</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>合機</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -42 千股)</t>
+          <t>📉 20d 巨變(減碼 -72 千股)</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-309173</v>
+        <v>-1539643</v>
       </c>
       <c r="D30" t="n">
-        <v>-523367</v>
+        <v>-1568249</v>
       </c>
       <c r="E30" t="n">
-        <v>-255650</v>
+        <v>-1456004</v>
       </c>
       <c r="F30" t="n">
-        <v>-481844</v>
+        <v>-1496195</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>卜蜂</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -24 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -3,751 千股)</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>34446</v>
+        <v>4348602</v>
       </c>
       <c r="D31" t="n">
-        <v>967620</v>
+        <v>28128099</v>
       </c>
       <c r="E31" t="n">
-        <v>78934</v>
+        <v>-3056869</v>
       </c>
       <c r="F31" t="n">
-        <v>991654</v>
+        <v>31878739</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 19 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -1,652 千股)</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-1456004</v>
+        <v>-348803</v>
       </c>
       <c r="D32" t="n">
-        <v>-1496195</v>
+        <v>-13595837</v>
       </c>
       <c r="E32" t="n">
-        <v>-1270466</v>
+        <v>3018222</v>
       </c>
       <c r="F32" t="n">
-        <v>-1514833</v>
+        <v>-11943903</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>寶雅*</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -5,790 千股)</t>
+          <t>📉 20d 巨變(減碼 -8 千股)</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-3056869</v>
+        <v>-89482</v>
       </c>
       <c r="D33" t="n">
-        <v>31878739</v>
+        <v>155689</v>
       </c>
       <c r="E33" t="n">
-        <v>3200128</v>
+        <v>-144598</v>
       </c>
       <c r="F33" t="n">
-        <v>37669057</v>
+        <v>163447</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>大統益</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,758 千股)</t>
+          <t>📈 20d 巨變(加碼 83 千股)</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3018222</v>
+        <v>489208</v>
       </c>
       <c r="D34" t="n">
-        <v>-11943903</v>
+        <v>589568</v>
       </c>
       <c r="E34" t="n">
-        <v>4101197</v>
+        <v>260208</v>
       </c>
       <c r="F34" t="n">
-        <v>-13701406</v>
+        <v>506790</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>豐藝</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -108 千股)</t>
+          <t>📈 20d 巨變(加碼 28 千股)</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-144598</v>
+        <v>-17879</v>
       </c>
       <c r="D35" t="n">
-        <v>163447</v>
+        <v>-429241</v>
       </c>
       <c r="E35" t="n">
-        <v>-119118</v>
+        <v>-58173</v>
       </c>
       <c r="F35" t="n">
-        <v>271407</v>
+        <v>-457554</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>智冠</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -9 千股)</t>
+          <t>📈 20d 巨變(加碼 5 千股)</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-58173</v>
+        <v>6000</v>
       </c>
       <c r="D36" t="n">
-        <v>-457554</v>
+        <v>59000</v>
       </c>
       <c r="E36" t="n">
-        <v>-71173</v>
+        <v>9000</v>
       </c>
       <c r="F36" t="n">
-        <v>-448616</v>
+        <v>54000</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>方土霖</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 48 千股)</t>
+          <t>📉 20d 巨變(減碼 -82 千股)</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>260208</v>
+        <v>-87213</v>
       </c>
       <c r="D37" t="n">
-        <v>506790</v>
+        <v>-889499</v>
       </c>
       <c r="E37" t="n">
-        <v>184014</v>
+        <v>-74218</v>
       </c>
       <c r="F37" t="n">
-        <v>458790</v>
+        <v>-807090</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>穎崴</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -172 千股)</t>
+          <t>📉 20d 巨變(減碼 -100 千股)</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-74218</v>
+        <v>-88850</v>
       </c>
       <c r="D38" t="n">
-        <v>-807090</v>
+        <v>-102776</v>
       </c>
       <c r="E38" t="n">
-        <v>-318607</v>
+        <v>-75850</v>
       </c>
       <c r="F38" t="n">
-        <v>-635129</v>
+        <v>-3197</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>八方雲集</t>
         </is>
       </c>
     </row>
@@ -6872,20 +6872,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -25 千股)</t>
+          <t>📉 20d 巨變(減碼 -6 千股)</t>
         </is>
       </c>
       <c r="C39" t="n">
+        <v>-33534</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-229121</v>
+      </c>
+      <c r="E39" t="n">
         <v>-124872</v>
       </c>
-      <c r="D39" t="n">
+      <c r="F39" t="n">
         <v>-223418</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-182865</v>
-      </c>
-      <c r="F39" t="n">
-        <v>-198674</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -6896,435 +6896,435 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -216 千股)</t>
+          <t>📉 20d 巨變(減碼 -7,813 千股)</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-75850</v>
+        <v>10210053</v>
       </c>
       <c r="D40" t="n">
-        <v>-3197</v>
+        <v>62041285</v>
       </c>
       <c r="E40" t="n">
-        <v>-67950</v>
+        <v>10963481</v>
       </c>
       <c r="F40" t="n">
-        <v>212461</v>
+        <v>69854759</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -16,398 千股)</t>
+          <t>📉 20d 巨變(減碼 -42 千股)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>10963481</v>
+        <v>-233072</v>
       </c>
       <c r="D41" t="n">
-        <v>69854759</v>
+        <v>-1290405</v>
       </c>
       <c r="E41" t="n">
-        <v>11959992</v>
+        <v>-208000</v>
       </c>
       <c r="F41" t="n">
-        <v>86252968</v>
+        <v>-1248333</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>聯合</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -99 千股)</t>
+          <t>📉 20d 巨變(減碼 -980 千股)</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-208000</v>
+        <v>394545</v>
       </c>
       <c r="D42" t="n">
-        <v>-1248333</v>
+        <v>3858187</v>
       </c>
       <c r="E42" t="n">
-        <v>-324000</v>
+        <v>408831</v>
       </c>
       <c r="F42" t="n">
-        <v>-1149333</v>
+        <v>4837820</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,105 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 175 千股)</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>408831</v>
+        <v>142063</v>
       </c>
       <c r="D43" t="n">
-        <v>4837820</v>
+        <v>-718735</v>
       </c>
       <c r="E43" t="n">
-        <v>1067236</v>
+        <v>-367938</v>
       </c>
       <c r="F43" t="n">
-        <v>6942447</v>
+        <v>-893664</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>亞力</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -203 千股)</t>
+          <t>📈 20d 巨變(加碼 13 千股)</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-367938</v>
+        <v>-198901</v>
       </c>
       <c r="D44" t="n">
-        <v>-893664</v>
+        <v>56007</v>
       </c>
       <c r="E44" t="n">
-        <v>257201</v>
+        <v>-288588</v>
       </c>
       <c r="F44" t="n">
-        <v>-690754</v>
+        <v>43148</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>大綜</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 68 千股)</t>
+          <t>📈 20d 巨變(加碼 1,448 千股)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>73382</v>
+        <v>1969542</v>
       </c>
       <c r="D45" t="n">
-        <v>-231237</v>
+        <v>3358603</v>
       </c>
       <c r="E45" t="n">
-        <v>251855</v>
+        <v>1072224</v>
       </c>
       <c r="F45" t="n">
-        <v>-298921</v>
+        <v>1910895</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>台燿</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -158 千股)</t>
+          <t>📈 20d 巨變(加碼 111 千股)</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-288588</v>
+        <v>93482</v>
       </c>
       <c r="D46" t="n">
-        <v>43148</v>
+        <v>-119909</v>
       </c>
       <c r="E46" t="n">
-        <v>-37854</v>
+        <v>73382</v>
       </c>
       <c r="F46" t="n">
-        <v>201507</v>
+        <v>-231237</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>漢科</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 744 千股)</t>
+          <t>📈 20d 巨變(加碼 22 千股)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1072224</v>
+        <v>2870651</v>
       </c>
       <c r="D47" t="n">
-        <v>1910895</v>
+        <v>4419187</v>
       </c>
       <c r="E47" t="n">
-        <v>2802843</v>
+        <v>3365468</v>
       </c>
       <c r="F47" t="n">
-        <v>1167165</v>
+        <v>4397470</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>立隆電</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -37 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,974 千股)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3365468</v>
+        <v>-6150088</v>
       </c>
       <c r="D48" t="n">
-        <v>4397470</v>
+        <v>702689</v>
       </c>
       <c r="E48" t="n">
-        <v>3203931</v>
+        <v>-7219533</v>
       </c>
       <c r="F48" t="n">
-        <v>4434632</v>
+        <v>2676611</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 374 千股)</t>
+          <t>📉 20d 巨變(減碼 -753 千股)</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-7219533</v>
+        <v>-1419061</v>
       </c>
       <c r="D49" t="n">
-        <v>2676611</v>
+        <v>-106456</v>
       </c>
       <c r="E49" t="n">
-        <v>-7457376</v>
+        <v>-2514008</v>
       </c>
       <c r="F49" t="n">
-        <v>2302769</v>
+        <v>646185</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>玉晶光</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 480 千股)</t>
+          <t>📉 20d 巨變(減碼 -449 千股)</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-2514008</v>
+        <v>-2654576</v>
       </c>
       <c r="D50" t="n">
-        <v>646185</v>
+        <v>-3310973</v>
       </c>
       <c r="E50" t="n">
-        <v>-3355756</v>
+        <v>-2214807</v>
       </c>
       <c r="F50" t="n">
-        <v>166137</v>
+        <v>-2861924</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>世芯-KY</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 125 千股)</t>
+          <t>📈 20d 巨變(加碼 2,808 千股)</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-2214807</v>
+        <v>-11012367</v>
       </c>
       <c r="D51" t="n">
-        <v>-2861924</v>
+        <v>-19390009</v>
       </c>
       <c r="E51" t="n">
-        <v>-2299614</v>
+        <v>-10907438</v>
       </c>
       <c r="F51" t="n">
-        <v>-2987077</v>
+        <v>-22197565</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,975 千股)</t>
+          <t>📉 20d 巨變(減碼 -25,969 千股)</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-10907438</v>
+        <v>-21478390</v>
       </c>
       <c r="D52" t="n">
-        <v>-22197565</v>
+        <v>-18020476</v>
       </c>
       <c r="E52" t="n">
-        <v>-7896331</v>
+        <v>-24297060</v>
       </c>
       <c r="F52" t="n">
-        <v>-19223011</v>
+        <v>7948555</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 20,255 千股)</t>
+          <t>📈 20d 巨變(加碼 1,393 千股)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-24297060</v>
+        <v>-8087993</v>
       </c>
       <c r="D53" t="n">
-        <v>7948555</v>
+        <v>27410116</v>
       </c>
       <c r="E53" t="n">
-        <v>-35204437</v>
+        <v>-5780922</v>
       </c>
       <c r="F53" t="n">
-        <v>-12306613</v>
+        <v>26017364</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 283 千股)</t>
+          <t>📉 20d 巨變(減碼 -337 千股)</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-5780922</v>
+        <v>-1264152</v>
       </c>
       <c r="D54" t="n">
-        <v>26017364</v>
+        <v>941808</v>
       </c>
       <c r="E54" t="n">
-        <v>419818</v>
+        <v>-764534</v>
       </c>
       <c r="F54" t="n">
-        <v>25734731</v>
+        <v>1278873</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>士電</t>
         </is>
       </c>
     </row>
@@ -7336,20 +7336,20 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -600 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 237 千股)</t>
         </is>
       </c>
       <c r="C55" t="n">
+        <v>173437</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2303928</v>
+      </c>
+      <c r="E55" t="n">
         <v>-1138518</v>
       </c>
-      <c r="D55" t="n">
+      <c r="F55" t="n">
         <v>2067082</v>
-      </c>
-      <c r="E55" t="n">
-        <v>-1223194</v>
-      </c>
-      <c r="F55" t="n">
-        <v>2666974</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -7360,29 +7360,29 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -289 千股)</t>
+          <t>📈 20d 巨變(加碼 578 千股)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-764534</v>
+        <v>-548154</v>
       </c>
       <c r="D56" t="n">
-        <v>1278873</v>
+        <v>-1816506</v>
       </c>
       <c r="E56" t="n">
-        <v>-4564</v>
+        <v>-763977</v>
       </c>
       <c r="F56" t="n">
-        <v>1567586</v>
+        <v>-2394805</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>鉅祥</t>
         </is>
       </c>
     </row>
@@ -7394,20 +7394,20 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -59 千股)</t>
+          <t>📉 20d 巨變(減碼 -74 千股)</t>
         </is>
       </c>
       <c r="C57" t="n">
+        <v>-65025</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-52636</v>
+      </c>
+      <c r="E57" t="n">
         <v>-40915</v>
       </c>
-      <c r="D57" t="n">
+      <c r="F57" t="n">
         <v>21085</v>
-      </c>
-      <c r="E57" t="n">
-        <v>-49231</v>
-      </c>
-      <c r="F57" t="n">
-        <v>79725</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -7418,58 +7418,58 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 647 千股)</t>
+          <t>📉 20d 巨變(減碼 -47 千股)</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-763977</v>
+        <v>18755</v>
       </c>
       <c r="D58" t="n">
-        <v>-2394805</v>
+        <v>349108</v>
       </c>
       <c r="E58" t="n">
-        <v>-436252</v>
+        <v>16874</v>
       </c>
       <c r="F58" t="n">
-        <v>-3041455</v>
+        <v>395694</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>普萊德</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -8 千股)</t>
+          <t>📈 20d 巨變(加碼 247 千股)</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>16874</v>
+        <v>-196561</v>
       </c>
       <c r="D59" t="n">
-        <v>395694</v>
+        <v>-1525136</v>
       </c>
       <c r="E59" t="n">
-        <v>-44998</v>
+        <v>-398351</v>
       </c>
       <c r="F59" t="n">
-        <v>403653</v>
+        <v>-1771926</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>勝一</t>
         </is>
       </c>
     </row>
@@ -7481,20 +7481,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -104 千股)</t>
+          <t>📉 20d 巨變(減碼 -219 千股)</t>
         </is>
       </c>
       <c r="C60" t="n">
+        <v>-450270</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-744778</v>
+      </c>
+      <c r="E60" t="n">
         <v>-240446</v>
       </c>
-      <c r="D60" t="n">
+      <c r="F60" t="n">
         <v>-525650</v>
-      </c>
-      <c r="E60" t="n">
-        <v>-51551</v>
-      </c>
-      <c r="F60" t="n">
-        <v>-421957</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -7505,29 +7505,29 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 14 千股)</t>
+          <t>📈 20d 巨變(加碼 245 千股)</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-398351</v>
+        <v>783680</v>
       </c>
       <c r="D61" t="n">
-        <v>-1771926</v>
+        <v>642442</v>
       </c>
       <c r="E61" t="n">
-        <v>-279283</v>
+        <v>449305</v>
       </c>
       <c r="F61" t="n">
-        <v>-1785436</v>
+        <v>397599</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>祥碩</t>
         </is>
       </c>
     </row>
@@ -7539,20 +7539,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -95 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -392 千股)</t>
         </is>
       </c>
       <c r="C62" t="n">
+        <v>62768</v>
+      </c>
+      <c r="D62" t="n">
+        <v>-1978692</v>
+      </c>
+      <c r="E62" t="n">
         <v>-242464</v>
       </c>
-      <c r="D62" t="n">
+      <c r="F62" t="n">
         <v>-1586899</v>
-      </c>
-      <c r="E62" t="n">
-        <v>-245612</v>
-      </c>
-      <c r="F62" t="n">
-        <v>-1492337</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -7563,174 +7563,174 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 295 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -148 千股)</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>449305</v>
+        <v>-224950</v>
       </c>
       <c r="D63" t="n">
-        <v>397599</v>
+        <v>-2840237</v>
       </c>
       <c r="E63" t="n">
-        <v>-170317</v>
+        <v>92408</v>
       </c>
       <c r="F63" t="n">
-        <v>102700</v>
+        <v>-2692420</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 308 千股)</t>
+          <t>📉 20d 巨變(減碼 -12 千股)</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>92408</v>
+        <v>840037</v>
       </c>
       <c r="D64" t="n">
-        <v>-2692420</v>
+        <v>-3673287</v>
       </c>
       <c r="E64" t="n">
-        <v>-1134938</v>
+        <v>691770</v>
       </c>
       <c r="F64" t="n">
-        <v>-3000021</v>
+        <v>-3661689</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>華星光</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 89 千股)</t>
+          <t>📉 20d 巨變(減碼 -854 千股)</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>691770</v>
+        <v>-4480149</v>
       </c>
       <c r="D65" t="n">
-        <v>-3661689</v>
+        <v>-1599352</v>
       </c>
       <c r="E65" t="n">
-        <v>-1390357</v>
+        <v>-1769102</v>
       </c>
       <c r="F65" t="n">
-        <v>-3750193</v>
+        <v>-745763</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -740 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,184 千股)</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-1623268</v>
+        <v>-969316</v>
       </c>
       <c r="D66" t="n">
-        <v>-973985</v>
+        <v>-1303812</v>
       </c>
       <c r="E66" t="n">
-        <v>-688347</v>
+        <v>-952719</v>
       </c>
       <c r="F66" t="n">
-        <v>-233602</v>
+        <v>-119917</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>宇瞻</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 161 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 6,340 千股)</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-952719</v>
+        <v>6120524</v>
       </c>
       <c r="D67" t="n">
-        <v>-119917</v>
+        <v>31972283</v>
       </c>
       <c r="E67" t="n">
-        <v>-1598741</v>
+        <v>-176747</v>
       </c>
       <c r="F67" t="n">
-        <v>-280642</v>
+        <v>25631958</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,634 千股)</t>
+          <t>📉 20d 巨變(減碼 -576 千股)</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-1769102</v>
+        <v>-2150375</v>
       </c>
       <c r="D68" t="n">
-        <v>-745763</v>
+        <v>-1549813</v>
       </c>
       <c r="E68" t="n">
-        <v>-2969338</v>
+        <v>-1623268</v>
       </c>
       <c r="F68" t="n">
-        <v>-3379534</v>
+        <v>-973985</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>聯亞</t>
         </is>
       </c>
     </row>
@@ -7742,20 +7742,20 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -6,640 千股)</t>
+          <t>📈 20d 巨變(加碼 14,133 千股)</t>
         </is>
       </c>
       <c r="C69" t="n">
+        <v>-12324778</v>
+      </c>
+      <c r="D69" t="n">
+        <v>-100782356</v>
+      </c>
+      <c r="E69" t="n">
         <v>-54905250</v>
       </c>
-      <c r="D69" t="n">
+      <c r="F69" t="n">
         <v>-114915491</v>
-      </c>
-      <c r="E69" t="n">
-        <v>-38830336</v>
-      </c>
-      <c r="F69" t="n">
-        <v>-108275409</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -7771,20 +7771,20 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 311 千股)</t>
+          <t>📈 20d 巨變(加碼 3,506 千股)</t>
         </is>
       </c>
       <c r="C70" t="n">
+        <v>4076684</v>
+      </c>
+      <c r="D70" t="n">
+        <v>3253326</v>
+      </c>
+      <c r="E70" t="n">
         <v>3092866</v>
       </c>
-      <c r="D70" t="n">
+      <c r="F70" t="n">
         <v>-252814</v>
-      </c>
-      <c r="E70" t="n">
-        <v>3388449</v>
-      </c>
-      <c r="F70" t="n">
-        <v>-563808</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -7795,174 +7795,174 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -3,385 千股)</t>
+          <t>📈 20d 巨變(加碼 7,774 千股)</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-176747</v>
+        <v>-4067225</v>
       </c>
       <c r="D71" t="n">
-        <v>25631958</v>
+        <v>-15352223</v>
       </c>
       <c r="E71" t="n">
-        <v>13079639</v>
+        <v>-4802590</v>
       </c>
       <c r="F71" t="n">
-        <v>29016789</v>
+        <v>-23125948</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -343 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -6 千股)</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-4802590</v>
+        <v>23945</v>
       </c>
       <c r="D72" t="n">
-        <v>-23125948</v>
+        <v>-4634763</v>
       </c>
       <c r="E72" t="n">
-        <v>-1867365</v>
+        <v>-3969403</v>
       </c>
       <c r="F72" t="n">
-        <v>-22783426</v>
+        <v>-4629221</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -59 千股)</t>
+          <t>🟢 外資 5d 翻綠</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-140115</v>
+        <v>25049</v>
       </c>
       <c r="D73" t="n">
-        <v>-413109</v>
+        <v>761857</v>
       </c>
       <c r="E73" t="n">
-        <v>-104949</v>
+        <v>-177232</v>
       </c>
       <c r="F73" t="n">
-        <v>-354477</v>
+        <v>760966</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>億泰</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,316 千股)</t>
+          <t>📉 20d 巨變(減碼 -40 千股)</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-3969403</v>
+        <v>-55689</v>
       </c>
       <c r="D74" t="n">
-        <v>-4629221</v>
+        <v>-453604</v>
       </c>
       <c r="E74" t="n">
-        <v>-4501754</v>
+        <v>-140115</v>
       </c>
       <c r="F74" t="n">
-        <v>-5944830</v>
+        <v>-413109</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>德昌</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 9 千股)</t>
+          <t>📈 20d 巨變(加碼 13 千股)</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-177232</v>
+        <v>38000</v>
       </c>
       <c r="D75" t="n">
-        <v>760966</v>
+        <v>-48550</v>
       </c>
       <c r="E75" t="n">
-        <v>354302</v>
+        <v>34000</v>
       </c>
       <c r="F75" t="n">
-        <v>752006</v>
+        <v>-61550</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>友輝</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 6 千股)</t>
+          <t>📉 20d 巨變(減碼 -132 千股)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>34000</v>
+        <v>-842786</v>
       </c>
       <c r="D76" t="n">
-        <v>-61550</v>
+        <v>-3067772</v>
       </c>
       <c r="E76" t="n">
-        <v>5000</v>
+        <v>-814586</v>
       </c>
       <c r="F76" t="n">
-        <v>-67550</v>
+        <v>-2935709</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>原相</t>
         </is>
       </c>
     </row>
@@ -7974,20 +7974,20 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 266 千股)</t>
+          <t>📈 20d 巨變(加碼 272 千股)</t>
         </is>
       </c>
       <c r="C77" t="n">
+        <v>-557950</v>
+      </c>
+      <c r="D77" t="n">
+        <v>-8068145</v>
+      </c>
+      <c r="E77" t="n">
         <v>-1205919</v>
       </c>
-      <c r="D77" t="n">
+      <c r="F77" t="n">
         <v>-8340490</v>
-      </c>
-      <c r="E77" t="n">
-        <v>-1176757</v>
-      </c>
-      <c r="F77" t="n">
-        <v>-8606147</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -7998,58 +7998,58 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -77 千股)</t>
+          <t>📈 20d 巨變(加碼 1,128 千股)</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-814586</v>
+        <v>-1201435</v>
       </c>
       <c r="D78" t="n">
-        <v>-2935709</v>
+        <v>344541</v>
       </c>
       <c r="E78" t="n">
-        <v>-902167</v>
+        <v>-2742460</v>
       </c>
       <c r="F78" t="n">
-        <v>-2858946</v>
+        <v>-783949</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,342 千股)</t>
+          <t>📈 20d 巨變(加碼 464 千股)</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-2742460</v>
+        <v>-3219142</v>
       </c>
       <c r="D79" t="n">
-        <v>-783949</v>
+        <v>-7531248</v>
       </c>
       <c r="E79" t="n">
-        <v>-1228909</v>
+        <v>-10100528</v>
       </c>
       <c r="F79" t="n">
-        <v>557944</v>
+        <v>-7995207</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
@@ -8061,20 +8061,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 31 千股)</t>
+          <t>📉 20d 巨變(減碼 -93 千股)</t>
         </is>
       </c>
       <c r="C80" t="n">
+        <v>702002</v>
+      </c>
+      <c r="D80" t="n">
+        <v>-1558021</v>
+      </c>
+      <c r="E80" t="n">
         <v>767117</v>
       </c>
-      <c r="D80" t="n">
+      <c r="F80" t="n">
         <v>-1464671</v>
-      </c>
-      <c r="E80" t="n">
-        <v>801511</v>
-      </c>
-      <c r="F80" t="n">
-        <v>-1496023</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -8090,20 +8090,20 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 8,376 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 13,122 千股)</t>
         </is>
       </c>
       <c r="C81" t="n">
+        <v>1227270</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1125790</v>
+      </c>
+      <c r="E81" t="n">
         <v>-11047969</v>
       </c>
-      <c r="D81" t="n">
+      <c r="F81" t="n">
         <v>-11995730</v>
-      </c>
-      <c r="E81" t="n">
-        <v>-6226405</v>
-      </c>
-      <c r="F81" t="n">
-        <v>-20371886</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -8114,406 +8114,406 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,883 千股)</t>
+          <t>📉 20d 巨變(減碼 -12 千股)</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-10100528</v>
+        <v>267000</v>
       </c>
       <c r="D82" t="n">
-        <v>-7995207</v>
+        <v>504404</v>
       </c>
       <c r="E82" t="n">
-        <v>-1386713</v>
+        <v>356000</v>
       </c>
       <c r="F82" t="n">
-        <v>-5111730</v>
+        <v>516524</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>東科-KY</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 210 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -60 千股)</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-169583</v>
+        <v>2000</v>
       </c>
       <c r="D83" t="n">
-        <v>-876233</v>
+        <v>232009</v>
       </c>
       <c r="E83" t="n">
-        <v>-336446</v>
+        <v>-84000</v>
       </c>
       <c r="F83" t="n">
-        <v>-1086486</v>
+        <v>292009</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -29 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 254 千股)</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>356000</v>
+        <v>128107</v>
       </c>
       <c r="D84" t="n">
-        <v>516524</v>
+        <v>-622118</v>
       </c>
       <c r="E84" t="n">
-        <v>515624</v>
+        <v>-169583</v>
       </c>
       <c r="F84" t="n">
-        <v>545524</v>
+        <v>-876233</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 30 千股)</t>
+          <t>📈 20d 巨變(加碼 2,068 千股)</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-84000</v>
+        <v>6553274</v>
       </c>
       <c r="D85" t="n">
-        <v>292009</v>
+        <v>6489230</v>
       </c>
       <c r="E85" t="n">
-        <v>-125000</v>
+        <v>6624646</v>
       </c>
       <c r="F85" t="n">
-        <v>262009</v>
+        <v>4421604</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 5,218 千股)</t>
+          <t>📈 20d 巨變(加碼 949 千股)</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>6624646</v>
+        <v>-920644</v>
       </c>
       <c r="D86" t="n">
-        <v>4421604</v>
+        <v>-10612251</v>
       </c>
       <c r="E86" t="n">
-        <v>2098171</v>
+        <v>-2503223</v>
       </c>
       <c r="F86" t="n">
-        <v>-796018</v>
+        <v>-11561252</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>宏捷科</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 6,978 千股)</t>
+          <t>📈 20d 巨變(加碼 1,984 千股)</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>43395130</v>
+        <v>3521318</v>
       </c>
       <c r="D87" t="n">
-        <v>61116687</v>
+        <v>3803322</v>
       </c>
       <c r="E87" t="n">
-        <v>42107380</v>
+        <v>2306190</v>
       </c>
       <c r="F87" t="n">
-        <v>54138286</v>
+        <v>1819068</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>研華</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 902 千股)</t>
+          <t>📈 20d 巨變(加碼 9,778 千股)</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2306190</v>
+        <v>49524280</v>
       </c>
       <c r="D88" t="n">
-        <v>1819068</v>
+        <v>70894993</v>
       </c>
       <c r="E88" t="n">
-        <v>1889863</v>
+        <v>43395130</v>
       </c>
       <c r="F88" t="n">
-        <v>917111</v>
+        <v>61116687</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 918 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -101 千股)</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-2503223</v>
+        <v>10686</v>
       </c>
       <c r="D89" t="n">
-        <v>-11561252</v>
+        <v>-185230</v>
       </c>
       <c r="E89" t="n">
-        <v>-1437432</v>
+        <v>-183974</v>
       </c>
       <c r="F89" t="n">
-        <v>-12479349</v>
+        <v>-84355</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>中保科</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -125 千股)</t>
+          <t>📉 20d 巨變(減碼 -8 千股)</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-183974</v>
+        <v>-125920</v>
       </c>
       <c r="D90" t="n">
-        <v>-84355</v>
+        <v>-126768</v>
       </c>
       <c r="E90" t="n">
-        <v>-183155</v>
+        <v>-123821</v>
       </c>
       <c r="F90" t="n">
-        <v>40309</v>
+        <v>-118669</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>竹陞科技</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -100 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 788 千股)</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-123821</v>
+        <v>39169</v>
       </c>
       <c r="D91" t="n">
-        <v>-118669</v>
+        <v>-6243970</v>
       </c>
       <c r="E91" t="n">
-        <v>-73183</v>
+        <v>-616225</v>
       </c>
       <c r="F91" t="n">
-        <v>-18842</v>
+        <v>-7031911</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 926 千股)</t>
+          <t>📈 20d 巨變(加碼 14 千股)</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-616225</v>
+        <v>35353</v>
       </c>
       <c r="D92" t="n">
-        <v>-7031911</v>
+        <v>69875</v>
       </c>
       <c r="E92" t="n">
-        <v>-457192</v>
+        <v>14345</v>
       </c>
       <c r="F92" t="n">
-        <v>-7958076</v>
+        <v>55865</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>安碁資訊</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,750 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 51 千股)</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3420405</v>
+        <v>5070</v>
       </c>
       <c r="D93" t="n">
-        <v>19386872</v>
+        <v>-59199</v>
       </c>
       <c r="E93" t="n">
-        <v>4151571</v>
+        <v>-89930</v>
       </c>
       <c r="F93" t="n">
-        <v>21136419</v>
+        <v>-109975</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>六方科-KY</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 23,115 千股)</t>
+          <t>📈 20d 巨變(加碼 560 千股)</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-64654213</v>
+        <v>290258</v>
       </c>
       <c r="D94" t="n">
-        <v>12948485</v>
+        <v>6054546</v>
       </c>
       <c r="E94" t="n">
-        <v>-141118626</v>
+        <v>1706793</v>
       </c>
       <c r="F94" t="n">
-        <v>-10166434</v>
+        <v>5494945</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 1,213 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,226 千股)</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1706793</v>
+        <v>3556484</v>
       </c>
       <c r="D95" t="n">
-        <v>5494945</v>
+        <v>18161267</v>
       </c>
       <c r="E95" t="n">
-        <v>-47834</v>
+        <v>3420405</v>
       </c>
       <c r="F95" t="n">
-        <v>4281687</v>
+        <v>19386872</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
@@ -8525,20 +8525,20 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -843 千股)</t>
+          <t>📉 20d 巨變(減碼 -54 千股)</t>
         </is>
       </c>
       <c r="C96" t="n">
+        <v>-835460</v>
+      </c>
+      <c r="D96" t="n">
+        <v>-161986</v>
+      </c>
+      <c r="E96" t="n">
         <v>-283090</v>
       </c>
-      <c r="D96" t="n">
+      <c r="F96" t="n">
         <v>-107715</v>
-      </c>
-      <c r="E96" t="n">
-        <v>-263181</v>
-      </c>
-      <c r="F96" t="n">
-        <v>735605</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -8549,87 +8549,87 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,944 千股)</t>
+          <t>📉 20d 巨變(減碼 -33,382 千股)</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-4866091</v>
+        <v>-69311123</v>
       </c>
       <c r="D97" t="n">
-        <v>-13067663</v>
+        <v>-20433393</v>
       </c>
       <c r="E97" t="n">
-        <v>-2149767</v>
+        <v>-64654213</v>
       </c>
       <c r="F97" t="n">
-        <v>-10124082</v>
+        <v>12948485</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 815 千股)</t>
+          <t>📉 20d 巨變(減碼 -84 千股)</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1671012</v>
+        <v>-98233</v>
       </c>
       <c r="D98" t="n">
-        <v>-6796663</v>
+        <v>167885</v>
       </c>
       <c r="E98" t="n">
-        <v>919078</v>
+        <v>-24347</v>
       </c>
       <c r="F98" t="n">
-        <v>-7611331</v>
+        <v>251782</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>信驊</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 6 千股)</t>
+          <t>📈 20d 巨變(加碼 172 千股)</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-24347</v>
+        <v>-4314230</v>
       </c>
       <c r="D99" t="n">
-        <v>251782</v>
+        <v>-12895569</v>
       </c>
       <c r="E99" t="n">
-        <v>58845</v>
+        <v>-4866091</v>
       </c>
       <c r="F99" t="n">
-        <v>245467</v>
+        <v>-13067663</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>緯穎</t>
         </is>
       </c>
     </row>
@@ -8641,20 +8641,20 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 147 千股)</t>
+          <t>📈 20d 巨變(加碼 10 千股)</t>
         </is>
       </c>
       <c r="C100" t="n">
+        <v>-30968</v>
+      </c>
+      <c r="D100" t="n">
+        <v>-3404039</v>
+      </c>
+      <c r="E100" t="n">
         <v>-24336</v>
       </c>
-      <c r="D100" t="n">
+      <c r="F100" t="n">
         <v>-3414486</v>
-      </c>
-      <c r="E100" t="n">
-        <v>282495</v>
-      </c>
-      <c r="F100" t="n">
-        <v>-3561387</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -8665,27 +8665,56 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -2,730 千股)</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>-1360213</v>
+      </c>
+      <c r="D101" t="n">
+        <v>-9526438</v>
+      </c>
+      <c r="E101" t="n">
+        <v>1671012</v>
+      </c>
+      <c r="F101" t="n">
+        <v>-6796663</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
           <t>6187</t>
         </is>
       </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 177 千股)</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 187 千股)</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>18035</v>
+      </c>
+      <c r="D102" t="n">
+        <v>-1242501</v>
+      </c>
+      <c r="E102" t="n">
         <v>329662</v>
       </c>
-      <c r="D101" t="n">
+      <c r="F102" t="n">
         <v>-1429625</v>
       </c>
-      <c r="E101" t="n">
-        <v>-105293</v>
-      </c>
-      <c r="F101" t="n">
-        <v>-1606778</v>
-      </c>
-      <c r="G101" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t>萬潤</t>
         </is>

--- a/data/台股_外資雷達.xlsx
+++ b/data/台股_外資雷達.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>49524</v>
+        <v>47016</v>
       </c>
       <c r="D2" t="n">
-        <v>70895</v>
+        <v>78969</v>
       </c>
       <c r="E2" t="n">
-        <v>140499</v>
+        <v>164776</v>
       </c>
       <c r="F2" t="n">
-        <v>-724</v>
+        <v>-1970</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>-1143</v>
       </c>
       <c r="H2" t="n">
-        <v>-39</v>
+        <v>329</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="M2" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="3">
@@ -547,22 +547,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10210</v>
+        <v>7030</v>
       </c>
       <c r="D3" t="n">
-        <v>62041</v>
+        <v>55705</v>
       </c>
       <c r="E3" t="n">
-        <v>200298</v>
+        <v>211228</v>
       </c>
       <c r="F3" t="n">
-        <v>378</v>
+        <v>2467</v>
       </c>
       <c r="G3" t="n">
-        <v>4463</v>
+        <v>6579</v>
       </c>
       <c r="H3" t="n">
-        <v>-3181</v>
+        <v>-3071</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -589,31 +589,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6121</v>
+        <v>7179</v>
       </c>
       <c r="D4" t="n">
-        <v>31972</v>
+        <v>32209</v>
       </c>
       <c r="E4" t="n">
-        <v>-15675</v>
+        <v>-4699</v>
       </c>
       <c r="F4" t="n">
-        <v>8462</v>
+        <v>-2174</v>
       </c>
       <c r="G4" t="n">
-        <v>14104</v>
+        <v>-11153</v>
       </c>
       <c r="H4" t="n">
-        <v>1016</v>
+        <v>2053</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -626,45 +626,45 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速*</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4349</v>
+        <v>-671</v>
       </c>
       <c r="D5" t="n">
-        <v>28128</v>
+        <v>26140</v>
       </c>
       <c r="E5" t="n">
-        <v>574546</v>
+        <v>-11669</v>
       </c>
       <c r="F5" t="n">
-        <v>6970</v>
+        <v>12620</v>
       </c>
       <c r="G5" t="n">
-        <v>20000</v>
+        <v>19227</v>
       </c>
       <c r="H5" t="n">
-        <v>-2123</v>
+        <v>1406</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -673,15 +673,15 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M5" t="n">
@@ -691,31 +691,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-8088</v>
+        <v>3046</v>
       </c>
       <c r="D6" t="n">
-        <v>27410</v>
+        <v>18204</v>
       </c>
       <c r="E6" t="n">
-        <v>-18375</v>
+        <v>105740</v>
       </c>
       <c r="F6" t="n">
-        <v>-934</v>
+        <v>-278</v>
       </c>
       <c r="G6" t="n">
-        <v>-11837</v>
+        <v>-2329</v>
       </c>
       <c r="H6" t="n">
-        <v>1188</v>
+        <v>-628</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -728,45 +728,45 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>🐌 龜速*</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3556</v>
+        <v>573</v>
       </c>
       <c r="D7" t="n">
-        <v>18161</v>
+        <v>15830</v>
       </c>
       <c r="E7" t="n">
-        <v>89038</v>
+        <v>22825</v>
       </c>
       <c r="F7" t="n">
-        <v>601</v>
+        <v>-71</v>
       </c>
       <c r="G7" t="n">
-        <v>-1547</v>
+        <v>39</v>
       </c>
       <c r="H7" t="n">
-        <v>-847</v>
+        <v>227</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -775,11 +775,11 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -787,54 +787,54 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>591</v>
+        <v>3918</v>
       </c>
       <c r="D8" t="n">
-        <v>15221</v>
+        <v>9216</v>
       </c>
       <c r="E8" t="n">
-        <v>22631</v>
+        <v>7933</v>
       </c>
       <c r="F8" t="n">
-        <v>-56</v>
+        <v>-479</v>
       </c>
       <c r="G8" t="n">
-        <v>57</v>
+        <v>1676</v>
       </c>
       <c r="H8" t="n">
-        <v>80</v>
+        <v>1445</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>🚀 大買</t>
+          <t>🟢 加碼</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -844,31 +844,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-1530</v>
+        <v>8072</v>
       </c>
       <c r="D9" t="n">
-        <v>8380</v>
+        <v>8886</v>
       </c>
       <c r="E9" t="n">
-        <v>10593</v>
+        <v>-1744</v>
       </c>
       <c r="F9" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>903</v>
+        <v>-8</v>
       </c>
       <c r="H9" t="n">
-        <v>1094</v>
+        <v>668</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -877,49 +877,49 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6553</v>
+        <v>-1164</v>
       </c>
       <c r="D10" t="n">
-        <v>6489</v>
+        <v>8622</v>
       </c>
       <c r="E10" t="n">
-        <v>-4307</v>
+        <v>11507</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G10" t="n">
-        <v>-8</v>
+        <v>929</v>
       </c>
       <c r="H10" t="n">
-        <v>620</v>
+        <v>1178</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -928,49 +928,49 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C11" t="n">
+        <v>23857</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8180</v>
+      </c>
+      <c r="E11" t="n">
+        <v>90947</v>
+      </c>
+      <c r="F11" t="n">
         <v>290</v>
       </c>
-      <c r="D11" t="n">
-        <v>6055</v>
-      </c>
-      <c r="E11" t="n">
-        <v>6268</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-251</v>
-      </c>
       <c r="G11" t="n">
-        <v>1653</v>
+        <v>-5321</v>
       </c>
       <c r="H11" t="n">
-        <v>1271</v>
+        <v>-3333</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -979,49 +979,49 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>706</v>
+        <v>4641</v>
       </c>
       <c r="D12" t="n">
-        <v>5020</v>
+        <v>7419</v>
       </c>
       <c r="E12" t="n">
-        <v>24969</v>
+        <v>61096</v>
       </c>
       <c r="F12" t="n">
-        <v>427</v>
+        <v>-13760</v>
       </c>
       <c r="G12" t="n">
-        <v>-89</v>
+        <v>-33149</v>
       </c>
       <c r="H12" t="n">
-        <v>41</v>
+        <v>-2282</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1030,49 +1030,49 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2871</v>
+        <v>-15045</v>
       </c>
       <c r="D13" t="n">
-        <v>4419</v>
+        <v>5940</v>
       </c>
       <c r="E13" t="n">
-        <v>16208</v>
+        <v>551158</v>
       </c>
       <c r="F13" t="n">
-        <v>-2502</v>
+        <v>16024</v>
       </c>
       <c r="G13" t="n">
-        <v>-6157</v>
+        <v>29279</v>
       </c>
       <c r="H13" t="n">
-        <v>-54</v>
+        <v>-2052</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1081,11 +1081,11 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1093,37 +1093,37 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>395</v>
+        <v>1821</v>
       </c>
       <c r="D14" t="n">
-        <v>3858</v>
+        <v>5379</v>
       </c>
       <c r="E14" t="n">
-        <v>11733</v>
+        <v>602</v>
       </c>
       <c r="F14" t="n">
-        <v>732</v>
+        <v>-4685</v>
       </c>
       <c r="G14" t="n">
-        <v>-441</v>
+        <v>-15536</v>
       </c>
       <c r="H14" t="n">
-        <v>-103</v>
+        <v>964</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1132,49 +1132,49 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3521</v>
+        <v>329</v>
       </c>
       <c r="D15" t="n">
-        <v>3803</v>
+        <v>5248</v>
       </c>
       <c r="E15" t="n">
-        <v>1506</v>
+        <v>24396</v>
       </c>
       <c r="F15" t="n">
-        <v>-91</v>
+        <v>859</v>
       </c>
       <c r="G15" t="n">
-        <v>592</v>
+        <v>343</v>
       </c>
       <c r="H15" t="n">
-        <v>-137</v>
+        <v>82</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1183,49 +1183,49 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1970</v>
+        <v>2643</v>
       </c>
       <c r="D16" t="n">
-        <v>3359</v>
+        <v>5002</v>
       </c>
       <c r="E16" t="n">
-        <v>-926</v>
+        <v>14841</v>
       </c>
       <c r="F16" t="n">
-        <v>-5125</v>
+        <v>-2572</v>
       </c>
       <c r="G16" t="n">
-        <v>-14662</v>
+        <v>-6618</v>
       </c>
       <c r="H16" t="n">
-        <v>956</v>
+        <v>-45</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1238,45 +1238,45 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>4077</v>
+        <v>2674</v>
       </c>
       <c r="D17" t="n">
-        <v>3253</v>
+        <v>3809</v>
       </c>
       <c r="E17" t="n">
-        <v>-4545</v>
+        <v>1502</v>
       </c>
       <c r="F17" t="n">
-        <v>101</v>
+        <v>-162</v>
       </c>
       <c r="G17" t="n">
-        <v>2253</v>
+        <v>578</v>
       </c>
       <c r="H17" t="n">
-        <v>-339</v>
+        <v>-68</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1297,37 +1297,37 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>173</v>
+        <v>4440</v>
       </c>
       <c r="D18" t="n">
-        <v>2304</v>
+        <v>3610</v>
       </c>
       <c r="E18" t="n">
-        <v>11131</v>
+        <v>-2339</v>
       </c>
       <c r="F18" t="n">
-        <v>567</v>
+        <v>22</v>
       </c>
       <c r="G18" t="n">
-        <v>-11853</v>
+        <v>2246</v>
       </c>
       <c r="H18" t="n">
-        <v>-28</v>
+        <v>-213</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1336,49 +1336,49 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>970</v>
+        <v>943</v>
       </c>
       <c r="D19" t="n">
-        <v>2095</v>
+        <v>2907</v>
       </c>
       <c r="E19" t="n">
-        <v>233</v>
+        <v>6197</v>
       </c>
       <c r="F19" t="n">
-        <v>587</v>
+        <v>9</v>
       </c>
       <c r="G19" t="n">
-        <v>228</v>
+        <v>-359</v>
       </c>
       <c r="H19" t="n">
-        <v>-111</v>
+        <v>121</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1391,11 +1391,11 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M19" t="n">
@@ -1405,31 +1405,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>841</v>
+        <v>847</v>
       </c>
       <c r="D20" t="n">
-        <v>2087</v>
+        <v>2147</v>
       </c>
       <c r="E20" t="n">
-        <v>6052</v>
+        <v>11203</v>
       </c>
       <c r="F20" t="n">
-        <v>36</v>
+        <v>789</v>
       </c>
       <c r="G20" t="n">
-        <v>-353</v>
+        <v>-10799</v>
       </c>
       <c r="H20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1438,53 +1438,53 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-9</v>
+        <v>-721</v>
       </c>
       <c r="D21" t="n">
-        <v>1814</v>
+        <v>2084</v>
       </c>
       <c r="E21" t="n">
-        <v>-2052</v>
+        <v>149</v>
       </c>
       <c r="F21" t="n">
-        <v>82</v>
+        <v>676</v>
       </c>
       <c r="G21" t="n">
-        <v>-400</v>
+        <v>523</v>
       </c>
       <c r="H21" t="n">
-        <v>198</v>
+        <v>-80</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>🟡 中性</t>
+          <t>🟢 加碼</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1516,22 +1516,22 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>79</v>
+        <v>138</v>
       </c>
       <c r="D22" t="n">
-        <v>1381</v>
+        <v>1394</v>
       </c>
       <c r="E22" t="n">
-        <v>-290</v>
+        <v>-194</v>
       </c>
       <c r="F22" t="n">
-        <v>273</v>
+        <v>190</v>
       </c>
       <c r="G22" t="n">
-        <v>109</v>
+        <v>4</v>
       </c>
       <c r="H22" t="n">
-        <v>-57</v>
+        <v>-45</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1558,31 +1558,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1227</v>
+        <v>-319</v>
       </c>
       <c r="D23" t="n">
-        <v>1126</v>
+        <v>1325</v>
       </c>
       <c r="E23" t="n">
-        <v>75132</v>
+        <v>-2102</v>
       </c>
       <c r="F23" t="n">
-        <v>2509</v>
+        <v>78</v>
       </c>
       <c r="G23" t="n">
-        <v>5358</v>
+        <v>16</v>
       </c>
       <c r="H23" t="n">
-        <v>-2730</v>
+        <v>280</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1591,11 +1591,11 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1618,13 +1618,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>203</v>
+        <v>288</v>
       </c>
       <c r="D24" t="n">
-        <v>1027</v>
+        <v>1150</v>
       </c>
       <c r="E24" t="n">
-        <v>1883</v>
+        <v>2027</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-44</v>
+        <v>-33</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1660,31 +1660,31 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-1264</v>
+        <v>-48</v>
       </c>
       <c r="D25" t="n">
-        <v>942</v>
+        <v>1084</v>
       </c>
       <c r="E25" t="n">
-        <v>64</v>
+        <v>8171</v>
       </c>
       <c r="F25" t="n">
-        <v>21</v>
+        <v>-3</v>
       </c>
       <c r="G25" t="n">
-        <v>71</v>
+        <v>-19</v>
       </c>
       <c r="H25" t="n">
-        <v>13</v>
+        <v>133</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1693,49 +1693,49 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>116</v>
+        <v>1200</v>
       </c>
       <c r="D26" t="n">
-        <v>885</v>
+        <v>1034</v>
       </c>
       <c r="E26" t="n">
-        <v>4459</v>
+        <v>2637</v>
       </c>
       <c r="F26" t="n">
-        <v>-93</v>
+        <v>58</v>
       </c>
       <c r="G26" t="n">
-        <v>2033</v>
+        <v>235</v>
       </c>
       <c r="H26" t="n">
-        <v>95</v>
+        <v>-35</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1744,100 +1744,100 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>25</v>
+        <v>213</v>
       </c>
       <c r="D27" t="n">
-        <v>762</v>
+        <v>952</v>
       </c>
       <c r="E27" t="n">
-        <v>327</v>
+        <v>5298</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-96</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>2030</v>
       </c>
       <c r="H27" t="n">
+        <v>317</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>100</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>🚀 加速器</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
         <v>5</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
-        <v>78</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>🛬 穩定</t>
-        </is>
-      </c>
-      <c r="M27" t="n">
-        <v>-2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-6150</v>
+        <v>155</v>
       </c>
       <c r="D28" t="n">
-        <v>703</v>
+        <v>890</v>
       </c>
       <c r="E28" t="n">
-        <v>9727</v>
+        <v>899</v>
       </c>
       <c r="F28" t="n">
-        <v>637</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>1513</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1040</v>
+        <v>7</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1850,45 +1850,45 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>784</v>
+        <v>585</v>
       </c>
       <c r="D29" t="n">
-        <v>642</v>
+        <v>752</v>
       </c>
       <c r="E29" t="n">
-        <v>2275</v>
+        <v>2886</v>
       </c>
       <c r="F29" t="n">
-        <v>59</v>
+        <v>-5</v>
       </c>
       <c r="G29" t="n">
-        <v>236</v>
+        <v>-38</v>
       </c>
       <c r="H29" t="n">
-        <v>-63</v>
+        <v>-44</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1897,49 +1897,49 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="D30" t="n">
-        <v>590</v>
+        <v>706</v>
       </c>
       <c r="E30" t="n">
-        <v>3038</v>
+        <v>-1558</v>
       </c>
       <c r="F30" t="n">
-        <v>-2</v>
+        <v>-555</v>
       </c>
       <c r="G30" t="n">
-        <v>-34</v>
+        <v>-144</v>
       </c>
       <c r="H30" t="n">
-        <v>-46</v>
+        <v>64</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1948,19 +1948,19 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -1975,13 +1975,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>267</v>
+        <v>199</v>
       </c>
       <c r="D31" t="n">
-        <v>504</v>
+        <v>664</v>
       </c>
       <c r="E31" t="n">
-        <v>-393</v>
+        <v>-338</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1990,7 +1990,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2026,22 +2026,22 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-214</v>
+        <v>-37</v>
       </c>
       <c r="D32" t="n">
-        <v>492</v>
+        <v>622</v>
       </c>
       <c r="E32" t="n">
-        <v>253</v>
+        <v>677</v>
       </c>
       <c r="F32" t="n">
-        <v>-279</v>
+        <v>-492</v>
       </c>
       <c r="G32" t="n">
-        <v>-2295</v>
+        <v>-2487</v>
       </c>
       <c r="H32" t="n">
-        <v>-28</v>
+        <v>-14</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2068,31 +2068,31 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>343</v>
+        <v>-1279</v>
       </c>
       <c r="D33" t="n">
-        <v>426</v>
+        <v>385</v>
       </c>
       <c r="E33" t="n">
-        <v>-2870</v>
+        <v>-737</v>
       </c>
       <c r="F33" t="n">
-        <v>-1061</v>
+        <v>96</v>
       </c>
       <c r="G33" t="n">
-        <v>-2996</v>
+        <v>143</v>
       </c>
       <c r="H33" t="n">
-        <v>327</v>
+        <v>34</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2101,49 +2101,49 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>19</v>
+        <v>682</v>
       </c>
       <c r="D34" t="n">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="E34" t="n">
-        <v>718</v>
+        <v>-753</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>-1752</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-3167</v>
       </c>
       <c r="H34" t="n">
-        <v>7</v>
+        <v>306</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2152,49 +2152,49 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-1201</v>
+        <v>-487</v>
       </c>
       <c r="D35" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="E35" t="n">
-        <v>2030</v>
+        <v>9434</v>
       </c>
       <c r="F35" t="n">
-        <v>-469</v>
+        <v>855</v>
       </c>
       <c r="G35" t="n">
-        <v>-1989</v>
+        <v>-318</v>
       </c>
       <c r="H35" t="n">
-        <v>-295</v>
+        <v>-57</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2207,45 +2207,45 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D36" t="n">
-        <v>311</v>
+        <v>340</v>
       </c>
       <c r="E36" t="n">
-        <v>-1431</v>
+        <v>844</v>
       </c>
       <c r="F36" t="n">
-        <v>-409</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2254,40 +2254,40 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>-56</v>
       </c>
       <c r="D37" t="n">
-        <v>232</v>
+        <v>329</v>
       </c>
       <c r="E37" t="n">
-        <v>833</v>
+        <v>685</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -2296,58 +2296,58 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
+        <v>43</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>76</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>🚀 加速器</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
         <v>1</v>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K37" t="n">
-        <v>77</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>🚀 加速器</t>
-        </is>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-159</v>
+        <v>266</v>
       </c>
       <c r="D38" t="n">
-        <v>205</v>
+        <v>163</v>
       </c>
       <c r="E38" t="n">
-        <v>-876</v>
+        <v>-2239</v>
       </c>
       <c r="F38" t="n">
-        <v>97</v>
+        <v>-1</v>
       </c>
       <c r="G38" t="n">
-        <v>-251</v>
+        <v>-1</v>
       </c>
       <c r="H38" t="n">
-        <v>35</v>
+        <v>-11</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2356,110 +2356,110 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-98</v>
+        <v>-6</v>
       </c>
       <c r="D39" t="n">
-        <v>168</v>
+        <v>147</v>
       </c>
       <c r="E39" t="n">
-        <v>-380</v>
+        <v>856</v>
       </c>
       <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
         <v>77</v>
       </c>
-      <c r="G39" t="n">
-        <v>204</v>
-      </c>
-      <c r="H39" t="n">
-        <v>6</v>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>🚀 加速器</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-89</v>
+        <v>-68</v>
       </c>
       <c r="D40" t="n">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="E40" t="n">
-        <v>585</v>
+        <v>-344</v>
       </c>
       <c r="F40" t="n">
-        <v>-23</v>
+        <v>121</v>
       </c>
       <c r="G40" t="n">
-        <v>-28</v>
+        <v>254</v>
       </c>
       <c r="H40" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K40" t="n">
-        <v>86</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M40" t="n">
-        <v>-3</v>
-      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2473,13 +2473,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>35</v>
+        <v>-29</v>
       </c>
       <c r="D41" t="n">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="E41" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -2488,7 +2488,7 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2515,31 +2515,31 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>方土霖</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>59</v>
+        <v>81</v>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>-1817</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>-1327</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2552,45 +2552,45 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-199</v>
+        <v>-35</v>
       </c>
       <c r="D43" t="n">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="E43" t="n">
-        <v>487</v>
+        <v>759</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>-23</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>-28</v>
       </c>
       <c r="H43" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2599,40 +2599,40 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>方土霖</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D44" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="E44" t="n">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2641,7 +2641,7 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2654,45 +2654,45 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-27</v>
+        <v>-1378</v>
       </c>
       <c r="D45" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="E45" t="n">
-        <v>707</v>
+        <v>2992</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>-464</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>-1987</v>
       </c>
       <c r="H45" t="n">
-        <v>-2</v>
+        <v>-280</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2701,49 +2701,49 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M45" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C46" t="n">
+        <v>-349</v>
+      </c>
+      <c r="D46" t="n">
         <v>38</v>
       </c>
-      <c r="D46" t="n">
-        <v>-49</v>
-      </c>
       <c r="E46" t="n">
-        <v>-273</v>
+        <v>-948</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>-274</v>
       </c>
       <c r="H46" t="n">
-        <v>-0</v>
+        <v>26</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2752,49 +2752,49 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>-2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>大車隊</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-65</v>
+        <v>-7</v>
       </c>
       <c r="D47" t="n">
-        <v>-53</v>
+        <v>8</v>
       </c>
       <c r="E47" t="n">
-        <v>-479</v>
+        <v>-18</v>
       </c>
       <c r="F47" t="n">
-        <v>-29</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>-277</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>-12</v>
+        <v>-2</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2803,11 +2803,11 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2821,22 +2821,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5</v>
+        <v>-42</v>
       </c>
       <c r="D48" t="n">
-        <v>-59</v>
+        <v>-13</v>
       </c>
       <c r="E48" t="n">
-        <v>-2</v>
+        <v>681</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -2854,49 +2854,49 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-89</v>
+        <v>27</v>
       </c>
       <c r="D49" t="n">
-        <v>-103</v>
+        <v>-54</v>
       </c>
       <c r="E49" t="n">
-        <v>1114</v>
+        <v>-24</v>
       </c>
       <c r="F49" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2905,49 +2905,49 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>🐌 龜速*</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-1419</v>
+        <v>17</v>
       </c>
       <c r="D50" t="n">
-        <v>-106</v>
+        <v>-86</v>
       </c>
       <c r="E50" t="n">
-        <v>-1630</v>
+        <v>-213</v>
       </c>
       <c r="F50" t="n">
-        <v>1032</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>8626</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>60</v>
+        <v>-0</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2960,45 +2960,45 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>93</v>
+        <v>-237</v>
       </c>
       <c r="D51" t="n">
-        <v>-120</v>
+        <v>-118</v>
       </c>
       <c r="E51" t="n">
-        <v>-2163</v>
+        <v>19</v>
       </c>
       <c r="F51" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="G51" t="n">
-        <v>-1</v>
+        <v>50</v>
       </c>
       <c r="H51" t="n">
-        <v>-22</v>
+        <v>60</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3011,45 +3011,45 @@
         </is>
       </c>
       <c r="K51" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-126</v>
+        <v>398</v>
       </c>
       <c r="D52" t="n">
-        <v>-127</v>
+        <v>-119</v>
       </c>
       <c r="E52" t="n">
-        <v>65</v>
+        <v>2871</v>
       </c>
       <c r="F52" t="n">
-        <v>33</v>
+        <v>-302</v>
       </c>
       <c r="G52" t="n">
-        <v>50</v>
+        <v>-256</v>
       </c>
       <c r="H52" t="n">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3062,45 +3062,45 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-835</v>
+        <v>26</v>
       </c>
       <c r="D53" t="n">
-        <v>-162</v>
+        <v>-163</v>
       </c>
       <c r="E53" t="n">
-        <v>808</v>
+        <v>360</v>
       </c>
       <c r="F53" t="n">
-        <v>985</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>1595</v>
+        <v>-41</v>
       </c>
       <c r="H53" t="n">
-        <v>-93</v>
+        <v>-18</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3109,49 +3109,49 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>11</v>
+        <v>336</v>
       </c>
       <c r="D54" t="n">
-        <v>-185</v>
+        <v>-186</v>
       </c>
       <c r="E54" t="n">
-        <v>2186</v>
+        <v>-776</v>
       </c>
       <c r="F54" t="n">
-        <v>-216</v>
+        <v>105</v>
       </c>
       <c r="G54" t="n">
-        <v>-169</v>
+        <v>447</v>
       </c>
       <c r="H54" t="n">
-        <v>7</v>
+        <v>126</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3160,49 +3160,49 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M54" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-34</v>
+        <v>-100</v>
       </c>
       <c r="D55" t="n">
-        <v>-229</v>
+        <v>-202</v>
       </c>
       <c r="E55" t="n">
-        <v>94</v>
+        <v>-400</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>-29</v>
       </c>
       <c r="G55" t="n">
-        <v>-41</v>
+        <v>-277</v>
       </c>
       <c r="H55" t="n">
-        <v>-21</v>
+        <v>4</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3211,49 +3211,49 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-197</v>
+        <v>-115</v>
       </c>
       <c r="D56" t="n">
         <v>-242</v>
       </c>
       <c r="E56" t="n">
-        <v>-2247</v>
+        <v>1166</v>
       </c>
       <c r="F56" t="n">
-        <v>192</v>
+        <v>15</v>
       </c>
       <c r="G56" t="n">
-        <v>-1349</v>
+        <v>14</v>
       </c>
       <c r="H56" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3266,45 +3266,45 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速*</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-18</v>
+        <v>71</v>
       </c>
       <c r="D57" t="n">
-        <v>-429</v>
+        <v>-263</v>
       </c>
       <c r="E57" t="n">
-        <v>-869</v>
+        <v>-4829</v>
       </c>
       <c r="F57" t="n">
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>-227</v>
       </c>
       <c r="H57" t="n">
-        <v>-4</v>
+        <v>2421</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3313,11 +3313,11 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3325,28 +3325,28 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>智冠</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-56</v>
+        <v>-25</v>
       </c>
       <c r="D58" t="n">
-        <v>-454</v>
+        <v>-441</v>
       </c>
       <c r="E58" t="n">
-        <v>-2043</v>
+        <v>-825</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3364,100 +3364,100 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>德昌</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>499</v>
+        <v>25</v>
       </c>
       <c r="D59" t="n">
-        <v>-497</v>
+        <v>-456</v>
       </c>
       <c r="E59" t="n">
-        <v>-6238</v>
+        <v>-1893</v>
       </c>
       <c r="F59" t="n">
-        <v>-198</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
         <v>79</v>
       </c>
-      <c r="H59" t="n">
-        <v>90</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K59" t="n">
-        <v>51</v>
-      </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>583</v>
+        <v>156</v>
       </c>
       <c r="D60" t="n">
-        <v>-545</v>
+        <v>-465</v>
       </c>
       <c r="E60" t="n">
-        <v>-8414</v>
+        <v>-2293</v>
       </c>
       <c r="F60" t="n">
-        <v>-2187</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>-7873</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>190</v>
+        <v>-54</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3470,45 +3470,45 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-91</v>
+        <v>135</v>
       </c>
       <c r="D61" t="n">
-        <v>-548</v>
+        <v>-524</v>
       </c>
       <c r="E61" t="n">
-        <v>-3477</v>
+        <v>-6970</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>-243</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="H61" t="n">
-        <v>-63</v>
+        <v>156</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3517,100 +3517,100 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>128</v>
+        <v>1889</v>
       </c>
       <c r="D62" t="n">
-        <v>-622</v>
+        <v>-553</v>
       </c>
       <c r="E62" t="n">
-        <v>867</v>
+        <v>-1529</v>
       </c>
       <c r="F62" t="n">
+        <v>-2680</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-2579</v>
+      </c>
+      <c r="H62" t="n">
+        <v>186</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>64</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>🚀 加速器</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
         <v>0</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-219</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K62" t="n">
-        <v>78</v>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M62" t="n">
-        <v>-2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D63" t="n">
-        <v>-656</v>
+        <v>-607</v>
       </c>
       <c r="E63" t="n">
-        <v>-1165</v>
+        <v>1745</v>
       </c>
       <c r="F63" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>425</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>90</v>
+        <v>-204</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3619,19 +3619,19 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="64">
@@ -3646,13 +3646,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>219</v>
+        <v>-159</v>
       </c>
       <c r="D64" t="n">
-        <v>-657</v>
+        <v>-633</v>
       </c>
       <c r="E64" t="n">
-        <v>-3035</v>
+        <v>-3158</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -3661,7 +3661,7 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3697,22 +3697,22 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>142</v>
+        <v>246</v>
       </c>
       <c r="D65" t="n">
-        <v>-719</v>
+        <v>-777</v>
       </c>
       <c r="E65" t="n">
-        <v>-2679</v>
+        <v>-5627</v>
       </c>
       <c r="F65" t="n">
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H65" t="n">
-        <v>-57</v>
+        <v>-67</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3739,31 +3739,31 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-450</v>
+        <v>-1184</v>
       </c>
       <c r="D66" t="n">
-        <v>-745</v>
+        <v>-835</v>
       </c>
       <c r="E66" t="n">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="F66" t="n">
-        <v>8</v>
+        <v>1001</v>
       </c>
       <c r="G66" t="n">
-        <v>-20</v>
+        <v>1585</v>
       </c>
       <c r="H66" t="n">
-        <v>-35</v>
+        <v>-111</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3772,11 +3772,11 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -3799,22 +3799,22 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-87</v>
+        <v>-44</v>
       </c>
       <c r="D67" t="n">
-        <v>-889</v>
+        <v>-867</v>
       </c>
       <c r="E67" t="n">
-        <v>517</v>
+        <v>761</v>
       </c>
       <c r="F67" t="n">
-        <v>-200</v>
+        <v>-223</v>
       </c>
       <c r="G67" t="n">
-        <v>590</v>
+        <v>554</v>
       </c>
       <c r="H67" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3841,31 +3841,31 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-89</v>
+        <v>-245</v>
       </c>
       <c r="D68" t="n">
-        <v>-999</v>
+        <v>-867</v>
       </c>
       <c r="E68" t="n">
-        <v>1503</v>
+        <v>-7766</v>
       </c>
       <c r="F68" t="n">
-        <v>-229</v>
+        <v>-2206</v>
       </c>
       <c r="G68" t="n">
-        <v>-482</v>
+        <v>-8332</v>
       </c>
       <c r="H68" t="n">
-        <v>-46</v>
+        <v>333</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3878,11 +3878,11 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M68" t="n">
@@ -3901,22 +3901,22 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-96</v>
+        <v>35</v>
       </c>
       <c r="D69" t="n">
-        <v>-1089</v>
+        <v>-877</v>
       </c>
       <c r="E69" t="n">
-        <v>-3251</v>
+        <v>-1636</v>
       </c>
       <c r="F69" t="n">
-        <v>-50</v>
+        <v>-255</v>
       </c>
       <c r="G69" t="n">
-        <v>88</v>
+        <v>-54</v>
       </c>
       <c r="H69" t="n">
-        <v>-74</v>
+        <v>-68</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3943,70 +3943,82 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D70" t="n">
-        <v>-1243</v>
+        <v>-1027</v>
       </c>
       <c r="E70" t="n">
-        <v>1562</v>
+        <v>1489</v>
       </c>
       <c r="F70" t="n">
-        <v>-111</v>
+        <v>-192</v>
       </c>
       <c r="G70" t="n">
-        <v>1637</v>
+        <v>-482</v>
       </c>
       <c r="H70" t="n">
-        <v>-32</v>
+        <v>40</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>91</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>✈️ 高飛</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-233</v>
+        <v>-1284</v>
       </c>
       <c r="D71" t="n">
-        <v>-1290</v>
+        <v>-1086</v>
       </c>
       <c r="E71" t="n">
-        <v>-1740</v>
+        <v>-11898</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>391</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1265</v>
       </c>
       <c r="H71" t="n">
-        <v>2</v>
+        <v>-347</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -4019,11 +4031,11 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M71" t="n">
@@ -4033,133 +4045,121 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-969</v>
+        <v>-791</v>
       </c>
       <c r="D72" t="n">
-        <v>-1304</v>
+        <v>-1112</v>
       </c>
       <c r="E72" t="n">
-        <v>-898</v>
+        <v>-433</v>
       </c>
       <c r="F72" t="n">
+        <v>15</v>
+      </c>
+      <c r="G72" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-13</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>73</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>🛬 穩定</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
         <v>-1</v>
-      </c>
-      <c r="G72" t="n">
-        <v>-281</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-263</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K72" t="n">
-        <v>69</v>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M72" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-197</v>
+        <v>-170</v>
       </c>
       <c r="D73" t="n">
-        <v>-1525</v>
+        <v>-1175</v>
       </c>
       <c r="E73" t="n">
-        <v>-3144</v>
+        <v>1814</v>
       </c>
       <c r="F73" t="n">
-        <v>38</v>
+        <v>-138</v>
       </c>
       <c r="G73" t="n">
-        <v>-1</v>
+        <v>2188</v>
       </c>
       <c r="H73" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K73" t="n">
-        <v>71</v>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M73" t="n">
-        <v>-3</v>
-      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>聯合</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-2150</v>
+        <v>-115</v>
       </c>
       <c r="D74" t="n">
-        <v>-1550</v>
+        <v>-1253</v>
       </c>
       <c r="E74" t="n">
-        <v>-7189</v>
+        <v>-1795</v>
       </c>
       <c r="F74" t="n">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>1850</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-338</v>
+        <v>2</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4168,49 +4168,49 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>702</v>
+        <v>-1113</v>
       </c>
       <c r="D75" t="n">
-        <v>-1558</v>
+        <v>-1384</v>
       </c>
       <c r="E75" t="n">
-        <v>-2149</v>
+        <v>320</v>
       </c>
       <c r="F75" t="n">
-        <v>-598</v>
+        <v>-22</v>
       </c>
       <c r="G75" t="n">
-        <v>1403</v>
+        <v>476</v>
       </c>
       <c r="H75" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4219,49 +4219,49 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M75" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-1540</v>
+        <v>-1095</v>
       </c>
       <c r="D76" t="n">
-        <v>-1568</v>
+        <v>-1471</v>
       </c>
       <c r="E76" t="n">
-        <v>1234</v>
+        <v>-2660</v>
       </c>
       <c r="F76" t="n">
-        <v>223</v>
+        <v>494</v>
       </c>
       <c r="G76" t="n">
-        <v>510</v>
+        <v>8808</v>
       </c>
       <c r="H76" t="n">
-        <v>28</v>
+        <v>184</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4270,11 +4270,11 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -4282,37 +4282,37 @@
         </is>
       </c>
       <c r="M76" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-4480</v>
+        <v>-1386</v>
       </c>
       <c r="D77" t="n">
-        <v>-1599</v>
+        <v>-1529</v>
       </c>
       <c r="E77" t="n">
-        <v>972</v>
+        <v>-543</v>
       </c>
       <c r="F77" t="n">
-        <v>488</v>
+        <v>-1</v>
       </c>
       <c r="G77" t="n">
-        <v>-1141</v>
+        <v>-281</v>
       </c>
       <c r="H77" t="n">
-        <v>287</v>
+        <v>-241</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4321,11 +4321,11 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -4339,31 +4339,31 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>勝一</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-3733</v>
+        <v>-62</v>
       </c>
       <c r="D78" t="n">
-        <v>-1681</v>
+        <v>-1571</v>
       </c>
       <c r="E78" t="n">
-        <v>6276</v>
+        <v>-3409</v>
       </c>
       <c r="F78" t="n">
+        <v>38</v>
+      </c>
+      <c r="G78" t="n">
         <v>-1</v>
       </c>
-      <c r="G78" t="n">
-        <v>-17</v>
-      </c>
       <c r="H78" t="n">
-        <v>57</v>
+        <v>-2</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4372,100 +4372,100 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-548</v>
+        <v>248</v>
       </c>
       <c r="D79" t="n">
-        <v>-1817</v>
+        <v>-1583</v>
       </c>
       <c r="E79" t="n">
-        <v>-5035</v>
+        <v>-2059</v>
       </c>
       <c r="F79" t="n">
+        <v>-511</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1450</v>
+      </c>
+      <c r="H79" t="n">
+        <v>56</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>66</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
         <v>0</v>
-      </c>
-      <c r="G79" t="n">
-        <v>-226</v>
-      </c>
-      <c r="H79" t="n">
-        <v>2297</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K79" t="n">
-        <v>78</v>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M79" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>63</v>
+        <v>-2293</v>
       </c>
       <c r="D80" t="n">
-        <v>-1979</v>
+        <v>-1608</v>
       </c>
       <c r="E80" t="n">
-        <v>119</v>
+        <v>-6971</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>581</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>1435</v>
       </c>
       <c r="H80" t="n">
-        <v>-188</v>
+        <v>-146</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4478,36 +4478,36 @@
         </is>
       </c>
       <c r="K80" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-2395</v>
+        <v>84</v>
       </c>
       <c r="D81" t="n">
-        <v>-2270</v>
+        <v>-1718</v>
       </c>
       <c r="E81" t="n">
-        <v>-2587</v>
+        <v>581</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -4516,20 +4516,20 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>2</v>
+        <v>-239</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -4537,139 +4537,139 @@
         </is>
       </c>
       <c r="M81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-225</v>
+        <v>-2133</v>
       </c>
       <c r="D82" t="n">
-        <v>-2840</v>
+        <v>-1910</v>
       </c>
       <c r="E82" t="n">
-        <v>-6332</v>
+        <v>-2263</v>
       </c>
       <c r="F82" t="n">
-        <v>-83</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>-820</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>🚀 加速器*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-1510</v>
+        <v>1450</v>
       </c>
       <c r="D83" t="n">
-        <v>-2878</v>
+        <v>-1950</v>
       </c>
       <c r="E83" t="n">
-        <v>-14446</v>
+        <v>-1018</v>
       </c>
       <c r="F83" t="n">
-        <v>757</v>
+        <v>-290</v>
       </c>
       <c r="G83" t="n">
-        <v>1256</v>
+        <v>3217</v>
       </c>
       <c r="H83" t="n">
-        <v>-316</v>
+        <v>-152</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>46</v>
+        <v>-1719</v>
       </c>
       <c r="D84" t="n">
-        <v>-2900</v>
+        <v>-2043</v>
       </c>
       <c r="E84" t="n">
-        <v>-4730</v>
+        <v>94838</v>
       </c>
       <c r="F84" t="n">
-        <v>-29</v>
+        <v>1555</v>
       </c>
       <c r="G84" t="n">
-        <v>-217</v>
+        <v>4748</v>
       </c>
       <c r="H84" t="n">
-        <v>15</v>
+        <v>-1604</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4678,97 +4678,85 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K84" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M84" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-843</v>
+        <v>-60</v>
       </c>
       <c r="D85" t="n">
-        <v>-3068</v>
+        <v>-2222</v>
       </c>
       <c r="E85" t="n">
-        <v>-1485</v>
+        <v>-5784</v>
       </c>
       <c r="F85" t="n">
-        <v>-303</v>
+        <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>-1030</v>
+        <v>-400</v>
       </c>
       <c r="H85" t="n">
-        <v>-1</v>
+        <v>-54</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
           <t>🟠 減碼</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K85" t="n">
-        <v>73</v>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M85" t="n">
-        <v>-1</v>
-      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-2655</v>
+        <v>561</v>
       </c>
       <c r="D86" t="n">
-        <v>-3311</v>
+        <v>-2302</v>
       </c>
       <c r="E86" t="n">
-        <v>-4528</v>
+        <v>-3815</v>
       </c>
       <c r="F86" t="n">
-        <v>-558</v>
+        <v>-29</v>
       </c>
       <c r="G86" t="n">
-        <v>-453</v>
+        <v>-217</v>
       </c>
       <c r="H86" t="n">
         <v>108</v>
@@ -4780,11 +4768,11 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K86" t="n">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4792,47 +4780,59 @@
         </is>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-31</v>
+        <v>-637</v>
       </c>
       <c r="D87" t="n">
-        <v>-3404</v>
+        <v>-2560</v>
       </c>
       <c r="E87" t="n">
-        <v>-6189</v>
+        <v>-1368</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>-302</v>
       </c>
       <c r="G87" t="n">
-        <v>-400</v>
+        <v>-1136</v>
       </c>
       <c r="H87" t="n">
-        <v>-4</v>
+        <v>8</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
           <t>🟠 減碼</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>73</v>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M87" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4846,22 +4846,22 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-639</v>
+        <v>1260</v>
       </c>
       <c r="D88" t="n">
-        <v>-3656</v>
+        <v>-2605</v>
       </c>
       <c r="E88" t="n">
-        <v>-21353</v>
+        <v>-18038</v>
       </c>
       <c r="F88" t="n">
-        <v>-556</v>
+        <v>-632</v>
       </c>
       <c r="G88" t="n">
-        <v>-1452</v>
+        <v>-1617</v>
       </c>
       <c r="H88" t="n">
-        <v>-350</v>
+        <v>-271</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4888,31 +4888,31 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>840</v>
+        <v>-4715</v>
       </c>
       <c r="D89" t="n">
-        <v>-3673</v>
+        <v>-2643</v>
       </c>
       <c r="E89" t="n">
-        <v>-2654</v>
+        <v>266</v>
       </c>
       <c r="F89" t="n">
-        <v>-982</v>
+        <v>734</v>
       </c>
       <c r="G89" t="n">
-        <v>4955</v>
+        <v>-2049</v>
       </c>
       <c r="H89" t="n">
-        <v>-175</v>
+        <v>100</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4921,19 +4921,19 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K89" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M89" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -4948,22 +4948,22 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-27619</v>
+        <v>-13329</v>
       </c>
       <c r="D90" t="n">
-        <v>-4616</v>
+        <v>-4372</v>
       </c>
       <c r="E90" t="n">
-        <v>-132721</v>
+        <v>-126523</v>
       </c>
       <c r="F90" t="n">
-        <v>445</v>
+        <v>1104</v>
       </c>
       <c r="G90" t="n">
-        <v>-2830</v>
+        <v>-2643</v>
       </c>
       <c r="H90" t="n">
-        <v>3296</v>
+        <v>4200</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="M90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -4999,22 +4999,22 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>24</v>
+        <v>797</v>
       </c>
       <c r="D91" t="n">
-        <v>-4635</v>
+        <v>-4605</v>
       </c>
       <c r="E91" t="n">
-        <v>-33483</v>
+        <v>-34977</v>
       </c>
       <c r="F91" t="n">
-        <v>109</v>
+        <v>27</v>
       </c>
       <c r="G91" t="n">
-        <v>335</v>
+        <v>362</v>
       </c>
       <c r="H91" t="n">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -5050,13 +5050,13 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>39</v>
+        <v>182</v>
       </c>
       <c r="D92" t="n">
-        <v>-6244</v>
+        <v>-5701</v>
       </c>
       <c r="E92" t="n">
-        <v>-13488</v>
+        <v>-14533</v>
       </c>
       <c r="F92" t="n">
         <v>-395</v>
@@ -5065,7 +5065,7 @@
         <v>-233</v>
       </c>
       <c r="H92" t="n">
-        <v>18</v>
+        <v>342</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -5092,31 +5092,31 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-3219</v>
+        <v>-780</v>
       </c>
       <c r="D93" t="n">
-        <v>-7531</v>
+        <v>-7794</v>
       </c>
       <c r="E93" t="n">
-        <v>72606</v>
+        <v>-16728</v>
       </c>
       <c r="F93" t="n">
-        <v>-377</v>
+        <v>-1</v>
       </c>
       <c r="G93" t="n">
-        <v>2365</v>
+        <v>-1</v>
       </c>
       <c r="H93" t="n">
-        <v>-504</v>
+        <v>-53</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -5129,45 +5129,45 @@
         </is>
       </c>
       <c r="K93" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-558</v>
+        <v>-639</v>
       </c>
       <c r="D94" t="n">
-        <v>-8068</v>
+        <v>-8230</v>
       </c>
       <c r="E94" t="n">
-        <v>-16437</v>
+        <v>-16110</v>
       </c>
       <c r="F94" t="n">
-        <v>-1</v>
+        <v>-307</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>1249</v>
       </c>
       <c r="H94" t="n">
-        <v>-64</v>
+        <v>483</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -5176,49 +5176,49 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K94" t="n">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M94" t="n">
-        <v>-5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-1491</v>
+        <v>-200</v>
       </c>
       <c r="D95" t="n">
-        <v>-8933</v>
+        <v>-9101</v>
       </c>
       <c r="E95" t="n">
-        <v>-16463</v>
+        <v>-23239</v>
       </c>
       <c r="F95" t="n">
-        <v>475</v>
+        <v>-100</v>
       </c>
       <c r="G95" t="n">
-        <v>1372</v>
+        <v>-100</v>
       </c>
       <c r="H95" t="n">
-        <v>446</v>
+        <v>-148</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5227,19 +5227,19 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K95" t="n">
-        <v>93</v>
+        <v>60</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M95" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="96">
@@ -5254,26 +5254,26 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-1360</v>
+        <v>-2982</v>
       </c>
       <c r="D96" t="n">
-        <v>-9526</v>
+        <v>-10214</v>
       </c>
       <c r="E96" t="n">
-        <v>-11719</v>
+        <v>-11109</v>
       </c>
       <c r="F96" t="n">
-        <v>-2179</v>
+        <v>-369</v>
       </c>
       <c r="G96" t="n">
-        <v>1586</v>
+        <v>2356</v>
       </c>
       <c r="H96" t="n">
-        <v>177</v>
+        <v>478</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🔴 大賣</t>
         </is>
       </c>
       <c r="J96" t="inlineStr"/>
@@ -5284,31 +5284,31 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-921</v>
+        <v>-4482</v>
       </c>
       <c r="D97" t="n">
-        <v>-10612</v>
+        <v>-11319</v>
       </c>
       <c r="E97" t="n">
-        <v>-24686</v>
+        <v>9088</v>
       </c>
       <c r="F97" t="n">
-        <v>-100</v>
+        <v>470</v>
       </c>
       <c r="G97" t="n">
-        <v>-100</v>
+        <v>1659</v>
       </c>
       <c r="H97" t="n">
-        <v>-154</v>
+        <v>971</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -5317,49 +5317,49 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K97" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M97" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-4314</v>
+        <v>-3938</v>
       </c>
       <c r="D98" t="n">
-        <v>-12896</v>
+        <v>-11595</v>
       </c>
       <c r="E98" t="n">
-        <v>-13599</v>
+        <v>84644</v>
       </c>
       <c r="F98" t="n">
-        <v>-191</v>
+        <v>-1241</v>
       </c>
       <c r="G98" t="n">
-        <v>-2682</v>
+        <v>1626</v>
       </c>
       <c r="H98" t="n">
-        <v>-1071</v>
+        <v>-190</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5372,45 +5372,45 @@
         </is>
       </c>
       <c r="K98" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-349</v>
+        <v>3478</v>
       </c>
       <c r="D99" t="n">
-        <v>-13596</v>
+        <v>-11947</v>
       </c>
       <c r="E99" t="n">
-        <v>-67910</v>
+        <v>-45371</v>
       </c>
       <c r="F99" t="n">
-        <v>1491</v>
+        <v>-258</v>
       </c>
       <c r="G99" t="n">
-        <v>-95</v>
+        <v>-7336</v>
       </c>
       <c r="H99" t="n">
-        <v>-229</v>
+        <v>874</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5423,7 +5423,7 @@
         </is>
       </c>
       <c r="K99" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -5431,37 +5431,37 @@
         </is>
       </c>
       <c r="M99" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-2925</v>
+        <v>-9193</v>
       </c>
       <c r="D100" t="n">
-        <v>-14834</v>
+        <v>-12298</v>
       </c>
       <c r="E100" t="n">
-        <v>-51432</v>
+        <v>-15081</v>
       </c>
       <c r="F100" t="n">
-        <v>-773</v>
+        <v>8472</v>
       </c>
       <c r="G100" t="n">
-        <v>-7311</v>
+        <v>7736</v>
       </c>
       <c r="H100" t="n">
-        <v>593</v>
+        <v>44</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -5470,15 +5470,15 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K100" t="n">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器*</t>
         </is>
       </c>
       <c r="M100" t="n">
@@ -5488,31 +5488,31 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>寶雅*</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-4067</v>
+        <v>-3500</v>
       </c>
       <c r="D101" t="n">
-        <v>-15352</v>
+        <v>-12848</v>
       </c>
       <c r="E101" t="n">
-        <v>54874</v>
+        <v>-69027</v>
       </c>
       <c r="F101" t="n">
-        <v>-714</v>
+        <v>2178</v>
       </c>
       <c r="G101" t="n">
-        <v>7899</v>
+        <v>592</v>
       </c>
       <c r="H101" t="n">
-        <v>-1472</v>
+        <v>-219</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5521,49 +5521,49 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K101" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M101" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-21478</v>
+        <v>-4139</v>
       </c>
       <c r="D102" t="n">
-        <v>-18020</v>
+        <v>-13105</v>
       </c>
       <c r="E102" t="n">
-        <v>60027</v>
+        <v>-13886</v>
       </c>
       <c r="F102" t="n">
-        <v>-3802</v>
+        <v>-931</v>
       </c>
       <c r="G102" t="n">
-        <v>-9057</v>
+        <v>-3390</v>
       </c>
       <c r="H102" t="n">
-        <v>-3356</v>
+        <v>-1042</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5572,19 +5572,19 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K102" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -5599,22 +5599,22 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-11012</v>
+        <v>-3003</v>
       </c>
       <c r="D103" t="n">
-        <v>-19390</v>
+        <v>-16853</v>
       </c>
       <c r="E103" t="n">
-        <v>-83008</v>
+        <v>-89131</v>
       </c>
       <c r="F103" t="n">
-        <v>2336</v>
+        <v>2408</v>
       </c>
       <c r="G103" t="n">
-        <v>-21001</v>
+        <v>-20155</v>
       </c>
       <c r="H103" t="n">
-        <v>1454</v>
+        <v>2435</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5641,31 +5641,31 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-69311</v>
+        <v>-6507</v>
       </c>
       <c r="D104" t="n">
-        <v>-20433</v>
+        <v>-18839</v>
       </c>
       <c r="E104" t="n">
-        <v>-681</v>
+        <v>46382</v>
       </c>
       <c r="F104" t="n">
-        <v>-15128</v>
+        <v>154</v>
       </c>
       <c r="G104" t="n">
-        <v>-32931</v>
+        <v>7577</v>
       </c>
       <c r="H104" t="n">
-        <v>-4808</v>
+        <v>-1398</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5678,15 +5678,15 @@
         </is>
       </c>
       <c r="K104" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M104" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="105">
@@ -5701,22 +5701,22 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-12325</v>
+        <v>-19086</v>
       </c>
       <c r="D105" t="n">
-        <v>-100782</v>
+        <v>-94692</v>
       </c>
       <c r="E105" t="n">
-        <v>151019</v>
+        <v>170040</v>
       </c>
       <c r="F105" t="n">
-        <v>5147</v>
+        <v>9240</v>
       </c>
       <c r="G105" t="n">
-        <v>36240</v>
+        <v>39217</v>
       </c>
       <c r="H105" t="n">
-        <v>734</v>
+        <v>1192</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -5737,7 +5737,7 @@
         </is>
       </c>
       <c r="M105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5751,7 +5751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5794,261 +5794,261 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -300 千股)</t>
+          <t>📈 20d 巨變(加碼 67 千股)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>343111</v>
+        <v>213102</v>
       </c>
       <c r="D2" t="n">
-        <v>426273</v>
+        <v>951978</v>
       </c>
       <c r="E2" t="n">
-        <v>20135</v>
+        <v>115861</v>
       </c>
       <c r="F2" t="n">
-        <v>726365</v>
+        <v>885463</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>奇鋐</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 246 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 1,051 千股)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>115861</v>
+        <v>1260134</v>
       </c>
       <c r="D3" t="n">
-        <v>885463</v>
+        <v>-2605451</v>
       </c>
       <c r="E3" t="n">
-        <v>549697</v>
+        <v>-639297</v>
       </c>
       <c r="F3" t="n">
-        <v>639380</v>
+        <v>-3656169</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>亞翔</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 189 千股)</t>
+          <t>📈 20d 巨變(加碼 13 千股)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-1491111</v>
+        <v>137541</v>
       </c>
       <c r="D4" t="n">
-        <v>-8932948</v>
+        <v>1394295</v>
       </c>
       <c r="E4" t="n">
-        <v>-1705983</v>
+        <v>79052</v>
       </c>
       <c r="F4" t="n">
-        <v>-9122032</v>
+        <v>1381453</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>健策</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -200 千股)</t>
+          <t>📉 20d 巨變(減碼 -64 千股)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-639297</v>
+        <v>681611</v>
       </c>
       <c r="D5" t="n">
-        <v>-3656169</v>
+        <v>362420</v>
       </c>
       <c r="E5" t="n">
-        <v>-206030</v>
+        <v>343111</v>
       </c>
       <c r="F5" t="n">
-        <v>-3455854</v>
+        <v>426273</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>台光電</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 73 千股)</t>
+          <t>📈 20d 巨變(加碼 703 千股)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-213601</v>
+        <v>-639289</v>
       </c>
       <c r="D6" t="n">
-        <v>491720</v>
+        <v>-8229822</v>
       </c>
       <c r="E6" t="n">
-        <v>-57933</v>
+        <v>-1491111</v>
       </c>
       <c r="F6" t="n">
-        <v>419071</v>
+        <v>-8932948</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 151 千股)</t>
+          <t>📈 20d 巨變(加碼 130 千股)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>79052</v>
+        <v>-36729</v>
       </c>
       <c r="D7" t="n">
-        <v>1381453</v>
+        <v>621923</v>
       </c>
       <c r="E7" t="n">
-        <v>20255</v>
+        <v>-213601</v>
       </c>
       <c r="F7" t="n">
-        <v>1230832</v>
+        <v>491720</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>勤誠</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -548 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 323 千股)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25102</v>
+        <v>2002</v>
       </c>
       <c r="D8" t="n">
-        <v>311470</v>
+        <v>80956</v>
       </c>
       <c r="E8" t="n">
-        <v>548930</v>
+        <v>-196816</v>
       </c>
       <c r="F8" t="n">
-        <v>859780</v>
+        <v>-241873</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>旺矽</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 4,060 千股)</t>
+          <t>📈 20d 巨變(加碼 394 千股)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-27619102</v>
+        <v>478481</v>
       </c>
       <c r="D9" t="n">
-        <v>-4616452</v>
+        <v>705677</v>
       </c>
       <c r="E9" t="n">
-        <v>-34357576</v>
+        <v>25102</v>
       </c>
       <c r="F9" t="n">
-        <v>-8676510</v>
+        <v>311470</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>光聖</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -78 千股)</t>
+          <t>📉 20d 巨變(減碼 -489 千股)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-1530237</v>
+        <v>-319084</v>
       </c>
       <c r="D10" t="n">
-        <v>8379729</v>
+        <v>1325292</v>
       </c>
       <c r="E10" t="n">
-        <v>-1272477</v>
+        <v>-9446</v>
       </c>
       <c r="F10" t="n">
-        <v>8457783</v>
+        <v>1814324</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>致茂</t>
         </is>
       </c>
     </row>
@@ -6060,20 +6060,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 819 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -323 千股)</t>
         </is>
       </c>
       <c r="C11" t="n">
+        <v>-245209</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-867374</v>
+      </c>
+      <c r="E11" t="n">
         <v>582550</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>-544788</v>
-      </c>
-      <c r="E11" t="n">
-        <v>164892</v>
-      </c>
-      <c r="F11" t="n">
-        <v>-1364263</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -6084,174 +6084,174 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 109 千股)</t>
+          <t>📈 20d 巨變(加碼 242 千股)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-9446</v>
+        <v>-1164487</v>
       </c>
       <c r="D12" t="n">
-        <v>1814324</v>
+        <v>8621562</v>
       </c>
       <c r="E12" t="n">
-        <v>-623168</v>
+        <v>-1530237</v>
       </c>
       <c r="F12" t="n">
-        <v>1705253</v>
+        <v>8379729</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>雙鴻</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -177 千股)</t>
+          <t>📈 20d 巨變(加碼 244 千股)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-2924887</v>
+        <v>-13328620</v>
       </c>
       <c r="D13" t="n">
-        <v>-14834469</v>
+        <v>-4372146</v>
       </c>
       <c r="E13" t="n">
-        <v>-10969822</v>
+        <v>-27619102</v>
       </c>
       <c r="F13" t="n">
-        <v>-14657061</v>
+        <v>-4616452</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 168 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 2,888 千股)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>840746</v>
+        <v>3478025</v>
       </c>
       <c r="D14" t="n">
-        <v>2086615</v>
+        <v>-11946950</v>
       </c>
       <c r="E14" t="n">
-        <v>839724</v>
+        <v>-2924887</v>
       </c>
       <c r="F14" t="n">
-        <v>1918125</v>
+        <v>-14834469</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>台達電</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -62 千股)</t>
+          <t>📈 20d 巨變(加碼 820 千股)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-159131</v>
+        <v>942737</v>
       </c>
       <c r="D15" t="n">
-        <v>204756</v>
+        <v>2907039</v>
       </c>
       <c r="E15" t="n">
-        <v>-20521</v>
+        <v>840746</v>
       </c>
       <c r="F15" t="n">
-        <v>266445</v>
+        <v>2086615</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>帆宣</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 89 千股)</t>
+          <t>📈 20d 巨變(加碼 598 千股)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-1509760</v>
+        <v>560769</v>
       </c>
       <c r="D16" t="n">
-        <v>-2877872</v>
+        <v>-2301540</v>
       </c>
       <c r="E16" t="n">
-        <v>-1723597</v>
+        <v>45713</v>
       </c>
       <c r="F16" t="n">
-        <v>-2967191</v>
+        <v>-2899731</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>佳必琪</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 226 千股)</t>
+          <t>📈 20d 巨變(加碼 1,792 千股)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>45713</v>
+        <v>-1284004</v>
       </c>
       <c r="D17" t="n">
-        <v>-2899731</v>
+        <v>-1086135</v>
       </c>
       <c r="E17" t="n">
-        <v>-23253</v>
+        <v>-1509760</v>
       </c>
       <c r="F17" t="n">
-        <v>-3125507</v>
+        <v>-2877872</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>健鼎</t>
         </is>
       </c>
     </row>
@@ -6263,20 +6263,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 120 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -28 千股)</t>
         </is>
       </c>
       <c r="C18" t="n">
+        <v>22320</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-1026614</v>
+      </c>
+      <c r="E18" t="n">
         <v>-88754</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>-998712</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-345554</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-1119118</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -6287,29 +6287,29 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 173 千股)</t>
+          <t>📉 20d 巨變(減碼 -167 千股)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-95640</v>
+        <v>-348631</v>
       </c>
       <c r="D19" t="n">
-        <v>-1088657</v>
+        <v>38218</v>
       </c>
       <c r="E19" t="n">
-        <v>-86077</v>
+        <v>-159131</v>
       </c>
       <c r="F19" t="n">
-        <v>-1262118</v>
+        <v>204756</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>川湖</t>
         </is>
       </c>
     </row>
@@ -6321,20 +6321,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 674 千股)</t>
+          <t>📈 20d 巨變(加碼 227 千股)</t>
         </is>
       </c>
       <c r="C20" t="n">
+        <v>328807</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5247575</v>
+      </c>
+      <c r="E20" t="n">
         <v>705718</v>
       </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
         <v>5020474</v>
-      </c>
-      <c r="E20" t="n">
-        <v>333317</v>
-      </c>
-      <c r="F20" t="n">
-        <v>4346584</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -6345,203 +6345,203 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 326 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 212 千股)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>969972</v>
+        <v>35264</v>
       </c>
       <c r="D21" t="n">
-        <v>2094944</v>
+        <v>-876521</v>
       </c>
       <c r="E21" t="n">
-        <v>561262</v>
+        <v>-95640</v>
       </c>
       <c r="F21" t="n">
-        <v>1768910</v>
+        <v>-1088657</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>崇越</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 617 千股)</t>
+          <t>📈 20d 巨變(加碼 360 千股)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>82690</v>
+        <v>-2132958</v>
       </c>
       <c r="D22" t="n">
-        <v>-655599</v>
+        <v>-1910322</v>
       </c>
       <c r="E22" t="n">
-        <v>-124909</v>
+        <v>-2394722</v>
       </c>
       <c r="F22" t="n">
-        <v>-1272894</v>
+        <v>-2270298</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>建榮</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -455 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -11 千股)</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-2394722</v>
+        <v>-720715</v>
       </c>
       <c r="D23" t="n">
-        <v>-2270298</v>
+        <v>2084402</v>
       </c>
       <c r="E23" t="n">
-        <v>-2819244</v>
+        <v>969972</v>
       </c>
       <c r="F23" t="n">
-        <v>-1815520</v>
+        <v>2094944</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>中砂</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 233 千股)</t>
+          <t>📈 20d 巨變(加碼 469 千股)</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>499293</v>
+        <v>335727</v>
       </c>
       <c r="D24" t="n">
-        <v>-497121</v>
+        <v>-186408</v>
       </c>
       <c r="E24" t="n">
-        <v>529543</v>
+        <v>82690</v>
       </c>
       <c r="F24" t="n">
-        <v>-730543</v>
+        <v>-655599</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>華城</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 200 千股)</t>
+          <t>📉 20d 巨變(減碼 -27 千股)</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-3732764</v>
+        <v>135383</v>
       </c>
       <c r="D25" t="n">
-        <v>-1680640</v>
+        <v>-524318</v>
       </c>
       <c r="E25" t="n">
-        <v>-3635553</v>
+        <v>499293</v>
       </c>
       <c r="F25" t="n">
-        <v>-1880910</v>
+        <v>-497121</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>大立光</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -15 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -30 千股)</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>218782</v>
+        <v>-7006</v>
       </c>
       <c r="D26" t="n">
-        <v>-657400</v>
+        <v>7714</v>
       </c>
       <c r="E26" t="n">
-        <v>250917</v>
+        <v>13000</v>
       </c>
       <c r="F26" t="n">
-        <v>-642090</v>
+        <v>37221</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>大車隊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 529 千股)</t>
+          <t>📈 20d 巨變(加碼 2,764 千股)</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>591133</v>
+        <v>-48147</v>
       </c>
       <c r="D27" t="n">
-        <v>15220548</v>
+        <v>1083721</v>
       </c>
       <c r="E27" t="n">
-        <v>182195</v>
+        <v>-3732764</v>
       </c>
       <c r="F27" t="n">
-        <v>14691920</v>
+        <v>-1680640</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>零壹</t>
         </is>
       </c>
     </row>
@@ -6553,20 +6553,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -24 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 83 千股)</t>
         </is>
       </c>
       <c r="C28" t="n">
+        <v>156037</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-464862</v>
+      </c>
+      <c r="E28" t="n">
         <v>-91173</v>
       </c>
-      <c r="D28" t="n">
+      <c r="F28" t="n">
         <v>-547672</v>
-      </c>
-      <c r="E28" t="n">
-        <v>-309173</v>
-      </c>
-      <c r="F28" t="n">
-        <v>-523367</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -6577,290 +6577,290 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 59 千股)</t>
+          <t>📈 20d 巨變(加碼 609 千股)</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>203303</v>
+        <v>572620</v>
       </c>
       <c r="D29" t="n">
-        <v>1027113</v>
+        <v>15829618</v>
       </c>
       <c r="E29" t="n">
-        <v>34446</v>
+        <v>591133</v>
       </c>
       <c r="F29" t="n">
-        <v>967620</v>
+        <v>15220548</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -72 千股)</t>
+          <t>📉 20d 巨變(減碼 -29 千股)</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-1539643</v>
+        <v>-41770</v>
       </c>
       <c r="D30" t="n">
-        <v>-1568249</v>
+        <v>-12682</v>
       </c>
       <c r="E30" t="n">
-        <v>-1456004</v>
+        <v>-27263</v>
       </c>
       <c r="F30" t="n">
-        <v>-1496195</v>
+        <v>15953</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>崇友</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -3,751 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 24 千股)</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4348602</v>
+        <v>-159008</v>
       </c>
       <c r="D31" t="n">
-        <v>28128099</v>
+        <v>-633400</v>
       </c>
       <c r="E31" t="n">
-        <v>-3056869</v>
+        <v>218782</v>
       </c>
       <c r="F31" t="n">
-        <v>31878739</v>
+        <v>-657400</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>湧德</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -1,652 千股)</t>
+          <t>📈 20d 巨變(加碼 123 千股)</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-348803</v>
+        <v>288054</v>
       </c>
       <c r="D32" t="n">
-        <v>-13595837</v>
+        <v>1150231</v>
       </c>
       <c r="E32" t="n">
-        <v>3018222</v>
+        <v>203303</v>
       </c>
       <c r="F32" t="n">
-        <v>-11943903</v>
+        <v>1027113</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>合機</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -8 千股)</t>
+          <t>📈 20d 巨變(加碼 184 千股)</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-89482</v>
+        <v>-1112669</v>
       </c>
       <c r="D33" t="n">
-        <v>155689</v>
+        <v>-1384298</v>
       </c>
       <c r="E33" t="n">
-        <v>-144598</v>
+        <v>-1539643</v>
       </c>
       <c r="F33" t="n">
-        <v>163447</v>
+        <v>-1568249</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>卜蜂</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 83 千股)</t>
+          <t>📉 20d 巨變(減碼 -75 千股)</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>489208</v>
+        <v>-34694</v>
       </c>
       <c r="D34" t="n">
-        <v>589568</v>
+        <v>80774</v>
       </c>
       <c r="E34" t="n">
-        <v>260208</v>
+        <v>-89482</v>
       </c>
       <c r="F34" t="n">
-        <v>506790</v>
+        <v>155689</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>大統益</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 28 千股)</t>
+          <t>📈 20d 巨變(加碼 748 千股)</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-17879</v>
+        <v>-3500209</v>
       </c>
       <c r="D35" t="n">
-        <v>-429241</v>
+        <v>-12848208</v>
       </c>
       <c r="E35" t="n">
-        <v>-58173</v>
+        <v>-348803</v>
       </c>
       <c r="F35" t="n">
-        <v>-457554</v>
+        <v>-13595837</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>寶雅*</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 5 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -22,188 千股)</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>6000</v>
+        <v>-15044921</v>
       </c>
       <c r="D36" t="n">
-        <v>59000</v>
+        <v>5940109</v>
       </c>
       <c r="E36" t="n">
-        <v>9000</v>
+        <v>4348602</v>
       </c>
       <c r="F36" t="n">
-        <v>54000</v>
+        <v>28128099</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>方土霖</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -82 千股)</t>
+          <t>📈 20d 巨變(加碼 162 千股)</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-87213</v>
+        <v>585111</v>
       </c>
       <c r="D37" t="n">
-        <v>-889499</v>
+        <v>751669</v>
       </c>
       <c r="E37" t="n">
-        <v>-74218</v>
+        <v>489208</v>
       </c>
       <c r="F37" t="n">
-        <v>-807090</v>
+        <v>589568</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>豐藝</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -100 千股)</t>
+          <t>📉 20d 巨變(減碼 -12 千股)</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-88850</v>
+        <v>-25335</v>
       </c>
       <c r="D38" t="n">
-        <v>-102776</v>
+        <v>-441138</v>
       </c>
       <c r="E38" t="n">
-        <v>-75850</v>
+        <v>-17879</v>
       </c>
       <c r="F38" t="n">
-        <v>-3197</v>
+        <v>-429241</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>智冠</t>
         </is>
       </c>
     </row>
@@ -6872,20 +6872,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -6 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 66 千股)</t>
         </is>
       </c>
       <c r="C39" t="n">
+        <v>26487</v>
+      </c>
+      <c r="D39" t="n">
+        <v>-163055</v>
+      </c>
+      <c r="E39" t="n">
         <v>-33534</v>
       </c>
-      <c r="D39" t="n">
+      <c r="F39" t="n">
         <v>-229121</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-124872</v>
-      </c>
-      <c r="F39" t="n">
-        <v>-223418</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -6896,261 +6896,261 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -7,813 千股)</t>
+          <t>📉 20d 巨變(減碼 -140 千股)</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>10210053</v>
+        <v>-114980</v>
       </c>
       <c r="D40" t="n">
-        <v>62041285</v>
+        <v>-242279</v>
       </c>
       <c r="E40" t="n">
-        <v>10963481</v>
+        <v>-88850</v>
       </c>
       <c r="F40" t="n">
-        <v>69854759</v>
+        <v>-102776</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>八方雲集</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -42 千股)</t>
+          <t>📈 20d 巨變(加碼 22 千股)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-233072</v>
+        <v>-43923</v>
       </c>
       <c r="D41" t="n">
-        <v>-1290405</v>
+        <v>-867204</v>
       </c>
       <c r="E41" t="n">
-        <v>-208000</v>
+        <v>-87213</v>
       </c>
       <c r="F41" t="n">
-        <v>-1248333</v>
+        <v>-889499</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>穎崴</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -980 千股)</t>
+          <t>📉 20d 巨變(減碼 -6,336 千股)</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>394545</v>
+        <v>7029659</v>
       </c>
       <c r="D42" t="n">
-        <v>3858187</v>
+        <v>55704981</v>
       </c>
       <c r="E42" t="n">
-        <v>408831</v>
+        <v>10210053</v>
       </c>
       <c r="F42" t="n">
-        <v>4837820</v>
+        <v>62041285</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 175 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -3,508 千股)</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>142063</v>
+        <v>-487181</v>
       </c>
       <c r="D43" t="n">
-        <v>-718735</v>
+        <v>350466</v>
       </c>
       <c r="E43" t="n">
-        <v>-367938</v>
+        <v>394545</v>
       </c>
       <c r="F43" t="n">
-        <v>-893664</v>
+        <v>3858187</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 13 千股)</t>
+          <t>📉 20d 巨變(減碼 -59 千股)</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-198901</v>
+        <v>245835</v>
       </c>
       <c r="D44" t="n">
-        <v>56007</v>
+        <v>-777337</v>
       </c>
       <c r="E44" t="n">
-        <v>-288588</v>
+        <v>142063</v>
       </c>
       <c r="F44" t="n">
-        <v>43148</v>
+        <v>-718735</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>亞力</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,448 千股)</t>
+          <t>📈 20d 巨變(加碼 37 千股)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1969542</v>
+        <v>-115072</v>
       </c>
       <c r="D45" t="n">
-        <v>3358603</v>
+        <v>-1253405</v>
       </c>
       <c r="E45" t="n">
-        <v>1072224</v>
+        <v>-233072</v>
       </c>
       <c r="F45" t="n">
-        <v>1910895</v>
+        <v>-1290405</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>聯合</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 111 千股)</t>
+          <t>📈 20d 巨變(加碼 273 千股)</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>93482</v>
+        <v>-56293</v>
       </c>
       <c r="D46" t="n">
-        <v>-119909</v>
+        <v>328665</v>
       </c>
       <c r="E46" t="n">
-        <v>73382</v>
+        <v>-198901</v>
       </c>
       <c r="F46" t="n">
-        <v>-231237</v>
+        <v>56007</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>大綜</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 22 千股)</t>
+          <t>📈 20d 巨變(加碼 283 千股)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2870651</v>
+        <v>266252</v>
       </c>
       <c r="D47" t="n">
-        <v>4419187</v>
+        <v>163102</v>
       </c>
       <c r="E47" t="n">
-        <v>3365468</v>
+        <v>93482</v>
       </c>
       <c r="F47" t="n">
-        <v>4397470</v>
+        <v>-119909</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>漢科</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,974 千股)</t>
+          <t>📈 20d 巨變(加碼 2,020 千股)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-6150088</v>
+        <v>1821272</v>
       </c>
       <c r="D48" t="n">
-        <v>702689</v>
+        <v>5378978</v>
       </c>
       <c r="E48" t="n">
-        <v>-7219533</v>
+        <v>1969542</v>
       </c>
       <c r="F48" t="n">
-        <v>2676611</v>
+        <v>3358603</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>台燿</t>
         </is>
       </c>
     </row>
@@ -7162,20 +7162,20 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -753 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,365 千股)</t>
         </is>
       </c>
       <c r="C49" t="n">
+        <v>-1095412</v>
+      </c>
+      <c r="D49" t="n">
+        <v>-1471024</v>
+      </c>
+      <c r="E49" t="n">
         <v>-1419061</v>
       </c>
-      <c r="D49" t="n">
+      <c r="F49" t="n">
         <v>-106456</v>
-      </c>
-      <c r="E49" t="n">
-        <v>-2514008</v>
-      </c>
-      <c r="F49" t="n">
-        <v>646185</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -7186,29 +7186,29 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -449 千股)</t>
+          <t>📉 20d 巨變(減碼 -12,021 千股)</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-2654576</v>
+        <v>-4481844</v>
       </c>
       <c r="D50" t="n">
-        <v>-3310973</v>
+        <v>-11318698</v>
       </c>
       <c r="E50" t="n">
-        <v>-2214807</v>
+        <v>-6150088</v>
       </c>
       <c r="F50" t="n">
-        <v>-2861924</v>
+        <v>702689</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
@@ -7220,20 +7220,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,808 千股)</t>
+          <t>📈 20d 巨變(加碼 2,537 千股)</t>
         </is>
       </c>
       <c r="C51" t="n">
+        <v>-3002894</v>
+      </c>
+      <c r="D51" t="n">
+        <v>-16853262</v>
+      </c>
+      <c r="E51" t="n">
         <v>-11012367</v>
       </c>
-      <c r="D51" t="n">
+      <c r="F51" t="n">
         <v>-19390009</v>
-      </c>
-      <c r="E51" t="n">
-        <v>-10907438</v>
-      </c>
-      <c r="F51" t="n">
-        <v>-22197565</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -7244,638 +7244,638 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -25,969 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 2,758 千股)</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-21478390</v>
+        <v>1889496</v>
       </c>
       <c r="D52" t="n">
-        <v>-18020476</v>
+        <v>-553262</v>
       </c>
       <c r="E52" t="n">
-        <v>-24297060</v>
+        <v>-2654576</v>
       </c>
       <c r="F52" t="n">
-        <v>7948555</v>
+        <v>-3310973</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>世芯-KY</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,393 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 26,200 千股)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-8087993</v>
+        <v>23857230</v>
       </c>
       <c r="D53" t="n">
-        <v>27410116</v>
+        <v>8179766</v>
       </c>
       <c r="E53" t="n">
-        <v>-5780922</v>
+        <v>-21478390</v>
       </c>
       <c r="F53" t="n">
-        <v>26017364</v>
+        <v>-18020476</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -337 千股)</t>
+          <t>📈 20d 巨變(加碼 583 千股)</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-1264152</v>
+        <v>2643273</v>
       </c>
       <c r="D54" t="n">
-        <v>941808</v>
+        <v>5002112</v>
       </c>
       <c r="E54" t="n">
-        <v>-764534</v>
+        <v>2870651</v>
       </c>
       <c r="F54" t="n">
-        <v>1278873</v>
+        <v>4419187</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>立隆電</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 237 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 4,799 千股)</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>173437</v>
+        <v>7179234</v>
       </c>
       <c r="D55" t="n">
-        <v>2303928</v>
+        <v>32209473</v>
       </c>
       <c r="E55" t="n">
-        <v>-1138518</v>
+        <v>-8087993</v>
       </c>
       <c r="F55" t="n">
-        <v>2067082</v>
+        <v>27410116</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 578 千股)</t>
+          <t>📉 20d 巨變(減碼 -157 千股)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-548154</v>
+        <v>846571</v>
       </c>
       <c r="D56" t="n">
-        <v>-1816506</v>
+        <v>2147303</v>
       </c>
       <c r="E56" t="n">
-        <v>-763977</v>
+        <v>173437</v>
       </c>
       <c r="F56" t="n">
-        <v>-2394805</v>
+        <v>2303928</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>鈊象</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -74 千股)</t>
+          <t>📉 20d 巨變(減碼 -557 千股)</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-65025</v>
+        <v>-1278685</v>
       </c>
       <c r="D57" t="n">
-        <v>-52636</v>
+        <v>385182</v>
       </c>
       <c r="E57" t="n">
-        <v>-40915</v>
+        <v>-1264152</v>
       </c>
       <c r="F57" t="n">
-        <v>21085</v>
+        <v>941808</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>士電</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -47 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 1,554 千股)</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>18755</v>
+        <v>71250</v>
       </c>
       <c r="D58" t="n">
-        <v>349108</v>
+        <v>-262634</v>
       </c>
       <c r="E58" t="n">
-        <v>16874</v>
+        <v>-548154</v>
       </c>
       <c r="F58" t="n">
-        <v>395694</v>
+        <v>-1816506</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>鉅祥</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 247 千股)</t>
+          <t>📉 20d 巨變(減碼 -150 千股)</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-196561</v>
+        <v>-100410</v>
       </c>
       <c r="D59" t="n">
-        <v>-1525136</v>
+        <v>-202299</v>
       </c>
       <c r="E59" t="n">
-        <v>-398351</v>
+        <v>-65025</v>
       </c>
       <c r="F59" t="n">
-        <v>-1771926</v>
+        <v>-52636</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>達欣工</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -219 千股)</t>
+          <t>📉 20d 巨變(減碼 -9 千股)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-450270</v>
+        <v>44755</v>
       </c>
       <c r="D60" t="n">
-        <v>-744778</v>
+        <v>339880</v>
       </c>
       <c r="E60" t="n">
-        <v>-240446</v>
+        <v>18755</v>
       </c>
       <c r="F60" t="n">
-        <v>-525650</v>
+        <v>349108</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>普萊德</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 245 千股)</t>
+          <t>📉 20d 巨變(減碼 -368 千股)</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>783680</v>
+        <v>-791032</v>
       </c>
       <c r="D61" t="n">
-        <v>642442</v>
+        <v>-1112427</v>
       </c>
       <c r="E61" t="n">
-        <v>449305</v>
+        <v>-450270</v>
       </c>
       <c r="F61" t="n">
-        <v>397599</v>
+        <v>-744778</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -392 千股)</t>
+          <t>📉 20d 巨變(減碼 -46 千股)</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>62768</v>
+        <v>-61789</v>
       </c>
       <c r="D62" t="n">
-        <v>-1978692</v>
+        <v>-1571422</v>
       </c>
       <c r="E62" t="n">
-        <v>-242464</v>
+        <v>-196561</v>
       </c>
       <c r="F62" t="n">
-        <v>-1586899</v>
+        <v>-1525136</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>勝一</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -148 千股)</t>
+          <t>📈 20d 巨變(加碼 391 千股)</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-224950</v>
+        <v>1199979</v>
       </c>
       <c r="D63" t="n">
-        <v>-2840237</v>
+        <v>1033520</v>
       </c>
       <c r="E63" t="n">
-        <v>92408</v>
+        <v>783680</v>
       </c>
       <c r="F63" t="n">
-        <v>-2692420</v>
+        <v>642442</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>祥碩</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -12 千股)</t>
+          <t>📈 20d 巨變(加碼 261 千股)</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>840037</v>
+        <v>83818</v>
       </c>
       <c r="D64" t="n">
-        <v>-3673287</v>
+        <v>-1717742</v>
       </c>
       <c r="E64" t="n">
-        <v>691770</v>
+        <v>62768</v>
       </c>
       <c r="F64" t="n">
-        <v>-3661689</v>
+        <v>-1978692</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>信立</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -854 千股)</t>
+          <t>📉 20d 巨變(減碼 -9,458 千股)</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-4480149</v>
+        <v>-9193144</v>
       </c>
       <c r="D65" t="n">
-        <v>-1599352</v>
+        <v>-12297744</v>
       </c>
       <c r="E65" t="n">
-        <v>-1769102</v>
+        <v>-224950</v>
       </c>
       <c r="F65" t="n">
-        <v>-745763</v>
+        <v>-2840237</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,184 千股)</t>
+          <t>📈 20d 巨變(加碼 1,723 千股)</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-969316</v>
+        <v>1449962</v>
       </c>
       <c r="D66" t="n">
-        <v>-1303812</v>
+        <v>-1950492</v>
       </c>
       <c r="E66" t="n">
-        <v>-952719</v>
+        <v>840037</v>
       </c>
       <c r="F66" t="n">
-        <v>-119917</v>
+        <v>-3673287</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>華星光</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 6,340 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,043 千股)</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>6120524</v>
+        <v>-4714730</v>
       </c>
       <c r="D67" t="n">
-        <v>31972283</v>
+        <v>-2642776</v>
       </c>
       <c r="E67" t="n">
-        <v>-176747</v>
+        <v>-4480149</v>
       </c>
       <c r="F67" t="n">
-        <v>25631958</v>
+        <v>-1599352</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -576 千股)</t>
+          <t>📉 20d 巨變(減碼 -225 千股)</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-2150375</v>
+        <v>-1386123</v>
       </c>
       <c r="D68" t="n">
-        <v>-1549813</v>
+        <v>-1528898</v>
       </c>
       <c r="E68" t="n">
-        <v>-1623268</v>
+        <v>-969316</v>
       </c>
       <c r="F68" t="n">
-        <v>-973985</v>
+        <v>-1303812</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>宇瞻</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 14,133 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -5,832 千股)</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-12324778</v>
+        <v>-670768</v>
       </c>
       <c r="D69" t="n">
-        <v>-100782356</v>
+        <v>26140424</v>
       </c>
       <c r="E69" t="n">
-        <v>-54905250</v>
+        <v>6120524</v>
       </c>
       <c r="F69" t="n">
-        <v>-114915491</v>
+        <v>31972283</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 3,506 千股)</t>
+          <t>📉 20d 巨變(減碼 -58 千股)</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>4076684</v>
+        <v>-2292711</v>
       </c>
       <c r="D70" t="n">
-        <v>3253326</v>
+        <v>-1607776</v>
       </c>
       <c r="E70" t="n">
-        <v>3092866</v>
+        <v>-2150375</v>
       </c>
       <c r="F70" t="n">
-        <v>-252814</v>
+        <v>-1549813</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>聯亞</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 7,774 千股)</t>
+          <t>📈 20d 巨變(加碼 356 千股)</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-4067225</v>
+        <v>4440229</v>
       </c>
       <c r="D71" t="n">
-        <v>-15352223</v>
+        <v>3609811</v>
       </c>
       <c r="E71" t="n">
-        <v>-4802590</v>
+        <v>4076684</v>
       </c>
       <c r="F71" t="n">
-        <v>-23125948</v>
+        <v>3253326</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -6 千股)</t>
+          <t>📈 20d 巨變(加碼 6,090 千股)</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>23945</v>
+        <v>-19086172</v>
       </c>
       <c r="D72" t="n">
-        <v>-4634763</v>
+        <v>-94692066</v>
       </c>
       <c r="E72" t="n">
-        <v>-3969403</v>
+        <v>-12324778</v>
       </c>
       <c r="F72" t="n">
-        <v>-4629221</v>
+        <v>-100782356</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠</t>
+          <t>📉 20d 巨變(減碼 -3,487 千股)</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>25049</v>
+        <v>-6506870</v>
       </c>
       <c r="D73" t="n">
-        <v>761857</v>
+        <v>-18839137</v>
       </c>
       <c r="E73" t="n">
-        <v>-177232</v>
+        <v>-4067225</v>
       </c>
       <c r="F73" t="n">
-        <v>760966</v>
+        <v>-15352223</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
@@ -7887,20 +7887,20 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -40 千股)</t>
+          <t>🟢 外資 5d 翻綠</t>
         </is>
       </c>
       <c r="C74" t="n">
+        <v>25354</v>
+      </c>
+      <c r="D74" t="n">
+        <v>-456187</v>
+      </c>
+      <c r="E74" t="n">
         <v>-55689</v>
       </c>
-      <c r="D74" t="n">
+      <c r="F74" t="n">
         <v>-453604</v>
-      </c>
-      <c r="E74" t="n">
-        <v>-140115</v>
-      </c>
-      <c r="F74" t="n">
-        <v>-413109</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -7911,145 +7911,145 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 13 千股)</t>
+          <t>📈 20d 巨變(加碼 128 千股)</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>38000</v>
+        <v>155354</v>
       </c>
       <c r="D75" t="n">
-        <v>-48550</v>
+        <v>889910</v>
       </c>
       <c r="E75" t="n">
-        <v>34000</v>
+        <v>25049</v>
       </c>
       <c r="F75" t="n">
-        <v>-61550</v>
+        <v>761857</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>億泰</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -132 千股)</t>
+          <t>📈 20d 巨變(加碼 30 千股)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-842786</v>
+        <v>796929</v>
       </c>
       <c r="D76" t="n">
-        <v>-3067772</v>
+        <v>-4604889</v>
       </c>
       <c r="E76" t="n">
-        <v>-814586</v>
+        <v>23945</v>
       </c>
       <c r="F76" t="n">
-        <v>-2935709</v>
+        <v>-4634763</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 272 千股)</t>
+          <t>📉 20d 巨變(減碼 -38 千股)</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-557950</v>
+        <v>16929</v>
       </c>
       <c r="D77" t="n">
-        <v>-8068145</v>
+        <v>-86071</v>
       </c>
       <c r="E77" t="n">
-        <v>-1205919</v>
+        <v>38000</v>
       </c>
       <c r="F77" t="n">
-        <v>-8340490</v>
+        <v>-48550</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>友輝</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,128 千股)</t>
+          <t>📈 20d 巨變(加碼 274 千股)</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-1201435</v>
+        <v>-780000</v>
       </c>
       <c r="D78" t="n">
-        <v>344541</v>
+        <v>-7794145</v>
       </c>
       <c r="E78" t="n">
-        <v>-2742460</v>
+        <v>-557950</v>
       </c>
       <c r="F78" t="n">
-        <v>-783949</v>
+        <v>-8068145</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>智易</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 464 千股)</t>
+          <t>📉 20d 巨變(減碼 -296 千股)</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-3219142</v>
+        <v>-1377519</v>
       </c>
       <c r="D79" t="n">
-        <v>-7531248</v>
+        <v>48455</v>
       </c>
       <c r="E79" t="n">
-        <v>-10100528</v>
+        <v>-1201435</v>
       </c>
       <c r="F79" t="n">
-        <v>-7995207</v>
+        <v>344541</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
@@ -8061,20 +8061,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -93 千股)</t>
+          <t>📉 20d 巨變(減碼 -25 千股)</t>
         </is>
       </c>
       <c r="C80" t="n">
+        <v>247668</v>
+      </c>
+      <c r="D80" t="n">
+        <v>-1582668</v>
+      </c>
+      <c r="E80" t="n">
         <v>702002</v>
       </c>
-      <c r="D80" t="n">
+      <c r="F80" t="n">
         <v>-1558021</v>
-      </c>
-      <c r="E80" t="n">
-        <v>767117</v>
-      </c>
-      <c r="F80" t="n">
-        <v>-1464671</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -8085,87 +8085,87 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 13,122 千股)</t>
+          <t>📉 20d 巨變(減碼 -4,063 千股)</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1227270</v>
+        <v>-3938296</v>
       </c>
       <c r="D81" t="n">
-        <v>1125790</v>
+        <v>-11594702</v>
       </c>
       <c r="E81" t="n">
-        <v>-11047969</v>
+        <v>-3219142</v>
       </c>
       <c r="F81" t="n">
-        <v>-11995730</v>
+        <v>-7531248</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -12 千股)</t>
+          <t>📈 20d 巨變(加碼 508 千股)</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>267000</v>
+        <v>-637403</v>
       </c>
       <c r="D82" t="n">
-        <v>504404</v>
+        <v>-2559521</v>
       </c>
       <c r="E82" t="n">
-        <v>356000</v>
+        <v>-842786</v>
       </c>
       <c r="F82" t="n">
-        <v>516524</v>
+        <v>-3067772</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>原相</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -60 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -3,169 千股)</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>2000</v>
+        <v>-1719450</v>
       </c>
       <c r="D83" t="n">
-        <v>232009</v>
+        <v>-2042935</v>
       </c>
       <c r="E83" t="n">
-        <v>-84000</v>
+        <v>1227270</v>
       </c>
       <c r="F83" t="n">
-        <v>292009</v>
+        <v>1125790</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
@@ -8177,20 +8177,20 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 254 千股)</t>
+          <t>📈 20d 巨變(加碼 15 千股)</t>
         </is>
       </c>
       <c r="C84" t="n">
+        <v>70991</v>
+      </c>
+      <c r="D84" t="n">
+        <v>-606828</v>
+      </c>
+      <c r="E84" t="n">
         <v>128107</v>
       </c>
-      <c r="D84" t="n">
+      <c r="F84" t="n">
         <v>-622118</v>
-      </c>
-      <c r="E84" t="n">
-        <v>-169583</v>
-      </c>
-      <c r="F84" t="n">
-        <v>-876233</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -8201,348 +8201,348 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,068 千股)</t>
+          <t>📈 20d 巨變(加碼 160 千股)</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>6553274</v>
+        <v>199000</v>
       </c>
       <c r="D85" t="n">
-        <v>6489230</v>
+        <v>664404</v>
       </c>
       <c r="E85" t="n">
-        <v>6624646</v>
+        <v>267000</v>
       </c>
       <c r="F85" t="n">
-        <v>4421604</v>
+        <v>504404</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>東科-KY</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 949 千股)</t>
+          <t>📈 20d 巨變(加碼 2,397 千股)</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-920644</v>
+        <v>8072182</v>
       </c>
       <c r="D86" t="n">
-        <v>-10612251</v>
+        <v>8885812</v>
       </c>
       <c r="E86" t="n">
-        <v>-2503223</v>
+        <v>6553274</v>
       </c>
       <c r="F86" t="n">
-        <v>-11561252</v>
+        <v>6489230</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,984 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -85 千股)</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>3521318</v>
+        <v>-6000</v>
       </c>
       <c r="D87" t="n">
-        <v>3803322</v>
+        <v>147009</v>
       </c>
       <c r="E87" t="n">
-        <v>2306190</v>
+        <v>2000</v>
       </c>
       <c r="F87" t="n">
-        <v>1819068</v>
+        <v>232009</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 9,778 千股)</t>
+          <t>📈 20d 巨變(加碼 5 千股)</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>49524280</v>
+        <v>2673600</v>
       </c>
       <c r="D88" t="n">
-        <v>70894993</v>
+        <v>3808580</v>
       </c>
       <c r="E88" t="n">
-        <v>43395130</v>
+        <v>3521318</v>
       </c>
       <c r="F88" t="n">
-        <v>61116687</v>
+        <v>3803322</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>研華</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -101 千股)</t>
+          <t>📈 20d 巨變(加碼 8,074 千股)</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>10686</v>
+        <v>47016221</v>
       </c>
       <c r="D89" t="n">
-        <v>-185230</v>
+        <v>78969213</v>
       </c>
       <c r="E89" t="n">
-        <v>-183974</v>
+        <v>49524280</v>
       </c>
       <c r="F89" t="n">
-        <v>-84355</v>
+        <v>70894993</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -8 千股)</t>
+          <t>📈 20d 巨變(加碼 1,511 千股)</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-125920</v>
+        <v>-199668</v>
       </c>
       <c r="D90" t="n">
-        <v>-126768</v>
+        <v>-9101162</v>
       </c>
       <c r="E90" t="n">
-        <v>-123821</v>
+        <v>-920644</v>
       </c>
       <c r="F90" t="n">
-        <v>-118669</v>
+        <v>-10612251</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>宏捷科</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 788 千股)</t>
+          <t>📈 20d 巨變(加碼 66 千股)</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>39169</v>
+        <v>397516</v>
       </c>
       <c r="D91" t="n">
-        <v>-6243970</v>
+        <v>-119027</v>
       </c>
       <c r="E91" t="n">
-        <v>-616225</v>
+        <v>10686</v>
       </c>
       <c r="F91" t="n">
-        <v>-7031911</v>
+        <v>-185230</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>中保科</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 14 千股)</t>
+          <t>📈 20d 巨變(加碼 9 千股)</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>35353</v>
+        <v>-237413</v>
       </c>
       <c r="D92" t="n">
-        <v>69875</v>
+        <v>-117553</v>
       </c>
       <c r="E92" t="n">
-        <v>14345</v>
+        <v>-125920</v>
       </c>
       <c r="F92" t="n">
-        <v>55865</v>
+        <v>-126768</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>竹陞科技</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 51 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 43 千股)</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>5070</v>
+        <v>-29433</v>
       </c>
       <c r="D93" t="n">
-        <v>-59199</v>
+        <v>113112</v>
       </c>
       <c r="E93" t="n">
-        <v>-89930</v>
+        <v>35353</v>
       </c>
       <c r="F93" t="n">
-        <v>-109975</v>
+        <v>69875</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>安碁資訊</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 560 千股)</t>
+          <t>📈 20d 巨變(加碼 5 千股)</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>290258</v>
+        <v>27091</v>
       </c>
       <c r="D94" t="n">
-        <v>6054546</v>
+        <v>-54178</v>
       </c>
       <c r="E94" t="n">
-        <v>1706793</v>
+        <v>5070</v>
       </c>
       <c r="F94" t="n">
-        <v>5494945</v>
+        <v>-59199</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>六方科-KY</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,226 千股)</t>
+          <t>📈 20d 巨變(加碼 543 千股)</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3556484</v>
+        <v>182483</v>
       </c>
       <c r="D95" t="n">
-        <v>18161267</v>
+        <v>-5701351</v>
       </c>
       <c r="E95" t="n">
-        <v>3420405</v>
+        <v>39169</v>
       </c>
       <c r="F95" t="n">
-        <v>19386872</v>
+        <v>-6243970</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -54 千股)</t>
+          <t>📈 20d 巨變(加碼 43 千股)</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-835460</v>
+        <v>3046371</v>
       </c>
       <c r="D96" t="n">
-        <v>-161986</v>
+        <v>18204028</v>
       </c>
       <c r="E96" t="n">
-        <v>-283090</v>
+        <v>3556484</v>
       </c>
       <c r="F96" t="n">
-        <v>-107715</v>
+        <v>18161267</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
@@ -8554,20 +8554,20 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -33,382 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 27,853 千股)</t>
         </is>
       </c>
       <c r="C97" t="n">
+        <v>4640801</v>
+      </c>
+      <c r="D97" t="n">
+        <v>7419144</v>
+      </c>
+      <c r="E97" t="n">
         <v>-69311123</v>
       </c>
-      <c r="D97" t="n">
+      <c r="F97" t="n">
         <v>-20433393</v>
-      </c>
-      <c r="E97" t="n">
-        <v>-64654213</v>
-      </c>
-      <c r="F97" t="n">
-        <v>12948485</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -8578,145 +8578,203 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -84 千股)</t>
+          <t>📈 20d 巨變(加碼 3,162 千股)</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-98233</v>
+        <v>3918493</v>
       </c>
       <c r="D98" t="n">
-        <v>167885</v>
+        <v>9216467</v>
       </c>
       <c r="E98" t="n">
-        <v>-24347</v>
+        <v>290258</v>
       </c>
       <c r="F98" t="n">
-        <v>251782</v>
+        <v>6054546</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 172 千股)</t>
+          <t>📉 20d 巨變(減碼 -673 千股)</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-4314230</v>
+        <v>-1183926</v>
       </c>
       <c r="D99" t="n">
-        <v>-12895569</v>
+        <v>-835387</v>
       </c>
       <c r="E99" t="n">
-        <v>-4866091</v>
+        <v>-835460</v>
       </c>
       <c r="F99" t="n">
-        <v>-13067663</v>
+        <v>-161986</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>創意</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 10 千股)</t>
+          <t>📉 20d 巨變(減碼 -210 千股)</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-30968</v>
+        <v>-4139047</v>
       </c>
       <c r="D100" t="n">
-        <v>-3404039</v>
+        <v>-13105329</v>
       </c>
       <c r="E100" t="n">
-        <v>-24336</v>
+        <v>-4314230</v>
       </c>
       <c r="F100" t="n">
-        <v>-3414486</v>
+        <v>-12895569</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>緯穎</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -2,730 千股)</t>
+          <t>📉 20d 巨變(減碼 -24 千股)</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-1360213</v>
+        <v>-67592</v>
       </c>
       <c r="D101" t="n">
-        <v>-9526438</v>
+        <v>144327</v>
       </c>
       <c r="E101" t="n">
-        <v>1671012</v>
+        <v>-98233</v>
       </c>
       <c r="F101" t="n">
-        <v>-6796663</v>
+        <v>167885</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>信驊</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>2368</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>📉 20d 巨變(減碼 -688 千股)</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>-2982060</v>
+      </c>
+      <c r="D102" t="n">
+        <v>-10214001</v>
+      </c>
+      <c r="E102" t="n">
+        <v>-1360213</v>
+      </c>
+      <c r="F102" t="n">
+        <v>-9526438</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>金像電</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
           <t>6187</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 187 千股)</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 67 千股)</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>-170103</v>
+      </c>
+      <c r="D103" t="n">
+        <v>-1175206</v>
+      </c>
+      <c r="E103" t="n">
         <v>18035</v>
       </c>
-      <c r="D102" t="n">
+      <c r="F103" t="n">
         <v>-1242501</v>
       </c>
-      <c r="E102" t="n">
-        <v>329662</v>
-      </c>
-      <c r="F102" t="n">
-        <v>-1429625</v>
-      </c>
-      <c r="G102" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>萬潤</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>5439</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>📈 20d 巨變(加碼 1,182 千股)</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>-59892</v>
+      </c>
+      <c r="D104" t="n">
+        <v>-2221564</v>
+      </c>
+      <c r="E104" t="n">
+        <v>-30968</v>
+      </c>
+      <c r="F104" t="n">
+        <v>-3404039</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>高技</t>
         </is>
       </c>
     </row>

--- a/data/台股_外資雷達.xlsx
+++ b/data/台股_外資雷達.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>47016</v>
+        <v>36242</v>
       </c>
       <c r="D2" t="n">
-        <v>78969</v>
+        <v>81555</v>
       </c>
       <c r="E2" t="n">
-        <v>164776</v>
+        <v>179344</v>
       </c>
       <c r="F2" t="n">
-        <v>-1970</v>
+        <v>-1752</v>
       </c>
       <c r="G2" t="n">
-        <v>-1143</v>
+        <v>-837</v>
       </c>
       <c r="H2" t="n">
-        <v>329</v>
+        <v>406</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -547,22 +547,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7030</v>
+        <v>7465</v>
       </c>
       <c r="D3" t="n">
-        <v>55705</v>
+        <v>52361</v>
       </c>
       <c r="E3" t="n">
-        <v>211228</v>
+        <v>222162</v>
       </c>
       <c r="F3" t="n">
-        <v>2467</v>
+        <v>2597</v>
       </c>
       <c r="G3" t="n">
-        <v>6579</v>
+        <v>6585</v>
       </c>
       <c r="H3" t="n">
-        <v>-3071</v>
+        <v>-3023</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7179</v>
+        <v>12311</v>
       </c>
       <c r="D4" t="n">
-        <v>32209</v>
+        <v>36769</v>
       </c>
       <c r="E4" t="n">
-        <v>-4699</v>
+        <v>5026</v>
       </c>
       <c r="F4" t="n">
-        <v>-2174</v>
+        <v>-1654</v>
       </c>
       <c r="G4" t="n">
-        <v>-11153</v>
+        <v>-11623</v>
       </c>
       <c r="H4" t="n">
-        <v>2053</v>
+        <v>3225</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -649,22 +649,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-671</v>
+        <v>-2226</v>
       </c>
       <c r="D5" t="n">
-        <v>26140</v>
+        <v>23707</v>
       </c>
       <c r="E5" t="n">
-        <v>-11669</v>
+        <v>-9555</v>
       </c>
       <c r="F5" t="n">
-        <v>12620</v>
+        <v>14039</v>
       </c>
       <c r="G5" t="n">
-        <v>19227</v>
+        <v>20795</v>
       </c>
       <c r="H5" t="n">
-        <v>1406</v>
+        <v>1428</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -700,22 +700,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3046</v>
+        <v>2188</v>
       </c>
       <c r="D6" t="n">
-        <v>18204</v>
+        <v>17229</v>
       </c>
       <c r="E6" t="n">
-        <v>105740</v>
+        <v>108148</v>
       </c>
       <c r="F6" t="n">
-        <v>-278</v>
+        <v>-121</v>
       </c>
       <c r="G6" t="n">
-        <v>-2329</v>
+        <v>-1525</v>
       </c>
       <c r="H6" t="n">
-        <v>-628</v>
+        <v>-610</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>573</v>
+        <v>332</v>
       </c>
       <c r="D7" t="n">
-        <v>15830</v>
+        <v>15635</v>
       </c>
       <c r="E7" t="n">
-        <v>22825</v>
+        <v>22830</v>
       </c>
       <c r="F7" t="n">
-        <v>-71</v>
+        <v>-81</v>
       </c>
       <c r="G7" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="H7" t="n">
-        <v>227</v>
+        <v>180</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -793,133 +793,133 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3918</v>
+        <v>28359</v>
       </c>
       <c r="D8" t="n">
-        <v>9216</v>
+        <v>15546</v>
       </c>
       <c r="E8" t="n">
-        <v>7933</v>
+        <v>89567</v>
       </c>
       <c r="F8" t="n">
-        <v>-479</v>
+        <v>3791</v>
       </c>
       <c r="G8" t="n">
-        <v>1676</v>
+        <v>-6247</v>
       </c>
       <c r="H8" t="n">
-        <v>1445</v>
+        <v>-2930</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>🟢 加碼</t>
+          <t>🚀 大買</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8072</v>
+        <v>6341</v>
       </c>
       <c r="D9" t="n">
-        <v>8886</v>
+        <v>12506</v>
       </c>
       <c r="E9" t="n">
-        <v>-1744</v>
+        <v>12158</v>
       </c>
       <c r="F9" t="n">
+        <v>-272</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2084</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1796</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>🚀 大買</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>44</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>📉 減速</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
         <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-8</v>
-      </c>
-      <c r="H9" t="n">
-        <v>668</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>🟢 加碼</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>75</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-1164</v>
+        <v>4273</v>
       </c>
       <c r="D10" t="n">
-        <v>8622</v>
+        <v>8801</v>
       </c>
       <c r="E10" t="n">
-        <v>11507</v>
+        <v>3918</v>
       </c>
       <c r="F10" t="n">
-        <v>25</v>
+        <v>-9366</v>
       </c>
       <c r="G10" t="n">
-        <v>929</v>
+        <v>-19913</v>
       </c>
       <c r="H10" t="n">
-        <v>1178</v>
+        <v>1046</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -928,49 +928,49 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23857</v>
+        <v>7638</v>
       </c>
       <c r="D11" t="n">
-        <v>8180</v>
+        <v>8730</v>
       </c>
       <c r="E11" t="n">
-        <v>90947</v>
+        <v>-582</v>
       </c>
       <c r="F11" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-5321</v>
+        <v>-8</v>
       </c>
       <c r="H11" t="n">
-        <v>-3333</v>
+        <v>641</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -979,11 +979,11 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -997,31 +997,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4641</v>
+        <v>-1083</v>
       </c>
       <c r="D12" t="n">
-        <v>7419</v>
+        <v>7730</v>
       </c>
       <c r="E12" t="n">
-        <v>61096</v>
+        <v>12033</v>
       </c>
       <c r="F12" t="n">
-        <v>-13760</v>
+        <v>145</v>
       </c>
       <c r="G12" t="n">
-        <v>-33149</v>
+        <v>918</v>
       </c>
       <c r="H12" t="n">
-        <v>-2282</v>
+        <v>1213</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1030,49 +1030,49 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-15045</v>
+        <v>559</v>
       </c>
       <c r="D13" t="n">
-        <v>5940</v>
+        <v>5651</v>
       </c>
       <c r="E13" t="n">
-        <v>551158</v>
+        <v>24797</v>
       </c>
       <c r="F13" t="n">
-        <v>16024</v>
+        <v>1254</v>
       </c>
       <c r="G13" t="n">
-        <v>29279</v>
+        <v>809</v>
       </c>
       <c r="H13" t="n">
-        <v>-2052</v>
+        <v>203</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1085,11 +1085,11 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -1099,31 +1099,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1821</v>
+        <v>4990</v>
       </c>
       <c r="D14" t="n">
-        <v>5379</v>
+        <v>4920</v>
       </c>
       <c r="E14" t="n">
-        <v>602</v>
+        <v>-911</v>
       </c>
       <c r="F14" t="n">
-        <v>-4685</v>
+        <v>-0</v>
       </c>
       <c r="G14" t="n">
-        <v>-15536</v>
+        <v>2238</v>
       </c>
       <c r="H14" t="n">
-        <v>964</v>
+        <v>-99</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1132,49 +1132,49 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>329</v>
+        <v>1933</v>
       </c>
       <c r="D15" t="n">
-        <v>5248</v>
+        <v>4726</v>
       </c>
       <c r="E15" t="n">
-        <v>24396</v>
+        <v>14532</v>
       </c>
       <c r="F15" t="n">
-        <v>859</v>
+        <v>-2728</v>
       </c>
       <c r="G15" t="n">
-        <v>343</v>
+        <v>-7274</v>
       </c>
       <c r="H15" t="n">
-        <v>82</v>
+        <v>-55</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1183,49 +1183,49 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2643</v>
+        <v>3250</v>
       </c>
       <c r="D16" t="n">
-        <v>5002</v>
+        <v>4273</v>
       </c>
       <c r="E16" t="n">
-        <v>14841</v>
+        <v>2168</v>
       </c>
       <c r="F16" t="n">
-        <v>-2572</v>
+        <v>-135</v>
       </c>
       <c r="G16" t="n">
-        <v>-6618</v>
+        <v>637</v>
       </c>
       <c r="H16" t="n">
-        <v>-45</v>
+        <v>13</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1234,49 +1234,49 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2674</v>
+        <v>115</v>
       </c>
       <c r="D17" t="n">
-        <v>3809</v>
+        <v>2638</v>
       </c>
       <c r="E17" t="n">
-        <v>1502</v>
+        <v>6225</v>
       </c>
       <c r="F17" t="n">
-        <v>-162</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>578</v>
+        <v>-359</v>
       </c>
       <c r="H17" t="n">
-        <v>-68</v>
+        <v>51</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1285,11 +1285,11 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1297,37 +1297,37 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4440</v>
+        <v>466</v>
       </c>
       <c r="D18" t="n">
-        <v>3610</v>
+        <v>2598</v>
       </c>
       <c r="E18" t="n">
-        <v>-2339</v>
+        <v>778</v>
       </c>
       <c r="F18" t="n">
-        <v>22</v>
+        <v>896</v>
       </c>
       <c r="G18" t="n">
-        <v>2246</v>
+        <v>1032</v>
       </c>
       <c r="H18" t="n">
-        <v>-213</v>
+        <v>-144</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1336,155 +1336,155 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>943</v>
+        <v>700</v>
       </c>
       <c r="D19" t="n">
-        <v>2907</v>
+        <v>1856</v>
       </c>
       <c r="E19" t="n">
-        <v>6197</v>
+        <v>10669</v>
       </c>
       <c r="F19" t="n">
-        <v>9</v>
+        <v>837</v>
       </c>
       <c r="G19" t="n">
-        <v>-359</v>
+        <v>-9847</v>
       </c>
       <c r="H19" t="n">
-        <v>121</v>
+        <v>19</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>🟢 加碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>97</v>
+        <v>66</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>847</v>
+        <v>322</v>
       </c>
       <c r="D20" t="n">
-        <v>2147</v>
+        <v>1849</v>
       </c>
       <c r="E20" t="n">
-        <v>11203</v>
+        <v>-2761</v>
       </c>
       <c r="F20" t="n">
-        <v>789</v>
+        <v>-190</v>
       </c>
       <c r="G20" t="n">
-        <v>-10799</v>
+        <v>-219</v>
       </c>
       <c r="H20" t="n">
-        <v>9</v>
+        <v>254</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>🟢 加碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-721</v>
+        <v>-14547</v>
       </c>
       <c r="D21" t="n">
-        <v>2084</v>
+        <v>1205</v>
       </c>
       <c r="E21" t="n">
-        <v>149</v>
+        <v>491027</v>
       </c>
       <c r="F21" t="n">
-        <v>676</v>
+        <v>17455</v>
       </c>
       <c r="G21" t="n">
-        <v>523</v>
+        <v>30296</v>
       </c>
       <c r="H21" t="n">
-        <v>-80</v>
+        <v>-2064</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>🟢 加碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1501,37 +1501,37 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>合機</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>138</v>
+        <v>193</v>
       </c>
       <c r="D22" t="n">
-        <v>1394</v>
+        <v>1088</v>
       </c>
       <c r="E22" t="n">
-        <v>-194</v>
+        <v>2241</v>
       </c>
       <c r="F22" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-45</v>
+        <v>-34</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1544,45 +1544,45 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-319</v>
+        <v>1133</v>
       </c>
       <c r="D23" t="n">
-        <v>1325</v>
+        <v>1081</v>
       </c>
       <c r="E23" t="n">
-        <v>-2102</v>
+        <v>2666</v>
       </c>
       <c r="F23" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="G23" t="n">
-        <v>16</v>
+        <v>234</v>
       </c>
       <c r="H23" t="n">
-        <v>280</v>
+        <v>-39</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1591,49 +1591,49 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>288</v>
+        <v>-447</v>
       </c>
       <c r="D24" t="n">
-        <v>1150</v>
+        <v>869</v>
       </c>
       <c r="E24" t="n">
-        <v>2027</v>
+        <v>3449</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>-487</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-1979</v>
       </c>
       <c r="H24" t="n">
-        <v>-33</v>
+        <v>-139</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1642,11 +1642,11 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1654,37 +1654,37 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-48</v>
+        <v>364</v>
       </c>
       <c r="D25" t="n">
-        <v>1084</v>
+        <v>865</v>
       </c>
       <c r="E25" t="n">
-        <v>8171</v>
+        <v>1211</v>
       </c>
       <c r="F25" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>-19</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>133</v>
+        <v>10</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1693,49 +1693,49 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1200</v>
+        <v>210</v>
       </c>
       <c r="D26" t="n">
-        <v>1034</v>
+        <v>863</v>
       </c>
       <c r="E26" t="n">
-        <v>2637</v>
+        <v>-280</v>
       </c>
       <c r="F26" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G26" t="n">
-        <v>235</v>
+        <v>47</v>
       </c>
       <c r="H26" t="n">
-        <v>-35</v>
+        <v>-49</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1744,11 +1744,11 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1756,37 +1756,37 @@
         </is>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>213</v>
+        <v>138</v>
       </c>
       <c r="D27" t="n">
-        <v>952</v>
+        <v>730</v>
       </c>
       <c r="E27" t="n">
-        <v>5298</v>
+        <v>-231</v>
       </c>
       <c r="F27" t="n">
-        <v>-96</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>2030</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>317</v>
+        <v>7</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1795,49 +1795,49 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>155</v>
+        <v>18</v>
       </c>
       <c r="D28" t="n">
-        <v>890</v>
+        <v>614</v>
       </c>
       <c r="E28" t="n">
-        <v>899</v>
+        <v>966</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>-827</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-2676</v>
       </c>
       <c r="H28" t="n">
-        <v>7</v>
+        <v>-30</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1846,49 +1846,49 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C29" t="n">
+        <v>852</v>
+      </c>
+      <c r="D29" t="n">
         <v>585</v>
       </c>
-      <c r="D29" t="n">
-        <v>752</v>
-      </c>
       <c r="E29" t="n">
-        <v>2886</v>
+        <v>-723</v>
       </c>
       <c r="F29" t="n">
-        <v>-5</v>
+        <v>-2342</v>
       </c>
       <c r="G29" t="n">
-        <v>-38</v>
+        <v>-3744</v>
       </c>
       <c r="H29" t="n">
-        <v>-44</v>
+        <v>355</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1897,49 +1897,49 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>478</v>
+        <v>582</v>
       </c>
       <c r="D30" t="n">
-        <v>706</v>
+        <v>496</v>
       </c>
       <c r="E30" t="n">
-        <v>-1558</v>
+        <v>2965</v>
       </c>
       <c r="F30" t="n">
-        <v>-555</v>
+        <v>-5</v>
       </c>
       <c r="G30" t="n">
-        <v>-144</v>
+        <v>-38</v>
       </c>
       <c r="H30" t="n">
-        <v>64</v>
+        <v>-39</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1948,49 +1948,49 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>199</v>
+        <v>-32</v>
       </c>
       <c r="D31" t="n">
-        <v>664</v>
+        <v>391</v>
       </c>
       <c r="E31" t="n">
-        <v>-338</v>
+        <v>5015</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>2031</v>
       </c>
       <c r="H31" t="n">
-        <v>6</v>
+        <v>281</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1999,49 +1999,49 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-37</v>
+        <v>60</v>
       </c>
       <c r="D32" t="n">
-        <v>622</v>
+        <v>354</v>
       </c>
       <c r="E32" t="n">
-        <v>677</v>
+        <v>1068</v>
       </c>
       <c r="F32" t="n">
-        <v>-492</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-2487</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-14</v>
+        <v>7</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2050,19 +2050,19 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="33">
@@ -2077,22 +2077,22 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-1279</v>
+        <v>-670</v>
       </c>
       <c r="D33" t="n">
-        <v>385</v>
+        <v>343</v>
       </c>
       <c r="E33" t="n">
-        <v>-737</v>
+        <v>-561</v>
       </c>
       <c r="F33" t="n">
-        <v>96</v>
+        <v>62</v>
       </c>
       <c r="G33" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="H33" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2119,31 +2119,31 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>682</v>
+        <v>305</v>
       </c>
       <c r="D34" t="n">
-        <v>362</v>
+        <v>316</v>
       </c>
       <c r="E34" t="n">
-        <v>-753</v>
+        <v>-1769</v>
       </c>
       <c r="F34" t="n">
-        <v>-1752</v>
+        <v>-1030</v>
       </c>
       <c r="G34" t="n">
-        <v>-3167</v>
+        <v>-608</v>
       </c>
       <c r="H34" t="n">
-        <v>306</v>
+        <v>68</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2164,37 +2164,37 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-487</v>
+        <v>197</v>
       </c>
       <c r="D35" t="n">
-        <v>350</v>
+        <v>286</v>
       </c>
       <c r="E35" t="n">
-        <v>9434</v>
+        <v>-576</v>
       </c>
       <c r="F35" t="n">
-        <v>855</v>
+        <v>103</v>
       </c>
       <c r="G35" t="n">
-        <v>-318</v>
+        <v>446</v>
       </c>
       <c r="H35" t="n">
-        <v>-57</v>
+        <v>125</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2203,70 +2203,70 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>45</v>
+        <v>278</v>
       </c>
       <c r="D36" t="n">
-        <v>340</v>
+        <v>225</v>
       </c>
       <c r="E36" t="n">
-        <v>844</v>
+        <v>-1897</v>
       </c>
       <c r="F36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>77</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
         <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>7</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
-        <v>74</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M36" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="37">
@@ -2281,13 +2281,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-56</v>
+        <v>-120</v>
       </c>
       <c r="D37" t="n">
-        <v>329</v>
+        <v>160</v>
       </c>
       <c r="E37" t="n">
-        <v>685</v>
+        <v>475</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2323,31 +2323,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>266</v>
+        <v>-64</v>
       </c>
       <c r="D38" t="n">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="E38" t="n">
-        <v>-2239</v>
+        <v>799</v>
       </c>
       <c r="F38" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-11</v>
+        <v>1</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M38" t="n">
@@ -2374,92 +2374,92 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-6</v>
+        <v>-35</v>
       </c>
       <c r="D39" t="n">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="E39" t="n">
-        <v>856</v>
+        <v>-313</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>311</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K39" t="n">
-        <v>77</v>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>🚀 加速器</t>
-        </is>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-68</v>
+        <v>33</v>
       </c>
       <c r="D40" t="n">
-        <v>144</v>
+        <v>84</v>
       </c>
       <c r="E40" t="n">
-        <v>-344</v>
+        <v>785</v>
       </c>
       <c r="F40" t="n">
-        <v>121</v>
+        <v>-23</v>
       </c>
       <c r="G40" t="n">
-        <v>254</v>
+        <v>-28</v>
       </c>
       <c r="H40" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>86</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>📉 減速</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2473,13 +2473,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-29</v>
+        <v>-44</v>
       </c>
       <c r="D41" t="n">
-        <v>113</v>
+        <v>60</v>
       </c>
       <c r="E41" t="n">
-        <v>168</v>
+        <v>127</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -2488,7 +2488,7 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2515,31 +2515,31 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>方土霖</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="E42" t="n">
-        <v>-1817</v>
+        <v>53</v>
       </c>
       <c r="F42" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>-1327</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2552,45 +2552,45 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-35</v>
+        <v>165</v>
       </c>
       <c r="D43" t="n">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="E43" t="n">
-        <v>759</v>
+        <v>-3516</v>
       </c>
       <c r="F43" t="n">
-        <v>-23</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>-28</v>
+        <v>-227</v>
       </c>
       <c r="H43" t="n">
-        <v>9</v>
+        <v>2370</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2599,100 +2599,100 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M43" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>方土霖</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>6</v>
+        <v>-1211</v>
       </c>
       <c r="D44" t="n">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="E44" t="n">
-        <v>57</v>
+        <v>-10850</v>
       </c>
       <c r="F44" t="n">
+        <v>432</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1131</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-257</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>90</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
         <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K44" t="n">
-        <v>89</v>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M44" t="n">
-        <v>-2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>大車隊</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-1378</v>
+        <v>-14</v>
       </c>
       <c r="D45" t="n">
-        <v>48</v>
+        <v>-6</v>
       </c>
       <c r="E45" t="n">
-        <v>2992</v>
+        <v>-22</v>
       </c>
       <c r="F45" t="n">
-        <v>-464</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>-1987</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-280</v>
+        <v>-1</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2701,11 +2701,11 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2713,37 +2713,37 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-349</v>
+        <v>77</v>
       </c>
       <c r="D46" t="n">
-        <v>38</v>
+        <v>-28</v>
       </c>
       <c r="E46" t="n">
-        <v>-948</v>
+        <v>-120</v>
       </c>
       <c r="F46" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>-274</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>26</v>
+        <v>-0</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2752,40 +2752,40 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-7</v>
+        <v>-20</v>
       </c>
       <c r="D47" t="n">
-        <v>8</v>
+        <v>-41</v>
       </c>
       <c r="E47" t="n">
-        <v>-18</v>
+        <v>682</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -2807,11 +2807,11 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M47" t="n">
@@ -2821,31 +2821,31 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C48" t="n">
+        <v>-166</v>
+      </c>
+      <c r="D48" t="n">
         <v>-42</v>
       </c>
-      <c r="D48" t="n">
-        <v>-13</v>
-      </c>
       <c r="E48" t="n">
-        <v>681</v>
+        <v>-1788</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>-171</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>-1649</v>
       </c>
       <c r="H48" t="n">
-        <v>-2</v>
+        <v>72</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2858,15 +2858,15 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -2881,13 +2881,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D49" t="n">
-        <v>-54</v>
+        <v>-56</v>
       </c>
       <c r="E49" t="n">
-        <v>-24</v>
+        <v>-11</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -2923,31 +2923,31 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>17</v>
+        <v>552</v>
       </c>
       <c r="D50" t="n">
-        <v>-86</v>
+        <v>-62</v>
       </c>
       <c r="E50" t="n">
-        <v>-213</v>
+        <v>-119679</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1306</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>-2066</v>
       </c>
       <c r="H50" t="n">
-        <v>-0</v>
+        <v>4838</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2956,49 +2956,49 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-237</v>
+        <v>-473</v>
       </c>
       <c r="D51" t="n">
-        <v>-118</v>
+        <v>-113</v>
       </c>
       <c r="E51" t="n">
-        <v>19</v>
+        <v>-1074</v>
       </c>
       <c r="F51" t="n">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c r="G51" t="n">
-        <v>50</v>
+        <v>-345</v>
       </c>
       <c r="H51" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3007,49 +3007,49 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>398</v>
+        <v>774</v>
       </c>
       <c r="D52" t="n">
-        <v>-119</v>
+        <v>-144</v>
       </c>
       <c r="E52" t="n">
-        <v>2871</v>
+        <v>-4918</v>
       </c>
       <c r="F52" t="n">
-        <v>-302</v>
+        <v>-29</v>
       </c>
       <c r="G52" t="n">
-        <v>-256</v>
+        <v>196</v>
       </c>
       <c r="H52" t="n">
-        <v>11</v>
+        <v>-53</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3062,11 +3062,11 @@
         </is>
       </c>
       <c r="K52" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M52" t="n">
@@ -3076,31 +3076,31 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>26</v>
+        <v>-40</v>
       </c>
       <c r="D53" t="n">
-        <v>-163</v>
+        <v>-156</v>
       </c>
       <c r="E53" t="n">
-        <v>360</v>
+        <v>-351</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>-29</v>
       </c>
       <c r="G53" t="n">
-        <v>-41</v>
+        <v>-277</v>
       </c>
       <c r="H53" t="n">
-        <v>-18</v>
+        <v>7</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3109,49 +3109,49 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>336</v>
+        <v>-212</v>
       </c>
       <c r="D54" t="n">
-        <v>-186</v>
+        <v>-167</v>
       </c>
       <c r="E54" t="n">
-        <v>-776</v>
+        <v>-41</v>
       </c>
       <c r="F54" t="n">
-        <v>105</v>
+        <v>17</v>
       </c>
       <c r="G54" t="n">
-        <v>447</v>
+        <v>50</v>
       </c>
       <c r="H54" t="n">
-        <v>126</v>
+        <v>42</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3160,49 +3160,49 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-100</v>
+        <v>272</v>
       </c>
       <c r="D55" t="n">
-        <v>-202</v>
+        <v>-172</v>
       </c>
       <c r="E55" t="n">
-        <v>-400</v>
+        <v>2785</v>
       </c>
       <c r="F55" t="n">
-        <v>-29</v>
+        <v>-319</v>
       </c>
       <c r="G55" t="n">
-        <v>-277</v>
+        <v>-255</v>
       </c>
       <c r="H55" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3215,45 +3215,45 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-115</v>
+        <v>49</v>
       </c>
       <c r="D56" t="n">
-        <v>-242</v>
+        <v>-178</v>
       </c>
       <c r="E56" t="n">
-        <v>1166</v>
+        <v>419</v>
       </c>
       <c r="F56" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>14</v>
+        <v>-40</v>
       </c>
       <c r="H56" t="n">
-        <v>5</v>
+        <v>-22</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3266,45 +3266,45 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>🐌 龜速*</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>71</v>
+        <v>-7603</v>
       </c>
       <c r="D57" t="n">
-        <v>-263</v>
+        <v>-201</v>
       </c>
       <c r="E57" t="n">
-        <v>-4829</v>
+        <v>89826</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>1162</v>
       </c>
       <c r="G57" t="n">
-        <v>-227</v>
+        <v>5134</v>
       </c>
       <c r="H57" t="n">
-        <v>2421</v>
+        <v>-1500</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3325,37 +3325,37 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-25</v>
+        <v>-80</v>
       </c>
       <c r="D58" t="n">
-        <v>-441</v>
+        <v>-349</v>
       </c>
       <c r="E58" t="n">
-        <v>-825</v>
+        <v>1245</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H58" t="n">
-        <v>-5</v>
+        <v>4</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3368,45 +3368,45 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🐌 龜速*</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>25</v>
+        <v>-1457</v>
       </c>
       <c r="D59" t="n">
-        <v>-456</v>
+        <v>-432</v>
       </c>
       <c r="E59" t="n">
-        <v>-1893</v>
+        <v>8818</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>847</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>-316</v>
       </c>
       <c r="H59" t="n">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3415,15 +3415,15 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>79</v>
+        <v>57</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M59" t="n">
@@ -3433,22 +3433,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>智冠</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>156</v>
+        <v>-19</v>
       </c>
       <c r="D60" t="n">
-        <v>-465</v>
+        <v>-432</v>
       </c>
       <c r="E60" t="n">
-        <v>-2293</v>
+        <v>-812</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -3457,7 +3457,7 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-54</v>
+        <v>-3</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3470,11 +3470,11 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M60" t="n">
@@ -3484,31 +3484,31 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="D61" t="n">
-        <v>-524</v>
+        <v>-477</v>
       </c>
       <c r="E61" t="n">
-        <v>-6970</v>
+        <v>-1920</v>
       </c>
       <c r="F61" t="n">
-        <v>-243</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>156</v>
+        <v>-51</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3517,49 +3517,49 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>德昌</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1889</v>
+        <v>4</v>
       </c>
       <c r="D62" t="n">
-        <v>-553</v>
+        <v>-482</v>
       </c>
       <c r="E62" t="n">
-        <v>-1529</v>
+        <v>-1839</v>
       </c>
       <c r="F62" t="n">
-        <v>-2680</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>-2579</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>186</v>
+        <v>-1</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3568,40 +3568,40 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>71</v>
+        <v>-56</v>
       </c>
       <c r="D63" t="n">
-        <v>-607</v>
+        <v>-518</v>
       </c>
       <c r="E63" t="n">
-        <v>1745</v>
+        <v>-2592</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -3610,7 +3610,7 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-204</v>
+        <v>-33</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3619,11 +3619,11 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -3631,37 +3631,37 @@
         </is>
       </c>
       <c r="M63" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-159</v>
+        <v>-949</v>
       </c>
       <c r="D64" t="n">
-        <v>-633</v>
+        <v>-598</v>
       </c>
       <c r="E64" t="n">
-        <v>-3158</v>
+        <v>539</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>678</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="H64" t="n">
-        <v>-32</v>
+        <v>-126</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3670,49 +3670,49 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>246</v>
+        <v>1275</v>
       </c>
       <c r="D65" t="n">
-        <v>-777</v>
+        <v>-669</v>
       </c>
       <c r="E65" t="n">
-        <v>-5627</v>
+        <v>6992</v>
       </c>
       <c r="F65" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="G65" t="n">
-        <v>196</v>
+        <v>-19</v>
       </c>
       <c r="H65" t="n">
-        <v>-67</v>
+        <v>78</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3721,49 +3721,49 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-1184</v>
+        <v>1373</v>
       </c>
       <c r="D66" t="n">
-        <v>-835</v>
+        <v>-711</v>
       </c>
       <c r="E66" t="n">
-        <v>200</v>
+        <v>-1345</v>
       </c>
       <c r="F66" t="n">
-        <v>1001</v>
+        <v>-2708</v>
       </c>
       <c r="G66" t="n">
-        <v>1585</v>
+        <v>-2606</v>
       </c>
       <c r="H66" t="n">
-        <v>-111</v>
+        <v>254</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3776,45 +3776,45 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-44</v>
+        <v>-670</v>
       </c>
       <c r="D67" t="n">
-        <v>-867</v>
+        <v>-888</v>
       </c>
       <c r="E67" t="n">
-        <v>761</v>
+        <v>-7403</v>
       </c>
       <c r="F67" t="n">
-        <v>-223</v>
+        <v>-26</v>
       </c>
       <c r="G67" t="n">
-        <v>554</v>
+        <v>79</v>
       </c>
       <c r="H67" t="n">
-        <v>23</v>
+        <v>378</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3823,49 +3823,49 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M67" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-245</v>
+        <v>108</v>
       </c>
       <c r="D68" t="n">
-        <v>-867</v>
+        <v>-939</v>
       </c>
       <c r="E68" t="n">
-        <v>-7766</v>
+        <v>1629</v>
       </c>
       <c r="F68" t="n">
-        <v>-2206</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>-8332</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>333</v>
+        <v>-216</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3874,49 +3874,49 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="D69" t="n">
-        <v>-877</v>
+        <v>-984</v>
       </c>
       <c r="E69" t="n">
-        <v>-1636</v>
+        <v>1432</v>
       </c>
       <c r="F69" t="n">
-        <v>-255</v>
+        <v>-120</v>
       </c>
       <c r="G69" t="n">
-        <v>-54</v>
+        <v>-482</v>
       </c>
       <c r="H69" t="n">
-        <v>-68</v>
+        <v>36</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3929,45 +3929,45 @@
         </is>
       </c>
       <c r="K69" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>22</v>
+        <v>-388</v>
       </c>
       <c r="D70" t="n">
-        <v>-1027</v>
+        <v>-1084</v>
       </c>
       <c r="E70" t="n">
-        <v>1489</v>
+        <v>-6946</v>
       </c>
       <c r="F70" t="n">
-        <v>-192</v>
+        <v>-2789</v>
       </c>
       <c r="G70" t="n">
-        <v>-482</v>
+        <v>-8645</v>
       </c>
       <c r="H70" t="n">
-        <v>40</v>
+        <v>416</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3980,11 +3980,11 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M70" t="n">
@@ -3994,31 +3994,31 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-1284</v>
+        <v>-52</v>
       </c>
       <c r="D71" t="n">
-        <v>-1086</v>
+        <v>-1102</v>
       </c>
       <c r="E71" t="n">
-        <v>-11898</v>
+        <v>-1589</v>
       </c>
       <c r="F71" t="n">
-        <v>391</v>
+        <v>-275</v>
       </c>
       <c r="G71" t="n">
-        <v>1265</v>
+        <v>-31</v>
       </c>
       <c r="H71" t="n">
-        <v>-347</v>
+        <v>-66</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -4031,45 +4031,45 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-791</v>
+        <v>-465</v>
       </c>
       <c r="D72" t="n">
-        <v>-1112</v>
+        <v>-1210</v>
       </c>
       <c r="E72" t="n">
-        <v>-433</v>
+        <v>375</v>
       </c>
       <c r="F72" t="n">
-        <v>15</v>
+        <v>-609</v>
       </c>
       <c r="G72" t="n">
-        <v>-13</v>
+        <v>90</v>
       </c>
       <c r="H72" t="n">
-        <v>-13</v>
+        <v>36</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -4078,88 +4078,100 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>聯合</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-170</v>
+        <v>-94</v>
       </c>
       <c r="D73" t="n">
-        <v>-1175</v>
+        <v>-1238</v>
       </c>
       <c r="E73" t="n">
-        <v>1814</v>
+        <v>-1807</v>
       </c>
       <c r="F73" t="n">
-        <v>-138</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>2188</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>87</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>🚀 加速器</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-115</v>
+        <v>-887</v>
       </c>
       <c r="D74" t="n">
-        <v>-1253</v>
+        <v>-1247</v>
       </c>
       <c r="E74" t="n">
-        <v>-1795</v>
+        <v>-116</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>433</v>
       </c>
       <c r="H74" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4172,45 +4184,45 @@
         </is>
       </c>
       <c r="K74" t="n">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-1113</v>
+        <v>57</v>
       </c>
       <c r="D75" t="n">
-        <v>-1384</v>
+        <v>-1345</v>
       </c>
       <c r="E75" t="n">
-        <v>320</v>
+        <v>575</v>
       </c>
       <c r="F75" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>476</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>29</v>
+        <v>-279</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4219,151 +4231,139 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M75" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-1095</v>
+        <v>-608</v>
       </c>
       <c r="D76" t="n">
-        <v>-1471</v>
+        <v>-1380</v>
       </c>
       <c r="E76" t="n">
-        <v>-2660</v>
+        <v>1318</v>
       </c>
       <c r="F76" t="n">
-        <v>494</v>
+        <v>-242</v>
       </c>
       <c r="G76" t="n">
-        <v>8808</v>
+        <v>1939</v>
       </c>
       <c r="H76" t="n">
-        <v>184</v>
+        <v>7</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K76" t="n">
-        <v>69</v>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M76" t="n">
-        <v>-3</v>
-      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-1386</v>
+        <v>-993</v>
       </c>
       <c r="D77" t="n">
-        <v>-1529</v>
+        <v>-1507</v>
       </c>
       <c r="E77" t="n">
-        <v>-543</v>
+        <v>-624</v>
       </c>
       <c r="F77" t="n">
+        <v>8</v>
+      </c>
+      <c r="G77" t="n">
+        <v>-15</v>
+      </c>
+      <c r="H77" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>73</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>🛬 穩定</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
         <v>-1</v>
-      </c>
-      <c r="G77" t="n">
-        <v>-281</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-241</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K77" t="n">
-        <v>69</v>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M77" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-62</v>
+        <v>597</v>
       </c>
       <c r="D78" t="n">
-        <v>-1571</v>
+        <v>-1527</v>
       </c>
       <c r="E78" t="n">
-        <v>-3409</v>
+        <v>-1556</v>
       </c>
       <c r="F78" t="n">
-        <v>38</v>
+        <v>1119</v>
       </c>
       <c r="G78" t="n">
-        <v>-1</v>
+        <v>3707</v>
       </c>
       <c r="H78" t="n">
-        <v>-2</v>
+        <v>-155</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4376,45 +4376,45 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>勝一</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>248</v>
+        <v>113</v>
       </c>
       <c r="D79" t="n">
-        <v>-1583</v>
+        <v>-1640</v>
       </c>
       <c r="E79" t="n">
-        <v>-2059</v>
+        <v>-3415</v>
       </c>
       <c r="F79" t="n">
-        <v>-511</v>
+        <v>39</v>
       </c>
       <c r="G79" t="n">
-        <v>1450</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>56</v>
+        <v>-25</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4427,45 +4427,45 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-2293</v>
+        <v>-2298</v>
       </c>
       <c r="D80" t="n">
-        <v>-1608</v>
+        <v>-1749</v>
       </c>
       <c r="E80" t="n">
-        <v>-6971</v>
+        <v>-3182</v>
       </c>
       <c r="F80" t="n">
-        <v>581</v>
+        <v>446</v>
       </c>
       <c r="G80" t="n">
-        <v>1435</v>
+        <v>8767</v>
       </c>
       <c r="H80" t="n">
-        <v>-146</v>
+        <v>259</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4478,45 +4478,45 @@
         </is>
       </c>
       <c r="K80" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M80" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>84</v>
+        <v>-277</v>
       </c>
       <c r="D81" t="n">
-        <v>-1718</v>
+        <v>-1894</v>
       </c>
       <c r="E81" t="n">
-        <v>581</v>
+        <v>-2456</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>-183</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>1536</v>
       </c>
       <c r="H81" t="n">
-        <v>-239</v>
+        <v>26</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4529,11 +4529,11 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M81" t="n">
@@ -4552,13 +4552,13 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-2133</v>
+        <v>-903</v>
       </c>
       <c r="D82" t="n">
-        <v>-1910</v>
+        <v>-1898</v>
       </c>
       <c r="E82" t="n">
-        <v>-2263</v>
+        <v>-2422</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -4567,7 +4567,7 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4594,35 +4594,35 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1450</v>
+        <v>-3034</v>
       </c>
       <c r="D83" t="n">
-        <v>-1950</v>
+        <v>-2136</v>
       </c>
       <c r="E83" t="n">
-        <v>-1018</v>
+        <v>-7889</v>
       </c>
       <c r="F83" t="n">
-        <v>-290</v>
+        <v>1240</v>
       </c>
       <c r="G83" t="n">
-        <v>3217</v>
+        <v>2132</v>
       </c>
       <c r="H83" t="n">
-        <v>-152</v>
+        <v>-268</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>🟡 中性</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4631,45 +4631,45 @@
         </is>
       </c>
       <c r="K83" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M83" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-1719</v>
+        <v>459</v>
       </c>
       <c r="D84" t="n">
-        <v>-2043</v>
+        <v>-2375</v>
       </c>
       <c r="E84" t="n">
-        <v>94838</v>
+        <v>-3613</v>
       </c>
       <c r="F84" t="n">
-        <v>1555</v>
+        <v>-29</v>
       </c>
       <c r="G84" t="n">
-        <v>4748</v>
+        <v>-217</v>
       </c>
       <c r="H84" t="n">
-        <v>-1604</v>
+        <v>49</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4678,19 +4678,19 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K84" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M84" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
@@ -4705,22 +4705,22 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-60</v>
+        <v>-350</v>
       </c>
       <c r="D85" t="n">
-        <v>-2222</v>
+        <v>-2514</v>
       </c>
       <c r="E85" t="n">
-        <v>-5784</v>
+        <v>-5505</v>
       </c>
       <c r="F85" t="n">
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>-400</v>
+        <v>-268</v>
       </c>
       <c r="H85" t="n">
-        <v>-54</v>
+        <v>-43</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4735,31 +4735,31 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>561</v>
+        <v>-894</v>
       </c>
       <c r="D86" t="n">
-        <v>-2302</v>
+        <v>-2769</v>
       </c>
       <c r="E86" t="n">
-        <v>-3815</v>
+        <v>-792</v>
       </c>
       <c r="F86" t="n">
-        <v>-29</v>
+        <v>-330</v>
       </c>
       <c r="G86" t="n">
-        <v>-217</v>
+        <v>-946</v>
       </c>
       <c r="H86" t="n">
-        <v>108</v>
+        <v>18</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4768,49 +4768,49 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K86" t="n">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M86" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-637</v>
+        <v>670</v>
       </c>
       <c r="D87" t="n">
-        <v>-2560</v>
+        <v>-3166</v>
       </c>
       <c r="E87" t="n">
-        <v>-1368</v>
+        <v>-17543</v>
       </c>
       <c r="F87" t="n">
-        <v>-302</v>
+        <v>-538</v>
       </c>
       <c r="G87" t="n">
-        <v>-1136</v>
+        <v>-1613</v>
       </c>
       <c r="H87" t="n">
-        <v>8</v>
+        <v>-383</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4819,49 +4819,49 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M87" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>1260</v>
+        <v>-4887</v>
       </c>
       <c r="D88" t="n">
-        <v>-2605</v>
+        <v>-3179</v>
       </c>
       <c r="E88" t="n">
-        <v>-18038</v>
+        <v>-1282</v>
       </c>
       <c r="F88" t="n">
-        <v>-632</v>
+        <v>2812</v>
       </c>
       <c r="G88" t="n">
-        <v>-1617</v>
+        <v>324</v>
       </c>
       <c r="H88" t="n">
-        <v>-271</v>
+        <v>186</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4870,15 +4870,15 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K88" t="n">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M88" t="n">
@@ -4888,31 +4888,31 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-4715</v>
+        <v>-1500</v>
       </c>
       <c r="D89" t="n">
-        <v>-2643</v>
+        <v>-4221</v>
       </c>
       <c r="E89" t="n">
-        <v>266</v>
+        <v>-304</v>
       </c>
       <c r="F89" t="n">
-        <v>734</v>
+        <v>-1</v>
       </c>
       <c r="G89" t="n">
-        <v>-2049</v>
+        <v>-281</v>
       </c>
       <c r="H89" t="n">
-        <v>100</v>
+        <v>-259</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4921,11 +4921,11 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K89" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -4933,37 +4933,37 @@
         </is>
       </c>
       <c r="M89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>長榮航太</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-13329</v>
+        <v>264</v>
       </c>
       <c r="D90" t="n">
-        <v>-4372</v>
+        <v>-4569</v>
       </c>
       <c r="E90" t="n">
-        <v>-126523</v>
+        <v>-13568</v>
       </c>
       <c r="F90" t="n">
-        <v>1104</v>
+        <v>-395</v>
       </c>
       <c r="G90" t="n">
-        <v>-2643</v>
+        <v>-231</v>
       </c>
       <c r="H90" t="n">
-        <v>4200</v>
+        <v>415</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4972,19 +4972,19 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K90" t="n">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -4999,22 +4999,22 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="D91" t="n">
-        <v>-4605</v>
+        <v>-4711</v>
       </c>
       <c r="E91" t="n">
-        <v>-34977</v>
+        <v>-35464</v>
       </c>
       <c r="F91" t="n">
-        <v>27</v>
+        <v>-20</v>
       </c>
       <c r="G91" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H91" t="n">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -5041,31 +5041,31 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>182</v>
+        <v>1117</v>
       </c>
       <c r="D92" t="n">
-        <v>-5701</v>
+        <v>-7090</v>
       </c>
       <c r="E92" t="n">
-        <v>-14533</v>
+        <v>-16093</v>
       </c>
       <c r="F92" t="n">
-        <v>-395</v>
+        <v>-50</v>
       </c>
       <c r="G92" t="n">
-        <v>-233</v>
+        <v>731</v>
       </c>
       <c r="H92" t="n">
-        <v>342</v>
+        <v>319</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -5074,19 +5074,19 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K92" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
@@ -5101,13 +5101,13 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-780</v>
+        <v>-991</v>
       </c>
       <c r="D93" t="n">
-        <v>-7794</v>
+        <v>-7644</v>
       </c>
       <c r="E93" t="n">
-        <v>-16728</v>
+        <v>-17056</v>
       </c>
       <c r="F93" t="n">
         <v>-1</v>
@@ -5116,7 +5116,7 @@
         <v>-1</v>
       </c>
       <c r="H93" t="n">
-        <v>-53</v>
+        <v>-51</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -5143,31 +5143,31 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-639</v>
+        <v>5444</v>
       </c>
       <c r="D94" t="n">
-        <v>-8230</v>
+        <v>-9313</v>
       </c>
       <c r="E94" t="n">
-        <v>-16110</v>
+        <v>-42046</v>
       </c>
       <c r="F94" t="n">
-        <v>-307</v>
+        <v>3213</v>
       </c>
       <c r="G94" t="n">
-        <v>1249</v>
+        <v>-3987</v>
       </c>
       <c r="H94" t="n">
-        <v>483</v>
+        <v>1732</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -5180,15 +5180,15 @@
         </is>
       </c>
       <c r="K94" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -5203,13 +5203,13 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-200</v>
+        <v>-698</v>
       </c>
       <c r="D95" t="n">
-        <v>-9101</v>
+        <v>-9495</v>
       </c>
       <c r="E95" t="n">
-        <v>-23239</v>
+        <v>-23997</v>
       </c>
       <c r="F95" t="n">
         <v>-100</v>
@@ -5218,7 +5218,7 @@
         <v>-100</v>
       </c>
       <c r="H95" t="n">
-        <v>-148</v>
+        <v>-44</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5254,22 +5254,22 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-2982</v>
+        <v>-5887</v>
       </c>
       <c r="D96" t="n">
-        <v>-10214</v>
+        <v>-11573</v>
       </c>
       <c r="E96" t="n">
-        <v>-11109</v>
+        <v>-12864</v>
       </c>
       <c r="F96" t="n">
-        <v>-369</v>
+        <v>189</v>
       </c>
       <c r="G96" t="n">
-        <v>2356</v>
+        <v>2470</v>
       </c>
       <c r="H96" t="n">
-        <v>478</v>
+        <v>849</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -5284,31 +5284,31 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-4482</v>
+        <v>23696</v>
       </c>
       <c r="D97" t="n">
-        <v>-11319</v>
+        <v>-11647</v>
       </c>
       <c r="E97" t="n">
-        <v>9088</v>
+        <v>29501</v>
       </c>
       <c r="F97" t="n">
-        <v>470</v>
+        <v>-6412</v>
       </c>
       <c r="G97" t="n">
-        <v>1659</v>
+        <v>-33974</v>
       </c>
       <c r="H97" t="n">
-        <v>971</v>
+        <v>-2854</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -5317,49 +5317,49 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K97" t="n">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M97" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-3938</v>
+        <v>-3602</v>
       </c>
       <c r="D98" t="n">
-        <v>-11595</v>
+        <v>-12758</v>
       </c>
       <c r="E98" t="n">
-        <v>84644</v>
+        <v>-13444</v>
       </c>
       <c r="F98" t="n">
-        <v>-1241</v>
+        <v>-1768</v>
       </c>
       <c r="G98" t="n">
-        <v>1626</v>
+        <v>-4145</v>
       </c>
       <c r="H98" t="n">
-        <v>-190</v>
+        <v>-1026</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5372,45 +5372,45 @@
         </is>
       </c>
       <c r="K98" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>3478</v>
+        <v>-10339</v>
       </c>
       <c r="D99" t="n">
-        <v>-11947</v>
+        <v>-13012</v>
       </c>
       <c r="E99" t="n">
-        <v>-45371</v>
+        <v>-15454</v>
       </c>
       <c r="F99" t="n">
-        <v>-258</v>
+        <v>8472</v>
       </c>
       <c r="G99" t="n">
-        <v>-7336</v>
+        <v>7739</v>
       </c>
       <c r="H99" t="n">
-        <v>874</v>
+        <v>5</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5419,15 +5419,15 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K99" t="n">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器*</t>
         </is>
       </c>
       <c r="M99" t="n">
@@ -5437,31 +5437,31 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>寶雅*</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-9193</v>
+        <v>-4449</v>
       </c>
       <c r="D100" t="n">
-        <v>-12298</v>
+        <v>-13619</v>
       </c>
       <c r="E100" t="n">
-        <v>-15081</v>
+        <v>-68913</v>
       </c>
       <c r="F100" t="n">
-        <v>8472</v>
+        <v>2139</v>
       </c>
       <c r="G100" t="n">
-        <v>7736</v>
+        <v>875</v>
       </c>
       <c r="H100" t="n">
-        <v>44</v>
+        <v>-282</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -5470,49 +5470,49 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K100" t="n">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>🚀 加速器*</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M100" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-3500</v>
+        <v>-5120</v>
       </c>
       <c r="D101" t="n">
-        <v>-12848</v>
+        <v>-14286</v>
       </c>
       <c r="E101" t="n">
-        <v>-69027</v>
+        <v>91210</v>
       </c>
       <c r="F101" t="n">
-        <v>2178</v>
+        <v>-1758</v>
       </c>
       <c r="G101" t="n">
-        <v>592</v>
+        <v>1223</v>
       </c>
       <c r="H101" t="n">
-        <v>-219</v>
+        <v>-321</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5521,49 +5521,49 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K101" t="n">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M101" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-4139</v>
+        <v>-5558</v>
       </c>
       <c r="D102" t="n">
-        <v>-13105</v>
+        <v>-15320</v>
       </c>
       <c r="E102" t="n">
-        <v>-13886</v>
+        <v>-91452</v>
       </c>
       <c r="F102" t="n">
-        <v>-931</v>
+        <v>2355</v>
       </c>
       <c r="G102" t="n">
-        <v>-3390</v>
+        <v>-19400</v>
       </c>
       <c r="H102" t="n">
-        <v>-1042</v>
+        <v>2761</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5572,49 +5572,49 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K102" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M102" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-3003</v>
+        <v>-1797</v>
       </c>
       <c r="D103" t="n">
-        <v>-16853</v>
+        <v>-20656</v>
       </c>
       <c r="E103" t="n">
-        <v>-89131</v>
+        <v>10028</v>
       </c>
       <c r="F103" t="n">
-        <v>2408</v>
+        <v>356</v>
       </c>
       <c r="G103" t="n">
-        <v>-20155</v>
+        <v>1498</v>
       </c>
       <c r="H103" t="n">
-        <v>2435</v>
+        <v>808</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5623,19 +5623,19 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K103" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M103" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -5650,22 +5650,22 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-6507</v>
+        <v>-5941</v>
       </c>
       <c r="D104" t="n">
-        <v>-18839</v>
+        <v>-25930</v>
       </c>
       <c r="E104" t="n">
-        <v>46382</v>
+        <v>48099</v>
       </c>
       <c r="F104" t="n">
-        <v>154</v>
+        <v>-77</v>
       </c>
       <c r="G104" t="n">
-        <v>7577</v>
+        <v>7303</v>
       </c>
       <c r="H104" t="n">
-        <v>-1398</v>
+        <v>-1703</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5701,22 +5701,22 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-19086</v>
+        <v>-3956</v>
       </c>
       <c r="D105" t="n">
-        <v>-94692</v>
+        <v>-88485</v>
       </c>
       <c r="E105" t="n">
-        <v>170040</v>
+        <v>171599</v>
       </c>
       <c r="F105" t="n">
-        <v>9240</v>
+        <v>4039</v>
       </c>
       <c r="G105" t="n">
-        <v>39217</v>
+        <v>35220</v>
       </c>
       <c r="H105" t="n">
-        <v>1192</v>
+        <v>1282</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -5794,87 +5794,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 67 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -8 千股)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>213102</v>
+        <v>18185</v>
       </c>
       <c r="D2" t="n">
-        <v>951978</v>
+        <v>614051</v>
       </c>
       <c r="E2" t="n">
-        <v>115861</v>
+        <v>-36729</v>
       </c>
       <c r="F2" t="n">
-        <v>885463</v>
+        <v>621923</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>勤誠</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 1,051 千股)</t>
+          <t>📉 20d 巨變(減碼 -531 千股)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1260134</v>
+        <v>209557</v>
       </c>
       <c r="D3" t="n">
-        <v>-2605451</v>
+        <v>863187</v>
       </c>
       <c r="E3" t="n">
-        <v>-639297</v>
+        <v>137541</v>
       </c>
       <c r="F3" t="n">
-        <v>-3656169</v>
+        <v>1394295</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>健策</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 13 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -561 千股)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>137541</v>
+        <v>-32233</v>
       </c>
       <c r="D4" t="n">
-        <v>1394295</v>
+        <v>390623</v>
       </c>
       <c r="E4" t="n">
-        <v>79052</v>
+        <v>213102</v>
       </c>
       <c r="F4" t="n">
-        <v>1381453</v>
+        <v>951978</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>奇鋐</t>
         </is>
       </c>
     </row>
@@ -5886,20 +5886,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -64 千股)</t>
+          <t>📈 20d 巨變(加碼 222 千股)</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>851763</v>
+      </c>
+      <c r="D5" t="n">
+        <v>584712</v>
+      </c>
+      <c r="E5" t="n">
         <v>681611</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>362420</v>
-      </c>
-      <c r="E5" t="n">
-        <v>343111</v>
-      </c>
-      <c r="F5" t="n">
-        <v>426273</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -5910,87 +5910,87 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 703 千股)</t>
+          <t>📉 20d 巨變(減碼 -560 千股)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-639289</v>
+        <v>669536</v>
       </c>
       <c r="D6" t="n">
-        <v>-8229822</v>
+        <v>-3165856</v>
       </c>
       <c r="E6" t="n">
-        <v>-1491111</v>
+        <v>1260134</v>
       </c>
       <c r="F6" t="n">
-        <v>-8932948</v>
+        <v>-2605451</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>亞翔</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 130 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 1,140 千股)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-36729</v>
+        <v>1116580</v>
       </c>
       <c r="D7" t="n">
-        <v>621923</v>
+        <v>-7090103</v>
       </c>
       <c r="E7" t="n">
-        <v>-213601</v>
+        <v>-639289</v>
       </c>
       <c r="F7" t="n">
-        <v>491720</v>
+        <v>-8229822</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 323 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 524 千股)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2002</v>
+        <v>322273</v>
       </c>
       <c r="D8" t="n">
-        <v>80956</v>
+        <v>1849367</v>
       </c>
       <c r="E8" t="n">
-        <v>-196816</v>
+        <v>-319084</v>
       </c>
       <c r="F8" t="n">
-        <v>-241873</v>
+        <v>1325292</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>致茂</t>
         </is>
       </c>
     </row>
@@ -6002,20 +6002,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 394 千股)</t>
+          <t>📉 20d 巨變(減碼 -390 千股)</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>305231</v>
+      </c>
+      <c r="D9" t="n">
+        <v>315853</v>
+      </c>
+      <c r="E9" t="n">
         <v>478481</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>705677</v>
-      </c>
-      <c r="E9" t="n">
-        <v>25102</v>
-      </c>
-      <c r="F9" t="n">
-        <v>311470</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -6026,116 +6026,116 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -489 千股)</t>
+          <t>📉 20d 巨變(減碼 -217 千股)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-319084</v>
+        <v>-387547</v>
       </c>
       <c r="D10" t="n">
-        <v>1325292</v>
+        <v>-1084320</v>
       </c>
       <c r="E10" t="n">
-        <v>-9446</v>
+        <v>-245209</v>
       </c>
       <c r="F10" t="n">
-        <v>1814324</v>
+        <v>-867374</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>智邦</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -323 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 4,310 千股)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-245209</v>
+        <v>551906</v>
       </c>
       <c r="D11" t="n">
-        <v>-867374</v>
+        <v>-61917</v>
       </c>
       <c r="E11" t="n">
-        <v>582550</v>
+        <v>-13328620</v>
       </c>
       <c r="F11" t="n">
-        <v>-544788</v>
+        <v>-4372146</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 242 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -123 千股)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-1164487</v>
+        <v>-166265</v>
       </c>
       <c r="D12" t="n">
-        <v>8621562</v>
+        <v>-42251</v>
       </c>
       <c r="E12" t="n">
-        <v>-1530237</v>
+        <v>2002</v>
       </c>
       <c r="F12" t="n">
-        <v>8379729</v>
+        <v>80956</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>旺矽</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 244 千股)</t>
+          <t>📉 20d 巨變(減碼 -892 千股)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-13328620</v>
+        <v>-1083126</v>
       </c>
       <c r="D13" t="n">
-        <v>-4372146</v>
+        <v>7729620</v>
       </c>
       <c r="E13" t="n">
-        <v>-27619102</v>
+        <v>-1164487</v>
       </c>
       <c r="F13" t="n">
-        <v>-4616452</v>
+        <v>8621562</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>雙鴻</t>
         </is>
       </c>
     </row>
@@ -6147,20 +6147,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 2,888 千股)</t>
+          <t>📈 20d 巨變(加碼 2,634 千股)</t>
         </is>
       </c>
       <c r="C14" t="n">
+        <v>5444224</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-9313210</v>
+      </c>
+      <c r="E14" t="n">
         <v>3478025</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>-11946950</v>
-      </c>
-      <c r="E14" t="n">
-        <v>-2924887</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-14834469</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -6176,20 +6176,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 820 千股)</t>
+          <t>📉 20d 巨變(減碼 -269 千股)</t>
         </is>
       </c>
       <c r="C15" t="n">
+        <v>114814</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2637718</v>
+      </c>
+      <c r="E15" t="n">
         <v>942737</v>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>2907039</v>
-      </c>
-      <c r="E15" t="n">
-        <v>840746</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2086615</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -6200,58 +6200,58 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 598 千股)</t>
+          <t>📈 20d 巨變(加碼 1,106 千股)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>560769</v>
+        <v>-1210981</v>
       </c>
       <c r="D16" t="n">
-        <v>-2301540</v>
+        <v>19886</v>
       </c>
       <c r="E16" t="n">
-        <v>45713</v>
+        <v>-1284004</v>
       </c>
       <c r="F16" t="n">
-        <v>-2899731</v>
+        <v>-1086135</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>健鼎</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,792 千股)</t>
+          <t>📉 20d 巨變(減碼 -73 千股)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-1284004</v>
+        <v>459195</v>
       </c>
       <c r="D17" t="n">
-        <v>-1086135</v>
+        <v>-2374565</v>
       </c>
       <c r="E17" t="n">
-        <v>-1509760</v>
+        <v>560769</v>
       </c>
       <c r="F17" t="n">
-        <v>-2877872</v>
+        <v>-2301540</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>佳必琪</t>
         </is>
       </c>
     </row>
@@ -6263,20 +6263,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -28 千股)</t>
+          <t>📈 20d 巨變(加碼 43 千股)</t>
         </is>
       </c>
       <c r="C18" t="n">
+        <v>52840</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-983777</v>
+      </c>
+      <c r="E18" t="n">
         <v>22320</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>-1026614</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-88754</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-998712</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -6287,29 +6287,29 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -167 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -226 千股)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-348631</v>
+        <v>-52014</v>
       </c>
       <c r="D19" t="n">
-        <v>38218</v>
+        <v>-1102295</v>
       </c>
       <c r="E19" t="n">
-        <v>-159131</v>
+        <v>35264</v>
       </c>
       <c r="F19" t="n">
-        <v>204756</v>
+        <v>-876521</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>崇越</t>
         </is>
       </c>
     </row>
@@ -6321,20 +6321,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 227 千股)</t>
+          <t>📈 20d 巨變(加碼 403 千股)</t>
         </is>
       </c>
       <c r="C20" t="n">
+        <v>559356</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5650898</v>
+      </c>
+      <c r="E20" t="n">
         <v>328807</v>
       </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
         <v>5247575</v>
-      </c>
-      <c r="E20" t="n">
-        <v>705718</v>
-      </c>
-      <c r="F20" t="n">
-        <v>5020474</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -6345,116 +6345,116 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 212 千股)</t>
+          <t>📉 20d 巨變(減碼 -151 千股)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>35264</v>
+        <v>-472862</v>
       </c>
       <c r="D21" t="n">
-        <v>-876521</v>
+        <v>-112765</v>
       </c>
       <c r="E21" t="n">
-        <v>-95640</v>
+        <v>-348631</v>
       </c>
       <c r="F21" t="n">
-        <v>-1088657</v>
+        <v>38218</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>川湖</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 360 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 514 千股)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-2132958</v>
+        <v>465979</v>
       </c>
       <c r="D22" t="n">
-        <v>-1910322</v>
+        <v>2598485</v>
       </c>
       <c r="E22" t="n">
-        <v>-2394722</v>
+        <v>-720715</v>
       </c>
       <c r="F22" t="n">
-        <v>-2270298</v>
+        <v>2084402</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>中砂</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -11 千股)</t>
+          <t>📈 20d 巨變(加碼 472 千股)</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-720715</v>
+        <v>196607</v>
       </c>
       <c r="D23" t="n">
-        <v>2084402</v>
+        <v>286045</v>
       </c>
       <c r="E23" t="n">
-        <v>969972</v>
+        <v>335727</v>
       </c>
       <c r="F23" t="n">
-        <v>2094944</v>
+        <v>-186408</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>華城</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 469 千股)</t>
+          <t>📈 20d 巨變(加碼 12 千股)</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>335727</v>
+        <v>-903409</v>
       </c>
       <c r="D24" t="n">
-        <v>-186408</v>
+        <v>-1898176</v>
       </c>
       <c r="E24" t="n">
-        <v>82690</v>
+        <v>-2132958</v>
       </c>
       <c r="F24" t="n">
-        <v>-655599</v>
+        <v>-1910322</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>建榮</t>
         </is>
       </c>
     </row>
@@ -6466,20 +6466,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -27 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -363 千股)</t>
         </is>
       </c>
       <c r="C25" t="n">
+        <v>-670278</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-887750</v>
+      </c>
+      <c r="E25" t="n">
         <v>135383</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
         <v>-524318</v>
-      </c>
-      <c r="E25" t="n">
-        <v>499293</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-497121</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -6490,174 +6490,174 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -30 千股)</t>
+          <t>📈 20d 巨變(加碼 115 千股)</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-7006</v>
+        <v>-55849</v>
       </c>
       <c r="D26" t="n">
-        <v>7714</v>
+        <v>-518241</v>
       </c>
       <c r="E26" t="n">
-        <v>13000</v>
+        <v>-159008</v>
       </c>
       <c r="F26" t="n">
-        <v>37221</v>
+        <v>-633400</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>湧德</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,764 千股)</t>
+          <t>📉 20d 巨變(減碼 -28 千股)</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-48147</v>
+        <v>-19770</v>
       </c>
       <c r="D27" t="n">
-        <v>1083721</v>
+        <v>-40732</v>
       </c>
       <c r="E27" t="n">
-        <v>-3732764</v>
+        <v>-41770</v>
       </c>
       <c r="F27" t="n">
-        <v>-1680640</v>
+        <v>-12682</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>崇友</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 83 千股)</t>
+          <t>📉 20d 巨變(減碼 -14 千股)</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>156037</v>
+        <v>-14006</v>
       </c>
       <c r="D28" t="n">
-        <v>-464862</v>
+        <v>-6286</v>
       </c>
       <c r="E28" t="n">
-        <v>-91173</v>
+        <v>-7006</v>
       </c>
       <c r="F28" t="n">
-        <v>-547672</v>
+        <v>7714</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>大車隊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 609 千股)</t>
+          <t>📉 20d 巨變(減碼 -12 千股)</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>572620</v>
+        <v>106037</v>
       </c>
       <c r="D29" t="n">
-        <v>15829618</v>
+        <v>-476862</v>
       </c>
       <c r="E29" t="n">
-        <v>591133</v>
+        <v>156037</v>
       </c>
       <c r="F29" t="n">
-        <v>15220548</v>
+        <v>-464862</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>隆大</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -29 千股)</t>
+          <t>📉 20d 巨變(減碼 -195 千股)</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-41770</v>
+        <v>332146</v>
       </c>
       <c r="D30" t="n">
-        <v>-12682</v>
+        <v>15634923</v>
       </c>
       <c r="E30" t="n">
-        <v>-27263</v>
+        <v>572620</v>
       </c>
       <c r="F30" t="n">
-        <v>15953</v>
+        <v>15829618</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 24 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -1,753 千股)</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-159008</v>
+        <v>1274857</v>
       </c>
       <c r="D31" t="n">
-        <v>-633400</v>
+        <v>-669262</v>
       </c>
       <c r="E31" t="n">
-        <v>218782</v>
+        <v>-48147</v>
       </c>
       <c r="F31" t="n">
-        <v>-657400</v>
+        <v>1083721</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>零壹</t>
         </is>
       </c>
     </row>
@@ -6669,20 +6669,20 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 123 千股)</t>
+          <t>📉 20d 巨變(減碼 -62 千股)</t>
         </is>
       </c>
       <c r="C32" t="n">
+        <v>192836</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1088492</v>
+      </c>
+      <c r="E32" t="n">
         <v>288054</v>
       </c>
-      <c r="D32" t="n">
+      <c r="F32" t="n">
         <v>1150231</v>
-      </c>
-      <c r="E32" t="n">
-        <v>203303</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1027113</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -6693,116 +6693,116 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 184 千股)</t>
+          <t>📉 20d 巨變(減碼 -4,735 千股)</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-1112669</v>
+        <v>-14546783</v>
       </c>
       <c r="D33" t="n">
-        <v>-1384298</v>
+        <v>1205063</v>
       </c>
       <c r="E33" t="n">
-        <v>-1539643</v>
+        <v>-15044921</v>
       </c>
       <c r="F33" t="n">
-        <v>-1568249</v>
+        <v>5940109</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -75 千股)</t>
+          <t>📉 20d 巨變(減碼 -771 千股)</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-34694</v>
+        <v>-4449229</v>
       </c>
       <c r="D34" t="n">
-        <v>80774</v>
+        <v>-13619466</v>
       </c>
       <c r="E34" t="n">
-        <v>-89482</v>
+        <v>-3500209</v>
       </c>
       <c r="F34" t="n">
-        <v>155689</v>
+        <v>-12848208</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>寶雅*</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 748 千股)</t>
+          <t>🟢 外資 5d 翻綠</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-3500209</v>
+        <v>33175</v>
       </c>
       <c r="D35" t="n">
-        <v>-12848208</v>
+        <v>83522</v>
       </c>
       <c r="E35" t="n">
-        <v>-348803</v>
+        <v>-34694</v>
       </c>
       <c r="F35" t="n">
-        <v>-13595837</v>
+        <v>80774</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>大統益</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -22,188 千股)</t>
+          <t>📈 20d 巨變(加碼 137 千股)</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-15044921</v>
+        <v>-887205</v>
       </c>
       <c r="D36" t="n">
-        <v>5940109</v>
+        <v>-1246989</v>
       </c>
       <c r="E36" t="n">
-        <v>4348602</v>
+        <v>-1112669</v>
       </c>
       <c r="F36" t="n">
-        <v>28128099</v>
+        <v>-1384298</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>卜蜂</t>
         </is>
       </c>
     </row>
@@ -6814,20 +6814,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 162 千股)</t>
+          <t>📉 20d 巨變(減碼 -256 千股)</t>
         </is>
       </c>
       <c r="C37" t="n">
+        <v>582134</v>
+      </c>
+      <c r="D37" t="n">
+        <v>495692</v>
+      </c>
+      <c r="E37" t="n">
         <v>585111</v>
       </c>
-      <c r="D37" t="n">
+      <c r="F37" t="n">
         <v>751669</v>
-      </c>
-      <c r="E37" t="n">
-        <v>489208</v>
-      </c>
-      <c r="F37" t="n">
-        <v>589568</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -6838,116 +6838,116 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -12 千股)</t>
+          <t>📉 20d 巨變(減碼 -5 千股)</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-25335</v>
+        <v>1000</v>
       </c>
       <c r="D38" t="n">
-        <v>-441138</v>
+        <v>54000</v>
       </c>
       <c r="E38" t="n">
-        <v>-17879</v>
+        <v>6000</v>
       </c>
       <c r="F38" t="n">
-        <v>-429241</v>
+        <v>59000</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>方土霖</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 66 千股)</t>
+          <t>📈 20d 巨變(加碼 9 千股)</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>26487</v>
+        <v>-19323</v>
       </c>
       <c r="D39" t="n">
-        <v>-163055</v>
+        <v>-432030</v>
       </c>
       <c r="E39" t="n">
-        <v>-33534</v>
+        <v>-25335</v>
       </c>
       <c r="F39" t="n">
-        <v>-229121</v>
+        <v>-441138</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>智冠</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -140 千股)</t>
+          <t>📉 20d 巨變(減碼 -342 千股)</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-114980</v>
+        <v>-465482</v>
       </c>
       <c r="D40" t="n">
-        <v>-242279</v>
+        <v>-1209574</v>
       </c>
       <c r="E40" t="n">
-        <v>-88850</v>
+        <v>-43923</v>
       </c>
       <c r="F40" t="n">
-        <v>-102776</v>
+        <v>-867204</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>穎崴</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 22 千股)</t>
+          <t>📉 20d 巨變(減碼 -107 千股)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-43923</v>
+        <v>-79980</v>
       </c>
       <c r="D41" t="n">
-        <v>-867204</v>
+        <v>-349090</v>
       </c>
       <c r="E41" t="n">
-        <v>-87213</v>
+        <v>-114980</v>
       </c>
       <c r="F41" t="n">
-        <v>-889499</v>
+        <v>-242279</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>八方雲集</t>
         </is>
       </c>
     </row>
@@ -6959,20 +6959,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -6,336 千股)</t>
+          <t>📉 20d 巨變(減碼 -3,344 千股)</t>
         </is>
       </c>
       <c r="C42" t="n">
+        <v>7464533</v>
+      </c>
+      <c r="D42" t="n">
+        <v>52360867</v>
+      </c>
+      <c r="E42" t="n">
         <v>7029659</v>
       </c>
-      <c r="D42" t="n">
+      <c r="F42" t="n">
         <v>55704981</v>
-      </c>
-      <c r="E42" t="n">
-        <v>10210053</v>
-      </c>
-      <c r="F42" t="n">
-        <v>62041285</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -6983,29 +6983,29 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -3,508 千股)</t>
+          <t>📉 20d 巨變(減碼 -15 千股)</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-487181</v>
+        <v>49447</v>
       </c>
       <c r="D43" t="n">
-        <v>350466</v>
+        <v>-178155</v>
       </c>
       <c r="E43" t="n">
-        <v>394545</v>
+        <v>26487</v>
       </c>
       <c r="F43" t="n">
-        <v>3858187</v>
+        <v>-163055</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>華景電</t>
         </is>
       </c>
     </row>
@@ -7017,20 +7017,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -59 千股)</t>
+          <t>📈 20d 巨變(加碼 633 千股)</t>
         </is>
       </c>
       <c r="C44" t="n">
+        <v>773859</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-144157</v>
+      </c>
+      <c r="E44" t="n">
         <v>245835</v>
       </c>
-      <c r="D44" t="n">
+      <c r="F44" t="n">
         <v>-777337</v>
-      </c>
-      <c r="E44" t="n">
-        <v>142063</v>
-      </c>
-      <c r="F44" t="n">
-        <v>-718735</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -7041,145 +7041,145 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 37 千股)</t>
+          <t>📉 20d 巨變(減碼 -168 千股)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-115072</v>
+        <v>-119554</v>
       </c>
       <c r="D45" t="n">
-        <v>-1253405</v>
+        <v>160312</v>
       </c>
       <c r="E45" t="n">
-        <v>-233072</v>
+        <v>-56293</v>
       </c>
       <c r="F45" t="n">
-        <v>-1290405</v>
+        <v>328665</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>大綜</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 273 千股)</t>
+          <t>📈 20d 巨變(加碼 15 千股)</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-56293</v>
+        <v>-94072</v>
       </c>
       <c r="D46" t="n">
-        <v>328665</v>
+        <v>-1238405</v>
       </c>
       <c r="E46" t="n">
-        <v>-198901</v>
+        <v>-115072</v>
       </c>
       <c r="F46" t="n">
-        <v>56007</v>
+        <v>-1253405</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>聯合</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 283 千股)</t>
+          <t>📉 20d 巨變(減碼 -783 千股)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>266252</v>
+        <v>-1457167</v>
       </c>
       <c r="D47" t="n">
-        <v>163102</v>
+        <v>-432496</v>
       </c>
       <c r="E47" t="n">
-        <v>93482</v>
+        <v>-487181</v>
       </c>
       <c r="F47" t="n">
-        <v>-119909</v>
+        <v>350466</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,020 千股)</t>
+          <t>📈 20d 巨變(加碼 62 千股)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1821272</v>
+        <v>277645</v>
       </c>
       <c r="D48" t="n">
-        <v>5378978</v>
+        <v>224995</v>
       </c>
       <c r="E48" t="n">
-        <v>1969542</v>
+        <v>266252</v>
       </c>
       <c r="F48" t="n">
-        <v>3358603</v>
+        <v>163102</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>漢科</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,365 千股)</t>
+          <t>📈 20d 巨變(加碼 3,422 千股)</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-1095412</v>
+        <v>4273427</v>
       </c>
       <c r="D49" t="n">
-        <v>-1471024</v>
+        <v>8800989</v>
       </c>
       <c r="E49" t="n">
-        <v>-1419061</v>
+        <v>1821272</v>
       </c>
       <c r="F49" t="n">
-        <v>-106456</v>
+        <v>5378978</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>台燿</t>
         </is>
       </c>
     </row>
@@ -7191,20 +7191,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -12,021 千股)</t>
+          <t>📉 20d 巨變(減碼 -9,337 千股)</t>
         </is>
       </c>
       <c r="C50" t="n">
+        <v>-1797139</v>
+      </c>
+      <c r="D50" t="n">
+        <v>-20655865</v>
+      </c>
+      <c r="E50" t="n">
         <v>-4481844</v>
       </c>
-      <c r="D50" t="n">
+      <c r="F50" t="n">
         <v>-11318698</v>
-      </c>
-      <c r="E50" t="n">
-        <v>-6150088</v>
-      </c>
-      <c r="F50" t="n">
-        <v>702689</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -7215,319 +7215,319 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,537 千股)</t>
+          <t>📉 20d 巨變(減碼 -278 千股)</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-3002894</v>
+        <v>-2298043</v>
       </c>
       <c r="D51" t="n">
-        <v>-16853262</v>
+        <v>-1749169</v>
       </c>
       <c r="E51" t="n">
-        <v>-11012367</v>
+        <v>-1095412</v>
       </c>
       <c r="F51" t="n">
-        <v>-19390009</v>
+        <v>-1471024</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>玉晶光</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 2,758 千股)</t>
+          <t>📉 20d 巨變(減碼 -276 千股)</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1889496</v>
+        <v>1933113</v>
       </c>
       <c r="D52" t="n">
-        <v>-553262</v>
+        <v>4726210</v>
       </c>
       <c r="E52" t="n">
-        <v>-2654576</v>
+        <v>2643273</v>
       </c>
       <c r="F52" t="n">
-        <v>-3310973</v>
+        <v>5002112</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>立隆電</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 26,200 千股)</t>
+          <t>📉 20d 巨變(減碼 -158 千股)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>23857230</v>
+        <v>1372583</v>
       </c>
       <c r="D53" t="n">
-        <v>8179766</v>
+        <v>-710958</v>
       </c>
       <c r="E53" t="n">
-        <v>-21478390</v>
+        <v>1889496</v>
       </c>
       <c r="F53" t="n">
-        <v>-18020476</v>
+        <v>-553262</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>世芯-KY</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 583 千股)</t>
+          <t>📈 20d 巨變(加碼 7,366 千股)</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>2643273</v>
+        <v>28358558</v>
       </c>
       <c r="D54" t="n">
-        <v>5002112</v>
+        <v>15545992</v>
       </c>
       <c r="E54" t="n">
-        <v>2870651</v>
+        <v>23857230</v>
       </c>
       <c r="F54" t="n">
-        <v>4419187</v>
+        <v>8179766</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 4,799 千股)</t>
+          <t>📈 20d 巨變(加碼 1,533 千股)</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>7179234</v>
+        <v>-5557918</v>
       </c>
       <c r="D55" t="n">
-        <v>32209473</v>
+        <v>-15320298</v>
       </c>
       <c r="E55" t="n">
-        <v>-8087993</v>
+        <v>-3002894</v>
       </c>
       <c r="F55" t="n">
-        <v>27410116</v>
+        <v>-16853262</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -157 千股)</t>
+          <t>📈 20d 巨變(加碼 4,559 千股)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>846571</v>
+        <v>12310583</v>
       </c>
       <c r="D56" t="n">
-        <v>2147303</v>
+        <v>36768774</v>
       </c>
       <c r="E56" t="n">
-        <v>173437</v>
+        <v>7179234</v>
       </c>
       <c r="F56" t="n">
-        <v>2303928</v>
+        <v>32209473</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -557 千股)</t>
+          <t>📉 20d 巨變(減碼 -291 千股)</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-1278685</v>
+        <v>699665</v>
       </c>
       <c r="D57" t="n">
-        <v>385182</v>
+        <v>1856434</v>
       </c>
       <c r="E57" t="n">
-        <v>-1264152</v>
+        <v>846571</v>
       </c>
       <c r="F57" t="n">
-        <v>941808</v>
+        <v>2147303</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>鈊象</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 1,554 千股)</t>
+          <t>📉 20d 巨變(減碼 -42 千股)</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>71250</v>
+        <v>-670277</v>
       </c>
       <c r="D58" t="n">
-        <v>-262634</v>
+        <v>342976</v>
       </c>
       <c r="E58" t="n">
-        <v>-548154</v>
+        <v>-1278685</v>
       </c>
       <c r="F58" t="n">
-        <v>-1816506</v>
+        <v>385182</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>士電</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -150 千股)</t>
+          <t>📈 20d 巨變(加碼 14 千股)</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-100410</v>
+        <v>60460</v>
       </c>
       <c r="D59" t="n">
-        <v>-202299</v>
+        <v>353842</v>
       </c>
       <c r="E59" t="n">
-        <v>-65025</v>
+        <v>44755</v>
       </c>
       <c r="F59" t="n">
-        <v>-52636</v>
+        <v>339880</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>普萊德</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -9 千股)</t>
+          <t>📈 20d 巨變(加碼 46 千股)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>44755</v>
+        <v>-40007</v>
       </c>
       <c r="D60" t="n">
-        <v>339880</v>
+        <v>-156117</v>
       </c>
       <c r="E60" t="n">
-        <v>18755</v>
+        <v>-100410</v>
       </c>
       <c r="F60" t="n">
-        <v>349108</v>
+        <v>-202299</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>達欣工</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -368 千股)</t>
+          <t>📈 20d 巨變(加碼 314 千股)</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-791032</v>
+        <v>165210</v>
       </c>
       <c r="D61" t="n">
-        <v>-1112427</v>
+        <v>51628</v>
       </c>
       <c r="E61" t="n">
-        <v>-450270</v>
+        <v>71250</v>
       </c>
       <c r="F61" t="n">
-        <v>-744778</v>
+        <v>-262634</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>鉅祥</t>
         </is>
       </c>
     </row>
@@ -7539,20 +7539,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -46 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -68 千股)</t>
         </is>
       </c>
       <c r="C62" t="n">
+        <v>112959</v>
+      </c>
+      <c r="D62" t="n">
+        <v>-1639888</v>
+      </c>
+      <c r="E62" t="n">
         <v>-61789</v>
       </c>
-      <c r="D62" t="n">
+      <c r="F62" t="n">
         <v>-1571422</v>
-      </c>
-      <c r="E62" t="n">
-        <v>-196561</v>
-      </c>
-      <c r="F62" t="n">
-        <v>-1525136</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -7563,145 +7563,145 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 391 千股)</t>
+          <t>📉 20d 巨變(減碼 -395 千股)</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>1199979</v>
+        <v>-992971</v>
       </c>
       <c r="D63" t="n">
-        <v>1033520</v>
+        <v>-1507498</v>
       </c>
       <c r="E63" t="n">
-        <v>783680</v>
+        <v>-791032</v>
       </c>
       <c r="F63" t="n">
-        <v>642442</v>
+        <v>-1112427</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 261 千股)</t>
+          <t>📈 20d 巨變(加碼 424 千股)</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>83818</v>
+        <v>597453</v>
       </c>
       <c r="D64" t="n">
-        <v>-1717742</v>
+        <v>-1526964</v>
       </c>
       <c r="E64" t="n">
-        <v>62768</v>
+        <v>1449962</v>
       </c>
       <c r="F64" t="n">
-        <v>-1978692</v>
+        <v>-1950492</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>華星光</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -9,458 千股)</t>
+          <t>📈 20d 巨變(加碼 373 千股)</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-9193144</v>
+        <v>56765</v>
       </c>
       <c r="D65" t="n">
-        <v>-12297744</v>
+        <v>-1344742</v>
       </c>
       <c r="E65" t="n">
-        <v>-224950</v>
+        <v>83818</v>
       </c>
       <c r="F65" t="n">
-        <v>-2840237</v>
+        <v>-1717742</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>信立</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,723 千股)</t>
+          <t>📈 20d 巨變(加碼 47 千股)</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1449962</v>
+        <v>1133474</v>
       </c>
       <c r="D66" t="n">
-        <v>-1950492</v>
+        <v>1080622</v>
       </c>
       <c r="E66" t="n">
-        <v>840037</v>
+        <v>1199979</v>
       </c>
       <c r="F66" t="n">
-        <v>-3673287</v>
+        <v>1033520</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>祥碩</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,043 千股)</t>
+          <t>📉 20d 巨變(減碼 -714 千股)</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-4714730</v>
+        <v>-10338604</v>
       </c>
       <c r="D67" t="n">
-        <v>-2642776</v>
+        <v>-13012012</v>
       </c>
       <c r="E67" t="n">
-        <v>-4480149</v>
+        <v>-9193144</v>
       </c>
       <c r="F67" t="n">
-        <v>-1599352</v>
+        <v>-12297744</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
@@ -7713,20 +7713,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -225 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,692 千股)</t>
         </is>
       </c>
       <c r="C68" t="n">
+        <v>-1500440</v>
+      </c>
+      <c r="D68" t="n">
+        <v>-4221219</v>
+      </c>
+      <c r="E68" t="n">
         <v>-1386123</v>
       </c>
-      <c r="D68" t="n">
+      <c r="F68" t="n">
         <v>-1528898</v>
-      </c>
-      <c r="E68" t="n">
-        <v>-969316</v>
-      </c>
-      <c r="F68" t="n">
-        <v>-1303812</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -7742,20 +7742,20 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -5,832 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,434 千股)</t>
         </is>
       </c>
       <c r="C69" t="n">
+        <v>-2226357</v>
+      </c>
+      <c r="D69" t="n">
+        <v>23706646</v>
+      </c>
+      <c r="E69" t="n">
         <v>-670768</v>
       </c>
-      <c r="D69" t="n">
+      <c r="F69" t="n">
         <v>26140424</v>
-      </c>
-      <c r="E69" t="n">
-        <v>6120524</v>
-      </c>
-      <c r="F69" t="n">
-        <v>31972283</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -7766,58 +7766,58 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -58 千股)</t>
+          <t>📉 20d 巨變(減碼 -536 千股)</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-2292711</v>
+        <v>-4887010</v>
       </c>
       <c r="D70" t="n">
-        <v>-1607776</v>
+        <v>-3178758</v>
       </c>
       <c r="E70" t="n">
-        <v>-2150375</v>
+        <v>-4714730</v>
       </c>
       <c r="F70" t="n">
-        <v>-1549813</v>
+        <v>-2642776</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 356 千股)</t>
+          <t>📉 20d 巨變(減碼 -528 千股)</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>4440229</v>
+        <v>-3033517</v>
       </c>
       <c r="D71" t="n">
-        <v>3609811</v>
+        <v>-2135552</v>
       </c>
       <c r="E71" t="n">
-        <v>4076684</v>
+        <v>-2292711</v>
       </c>
       <c r="F71" t="n">
-        <v>3253326</v>
+        <v>-1607776</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>聯亞</t>
         </is>
       </c>
     </row>
@@ -7829,20 +7829,20 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 6,090 千股)</t>
+          <t>📈 20d 巨變(加碼 6,207 千股)</t>
         </is>
       </c>
       <c r="C72" t="n">
+        <v>-3955531</v>
+      </c>
+      <c r="D72" t="n">
+        <v>-88484636</v>
+      </c>
+      <c r="E72" t="n">
         <v>-19086172</v>
       </c>
-      <c r="D72" t="n">
+      <c r="F72" t="n">
         <v>-94692066</v>
-      </c>
-      <c r="E72" t="n">
-        <v>-12324778</v>
-      </c>
-      <c r="F72" t="n">
-        <v>-100782356</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -7853,348 +7853,348 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -3,487 千股)</t>
+          <t>📈 20d 巨變(加碼 1,310 千股)</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-6506870</v>
+        <v>4990189</v>
       </c>
       <c r="D73" t="n">
-        <v>-18839137</v>
+        <v>4919837</v>
       </c>
       <c r="E73" t="n">
-        <v>-4067225</v>
+        <v>4440229</v>
       </c>
       <c r="F73" t="n">
-        <v>-15352223</v>
+        <v>3609811</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠</t>
+          <t>📉 20d 巨變(減碼 -7,091 千股)</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>25354</v>
+        <v>-5940683</v>
       </c>
       <c r="D74" t="n">
-        <v>-456187</v>
+        <v>-25930206</v>
       </c>
       <c r="E74" t="n">
-        <v>-55689</v>
+        <v>-6506870</v>
       </c>
       <c r="F74" t="n">
-        <v>-453604</v>
+        <v>-18839137</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 128 千股)</t>
+          <t>📉 20d 巨變(減碼 -106 千股)</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>155354</v>
+        <v>791703</v>
       </c>
       <c r="D75" t="n">
-        <v>889910</v>
+        <v>-4710884</v>
       </c>
       <c r="E75" t="n">
-        <v>25049</v>
+        <v>796929</v>
       </c>
       <c r="F75" t="n">
-        <v>761857</v>
+        <v>-4604889</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 30 千股)</t>
+          <t>📈 20d 巨變(加碼 58 千股)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>796929</v>
+        <v>76929</v>
       </c>
       <c r="D76" t="n">
-        <v>-4604889</v>
+        <v>-28071</v>
       </c>
       <c r="E76" t="n">
-        <v>23945</v>
+        <v>16929</v>
       </c>
       <c r="F76" t="n">
-        <v>-4634763</v>
+        <v>-86071</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>友輝</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -38 千股)</t>
+          <t>📉 20d 巨變(減碼 -26 千股)</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>16929</v>
+        <v>3804</v>
       </c>
       <c r="D77" t="n">
-        <v>-86071</v>
+        <v>-482157</v>
       </c>
       <c r="E77" t="n">
-        <v>38000</v>
+        <v>25354</v>
       </c>
       <c r="F77" t="n">
-        <v>-48550</v>
+        <v>-456187</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>德昌</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 274 千股)</t>
+          <t>📉 20d 巨變(減碼 -25 千股)</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-780000</v>
+        <v>364390</v>
       </c>
       <c r="D78" t="n">
-        <v>-7794145</v>
+        <v>864924</v>
       </c>
       <c r="E78" t="n">
-        <v>-557950</v>
+        <v>155354</v>
       </c>
       <c r="F78" t="n">
-        <v>-8068145</v>
+        <v>889910</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>億泰</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -296 千股)</t>
+          <t>📈 20d 巨變(加碼 150 千股)</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-1377519</v>
+        <v>-990710</v>
       </c>
       <c r="D79" t="n">
-        <v>48455</v>
+        <v>-7644067</v>
       </c>
       <c r="E79" t="n">
-        <v>-1201435</v>
+        <v>-780000</v>
       </c>
       <c r="F79" t="n">
-        <v>344541</v>
+        <v>-7794145</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>智易</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -25 千股)</t>
+          <t>📈 20d 巨變(加碼 821 千股)</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>247668</v>
+        <v>-447289</v>
       </c>
       <c r="D80" t="n">
-        <v>-1582668</v>
+        <v>869034</v>
       </c>
       <c r="E80" t="n">
-        <v>702002</v>
+        <v>-1377519</v>
       </c>
       <c r="F80" t="n">
-        <v>-1558021</v>
+        <v>48455</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -4,063 千股)</t>
+          <t>📉 20d 巨變(減碼 -209 千股)</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-3938296</v>
+        <v>-894468</v>
       </c>
       <c r="D81" t="n">
-        <v>-11594702</v>
+        <v>-2768746</v>
       </c>
       <c r="E81" t="n">
-        <v>-3219142</v>
+        <v>-637403</v>
       </c>
       <c r="F81" t="n">
-        <v>-7531248</v>
+        <v>-2559521</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>原相</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 508 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,691 千股)</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-637403</v>
+        <v>-5120170</v>
       </c>
       <c r="D82" t="n">
-        <v>-2559521</v>
+        <v>-14286055</v>
       </c>
       <c r="E82" t="n">
-        <v>-842786</v>
+        <v>-3938296</v>
       </c>
       <c r="F82" t="n">
-        <v>-3067772</v>
+        <v>-11594702</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -3,169 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -311 千股)</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-1719450</v>
+        <v>-276589</v>
       </c>
       <c r="D83" t="n">
-        <v>-2042935</v>
+        <v>-1893791</v>
       </c>
       <c r="E83" t="n">
-        <v>1227270</v>
+        <v>247668</v>
       </c>
       <c r="F83" t="n">
-        <v>1125790</v>
+        <v>-1582668</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>精測</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 15 千股)</t>
+          <t>📈 20d 巨變(加碼 1,842 千股)</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>70991</v>
+        <v>-7602548</v>
       </c>
       <c r="D84" t="n">
-        <v>-606828</v>
+        <v>-201381</v>
       </c>
       <c r="E84" t="n">
-        <v>128107</v>
+        <v>-1719450</v>
       </c>
       <c r="F84" t="n">
-        <v>-622118</v>
+        <v>-2042935</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
@@ -8206,20 +8206,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 160 千股)</t>
+          <t>📈 20d 巨變(加碼 65 千股)</t>
         </is>
       </c>
       <c r="C85" t="n">
+        <v>138201</v>
+      </c>
+      <c r="D85" t="n">
+        <v>729745</v>
+      </c>
+      <c r="E85" t="n">
         <v>199000</v>
       </c>
-      <c r="D85" t="n">
+      <c r="F85" t="n">
         <v>664404</v>
-      </c>
-      <c r="E85" t="n">
-        <v>267000</v>
-      </c>
-      <c r="F85" t="n">
-        <v>504404</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -8230,29 +8230,29 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,397 千股)</t>
+          <t>📉 20d 巨變(減碼 -332 千股)</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>8072182</v>
+        <v>108179</v>
       </c>
       <c r="D86" t="n">
-        <v>8885812</v>
+        <v>-939220</v>
       </c>
       <c r="E86" t="n">
-        <v>6553274</v>
+        <v>70991</v>
       </c>
       <c r="F86" t="n">
-        <v>6489230</v>
+        <v>-606828</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
     </row>
@@ -8264,20 +8264,20 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -85 千股)</t>
+          <t>📉 20d 巨變(減碼 -12 千股)</t>
         </is>
       </c>
       <c r="C87" t="n">
+        <v>-64000</v>
+      </c>
+      <c r="D87" t="n">
+        <v>135009</v>
+      </c>
+      <c r="E87" t="n">
         <v>-6000</v>
       </c>
-      <c r="D87" t="n">
+      <c r="F87" t="n">
         <v>147009</v>
-      </c>
-      <c r="E87" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F87" t="n">
-        <v>232009</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -8288,116 +8288,116 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 5 千股)</t>
+          <t>📉 20d 巨變(減碼 -156 千股)</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>2673600</v>
+        <v>7638318</v>
       </c>
       <c r="D88" t="n">
-        <v>3808580</v>
+        <v>8729983</v>
       </c>
       <c r="E88" t="n">
-        <v>3521318</v>
+        <v>8072182</v>
       </c>
       <c r="F88" t="n">
-        <v>3803322</v>
+        <v>8885812</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 8,074 千股)</t>
+          <t>📉 20d 巨變(減碼 -393 千股)</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>47016221</v>
+        <v>-698227</v>
       </c>
       <c r="D89" t="n">
-        <v>78969213</v>
+        <v>-9494631</v>
       </c>
       <c r="E89" t="n">
-        <v>49524280</v>
+        <v>-199668</v>
       </c>
       <c r="F89" t="n">
-        <v>70894993</v>
+        <v>-9101162</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>宏捷科</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,511 千股)</t>
+          <t>📈 20d 巨變(加碼 464 千股)</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-199668</v>
+        <v>3250475</v>
       </c>
       <c r="D90" t="n">
-        <v>-9101162</v>
+        <v>4272650</v>
       </c>
       <c r="E90" t="n">
-        <v>-920644</v>
+        <v>2673600</v>
       </c>
       <c r="F90" t="n">
-        <v>-10612251</v>
+        <v>3808580</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>研華</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 66 千股)</t>
+          <t>📈 20d 巨變(加碼 2,586 千股)</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>397516</v>
+        <v>36242499</v>
       </c>
       <c r="D91" t="n">
-        <v>-119027</v>
+        <v>81555174</v>
       </c>
       <c r="E91" t="n">
-        <v>10686</v>
+        <v>47016221</v>
       </c>
       <c r="F91" t="n">
-        <v>-185230</v>
+        <v>78969213</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
@@ -8409,20 +8409,20 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 9 千股)</t>
+          <t>📉 20d 巨變(減碼 -50 千股)</t>
         </is>
       </c>
       <c r="C92" t="n">
+        <v>-212378</v>
+      </c>
+      <c r="D92" t="n">
+        <v>-167173</v>
+      </c>
+      <c r="E92" t="n">
         <v>-237413</v>
       </c>
-      <c r="D92" t="n">
+      <c r="F92" t="n">
         <v>-117553</v>
-      </c>
-      <c r="E92" t="n">
-        <v>-125920</v>
-      </c>
-      <c r="F92" t="n">
-        <v>-126768</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -8433,174 +8433,174 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 43 千股)</t>
+          <t>📉 20d 巨變(減碼 -53 千股)</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-29433</v>
+        <v>272296</v>
       </c>
       <c r="D93" t="n">
-        <v>113112</v>
+        <v>-172416</v>
       </c>
       <c r="E93" t="n">
-        <v>35353</v>
+        <v>397516</v>
       </c>
       <c r="F93" t="n">
-        <v>69875</v>
+        <v>-119027</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>中保科</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 5 千股)</t>
+          <t>📈 20d 巨變(加碼 1,132 千股)</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>27091</v>
+        <v>264303</v>
       </c>
       <c r="D94" t="n">
-        <v>-54178</v>
+        <v>-4569412</v>
       </c>
       <c r="E94" t="n">
-        <v>5070</v>
+        <v>182483</v>
       </c>
       <c r="F94" t="n">
-        <v>-59199</v>
+        <v>-5701351</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 543 千股)</t>
+          <t>📉 20d 巨變(減碼 -53 千股)</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>182483</v>
+        <v>-44328</v>
       </c>
       <c r="D95" t="n">
-        <v>-5701351</v>
+        <v>59974</v>
       </c>
       <c r="E95" t="n">
-        <v>39169</v>
+        <v>-29433</v>
       </c>
       <c r="F95" t="n">
-        <v>-6243970</v>
+        <v>113112</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>安碁資訊</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 43 千股)</t>
+          <t>📉 20d 巨變(減碼 -19,066 千股)</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>3046371</v>
+        <v>23695530</v>
       </c>
       <c r="D96" t="n">
-        <v>18204028</v>
+        <v>-11647115</v>
       </c>
       <c r="E96" t="n">
-        <v>3556484</v>
+        <v>4640801</v>
       </c>
       <c r="F96" t="n">
-        <v>18161267</v>
+        <v>7419144</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 27,853 千股)</t>
+          <t>📈 20d 巨變(加碼 3,289 千股)</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>4640801</v>
+        <v>6340567</v>
       </c>
       <c r="D97" t="n">
-        <v>7419144</v>
+        <v>12505517</v>
       </c>
       <c r="E97" t="n">
-        <v>-69311123</v>
+        <v>3918493</v>
       </c>
       <c r="F97" t="n">
-        <v>-20433393</v>
+        <v>9216467</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 3,162 千股)</t>
+          <t>📉 20d 巨變(減碼 -975 千股)</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>3918493</v>
+        <v>2187737</v>
       </c>
       <c r="D98" t="n">
-        <v>9216467</v>
+        <v>17228760</v>
       </c>
       <c r="E98" t="n">
-        <v>290258</v>
+        <v>3046371</v>
       </c>
       <c r="F98" t="n">
-        <v>6054546</v>
+        <v>18204028</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
@@ -8612,20 +8612,20 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -673 千股)</t>
+          <t>📈 20d 巨變(加碼 237 千股)</t>
         </is>
       </c>
       <c r="C99" t="n">
+        <v>-949042</v>
+      </c>
+      <c r="D99" t="n">
+        <v>-598424</v>
+      </c>
+      <c r="E99" t="n">
         <v>-1183926</v>
       </c>
-      <c r="D99" t="n">
+      <c r="F99" t="n">
         <v>-835387</v>
-      </c>
-      <c r="E99" t="n">
-        <v>-835460</v>
-      </c>
-      <c r="F99" t="n">
-        <v>-161986</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -8641,20 +8641,20 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -210 千股)</t>
+          <t>📈 20d 巨變(加碼 348 千股)</t>
         </is>
       </c>
       <c r="C100" t="n">
+        <v>-3602128</v>
+      </c>
+      <c r="D100" t="n">
+        <v>-12757670</v>
+      </c>
+      <c r="E100" t="n">
         <v>-4139047</v>
       </c>
-      <c r="D100" t="n">
+      <c r="F100" t="n">
         <v>-13105329</v>
-      </c>
-      <c r="E100" t="n">
-        <v>-4314230</v>
-      </c>
-      <c r="F100" t="n">
-        <v>-12895569</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -8670,20 +8670,20 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -24 千股)</t>
+          <t>📉 20d 巨變(減碼 -22 千股)</t>
         </is>
       </c>
       <c r="C101" t="n">
+        <v>-34985</v>
+      </c>
+      <c r="D101" t="n">
+        <v>122724</v>
+      </c>
+      <c r="E101" t="n">
         <v>-67592</v>
       </c>
-      <c r="D101" t="n">
+      <c r="F101" t="n">
         <v>144327</v>
-      </c>
-      <c r="E101" t="n">
-        <v>-98233</v>
-      </c>
-      <c r="F101" t="n">
-        <v>167885</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -8694,87 +8694,87 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -688 千股)</t>
+          <t>📉 20d 巨變(減碼 -293 千股)</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-2982060</v>
+        <v>-349998</v>
       </c>
       <c r="D102" t="n">
-        <v>-10214001</v>
+        <v>-2514433</v>
       </c>
       <c r="E102" t="n">
-        <v>-1360213</v>
+        <v>-59892</v>
       </c>
       <c r="F102" t="n">
-        <v>-9526438</v>
+        <v>-2221564</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>高技</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 67 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,359 千股)</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-170103</v>
+        <v>-5886883</v>
       </c>
       <c r="D103" t="n">
-        <v>-1175206</v>
+        <v>-11573309</v>
       </c>
       <c r="E103" t="n">
-        <v>18035</v>
+        <v>-2982060</v>
       </c>
       <c r="F103" t="n">
-        <v>-1242501</v>
+        <v>-10214001</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>金像電</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,182 千股)</t>
+          <t>📉 20d 巨變(減碼 -205 千股)</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-59892</v>
+        <v>-608136</v>
       </c>
       <c r="D104" t="n">
-        <v>-2221564</v>
+        <v>-1379810</v>
       </c>
       <c r="E104" t="n">
-        <v>-30968</v>
+        <v>-170103</v>
       </c>
       <c r="F104" t="n">
-        <v>-3404039</v>
+        <v>-1175206</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>萬潤</t>
         </is>
       </c>
     </row>

--- a/data/台股_外資雷達.xlsx
+++ b/data/台股_外資雷達.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36242</v>
+        <v>26808</v>
       </c>
       <c r="D2" t="n">
-        <v>81555</v>
+        <v>83075</v>
       </c>
       <c r="E2" t="n">
-        <v>179344</v>
+        <v>174769</v>
       </c>
       <c r="F2" t="n">
-        <v>-1752</v>
+        <v>-1665</v>
       </c>
       <c r="G2" t="n">
-        <v>-837</v>
+        <v>-830</v>
       </c>
       <c r="H2" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -547,22 +547,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7465</v>
+        <v>8908</v>
       </c>
       <c r="D3" t="n">
-        <v>52361</v>
+        <v>50779</v>
       </c>
       <c r="E3" t="n">
-        <v>222162</v>
+        <v>201086</v>
       </c>
       <c r="F3" t="n">
-        <v>2597</v>
+        <v>2447</v>
       </c>
       <c r="G3" t="n">
-        <v>6585</v>
+        <v>5708</v>
       </c>
       <c r="H3" t="n">
-        <v>-3023</v>
+        <v>-2331</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12311</v>
+        <v>25887</v>
       </c>
       <c r="D4" t="n">
-        <v>36769</v>
+        <v>44906</v>
       </c>
       <c r="E4" t="n">
-        <v>5026</v>
+        <v>14206</v>
       </c>
       <c r="F4" t="n">
-        <v>-1654</v>
+        <v>481</v>
       </c>
       <c r="G4" t="n">
-        <v>-11623</v>
+        <v>-8968</v>
       </c>
       <c r="H4" t="n">
-        <v>3225</v>
+        <v>4277</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -640,31 +640,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-2226</v>
+        <v>1602</v>
       </c>
       <c r="D5" t="n">
-        <v>23707</v>
+        <v>22132</v>
       </c>
       <c r="E5" t="n">
-        <v>-9555</v>
+        <v>90895</v>
       </c>
       <c r="F5" t="n">
-        <v>14039</v>
+        <v>1235</v>
       </c>
       <c r="G5" t="n">
-        <v>20795</v>
+        <v>5518</v>
       </c>
       <c r="H5" t="n">
-        <v>1428</v>
+        <v>-1729</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -677,45 +677,45 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2188</v>
+        <v>-4794</v>
       </c>
       <c r="D6" t="n">
-        <v>17229</v>
+        <v>20273</v>
       </c>
       <c r="E6" t="n">
-        <v>108148</v>
+        <v>-7094</v>
       </c>
       <c r="F6" t="n">
-        <v>-121</v>
+        <v>15199</v>
       </c>
       <c r="G6" t="n">
-        <v>-1525</v>
+        <v>22314</v>
       </c>
       <c r="H6" t="n">
-        <v>-610</v>
+        <v>1785</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -728,15 +728,15 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>332</v>
+        <v>906</v>
       </c>
       <c r="D7" t="n">
-        <v>15635</v>
+        <v>16464</v>
       </c>
       <c r="E7" t="n">
-        <v>22830</v>
+        <v>23764</v>
       </c>
       <c r="F7" t="n">
-        <v>-81</v>
+        <v>-70</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H7" t="n">
-        <v>180</v>
+        <v>242</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -793,31 +793,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>28359</v>
+        <v>8882</v>
       </c>
       <c r="D8" t="n">
-        <v>15546</v>
+        <v>13632</v>
       </c>
       <c r="E8" t="n">
-        <v>89567</v>
+        <v>14389</v>
       </c>
       <c r="F8" t="n">
-        <v>3791</v>
+        <v>120</v>
       </c>
       <c r="G8" t="n">
-        <v>-6247</v>
+        <v>2611</v>
       </c>
       <c r="H8" t="n">
-        <v>-2930</v>
+        <v>1757</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -826,49 +826,49 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6341</v>
+        <v>793</v>
       </c>
       <c r="D9" t="n">
-        <v>12506</v>
+        <v>13267</v>
       </c>
       <c r="E9" t="n">
-        <v>12158</v>
+        <v>102420</v>
       </c>
       <c r="F9" t="n">
-        <v>-272</v>
+        <v>250</v>
       </c>
       <c r="G9" t="n">
-        <v>2084</v>
+        <v>-198</v>
       </c>
       <c r="H9" t="n">
-        <v>1796</v>
+        <v>-516</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -877,53 +877,53 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4273</v>
+        <v>10840</v>
       </c>
       <c r="D10" t="n">
-        <v>8801</v>
+        <v>10168</v>
       </c>
       <c r="E10" t="n">
-        <v>3918</v>
+        <v>1757</v>
       </c>
       <c r="F10" t="n">
-        <v>-9366</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-19913</v>
+        <v>-8</v>
       </c>
       <c r="H10" t="n">
-        <v>1046</v>
+        <v>629</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>🟢 加碼</t>
+          <t>🚀 大買</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -932,96 +932,96 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7638</v>
+        <v>-1955</v>
       </c>
       <c r="D11" t="n">
-        <v>8730</v>
+        <v>8465</v>
       </c>
       <c r="E11" t="n">
-        <v>-582</v>
+        <v>463659</v>
       </c>
       <c r="F11" t="n">
+        <v>18933</v>
+      </c>
+      <c r="G11" t="n">
+        <v>34281</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-1856</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>🟢 加碼</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>92</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
         <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-8</v>
-      </c>
-      <c r="H11" t="n">
-        <v>641</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>🟢 加碼</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>75</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M11" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-1083</v>
+        <v>4127</v>
       </c>
       <c r="D12" t="n">
-        <v>7730</v>
+        <v>7445</v>
       </c>
       <c r="E12" t="n">
-        <v>12033</v>
+        <v>3364</v>
       </c>
       <c r="F12" t="n">
-        <v>145</v>
+        <v>-9445</v>
       </c>
       <c r="G12" t="n">
-        <v>918</v>
+        <v>-20259</v>
       </c>
       <c r="H12" t="n">
-        <v>1213</v>
+        <v>1004</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1030,49 +1030,49 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>559</v>
+        <v>-1305</v>
       </c>
       <c r="D13" t="n">
-        <v>5651</v>
+        <v>6896</v>
       </c>
       <c r="E13" t="n">
-        <v>24797</v>
+        <v>12217</v>
       </c>
       <c r="F13" t="n">
-        <v>1254</v>
+        <v>358</v>
       </c>
       <c r="G13" t="n">
-        <v>809</v>
+        <v>659</v>
       </c>
       <c r="H13" t="n">
-        <v>203</v>
+        <v>979</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1085,15 +1085,15 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1108,22 +1108,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4990</v>
+        <v>7073</v>
       </c>
       <c r="D14" t="n">
-        <v>4920</v>
+        <v>6495</v>
       </c>
       <c r="E14" t="n">
-        <v>-911</v>
+        <v>482</v>
       </c>
       <c r="F14" t="n">
-        <v>-0</v>
+        <v>-190</v>
       </c>
       <c r="G14" t="n">
-        <v>2238</v>
+        <v>2168</v>
       </c>
       <c r="H14" t="n">
-        <v>-99</v>
+        <v>-4</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1150,31 +1150,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1933</v>
+        <v>1277</v>
       </c>
       <c r="D15" t="n">
-        <v>4726</v>
+        <v>5776</v>
       </c>
       <c r="E15" t="n">
-        <v>14532</v>
+        <v>24706</v>
       </c>
       <c r="F15" t="n">
-        <v>-2728</v>
+        <v>1231</v>
       </c>
       <c r="G15" t="n">
-        <v>-7274</v>
+        <v>854</v>
       </c>
       <c r="H15" t="n">
-        <v>-55</v>
+        <v>247</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1183,19 +1183,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1210,22 +1210,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3250</v>
+        <v>2905</v>
       </c>
       <c r="D16" t="n">
-        <v>4273</v>
+        <v>5284</v>
       </c>
       <c r="E16" t="n">
-        <v>2168</v>
+        <v>1695</v>
       </c>
       <c r="F16" t="n">
-        <v>-135</v>
+        <v>-246</v>
       </c>
       <c r="G16" t="n">
-        <v>637</v>
+        <v>-93</v>
       </c>
       <c r="H16" t="n">
-        <v>13</v>
+        <v>-42</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1252,31 +1252,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>115</v>
+        <v>1320</v>
       </c>
       <c r="D17" t="n">
-        <v>2638</v>
+        <v>4652</v>
       </c>
       <c r="E17" t="n">
-        <v>6225</v>
+        <v>15380</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>-2170</v>
       </c>
       <c r="G17" t="n">
-        <v>-359</v>
+        <v>-7169</v>
       </c>
       <c r="H17" t="n">
-        <v>51</v>
+        <v>-15</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1285,49 +1285,49 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>466</v>
+        <v>193</v>
       </c>
       <c r="D18" t="n">
-        <v>2598</v>
+        <v>3176</v>
       </c>
       <c r="E18" t="n">
-        <v>778</v>
+        <v>5991</v>
       </c>
       <c r="F18" t="n">
-        <v>896</v>
+        <v>-60</v>
       </c>
       <c r="G18" t="n">
-        <v>1032</v>
+        <v>-423</v>
       </c>
       <c r="H18" t="n">
-        <v>-144</v>
+        <v>107</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1340,11 +1340,11 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M18" t="n">
@@ -1354,133 +1354,133 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>700</v>
+        <v>765</v>
       </c>
       <c r="D19" t="n">
-        <v>1856</v>
+        <v>2845</v>
       </c>
       <c r="E19" t="n">
-        <v>10669</v>
+        <v>988</v>
       </c>
       <c r="F19" t="n">
-        <v>837</v>
+        <v>984</v>
       </c>
       <c r="G19" t="n">
-        <v>-9847</v>
+        <v>1118</v>
       </c>
       <c r="H19" t="n">
-        <v>19</v>
+        <v>-147</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>🟡 中性</t>
+          <t>🟢 加碼</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>322</v>
+        <v>1212</v>
       </c>
       <c r="D20" t="n">
-        <v>1849</v>
+        <v>2497</v>
       </c>
       <c r="E20" t="n">
-        <v>-2761</v>
+        <v>11132</v>
       </c>
       <c r="F20" t="n">
-        <v>-190</v>
+        <v>887</v>
       </c>
       <c r="G20" t="n">
-        <v>-219</v>
+        <v>-8799</v>
       </c>
       <c r="H20" t="n">
-        <v>254</v>
+        <v>58</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>🟡 中性</t>
+          <t>🟢 加碼</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-14547</v>
+        <v>916</v>
       </c>
       <c r="D21" t="n">
-        <v>1205</v>
+        <v>1324</v>
       </c>
       <c r="E21" t="n">
-        <v>491027</v>
+        <v>-9114</v>
       </c>
       <c r="F21" t="n">
-        <v>17455</v>
+        <v>486</v>
       </c>
       <c r="G21" t="n">
-        <v>30296</v>
+        <v>1203</v>
       </c>
       <c r="H21" t="n">
-        <v>-2064</v>
+        <v>-276</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>193</v>
+        <v>386</v>
       </c>
       <c r="D22" t="n">
-        <v>1088</v>
+        <v>1248</v>
       </c>
       <c r="E22" t="n">
-        <v>2241</v>
+        <v>2933</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1531,7 +1531,7 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-34</v>
+        <v>-38</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1567,22 +1567,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1133</v>
+        <v>1154</v>
       </c>
       <c r="D23" t="n">
-        <v>1081</v>
+        <v>1075</v>
       </c>
       <c r="E23" t="n">
-        <v>2666</v>
+        <v>2842</v>
       </c>
       <c r="F23" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="H23" t="n">
-        <v>-39</v>
+        <v>-45</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1609,31 +1609,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-447</v>
+        <v>1360</v>
       </c>
       <c r="D24" t="n">
-        <v>869</v>
+        <v>897</v>
       </c>
       <c r="E24" t="n">
-        <v>3449</v>
+        <v>29</v>
       </c>
       <c r="F24" t="n">
-        <v>-487</v>
+        <v>-2896</v>
       </c>
       <c r="G24" t="n">
-        <v>-1979</v>
+        <v>-4250</v>
       </c>
       <c r="H24" t="n">
-        <v>-139</v>
+        <v>336</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1642,19 +1642,19 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -1669,13 +1669,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>364</v>
+        <v>401</v>
       </c>
       <c r="D25" t="n">
-        <v>865</v>
+        <v>877</v>
       </c>
       <c r="E25" t="n">
-        <v>1211</v>
+        <v>1215</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1684,7 +1684,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1711,31 +1711,31 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>210</v>
+        <v>382</v>
       </c>
       <c r="D26" t="n">
-        <v>863</v>
+        <v>847</v>
       </c>
       <c r="E26" t="n">
-        <v>-280</v>
+        <v>-3556</v>
       </c>
       <c r="F26" t="n">
-        <v>53</v>
+        <v>-251</v>
       </c>
       <c r="G26" t="n">
-        <v>47</v>
+        <v>595</v>
       </c>
       <c r="H26" t="n">
-        <v>-49</v>
+        <v>228</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1748,15 +1748,15 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1771,13 +1771,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D27" t="n">
-        <v>730</v>
+        <v>700</v>
       </c>
       <c r="E27" t="n">
-        <v>-231</v>
+        <v>-209</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1822,22 +1822,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>18</v>
+        <v>319</v>
       </c>
       <c r="D28" t="n">
-        <v>614</v>
+        <v>695</v>
       </c>
       <c r="E28" t="n">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="F28" t="n">
-        <v>-827</v>
+        <v>-849</v>
       </c>
       <c r="G28" t="n">
-        <v>-2676</v>
+        <v>-2586</v>
       </c>
       <c r="H28" t="n">
-        <v>-30</v>
+        <v>-1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1864,31 +1864,31 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>852</v>
+        <v>530</v>
       </c>
       <c r="D29" t="n">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="E29" t="n">
-        <v>-723</v>
+        <v>-1299</v>
       </c>
       <c r="F29" t="n">
-        <v>-2342</v>
+        <v>-1079</v>
       </c>
       <c r="G29" t="n">
-        <v>-3744</v>
+        <v>-2544</v>
       </c>
       <c r="H29" t="n">
-        <v>355</v>
+        <v>135</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -1924,13 +1924,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>582</v>
+        <v>657</v>
       </c>
       <c r="D30" t="n">
-        <v>496</v>
+        <v>586</v>
       </c>
       <c r="E30" t="n">
-        <v>2965</v>
+        <v>2968</v>
       </c>
       <c r="F30" t="n">
         <v>-5</v>
@@ -1939,7 +1939,7 @@
         <v>-38</v>
       </c>
       <c r="H30" t="n">
-        <v>-39</v>
+        <v>-37</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1966,31 +1966,31 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-32</v>
+        <v>59</v>
       </c>
       <c r="D31" t="n">
-        <v>391</v>
+        <v>444</v>
       </c>
       <c r="E31" t="n">
-        <v>5015</v>
+        <v>-593</v>
       </c>
       <c r="F31" t="n">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="G31" t="n">
-        <v>2031</v>
+        <v>181</v>
       </c>
       <c r="H31" t="n">
-        <v>281</v>
+        <v>-52</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2003,96 +2003,96 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>60</v>
+        <v>216</v>
       </c>
       <c r="D32" t="n">
-        <v>354</v>
+        <v>433</v>
       </c>
       <c r="E32" t="n">
-        <v>1068</v>
+        <v>-151</v>
       </c>
       <c r="F32" t="n">
+        <v>215</v>
+      </c>
+      <c r="G32" t="n">
+        <v>442</v>
+      </c>
+      <c r="H32" t="n">
+        <v>122</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>89</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>🚀 加速器</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
         <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>7</v>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K32" t="n">
-        <v>74</v>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M32" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-670</v>
+        <v>57</v>
       </c>
       <c r="D33" t="n">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="E33" t="n">
-        <v>-561</v>
+        <v>1138</v>
       </c>
       <c r="F33" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2113,37 +2113,37 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>305</v>
+        <v>1486</v>
       </c>
       <c r="D34" t="n">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="E34" t="n">
-        <v>-1769</v>
+        <v>7326</v>
       </c>
       <c r="F34" t="n">
-        <v>-1030</v>
+        <v>-3</v>
       </c>
       <c r="G34" t="n">
-        <v>-608</v>
+        <v>-19</v>
       </c>
       <c r="H34" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2164,37 +2164,37 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>197</v>
+        <v>285</v>
       </c>
       <c r="D35" t="n">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="E35" t="n">
-        <v>-576</v>
+        <v>-1742</v>
       </c>
       <c r="F35" t="n">
-        <v>103</v>
+        <v>-1</v>
       </c>
       <c r="G35" t="n">
-        <v>446</v>
+        <v>-1</v>
       </c>
       <c r="H35" t="n">
-        <v>125</v>
+        <v>-5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2203,15 +2203,15 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M35" t="n">
@@ -2221,31 +2221,31 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>278</v>
+        <v>142</v>
       </c>
       <c r="D36" t="n">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="E36" t="n">
-        <v>-1897</v>
+        <v>575</v>
       </c>
       <c r="F36" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-11</v>
+        <v>50</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2258,45 +2258,45 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-120</v>
+        <v>-226</v>
       </c>
       <c r="D37" t="n">
-        <v>160</v>
+        <v>202</v>
       </c>
       <c r="E37" t="n">
-        <v>475</v>
+        <v>783</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>-729</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-1976</v>
       </c>
       <c r="H37" t="n">
-        <v>47</v>
+        <v>-69</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2305,15 +2305,15 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M37" t="n">
@@ -2323,31 +2323,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-64</v>
+        <v>-247</v>
       </c>
       <c r="D38" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="E38" t="n">
-        <v>799</v>
+        <v>-1725</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>-1055</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-804</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2356,11 +2356,11 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2368,76 +2368,88 @@
         </is>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-35</v>
+        <v>67</v>
       </c>
       <c r="D39" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E39" t="n">
-        <v>-313</v>
+        <v>789</v>
       </c>
       <c r="F39" t="n">
-        <v>126</v>
+        <v>-7</v>
       </c>
       <c r="G39" t="n">
-        <v>311</v>
+        <v>-28</v>
       </c>
       <c r="H39" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>86</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>📉 減速</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>33</v>
+        <v>-505</v>
       </c>
       <c r="D40" t="n">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="E40" t="n">
-        <v>785</v>
+        <v>-1138</v>
       </c>
       <c r="F40" t="n">
-        <v>-23</v>
+        <v>55</v>
       </c>
       <c r="G40" t="n">
-        <v>-28</v>
+        <v>139</v>
       </c>
       <c r="H40" t="n">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2446,49 +2458,49 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-44</v>
+        <v>-750</v>
       </c>
       <c r="D41" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="E41" t="n">
-        <v>127</v>
+        <v>4777</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1974</v>
       </c>
       <c r="H41" t="n">
-        <v>23</v>
+        <v>253</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2497,40 +2509,40 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>方土霖</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>-42</v>
       </c>
       <c r="D42" t="n">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>680</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -2539,28 +2551,28 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>77</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>🚀 加速器</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
         <v>0</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K42" t="n">
-        <v>89</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M42" t="n">
-        <v>-2</v>
       </c>
     </row>
     <row r="43">
@@ -2575,22 +2587,22 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>165</v>
+        <v>393</v>
       </c>
       <c r="D43" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="E43" t="n">
-        <v>-3516</v>
+        <v>-2831</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>-227</v>
+        <v>-235</v>
       </c>
       <c r="H43" t="n">
-        <v>2370</v>
+        <v>2036</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2617,82 +2629,70 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-1211</v>
+        <v>-10</v>
       </c>
       <c r="D44" t="n">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="E44" t="n">
-        <v>-10850</v>
+        <v>-346</v>
       </c>
       <c r="F44" t="n">
-        <v>432</v>
+        <v>147</v>
       </c>
       <c r="G44" t="n">
-        <v>1131</v>
+        <v>327</v>
       </c>
       <c r="H44" t="n">
-        <v>-257</v>
+        <v>4</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K44" t="n">
-        <v>90</v>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-14</v>
+        <v>960</v>
       </c>
       <c r="D45" t="n">
-        <v>-6</v>
+        <v>55</v>
       </c>
       <c r="E45" t="n">
-        <v>-22</v>
+        <v>-4284</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>196</v>
       </c>
       <c r="H45" t="n">
-        <v>-1</v>
+        <v>-51</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2701,11 +2701,11 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2713,28 +2713,28 @@
         </is>
       </c>
       <c r="M45" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="D46" t="n">
-        <v>-28</v>
+        <v>53</v>
       </c>
       <c r="E46" t="n">
-        <v>-120</v>
+        <v>131</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2743,7 +2743,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>-0</v>
+        <v>25</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2760,32 +2760,32 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>方土霖</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-20</v>
+        <v>-1</v>
       </c>
       <c r="D47" t="n">
-        <v>-41</v>
+        <v>50</v>
       </c>
       <c r="E47" t="n">
-        <v>682</v>
+        <v>49</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -2794,58 +2794,58 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>89</v>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M47" t="n">
         <v>-2</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K47" t="n">
-        <v>91</v>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M47" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-166</v>
+        <v>107</v>
       </c>
       <c r="D48" t="n">
-        <v>-42</v>
+        <v>18</v>
       </c>
       <c r="E48" t="n">
-        <v>-1788</v>
+        <v>-62</v>
       </c>
       <c r="F48" t="n">
-        <v>-171</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>-1649</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2854,40 +2854,40 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>大車隊</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>46</v>
+        <v>-36</v>
       </c>
       <c r="D49" t="n">
-        <v>-56</v>
+        <v>-15</v>
       </c>
       <c r="E49" t="n">
-        <v>-11</v>
+        <v>-30</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -2896,7 +2896,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2905,49 +2905,49 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>552</v>
+        <v>50</v>
       </c>
       <c r="D50" t="n">
-        <v>-62</v>
+        <v>-17</v>
       </c>
       <c r="E50" t="n">
-        <v>-119679</v>
+        <v>4</v>
       </c>
       <c r="F50" t="n">
-        <v>1306</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>-2066</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>4838</v>
+        <v>-3</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2956,49 +2956,49 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-473</v>
+        <v>82</v>
       </c>
       <c r="D51" t="n">
-        <v>-113</v>
+        <v>-19</v>
       </c>
       <c r="E51" t="n">
-        <v>-1074</v>
+        <v>-256</v>
       </c>
       <c r="F51" t="n">
-        <v>147</v>
+        <v>-9</v>
       </c>
       <c r="G51" t="n">
-        <v>-345</v>
+        <v>-277</v>
       </c>
       <c r="H51" t="n">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3007,49 +3007,49 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>774</v>
+        <v>-17</v>
       </c>
       <c r="D52" t="n">
-        <v>-144</v>
+        <v>-67</v>
       </c>
       <c r="E52" t="n">
-        <v>-4918</v>
+        <v>664</v>
       </c>
       <c r="F52" t="n">
-        <v>-29</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-53</v>
+        <v>-2</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3058,49 +3058,49 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-40</v>
+        <v>-500</v>
       </c>
       <c r="D53" t="n">
-        <v>-156</v>
+        <v>-99</v>
       </c>
       <c r="E53" t="n">
-        <v>-351</v>
+        <v>-934</v>
       </c>
       <c r="F53" t="n">
-        <v>-29</v>
+        <v>167</v>
       </c>
       <c r="G53" t="n">
-        <v>-277</v>
+        <v>-480</v>
       </c>
       <c r="H53" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3109,19 +3109,19 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
@@ -3136,22 +3136,22 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-212</v>
+        <v>-146</v>
       </c>
       <c r="D54" t="n">
-        <v>-167</v>
+        <v>-153</v>
       </c>
       <c r="E54" t="n">
-        <v>-41</v>
+        <v>34</v>
       </c>
       <c r="F54" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
         <v>50</v>
       </c>
       <c r="H54" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3178,31 +3178,31 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>272</v>
+        <v>71</v>
       </c>
       <c r="D55" t="n">
-        <v>-172</v>
+        <v>-161</v>
       </c>
       <c r="E55" t="n">
-        <v>2785</v>
+        <v>473</v>
       </c>
       <c r="F55" t="n">
-        <v>-319</v>
+        <v>-1</v>
       </c>
       <c r="G55" t="n">
-        <v>-255</v>
+        <v>-41</v>
       </c>
       <c r="H55" t="n">
-        <v>25</v>
+        <v>-21</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3211,49 +3211,49 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>49</v>
+        <v>-11</v>
       </c>
       <c r="D56" t="n">
-        <v>-178</v>
+        <v>-329</v>
       </c>
       <c r="E56" t="n">
-        <v>419</v>
+        <v>1412</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="G56" t="n">
-        <v>-40</v>
+        <v>53</v>
       </c>
       <c r="H56" t="n">
-        <v>-22</v>
+        <v>3</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3266,45 +3266,45 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🐌 龜速*</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>德昌</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-7603</v>
+        <v>19</v>
       </c>
       <c r="D57" t="n">
-        <v>-201</v>
+        <v>-404</v>
       </c>
       <c r="E57" t="n">
-        <v>89826</v>
+        <v>-1304</v>
       </c>
       <c r="F57" t="n">
-        <v>1162</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>5134</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-1500</v>
+        <v>-7</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3317,45 +3317,45 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>智冠</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-80</v>
+        <v>-33</v>
       </c>
       <c r="D58" t="n">
-        <v>-349</v>
+        <v>-422</v>
       </c>
       <c r="E58" t="n">
-        <v>1245</v>
+        <v>-834</v>
       </c>
       <c r="F58" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3368,45 +3368,45 @@
         </is>
       </c>
       <c r="K58" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>🐌 龜速*</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-1457</v>
+        <v>-55</v>
       </c>
       <c r="D59" t="n">
-        <v>-432</v>
+        <v>-467</v>
       </c>
       <c r="E59" t="n">
-        <v>8818</v>
+        <v>-2820</v>
       </c>
       <c r="F59" t="n">
-        <v>847</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>-316</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>15</v>
+        <v>-37</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3415,15 +3415,15 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M59" t="n">
@@ -3433,31 +3433,31 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-19</v>
+        <v>176</v>
       </c>
       <c r="D60" t="n">
-        <v>-432</v>
+        <v>-471</v>
       </c>
       <c r="E60" t="n">
-        <v>-812</v>
+        <v>2406</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>-297</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>-255</v>
       </c>
       <c r="H60" t="n">
-        <v>-3</v>
+        <v>26</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3466,11 +3466,11 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -3493,13 +3493,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="D61" t="n">
-        <v>-477</v>
+        <v>-490</v>
       </c>
       <c r="E61" t="n">
-        <v>-1920</v>
+        <v>-1467</v>
       </c>
       <c r="F61" t="n">
         <v>0</v>
@@ -3508,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-51</v>
+        <v>-24</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3535,82 +3535,82 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>1697</v>
       </c>
       <c r="D62" t="n">
-        <v>-482</v>
+        <v>-612</v>
       </c>
       <c r="E62" t="n">
-        <v>-1839</v>
+        <v>-1295</v>
       </c>
       <c r="F62" t="n">
+        <v>-2553</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-2648</v>
+      </c>
+      <c r="H62" t="n">
+        <v>253</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>64</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>🚀 加速器</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
         <v>0</v>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-1</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K62" t="n">
-        <v>79</v>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>🛬 穩定</t>
-        </is>
-      </c>
-      <c r="M62" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-56</v>
+        <v>-748</v>
       </c>
       <c r="D63" t="n">
-        <v>-518</v>
+        <v>-872</v>
       </c>
       <c r="E63" t="n">
-        <v>-2592</v>
+        <v>981</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>495</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>1319</v>
       </c>
       <c r="H63" t="n">
-        <v>-33</v>
+        <v>-80</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -3619,49 +3619,49 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-949</v>
+        <v>151</v>
       </c>
       <c r="D64" t="n">
-        <v>-598</v>
+        <v>-957</v>
       </c>
       <c r="E64" t="n">
-        <v>539</v>
+        <v>1195</v>
       </c>
       <c r="F64" t="n">
-        <v>678</v>
+        <v>-73</v>
       </c>
       <c r="G64" t="n">
-        <v>1400</v>
+        <v>-482</v>
       </c>
       <c r="H64" t="n">
-        <v>-126</v>
+        <v>50</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3670,49 +3670,49 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1275</v>
+        <v>80</v>
       </c>
       <c r="D65" t="n">
-        <v>-669</v>
+        <v>-984</v>
       </c>
       <c r="E65" t="n">
-        <v>6992</v>
+        <v>474</v>
       </c>
       <c r="F65" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>-19</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>78</v>
+        <v>-282</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3721,11 +3721,11 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3733,37 +3733,37 @@
         </is>
       </c>
       <c r="M65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1373</v>
+        <v>-27</v>
       </c>
       <c r="D66" t="n">
-        <v>-711</v>
+        <v>-1065</v>
       </c>
       <c r="E66" t="n">
-        <v>-1345</v>
+        <v>-1469</v>
       </c>
       <c r="F66" t="n">
-        <v>-2708</v>
+        <v>-374</v>
       </c>
       <c r="G66" t="n">
-        <v>-2606</v>
+        <v>-38</v>
       </c>
       <c r="H66" t="n">
-        <v>254</v>
+        <v>-62</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3772,49 +3772,49 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-670</v>
+        <v>-1</v>
       </c>
       <c r="D67" t="n">
-        <v>-888</v>
+        <v>-1101</v>
       </c>
       <c r="E67" t="n">
-        <v>-7403</v>
+        <v>-6890</v>
       </c>
       <c r="F67" t="n">
-        <v>-26</v>
+        <v>-2967</v>
       </c>
       <c r="G67" t="n">
-        <v>79</v>
+        <v>-8678</v>
       </c>
       <c r="H67" t="n">
-        <v>378</v>
+        <v>439</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3823,49 +3823,49 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M67" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>108</v>
+        <v>-377</v>
       </c>
       <c r="D68" t="n">
-        <v>-939</v>
+        <v>-1183</v>
       </c>
       <c r="E68" t="n">
-        <v>1629</v>
+        <v>513</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>-862</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>-196</v>
       </c>
       <c r="H68" t="n">
-        <v>-216</v>
+        <v>35</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3874,49 +3874,49 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>53</v>
+        <v>146</v>
       </c>
       <c r="D69" t="n">
-        <v>-984</v>
+        <v>-1236</v>
       </c>
       <c r="E69" t="n">
-        <v>1432</v>
+        <v>1669</v>
       </c>
       <c r="F69" t="n">
-        <v>-120</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>-482</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>36</v>
+        <v>-243</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3925,49 +3925,49 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯合</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-388</v>
+        <v>-190</v>
       </c>
       <c r="D70" t="n">
-        <v>-1084</v>
+        <v>-1317</v>
       </c>
       <c r="E70" t="n">
-        <v>-6946</v>
+        <v>-1905</v>
       </c>
       <c r="F70" t="n">
-        <v>-2789</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>-8645</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>416</v>
+        <v>1</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -3988,88 +3988,76 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-52</v>
+        <v>-502</v>
       </c>
       <c r="D71" t="n">
-        <v>-1102</v>
+        <v>-1348</v>
       </c>
       <c r="E71" t="n">
-        <v>-1589</v>
+        <v>720</v>
       </c>
       <c r="F71" t="n">
-        <v>-275</v>
+        <v>-412</v>
       </c>
       <c r="G71" t="n">
-        <v>-31</v>
+        <v>1637</v>
       </c>
       <c r="H71" t="n">
-        <v>-66</v>
+        <v>-0</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K71" t="n">
-        <v>96</v>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M71" t="n">
-        <v>1</v>
-      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-465</v>
+        <v>-1552</v>
       </c>
       <c r="D72" t="n">
-        <v>-1210</v>
+        <v>-1417</v>
       </c>
       <c r="E72" t="n">
-        <v>375</v>
+        <v>-7431</v>
       </c>
       <c r="F72" t="n">
-        <v>-609</v>
+        <v>429</v>
       </c>
       <c r="G72" t="n">
-        <v>90</v>
+        <v>355</v>
       </c>
       <c r="H72" t="n">
-        <v>36</v>
+        <v>399</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -4078,49 +4066,49 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-94</v>
+        <v>35575</v>
       </c>
       <c r="D73" t="n">
-        <v>-1238</v>
+        <v>-1516</v>
       </c>
       <c r="E73" t="n">
-        <v>-1807</v>
+        <v>44084</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>-16433</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>-49391</v>
       </c>
       <c r="H73" t="n">
-        <v>2</v>
+        <v>-3006</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4129,49 +4117,49 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-887</v>
+        <v>-1962</v>
       </c>
       <c r="D74" t="n">
-        <v>-1247</v>
+        <v>-1680</v>
       </c>
       <c r="E74" t="n">
-        <v>-116</v>
+        <v>7232</v>
       </c>
       <c r="F74" t="n">
-        <v>-22</v>
+        <v>787</v>
       </c>
       <c r="G74" t="n">
-        <v>433</v>
+        <v>-310</v>
       </c>
       <c r="H74" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4180,49 +4168,49 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M74" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>57</v>
+        <v>-1184</v>
       </c>
       <c r="D75" t="n">
-        <v>-1345</v>
+        <v>-1745</v>
       </c>
       <c r="E75" t="n">
-        <v>575</v>
+        <v>-816</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>-23</v>
       </c>
       <c r="H75" t="n">
-        <v>-279</v>
+        <v>-7</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4235,88 +4223,100 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>勝一</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-608</v>
+        <v>-160</v>
       </c>
       <c r="D76" t="n">
-        <v>-1380</v>
+        <v>-1848</v>
       </c>
       <c r="E76" t="n">
-        <v>1318</v>
+        <v>-3641</v>
       </c>
       <c r="F76" t="n">
-        <v>-242</v>
+        <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>1939</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>7</v>
+        <v>-20</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>71</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>📉 減速</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>-3</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-993</v>
+        <v>-712</v>
       </c>
       <c r="D77" t="n">
-        <v>-1507</v>
+        <v>-2159</v>
       </c>
       <c r="E77" t="n">
-        <v>-624</v>
+        <v>-2671</v>
       </c>
       <c r="F77" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G77" t="n">
-        <v>-15</v>
+        <v>1530</v>
       </c>
       <c r="H77" t="n">
-        <v>-7</v>
+        <v>44</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>🟡 中性</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -4325,58 +4325,58 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M77" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>597</v>
+        <v>-530</v>
       </c>
       <c r="D78" t="n">
-        <v>-1527</v>
+        <v>-2171</v>
       </c>
       <c r="E78" t="n">
-        <v>-1556</v>
+        <v>-2374</v>
       </c>
       <c r="F78" t="n">
-        <v>1119</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>3707</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-155</v>
+        <v>68</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>🟡 中性</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4384,143 +4384,131 @@
         </is>
       </c>
       <c r="M78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>113</v>
+        <v>257</v>
       </c>
       <c r="D79" t="n">
-        <v>-1640</v>
+        <v>-2216</v>
       </c>
       <c r="E79" t="n">
-        <v>-3415</v>
+        <v>-4916</v>
       </c>
       <c r="F79" t="n">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>-149</v>
       </c>
       <c r="H79" t="n">
-        <v>-25</v>
+        <v>78</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K79" t="n">
-        <v>71</v>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M79" t="n">
-        <v>-3</v>
-      </c>
+          <t>🟠 減碼</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-2298</v>
+        <v>617</v>
       </c>
       <c r="D80" t="n">
-        <v>-1749</v>
+        <v>-2345</v>
       </c>
       <c r="E80" t="n">
-        <v>-3182</v>
+        <v>-2965</v>
       </c>
       <c r="F80" t="n">
-        <v>446</v>
+        <v>-9</v>
       </c>
       <c r="G80" t="n">
-        <v>8767</v>
+        <v>-217</v>
       </c>
       <c r="H80" t="n">
-        <v>259</v>
+        <v>2</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>🟡 中性</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K80" t="n">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M80" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-277</v>
+        <v>471</v>
       </c>
       <c r="D81" t="n">
-        <v>-1894</v>
+        <v>-2423</v>
       </c>
       <c r="E81" t="n">
-        <v>-2456</v>
+        <v>-1065</v>
       </c>
       <c r="F81" t="n">
-        <v>-183</v>
+        <v>406</v>
       </c>
       <c r="G81" t="n">
-        <v>1536</v>
+        <v>1137</v>
       </c>
       <c r="H81" t="n">
-        <v>26</v>
+        <v>-261</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>🟡 中性</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4533,45 +4521,45 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-903</v>
+        <v>-1309</v>
       </c>
       <c r="D82" t="n">
-        <v>-1898</v>
+        <v>-2428</v>
       </c>
       <c r="E82" t="n">
-        <v>-2422</v>
+        <v>-1610</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>433</v>
       </c>
       <c r="H82" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>🟡 中性</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -4580,15 +4568,15 @@
         </is>
       </c>
       <c r="K82" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M82" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="83">
@@ -4603,22 +4591,22 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-3034</v>
+        <v>-3603</v>
       </c>
       <c r="D83" t="n">
-        <v>-2136</v>
+        <v>-2599</v>
       </c>
       <c r="E83" t="n">
-        <v>-7889</v>
+        <v>-7939</v>
       </c>
       <c r="F83" t="n">
-        <v>1240</v>
+        <v>1401</v>
       </c>
       <c r="G83" t="n">
-        <v>2132</v>
+        <v>2175</v>
       </c>
       <c r="H83" t="n">
-        <v>-268</v>
+        <v>-256</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4645,31 +4633,31 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>459</v>
+        <v>-3707</v>
       </c>
       <c r="D84" t="n">
-        <v>-2375</v>
+        <v>-2757</v>
       </c>
       <c r="E84" t="n">
-        <v>-3613</v>
+        <v>-3735</v>
       </c>
       <c r="F84" t="n">
-        <v>-29</v>
+        <v>52</v>
       </c>
       <c r="G84" t="n">
-        <v>-217</v>
+        <v>8767</v>
       </c>
       <c r="H84" t="n">
-        <v>49</v>
+        <v>111</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -4678,88 +4666,100 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K84" t="n">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M84" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-350</v>
+        <v>-778</v>
       </c>
       <c r="D85" t="n">
-        <v>-2514</v>
+        <v>-2878</v>
       </c>
       <c r="E85" t="n">
-        <v>-5505</v>
+        <v>-76</v>
       </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>-222</v>
       </c>
       <c r="G85" t="n">
-        <v>-268</v>
+        <v>-949</v>
       </c>
       <c r="H85" t="n">
-        <v>-43</v>
+        <v>66</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
           <t>🟠 減碼</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>73</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M85" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-894</v>
+        <v>-1419</v>
       </c>
       <c r="D86" t="n">
-        <v>-2769</v>
+        <v>-3113</v>
       </c>
       <c r="E86" t="n">
-        <v>-792</v>
+        <v>-11</v>
       </c>
       <c r="F86" t="n">
-        <v>-330</v>
+        <v>-1</v>
       </c>
       <c r="G86" t="n">
-        <v>-946</v>
+        <v>-281</v>
       </c>
       <c r="H86" t="n">
-        <v>18</v>
+        <v>-161</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         </is>
       </c>
       <c r="K86" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4780,37 +4780,37 @@
         </is>
       </c>
       <c r="M86" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>670</v>
+        <v>449</v>
       </c>
       <c r="D87" t="n">
-        <v>-3166</v>
+        <v>-3240</v>
       </c>
       <c r="E87" t="n">
-        <v>-17543</v>
+        <v>-111260</v>
       </c>
       <c r="F87" t="n">
-        <v>-538</v>
+        <v>914</v>
       </c>
       <c r="G87" t="n">
-        <v>-1613</v>
+        <v>-3130</v>
       </c>
       <c r="H87" t="n">
-        <v>-383</v>
+        <v>4830</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4831,37 +4831,37 @@
         </is>
       </c>
       <c r="M87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-4887</v>
+        <v>-602</v>
       </c>
       <c r="D88" t="n">
-        <v>-3179</v>
+        <v>-3260</v>
       </c>
       <c r="E88" t="n">
-        <v>-1282</v>
+        <v>-17077</v>
       </c>
       <c r="F88" t="n">
-        <v>2812</v>
+        <v>-526</v>
       </c>
       <c r="G88" t="n">
-        <v>324</v>
+        <v>-1626</v>
       </c>
       <c r="H88" t="n">
-        <v>186</v>
+        <v>-520</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4870,15 +4870,15 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K88" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M88" t="n">
@@ -4888,31 +4888,31 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>長榮航太</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-1500</v>
+        <v>311</v>
       </c>
       <c r="D89" t="n">
-        <v>-4221</v>
+        <v>-4518</v>
       </c>
       <c r="E89" t="n">
-        <v>-304</v>
+        <v>-15129</v>
       </c>
       <c r="F89" t="n">
-        <v>-1</v>
+        <v>-356</v>
       </c>
       <c r="G89" t="n">
-        <v>-281</v>
+        <v>-230</v>
       </c>
       <c r="H89" t="n">
-        <v>-259</v>
+        <v>450</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4925,45 +4925,45 @@
         </is>
       </c>
       <c r="K89" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>264</v>
+        <v>754</v>
       </c>
       <c r="D90" t="n">
-        <v>-4569</v>
+        <v>-4742</v>
       </c>
       <c r="E90" t="n">
-        <v>-13568</v>
+        <v>-31853</v>
       </c>
       <c r="F90" t="n">
-        <v>-395</v>
+        <v>-51</v>
       </c>
       <c r="G90" t="n">
-        <v>-231</v>
+        <v>364</v>
       </c>
       <c r="H90" t="n">
-        <v>415</v>
+        <v>74</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4980,41 +4980,41 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>792</v>
+        <v>743</v>
       </c>
       <c r="D91" t="n">
-        <v>-4711</v>
+        <v>-6223</v>
       </c>
       <c r="E91" t="n">
-        <v>-35464</v>
+        <v>-16237</v>
       </c>
       <c r="F91" t="n">
-        <v>-20</v>
+        <v>446</v>
       </c>
       <c r="G91" t="n">
-        <v>364</v>
+        <v>664</v>
       </c>
       <c r="H91" t="n">
-        <v>212</v>
+        <v>348</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -5023,49 +5023,49 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K91" t="n">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M91" t="n">
-        <v>-4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1117</v>
+        <v>12482</v>
       </c>
       <c r="D92" t="n">
-        <v>-7090</v>
+        <v>-6466</v>
       </c>
       <c r="E92" t="n">
-        <v>-16093</v>
+        <v>51692</v>
       </c>
       <c r="F92" t="n">
-        <v>-50</v>
+        <v>5213</v>
       </c>
       <c r="G92" t="n">
-        <v>731</v>
+        <v>-4426</v>
       </c>
       <c r="H92" t="n">
-        <v>319</v>
+        <v>-3995</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -5074,49 +5074,49 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K92" t="n">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-991</v>
+        <v>-6264</v>
       </c>
       <c r="D93" t="n">
-        <v>-7644</v>
+        <v>-6807</v>
       </c>
       <c r="E93" t="n">
-        <v>-17056</v>
+        <v>-3282</v>
       </c>
       <c r="F93" t="n">
-        <v>-1</v>
+        <v>2749</v>
       </c>
       <c r="G93" t="n">
-        <v>-1</v>
+        <v>2674</v>
       </c>
       <c r="H93" t="n">
-        <v>-51</v>
+        <v>201</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -5125,49 +5125,49 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K93" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M93" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>5444</v>
+        <v>-998</v>
       </c>
       <c r="D94" t="n">
-        <v>-9313</v>
+        <v>-7384</v>
       </c>
       <c r="E94" t="n">
-        <v>-42046</v>
+        <v>-17350</v>
       </c>
       <c r="F94" t="n">
-        <v>3213</v>
+        <v>-1</v>
       </c>
       <c r="G94" t="n">
-        <v>-3987</v>
+        <v>-1</v>
       </c>
       <c r="H94" t="n">
-        <v>1732</v>
+        <v>-51</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -5176,49 +5176,49 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K94" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M94" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-698</v>
+        <v>2274</v>
       </c>
       <c r="D95" t="n">
-        <v>-9495</v>
+        <v>-8761</v>
       </c>
       <c r="E95" t="n">
-        <v>-23997</v>
+        <v>-42554</v>
       </c>
       <c r="F95" t="n">
-        <v>-100</v>
+        <v>5820</v>
       </c>
       <c r="G95" t="n">
-        <v>-100</v>
+        <v>-2248</v>
       </c>
       <c r="H95" t="n">
-        <v>-44</v>
+        <v>1377</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5227,11 +5227,11 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K95" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -5239,80 +5239,92 @@
         </is>
       </c>
       <c r="M95" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-5887</v>
+        <v>-221</v>
       </c>
       <c r="D96" t="n">
-        <v>-11573</v>
+        <v>-8827</v>
       </c>
       <c r="E96" t="n">
-        <v>-12864</v>
+        <v>-23091</v>
       </c>
       <c r="F96" t="n">
-        <v>189</v>
+        <v>-100</v>
       </c>
       <c r="G96" t="n">
-        <v>2470</v>
+        <v>-100</v>
       </c>
       <c r="H96" t="n">
-        <v>849</v>
+        <v>-43</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>🔴 大賣</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
+          <t>🟠 減碼</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>60</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>🛬 穩定</t>
+        </is>
+      </c>
+      <c r="M96" t="n">
+        <v>-4</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>23696</v>
+        <v>3000</v>
       </c>
       <c r="D97" t="n">
-        <v>-11647</v>
+        <v>-8901</v>
       </c>
       <c r="E97" t="n">
-        <v>29501</v>
+        <v>-79090</v>
       </c>
       <c r="F97" t="n">
-        <v>-6412</v>
+        <v>2344</v>
       </c>
       <c r="G97" t="n">
-        <v>-33974</v>
+        <v>-16872</v>
       </c>
       <c r="H97" t="n">
-        <v>-2854</v>
+        <v>4035</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>🔴 大賣</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -5321,7 +5333,7 @@
         </is>
       </c>
       <c r="K97" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -5344,22 +5356,22 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-3602</v>
+        <v>-1883</v>
       </c>
       <c r="D98" t="n">
-        <v>-12758</v>
+        <v>-11838</v>
       </c>
       <c r="E98" t="n">
-        <v>-13444</v>
+        <v>-12070</v>
       </c>
       <c r="F98" t="n">
-        <v>-1768</v>
+        <v>-3005</v>
       </c>
       <c r="G98" t="n">
-        <v>-4145</v>
+        <v>-5395</v>
       </c>
       <c r="H98" t="n">
-        <v>-1026</v>
+        <v>-1025</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5395,22 +5407,22 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-10339</v>
+        <v>-10704</v>
       </c>
       <c r="D99" t="n">
-        <v>-13012</v>
+        <v>-12891</v>
       </c>
       <c r="E99" t="n">
-        <v>-15454</v>
+        <v>-14369</v>
       </c>
       <c r="F99" t="n">
-        <v>8472</v>
+        <v>8425</v>
       </c>
       <c r="G99" t="n">
-        <v>7739</v>
+        <v>7659</v>
       </c>
       <c r="H99" t="n">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5437,53 +5449,41 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-4449</v>
+        <v>-7744</v>
       </c>
       <c r="D100" t="n">
-        <v>-13619</v>
+        <v>-13698</v>
       </c>
       <c r="E100" t="n">
-        <v>-68913</v>
+        <v>-16999</v>
       </c>
       <c r="F100" t="n">
-        <v>2139</v>
+        <v>683</v>
       </c>
       <c r="G100" t="n">
-        <v>875</v>
+        <v>2690</v>
       </c>
       <c r="H100" t="n">
-        <v>-282</v>
+        <v>671</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
           <t>🔴 大賣</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K100" t="n">
-        <v>92</v>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>🛬 穩定</t>
-        </is>
-      </c>
-      <c r="M100" t="n">
-        <v>-3</v>
-      </c>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5497,22 +5497,22 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-5120</v>
+        <v>-5161</v>
       </c>
       <c r="D101" t="n">
-        <v>-14286</v>
+        <v>-14163</v>
       </c>
       <c r="E101" t="n">
-        <v>91210</v>
+        <v>85883</v>
       </c>
       <c r="F101" t="n">
-        <v>-1758</v>
+        <v>-818</v>
       </c>
       <c r="G101" t="n">
-        <v>1223</v>
+        <v>1271</v>
       </c>
       <c r="H101" t="n">
-        <v>-321</v>
+        <v>-238</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5539,31 +5539,31 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>寶雅*</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-5558</v>
+        <v>-6844</v>
       </c>
       <c r="D102" t="n">
-        <v>-15320</v>
+        <v>-14378</v>
       </c>
       <c r="E102" t="n">
-        <v>-91452</v>
+        <v>-70170</v>
       </c>
       <c r="F102" t="n">
-        <v>2355</v>
+        <v>2295</v>
       </c>
       <c r="G102" t="n">
-        <v>-19400</v>
+        <v>1446</v>
       </c>
       <c r="H102" t="n">
-        <v>2761</v>
+        <v>-248</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -5572,19 +5572,19 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K102" t="n">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M102" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="103">
@@ -5599,22 +5599,22 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-1797</v>
+        <v>-705</v>
       </c>
       <c r="D103" t="n">
-        <v>-20656</v>
+        <v>-14883</v>
       </c>
       <c r="E103" t="n">
-        <v>10028</v>
+        <v>9058</v>
       </c>
       <c r="F103" t="n">
-        <v>356</v>
+        <v>304</v>
       </c>
       <c r="G103" t="n">
-        <v>1498</v>
+        <v>976</v>
       </c>
       <c r="H103" t="n">
-        <v>808</v>
+        <v>214</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5650,22 +5650,22 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-5941</v>
+        <v>-2520</v>
       </c>
       <c r="D104" t="n">
-        <v>-25930</v>
+        <v>-25053</v>
       </c>
       <c r="E104" t="n">
-        <v>48099</v>
+        <v>49119</v>
       </c>
       <c r="F104" t="n">
-        <v>-77</v>
+        <v>-244</v>
       </c>
       <c r="G104" t="n">
-        <v>7303</v>
+        <v>4641</v>
       </c>
       <c r="H104" t="n">
-        <v>-1703</v>
+        <v>-2181</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5701,22 +5701,22 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-3956</v>
+        <v>-32812</v>
       </c>
       <c r="D105" t="n">
-        <v>-88485</v>
+        <v>-109449</v>
       </c>
       <c r="E105" t="n">
-        <v>171599</v>
+        <v>146463</v>
       </c>
       <c r="F105" t="n">
-        <v>4039</v>
+        <v>-2370</v>
       </c>
       <c r="G105" t="n">
-        <v>35220</v>
+        <v>29629</v>
       </c>
       <c r="H105" t="n">
-        <v>1282</v>
+        <v>1161</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -5794,29 +5794,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -8 千股)</t>
+          <t>📈 20d 巨變(加碼 313 千股)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18185</v>
+        <v>1359948</v>
       </c>
       <c r="D2" t="n">
-        <v>614051</v>
+        <v>897264</v>
       </c>
       <c r="E2" t="n">
-        <v>-36729</v>
+        <v>851763</v>
       </c>
       <c r="F2" t="n">
-        <v>621923</v>
+        <v>584712</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>台光電</t>
         </is>
       </c>
     </row>
@@ -5828,20 +5828,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -531 千股)</t>
+          <t>📉 20d 巨變(減碼 -419 千股)</t>
         </is>
       </c>
       <c r="C3" t="n">
+        <v>58583</v>
+      </c>
+      <c r="D3" t="n">
+        <v>443937</v>
+      </c>
+      <c r="E3" t="n">
         <v>209557</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>863187</v>
-      </c>
-      <c r="E3" t="n">
-        <v>137541</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1394295</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -5852,116 +5852,116 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -561 千股)</t>
+          <t>📈 20d 巨變(加碼 81 千股)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-32233</v>
+        <v>318688</v>
       </c>
       <c r="D4" t="n">
-        <v>390623</v>
+        <v>694714</v>
       </c>
       <c r="E4" t="n">
-        <v>213102</v>
+        <v>18185</v>
       </c>
       <c r="F4" t="n">
-        <v>951978</v>
+        <v>614051</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>勤誠</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 222 千股)</t>
+          <t>📈 20d 巨變(加碼 867 千股)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>851763</v>
+        <v>743155</v>
       </c>
       <c r="D5" t="n">
-        <v>584712</v>
+        <v>-6222989</v>
       </c>
       <c r="E5" t="n">
-        <v>681611</v>
+        <v>1116580</v>
       </c>
       <c r="F5" t="n">
-        <v>362420</v>
+        <v>-7090103</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -560 千股)</t>
+          <t>📉 20d 巨變(減碼 -306 千股)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>669536</v>
+        <v>-750072</v>
       </c>
       <c r="D6" t="n">
-        <v>-3165856</v>
+        <v>84978</v>
       </c>
       <c r="E6" t="n">
-        <v>1260134</v>
+        <v>-32233</v>
       </c>
       <c r="F6" t="n">
-        <v>-2605451</v>
+        <v>390623</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>奇鋐</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 1,140 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -94 千股)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1116580</v>
+        <v>-601814</v>
       </c>
       <c r="D7" t="n">
-        <v>-7090103</v>
+        <v>-3259604</v>
       </c>
       <c r="E7" t="n">
-        <v>-639289</v>
+        <v>669536</v>
       </c>
       <c r="F7" t="n">
-        <v>-8229822</v>
+        <v>-3165856</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>亞翔</t>
         </is>
       </c>
     </row>
@@ -5973,20 +5973,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 524 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,003 千股)</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>382368</v>
+      </c>
+      <c r="D8" t="n">
+        <v>846530</v>
+      </c>
+      <c r="E8" t="n">
         <v>322273</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>1849367</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-319084</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1325292</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -6002,20 +6002,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -390 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -163 千股)</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>-247304</v>
+      </c>
+      <c r="D9" t="n">
+        <v>152737</v>
+      </c>
+      <c r="E9" t="n">
         <v>305231</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>315853</v>
-      </c>
-      <c r="E9" t="n">
-        <v>478481</v>
-      </c>
-      <c r="F9" t="n">
-        <v>705677</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -6026,116 +6026,116 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -217 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 632 千股)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-387547</v>
+        <v>529626</v>
       </c>
       <c r="D10" t="n">
-        <v>-1084320</v>
+        <v>589461</v>
       </c>
       <c r="E10" t="n">
-        <v>-245209</v>
+        <v>-166265</v>
       </c>
       <c r="F10" t="n">
-        <v>-867374</v>
+        <v>-42251</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>旺矽</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 4,310 千股)</t>
+          <t>📉 20d 巨變(減碼 -833 千股)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>551906</v>
+        <v>-1304926</v>
       </c>
       <c r="D11" t="n">
-        <v>-61917</v>
+        <v>6896264</v>
       </c>
       <c r="E11" t="n">
-        <v>-13328620</v>
+        <v>-1083126</v>
       </c>
       <c r="F11" t="n">
-        <v>-4372146</v>
+        <v>7729620</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>雙鴻</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -123 千股)</t>
+          <t>📉 20d 巨變(減碼 -16 千股)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-166265</v>
+        <v>-608</v>
       </c>
       <c r="D12" t="n">
-        <v>-42251</v>
+        <v>-1100592</v>
       </c>
       <c r="E12" t="n">
-        <v>2002</v>
+        <v>-387547</v>
       </c>
       <c r="F12" t="n">
-        <v>80956</v>
+        <v>-1084320</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>智邦</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -892 千股)</t>
+          <t>📉 20d 巨變(減碼 -3,178 千股)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-1083126</v>
+        <v>449162</v>
       </c>
       <c r="D13" t="n">
-        <v>7729620</v>
+        <v>-3240294</v>
       </c>
       <c r="E13" t="n">
-        <v>-1164487</v>
+        <v>551906</v>
       </c>
       <c r="F13" t="n">
-        <v>8621562</v>
+        <v>-61917</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
@@ -6147,20 +6147,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,634 千股)</t>
+          <t>📈 20d 巨變(加碼 552 千股)</t>
         </is>
       </c>
       <c r="C14" t="n">
+        <v>2273935</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-8761282</v>
+      </c>
+      <c r="E14" t="n">
         <v>5444224</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>-9313210</v>
-      </c>
-      <c r="E14" t="n">
-        <v>3478025</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-11946950</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -6176,20 +6176,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -269 千股)</t>
+          <t>📈 20d 巨變(加碼 538 千股)</t>
         </is>
       </c>
       <c r="C15" t="n">
+        <v>193017</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3175916</v>
+      </c>
+      <c r="E15" t="n">
         <v>114814</v>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>2637718</v>
-      </c>
-      <c r="E15" t="n">
-        <v>942737</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2907039</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -6200,29 +6200,29 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,106 千股)</t>
+          <t>📈 20d 巨變(加碼 27 千股)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-1210981</v>
+        <v>151076</v>
       </c>
       <c r="D16" t="n">
-        <v>19886</v>
+        <v>-957026</v>
       </c>
       <c r="E16" t="n">
-        <v>-1284004</v>
+        <v>52840</v>
       </c>
       <c r="F16" t="n">
-        <v>-1086135</v>
+        <v>-983777</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>辛耘</t>
         </is>
       </c>
     </row>
@@ -6234,20 +6234,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -73 千股)</t>
+          <t>📈 20d 巨變(加碼 30 千股)</t>
         </is>
       </c>
       <c r="C17" t="n">
+        <v>616713</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-2344651</v>
+      </c>
+      <c r="E17" t="n">
         <v>459195</v>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
         <v>-2374565</v>
-      </c>
-      <c r="E17" t="n">
-        <v>560769</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-2301540</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -6258,203 +6258,203 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 43 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 1,304 千股)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>52840</v>
+        <v>916087</v>
       </c>
       <c r="D18" t="n">
-        <v>-983777</v>
+        <v>1323860</v>
       </c>
       <c r="E18" t="n">
-        <v>22320</v>
+        <v>-1210981</v>
       </c>
       <c r="F18" t="n">
-        <v>-1026614</v>
+        <v>19886</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>健鼎</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -226 千股)</t>
+          <t>📈 20d 巨變(加碼 14 千股)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-52014</v>
+        <v>-500044</v>
       </c>
       <c r="D19" t="n">
-        <v>-1102295</v>
+        <v>-98766</v>
       </c>
       <c r="E19" t="n">
-        <v>35264</v>
+        <v>-472862</v>
       </c>
       <c r="F19" t="n">
-        <v>-876521</v>
+        <v>-112765</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>川湖</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 403 千股)</t>
+          <t>📈 20d 巨變(加碼 37 千股)</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>559356</v>
+        <v>-26981</v>
       </c>
       <c r="D20" t="n">
-        <v>5650898</v>
+        <v>-1065455</v>
       </c>
       <c r="E20" t="n">
-        <v>328807</v>
+        <v>-52014</v>
       </c>
       <c r="F20" t="n">
-        <v>5247575</v>
+        <v>-1102295</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>崇越</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -151 千股)</t>
+          <t>📈 20d 巨變(加碼 126 千股)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-472862</v>
+        <v>1276930</v>
       </c>
       <c r="D21" t="n">
-        <v>-112765</v>
+        <v>5776498</v>
       </c>
       <c r="E21" t="n">
-        <v>-348631</v>
+        <v>559356</v>
       </c>
       <c r="F21" t="n">
-        <v>38218</v>
+        <v>5650898</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 514 千股)</t>
+          <t>📉 20d 巨變(減碼 -273 千股)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>465979</v>
+        <v>-530029</v>
       </c>
       <c r="D22" t="n">
-        <v>2598485</v>
+        <v>-2170846</v>
       </c>
       <c r="E22" t="n">
-        <v>-720715</v>
+        <v>-903409</v>
       </c>
       <c r="F22" t="n">
-        <v>2084402</v>
+        <v>-1898176</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>建榮</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 472 千股)</t>
+          <t>📈 20d 巨變(加碼 247 千股)</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>196607</v>
+        <v>765131</v>
       </c>
       <c r="D23" t="n">
-        <v>286045</v>
+        <v>2845163</v>
       </c>
       <c r="E23" t="n">
-        <v>335727</v>
+        <v>465979</v>
       </c>
       <c r="F23" t="n">
-        <v>-186408</v>
+        <v>2598485</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>中砂</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 12 千股)</t>
+          <t>📈 20d 巨變(加碼 147 千股)</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-903409</v>
+        <v>216131</v>
       </c>
       <c r="D24" t="n">
-        <v>-1898176</v>
+        <v>433380</v>
       </c>
       <c r="E24" t="n">
-        <v>-2132958</v>
+        <v>196607</v>
       </c>
       <c r="F24" t="n">
-        <v>-1910322</v>
+        <v>286045</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>華城</t>
         </is>
       </c>
     </row>
@@ -6466,20 +6466,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -363 千股)</t>
+          <t>📉 20d 巨變(減碼 -529 千股)</t>
         </is>
       </c>
       <c r="C25" t="n">
+        <v>-1551893</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-1416938</v>
+      </c>
+      <c r="E25" t="n">
         <v>-670278</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
         <v>-887750</v>
-      </c>
-      <c r="E25" t="n">
-        <v>135383</v>
-      </c>
-      <c r="F25" t="n">
-        <v>-524318</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -6490,203 +6490,203 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 115 千股)</t>
+          <t>📉 20d 巨變(減碼 -9 千股)</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-55849</v>
+        <v>-36006</v>
       </c>
       <c r="D26" t="n">
-        <v>-518241</v>
+        <v>-15286</v>
       </c>
       <c r="E26" t="n">
-        <v>-159008</v>
+        <v>-14006</v>
       </c>
       <c r="F26" t="n">
-        <v>-633400</v>
+        <v>-6286</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>大車隊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -28 千股)</t>
+          <t>📈 20d 巨變(加碼 980 千股)</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-19770</v>
+        <v>1485770</v>
       </c>
       <c r="D27" t="n">
-        <v>-40732</v>
+        <v>310438</v>
       </c>
       <c r="E27" t="n">
-        <v>-41770</v>
+        <v>1274857</v>
       </c>
       <c r="F27" t="n">
-        <v>-12682</v>
+        <v>-669262</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>零壹</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -14 千股)</t>
+          <t>📈 20d 巨變(加碼 51 千股)</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-14006</v>
+        <v>-55036</v>
       </c>
       <c r="D28" t="n">
-        <v>-6286</v>
+        <v>-467428</v>
       </c>
       <c r="E28" t="n">
-        <v>-7006</v>
+        <v>-55849</v>
       </c>
       <c r="F28" t="n">
-        <v>7714</v>
+        <v>-518241</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>湧德</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -12 千股)</t>
+          <t>📉 20d 巨變(減碼 -26 千股)</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>106037</v>
+        <v>-17083</v>
       </c>
       <c r="D29" t="n">
-        <v>-476862</v>
+        <v>-66885</v>
       </c>
       <c r="E29" t="n">
-        <v>156037</v>
+        <v>-19770</v>
       </c>
       <c r="F29" t="n">
-        <v>-464862</v>
+        <v>-40732</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>崇友</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -195 千股)</t>
+          <t>📈 20d 巨變(加碼 160 千股)</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>332146</v>
+        <v>386138</v>
       </c>
       <c r="D30" t="n">
-        <v>15634923</v>
+        <v>1248444</v>
       </c>
       <c r="E30" t="n">
-        <v>572620</v>
+        <v>192836</v>
       </c>
       <c r="F30" t="n">
-        <v>15829618</v>
+        <v>1088492</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>合機</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -1,753 千股)</t>
+          <t>📉 20d 巨變(減碼 -13 千股)</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1274857</v>
+        <v>53687</v>
       </c>
       <c r="D31" t="n">
-        <v>-669262</v>
+        <v>-489862</v>
       </c>
       <c r="E31" t="n">
-        <v>-48147</v>
+        <v>106037</v>
       </c>
       <c r="F31" t="n">
-        <v>1083721</v>
+        <v>-476862</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>隆大</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -62 千股)</t>
+          <t>📈 20d 巨變(加碼 829 千股)</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>192836</v>
+        <v>906409</v>
       </c>
       <c r="D32" t="n">
-        <v>1088492</v>
+        <v>16463522</v>
       </c>
       <c r="E32" t="n">
-        <v>288054</v>
+        <v>332146</v>
       </c>
       <c r="F32" t="n">
-        <v>1150231</v>
+        <v>15634923</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
@@ -6698,20 +6698,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -4,735 千股)</t>
+          <t>📈 20d 巨變(加碼 7,260 千股)</t>
         </is>
       </c>
       <c r="C33" t="n">
+        <v>-1955200</v>
+      </c>
+      <c r="D33" t="n">
+        <v>8465438</v>
+      </c>
+      <c r="E33" t="n">
         <v>-14546783</v>
       </c>
-      <c r="D33" t="n">
+      <c r="F33" t="n">
         <v>1205063</v>
-      </c>
-      <c r="E33" t="n">
-        <v>-15044921</v>
-      </c>
-      <c r="F33" t="n">
-        <v>5940109</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -6722,87 +6722,87 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -771 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,181 千股)</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-4449229</v>
+        <v>-1309233</v>
       </c>
       <c r="D34" t="n">
-        <v>-13619466</v>
+        <v>-2427788</v>
       </c>
       <c r="E34" t="n">
-        <v>-3500209</v>
+        <v>-887205</v>
       </c>
       <c r="F34" t="n">
-        <v>-12848208</v>
+        <v>-1246989</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>卜蜂</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠</t>
+          <t>📉 20d 巨變(減碼 -758 千股)</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>33175</v>
+        <v>-6843521</v>
       </c>
       <c r="D35" t="n">
-        <v>83522</v>
+        <v>-14377743</v>
       </c>
       <c r="E35" t="n">
-        <v>-34694</v>
+        <v>-4449229</v>
       </c>
       <c r="F35" t="n">
-        <v>80774</v>
+        <v>-13619466</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>寶雅*</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 137 千股)</t>
+          <t>📈 20d 巨變(加碼 46 千股)</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-887205</v>
+        <v>66854</v>
       </c>
       <c r="D36" t="n">
-        <v>-1246989</v>
+        <v>129186</v>
       </c>
       <c r="E36" t="n">
-        <v>-1112669</v>
+        <v>33175</v>
       </c>
       <c r="F36" t="n">
-        <v>-1384298</v>
+        <v>83522</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>大統益</t>
         </is>
       </c>
     </row>
@@ -6814,20 +6814,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -256 千股)</t>
+          <t>📈 20d 巨變(加碼 90 千股)</t>
         </is>
       </c>
       <c r="C37" t="n">
+        <v>656629</v>
+      </c>
+      <c r="D37" t="n">
+        <v>585719</v>
+      </c>
+      <c r="E37" t="n">
         <v>582134</v>
       </c>
-      <c r="D37" t="n">
+      <c r="F37" t="n">
         <v>495692</v>
-      </c>
-      <c r="E37" t="n">
-        <v>585111</v>
-      </c>
-      <c r="F37" t="n">
-        <v>751669</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -6838,464 +6838,464 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -5 千股)</t>
+          <t>📈 20d 巨變(加碼 10 千股)</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1000</v>
+        <v>-33026</v>
       </c>
       <c r="D38" t="n">
-        <v>54000</v>
+        <v>-422120</v>
       </c>
       <c r="E38" t="n">
-        <v>6000</v>
+        <v>-19323</v>
       </c>
       <c r="F38" t="n">
-        <v>59000</v>
+        <v>-432030</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>方土霖</t>
+          <t>智冠</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 9 千股)</t>
+          <t>📈 20d 巨變(加碼 17 千股)</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-19323</v>
+        <v>71447</v>
       </c>
       <c r="D39" t="n">
-        <v>-432030</v>
+        <v>-161161</v>
       </c>
       <c r="E39" t="n">
-        <v>-25335</v>
+        <v>49447</v>
       </c>
       <c r="F39" t="n">
-        <v>-441138</v>
+        <v>-178155</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>華景電</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -342 千股)</t>
+          <t>📈 20d 巨變(加碼 20 千股)</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-465482</v>
+        <v>-10980</v>
       </c>
       <c r="D40" t="n">
-        <v>-1209574</v>
+        <v>-329240</v>
       </c>
       <c r="E40" t="n">
-        <v>-43923</v>
+        <v>-79980</v>
       </c>
       <c r="F40" t="n">
-        <v>-867204</v>
+        <v>-349090</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>八方雲集</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -107 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,581 千股)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-79980</v>
+        <v>8907643</v>
       </c>
       <c r="D41" t="n">
-        <v>-349090</v>
+        <v>50779443</v>
       </c>
       <c r="E41" t="n">
-        <v>-114980</v>
+        <v>7464533</v>
       </c>
       <c r="F41" t="n">
-        <v>-242279</v>
+        <v>52360867</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -3,344 千股)</t>
+          <t>📈 20d 巨變(加碼 26 千股)</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7464533</v>
+        <v>-376558</v>
       </c>
       <c r="D42" t="n">
-        <v>52360867</v>
+        <v>-1183475</v>
       </c>
       <c r="E42" t="n">
-        <v>7029659</v>
+        <v>-465482</v>
       </c>
       <c r="F42" t="n">
-        <v>55704981</v>
+        <v>-1209574</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>穎崴</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -15 千股)</t>
+          <t>📈 20d 巨變(加碼 199 千股)</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>49447</v>
+        <v>960416</v>
       </c>
       <c r="D43" t="n">
-        <v>-178155</v>
+        <v>55313</v>
       </c>
       <c r="E43" t="n">
-        <v>26487</v>
+        <v>773859</v>
       </c>
       <c r="F43" t="n">
-        <v>-163055</v>
+        <v>-144157</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>亞力</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 633 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,247 千股)</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>773859</v>
+        <v>-1962156</v>
       </c>
       <c r="D44" t="n">
-        <v>-144157</v>
+        <v>-1679889</v>
       </c>
       <c r="E44" t="n">
-        <v>245835</v>
+        <v>-1457167</v>
       </c>
       <c r="F44" t="n">
-        <v>-777337</v>
+        <v>-432496</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -168 千股)</t>
+          <t>📉 20d 巨變(減碼 -79 千股)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-119554</v>
+        <v>-190072</v>
       </c>
       <c r="D45" t="n">
-        <v>160312</v>
+        <v>-1317405</v>
       </c>
       <c r="E45" t="n">
-        <v>-56293</v>
+        <v>-94072</v>
       </c>
       <c r="F45" t="n">
-        <v>328665</v>
+        <v>-1238405</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>聯合</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 15 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 81 千股)</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-94072</v>
+        <v>142188</v>
       </c>
       <c r="D46" t="n">
-        <v>-1238405</v>
+        <v>241627</v>
       </c>
       <c r="E46" t="n">
-        <v>-115072</v>
+        <v>-119554</v>
       </c>
       <c r="F46" t="n">
-        <v>-1253405</v>
+        <v>160312</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>大綜</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -783 千股)</t>
+          <t>📈 20d 巨變(加碼 51 千股)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-1457167</v>
+        <v>284986</v>
       </c>
       <c r="D47" t="n">
-        <v>-432496</v>
+        <v>276413</v>
       </c>
       <c r="E47" t="n">
-        <v>-487181</v>
+        <v>277645</v>
       </c>
       <c r="F47" t="n">
-        <v>350466</v>
+        <v>224995</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>漢科</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 62 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,356 千股)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>277645</v>
+        <v>4127406</v>
       </c>
       <c r="D48" t="n">
-        <v>224995</v>
+        <v>7444867</v>
       </c>
       <c r="E48" t="n">
-        <v>266252</v>
+        <v>4273427</v>
       </c>
       <c r="F48" t="n">
-        <v>163102</v>
+        <v>8800989</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>台燿</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 3,422 千股)</t>
+          <t>📈 20d 巨變(加碼 99 千股)</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4273427</v>
+        <v>1696536</v>
       </c>
       <c r="D49" t="n">
-        <v>8800989</v>
+        <v>-611597</v>
       </c>
       <c r="E49" t="n">
-        <v>1821272</v>
+        <v>1372583</v>
       </c>
       <c r="F49" t="n">
-        <v>5378978</v>
+        <v>-710958</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>世芯-KY</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -9,337 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 6,419 千股)</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-1797139</v>
+        <v>2999995</v>
       </c>
       <c r="D50" t="n">
-        <v>-20655865</v>
+        <v>-8900948</v>
       </c>
       <c r="E50" t="n">
-        <v>-4481844</v>
+        <v>-5557918</v>
       </c>
       <c r="F50" t="n">
-        <v>-11318698</v>
+        <v>-15320298</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -278 千股)</t>
+          <t>📈 20d 巨變(加碼 5,773 千股)</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-2298043</v>
+        <v>-705430</v>
       </c>
       <c r="D51" t="n">
-        <v>-1749169</v>
+        <v>-14883040</v>
       </c>
       <c r="E51" t="n">
-        <v>-1095412</v>
+        <v>-1797139</v>
       </c>
       <c r="F51" t="n">
-        <v>-1471024</v>
+        <v>-20655865</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -276 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,008 千股)</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1933113</v>
+        <v>-3706772</v>
       </c>
       <c r="D52" t="n">
-        <v>4726210</v>
+        <v>-2757067</v>
       </c>
       <c r="E52" t="n">
-        <v>2643273</v>
+        <v>-2298043</v>
       </c>
       <c r="F52" t="n">
-        <v>5002112</v>
+        <v>-1749169</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>玉晶光</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -158 千股)</t>
+          <t>📉 20d 巨變(減碼 -74 千股)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1372583</v>
+        <v>1320154</v>
       </c>
       <c r="D53" t="n">
-        <v>-710958</v>
+        <v>4651731</v>
       </c>
       <c r="E53" t="n">
-        <v>1889496</v>
+        <v>1933113</v>
       </c>
       <c r="F53" t="n">
-        <v>-553262</v>
+        <v>4726210</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>立隆電</t>
         </is>
       </c>
     </row>
@@ -7307,20 +7307,20 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 7,366 千股)</t>
+          <t>📉 20d 巨變(減碼 -22,012 千股)</t>
         </is>
       </c>
       <c r="C54" t="n">
+        <v>12482165</v>
+      </c>
+      <c r="D54" t="n">
+        <v>-6465908</v>
+      </c>
+      <c r="E54" t="n">
         <v>28358558</v>
       </c>
-      <c r="D54" t="n">
+      <c r="F54" t="n">
         <v>15545992</v>
-      </c>
-      <c r="E54" t="n">
-        <v>23857230</v>
-      </c>
-      <c r="F54" t="n">
-        <v>8179766</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -7331,116 +7331,116 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,533 千股)</t>
+          <t>📈 20d 巨變(加碼 8,137 千股)</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-5557918</v>
+        <v>25887340</v>
       </c>
       <c r="D55" t="n">
-        <v>-15320298</v>
+        <v>44905786</v>
       </c>
       <c r="E55" t="n">
-        <v>-3002894</v>
+        <v>12310583</v>
       </c>
       <c r="F55" t="n">
-        <v>-16853262</v>
+        <v>36768774</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 4,559 千股)</t>
+          <t>📈 20d 巨變(加碼 640 千股)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>12310583</v>
+        <v>1211758</v>
       </c>
       <c r="D56" t="n">
-        <v>36768774</v>
+        <v>2496827</v>
       </c>
       <c r="E56" t="n">
-        <v>7179234</v>
+        <v>699665</v>
       </c>
       <c r="F56" t="n">
-        <v>32209473</v>
+        <v>1856434</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>鈊象</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -291 千股)</t>
+          <t>📉 20d 巨變(減碼 -233 千股)</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>699665</v>
+        <v>-504736</v>
       </c>
       <c r="D57" t="n">
-        <v>1856434</v>
+        <v>109739</v>
       </c>
       <c r="E57" t="n">
-        <v>846571</v>
+        <v>-670277</v>
       </c>
       <c r="F57" t="n">
-        <v>2147303</v>
+        <v>342976</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>士電</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -42 千股)</t>
+          <t>📈 20d 巨變(加碼 27 千股)</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-670277</v>
+        <v>392762</v>
       </c>
       <c r="D58" t="n">
-        <v>342976</v>
+        <v>78817</v>
       </c>
       <c r="E58" t="n">
-        <v>-1278685</v>
+        <v>165210</v>
       </c>
       <c r="F58" t="n">
-        <v>385182</v>
+        <v>51628</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>鉅祥</t>
         </is>
       </c>
     </row>
@@ -7452,20 +7452,20 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 14 千股)</t>
+          <t>📉 20d 巨變(減碼 -20 千股)</t>
         </is>
       </c>
       <c r="C59" t="n">
+        <v>57390</v>
+      </c>
+      <c r="D59" t="n">
+        <v>333938</v>
+      </c>
+      <c r="E59" t="n">
         <v>60460</v>
       </c>
-      <c r="D59" t="n">
+      <c r="F59" t="n">
         <v>353842</v>
-      </c>
-      <c r="E59" t="n">
-        <v>44755</v>
-      </c>
-      <c r="F59" t="n">
-        <v>339880</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -7481,20 +7481,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 46 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 137 千股)</t>
         </is>
       </c>
       <c r="C60" t="n">
+        <v>81914</v>
+      </c>
+      <c r="D60" t="n">
+        <v>-18721</v>
+      </c>
+      <c r="E60" t="n">
         <v>-40007</v>
       </c>
-      <c r="D60" t="n">
+      <c r="F60" t="n">
         <v>-156117</v>
-      </c>
-      <c r="E60" t="n">
-        <v>-100410</v>
-      </c>
-      <c r="F60" t="n">
-        <v>-202299</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -7505,29 +7505,29 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 314 千股)</t>
+          <t>📉 20d 巨變(減碼 -5 千股)</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>165210</v>
+        <v>1154356</v>
       </c>
       <c r="D61" t="n">
-        <v>51628</v>
+        <v>1075182</v>
       </c>
       <c r="E61" t="n">
-        <v>71250</v>
+        <v>1133474</v>
       </c>
       <c r="F61" t="n">
-        <v>-262634</v>
+        <v>1080622</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>祥碩</t>
         </is>
       </c>
     </row>
@@ -7539,20 +7539,20 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -68 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -208 千股)</t>
         </is>
       </c>
       <c r="C62" t="n">
+        <v>-160490</v>
+      </c>
+      <c r="D62" t="n">
+        <v>-1847615</v>
+      </c>
+      <c r="E62" t="n">
         <v>112959</v>
       </c>
-      <c r="D62" t="n">
+      <c r="F62" t="n">
         <v>-1639888</v>
-      </c>
-      <c r="E62" t="n">
-        <v>-61789</v>
-      </c>
-      <c r="F62" t="n">
-        <v>-1571422</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -7568,20 +7568,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -395 千股)</t>
+          <t>📉 20d 巨變(減碼 -237 千股)</t>
         </is>
       </c>
       <c r="C63" t="n">
+        <v>-1183696</v>
+      </c>
+      <c r="D63" t="n">
+        <v>-1744641</v>
+      </c>
+      <c r="E63" t="n">
         <v>-992971</v>
       </c>
-      <c r="D63" t="n">
+      <c r="F63" t="n">
         <v>-1507498</v>
-      </c>
-      <c r="E63" t="n">
-        <v>-791032</v>
-      </c>
-      <c r="F63" t="n">
-        <v>-1112427</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -7592,203 +7592,203 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 424 千股)</t>
+          <t>📈 20d 巨變(加碼 361 千股)</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>597453</v>
+        <v>79765</v>
       </c>
       <c r="D64" t="n">
-        <v>-1526964</v>
+        <v>-983742</v>
       </c>
       <c r="E64" t="n">
-        <v>1449962</v>
+        <v>56765</v>
       </c>
       <c r="F64" t="n">
-        <v>-1950492</v>
+        <v>-1344742</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>信立</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 373 千股)</t>
+          <t>📈 20d 巨變(加碼 121 千股)</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>56765</v>
+        <v>-10704384</v>
       </c>
       <c r="D65" t="n">
-        <v>-1344742</v>
+        <v>-12891228</v>
       </c>
       <c r="E65" t="n">
-        <v>83818</v>
+        <v>-10338604</v>
       </c>
       <c r="F65" t="n">
-        <v>-1717742</v>
+        <v>-13012012</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 47 千股)</t>
+          <t>📉 20d 巨變(減碼 -897 千股)</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1133474</v>
+        <v>471380</v>
       </c>
       <c r="D66" t="n">
-        <v>1080622</v>
+        <v>-2423465</v>
       </c>
       <c r="E66" t="n">
-        <v>1199979</v>
+        <v>597453</v>
       </c>
       <c r="F66" t="n">
-        <v>1033520</v>
+        <v>-1526964</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>華星光</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -714 千股)</t>
+          <t>📉 20d 巨變(減碼 -3,434 千股)</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-10338604</v>
+        <v>-4793575</v>
       </c>
       <c r="D67" t="n">
-        <v>-13012012</v>
+        <v>20272878</v>
       </c>
       <c r="E67" t="n">
-        <v>-9193144</v>
+        <v>-2226357</v>
       </c>
       <c r="F67" t="n">
-        <v>-12297744</v>
+        <v>23706646</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,692 千股)</t>
+          <t>📉 20d 巨變(減碼 -3,628 千股)</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-1500440</v>
+        <v>-6264029</v>
       </c>
       <c r="D68" t="n">
-        <v>-4221219</v>
+        <v>-6806679</v>
       </c>
       <c r="E68" t="n">
-        <v>-1386123</v>
+        <v>-4887010</v>
       </c>
       <c r="F68" t="n">
-        <v>-1528898</v>
+        <v>-3178758</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>聯鈞</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,434 千股)</t>
+          <t>📈 20d 巨變(加碼 1,575 千股)</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-2226357</v>
+        <v>7073108</v>
       </c>
       <c r="D69" t="n">
-        <v>23706646</v>
+        <v>6494847</v>
       </c>
       <c r="E69" t="n">
-        <v>-670768</v>
+        <v>4990189</v>
       </c>
       <c r="F69" t="n">
-        <v>26140424</v>
+        <v>4919837</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -536 千股)</t>
+          <t>📉 20d 巨變(減碼 -20,964 千股)</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-4887010</v>
+        <v>-32812476</v>
       </c>
       <c r="D70" t="n">
-        <v>-3178758</v>
+        <v>-109448520</v>
       </c>
       <c r="E70" t="n">
-        <v>-4714730</v>
+        <v>-3955531</v>
       </c>
       <c r="F70" t="n">
-        <v>-2642776</v>
+        <v>-88484636</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
@@ -7800,20 +7800,20 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -528 千股)</t>
+          <t>📉 20d 巨變(減碼 -463 千股)</t>
         </is>
       </c>
       <c r="C71" t="n">
+        <v>-3602726</v>
+      </c>
+      <c r="D71" t="n">
+        <v>-2598987</v>
+      </c>
+      <c r="E71" t="n">
         <v>-3033517</v>
       </c>
-      <c r="D71" t="n">
+      <c r="F71" t="n">
         <v>-2135552</v>
-      </c>
-      <c r="E71" t="n">
-        <v>-2292711</v>
-      </c>
-      <c r="F71" t="n">
-        <v>-1607776</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -7824,87 +7824,87 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 6,207 千股)</t>
+          <t>📈 20d 巨變(加碼 1,109 千股)</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-3955531</v>
+        <v>-1419346</v>
       </c>
       <c r="D72" t="n">
-        <v>-88484636</v>
+        <v>-3112504</v>
       </c>
       <c r="E72" t="n">
-        <v>-19086172</v>
+        <v>-1500440</v>
       </c>
       <c r="F72" t="n">
-        <v>-94692066</v>
+        <v>-4221219</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>宇瞻</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,310 千股)</t>
+          <t>📈 20d 巨變(加碼 878 千股)</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>4990189</v>
+        <v>-2519724</v>
       </c>
       <c r="D73" t="n">
-        <v>4919837</v>
+        <v>-25052637</v>
       </c>
       <c r="E73" t="n">
-        <v>4440229</v>
+        <v>-5940683</v>
       </c>
       <c r="F73" t="n">
-        <v>3609811</v>
+        <v>-25930206</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -7,091 千股)</t>
+          <t>📈 20d 巨變(加碼 78 千股)</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-5940683</v>
+        <v>18912</v>
       </c>
       <c r="D74" t="n">
-        <v>-25930206</v>
+        <v>-404344</v>
       </c>
       <c r="E74" t="n">
-        <v>-6506870</v>
+        <v>3804</v>
       </c>
       <c r="F74" t="n">
-        <v>-18839137</v>
+        <v>-482157</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>德昌</t>
         </is>
       </c>
     </row>
@@ -7916,20 +7916,20 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -106 千股)</t>
+          <t>📉 20d 巨變(減碼 -31 千股)</t>
         </is>
       </c>
       <c r="C75" t="n">
+        <v>754419</v>
+      </c>
+      <c r="D75" t="n">
+        <v>-4742299</v>
+      </c>
+      <c r="E75" t="n">
         <v>791703</v>
       </c>
-      <c r="D75" t="n">
+      <c r="F75" t="n">
         <v>-4710884</v>
-      </c>
-      <c r="E75" t="n">
-        <v>796929</v>
-      </c>
-      <c r="F75" t="n">
-        <v>-4604889</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -7940,116 +7940,116 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 58 千股)</t>
+          <t>📈 20d 巨變(加碼 12 千股)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>76929</v>
+        <v>401310</v>
       </c>
       <c r="D76" t="n">
-        <v>-28071</v>
+        <v>877379</v>
       </c>
       <c r="E76" t="n">
-        <v>16929</v>
+        <v>364390</v>
       </c>
       <c r="F76" t="n">
-        <v>-86071</v>
+        <v>864924</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>億泰</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -26 千股)</t>
+          <t>📈 20d 巨變(加碼 46 千股)</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>3804</v>
+        <v>106929</v>
       </c>
       <c r="D77" t="n">
-        <v>-482157</v>
+        <v>17929</v>
       </c>
       <c r="E77" t="n">
-        <v>25354</v>
+        <v>76929</v>
       </c>
       <c r="F77" t="n">
-        <v>-456187</v>
+        <v>-28071</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>友輝</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -25 千股)</t>
+          <t>📈 20d 巨變(加碼 261 千股)</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>364390</v>
+        <v>-997915</v>
       </c>
       <c r="D78" t="n">
-        <v>864924</v>
+        <v>-7383519</v>
       </c>
       <c r="E78" t="n">
-        <v>155354</v>
+        <v>-990710</v>
       </c>
       <c r="F78" t="n">
-        <v>889910</v>
+        <v>-7644067</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>智易</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 150 千股)</t>
+          <t>📉 20d 巨變(減碼 -109 千股)</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-990710</v>
+        <v>-778206</v>
       </c>
       <c r="D79" t="n">
-        <v>-7644067</v>
+        <v>-2877543</v>
       </c>
       <c r="E79" t="n">
-        <v>-780000</v>
+        <v>-894468</v>
       </c>
       <c r="F79" t="n">
-        <v>-7794145</v>
+        <v>-2768746</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>原相</t>
         </is>
       </c>
     </row>
@@ -8061,20 +8061,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 821 千股)</t>
+          <t>📉 20d 巨變(減碼 -667 千股)</t>
         </is>
       </c>
       <c r="C80" t="n">
+        <v>-226133</v>
+      </c>
+      <c r="D80" t="n">
+        <v>202059</v>
+      </c>
+      <c r="E80" t="n">
         <v>-447289</v>
       </c>
-      <c r="D80" t="n">
+      <c r="F80" t="n">
         <v>869034</v>
-      </c>
-      <c r="E80" t="n">
-        <v>-1377519</v>
-      </c>
-      <c r="F80" t="n">
-        <v>48455</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -8085,29 +8085,29 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -209 千股)</t>
+          <t>📉 20d 巨變(減碼 -265 千股)</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-894468</v>
+        <v>-712133</v>
       </c>
       <c r="D81" t="n">
-        <v>-2768746</v>
+        <v>-2159097</v>
       </c>
       <c r="E81" t="n">
-        <v>-637403</v>
+        <v>-276589</v>
       </c>
       <c r="F81" t="n">
-        <v>-2559521</v>
+        <v>-1893791</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>精測</t>
         </is>
       </c>
     </row>
@@ -8119,20 +8119,20 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,691 千股)</t>
+          <t>📈 20d 巨變(加碼 124 千股)</t>
         </is>
       </c>
       <c r="C82" t="n">
+        <v>-5160953</v>
+      </c>
+      <c r="D82" t="n">
+        <v>-14162537</v>
+      </c>
+      <c r="E82" t="n">
         <v>-5120170</v>
       </c>
-      <c r="D82" t="n">
+      <c r="F82" t="n">
         <v>-14286055</v>
-      </c>
-      <c r="E82" t="n">
-        <v>-3938296</v>
-      </c>
-      <c r="F82" t="n">
-        <v>-11594702</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -8143,145 +8143,145 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -311 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 22,333 千股)</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-276589</v>
+        <v>1602170</v>
       </c>
       <c r="D83" t="n">
-        <v>-1893791</v>
+        <v>22131664</v>
       </c>
       <c r="E83" t="n">
-        <v>247668</v>
+        <v>-7602548</v>
       </c>
       <c r="F83" t="n">
-        <v>-1582668</v>
+        <v>-201381</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,842 千股)</t>
+          <t>📉 20d 巨變(減碼 -53 千股)</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-7602548</v>
+        <v>-42000</v>
       </c>
       <c r="D84" t="n">
-        <v>-201381</v>
+        <v>82009</v>
       </c>
       <c r="E84" t="n">
-        <v>-1719450</v>
+        <v>-64000</v>
       </c>
       <c r="F84" t="n">
-        <v>-2042935</v>
+        <v>135009</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 65 千股)</t>
+          <t>📉 20d 巨變(減碼 -297 千股)</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>138201</v>
+        <v>146096</v>
       </c>
       <c r="D85" t="n">
-        <v>729745</v>
+        <v>-1236292</v>
       </c>
       <c r="E85" t="n">
-        <v>199000</v>
+        <v>108179</v>
       </c>
       <c r="F85" t="n">
-        <v>664404</v>
+        <v>-939220</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -332 千股)</t>
+          <t>📉 20d 巨變(減碼 -30 千股)</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>108179</v>
+        <v>141640</v>
       </c>
       <c r="D86" t="n">
-        <v>-939220</v>
+        <v>700184</v>
       </c>
       <c r="E86" t="n">
-        <v>70991</v>
+        <v>138201</v>
       </c>
       <c r="F86" t="n">
-        <v>-606828</v>
+        <v>729745</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>東科-KY</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -12 千股)</t>
+          <t>📈 20d 巨變(加碼 667 千股)</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-64000</v>
+        <v>-220549</v>
       </c>
       <c r="D87" t="n">
-        <v>135009</v>
+        <v>-8827191</v>
       </c>
       <c r="E87" t="n">
-        <v>-6000</v>
+        <v>-698227</v>
       </c>
       <c r="F87" t="n">
-        <v>147009</v>
+        <v>-9494631</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>宏捷科</t>
         </is>
       </c>
     </row>
@@ -8293,20 +8293,20 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -156 千股)</t>
+          <t>📈 20d 巨變(加碼 1,438 千股)</t>
         </is>
       </c>
       <c r="C88" t="n">
+        <v>10840094</v>
+      </c>
+      <c r="D88" t="n">
+        <v>10168356</v>
+      </c>
+      <c r="E88" t="n">
         <v>7638318</v>
       </c>
-      <c r="D88" t="n">
+      <c r="F88" t="n">
         <v>8729983</v>
-      </c>
-      <c r="E88" t="n">
-        <v>8072182</v>
-      </c>
-      <c r="F88" t="n">
-        <v>8885812</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -8317,29 +8317,29 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -393 千股)</t>
+          <t>📈 20d 巨變(加碼 1,520 千股)</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-698227</v>
+        <v>26808253</v>
       </c>
       <c r="D89" t="n">
-        <v>-9494631</v>
+        <v>83075410</v>
       </c>
       <c r="E89" t="n">
-        <v>-199668</v>
+        <v>36242499</v>
       </c>
       <c r="F89" t="n">
-        <v>-9101162</v>
+        <v>81555174</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
@@ -8351,20 +8351,20 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 464 千股)</t>
+          <t>📈 20d 巨變(加碼 1,011 千股)</t>
         </is>
       </c>
       <c r="C90" t="n">
+        <v>2905425</v>
+      </c>
+      <c r="D90" t="n">
+        <v>5283617</v>
+      </c>
+      <c r="E90" t="n">
         <v>3250475</v>
       </c>
-      <c r="D90" t="n">
+      <c r="F90" t="n">
         <v>4272650</v>
-      </c>
-      <c r="E90" t="n">
-        <v>2673600</v>
-      </c>
-      <c r="F90" t="n">
-        <v>3808580</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -8375,29 +8375,29 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,586 千股)</t>
+          <t>📉 20d 巨變(減碼 -298 千股)</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>36242499</v>
+        <v>176396</v>
       </c>
       <c r="D91" t="n">
-        <v>81555174</v>
+        <v>-470669</v>
       </c>
       <c r="E91" t="n">
-        <v>47016221</v>
+        <v>272296</v>
       </c>
       <c r="F91" t="n">
-        <v>78969213</v>
+        <v>-172416</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>中保科</t>
         </is>
       </c>
     </row>
@@ -8409,20 +8409,20 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -50 千股)</t>
+          <t>📈 20d 巨變(加碼 14 千股)</t>
         </is>
       </c>
       <c r="C92" t="n">
+        <v>-145902</v>
+      </c>
+      <c r="D92" t="n">
+        <v>-152759</v>
+      </c>
+      <c r="E92" t="n">
         <v>-212378</v>
       </c>
-      <c r="D92" t="n">
+      <c r="F92" t="n">
         <v>-167173</v>
-      </c>
-      <c r="E92" t="n">
-        <v>-237413</v>
-      </c>
-      <c r="F92" t="n">
-        <v>-117553</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -8433,29 +8433,29 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -53 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -7 千股)</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>272296</v>
+        <v>50745</v>
       </c>
       <c r="D93" t="n">
-        <v>-172416</v>
+        <v>53039</v>
       </c>
       <c r="E93" t="n">
-        <v>397516</v>
+        <v>-44328</v>
       </c>
       <c r="F93" t="n">
-        <v>-119027</v>
+        <v>59974</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>安碁資訊</t>
         </is>
       </c>
     </row>
@@ -8467,20 +8467,20 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,132 千股)</t>
+          <t>📈 20d 巨變(加碼 52 千股)</t>
         </is>
       </c>
       <c r="C94" t="n">
+        <v>311140</v>
+      </c>
+      <c r="D94" t="n">
+        <v>-4517535</v>
+      </c>
+      <c r="E94" t="n">
         <v>264303</v>
       </c>
-      <c r="D94" t="n">
+      <c r="F94" t="n">
         <v>-4569412</v>
-      </c>
-      <c r="E94" t="n">
-        <v>182483</v>
-      </c>
-      <c r="F94" t="n">
-        <v>-5701351</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -8491,261 +8491,261 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -53 千股)</t>
+          <t>📉 20d 巨變(減碼 -3,962 千股)</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-44328</v>
+        <v>793066</v>
       </c>
       <c r="D95" t="n">
-        <v>59974</v>
+        <v>13267255</v>
       </c>
       <c r="E95" t="n">
-        <v>-29433</v>
+        <v>2187737</v>
       </c>
       <c r="F95" t="n">
-        <v>113112</v>
+        <v>17228760</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -19,066 千股)</t>
+          <t>📈 20d 巨變(加碼 1,127 千股)</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>23695530</v>
+        <v>8882370</v>
       </c>
       <c r="D96" t="n">
-        <v>-11647115</v>
+        <v>13632155</v>
       </c>
       <c r="E96" t="n">
-        <v>4640801</v>
+        <v>6340567</v>
       </c>
       <c r="F96" t="n">
-        <v>7419144</v>
+        <v>12505517</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>聯發科</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 3,289 千股)</t>
+          <t>📈 20d 巨變(加碼 40 千股)</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>6340567</v>
+        <v>49646</v>
       </c>
       <c r="D97" t="n">
-        <v>12505517</v>
+        <v>-16553</v>
       </c>
       <c r="E97" t="n">
-        <v>3918493</v>
+        <v>46091</v>
       </c>
       <c r="F97" t="n">
-        <v>9216467</v>
+        <v>-56178</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>六方科-KY</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -975 千股)</t>
+          <t>📉 20d 巨變(減碼 -274 千股)</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>2187737</v>
+        <v>-748492</v>
       </c>
       <c r="D98" t="n">
-        <v>17228760</v>
+        <v>-872160</v>
       </c>
       <c r="E98" t="n">
-        <v>3046371</v>
+        <v>-949042</v>
       </c>
       <c r="F98" t="n">
-        <v>18204028</v>
+        <v>-598424</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>創意</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 237 千股)</t>
+          <t>📈 20d 巨變(加碼 920 千股)</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-949042</v>
+        <v>-1882810</v>
       </c>
       <c r="D99" t="n">
-        <v>-598424</v>
+        <v>-11837678</v>
       </c>
       <c r="E99" t="n">
-        <v>-1183926</v>
+        <v>-3602128</v>
       </c>
       <c r="F99" t="n">
-        <v>-835387</v>
+        <v>-12757670</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>緯穎</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 348 千股)</t>
+          <t>📈 20d 巨變(加碼 10,132 千股)</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-3602128</v>
+        <v>35574502</v>
       </c>
       <c r="D100" t="n">
-        <v>-12757670</v>
+        <v>-1515536</v>
       </c>
       <c r="E100" t="n">
-        <v>-4139047</v>
+        <v>23695530</v>
       </c>
       <c r="F100" t="n">
-        <v>-13105329</v>
+        <v>-11647115</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -22 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 299 千股)</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-34985</v>
+        <v>256716</v>
       </c>
       <c r="D101" t="n">
-        <v>122724</v>
+        <v>-2215619</v>
       </c>
       <c r="E101" t="n">
-        <v>-67592</v>
+        <v>-349998</v>
       </c>
       <c r="F101" t="n">
-        <v>144327</v>
+        <v>-2514433</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>高技</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -293 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,125 千股)</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-349998</v>
+        <v>-7743511</v>
       </c>
       <c r="D102" t="n">
-        <v>-2514433</v>
+        <v>-13697978</v>
       </c>
       <c r="E102" t="n">
-        <v>-59892</v>
+        <v>-5886883</v>
       </c>
       <c r="F102" t="n">
-        <v>-2221564</v>
+        <v>-11573309</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>金像電</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,359 千股)</t>
+          <t>📉 20d 巨變(減碼 -62 千股)</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-5886883</v>
+        <v>-10083</v>
       </c>
       <c r="D103" t="n">
-        <v>-11573309</v>
+        <v>60739</v>
       </c>
       <c r="E103" t="n">
-        <v>-2982060</v>
+        <v>-34985</v>
       </c>
       <c r="F103" t="n">
-        <v>-10214001</v>
+        <v>122724</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>信驊</t>
         </is>
       </c>
     </row>
@@ -8757,20 +8757,20 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -205 千股)</t>
+          <t>📈 20d 巨變(加碼 32 千股)</t>
         </is>
       </c>
       <c r="C104" t="n">
+        <v>-501867</v>
+      </c>
+      <c r="D104" t="n">
+        <v>-1347865</v>
+      </c>
+      <c r="E104" t="n">
         <v>-608136</v>
       </c>
-      <c r="D104" t="n">
+      <c r="F104" t="n">
         <v>-1379810</v>
-      </c>
-      <c r="E104" t="n">
-        <v>-170103</v>
-      </c>
-      <c r="F104" t="n">
-        <v>-1175206</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>

--- a/data/台股_外資雷達.xlsx
+++ b/data/台股_外資雷達.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26808</v>
+        <v>24583</v>
       </c>
       <c r="D2" t="n">
-        <v>83075</v>
+        <v>88691</v>
       </c>
       <c r="E2" t="n">
-        <v>174769</v>
+        <v>178402</v>
       </c>
       <c r="F2" t="n">
-        <v>-1665</v>
+        <v>-366</v>
       </c>
       <c r="G2" t="n">
-        <v>-830</v>
+        <v>143</v>
       </c>
       <c r="H2" t="n">
-        <v>408</v>
+        <v>281</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -538,31 +538,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8908</v>
+        <v>27290</v>
       </c>
       <c r="D3" t="n">
-        <v>50779</v>
+        <v>47974</v>
       </c>
       <c r="E3" t="n">
-        <v>201086</v>
+        <v>18214</v>
       </c>
       <c r="F3" t="n">
-        <v>2447</v>
+        <v>-757</v>
       </c>
       <c r="G3" t="n">
-        <v>5708</v>
+        <v>-10442</v>
       </c>
       <c r="H3" t="n">
-        <v>-2331</v>
+        <v>4206</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -571,49 +571,49 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🐌 龜速*</t>
         </is>
       </c>
       <c r="M3" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25887</v>
+        <v>7976</v>
       </c>
       <c r="D4" t="n">
-        <v>44906</v>
+        <v>47150</v>
       </c>
       <c r="E4" t="n">
-        <v>14206</v>
+        <v>202402</v>
       </c>
       <c r="F4" t="n">
-        <v>481</v>
+        <v>2007</v>
       </c>
       <c r="G4" t="n">
-        <v>-8968</v>
+        <v>5984</v>
       </c>
       <c r="H4" t="n">
-        <v>4277</v>
+        <v>-2149</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>🐌 龜速*</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
@@ -649,22 +649,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1602</v>
+        <v>9151</v>
       </c>
       <c r="D5" t="n">
-        <v>22132</v>
+        <v>30063</v>
       </c>
       <c r="E5" t="n">
-        <v>90895</v>
+        <v>96756</v>
       </c>
       <c r="F5" t="n">
-        <v>1235</v>
+        <v>921</v>
       </c>
       <c r="G5" t="n">
-        <v>5518</v>
+        <v>6475</v>
       </c>
       <c r="H5" t="n">
-        <v>-1729</v>
+        <v>-1486</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -691,31 +691,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-4794</v>
+        <v>35170</v>
       </c>
       <c r="D6" t="n">
-        <v>20273</v>
+        <v>19572</v>
       </c>
       <c r="E6" t="n">
-        <v>-7094</v>
+        <v>80888</v>
       </c>
       <c r="F6" t="n">
-        <v>15199</v>
+        <v>4210</v>
       </c>
       <c r="G6" t="n">
-        <v>22314</v>
+        <v>-5029</v>
       </c>
       <c r="H6" t="n">
-        <v>1785</v>
+        <v>-3153</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -724,19 +724,19 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>906</v>
+        <v>1049</v>
       </c>
       <c r="D7" t="n">
-        <v>16464</v>
+        <v>15569</v>
       </c>
       <c r="E7" t="n">
-        <v>23764</v>
+        <v>23807</v>
       </c>
       <c r="F7" t="n">
-        <v>-70</v>
+        <v>-87</v>
       </c>
       <c r="G7" t="n">
-        <v>9</v>
+        <v>-33</v>
       </c>
       <c r="H7" t="n">
-        <v>242</v>
+        <v>-60</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -793,31 +793,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>8882</v>
+        <v>-7400</v>
       </c>
       <c r="D8" t="n">
-        <v>13632</v>
+        <v>14743</v>
       </c>
       <c r="E8" t="n">
-        <v>14389</v>
+        <v>-9858</v>
       </c>
       <c r="F8" t="n">
-        <v>120</v>
+        <v>12097</v>
       </c>
       <c r="G8" t="n">
-        <v>2611</v>
+        <v>22844</v>
       </c>
       <c r="H8" t="n">
-        <v>1757</v>
+        <v>1786</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -826,15 +826,15 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -853,22 +853,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>793</v>
+        <v>1133</v>
       </c>
       <c r="D9" t="n">
-        <v>13267</v>
+        <v>14140</v>
       </c>
       <c r="E9" t="n">
-        <v>102420</v>
+        <v>102058</v>
       </c>
       <c r="F9" t="n">
-        <v>250</v>
+        <v>732</v>
       </c>
       <c r="G9" t="n">
-        <v>-198</v>
+        <v>1123</v>
       </c>
       <c r="H9" t="n">
-        <v>-516</v>
+        <v>-325</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -895,52 +895,52 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10840</v>
+        <v>8382</v>
       </c>
       <c r="D10" t="n">
-        <v>10168</v>
+        <v>12897</v>
       </c>
       <c r="E10" t="n">
-        <v>1757</v>
+        <v>14885</v>
       </c>
       <c r="F10" t="n">
+        <v>585</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2819</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1656</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>🚀 大買</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>44</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>📉 減速</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
         <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-8</v>
-      </c>
-      <c r="H10" t="n">
-        <v>629</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>🚀 大買</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>75</v>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M10" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -955,26 +955,26 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-1955</v>
+        <v>12150</v>
       </c>
       <c r="D11" t="n">
-        <v>8465</v>
+        <v>10975</v>
       </c>
       <c r="E11" t="n">
-        <v>463659</v>
+        <v>474866</v>
       </c>
       <c r="F11" t="n">
-        <v>18933</v>
+        <v>24314</v>
       </c>
       <c r="G11" t="n">
-        <v>34281</v>
+        <v>41759</v>
       </c>
       <c r="H11" t="n">
-        <v>-1856</v>
+        <v>-1065</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>🟢 加碼</t>
+          <t>🚀 大買</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1006,22 +1006,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4127</v>
+        <v>4209</v>
       </c>
       <c r="D12" t="n">
-        <v>7445</v>
+        <v>9003</v>
       </c>
       <c r="E12" t="n">
-        <v>3364</v>
+        <v>3846</v>
       </c>
       <c r="F12" t="n">
-        <v>-9445</v>
+        <v>-8958</v>
       </c>
       <c r="G12" t="n">
-        <v>-20259</v>
+        <v>-20601</v>
       </c>
       <c r="H12" t="n">
-        <v>1004</v>
+        <v>971</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1048,31 +1048,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-1305</v>
+        <v>5583</v>
       </c>
       <c r="D13" t="n">
-        <v>6896</v>
+        <v>8184</v>
       </c>
       <c r="E13" t="n">
-        <v>12217</v>
+        <v>1370</v>
       </c>
       <c r="F13" t="n">
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>659</v>
+        <v>-8</v>
       </c>
       <c r="H13" t="n">
-        <v>979</v>
+        <v>644</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1081,19 +1081,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1108,22 +1108,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7073</v>
+        <v>7228</v>
       </c>
       <c r="D14" t="n">
-        <v>6495</v>
+        <v>7444</v>
       </c>
       <c r="E14" t="n">
-        <v>482</v>
+        <v>1586</v>
       </c>
       <c r="F14" t="n">
-        <v>-190</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>2168</v>
+        <v>2343</v>
       </c>
       <c r="H14" t="n">
-        <v>-4</v>
+        <v>-74</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1150,31 +1150,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1277</v>
+        <v>-96</v>
       </c>
       <c r="D15" t="n">
-        <v>5776</v>
+        <v>7386</v>
       </c>
       <c r="E15" t="n">
-        <v>24706</v>
+        <v>12309</v>
       </c>
       <c r="F15" t="n">
-        <v>1231</v>
+        <v>574</v>
       </c>
       <c r="G15" t="n">
-        <v>854</v>
+        <v>780</v>
       </c>
       <c r="H15" t="n">
-        <v>247</v>
+        <v>964</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1187,45 +1187,45 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2905</v>
+        <v>1417</v>
       </c>
       <c r="D16" t="n">
-        <v>5284</v>
+        <v>5960</v>
       </c>
       <c r="E16" t="n">
-        <v>1695</v>
+        <v>25030</v>
       </c>
       <c r="F16" t="n">
-        <v>-246</v>
+        <v>1248</v>
       </c>
       <c r="G16" t="n">
-        <v>-93</v>
+        <v>886</v>
       </c>
       <c r="H16" t="n">
-        <v>-42</v>
+        <v>203</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1234,49 +1234,49 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1320</v>
+        <v>3179</v>
       </c>
       <c r="D17" t="n">
-        <v>4652</v>
+        <v>5623</v>
       </c>
       <c r="E17" t="n">
-        <v>15380</v>
+        <v>2357</v>
       </c>
       <c r="F17" t="n">
-        <v>-2170</v>
+        <v>-422</v>
       </c>
       <c r="G17" t="n">
-        <v>-7169</v>
+        <v>-410</v>
       </c>
       <c r="H17" t="n">
-        <v>-15</v>
+        <v>-92</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1285,49 +1285,49 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>193</v>
+        <v>-49</v>
       </c>
       <c r="D18" t="n">
-        <v>3176</v>
+        <v>3812</v>
       </c>
       <c r="E18" t="n">
-        <v>5991</v>
+        <v>14549</v>
       </c>
       <c r="F18" t="n">
-        <v>-60</v>
+        <v>-1650</v>
       </c>
       <c r="G18" t="n">
-        <v>-423</v>
+        <v>-7070</v>
       </c>
       <c r="H18" t="n">
-        <v>107</v>
+        <v>-15</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1336,49 +1336,49 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>765</v>
+        <v>1470</v>
       </c>
       <c r="D19" t="n">
-        <v>2845</v>
+        <v>3728</v>
       </c>
       <c r="E19" t="n">
-        <v>988</v>
+        <v>11410</v>
       </c>
       <c r="F19" t="n">
-        <v>984</v>
+        <v>621</v>
       </c>
       <c r="G19" t="n">
-        <v>1118</v>
+        <v>-7668</v>
       </c>
       <c r="H19" t="n">
-        <v>-147</v>
+        <v>-22</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1387,49 +1387,49 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1212</v>
+        <v>554</v>
       </c>
       <c r="D20" t="n">
-        <v>2497</v>
+        <v>3145</v>
       </c>
       <c r="E20" t="n">
-        <v>11132</v>
+        <v>6273</v>
       </c>
       <c r="F20" t="n">
-        <v>887</v>
+        <v>-61</v>
       </c>
       <c r="G20" t="n">
-        <v>-8799</v>
+        <v>-357</v>
       </c>
       <c r="H20" t="n">
-        <v>58</v>
+        <v>133</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1438,53 +1438,53 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>916</v>
+        <v>1127</v>
       </c>
       <c r="D21" t="n">
-        <v>1324</v>
+        <v>3077</v>
       </c>
       <c r="E21" t="n">
-        <v>-9114</v>
+        <v>1241</v>
       </c>
       <c r="F21" t="n">
-        <v>486</v>
+        <v>1275</v>
       </c>
       <c r="G21" t="n">
-        <v>1203</v>
+        <v>1446</v>
       </c>
       <c r="H21" t="n">
-        <v>-276</v>
+        <v>-189</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>🟡 中性</t>
+          <t>🟢 加碼</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1493,7 +1493,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="D22" t="n">
-        <v>1248</v>
+        <v>1324</v>
       </c>
       <c r="E22" t="n">
-        <v>2933</v>
+        <v>2939</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1531,7 +1531,7 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-38</v>
+        <v>-11</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1558,31 +1558,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1154</v>
+        <v>737</v>
       </c>
       <c r="D23" t="n">
-        <v>1075</v>
+        <v>1284</v>
       </c>
       <c r="E23" t="n">
-        <v>2842</v>
+        <v>-3305</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>-553</v>
       </c>
       <c r="G23" t="n">
-        <v>232</v>
+        <v>450</v>
       </c>
       <c r="H23" t="n">
-        <v>-45</v>
+        <v>239</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1591,49 +1591,49 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1360</v>
+        <v>1153</v>
       </c>
       <c r="D24" t="n">
-        <v>897</v>
+        <v>1258</v>
       </c>
       <c r="E24" t="n">
-        <v>29</v>
+        <v>3525</v>
       </c>
       <c r="F24" t="n">
-        <v>-2896</v>
+        <v>-3</v>
       </c>
       <c r="G24" t="n">
-        <v>-4250</v>
+        <v>-34</v>
       </c>
       <c r="H24" t="n">
-        <v>336</v>
+        <v>-55</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1642,100 +1642,100 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>90</v>
+        <v>32</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>401</v>
+        <v>1644</v>
       </c>
       <c r="D25" t="n">
-        <v>877</v>
+        <v>1241</v>
       </c>
       <c r="E25" t="n">
-        <v>1215</v>
+        <v>-9274</v>
       </c>
       <c r="F25" t="n">
+        <v>40</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1036</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-347</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>90</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
         <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>9</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>78</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>🛬 穩定</t>
-        </is>
-      </c>
-      <c r="M25" t="n">
-        <v>-2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>382</v>
+        <v>802</v>
       </c>
       <c r="D26" t="n">
-        <v>847</v>
+        <v>1149</v>
       </c>
       <c r="E26" t="n">
-        <v>-3556</v>
+        <v>-1002</v>
       </c>
       <c r="F26" t="n">
-        <v>-251</v>
+        <v>-1188</v>
       </c>
       <c r="G26" t="n">
-        <v>595</v>
+        <v>-2216</v>
       </c>
       <c r="H26" t="n">
-        <v>228</v>
+        <v>130</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1748,96 +1748,96 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>142</v>
+        <v>640</v>
       </c>
       <c r="D27" t="n">
-        <v>700</v>
+        <v>949</v>
       </c>
       <c r="E27" t="n">
-        <v>-209</v>
+        <v>2884</v>
       </c>
       <c r="F27" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G27" t="n">
+        <v>232</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-80</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>60</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>✈️ 高飛</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
         <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>6</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
-        <v>78</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M27" t="n">
-        <v>-3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>319</v>
+        <v>-74</v>
       </c>
       <c r="D28" t="n">
-        <v>695</v>
+        <v>797</v>
       </c>
       <c r="E28" t="n">
-        <v>964</v>
+        <v>-550</v>
       </c>
       <c r="F28" t="n">
-        <v>-849</v>
+        <v>152</v>
       </c>
       <c r="G28" t="n">
-        <v>-2586</v>
+        <v>113</v>
       </c>
       <c r="H28" t="n">
-        <v>-1</v>
+        <v>-27</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1854,41 +1854,41 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>530</v>
+        <v>429</v>
       </c>
       <c r="D29" t="n">
-        <v>589</v>
+        <v>791</v>
       </c>
       <c r="E29" t="n">
-        <v>-1299</v>
+        <v>1216</v>
       </c>
       <c r="F29" t="n">
-        <v>-1079</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>-2544</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>135</v>
+        <v>7</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1897,49 +1897,49 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>657</v>
+        <v>-529</v>
       </c>
       <c r="D30" t="n">
-        <v>586</v>
+        <v>728</v>
       </c>
       <c r="E30" t="n">
-        <v>2968</v>
+        <v>4797</v>
       </c>
       <c r="F30" t="n">
-        <v>-5</v>
+        <v>318</v>
       </c>
       <c r="G30" t="n">
-        <v>-38</v>
+        <v>1757</v>
       </c>
       <c r="H30" t="n">
-        <v>-37</v>
+        <v>181</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1948,49 +1948,49 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>59</v>
+        <v>196</v>
       </c>
       <c r="D31" t="n">
-        <v>444</v>
+        <v>702</v>
       </c>
       <c r="E31" t="n">
-        <v>-593</v>
+        <v>-131</v>
       </c>
       <c r="F31" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>181</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-52</v>
+        <v>4</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1999,49 +1999,49 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M31" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>216</v>
+        <v>1104</v>
       </c>
       <c r="D32" t="n">
-        <v>433</v>
+        <v>657</v>
       </c>
       <c r="E32" t="n">
-        <v>-151</v>
+        <v>-159</v>
       </c>
       <c r="F32" t="n">
-        <v>215</v>
+        <v>-2779</v>
       </c>
       <c r="G32" t="n">
-        <v>442</v>
+        <v>-4324</v>
       </c>
       <c r="H32" t="n">
-        <v>122</v>
+        <v>387</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2062,37 +2062,37 @@
         </is>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>57</v>
+        <v>255</v>
       </c>
       <c r="D33" t="n">
-        <v>334</v>
+        <v>560</v>
       </c>
       <c r="E33" t="n">
-        <v>1138</v>
+        <v>1000</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>-837</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>-2744</v>
       </c>
       <c r="H33" t="n">
-        <v>6</v>
+        <v>-21</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2101,49 +2101,49 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1486</v>
+        <v>-290</v>
       </c>
       <c r="D34" t="n">
-        <v>310</v>
+        <v>446</v>
       </c>
       <c r="E34" t="n">
-        <v>7326</v>
+        <v>-1553</v>
       </c>
       <c r="F34" t="n">
-        <v>-3</v>
+        <v>-1270</v>
       </c>
       <c r="G34" t="n">
-        <v>-19</v>
+        <v>-976</v>
       </c>
       <c r="H34" t="n">
-        <v>79</v>
+        <v>18</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2164,37 +2164,37 @@
         </is>
       </c>
       <c r="M34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>285</v>
+        <v>126</v>
       </c>
       <c r="D35" t="n">
-        <v>276</v>
+        <v>386</v>
       </c>
       <c r="E35" t="n">
-        <v>-1742</v>
+        <v>-266</v>
       </c>
       <c r="F35" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="G35" t="n">
-        <v>-1</v>
+        <v>438</v>
       </c>
       <c r="H35" t="n">
-        <v>-5</v>
+        <v>101</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2203,15 +2203,15 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M35" t="n">
@@ -2221,82 +2221,82 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>142</v>
+        <v>316</v>
       </c>
       <c r="D36" t="n">
-        <v>242</v>
+        <v>345</v>
       </c>
       <c r="E36" t="n">
-        <v>575</v>
+        <v>-1689</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>77</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
         <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>50</v>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
-        <v>76</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>🚀 加速器</t>
-        </is>
-      </c>
-      <c r="M36" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-226</v>
+        <v>281</v>
       </c>
       <c r="D37" t="n">
-        <v>202</v>
+        <v>305</v>
       </c>
       <c r="E37" t="n">
-        <v>783</v>
+        <v>648</v>
       </c>
       <c r="F37" t="n">
-        <v>-729</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>-1976</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-69</v>
+        <v>29</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2305,15 +2305,15 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M37" t="n">
@@ -2323,31 +2323,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-247</v>
+        <v>69</v>
       </c>
       <c r="D38" t="n">
-        <v>153</v>
+        <v>305</v>
       </c>
       <c r="E38" t="n">
-        <v>-1725</v>
+        <v>1164</v>
       </c>
       <c r="F38" t="n">
-        <v>-1055</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>-804</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2356,49 +2356,49 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>67</v>
+        <v>2493</v>
       </c>
       <c r="D39" t="n">
-        <v>129</v>
+        <v>296</v>
       </c>
       <c r="E39" t="n">
-        <v>789</v>
+        <v>7357</v>
       </c>
       <c r="F39" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="G39" t="n">
-        <v>-28</v>
+        <v>-17</v>
       </c>
       <c r="H39" t="n">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2411,45 +2411,45 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>大統益</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-505</v>
+        <v>76</v>
       </c>
       <c r="D40" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E40" t="n">
-        <v>-1138</v>
+        <v>788</v>
       </c>
       <c r="F40" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>139</v>
+        <v>-28</v>
       </c>
       <c r="H40" t="n">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2458,100 +2458,88 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M40" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-750</v>
+        <v>39</v>
       </c>
       <c r="D41" t="n">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="E41" t="n">
-        <v>4777</v>
+        <v>-297</v>
       </c>
       <c r="F41" t="n">
-        <v>174</v>
+        <v>51</v>
       </c>
       <c r="G41" t="n">
-        <v>1974</v>
+        <v>233</v>
       </c>
       <c r="H41" t="n">
-        <v>253</v>
+        <v>2</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K41" t="n">
-        <v>100</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>🚀 加速器</t>
-        </is>
-      </c>
-      <c r="M41" t="n">
-        <v>5</v>
-      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-42</v>
+        <v>254</v>
       </c>
       <c r="D42" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="E42" t="n">
-        <v>680</v>
+        <v>-113</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>-277</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2564,45 +2552,45 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>393</v>
+        <v>72</v>
       </c>
       <c r="D43" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E43" t="n">
-        <v>-2831</v>
+        <v>157</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>-235</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>2036</v>
+        <v>13</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2615,11 +2603,11 @@
         </is>
       </c>
       <c r="K43" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M43" t="n">
@@ -2629,70 +2617,82 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>方土霖</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-10</v>
+        <v>-3</v>
       </c>
       <c r="D44" t="n">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E44" t="n">
-        <v>-346</v>
+        <v>48</v>
       </c>
       <c r="F44" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>327</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>89</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>960</v>
+        <v>96</v>
       </c>
       <c r="D45" t="n">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="E45" t="n">
-        <v>-4284</v>
+        <v>-53</v>
       </c>
       <c r="F45" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>196</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>-51</v>
+        <v>0</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2705,11 +2705,11 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M45" t="n">
@@ -2719,22 +2719,22 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>51</v>
+        <v>-105</v>
       </c>
       <c r="D46" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>131</v>
+        <v>646</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2743,7 +2743,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2760,32 +2760,32 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>方土霖</t>
+          <t>大車隊</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-1</v>
+        <v>-49</v>
       </c>
       <c r="D47" t="n">
-        <v>50</v>
+        <v>-22</v>
       </c>
       <c r="E47" t="n">
-        <v>49</v>
+        <v>-34</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -2794,7 +2794,7 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2807,36 +2807,36 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M47" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="D48" t="n">
-        <v>18</v>
+        <v>-25</v>
       </c>
       <c r="E48" t="n">
-        <v>-62</v>
+        <v>7</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M48" t="n">
@@ -2872,31 +2872,31 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-36</v>
+        <v>1102</v>
       </c>
       <c r="D49" t="n">
-        <v>-15</v>
+        <v>-33</v>
       </c>
       <c r="E49" t="n">
-        <v>-30</v>
+        <v>-4283</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H49" t="n">
-        <v>-1</v>
+        <v>-70</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2905,11 +2905,11 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -2917,28 +2917,28 @@
         </is>
       </c>
       <c r="M49" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>50</v>
+        <v>-36</v>
       </c>
       <c r="D50" t="n">
-        <v>-17</v>
+        <v>-74</v>
       </c>
       <c r="E50" t="n">
-        <v>4</v>
+        <v>654</v>
       </c>
       <c r="F50" t="n">
         <v>0</v>
@@ -2956,49 +2956,49 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>82</v>
+        <v>-376</v>
       </c>
       <c r="D51" t="n">
-        <v>-19</v>
+        <v>-82</v>
       </c>
       <c r="E51" t="n">
-        <v>-256</v>
+        <v>-874</v>
       </c>
       <c r="F51" t="n">
-        <v>-9</v>
+        <v>66</v>
       </c>
       <c r="G51" t="n">
-        <v>-277</v>
+        <v>-514</v>
       </c>
       <c r="H51" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3007,49 +3007,49 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-17</v>
+        <v>5</v>
       </c>
       <c r="D52" t="n">
-        <v>-67</v>
+        <v>-120</v>
       </c>
       <c r="E52" t="n">
-        <v>664</v>
+        <v>80</v>
       </c>
       <c r="F52" t="n">
         <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H52" t="n">
-        <v>-2</v>
+        <v>41</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3058,49 +3058,49 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M52" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-500</v>
+        <v>35</v>
       </c>
       <c r="D53" t="n">
-        <v>-99</v>
+        <v>-183</v>
       </c>
       <c r="E53" t="n">
-        <v>-934</v>
+        <v>1434</v>
       </c>
       <c r="F53" t="n">
-        <v>167</v>
+        <v>39</v>
       </c>
       <c r="G53" t="n">
-        <v>-480</v>
+        <v>44</v>
       </c>
       <c r="H53" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3113,45 +3113,45 @@
         </is>
       </c>
       <c r="K53" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速*</t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-146</v>
+        <v>58</v>
       </c>
       <c r="D54" t="n">
-        <v>-153</v>
+        <v>-204</v>
       </c>
       <c r="E54" t="n">
-        <v>34</v>
+        <v>475</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G54" t="n">
-        <v>50</v>
+        <v>-41</v>
       </c>
       <c r="H54" t="n">
-        <v>44</v>
+        <v>-26</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3160,15 +3160,15 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M54" t="n">
@@ -3178,31 +3178,31 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="D55" t="n">
-        <v>-161</v>
+        <v>-332</v>
       </c>
       <c r="E55" t="n">
-        <v>473</v>
+        <v>-1261</v>
       </c>
       <c r="F55" t="n">
-        <v>-1</v>
+        <v>-958</v>
       </c>
       <c r="G55" t="n">
-        <v>-41</v>
+        <v>-1106</v>
       </c>
       <c r="H55" t="n">
-        <v>-21</v>
+        <v>81</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3211,49 +3211,49 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>96</v>
+        <v>66</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-11</v>
+        <v>2258</v>
       </c>
       <c r="D56" t="n">
-        <v>-329</v>
+        <v>-356</v>
       </c>
       <c r="E56" t="n">
-        <v>1412</v>
+        <v>-1174</v>
       </c>
       <c r="F56" t="n">
-        <v>51</v>
+        <v>-2521</v>
       </c>
       <c r="G56" t="n">
-        <v>53</v>
+        <v>-2653</v>
       </c>
       <c r="H56" t="n">
-        <v>3</v>
+        <v>142</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3262,49 +3262,49 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>🐌 龜速*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>19</v>
+        <v>875</v>
       </c>
       <c r="D57" t="n">
-        <v>-404</v>
+        <v>-399</v>
       </c>
       <c r="E57" t="n">
-        <v>-1304</v>
+        <v>319</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>-1968</v>
       </c>
       <c r="H57" t="n">
-        <v>-7</v>
+        <v>-349</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3313,11 +3313,11 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>79</v>
+        <v>63</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3343,10 +3343,10 @@
         <v>-33</v>
       </c>
       <c r="D58" t="n">
-        <v>-422</v>
+        <v>-406</v>
       </c>
       <c r="E58" t="n">
-        <v>-834</v>
+        <v>-839</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -3382,31 +3382,31 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-55</v>
+        <v>-347</v>
       </c>
       <c r="D59" t="n">
-        <v>-467</v>
+        <v>-431</v>
       </c>
       <c r="E59" t="n">
-        <v>-2820</v>
+        <v>-1191</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="H59" t="n">
-        <v>-37</v>
+        <v>46</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3415,49 +3415,49 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M59" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>德昌</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>176</v>
+        <v>21</v>
       </c>
       <c r="D60" t="n">
-        <v>-471</v>
+        <v>-431</v>
       </c>
       <c r="E60" t="n">
-        <v>2406</v>
+        <v>-1306</v>
       </c>
       <c r="F60" t="n">
-        <v>-297</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>-255</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>26</v>
+        <v>-7</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3470,45 +3470,45 @@
         </is>
       </c>
       <c r="K60" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>54</v>
+        <v>-282</v>
       </c>
       <c r="D61" t="n">
-        <v>-490</v>
+        <v>-469</v>
       </c>
       <c r="E61" t="n">
-        <v>-1467</v>
+        <v>1433</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>435</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1094</v>
       </c>
       <c r="H61" t="n">
-        <v>-24</v>
+        <v>-113</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -3517,49 +3517,49 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K61" t="n">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1697</v>
+        <v>-41</v>
       </c>
       <c r="D62" t="n">
-        <v>-612</v>
+        <v>-491</v>
       </c>
       <c r="E62" t="n">
-        <v>-1295</v>
+        <v>-2731</v>
       </c>
       <c r="F62" t="n">
-        <v>-2553</v>
+        <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>-2648</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>253</v>
+        <v>-45</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3568,100 +3568,88 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K62" t="n">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-748</v>
+        <v>-410</v>
       </c>
       <c r="D63" t="n">
-        <v>-872</v>
+        <v>-576</v>
       </c>
       <c r="E63" t="n">
-        <v>981</v>
+        <v>663</v>
       </c>
       <c r="F63" t="n">
-        <v>495</v>
+        <v>-608</v>
       </c>
       <c r="G63" t="n">
-        <v>1319</v>
+        <v>789</v>
       </c>
       <c r="H63" t="n">
-        <v>-80</v>
+        <v>-19</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K63" t="n">
-        <v>52</v>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>🛬 穩定</t>
-        </is>
-      </c>
-      <c r="M63" t="n">
-        <v>2</v>
-      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>151</v>
+        <v>264</v>
       </c>
       <c r="D64" t="n">
-        <v>-957</v>
+        <v>-600</v>
       </c>
       <c r="E64" t="n">
-        <v>1195</v>
+        <v>2437</v>
       </c>
       <c r="F64" t="n">
-        <v>-73</v>
+        <v>-200</v>
       </c>
       <c r="G64" t="n">
-        <v>-482</v>
+        <v>-254</v>
       </c>
       <c r="H64" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3670,49 +3658,49 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>80</v>
+        <v>548</v>
       </c>
       <c r="D65" t="n">
-        <v>-984</v>
+        <v>-604</v>
       </c>
       <c r="E65" t="n">
-        <v>474</v>
+        <v>-2952</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>-235</v>
       </c>
       <c r="H65" t="n">
-        <v>-282</v>
+        <v>1937</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3725,45 +3713,45 @@
         </is>
       </c>
       <c r="K65" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-27</v>
+        <v>31</v>
       </c>
       <c r="D66" t="n">
-        <v>-1065</v>
+        <v>-635</v>
       </c>
       <c r="E66" t="n">
-        <v>-1469</v>
+        <v>-1529</v>
       </c>
       <c r="F66" t="n">
-        <v>-374</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>-38</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-62</v>
+        <v>-26</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3776,7 +3764,7 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3784,37 +3772,37 @@
         </is>
       </c>
       <c r="M66" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-1</v>
+        <v>79</v>
       </c>
       <c r="D67" t="n">
-        <v>-1101</v>
+        <v>-828</v>
       </c>
       <c r="E67" t="n">
-        <v>-6890</v>
+        <v>521</v>
       </c>
       <c r="F67" t="n">
-        <v>-2967</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>-8678</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>439</v>
+        <v>-817</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3823,11 +3811,11 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3835,37 +3823,37 @@
         </is>
       </c>
       <c r="M67" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-377</v>
+        <v>-239</v>
       </c>
       <c r="D68" t="n">
-        <v>-1183</v>
+        <v>-1283</v>
       </c>
       <c r="E68" t="n">
-        <v>513</v>
+        <v>-1484</v>
       </c>
       <c r="F68" t="n">
-        <v>-862</v>
+        <v>-284</v>
       </c>
       <c r="G68" t="n">
-        <v>-196</v>
+        <v>-29</v>
       </c>
       <c r="H68" t="n">
-        <v>35</v>
+        <v>-60</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3878,45 +3866,45 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>146</v>
+        <v>-391</v>
       </c>
       <c r="D69" t="n">
-        <v>-1236</v>
+        <v>-1284</v>
       </c>
       <c r="E69" t="n">
-        <v>1669</v>
+        <v>455</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>-853</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>-219</v>
       </c>
       <c r="H69" t="n">
-        <v>-243</v>
+        <v>37</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3925,49 +3913,49 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-190</v>
+        <v>16317</v>
       </c>
       <c r="D70" t="n">
-        <v>-1317</v>
+        <v>-1321</v>
       </c>
       <c r="E70" t="n">
-        <v>-1905</v>
+        <v>-104136</v>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>-395</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>-3752</v>
       </c>
       <c r="H70" t="n">
-        <v>1</v>
+        <v>4928</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3980,84 +3968,96 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-502</v>
+        <v>-140</v>
       </c>
       <c r="D71" t="n">
-        <v>-1348</v>
+        <v>-1528</v>
       </c>
       <c r="E71" t="n">
-        <v>720</v>
+        <v>1585</v>
       </c>
       <c r="F71" t="n">
-        <v>-412</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>1637</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0</v>
+        <v>-359</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>78</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>📉 減速</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>-2</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-1552</v>
+        <v>-81</v>
       </c>
       <c r="D72" t="n">
-        <v>-1417</v>
+        <v>-1571</v>
       </c>
       <c r="E72" t="n">
-        <v>-7431</v>
+        <v>1048</v>
       </c>
       <c r="F72" t="n">
-        <v>429</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>355</v>
+        <v>-482</v>
       </c>
       <c r="H72" t="n">
-        <v>399</v>
+        <v>-53</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -4066,49 +4066,49 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>35575</v>
+        <v>-1845</v>
       </c>
       <c r="D73" t="n">
-        <v>-1516</v>
+        <v>-1612</v>
       </c>
       <c r="E73" t="n">
-        <v>44084</v>
+        <v>-7743</v>
       </c>
       <c r="F73" t="n">
-        <v>-16433</v>
+        <v>438</v>
       </c>
       <c r="G73" t="n">
-        <v>-49391</v>
+        <v>283</v>
       </c>
       <c r="H73" t="n">
-        <v>-3006</v>
+        <v>320</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4121,45 +4121,45 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M73" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>聯合</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-1962</v>
+        <v>-149</v>
       </c>
       <c r="D74" t="n">
-        <v>-1680</v>
+        <v>-1648</v>
       </c>
       <c r="E74" t="n">
-        <v>7232</v>
+        <v>-1900</v>
       </c>
       <c r="F74" t="n">
-        <v>787</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>-310</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4168,19 +4168,19 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>57</v>
+        <v>87</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M74" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4195,22 +4195,22 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-1184</v>
+        <v>-1052</v>
       </c>
       <c r="D75" t="n">
-        <v>-1745</v>
+        <v>-1722</v>
       </c>
       <c r="E75" t="n">
-        <v>-816</v>
+        <v>-894</v>
       </c>
       <c r="F75" t="n">
         <v>5</v>
       </c>
       <c r="G75" t="n">
-        <v>-23</v>
+        <v>-22</v>
       </c>
       <c r="H75" t="n">
-        <v>-7</v>
+        <v>-20</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4246,22 +4246,22 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-160</v>
+        <v>-114</v>
       </c>
       <c r="D76" t="n">
-        <v>-1848</v>
+        <v>-1883</v>
       </c>
       <c r="E76" t="n">
-        <v>-3641</v>
+        <v>-3630</v>
       </c>
       <c r="F76" t="n">
+        <v>2</v>
+      </c>
+      <c r="G76" t="n">
         <v>1</v>
       </c>
-      <c r="G76" t="n">
-        <v>0</v>
-      </c>
       <c r="H76" t="n">
-        <v>-20</v>
+        <v>-27</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4288,44 +4288,44 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-712</v>
+        <v>-1692</v>
       </c>
       <c r="D77" t="n">
-        <v>-2159</v>
+        <v>-1964</v>
       </c>
       <c r="E77" t="n">
-        <v>-2671</v>
+        <v>7006</v>
       </c>
       <c r="F77" t="n">
-        <v>12</v>
+        <v>473</v>
       </c>
       <c r="G77" t="n">
-        <v>1530</v>
+        <v>-237</v>
       </c>
       <c r="H77" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -4333,37 +4333,37 @@
         </is>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-530</v>
+        <v>-337</v>
       </c>
       <c r="D78" t="n">
-        <v>-2171</v>
+        <v>-2021</v>
       </c>
       <c r="E78" t="n">
-        <v>-2374</v>
+        <v>-7484</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>-3371</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>-8594</v>
       </c>
       <c r="H78" t="n">
-        <v>68</v>
+        <v>394</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4376,7 +4376,7 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -4384,47 +4384,59 @@
         </is>
       </c>
       <c r="M78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>257</v>
+        <v>-2232</v>
       </c>
       <c r="D79" t="n">
-        <v>-2216</v>
+        <v>-2181</v>
       </c>
       <c r="E79" t="n">
-        <v>-4916</v>
+        <v>-7979</v>
       </c>
       <c r="F79" t="n">
-        <v>119</v>
+        <v>641</v>
       </c>
       <c r="G79" t="n">
-        <v>-149</v>
+        <v>946</v>
       </c>
       <c r="H79" t="n">
-        <v>78</v>
+        <v>-441</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
           <t>🟠 減碼</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>70</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4438,22 +4450,22 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>617</v>
+        <v>496</v>
       </c>
       <c r="D80" t="n">
-        <v>-2345</v>
+        <v>-2187</v>
       </c>
       <c r="E80" t="n">
-        <v>-2965</v>
+        <v>-2983</v>
       </c>
       <c r="F80" t="n">
-        <v>-9</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
         <v>-217</v>
       </c>
       <c r="H80" t="n">
-        <v>2</v>
+        <v>-47</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -4480,31 +4492,31 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>471</v>
+        <v>-766</v>
       </c>
       <c r="D81" t="n">
-        <v>-2423</v>
+        <v>-2219</v>
       </c>
       <c r="E81" t="n">
-        <v>-1065</v>
+        <v>-2720</v>
       </c>
       <c r="F81" t="n">
-        <v>406</v>
+        <v>-136</v>
       </c>
       <c r="G81" t="n">
-        <v>1137</v>
+        <v>1453</v>
       </c>
       <c r="H81" t="n">
-        <v>-261</v>
+        <v>39</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4521,11 +4533,11 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M81" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -4540,22 +4552,22 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-1309</v>
+        <v>-1488</v>
       </c>
       <c r="D82" t="n">
-        <v>-2428</v>
+        <v>-2764</v>
       </c>
       <c r="E82" t="n">
-        <v>-1610</v>
+        <v>-1887</v>
       </c>
       <c r="F82" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
         <v>433</v>
       </c>
       <c r="H82" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4582,31 +4594,31 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-3603</v>
+        <v>-3651</v>
       </c>
       <c r="D83" t="n">
-        <v>-2599</v>
+        <v>-2820</v>
       </c>
       <c r="E83" t="n">
-        <v>-7939</v>
+        <v>-3831</v>
       </c>
       <c r="F83" t="n">
-        <v>1401</v>
+        <v>124</v>
       </c>
       <c r="G83" t="n">
-        <v>2175</v>
+        <v>8659</v>
       </c>
       <c r="H83" t="n">
-        <v>-256</v>
+        <v>58</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4619,96 +4631,84 @@
         </is>
       </c>
       <c r="K83" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M83" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-3707</v>
+        <v>-117</v>
       </c>
       <c r="D84" t="n">
-        <v>-2757</v>
+        <v>-3035</v>
       </c>
       <c r="E84" t="n">
-        <v>-3735</v>
+        <v>-5147</v>
       </c>
       <c r="F84" t="n">
-        <v>52</v>
+        <v>204</v>
       </c>
       <c r="G84" t="n">
-        <v>8767</v>
+        <v>-64</v>
       </c>
       <c r="H84" t="n">
-        <v>111</v>
+        <v>-47</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
           <t>🟠 減碼</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K84" t="n">
-        <v>69</v>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M84" t="n">
-        <v>-3</v>
-      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-778</v>
+        <v>-469</v>
       </c>
       <c r="D85" t="n">
-        <v>-2878</v>
+        <v>-3107</v>
       </c>
       <c r="E85" t="n">
-        <v>-76</v>
+        <v>-16971</v>
       </c>
       <c r="F85" t="n">
-        <v>-222</v>
+        <v>-912</v>
       </c>
       <c r="G85" t="n">
-        <v>-949</v>
+        <v>-2134</v>
       </c>
       <c r="H85" t="n">
-        <v>66</v>
+        <v>-562</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4717,100 +4717,100 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K85" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M85" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-1419</v>
+        <v>-687</v>
       </c>
       <c r="D86" t="n">
-        <v>-3113</v>
+        <v>-3108</v>
       </c>
       <c r="E86" t="n">
-        <v>-11</v>
+        <v>-139</v>
       </c>
       <c r="F86" t="n">
+        <v>-203</v>
+      </c>
+      <c r="G86" t="n">
+        <v>-925</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-21</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>🟠 減碼</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>73</v>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M86" t="n">
         <v>-1</v>
-      </c>
-      <c r="G86" t="n">
-        <v>-281</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-161</v>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>🟠 減碼</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K86" t="n">
-        <v>69</v>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>🐌 龜速</t>
-        </is>
-      </c>
-      <c r="M86" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>449</v>
+        <v>-1903</v>
       </c>
       <c r="D87" t="n">
-        <v>-3240</v>
+        <v>-3118</v>
       </c>
       <c r="E87" t="n">
-        <v>-111260</v>
+        <v>-240</v>
       </c>
       <c r="F87" t="n">
-        <v>914</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>-3130</v>
+        <v>-281</v>
       </c>
       <c r="H87" t="n">
-        <v>4830</v>
+        <v>-144</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4819,15 +4819,15 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K87" t="n">
-        <v>100</v>
+        <v>69</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M87" t="n">
@@ -4837,31 +4837,31 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-602</v>
+        <v>-510</v>
       </c>
       <c r="D88" t="n">
-        <v>-3260</v>
+        <v>-4382</v>
       </c>
       <c r="E88" t="n">
-        <v>-17077</v>
+        <v>-2610</v>
       </c>
       <c r="F88" t="n">
-        <v>-526</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>-1626</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>-520</v>
+        <v>64</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -4874,45 +4874,45 @@
         </is>
       </c>
       <c r="K88" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>311</v>
+        <v>-93</v>
       </c>
       <c r="D89" t="n">
-        <v>-4518</v>
+        <v>-5000</v>
       </c>
       <c r="E89" t="n">
-        <v>-15129</v>
+        <v>-31871</v>
       </c>
       <c r="F89" t="n">
-        <v>-356</v>
+        <v>12</v>
       </c>
       <c r="G89" t="n">
-        <v>-230</v>
+        <v>366</v>
       </c>
       <c r="H89" t="n">
-        <v>450</v>
+        <v>56</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4929,41 +4929,41 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>長榮航太</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>754</v>
+        <v>-120</v>
       </c>
       <c r="D90" t="n">
-        <v>-4742</v>
+        <v>-5099</v>
       </c>
       <c r="E90" t="n">
-        <v>-31853</v>
+        <v>-15288</v>
       </c>
       <c r="F90" t="n">
-        <v>-51</v>
+        <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>364</v>
+        <v>-230</v>
       </c>
       <c r="H90" t="n">
-        <v>74</v>
+        <v>393</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4980,11 +4980,11 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M90" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -4999,22 +4999,22 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>743</v>
+        <v>434</v>
       </c>
       <c r="D91" t="n">
-        <v>-6223</v>
+        <v>-5444</v>
       </c>
       <c r="E91" t="n">
-        <v>-16237</v>
+        <v>-16256</v>
       </c>
       <c r="F91" t="n">
-        <v>446</v>
+        <v>654</v>
       </c>
       <c r="G91" t="n">
-        <v>664</v>
+        <v>820</v>
       </c>
       <c r="H91" t="n">
-        <v>348</v>
+        <v>150</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -5041,31 +5041,31 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>12482</v>
+        <v>27225</v>
       </c>
       <c r="D92" t="n">
-        <v>-6466</v>
+        <v>-5628</v>
       </c>
       <c r="E92" t="n">
-        <v>51692</v>
+        <v>54208</v>
       </c>
       <c r="F92" t="n">
-        <v>5213</v>
+        <v>-19882</v>
       </c>
       <c r="G92" t="n">
-        <v>-4426</v>
+        <v>-52605</v>
       </c>
       <c r="H92" t="n">
-        <v>-3995</v>
+        <v>-3657</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -5078,45 +5078,45 @@
         </is>
       </c>
       <c r="K92" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M92" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-6264</v>
+        <v>-1241</v>
       </c>
       <c r="D93" t="n">
-        <v>-6807</v>
+        <v>-7254</v>
       </c>
       <c r="E93" t="n">
-        <v>-3282</v>
+        <v>-17879</v>
       </c>
       <c r="F93" t="n">
-        <v>2749</v>
+        <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>2674</v>
+        <v>-1</v>
       </c>
       <c r="H93" t="n">
-        <v>201</v>
+        <v>-56</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -5125,49 +5125,49 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K93" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M93" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-998</v>
+        <v>-228</v>
       </c>
       <c r="D94" t="n">
-        <v>-7384</v>
+        <v>-7692</v>
       </c>
       <c r="E94" t="n">
-        <v>-17350</v>
+        <v>-23488</v>
       </c>
       <c r="F94" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>-1</v>
+        <v>-100</v>
       </c>
       <c r="H94" t="n">
-        <v>-51</v>
+        <v>76</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -5176,49 +5176,49 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K94" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M94" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>2274</v>
+        <v>-7718</v>
       </c>
       <c r="D95" t="n">
-        <v>-8761</v>
+        <v>-7985</v>
       </c>
       <c r="E95" t="n">
-        <v>-42554</v>
+        <v>-3892</v>
       </c>
       <c r="F95" t="n">
-        <v>5820</v>
+        <v>2429</v>
       </c>
       <c r="G95" t="n">
-        <v>-2248</v>
+        <v>1622</v>
       </c>
       <c r="H95" t="n">
-        <v>1377</v>
+        <v>178</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -5227,15 +5227,15 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K95" t="n">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M95" t="n">
@@ -5245,31 +5245,31 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-221</v>
+        <v>2979</v>
       </c>
       <c r="D96" t="n">
-        <v>-8827</v>
+        <v>-9506</v>
       </c>
       <c r="E96" t="n">
-        <v>-23091</v>
+        <v>-42693</v>
       </c>
       <c r="F96" t="n">
-        <v>-100</v>
+        <v>5479</v>
       </c>
       <c r="G96" t="n">
-        <v>-100</v>
+        <v>-331</v>
       </c>
       <c r="H96" t="n">
-        <v>-43</v>
+        <v>1200</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -5278,11 +5278,11 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K96" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -5290,88 +5290,88 @@
         </is>
       </c>
       <c r="M96" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>3000</v>
+        <v>1194</v>
       </c>
       <c r="D97" t="n">
-        <v>-8901</v>
+        <v>-11069</v>
       </c>
       <c r="E97" t="n">
-        <v>-79090</v>
+        <v>-11762</v>
       </c>
       <c r="F97" t="n">
-        <v>2344</v>
+        <v>-3918</v>
       </c>
       <c r="G97" t="n">
-        <v>-16872</v>
+        <v>-6405</v>
       </c>
       <c r="H97" t="n">
-        <v>4035</v>
+        <v>-1096</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🔴 大賣</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K97" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M97" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-1883</v>
+        <v>-1004</v>
       </c>
       <c r="D98" t="n">
-        <v>-11838</v>
+        <v>-12860</v>
       </c>
       <c r="E98" t="n">
-        <v>-12070</v>
+        <v>8674</v>
       </c>
       <c r="F98" t="n">
-        <v>-3005</v>
+        <v>210</v>
       </c>
       <c r="G98" t="n">
-        <v>-5395</v>
+        <v>972</v>
       </c>
       <c r="H98" t="n">
-        <v>-1025</v>
+        <v>219</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5384,45 +5384,45 @@
         </is>
       </c>
       <c r="K98" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M98" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>寶雅*</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-10704</v>
+        <v>-7305</v>
       </c>
       <c r="D99" t="n">
-        <v>-12891</v>
+        <v>-13568</v>
       </c>
       <c r="E99" t="n">
-        <v>-14369</v>
+        <v>-70496</v>
       </c>
       <c r="F99" t="n">
-        <v>8425</v>
+        <v>1592</v>
       </c>
       <c r="G99" t="n">
-        <v>7659</v>
+        <v>1515</v>
       </c>
       <c r="H99" t="n">
-        <v>46</v>
+        <v>-239</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5431,88 +5431,100 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K99" t="n">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>🚀 加速器*</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M99" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-7744</v>
+        <v>-11123</v>
       </c>
       <c r="D100" t="n">
-        <v>-13698</v>
+        <v>-14129</v>
       </c>
       <c r="E100" t="n">
-        <v>-16999</v>
+        <v>-14902</v>
       </c>
       <c r="F100" t="n">
-        <v>683</v>
+        <v>8526</v>
       </c>
       <c r="G100" t="n">
-        <v>2690</v>
+        <v>7587</v>
       </c>
       <c r="H100" t="n">
-        <v>671</v>
+        <v>87</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
           <t>🔴 大賣</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>66</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>🚀 加速器*</t>
+        </is>
+      </c>
+      <c r="M100" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-5161</v>
+        <v>4191</v>
       </c>
       <c r="D101" t="n">
-        <v>-14163</v>
+        <v>-14157</v>
       </c>
       <c r="E101" t="n">
-        <v>85883</v>
+        <v>-84297</v>
       </c>
       <c r="F101" t="n">
-        <v>-818</v>
+        <v>1331</v>
       </c>
       <c r="G101" t="n">
-        <v>1271</v>
+        <v>-14332</v>
       </c>
       <c r="H101" t="n">
-        <v>-238</v>
+        <v>3728</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5521,100 +5533,88 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K101" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-6844</v>
+        <v>-7949</v>
       </c>
       <c r="D102" t="n">
-        <v>-14378</v>
+        <v>-14283</v>
       </c>
       <c r="E102" t="n">
-        <v>-70170</v>
+        <v>-17553</v>
       </c>
       <c r="F102" t="n">
-        <v>2295</v>
+        <v>1457</v>
       </c>
       <c r="G102" t="n">
-        <v>1446</v>
+        <v>3196</v>
       </c>
       <c r="H102" t="n">
-        <v>-248</v>
+        <v>545</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
           <t>🔴 大賣</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K102" t="n">
-        <v>92</v>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>🛬 穩定</t>
-        </is>
-      </c>
-      <c r="M102" t="n">
-        <v>-3</v>
-      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-705</v>
+        <v>-6953</v>
       </c>
       <c r="D103" t="n">
-        <v>-14883</v>
+        <v>-24704</v>
       </c>
       <c r="E103" t="n">
-        <v>9058</v>
+        <v>82029</v>
       </c>
       <c r="F103" t="n">
-        <v>304</v>
+        <v>-1546</v>
       </c>
       <c r="G103" t="n">
-        <v>976</v>
+        <v>1312</v>
       </c>
       <c r="H103" t="n">
-        <v>214</v>
+        <v>-206</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="K103" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="M103" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -5650,22 +5650,22 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-2520</v>
+        <v>-3203</v>
       </c>
       <c r="D104" t="n">
-        <v>-25053</v>
+        <v>-25112</v>
       </c>
       <c r="E104" t="n">
-        <v>49119</v>
+        <v>47157</v>
       </c>
       <c r="F104" t="n">
-        <v>-244</v>
+        <v>-786</v>
       </c>
       <c r="G104" t="n">
-        <v>4641</v>
+        <v>2925</v>
       </c>
       <c r="H104" t="n">
-        <v>-2181</v>
+        <v>-2846</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5701,22 +5701,22 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-32812</v>
+        <v>-27147</v>
       </c>
       <c r="D105" t="n">
-        <v>-109449</v>
+        <v>-116884</v>
       </c>
       <c r="E105" t="n">
-        <v>146463</v>
+        <v>142442</v>
       </c>
       <c r="F105" t="n">
-        <v>-2370</v>
+        <v>-7233</v>
       </c>
       <c r="G105" t="n">
-        <v>29629</v>
+        <v>26872</v>
       </c>
       <c r="H105" t="n">
-        <v>1161</v>
+        <v>1012</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -5794,58 +5794,58 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 313 千股)</t>
+          <t>📈 20d 巨變(加碼 153 千股)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1359948</v>
+        <v>-468514</v>
       </c>
       <c r="D2" t="n">
-        <v>897264</v>
+        <v>-3106913</v>
       </c>
       <c r="E2" t="n">
-        <v>851763</v>
+        <v>-601814</v>
       </c>
       <c r="F2" t="n">
-        <v>584712</v>
+        <v>-3259604</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>亞翔</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -419 千股)</t>
+          <t>📈 20d 巨變(加碼 643 千股)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>58583</v>
+        <v>-529108</v>
       </c>
       <c r="D3" t="n">
-        <v>443937</v>
+        <v>727667</v>
       </c>
       <c r="E3" t="n">
-        <v>209557</v>
+        <v>-750072</v>
       </c>
       <c r="F3" t="n">
-        <v>863187</v>
+        <v>84978</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>奇鋐</t>
         </is>
       </c>
     </row>
@@ -5857,20 +5857,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 81 千股)</t>
+          <t>📉 20d 巨變(減碼 -135 千股)</t>
         </is>
       </c>
       <c r="C4" t="n">
+        <v>255444</v>
+      </c>
+      <c r="D4" t="n">
+        <v>559575</v>
+      </c>
+      <c r="E4" t="n">
         <v>318688</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>694714</v>
-      </c>
-      <c r="E4" t="n">
-        <v>18185</v>
-      </c>
-      <c r="F4" t="n">
-        <v>614051</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -5881,116 +5881,116 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 867 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 353 千股)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>743155</v>
+        <v>-73880</v>
       </c>
       <c r="D5" t="n">
-        <v>-6222989</v>
+        <v>797206</v>
       </c>
       <c r="E5" t="n">
-        <v>1116580</v>
+        <v>58583</v>
       </c>
       <c r="F5" t="n">
-        <v>-7090103</v>
+        <v>443937</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>健策</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -306 千股)</t>
+          <t>📈 20d 巨變(加碼 779 千股)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-750072</v>
+        <v>433621</v>
       </c>
       <c r="D6" t="n">
-        <v>84978</v>
+        <v>-5443885</v>
       </c>
       <c r="E6" t="n">
-        <v>-32233</v>
+        <v>743155</v>
       </c>
       <c r="F6" t="n">
-        <v>390623</v>
+        <v>-6222989</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -94 千股)</t>
+          <t>📉 20d 巨變(減碼 -240 千股)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-601814</v>
+        <v>1104270</v>
       </c>
       <c r="D7" t="n">
-        <v>-3259604</v>
+        <v>657310</v>
       </c>
       <c r="E7" t="n">
-        <v>669536</v>
+        <v>1359948</v>
       </c>
       <c r="F7" t="n">
-        <v>-3165856</v>
+        <v>897264</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>台光電</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,003 千股)</t>
+          <t>📈 20d 巨變(加碼 1,919 千股)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>382368</v>
+        <v>16316905</v>
       </c>
       <c r="D8" t="n">
-        <v>846530</v>
+        <v>-1321263</v>
       </c>
       <c r="E8" t="n">
-        <v>322273</v>
+        <v>449162</v>
       </c>
       <c r="F8" t="n">
-        <v>1849367</v>
+        <v>-3240294</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
@@ -6002,20 +6002,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -163 千股)</t>
+          <t>📈 20d 巨變(加碼 293 千股)</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>-289923</v>
+      </c>
+      <c r="D9" t="n">
+        <v>445530</v>
+      </c>
+      <c r="E9" t="n">
         <v>-247304</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>152737</v>
-      </c>
-      <c r="E9" t="n">
-        <v>305231</v>
-      </c>
-      <c r="F9" t="n">
-        <v>315853</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -6026,116 +6026,116 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 632 千股)</t>
+          <t>📈 20d 巨變(加碼 490 千股)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>529626</v>
+        <v>-95588</v>
       </c>
       <c r="D10" t="n">
-        <v>589461</v>
+        <v>7385846</v>
       </c>
       <c r="E10" t="n">
-        <v>-166265</v>
+        <v>-1304926</v>
       </c>
       <c r="F10" t="n">
-        <v>-42251</v>
+        <v>6896264</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>雙鴻</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -833 千股)</t>
+          <t>📉 20d 巨變(減碼 -921 千股)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-1304926</v>
+        <v>-337159</v>
       </c>
       <c r="D11" t="n">
-        <v>6896264</v>
+        <v>-2021120</v>
       </c>
       <c r="E11" t="n">
-        <v>-1083126</v>
+        <v>-608</v>
       </c>
       <c r="F11" t="n">
-        <v>7729620</v>
+        <v>-1100592</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>智邦</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -16 千股)</t>
+          <t>📈 20d 巨變(加碼 560 千股)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-608</v>
+        <v>801689</v>
       </c>
       <c r="D12" t="n">
-        <v>-1100592</v>
+        <v>1149094</v>
       </c>
       <c r="E12" t="n">
-        <v>-387547</v>
+        <v>529626</v>
       </c>
       <c r="F12" t="n">
-        <v>-1084320</v>
+        <v>589461</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>旺矽</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -3,178 千股)</t>
+          <t>📈 20d 巨變(加碼 437 千股)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>449162</v>
+        <v>736713</v>
       </c>
       <c r="D13" t="n">
-        <v>-3240294</v>
+        <v>1283710</v>
       </c>
       <c r="E13" t="n">
-        <v>551906</v>
+        <v>382368</v>
       </c>
       <c r="F13" t="n">
-        <v>-61917</v>
+        <v>846530</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>致茂</t>
         </is>
       </c>
     </row>
@@ -6147,20 +6147,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 552 千股)</t>
+          <t>📉 20d 巨變(減碼 -745 千股)</t>
         </is>
       </c>
       <c r="C14" t="n">
+        <v>2979169</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-9506146</v>
+      </c>
+      <c r="E14" t="n">
         <v>2273935</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>-8761282</v>
-      </c>
-      <c r="E14" t="n">
-        <v>5444224</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-9313210</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -6176,20 +6176,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 538 千股)</t>
+          <t>📉 20d 巨變(減碼 -31 千股)</t>
         </is>
       </c>
       <c r="C15" t="n">
+        <v>553834</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3144962</v>
+      </c>
+      <c r="E15" t="n">
         <v>193017</v>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>3175916</v>
-      </c>
-      <c r="E15" t="n">
-        <v>114814</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2637718</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -6200,87 +6200,87 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 27 千股)</t>
+          <t>📉 20d 巨變(減碼 -217 千股)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>151076</v>
+        <v>-238998</v>
       </c>
       <c r="D16" t="n">
-        <v>-957026</v>
+        <v>-1282699</v>
       </c>
       <c r="E16" t="n">
-        <v>52840</v>
+        <v>-26981</v>
       </c>
       <c r="F16" t="n">
-        <v>-983777</v>
+        <v>-1065455</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>崇越</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 30 千股)</t>
+          <t>📉 20d 巨變(減碼 -83 千股)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>616713</v>
+        <v>1643862</v>
       </c>
       <c r="D17" t="n">
-        <v>-2344651</v>
+        <v>1240800</v>
       </c>
       <c r="E17" t="n">
-        <v>459195</v>
+        <v>916087</v>
       </c>
       <c r="F17" t="n">
-        <v>-2374565</v>
+        <v>1323860</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>健鼎</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 1,304 千股)</t>
+          <t>📈 20d 巨變(加碼 158 千股)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>916087</v>
+        <v>496352</v>
       </c>
       <c r="D18" t="n">
-        <v>1323860</v>
+        <v>-2186698</v>
       </c>
       <c r="E18" t="n">
-        <v>-1210981</v>
+        <v>616713</v>
       </c>
       <c r="F18" t="n">
-        <v>19886</v>
+        <v>-2344651</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>佳必琪</t>
         </is>
       </c>
     </row>
@@ -6292,20 +6292,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 14 千股)</t>
+          <t>📈 20d 巨變(加碼 17 千股)</t>
         </is>
       </c>
       <c r="C19" t="n">
+        <v>-376315</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-81511</v>
+      </c>
+      <c r="E19" t="n">
         <v>-500044</v>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>-98766</v>
-      </c>
-      <c r="E19" t="n">
-        <v>-472862</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-112765</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -6316,29 +6316,29 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 37 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -614 千股)</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-26981</v>
+        <v>-80535</v>
       </c>
       <c r="D20" t="n">
-        <v>-1065455</v>
+        <v>-1570983</v>
       </c>
       <c r="E20" t="n">
-        <v>-52014</v>
+        <v>151076</v>
       </c>
       <c r="F20" t="n">
-        <v>-1102295</v>
+        <v>-957026</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>辛耘</t>
         </is>
       </c>
     </row>
@@ -6350,20 +6350,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 126 千股)</t>
+          <t>📈 20d 巨變(加碼 183 千股)</t>
         </is>
       </c>
       <c r="C21" t="n">
+        <v>1416939</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5959965</v>
+      </c>
+      <c r="E21" t="n">
         <v>1276930</v>
       </c>
-      <c r="D21" t="n">
+      <c r="F21" t="n">
         <v>5776498</v>
-      </c>
-      <c r="E21" t="n">
-        <v>559356</v>
-      </c>
-      <c r="F21" t="n">
-        <v>5650898</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -6374,29 +6374,29 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -273 千股)</t>
+          <t>📉 20d 巨變(減碼 -47 千股)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-530029</v>
+        <v>126357</v>
       </c>
       <c r="D22" t="n">
-        <v>-2170846</v>
+        <v>386108</v>
       </c>
       <c r="E22" t="n">
-        <v>-903409</v>
+        <v>216131</v>
       </c>
       <c r="F22" t="n">
-        <v>-1898176</v>
+        <v>433380</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>華城</t>
         </is>
       </c>
     </row>
@@ -6408,20 +6408,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 247 千股)</t>
+          <t>📈 20d 巨變(加碼 232 千股)</t>
         </is>
       </c>
       <c r="C23" t="n">
+        <v>1126562</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3076704</v>
+      </c>
+      <c r="E23" t="n">
         <v>765131</v>
       </c>
-      <c r="D23" t="n">
+      <c r="F23" t="n">
         <v>2845163</v>
-      </c>
-      <c r="E23" t="n">
-        <v>465979</v>
-      </c>
-      <c r="F23" t="n">
-        <v>2598485</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -6432,58 +6432,58 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 147 千股)</t>
+          <t>📉 20d 巨變(減碼 -195 千股)</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>216131</v>
+        <v>-1844828</v>
       </c>
       <c r="D24" t="n">
-        <v>433380</v>
+        <v>-1612370</v>
       </c>
       <c r="E24" t="n">
-        <v>196607</v>
+        <v>-1551893</v>
       </c>
       <c r="F24" t="n">
-        <v>286045</v>
+        <v>-1416938</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>大立光</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -529 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,211 千股)</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-1551893</v>
+        <v>-510019</v>
       </c>
       <c r="D25" t="n">
-        <v>-1416938</v>
+        <v>-4381902</v>
       </c>
       <c r="E25" t="n">
-        <v>-670278</v>
+        <v>-530029</v>
       </c>
       <c r="F25" t="n">
-        <v>-887750</v>
+        <v>-2170846</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>建榮</t>
         </is>
       </c>
     </row>
@@ -6495,20 +6495,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -9 千股)</t>
+          <t>📉 20d 巨變(減碼 -7 千股)</t>
         </is>
       </c>
       <c r="C26" t="n">
+        <v>-49006</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-22326</v>
+      </c>
+      <c r="E26" t="n">
         <v>-36006</v>
       </c>
-      <c r="D26" t="n">
+      <c r="F26" t="n">
         <v>-15286</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-14006</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-6286</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -6519,783 +6519,783 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 980 千股)</t>
+          <t>📉 20d 巨變(減碼 -894 千股)</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1485770</v>
+        <v>1048634</v>
       </c>
       <c r="D27" t="n">
-        <v>310438</v>
+        <v>15569444</v>
       </c>
       <c r="E27" t="n">
-        <v>1274857</v>
+        <v>906409</v>
       </c>
       <c r="F27" t="n">
-        <v>-669262</v>
+        <v>16463522</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 51 千股)</t>
+          <t>📉 20d 巨變(減碼 -145 千股)</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-55036</v>
+        <v>31242</v>
       </c>
       <c r="D28" t="n">
-        <v>-467428</v>
+        <v>-634830</v>
       </c>
       <c r="E28" t="n">
-        <v>-55849</v>
+        <v>53687</v>
       </c>
       <c r="F28" t="n">
-        <v>-518241</v>
+        <v>-489862</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>隆大</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -26 千股)</t>
+          <t>📉 20d 巨變(減碼 -14 千股)</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-17083</v>
+        <v>2493009</v>
       </c>
       <c r="D29" t="n">
-        <v>-66885</v>
+        <v>296409</v>
       </c>
       <c r="E29" t="n">
-        <v>-19770</v>
+        <v>1485770</v>
       </c>
       <c r="F29" t="n">
-        <v>-40732</v>
+        <v>310438</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>零壹</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 160 千股)</t>
+          <t>📉 20d 巨變(減碼 -7 千股)</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>386138</v>
+        <v>-36083</v>
       </c>
       <c r="D30" t="n">
-        <v>1248444</v>
+        <v>-73785</v>
       </c>
       <c r="E30" t="n">
-        <v>192836</v>
+        <v>-17083</v>
       </c>
       <c r="F30" t="n">
-        <v>1088492</v>
+        <v>-66885</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>崇友</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -13 千股)</t>
+          <t>📉 20d 巨變(減碼 -23 千股)</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>53687</v>
+        <v>-41258</v>
       </c>
       <c r="D31" t="n">
-        <v>-489862</v>
+        <v>-490741</v>
       </c>
       <c r="E31" t="n">
-        <v>106037</v>
+        <v>-55036</v>
       </c>
       <c r="F31" t="n">
-        <v>-476862</v>
+        <v>-467428</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>湧德</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 829 千股)</t>
+          <t>📈 20d 巨變(加碼 75 千股)</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>906409</v>
+        <v>400000</v>
       </c>
       <c r="D32" t="n">
-        <v>16463522</v>
+        <v>1323793</v>
       </c>
       <c r="E32" t="n">
-        <v>332146</v>
+        <v>386138</v>
       </c>
       <c r="F32" t="n">
-        <v>15634923</v>
+        <v>1248444</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>合機</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 7,260 千股)</t>
+          <t>📈 20d 巨變(加碼 810 千股)</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-1955200</v>
+        <v>-7305075</v>
       </c>
       <c r="D33" t="n">
-        <v>8465438</v>
+        <v>-13568097</v>
       </c>
       <c r="E33" t="n">
-        <v>-14546783</v>
+        <v>-6843521</v>
       </c>
       <c r="F33" t="n">
-        <v>1205063</v>
+        <v>-14377743</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>寶雅*</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,181 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 2,509 千股)</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-1309233</v>
+        <v>12150162</v>
       </c>
       <c r="D34" t="n">
-        <v>-2427788</v>
+        <v>10974847</v>
       </c>
       <c r="E34" t="n">
-        <v>-887205</v>
+        <v>-1955200</v>
       </c>
       <c r="F34" t="n">
-        <v>-1246989</v>
+        <v>8465438</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -758 千股)</t>
+          <t>📉 20d 巨變(減碼 -336 千股)</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-6843521</v>
+        <v>-1488244</v>
       </c>
       <c r="D35" t="n">
-        <v>-14377743</v>
+        <v>-2763764</v>
       </c>
       <c r="E35" t="n">
-        <v>-4449229</v>
+        <v>-1309233</v>
       </c>
       <c r="F35" t="n">
-        <v>-13619466</v>
+        <v>-2427788</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>卜蜂</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 46 千股)</t>
+          <t>📈 20d 巨變(加碼 672 千股)</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>66854</v>
+        <v>1152883</v>
       </c>
       <c r="D36" t="n">
-        <v>129186</v>
+        <v>1257988</v>
       </c>
       <c r="E36" t="n">
-        <v>33175</v>
+        <v>656629</v>
       </c>
       <c r="F36" t="n">
-        <v>83522</v>
+        <v>585719</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>豐藝</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 90 千股)</t>
+          <t>📉 20d 巨變(減碼 -13 千股)</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>656629</v>
+        <v>76235</v>
       </c>
       <c r="D37" t="n">
-        <v>585719</v>
+        <v>116039</v>
       </c>
       <c r="E37" t="n">
-        <v>582134</v>
+        <v>66854</v>
       </c>
       <c r="F37" t="n">
-        <v>495692</v>
+        <v>129186</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>大統益</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 10 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 147 千股)</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-33026</v>
+        <v>34848</v>
       </c>
       <c r="D38" t="n">
-        <v>-422120</v>
+        <v>-182662</v>
       </c>
       <c r="E38" t="n">
-        <v>-19323</v>
+        <v>-10980</v>
       </c>
       <c r="F38" t="n">
-        <v>-432030</v>
+        <v>-329240</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>八方雲集</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 17 千股)</t>
+          <t>📉 20d 巨變(減碼 -15 千股)</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>71447</v>
+        <v>-3000</v>
       </c>
       <c r="D39" t="n">
-        <v>-161161</v>
+        <v>35000</v>
       </c>
       <c r="E39" t="n">
-        <v>49447</v>
+        <v>-1000</v>
       </c>
       <c r="F39" t="n">
-        <v>-178155</v>
+        <v>50000</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>方土霖</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 20 千股)</t>
+          <t>📈 20d 巨變(加碼 16 千股)</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-10980</v>
+        <v>-33026</v>
       </c>
       <c r="D40" t="n">
-        <v>-329240</v>
+        <v>-406120</v>
       </c>
       <c r="E40" t="n">
-        <v>-79980</v>
+        <v>-33026</v>
       </c>
       <c r="F40" t="n">
-        <v>-349090</v>
+        <v>-422120</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>智冠</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,581 千股)</t>
+          <t>📉 20d 巨變(減碼 -43 千股)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>8907643</v>
+        <v>58454</v>
       </c>
       <c r="D41" t="n">
-        <v>50779443</v>
+        <v>-203867</v>
       </c>
       <c r="E41" t="n">
-        <v>7464533</v>
+        <v>71447</v>
       </c>
       <c r="F41" t="n">
-        <v>52360867</v>
+        <v>-161161</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>華景電</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 26 千股)</t>
+          <t>📉 20d 巨變(減碼 -3,630 千股)</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-376558</v>
+        <v>7976018</v>
       </c>
       <c r="D42" t="n">
-        <v>-1183475</v>
+        <v>47149677</v>
       </c>
       <c r="E42" t="n">
-        <v>-465482</v>
+        <v>8907643</v>
       </c>
       <c r="F42" t="n">
-        <v>-1209574</v>
+        <v>50779443</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 199 千股)</t>
+          <t>📉 20d 巨變(減碼 -101 千股)</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>960416</v>
+        <v>-391260</v>
       </c>
       <c r="D43" t="n">
-        <v>55313</v>
+        <v>-1284074</v>
       </c>
       <c r="E43" t="n">
-        <v>773859</v>
+        <v>-376558</v>
       </c>
       <c r="F43" t="n">
-        <v>-144157</v>
+        <v>-1183475</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>穎崴</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,247 千股)</t>
+          <t>📉 20d 巨變(減碼 -89 千股)</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-1962156</v>
+        <v>1102129</v>
       </c>
       <c r="D44" t="n">
-        <v>-1679889</v>
+        <v>-33337</v>
       </c>
       <c r="E44" t="n">
-        <v>-1457167</v>
+        <v>960416</v>
       </c>
       <c r="F44" t="n">
-        <v>-432496</v>
+        <v>55313</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>亞力</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -79 千股)</t>
+          <t>📈 20d 巨變(加碼 64 千股)</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-190072</v>
+        <v>280647</v>
       </c>
       <c r="D45" t="n">
-        <v>-1317405</v>
+        <v>305332</v>
       </c>
       <c r="E45" t="n">
-        <v>-94072</v>
+        <v>142188</v>
       </c>
       <c r="F45" t="n">
-        <v>-1238405</v>
+        <v>241627</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>大綜</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 81 千股)</t>
+          <t>📉 20d 巨變(減碼 -284 千股)</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>142188</v>
+        <v>-1691852</v>
       </c>
       <c r="D46" t="n">
-        <v>241627</v>
+        <v>-1963623</v>
       </c>
       <c r="E46" t="n">
-        <v>-119554</v>
+        <v>-1962156</v>
       </c>
       <c r="F46" t="n">
-        <v>160312</v>
+        <v>-1679889</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 51 千股)</t>
+          <t>📉 20d 巨變(減碼 -331 千股)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>284986</v>
+        <v>-149072</v>
       </c>
       <c r="D47" t="n">
-        <v>276413</v>
+        <v>-1648405</v>
       </c>
       <c r="E47" t="n">
-        <v>277645</v>
+        <v>-190072</v>
       </c>
       <c r="F47" t="n">
-        <v>224995</v>
+        <v>-1317405</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>聯合</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,356 千股)</t>
+          <t>📈 20d 巨變(加碼 68 千股)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>4127406</v>
+        <v>316483</v>
       </c>
       <c r="D48" t="n">
-        <v>7444867</v>
+        <v>344594</v>
       </c>
       <c r="E48" t="n">
-        <v>4273427</v>
+        <v>284986</v>
       </c>
       <c r="F48" t="n">
-        <v>8800989</v>
+        <v>276413</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>漢科</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 99 千股)</t>
+          <t>📈 20d 巨變(加碼 1,558 千股)</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1696536</v>
+        <v>4209385</v>
       </c>
       <c r="D49" t="n">
-        <v>-611597</v>
+        <v>9002612</v>
       </c>
       <c r="E49" t="n">
-        <v>1372583</v>
+        <v>4127406</v>
       </c>
       <c r="F49" t="n">
-        <v>-710958</v>
+        <v>7444867</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>台燿</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 6,419 千股)</t>
+          <t>📈 20d 巨變(加碼 256 千股)</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2999995</v>
+        <v>2258443</v>
       </c>
       <c r="D50" t="n">
-        <v>-8900948</v>
+        <v>-355837</v>
       </c>
       <c r="E50" t="n">
-        <v>-5557918</v>
+        <v>1696536</v>
       </c>
       <c r="F50" t="n">
-        <v>-15320298</v>
+        <v>-611597</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>世芯-KY</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 5,773 千股)</t>
+          <t>📉 20d 巨變(減碼 -63 千股)</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-705430</v>
+        <v>-3650944</v>
       </c>
       <c r="D51" t="n">
-        <v>-14883040</v>
+        <v>-2820375</v>
       </c>
       <c r="E51" t="n">
-        <v>-1797139</v>
+        <v>-3706772</v>
       </c>
       <c r="F51" t="n">
-        <v>-20655865</v>
+        <v>-2757067</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>玉晶光</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,008 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -840 千股)</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-3706772</v>
+        <v>-48825</v>
       </c>
       <c r="D52" t="n">
-        <v>-2757067</v>
+        <v>3811875</v>
       </c>
       <c r="E52" t="n">
-        <v>-2298043</v>
+        <v>1320154</v>
       </c>
       <c r="F52" t="n">
-        <v>-1749169</v>
+        <v>4651731</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>立隆電</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -74 千股)</t>
+          <t>📈 20d 巨變(加碼 2,023 千股)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1320154</v>
+        <v>-1004107</v>
       </c>
       <c r="D53" t="n">
-        <v>4651731</v>
+        <v>-12860211</v>
       </c>
       <c r="E53" t="n">
-        <v>1933113</v>
+        <v>-705430</v>
       </c>
       <c r="F53" t="n">
-        <v>4726210</v>
+        <v>-14883040</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
@@ -7307,20 +7307,20 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -22,012 千股)</t>
+          <t>📈 20d 巨變(加碼 26,038 千股)</t>
         </is>
       </c>
       <c r="C54" t="n">
+        <v>35170358</v>
+      </c>
+      <c r="D54" t="n">
+        <v>19572477</v>
+      </c>
+      <c r="E54" t="n">
         <v>12482165</v>
       </c>
-      <c r="D54" t="n">
+      <c r="F54" t="n">
         <v>-6465908</v>
-      </c>
-      <c r="E54" t="n">
-        <v>28358558</v>
-      </c>
-      <c r="F54" t="n">
-        <v>15545992</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -7331,58 +7331,58 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 8,137 千股)</t>
+          <t>📉 20d 巨變(減碼 -5,256 千股)</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>25887340</v>
+        <v>4190684</v>
       </c>
       <c r="D55" t="n">
-        <v>44905786</v>
+        <v>-14156943</v>
       </c>
       <c r="E55" t="n">
-        <v>12310583</v>
+        <v>2999995</v>
       </c>
       <c r="F55" t="n">
-        <v>36768774</v>
+        <v>-8900948</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 640 千股)</t>
+          <t>📈 20d 巨變(加碼 3,069 千股)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1211758</v>
+        <v>27289613</v>
       </c>
       <c r="D56" t="n">
-        <v>2496827</v>
+        <v>47974306</v>
       </c>
       <c r="E56" t="n">
-        <v>699665</v>
+        <v>25887340</v>
       </c>
       <c r="F56" t="n">
-        <v>1856434</v>
+        <v>44905786</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
@@ -7394,20 +7394,20 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -233 千股)</t>
+          <t>📉 20d 巨變(減碼 -541 千股)</t>
         </is>
       </c>
       <c r="C57" t="n">
+        <v>-346607</v>
+      </c>
+      <c r="D57" t="n">
+        <v>-431004</v>
+      </c>
+      <c r="E57" t="n">
         <v>-504736</v>
       </c>
-      <c r="D57" t="n">
+      <c r="F57" t="n">
         <v>109739</v>
-      </c>
-      <c r="E57" t="n">
-        <v>-670277</v>
-      </c>
-      <c r="F57" t="n">
-        <v>342976</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -7418,145 +7418,145 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 27 千股)</t>
+          <t>📈 20d 巨變(加碼 118 千股)</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>392762</v>
+        <v>253964</v>
       </c>
       <c r="D58" t="n">
-        <v>78817</v>
+        <v>99577</v>
       </c>
       <c r="E58" t="n">
-        <v>165210</v>
+        <v>81914</v>
       </c>
       <c r="F58" t="n">
-        <v>51628</v>
+        <v>-18721</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>達欣工</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -20 千股)</t>
+          <t>📈 20d 巨變(加碼 1,231 千股)</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>57390</v>
+        <v>1469617</v>
       </c>
       <c r="D59" t="n">
-        <v>333938</v>
+        <v>3727896</v>
       </c>
       <c r="E59" t="n">
-        <v>60460</v>
+        <v>1211758</v>
       </c>
       <c r="F59" t="n">
-        <v>353842</v>
+        <v>2496827</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>鈊象</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 137 千股)</t>
+          <t>📉 20d 巨變(減碼 -683 千股)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>81914</v>
+        <v>547879</v>
       </c>
       <c r="D60" t="n">
-        <v>-18721</v>
+        <v>-604205</v>
       </c>
       <c r="E60" t="n">
-        <v>-40007</v>
+        <v>392762</v>
       </c>
       <c r="F60" t="n">
-        <v>-156117</v>
+        <v>78817</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>鉅祥</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -5 千股)</t>
+          <t>📉 20d 巨變(減碼 -29 千股)</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1154356</v>
+        <v>69359</v>
       </c>
       <c r="D61" t="n">
-        <v>1075182</v>
+        <v>304918</v>
       </c>
       <c r="E61" t="n">
-        <v>1133474</v>
+        <v>57390</v>
       </c>
       <c r="F61" t="n">
-        <v>1080622</v>
+        <v>333938</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>普萊德</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -208 千股)</t>
+          <t>📈 20d 巨變(加碼 2,092 千股)</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-160490</v>
+        <v>49659</v>
       </c>
       <c r="D62" t="n">
-        <v>-1847615</v>
+        <v>-331944</v>
       </c>
       <c r="E62" t="n">
-        <v>112959</v>
+        <v>471380</v>
       </c>
       <c r="F62" t="n">
-        <v>-1639888</v>
+        <v>-2423465</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>華星光</t>
         </is>
       </c>
     </row>
@@ -7568,20 +7568,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -237 千股)</t>
+          <t>📈 20d 巨變(加碼 23 千股)</t>
         </is>
       </c>
       <c r="C63" t="n">
+        <v>-1051618</v>
+      </c>
+      <c r="D63" t="n">
+        <v>-1722083</v>
+      </c>
+      <c r="E63" t="n">
         <v>-1183696</v>
       </c>
-      <c r="D63" t="n">
+      <c r="F63" t="n">
         <v>-1744641</v>
-      </c>
-      <c r="E63" t="n">
-        <v>-992971</v>
-      </c>
-      <c r="F63" t="n">
-        <v>-1507498</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -7592,116 +7592,116 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 361 千股)</t>
+          <t>📉 20d 巨變(減碼 -35 千股)</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>79765</v>
+        <v>-113800</v>
       </c>
       <c r="D64" t="n">
-        <v>-983742</v>
+        <v>-1882640</v>
       </c>
       <c r="E64" t="n">
-        <v>56765</v>
+        <v>-160490</v>
       </c>
       <c r="F64" t="n">
-        <v>-1344742</v>
+        <v>-1847615</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>勝一</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 121 千股)</t>
+          <t>📈 20d 巨變(加碼 155 千股)</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-10704384</v>
+        <v>79327</v>
       </c>
       <c r="D65" t="n">
-        <v>-12891228</v>
+        <v>-828279</v>
       </c>
       <c r="E65" t="n">
-        <v>-10338604</v>
+        <v>79765</v>
       </c>
       <c r="F65" t="n">
-        <v>-13012012</v>
+        <v>-983742</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>信立</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -897 千股)</t>
+          <t>📉 20d 巨變(減碼 -126 千股)</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>471380</v>
+        <v>640341</v>
       </c>
       <c r="D66" t="n">
-        <v>-2423465</v>
+        <v>949146</v>
       </c>
       <c r="E66" t="n">
-        <v>597453</v>
+        <v>1154356</v>
       </c>
       <c r="F66" t="n">
-        <v>-1526964</v>
+        <v>1075182</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>祥碩</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -3,434 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,238 千股)</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-4793575</v>
+        <v>-11122629</v>
       </c>
       <c r="D67" t="n">
-        <v>20272878</v>
+        <v>-14128811</v>
       </c>
       <c r="E67" t="n">
-        <v>-2226357</v>
+        <v>-10704384</v>
       </c>
       <c r="F67" t="n">
-        <v>23706646</v>
+        <v>-12891228</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
@@ -7713,20 +7713,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -3,628 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,179 千股)</t>
         </is>
       </c>
       <c r="C68" t="n">
+        <v>-7718362</v>
+      </c>
+      <c r="D68" t="n">
+        <v>-7985353</v>
+      </c>
+      <c r="E68" t="n">
         <v>-6264029</v>
       </c>
-      <c r="D68" t="n">
+      <c r="F68" t="n">
         <v>-6806679</v>
-      </c>
-      <c r="E68" t="n">
-        <v>-4887010</v>
-      </c>
-      <c r="F68" t="n">
-        <v>-3178758</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -7737,174 +7737,174 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,575 千股)</t>
+          <t>📈 20d 巨變(加碼 418 千股)</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>7073108</v>
+        <v>-2232416</v>
       </c>
       <c r="D69" t="n">
-        <v>6494847</v>
+        <v>-2181048</v>
       </c>
       <c r="E69" t="n">
-        <v>4990189</v>
+        <v>-3602726</v>
       </c>
       <c r="F69" t="n">
-        <v>4919837</v>
+        <v>-2598987</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>聯亞</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -20,964 千股)</t>
+          <t>📉 20d 巨變(減碼 -5,530 千股)</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-32812476</v>
+        <v>-7399669</v>
       </c>
       <c r="D70" t="n">
-        <v>-109448520</v>
+        <v>14742997</v>
       </c>
       <c r="E70" t="n">
-        <v>-3955531</v>
+        <v>-4793575</v>
       </c>
       <c r="F70" t="n">
-        <v>-88484636</v>
+        <v>20272878</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -463 千股)</t>
+          <t>📉 20d 巨變(減碼 -5 千股)</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-3602726</v>
+        <v>-1903465</v>
       </c>
       <c r="D71" t="n">
-        <v>-2598987</v>
+        <v>-3117865</v>
       </c>
       <c r="E71" t="n">
-        <v>-3033517</v>
+        <v>-1419346</v>
       </c>
       <c r="F71" t="n">
-        <v>-2135552</v>
+        <v>-3112504</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>宇瞻</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,109 千股)</t>
+          <t>📉 20d 巨變(減碼 -7,435 千股)</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-1419346</v>
+        <v>-27146875</v>
       </c>
       <c r="D72" t="n">
-        <v>-3112504</v>
+        <v>-116883701</v>
       </c>
       <c r="E72" t="n">
-        <v>-1500440</v>
+        <v>-32812476</v>
       </c>
       <c r="F72" t="n">
-        <v>-4221219</v>
+        <v>-109448520</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 878 千股)</t>
+          <t>📈 20d 巨變(加碼 949 千股)</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-2519724</v>
+        <v>7227888</v>
       </c>
       <c r="D73" t="n">
-        <v>-25052637</v>
+        <v>7444172</v>
       </c>
       <c r="E73" t="n">
-        <v>-5940683</v>
+        <v>7073108</v>
       </c>
       <c r="F73" t="n">
-        <v>-25930206</v>
+        <v>6494847</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 78 千股)</t>
+          <t>📉 20d 巨變(減碼 -59 千股)</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>18912</v>
+        <v>-3202892</v>
       </c>
       <c r="D74" t="n">
-        <v>-404344</v>
+        <v>-25111868</v>
       </c>
       <c r="E74" t="n">
-        <v>3804</v>
+        <v>-2519724</v>
       </c>
       <c r="F74" t="n">
-        <v>-482157</v>
+        <v>-25052637</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
@@ -7916,20 +7916,20 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -31 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -258 千股)</t>
         </is>
       </c>
       <c r="C75" t="n">
+        <v>-93213</v>
+      </c>
+      <c r="D75" t="n">
+        <v>-5000266</v>
+      </c>
+      <c r="E75" t="n">
         <v>754419</v>
       </c>
-      <c r="D75" t="n">
+      <c r="F75" t="n">
         <v>-4742299</v>
-      </c>
-      <c r="E75" t="n">
-        <v>791703</v>
-      </c>
-      <c r="F75" t="n">
-        <v>-4710884</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -7940,29 +7940,29 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 12 千股)</t>
+          <t>📉 20d 巨變(減碼 -27 千股)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>401310</v>
+        <v>20846</v>
       </c>
       <c r="D76" t="n">
-        <v>877379</v>
+        <v>-431360</v>
       </c>
       <c r="E76" t="n">
-        <v>364390</v>
+        <v>18912</v>
       </c>
       <c r="F76" t="n">
-        <v>864924</v>
+        <v>-404344</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>德昌</t>
         </is>
       </c>
     </row>
@@ -7974,20 +7974,20 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 46 千股)</t>
+          <t>📈 20d 巨變(加碼 11 千股)</t>
         </is>
       </c>
       <c r="C77" t="n">
+        <v>95929</v>
+      </c>
+      <c r="D77" t="n">
+        <v>28929</v>
+      </c>
+      <c r="E77" t="n">
         <v>106929</v>
       </c>
-      <c r="D77" t="n">
+      <c r="F77" t="n">
         <v>17929</v>
-      </c>
-      <c r="E77" t="n">
-        <v>76929</v>
-      </c>
-      <c r="F77" t="n">
-        <v>-28071</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -7998,58 +7998,58 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 261 千股)</t>
+          <t>📉 20d 巨變(減碼 -86 千股)</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-997915</v>
+        <v>429350</v>
       </c>
       <c r="D78" t="n">
-        <v>-7383519</v>
+        <v>791450</v>
       </c>
       <c r="E78" t="n">
-        <v>-990710</v>
+        <v>401310</v>
       </c>
       <c r="F78" t="n">
-        <v>-7644067</v>
+        <v>877379</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>億泰</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -109 千股)</t>
+          <t>📈 20d 巨變(加碼 129 千股)</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-778206</v>
+        <v>-1240915</v>
       </c>
       <c r="D79" t="n">
-        <v>-2877543</v>
+        <v>-7254082</v>
       </c>
       <c r="E79" t="n">
-        <v>-894468</v>
+        <v>-997915</v>
       </c>
       <c r="F79" t="n">
-        <v>-2768746</v>
+        <v>-7383519</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>智易</t>
         </is>
       </c>
     </row>
@@ -8061,20 +8061,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -667 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -601 千股)</t>
         </is>
       </c>
       <c r="C80" t="n">
+        <v>875028</v>
+      </c>
+      <c r="D80" t="n">
+        <v>-398855</v>
+      </c>
+      <c r="E80" t="n">
         <v>-226133</v>
       </c>
-      <c r="D80" t="n">
+      <c r="F80" t="n">
         <v>202059</v>
-      </c>
-      <c r="E80" t="n">
-        <v>-447289</v>
-      </c>
-      <c r="F80" t="n">
-        <v>869034</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -8090,20 +8090,20 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -265 千股)</t>
+          <t>📉 20d 巨變(減碼 -60 千股)</t>
         </is>
       </c>
       <c r="C81" t="n">
+        <v>-766312</v>
+      </c>
+      <c r="D81" t="n">
+        <v>-2218710</v>
+      </c>
+      <c r="E81" t="n">
         <v>-712133</v>
       </c>
-      <c r="D81" t="n">
+      <c r="F81" t="n">
         <v>-2159097</v>
-      </c>
-      <c r="E81" t="n">
-        <v>-276589</v>
-      </c>
-      <c r="F81" t="n">
-        <v>-1893791</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -8119,20 +8119,20 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 124 千股)</t>
+          <t>📉 20d 巨變(減碼 -10,542 千股)</t>
         </is>
       </c>
       <c r="C82" t="n">
+        <v>-6953167</v>
+      </c>
+      <c r="D82" t="n">
+        <v>-24704220</v>
+      </c>
+      <c r="E82" t="n">
         <v>-5160953</v>
       </c>
-      <c r="D82" t="n">
+      <c r="F82" t="n">
         <v>-14162537</v>
-      </c>
-      <c r="E82" t="n">
-        <v>-5120170</v>
-      </c>
-      <c r="F82" t="n">
-        <v>-14286055</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -8143,58 +8143,58 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 22,333 千股)</t>
+          <t>📉 20d 巨變(減碼 -230 千股)</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>1602170</v>
+        <v>-687251</v>
       </c>
       <c r="D83" t="n">
-        <v>22131664</v>
+        <v>-3107789</v>
       </c>
       <c r="E83" t="n">
-        <v>-7602548</v>
+        <v>-778206</v>
       </c>
       <c r="F83" t="n">
-        <v>-201381</v>
+        <v>-2877543</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>原相</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -53 千股)</t>
+          <t>📈 20d 巨變(加碼 7,932 千股)</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-42000</v>
+        <v>9151152</v>
       </c>
       <c r="D84" t="n">
-        <v>82009</v>
+        <v>30063426</v>
       </c>
       <c r="E84" t="n">
-        <v>-64000</v>
+        <v>1602170</v>
       </c>
       <c r="F84" t="n">
-        <v>135009</v>
+        <v>22131664</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
@@ -8206,20 +8206,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -297 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -292 千股)</t>
         </is>
       </c>
       <c r="C85" t="n">
+        <v>-139616</v>
+      </c>
+      <c r="D85" t="n">
+        <v>-1528106</v>
+      </c>
+      <c r="E85" t="n">
         <v>146096</v>
       </c>
-      <c r="D85" t="n">
+      <c r="F85" t="n">
         <v>-1236292</v>
-      </c>
-      <c r="E85" t="n">
-        <v>108179</v>
-      </c>
-      <c r="F85" t="n">
-        <v>-939220</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -8230,29 +8230,29 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -30 千股)</t>
+          <t>📉 20d 巨變(減碼 -82 千股)</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>141640</v>
+        <v>-105000</v>
       </c>
       <c r="D86" t="n">
-        <v>700184</v>
+        <v>9</v>
       </c>
       <c r="E86" t="n">
-        <v>138201</v>
+        <v>-42000</v>
       </c>
       <c r="F86" t="n">
-        <v>729745</v>
+        <v>82009</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
     </row>
@@ -8264,20 +8264,20 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 667 千股)</t>
+          <t>📈 20d 巨變(加碼 1,135 千股)</t>
         </is>
       </c>
       <c r="C87" t="n">
+        <v>-228481</v>
+      </c>
+      <c r="D87" t="n">
+        <v>-7692023</v>
+      </c>
+      <c r="E87" t="n">
         <v>-220549</v>
       </c>
-      <c r="D87" t="n">
+      <c r="F87" t="n">
         <v>-8827191</v>
-      </c>
-      <c r="E87" t="n">
-        <v>-698227</v>
-      </c>
-      <c r="F87" t="n">
-        <v>-9494631</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -8293,20 +8293,20 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,438 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,984 千股)</t>
         </is>
       </c>
       <c r="C88" t="n">
+        <v>5582976</v>
+      </c>
+      <c r="D88" t="n">
+        <v>8183932</v>
+      </c>
+      <c r="E88" t="n">
         <v>10840094</v>
       </c>
-      <c r="D88" t="n">
+      <c r="F88" t="n">
         <v>10168356</v>
-      </c>
-      <c r="E88" t="n">
-        <v>7638318</v>
-      </c>
-      <c r="F88" t="n">
-        <v>8729983</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -8317,58 +8317,58 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,520 千股)</t>
+          <t>📈 20d 巨變(加碼 339 千股)</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>26808253</v>
+        <v>3179412</v>
       </c>
       <c r="D89" t="n">
-        <v>83075410</v>
+        <v>5622742</v>
       </c>
       <c r="E89" t="n">
-        <v>36242499</v>
+        <v>2905425</v>
       </c>
       <c r="F89" t="n">
-        <v>81555174</v>
+        <v>5283617</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>研華</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,011 千股)</t>
+          <t>📈 20d 巨變(加碼 5,616 千股)</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2905425</v>
+        <v>24582760</v>
       </c>
       <c r="D90" t="n">
-        <v>5283617</v>
+        <v>88691137</v>
       </c>
       <c r="E90" t="n">
-        <v>3250475</v>
+        <v>26808253</v>
       </c>
       <c r="F90" t="n">
-        <v>4272650</v>
+        <v>83075410</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
@@ -8380,20 +8380,20 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -298 千股)</t>
+          <t>📉 20d 巨變(減碼 -130 千股)</t>
         </is>
       </c>
       <c r="C91" t="n">
+        <v>263622</v>
+      </c>
+      <c r="D91" t="n">
+        <v>-600356</v>
+      </c>
+      <c r="E91" t="n">
         <v>176396</v>
       </c>
-      <c r="D91" t="n">
+      <c r="F91" t="n">
         <v>-470669</v>
-      </c>
-      <c r="E91" t="n">
-        <v>272296</v>
-      </c>
-      <c r="F91" t="n">
-        <v>-172416</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -8409,20 +8409,20 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 14 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 33 千股)</t>
         </is>
       </c>
       <c r="C92" t="n">
+        <v>4915</v>
+      </c>
+      <c r="D92" t="n">
+        <v>-119759</v>
+      </c>
+      <c r="E92" t="n">
         <v>-145902</v>
       </c>
-      <c r="D92" t="n">
+      <c r="F92" t="n">
         <v>-152759</v>
-      </c>
-      <c r="E92" t="n">
-        <v>-212378</v>
-      </c>
-      <c r="F92" t="n">
-        <v>-167173</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -8433,87 +8433,87 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -7 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -582 千股)</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>50745</v>
+        <v>-120195</v>
       </c>
       <c r="D93" t="n">
-        <v>53039</v>
+        <v>-5099458</v>
       </c>
       <c r="E93" t="n">
-        <v>-44328</v>
+        <v>311140</v>
       </c>
       <c r="F93" t="n">
-        <v>59974</v>
+        <v>-4517535</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 52 千股)</t>
+          <t>📈 20d 巨變(加碼 27 千股)</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>311140</v>
+        <v>72442</v>
       </c>
       <c r="D94" t="n">
-        <v>-4517535</v>
+        <v>80059</v>
       </c>
       <c r="E94" t="n">
-        <v>264303</v>
+        <v>50745</v>
       </c>
       <c r="F94" t="n">
-        <v>-4569412</v>
+        <v>53039</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>安碁資訊</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -3,962 千股)</t>
+          <t>📉 20d 巨變(減碼 -9 千股)</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>793066</v>
+        <v>57756</v>
       </c>
       <c r="D95" t="n">
-        <v>13267255</v>
+        <v>-25443</v>
       </c>
       <c r="E95" t="n">
-        <v>2187737</v>
+        <v>49646</v>
       </c>
       <c r="F95" t="n">
-        <v>17228760</v>
+        <v>-16553</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>六方科-KY</t>
         </is>
       </c>
     </row>
@@ -8525,20 +8525,20 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,127 千股)</t>
+          <t>📉 20d 巨變(減碼 -735 千股)</t>
         </is>
       </c>
       <c r="C96" t="n">
+        <v>8381759</v>
+      </c>
+      <c r="D96" t="n">
+        <v>12896722</v>
+      </c>
+      <c r="E96" t="n">
         <v>8882370</v>
       </c>
-      <c r="D96" t="n">
+      <c r="F96" t="n">
         <v>13632155</v>
-      </c>
-      <c r="E96" t="n">
-        <v>6340567</v>
-      </c>
-      <c r="F96" t="n">
-        <v>12505517</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -8549,145 +8549,145 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 40 千股)</t>
+          <t>📈 20d 巨變(加碼 873 千股)</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>49646</v>
+        <v>1132718</v>
       </c>
       <c r="D97" t="n">
-        <v>-16553</v>
+        <v>14140399</v>
       </c>
       <c r="E97" t="n">
-        <v>46091</v>
+        <v>793066</v>
       </c>
       <c r="F97" t="n">
-        <v>-56178</v>
+        <v>13267255</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -274 千股)</t>
+          <t>📉 20d 巨變(減碼 -4,112 千股)</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-748492</v>
+        <v>27224635</v>
       </c>
       <c r="D98" t="n">
-        <v>-872160</v>
+        <v>-5627928</v>
       </c>
       <c r="E98" t="n">
-        <v>-949042</v>
+        <v>35574502</v>
       </c>
       <c r="F98" t="n">
-        <v>-598424</v>
+        <v>-1515536</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 920 千股)</t>
+          <t>📈 20d 巨變(加碼 403 千股)</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-1882810</v>
+        <v>-281720</v>
       </c>
       <c r="D99" t="n">
-        <v>-11837678</v>
+        <v>-468980</v>
       </c>
       <c r="E99" t="n">
-        <v>-3602128</v>
+        <v>-748492</v>
       </c>
       <c r="F99" t="n">
-        <v>-12757670</v>
+        <v>-872160</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>創意</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 10,132 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 768 千股)</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>35574502</v>
+        <v>1194409</v>
       </c>
       <c r="D100" t="n">
-        <v>-1515536</v>
+        <v>-11069427</v>
       </c>
       <c r="E100" t="n">
-        <v>23695530</v>
+        <v>-1882810</v>
       </c>
       <c r="F100" t="n">
-        <v>-11647115</v>
+        <v>-11837678</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>緯穎</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 299 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 55 千股)</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>256716</v>
+        <v>39242</v>
       </c>
       <c r="D101" t="n">
-        <v>-2215619</v>
+        <v>115909</v>
       </c>
       <c r="E101" t="n">
-        <v>-349998</v>
+        <v>-10083</v>
       </c>
       <c r="F101" t="n">
-        <v>-2514433</v>
+        <v>60739</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>信驊</t>
         </is>
       </c>
     </row>
@@ -8699,20 +8699,20 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,125 千股)</t>
+          <t>📉 20d 巨變(減碼 -585 千股)</t>
         </is>
       </c>
       <c r="C102" t="n">
+        <v>-7948625</v>
+      </c>
+      <c r="D102" t="n">
+        <v>-14282925</v>
+      </c>
+      <c r="E102" t="n">
         <v>-7743511</v>
       </c>
-      <c r="D102" t="n">
+      <c r="F102" t="n">
         <v>-13697978</v>
-      </c>
-      <c r="E102" t="n">
-        <v>-5886883</v>
-      </c>
-      <c r="F102" t="n">
-        <v>-11573309</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -8723,29 +8723,29 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -62 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -820 千股)</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-10083</v>
+        <v>-116755</v>
       </c>
       <c r="D103" t="n">
-        <v>60739</v>
+        <v>-3035457</v>
       </c>
       <c r="E103" t="n">
-        <v>-34985</v>
+        <v>256716</v>
       </c>
       <c r="F103" t="n">
-        <v>122724</v>
+        <v>-2215619</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>高技</t>
         </is>
       </c>
     </row>
@@ -8757,20 +8757,20 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 32 千股)</t>
+          <t>📈 20d 巨變(加碼 772 千股)</t>
         </is>
       </c>
       <c r="C104" t="n">
+        <v>-410444</v>
+      </c>
+      <c r="D104" t="n">
+        <v>-575692</v>
+      </c>
+      <c r="E104" t="n">
         <v>-501867</v>
       </c>
-      <c r="D104" t="n">
+      <c r="F104" t="n">
         <v>-1347865</v>
-      </c>
-      <c r="E104" t="n">
-        <v>-608136</v>
-      </c>
-      <c r="F104" t="n">
-        <v>-1379810</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>

--- a/data/台股_外資雷達.xlsx
+++ b/data/台股_外資雷達.xlsx
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24583</v>
+        <v>17401</v>
       </c>
       <c r="D2" t="n">
-        <v>88691</v>
+        <v>91921</v>
       </c>
       <c r="E2" t="n">
-        <v>178402</v>
+        <v>181265</v>
       </c>
       <c r="F2" t="n">
-        <v>-366</v>
+        <v>276</v>
       </c>
       <c r="G2" t="n">
-        <v>143</v>
+        <v>25</v>
       </c>
       <c r="H2" t="n">
-        <v>281</v>
+        <v>52</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -547,22 +547,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27290</v>
+        <v>26733</v>
       </c>
       <c r="D3" t="n">
-        <v>47974</v>
+        <v>48073</v>
       </c>
       <c r="E3" t="n">
-        <v>18214</v>
+        <v>20120</v>
       </c>
       <c r="F3" t="n">
-        <v>-757</v>
+        <v>-3299</v>
       </c>
       <c r="G3" t="n">
-        <v>-10442</v>
+        <v>-11301</v>
       </c>
       <c r="H3" t="n">
-        <v>4206</v>
+        <v>4351</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7976</v>
+        <v>8648</v>
       </c>
       <c r="D4" t="n">
-        <v>47150</v>
+        <v>46352</v>
       </c>
       <c r="E4" t="n">
-        <v>202402</v>
+        <v>203837</v>
       </c>
       <c r="F4" t="n">
-        <v>2007</v>
+        <v>1723</v>
       </c>
       <c r="G4" t="n">
-        <v>5984</v>
+        <v>5800</v>
       </c>
       <c r="H4" t="n">
-        <v>-2149</v>
+        <v>-2092</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -640,31 +640,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>9151</v>
+        <v>8908</v>
       </c>
       <c r="D5" t="n">
-        <v>30063</v>
+        <v>13970</v>
       </c>
       <c r="E5" t="n">
-        <v>96756</v>
+        <v>15712</v>
       </c>
       <c r="F5" t="n">
-        <v>921</v>
+        <v>259</v>
       </c>
       <c r="G5" t="n">
-        <v>6475</v>
+        <v>2545</v>
       </c>
       <c r="H5" t="n">
-        <v>-1486</v>
+        <v>1871</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -673,49 +673,49 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>35170</v>
+        <v>592</v>
       </c>
       <c r="D6" t="n">
-        <v>19572</v>
+        <v>13023</v>
       </c>
       <c r="E6" t="n">
-        <v>80888</v>
+        <v>102099</v>
       </c>
       <c r="F6" t="n">
-        <v>4210</v>
+        <v>549</v>
       </c>
       <c r="G6" t="n">
-        <v>-5029</v>
+        <v>1189</v>
       </c>
       <c r="H6" t="n">
-        <v>-3153</v>
+        <v>62</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -724,11 +724,11 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="7">
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1049</v>
+        <v>1236</v>
       </c>
       <c r="D7" t="n">
-        <v>15569</v>
+        <v>10934</v>
       </c>
       <c r="E7" t="n">
-        <v>23807</v>
+        <v>24177</v>
       </c>
       <c r="F7" t="n">
-        <v>-87</v>
+        <v>-165</v>
       </c>
       <c r="G7" t="n">
-        <v>-33</v>
+        <v>-112</v>
       </c>
       <c r="H7" t="n">
-        <v>-60</v>
+        <v>-80</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -793,31 +793,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-7400</v>
+        <v>2394</v>
       </c>
       <c r="D8" t="n">
-        <v>14743</v>
+        <v>10296</v>
       </c>
       <c r="E8" t="n">
-        <v>-9858</v>
+        <v>3135</v>
       </c>
       <c r="F8" t="n">
-        <v>12097</v>
+        <v>-4665</v>
       </c>
       <c r="G8" t="n">
-        <v>22844</v>
+        <v>-19890</v>
       </c>
       <c r="H8" t="n">
-        <v>1786</v>
+        <v>1102</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -838,41 +838,41 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1133</v>
+        <v>4462</v>
       </c>
       <c r="D9" t="n">
-        <v>14140</v>
+        <v>8728</v>
       </c>
       <c r="E9" t="n">
-        <v>102058</v>
+        <v>1763</v>
       </c>
       <c r="F9" t="n">
-        <v>732</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>1123</v>
+        <v>-6</v>
       </c>
       <c r="H9" t="n">
-        <v>-325</v>
+        <v>672</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>🚀 大買</t>
+          <t>🟢 加碼</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -889,54 +889,54 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8382</v>
+        <v>-15843</v>
       </c>
       <c r="D10" t="n">
-        <v>12897</v>
+        <v>7589</v>
       </c>
       <c r="E10" t="n">
-        <v>14885</v>
+        <v>-13511</v>
       </c>
       <c r="F10" t="n">
-        <v>585</v>
+        <v>9819</v>
       </c>
       <c r="G10" t="n">
-        <v>2819</v>
+        <v>23639</v>
       </c>
       <c r="H10" t="n">
-        <v>1656</v>
+        <v>1108</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>🚀 大買</t>
+          <t>🟢 加碼</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M10" t="n">
@@ -946,82 +946,82 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12150</v>
+        <v>4779</v>
       </c>
       <c r="D11" t="n">
-        <v>10975</v>
+        <v>6613</v>
       </c>
       <c r="E11" t="n">
-        <v>474866</v>
+        <v>648</v>
       </c>
       <c r="F11" t="n">
-        <v>24314</v>
+        <v>545</v>
       </c>
       <c r="G11" t="n">
-        <v>41759</v>
+        <v>2843</v>
       </c>
       <c r="H11" t="n">
-        <v>-1065</v>
+        <v>-49</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>🚀 大買</t>
+          <t>🟢 加碼</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4209</v>
+        <v>-22</v>
       </c>
       <c r="D12" t="n">
-        <v>9003</v>
+        <v>6596</v>
       </c>
       <c r="E12" t="n">
-        <v>3846</v>
+        <v>12260</v>
       </c>
       <c r="F12" t="n">
-        <v>-8958</v>
+        <v>906</v>
       </c>
       <c r="G12" t="n">
-        <v>-20601</v>
+        <v>1113</v>
       </c>
       <c r="H12" t="n">
-        <v>971</v>
+        <v>1059</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1030,49 +1030,49 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>研華</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5583</v>
+        <v>2439</v>
       </c>
       <c r="D13" t="n">
-        <v>8184</v>
+        <v>6461</v>
       </c>
       <c r="E13" t="n">
-        <v>1370</v>
+        <v>2904</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-456</v>
       </c>
       <c r="G13" t="n">
-        <v>-8</v>
+        <v>-436</v>
       </c>
       <c r="H13" t="n">
-        <v>644</v>
+        <v>103</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1081,49 +1081,49 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M13" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>鈊象</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7228</v>
+        <v>3559</v>
       </c>
       <c r="D14" t="n">
-        <v>7444</v>
+        <v>6435</v>
       </c>
       <c r="E14" t="n">
-        <v>1586</v>
+        <v>14559</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>421</v>
       </c>
       <c r="G14" t="n">
-        <v>2343</v>
+        <v>-6426</v>
       </c>
       <c r="H14" t="n">
-        <v>-74</v>
+        <v>43</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1132,49 +1132,49 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>立隆電</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-96</v>
+        <v>-344</v>
       </c>
       <c r="D15" t="n">
-        <v>7386</v>
+        <v>3889</v>
       </c>
       <c r="E15" t="n">
-        <v>12309</v>
+        <v>14567</v>
       </c>
       <c r="F15" t="n">
-        <v>574</v>
+        <v>-1324</v>
       </c>
       <c r="G15" t="n">
-        <v>780</v>
+        <v>-7244</v>
       </c>
       <c r="H15" t="n">
-        <v>964</v>
+        <v>-89</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1183,49 +1183,49 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1417</v>
+        <v>1268</v>
       </c>
       <c r="D16" t="n">
-        <v>5960</v>
+        <v>3616</v>
       </c>
       <c r="E16" t="n">
-        <v>25030</v>
+        <v>1913</v>
       </c>
       <c r="F16" t="n">
-        <v>1248</v>
+        <v>1028</v>
       </c>
       <c r="G16" t="n">
-        <v>886</v>
+        <v>1382</v>
       </c>
       <c r="H16" t="n">
-        <v>203</v>
+        <v>-225</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1242,41 +1242,41 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3179</v>
+        <v>810</v>
       </c>
       <c r="D17" t="n">
-        <v>5623</v>
+        <v>3414</v>
       </c>
       <c r="E17" t="n">
-        <v>2357</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="n">
-        <v>-422</v>
+        <v>-62</v>
       </c>
       <c r="G17" t="n">
-        <v>-410</v>
+        <v>-353</v>
       </c>
       <c r="H17" t="n">
-        <v>-92</v>
+        <v>138</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1285,11 +1285,11 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1297,37 +1297,37 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>中興電</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-49</v>
+        <v>1399</v>
       </c>
       <c r="D18" t="n">
-        <v>3812</v>
+        <v>3166</v>
       </c>
       <c r="E18" t="n">
-        <v>14549</v>
+        <v>25577</v>
       </c>
       <c r="F18" t="n">
-        <v>-1650</v>
+        <v>828</v>
       </c>
       <c r="G18" t="n">
-        <v>-7070</v>
+        <v>988</v>
       </c>
       <c r="H18" t="n">
-        <v>-15</v>
+        <v>-113</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1336,49 +1336,49 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>長榮航</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1470</v>
+        <v>-3703</v>
       </c>
       <c r="D19" t="n">
-        <v>3728</v>
+        <v>2199</v>
       </c>
       <c r="E19" t="n">
-        <v>11410</v>
+        <v>462961</v>
       </c>
       <c r="F19" t="n">
-        <v>621</v>
+        <v>25838</v>
       </c>
       <c r="G19" t="n">
-        <v>-7668</v>
+        <v>45617</v>
       </c>
       <c r="H19" t="n">
-        <v>-22</v>
+        <v>-622</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1387,15 +1387,15 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M19" t="n">
@@ -1405,35 +1405,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>554</v>
+        <v>1347</v>
       </c>
       <c r="D20" t="n">
-        <v>3145</v>
+        <v>1782</v>
       </c>
       <c r="E20" t="n">
-        <v>6273</v>
+        <v>-2624</v>
       </c>
       <c r="F20" t="n">
-        <v>-61</v>
+        <v>-762</v>
       </c>
       <c r="G20" t="n">
-        <v>-357</v>
+        <v>481</v>
       </c>
       <c r="H20" t="n">
-        <v>133</v>
+        <v>277</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>🟢 加碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1442,11 +1442,11 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M20" t="n">
@@ -1456,82 +1456,82 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>6189</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1127</v>
+        <v>983</v>
       </c>
       <c r="D21" t="n">
-        <v>3077</v>
+        <v>1344</v>
       </c>
       <c r="E21" t="n">
-        <v>1241</v>
+        <v>3572</v>
       </c>
       <c r="F21" t="n">
-        <v>1275</v>
+        <v>-7</v>
       </c>
       <c r="G21" t="n">
-        <v>1446</v>
+        <v>-31</v>
       </c>
       <c r="H21" t="n">
-        <v>-189</v>
+        <v>-55</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>🟢 加碼</t>
+          <t>🟡 中性</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>400</v>
+        <v>-208</v>
       </c>
       <c r="D22" t="n">
-        <v>1324</v>
+        <v>1277</v>
       </c>
       <c r="E22" t="n">
-        <v>2939</v>
+        <v>4963</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>318</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>834</v>
       </c>
       <c r="H22" t="n">
-        <v>-11</v>
+        <v>17</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1544,45 +1544,45 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>-2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>737</v>
+        <v>2137</v>
       </c>
       <c r="D23" t="n">
-        <v>1284</v>
+        <v>1002</v>
       </c>
       <c r="E23" t="n">
-        <v>-3305</v>
+        <v>-9345</v>
       </c>
       <c r="F23" t="n">
-        <v>-553</v>
+        <v>58</v>
       </c>
       <c r="G23" t="n">
-        <v>450</v>
+        <v>1031</v>
       </c>
       <c r="H23" t="n">
-        <v>239</v>
+        <v>-291</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1603,37 +1603,37 @@
         </is>
       </c>
       <c r="M23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="D24" t="n">
-        <v>1258</v>
+        <v>918</v>
       </c>
       <c r="E24" t="n">
-        <v>3525</v>
+        <v>1539</v>
       </c>
       <c r="F24" t="n">
-        <v>-3</v>
+        <v>7</v>
       </c>
       <c r="G24" t="n">
-        <v>-34</v>
+        <v>-1937</v>
       </c>
       <c r="H24" t="n">
-        <v>-55</v>
+        <v>99</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1642,49 +1642,49 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M24" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1644</v>
+        <v>857</v>
       </c>
       <c r="D25" t="n">
-        <v>1241</v>
+        <v>900</v>
       </c>
       <c r="E25" t="n">
-        <v>-9274</v>
+        <v>-132</v>
       </c>
       <c r="F25" t="n">
-        <v>40</v>
+        <v>-2441</v>
       </c>
       <c r="G25" t="n">
-        <v>1036</v>
+        <v>-4413</v>
       </c>
       <c r="H25" t="n">
-        <v>-347</v>
+        <v>371</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1701,41 +1701,41 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>802</v>
+        <v>383</v>
       </c>
       <c r="D26" t="n">
-        <v>1149</v>
+        <v>815</v>
       </c>
       <c r="E26" t="n">
-        <v>-1002</v>
+        <v>2891</v>
       </c>
       <c r="F26" t="n">
-        <v>-1188</v>
+        <v>7</v>
       </c>
       <c r="G26" t="n">
-        <v>-2216</v>
+        <v>242</v>
       </c>
       <c r="H26" t="n">
-        <v>130</v>
+        <v>-88</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1744,49 +1744,49 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>640</v>
+        <v>290</v>
       </c>
       <c r="D27" t="n">
-        <v>949</v>
+        <v>746</v>
       </c>
       <c r="E27" t="n">
-        <v>2884</v>
+        <v>-1405</v>
       </c>
       <c r="F27" t="n">
-        <v>-3</v>
+        <v>-1274</v>
       </c>
       <c r="G27" t="n">
-        <v>232</v>
+        <v>-980</v>
       </c>
       <c r="H27" t="n">
-        <v>-80</v>
+        <v>24</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1795,49 +1795,49 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-74</v>
+        <v>203</v>
       </c>
       <c r="D28" t="n">
-        <v>797</v>
+        <v>725</v>
       </c>
       <c r="E28" t="n">
-        <v>-550</v>
+        <v>898</v>
       </c>
       <c r="F28" t="n">
-        <v>152</v>
+        <v>-800</v>
       </c>
       <c r="G28" t="n">
-        <v>113</v>
+        <v>-2763</v>
       </c>
       <c r="H28" t="n">
-        <v>-27</v>
+        <v>-20</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1854,41 +1854,41 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>429</v>
+        <v>890</v>
       </c>
       <c r="D29" t="n">
-        <v>791</v>
+        <v>704</v>
       </c>
       <c r="E29" t="n">
-        <v>1216</v>
+        <v>-1080</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>-1308</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-1556</v>
       </c>
       <c r="H29" t="n">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1897,49 +1897,49 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M29" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-529</v>
+        <v>203</v>
       </c>
       <c r="D30" t="n">
-        <v>728</v>
+        <v>674</v>
       </c>
       <c r="E30" t="n">
-        <v>4797</v>
+        <v>-113</v>
       </c>
       <c r="F30" t="n">
-        <v>318</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>1757</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>181</v>
+        <v>4</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1948,100 +1948,100 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>196</v>
+        <v>372</v>
       </c>
       <c r="D31" t="n">
-        <v>702</v>
+        <v>637</v>
       </c>
       <c r="E31" t="n">
-        <v>-131</v>
+        <v>-954</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-2943</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>-6325</v>
       </c>
       <c r="H31" t="n">
+        <v>28</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>🟡 中性</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>66</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>🚀 加速器</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
         <v>4</v>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K31" t="n">
-        <v>78</v>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M31" t="n">
-        <v>-3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>億泰</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1104</v>
+        <v>257</v>
       </c>
       <c r="D32" t="n">
-        <v>657</v>
+        <v>562</v>
       </c>
       <c r="E32" t="n">
-        <v>-159</v>
+        <v>1172</v>
       </c>
       <c r="F32" t="n">
-        <v>-2779</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-4324</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>387</v>
+        <v>6</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2050,49 +2050,49 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M32" t="n">
-        <v>5</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>255</v>
+        <v>2579</v>
       </c>
       <c r="D33" t="n">
-        <v>560</v>
+        <v>532</v>
       </c>
       <c r="E33" t="n">
-        <v>1000</v>
+        <v>7854</v>
       </c>
       <c r="F33" t="n">
-        <v>-837</v>
+        <v>-2</v>
       </c>
       <c r="G33" t="n">
-        <v>-2744</v>
+        <v>-15</v>
       </c>
       <c r="H33" t="n">
-        <v>-21</v>
+        <v>22</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2113,37 +2113,37 @@
         </is>
       </c>
       <c r="M33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>合機</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-290</v>
+        <v>252</v>
       </c>
       <c r="D34" t="n">
-        <v>446</v>
+        <v>466</v>
       </c>
       <c r="E34" t="n">
-        <v>-1553</v>
+        <v>2934</v>
       </c>
       <c r="F34" t="n">
-        <v>-1270</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>-976</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>18</v>
+        <v>-10</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2156,45 +2156,45 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>126</v>
+        <v>290</v>
       </c>
       <c r="D35" t="n">
         <v>386</v>
       </c>
       <c r="E35" t="n">
-        <v>-266</v>
+        <v>-1676</v>
       </c>
       <c r="F35" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>438</v>
+        <v>-1</v>
       </c>
       <c r="H35" t="n">
-        <v>101</v>
+        <v>-6</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2203,15 +2203,15 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M35" t="n">
@@ -2221,31 +2221,31 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>大綜</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>316</v>
+        <v>201</v>
       </c>
       <c r="D36" t="n">
-        <v>345</v>
+        <v>300</v>
       </c>
       <c r="E36" t="n">
-        <v>-1689</v>
+        <v>610</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-6</v>
+        <v>51</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2258,36 +2258,36 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>大綜</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>281</v>
+        <v>97</v>
       </c>
       <c r="D37" t="n">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="E37" t="n">
-        <v>648</v>
+        <v>1181</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2309,45 +2309,45 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>69</v>
+        <v>-452</v>
       </c>
       <c r="D38" t="n">
-        <v>305</v>
+        <v>221</v>
       </c>
       <c r="E38" t="n">
-        <v>1164</v>
+        <v>-888</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>426</v>
       </c>
       <c r="H38" t="n">
-        <v>6</v>
+        <v>-20</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2356,71 +2356,59 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2493</v>
+        <v>112</v>
       </c>
       <c r="D39" t="n">
-        <v>296</v>
+        <v>142</v>
       </c>
       <c r="E39" t="n">
-        <v>7357</v>
+        <v>-258</v>
       </c>
       <c r="F39" t="n">
-        <v>-2</v>
+        <v>-25</v>
       </c>
       <c r="G39" t="n">
-        <v>-17</v>
+        <v>259</v>
       </c>
       <c r="H39" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K39" t="n">
-        <v>97</v>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>🚀 加速器</t>
-        </is>
-      </c>
-      <c r="M39" t="n">
-        <v>2</v>
-      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2434,10 +2422,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="D40" t="n">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="E40" t="n">
         <v>788</v>
@@ -2449,7 +2437,7 @@
         <v>-28</v>
       </c>
       <c r="H40" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2476,70 +2464,82 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>安碁資訊</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D41" t="n">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="E41" t="n">
-        <v>-297</v>
+        <v>136</v>
       </c>
       <c r="F41" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>233</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>77</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>✈️ 高飛*</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>達欣工</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>254</v>
+        <v>79</v>
       </c>
       <c r="D42" t="n">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="E42" t="n">
-        <v>-113</v>
+        <v>-59</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>-277</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2552,36 +2552,36 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>4527</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>方土霖</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>72</v>
+        <v>-5</v>
       </c>
       <c r="D43" t="n">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="E43" t="n">
-        <v>157</v>
+        <v>48</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2590,7 +2590,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2599,49 +2599,49 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M43" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>方土霖</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-3</v>
+        <v>-143</v>
       </c>
       <c r="D44" t="n">
-        <v>35</v>
+        <v>-0</v>
       </c>
       <c r="E44" t="n">
-        <v>48</v>
+        <v>-765</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>-44</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>-508</v>
       </c>
       <c r="H44" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2654,36 +2654,36 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M44" t="n">
-        <v>-2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>大車隊</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>96</v>
+        <v>-38</v>
       </c>
       <c r="D45" t="n">
-        <v>29</v>
+        <v>-14</v>
       </c>
       <c r="E45" t="n">
-        <v>-53</v>
+        <v>-24</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2692,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2701,40 +2701,40 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M45" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>4569</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>六方科-KY</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-105</v>
+        <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>-28</v>
       </c>
       <c r="E46" t="n">
-        <v>646</v>
+        <v>6</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2743,7 +2743,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2760,41 +2760,41 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>達欣工</t>
         </is>
       </c>
       <c r="C47" t="n">
+        <v>154</v>
+      </c>
+      <c r="D47" t="n">
         <v>-49</v>
       </c>
-      <c r="D47" t="n">
-        <v>-22</v>
-      </c>
       <c r="E47" t="n">
-        <v>-34</v>
+        <v>-170</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>-277</v>
       </c>
       <c r="H47" t="n">
-        <v>-2</v>
+        <v>17</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2803,11 +2803,11 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2821,22 +2821,22 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>58</v>
+        <v>-44</v>
       </c>
       <c r="D48" t="n">
-        <v>-25</v>
+        <v>-62</v>
       </c>
       <c r="E48" t="n">
-        <v>7</v>
+        <v>664</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2854,49 +2854,49 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>亞力</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1102</v>
+        <v>-157</v>
       </c>
       <c r="D49" t="n">
-        <v>-33</v>
+        <v>-109</v>
       </c>
       <c r="E49" t="n">
-        <v>-4283</v>
+        <v>642</v>
       </c>
       <c r="F49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-70</v>
+        <v>1</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2909,45 +2909,45 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>八方雲集</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-36</v>
+        <v>32</v>
       </c>
       <c r="D50" t="n">
-        <v>-74</v>
+        <v>-134</v>
       </c>
       <c r="E50" t="n">
-        <v>654</v>
+        <v>1430</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="H50" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2960,11 +2960,11 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🐌 龜速*</t>
         </is>
       </c>
       <c r="M50" t="n">
@@ -2974,31 +2974,31 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-376</v>
+        <v>-16</v>
       </c>
       <c r="D51" t="n">
-        <v>-82</v>
+        <v>-167</v>
       </c>
       <c r="E51" t="n">
-        <v>-874</v>
+        <v>51</v>
       </c>
       <c r="F51" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>-514</v>
+        <v>50</v>
       </c>
       <c r="H51" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3007,49 +3007,49 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M51" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5</v>
+        <v>94</v>
       </c>
       <c r="D52" t="n">
-        <v>-120</v>
+        <v>-278</v>
       </c>
       <c r="E52" t="n">
-        <v>80</v>
+        <v>490</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G52" t="n">
-        <v>50</v>
+        <v>-41</v>
       </c>
       <c r="H52" t="n">
-        <v>41</v>
+        <v>-34</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3058,15 +3058,15 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M52" t="n">
@@ -3076,31 +3076,31 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>35</v>
+        <v>2539</v>
       </c>
       <c r="D53" t="n">
-        <v>-183</v>
+        <v>-288</v>
       </c>
       <c r="E53" t="n">
-        <v>1434</v>
+        <v>-1305</v>
       </c>
       <c r="F53" t="n">
-        <v>39</v>
+        <v>-2176</v>
       </c>
       <c r="G53" t="n">
-        <v>44</v>
+        <v>-2669</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>184</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3109,49 +3109,49 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>🐌 龜速*</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M53" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>智冠</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>58</v>
+        <v>-60</v>
       </c>
       <c r="D54" t="n">
-        <v>-204</v>
+        <v>-384</v>
       </c>
       <c r="E54" t="n">
-        <v>475</v>
+        <v>-851</v>
       </c>
       <c r="F54" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>-41</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-26</v>
+        <v>-3</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3164,45 +3164,45 @@
         </is>
       </c>
       <c r="K54" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M54" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>德昌</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="D55" t="n">
-        <v>-332</v>
+        <v>-409</v>
       </c>
       <c r="E55" t="n">
-        <v>-1261</v>
+        <v>-1279</v>
       </c>
       <c r="F55" t="n">
-        <v>-958</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>-1106</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>81</v>
+        <v>-3</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3215,45 +3215,45 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M55" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2258</v>
+        <v>246</v>
       </c>
       <c r="D56" t="n">
-        <v>-356</v>
+        <v>-442</v>
       </c>
       <c r="E56" t="n">
-        <v>-1174</v>
+        <v>1550</v>
       </c>
       <c r="F56" t="n">
-        <v>-2521</v>
+        <v>-247</v>
       </c>
       <c r="G56" t="n">
-        <v>-2653</v>
+        <v>785</v>
       </c>
       <c r="H56" t="n">
-        <v>142</v>
+        <v>-4</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3266,45 +3266,45 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>華城</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>875</v>
+        <v>-27</v>
       </c>
       <c r="D57" t="n">
-        <v>-399</v>
+        <v>-483</v>
       </c>
       <c r="E57" t="n">
-        <v>319</v>
+        <v>-403</v>
       </c>
       <c r="F57" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G57" t="n">
-        <v>-1968</v>
+        <v>437</v>
       </c>
       <c r="H57" t="n">
-        <v>-349</v>
+        <v>-147</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3313,49 +3313,49 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-33</v>
+        <v>98</v>
       </c>
       <c r="D58" t="n">
-        <v>-406</v>
+        <v>-802</v>
       </c>
       <c r="E58" t="n">
-        <v>-839</v>
+        <v>2401</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>-86</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>-260</v>
       </c>
       <c r="H58" t="n">
-        <v>-3</v>
+        <v>17</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3364,11 +3364,11 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -3382,31 +3382,31 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-347</v>
+        <v>-280</v>
       </c>
       <c r="D59" t="n">
-        <v>-431</v>
+        <v>-936</v>
       </c>
       <c r="E59" t="n">
-        <v>-1191</v>
+        <v>-1791</v>
       </c>
       <c r="F59" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>46</v>
+        <v>-26</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3415,15 +3415,15 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M59" t="n">
@@ -3433,31 +3433,31 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>1514</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>亞力</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>21</v>
+        <v>412</v>
       </c>
       <c r="D60" t="n">
-        <v>-431</v>
+        <v>-954</v>
       </c>
       <c r="E60" t="n">
-        <v>-1306</v>
+        <v>-4562</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="H60" t="n">
-        <v>-7</v>
+        <v>-121</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -3478,59 +3478,47 @@
         </is>
       </c>
       <c r="M60" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-282</v>
+        <v>52</v>
       </c>
       <c r="D61" t="n">
-        <v>-469</v>
+        <v>-969</v>
       </c>
       <c r="E61" t="n">
-        <v>1433</v>
+        <v>799</v>
       </c>
       <c r="F61" t="n">
-        <v>435</v>
+        <v>-864</v>
       </c>
       <c r="G61" t="n">
-        <v>1094</v>
+        <v>161</v>
       </c>
       <c r="H61" t="n">
-        <v>-113</v>
+        <v>-27</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K61" t="n">
-        <v>52</v>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>🛬 穩定</t>
-        </is>
-      </c>
-      <c r="M61" t="n">
-        <v>2</v>
-      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3544,13 +3532,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-41</v>
+        <v>25</v>
       </c>
       <c r="D62" t="n">
-        <v>-491</v>
+        <v>-1036</v>
       </c>
       <c r="E62" t="n">
-        <v>-2731</v>
+        <v>-2738</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -3559,7 +3547,7 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-45</v>
+        <v>-167</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -3586,70 +3574,82 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>6187</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-410</v>
+        <v>161</v>
       </c>
       <c r="D63" t="n">
-        <v>-576</v>
+        <v>-1106</v>
       </c>
       <c r="E63" t="n">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="F63" t="n">
-        <v>-608</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>789</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-19</v>
+        <v>-748</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
           <t>🟡 中性</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>75</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>🚀 加速器</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>264</v>
+        <v>622</v>
       </c>
       <c r="D64" t="n">
-        <v>-600</v>
+        <v>-1147</v>
       </c>
       <c r="E64" t="n">
-        <v>2437</v>
+        <v>-2748</v>
       </c>
       <c r="F64" t="n">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>-254</v>
+        <v>-225</v>
       </c>
       <c r="H64" t="n">
-        <v>18</v>
+        <v>1806</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="K64" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -3670,37 +3670,37 @@
         </is>
       </c>
       <c r="M64" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>548</v>
+        <v>-216</v>
       </c>
       <c r="D65" t="n">
-        <v>-604</v>
+        <v>-1255</v>
       </c>
       <c r="E65" t="n">
-        <v>-2952</v>
+        <v>-1525</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>-170</v>
       </c>
       <c r="G65" t="n">
-        <v>-235</v>
+        <v>-42</v>
       </c>
       <c r="H65" t="n">
-        <v>1937</v>
+        <v>-69</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -3709,49 +3709,49 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>士電</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>31</v>
+        <v>-462</v>
       </c>
       <c r="D66" t="n">
-        <v>-635</v>
+        <v>-1318</v>
       </c>
       <c r="E66" t="n">
-        <v>-1529</v>
+        <v>-1269</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="H66" t="n">
-        <v>-26</v>
+        <v>-187</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -3760,15 +3760,15 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M66" t="n">
@@ -3778,22 +3778,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>聯合</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>79</v>
+        <v>-169</v>
       </c>
       <c r="D67" t="n">
-        <v>-828</v>
+        <v>-1329</v>
       </c>
       <c r="E67" t="n">
-        <v>521</v>
+        <v>-1928</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -3802,7 +3802,7 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-817</v>
+        <v>3</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -3811,11 +3811,11 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3829,31 +3829,31 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-239</v>
+        <v>-430</v>
       </c>
       <c r="D68" t="n">
-        <v>-1283</v>
+        <v>-1615</v>
       </c>
       <c r="E68" t="n">
-        <v>-1484</v>
+        <v>339</v>
       </c>
       <c r="F68" t="n">
-        <v>-284</v>
+        <v>-848</v>
       </c>
       <c r="G68" t="n">
-        <v>-29</v>
+        <v>-68</v>
       </c>
       <c r="H68" t="n">
-        <v>-60</v>
+        <v>28</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3866,45 +3866,45 @@
         </is>
       </c>
       <c r="K68" t="n">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛*</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-391</v>
+        <v>-2026</v>
       </c>
       <c r="D69" t="n">
-        <v>-1284</v>
+        <v>-1663</v>
       </c>
       <c r="E69" t="n">
-        <v>455</v>
+        <v>-7935</v>
       </c>
       <c r="F69" t="n">
-        <v>-853</v>
+        <v>299</v>
       </c>
       <c r="G69" t="n">
-        <v>-219</v>
+        <v>-41</v>
       </c>
       <c r="H69" t="n">
-        <v>37</v>
+        <v>319</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3913,49 +3913,49 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M69" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>16317</v>
+        <v>-194</v>
       </c>
       <c r="D70" t="n">
-        <v>-1321</v>
+        <v>-1714</v>
       </c>
       <c r="E70" t="n">
-        <v>-104136</v>
+        <v>996</v>
       </c>
       <c r="F70" t="n">
-        <v>-395</v>
+        <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>-3752</v>
+        <v>-482</v>
       </c>
       <c r="H70" t="n">
-        <v>4928</v>
+        <v>-36</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -3976,37 +3976,37 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-140</v>
+        <v>-900</v>
       </c>
       <c r="D71" t="n">
-        <v>-1528</v>
+        <v>-1740</v>
       </c>
       <c r="E71" t="n">
-        <v>1585</v>
+        <v>-969</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="H71" t="n">
-        <v>-359</v>
+        <v>-30</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -4019,45 +4019,45 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M71" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-81</v>
+        <v>-412</v>
       </c>
       <c r="D72" t="n">
-        <v>-1571</v>
+        <v>-1878</v>
       </c>
       <c r="E72" t="n">
-        <v>1048</v>
+        <v>1553</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>-482</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-53</v>
+        <v>-382</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -4066,49 +4066,49 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M72" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-1845</v>
+        <v>-822</v>
       </c>
       <c r="D73" t="n">
-        <v>-1612</v>
+        <v>-1910</v>
       </c>
       <c r="E73" t="n">
-        <v>-7743</v>
+        <v>-7489</v>
       </c>
       <c r="F73" t="n">
-        <v>438</v>
+        <v>-2646</v>
       </c>
       <c r="G73" t="n">
-        <v>283</v>
+        <v>-9101</v>
       </c>
       <c r="H73" t="n">
-        <v>320</v>
+        <v>453</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4117,49 +4117,49 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M73" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>勝一</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-149</v>
+        <v>-397</v>
       </c>
       <c r="D74" t="n">
-        <v>-1648</v>
+        <v>-1987</v>
       </c>
       <c r="E74" t="n">
-        <v>-1900</v>
+        <v>-3689</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H74" t="n">
-        <v>3</v>
+        <v>-45</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4168,202 +4168,202 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-1052</v>
+        <v>465</v>
       </c>
       <c r="D75" t="n">
-        <v>-1722</v>
+        <v>-2038</v>
       </c>
       <c r="E75" t="n">
-        <v>-894</v>
+        <v>-2823</v>
       </c>
       <c r="F75" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>-22</v>
+        <v>-217</v>
       </c>
       <c r="H75" t="n">
-        <v>-20</v>
+        <v>-54</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>🟡 中性</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K75" t="n">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M75" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-114</v>
+        <v>-1325</v>
       </c>
       <c r="D76" t="n">
-        <v>-1883</v>
+        <v>-2139</v>
       </c>
       <c r="E76" t="n">
-        <v>-3630</v>
+        <v>-7781</v>
       </c>
       <c r="F76" t="n">
+        <v>436</v>
+      </c>
+      <c r="G76" t="n">
+        <v>-113</v>
+      </c>
+      <c r="H76" t="n">
+        <v>-461</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>🟠 減碼</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>70</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
         <v>2</v>
-      </c>
-      <c r="G76" t="n">
-        <v>1</v>
-      </c>
-      <c r="H76" t="n">
-        <v>-27</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>🟡 中性</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K76" t="n">
-        <v>71</v>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>📉 減速</t>
-        </is>
-      </c>
-      <c r="M76" t="n">
-        <v>-3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-1692</v>
+        <v>-45</v>
       </c>
       <c r="D77" t="n">
-        <v>-1964</v>
+        <v>-2147</v>
       </c>
       <c r="E77" t="n">
-        <v>7006</v>
+        <v>-16872</v>
       </c>
       <c r="F77" t="n">
-        <v>473</v>
+        <v>-748</v>
       </c>
       <c r="G77" t="n">
-        <v>-237</v>
+        <v>-2140</v>
       </c>
       <c r="H77" t="n">
-        <v>45</v>
+        <v>-536</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>🟡 中性</t>
+          <t>🟠 減碼</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K77" t="n">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M77" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-337</v>
+        <v>-662</v>
       </c>
       <c r="D78" t="n">
-        <v>-2021</v>
+        <v>-2192</v>
       </c>
       <c r="E78" t="n">
-        <v>-7484</v>
+        <v>-2694</v>
       </c>
       <c r="F78" t="n">
-        <v>-3371</v>
+        <v>-220</v>
       </c>
       <c r="G78" t="n">
-        <v>-8594</v>
+        <v>1260</v>
       </c>
       <c r="H78" t="n">
-        <v>394</v>
+        <v>60</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -4372,49 +4372,49 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K78" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-2232</v>
+        <v>-2526</v>
       </c>
       <c r="D79" t="n">
-        <v>-2181</v>
+        <v>-2762</v>
       </c>
       <c r="E79" t="n">
-        <v>-7979</v>
+        <v>6366</v>
       </c>
       <c r="F79" t="n">
-        <v>641</v>
+        <v>277</v>
       </c>
       <c r="G79" t="n">
-        <v>946</v>
+        <v>-151</v>
       </c>
       <c r="H79" t="n">
-        <v>-441</v>
+        <v>59</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -4423,11 +4423,11 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K79" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -4435,88 +4435,76 @@
         </is>
       </c>
       <c r="M79" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>496</v>
+        <v>120</v>
       </c>
       <c r="D80" t="n">
-        <v>-2187</v>
+        <v>-2902</v>
       </c>
       <c r="E80" t="n">
-        <v>-2983</v>
+        <v>-5288</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="G80" t="n">
-        <v>-217</v>
+        <v>-64</v>
       </c>
       <c r="H80" t="n">
-        <v>-47</v>
+        <v>-128</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
           <t>🟠 減碼</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K80" t="n">
-        <v>90</v>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>🚀 加速器</t>
-        </is>
-      </c>
-      <c r="M80" t="n">
-        <v>4</v>
-      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>卜蜂</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-766</v>
+        <v>-1788</v>
       </c>
       <c r="D81" t="n">
-        <v>-2219</v>
+        <v>-3096</v>
       </c>
       <c r="E81" t="n">
-        <v>-2720</v>
+        <v>-2124</v>
       </c>
       <c r="F81" t="n">
-        <v>-136</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>1453</v>
+        <v>425</v>
       </c>
       <c r="H81" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -4525,49 +4513,49 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K81" t="n">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-1488</v>
+        <v>-454</v>
       </c>
       <c r="D82" t="n">
-        <v>-2764</v>
+        <v>-3224</v>
       </c>
       <c r="E82" t="n">
-        <v>-1887</v>
+        <v>-220</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>-274</v>
       </c>
       <c r="G82" t="n">
-        <v>433</v>
+        <v>-997</v>
       </c>
       <c r="H82" t="n">
-        <v>20</v>
+        <v>-26</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -4576,19 +4564,19 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K82" t="n">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M82" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="83">
@@ -4603,22 +4591,22 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-3651</v>
+        <v>-2780</v>
       </c>
       <c r="D83" t="n">
-        <v>-2820</v>
+        <v>-3984</v>
       </c>
       <c r="E83" t="n">
-        <v>-3831</v>
+        <v>-3821</v>
       </c>
       <c r="F83" t="n">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="G83" t="n">
-        <v>8659</v>
+        <v>8597</v>
       </c>
       <c r="H83" t="n">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -4645,70 +4633,82 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>建榮</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-117</v>
+        <v>-206</v>
       </c>
       <c r="D84" t="n">
-        <v>-3035</v>
+        <v>-4288</v>
       </c>
       <c r="E84" t="n">
-        <v>-5147</v>
+        <v>-2598</v>
       </c>
       <c r="F84" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>-64</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>-47</v>
+        <v>86</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
           <t>🟠 減碼</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>93</v>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>🚀 加速器</t>
+        </is>
+      </c>
+      <c r="M84" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-469</v>
+        <v>205</v>
       </c>
       <c r="D85" t="n">
-        <v>-3107</v>
+        <v>-4295</v>
       </c>
       <c r="E85" t="n">
-        <v>-16971</v>
+        <v>-16587</v>
       </c>
       <c r="F85" t="n">
-        <v>-912</v>
+        <v>616</v>
       </c>
       <c r="G85" t="n">
-        <v>-2134</v>
+        <v>-0</v>
       </c>
       <c r="H85" t="n">
-        <v>-562</v>
+        <v>41</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -4721,45 +4721,45 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>✈️ 高飛</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M85" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-687</v>
+        <v>-1041</v>
       </c>
       <c r="D86" t="n">
-        <v>-3108</v>
+        <v>-4557</v>
       </c>
       <c r="E86" t="n">
-        <v>-139</v>
+        <v>-263</v>
       </c>
       <c r="F86" t="n">
-        <v>-203</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>-925</v>
+        <v>-281</v>
       </c>
       <c r="H86" t="n">
-        <v>-21</v>
+        <v>-221</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         </is>
       </c>
       <c r="K86" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4780,37 +4780,37 @@
         </is>
       </c>
       <c r="M86" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-1903</v>
+        <v>-244</v>
       </c>
       <c r="D87" t="n">
-        <v>-3118</v>
+        <v>-5163</v>
       </c>
       <c r="E87" t="n">
-        <v>-240</v>
+        <v>-31610</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="G87" t="n">
-        <v>-281</v>
+        <v>546</v>
       </c>
       <c r="H87" t="n">
-        <v>-144</v>
+        <v>72</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -4823,96 +4823,96 @@
         </is>
       </c>
       <c r="K87" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M87" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>長榮航太</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-510</v>
+        <v>-343</v>
       </c>
       <c r="D88" t="n">
-        <v>-4382</v>
+        <v>-5398</v>
       </c>
       <c r="E88" t="n">
-        <v>-2610</v>
+        <v>-15174</v>
       </c>
       <c r="F88" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G88" t="n">
+        <v>-292</v>
+      </c>
+      <c r="H88" t="n">
+        <v>-42</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>🟠 減碼</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>79</v>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>✈️ 高飛*</t>
+        </is>
+      </c>
+      <c r="M88" t="n">
         <v>0</v>
-      </c>
-      <c r="G88" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" t="n">
-        <v>64</v>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>🟠 減碼</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="K88" t="n">
-        <v>93</v>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>🚀 加速器</t>
-        </is>
-      </c>
-      <c r="M88" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-93</v>
+        <v>-1422</v>
       </c>
       <c r="D89" t="n">
-        <v>-5000</v>
+        <v>-7091</v>
       </c>
       <c r="E89" t="n">
-        <v>-31871</v>
+        <v>-18093</v>
       </c>
       <c r="F89" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>366</v>
+        <v>-1</v>
       </c>
       <c r="H89" t="n">
-        <v>56</v>
+        <v>-58</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="K89" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -4933,37 +4933,37 @@
         </is>
       </c>
       <c r="M89" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-120</v>
+        <v>-257</v>
       </c>
       <c r="D90" t="n">
-        <v>-5099</v>
+        <v>-8534</v>
       </c>
       <c r="E90" t="n">
-        <v>-15288</v>
+        <v>-23567</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>-230</v>
+        <v>-100</v>
       </c>
       <c r="H90" t="n">
-        <v>393</v>
+        <v>166</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -4972,49 +4972,49 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K90" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>✈️ 高飛*</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>434</v>
+        <v>-5345</v>
       </c>
       <c r="D91" t="n">
-        <v>-5444</v>
+        <v>-9147</v>
       </c>
       <c r="E91" t="n">
-        <v>-16256</v>
+        <v>-4688</v>
       </c>
       <c r="F91" t="n">
-        <v>654</v>
+        <v>1286</v>
       </c>
       <c r="G91" t="n">
-        <v>820</v>
+        <v>660</v>
       </c>
       <c r="H91" t="n">
-        <v>150</v>
+        <v>252</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -5023,206 +5023,206 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K91" t="n">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M91" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>27225</v>
+        <v>6855</v>
       </c>
       <c r="D92" t="n">
-        <v>-5628</v>
+        <v>-10490</v>
       </c>
       <c r="E92" t="n">
-        <v>54208</v>
+        <v>-108804</v>
       </c>
       <c r="F92" t="n">
-        <v>-19882</v>
+        <v>-1623</v>
       </c>
       <c r="G92" t="n">
-        <v>-52605</v>
+        <v>-4723</v>
       </c>
       <c r="H92" t="n">
-        <v>-3657</v>
+        <v>5013</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🔴 大賣</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K92" t="n">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>✈️ 高飛</t>
         </is>
       </c>
       <c r="M92" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-1241</v>
+        <v>3315</v>
       </c>
       <c r="D93" t="n">
-        <v>-7254</v>
+        <v>-10550</v>
       </c>
       <c r="E93" t="n">
-        <v>-17879</v>
+        <v>-43020</v>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>5645</v>
       </c>
       <c r="G93" t="n">
-        <v>-1</v>
+        <v>927</v>
       </c>
       <c r="H93" t="n">
-        <v>-56</v>
+        <v>1393</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🔴 大賣</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="K93" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🛬 穩定</t>
         </is>
       </c>
       <c r="M93" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-228</v>
+        <v>1175</v>
       </c>
       <c r="D94" t="n">
-        <v>-7692</v>
+        <v>-10720</v>
       </c>
       <c r="E94" t="n">
-        <v>-23488</v>
+        <v>-11716</v>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>-3873</v>
       </c>
       <c r="G94" t="n">
-        <v>-100</v>
+        <v>-6926</v>
       </c>
       <c r="H94" t="n">
-        <v>76</v>
+        <v>-1207</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🔴 大賣</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K94" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M94" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-7718</v>
+        <v>8376</v>
       </c>
       <c r="D95" t="n">
-        <v>-7985</v>
+        <v>-11185</v>
       </c>
       <c r="E95" t="n">
-        <v>-3892</v>
+        <v>-82164</v>
       </c>
       <c r="F95" t="n">
-        <v>2429</v>
+        <v>909</v>
       </c>
       <c r="G95" t="n">
-        <v>1622</v>
+        <v>-9275</v>
       </c>
       <c r="H95" t="n">
-        <v>178</v>
+        <v>3070</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🔴 大賣</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -5231,96 +5231,96 @@
         </is>
       </c>
       <c r="K95" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M95" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>2979</v>
+        <v>-23602</v>
       </c>
       <c r="D96" t="n">
-        <v>-9506</v>
+        <v>-12058</v>
       </c>
       <c r="E96" t="n">
-        <v>-42693</v>
+        <v>72883</v>
       </c>
       <c r="F96" t="n">
-        <v>5479</v>
+        <v>549</v>
       </c>
       <c r="G96" t="n">
-        <v>-331</v>
+        <v>6332</v>
       </c>
       <c r="H96" t="n">
-        <v>1200</v>
+        <v>-2058</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>🟠 減碼</t>
+          <t>🔴 大賣</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K96" t="n">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>🛬 穩定</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M96" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1194</v>
+        <v>-2168</v>
       </c>
       <c r="D97" t="n">
-        <v>-11069</v>
+        <v>-14666</v>
       </c>
       <c r="E97" t="n">
-        <v>-11762</v>
+        <v>6584</v>
       </c>
       <c r="F97" t="n">
-        <v>-3918</v>
+        <v>18</v>
       </c>
       <c r="G97" t="n">
-        <v>-6405</v>
+        <v>944</v>
       </c>
       <c r="H97" t="n">
-        <v>-1096</v>
+        <v>110</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -5333,45 +5333,45 @@
         </is>
       </c>
       <c r="K97" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>🚀 加速器</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-1004</v>
+        <v>-11014</v>
       </c>
       <c r="D98" t="n">
-        <v>-12860</v>
+        <v>-14690</v>
       </c>
       <c r="E98" t="n">
-        <v>8674</v>
+        <v>-15323</v>
       </c>
       <c r="F98" t="n">
-        <v>210</v>
+        <v>8508</v>
       </c>
       <c r="G98" t="n">
-        <v>972</v>
+        <v>7575</v>
       </c>
       <c r="H98" t="n">
-        <v>219</v>
+        <v>86</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -5384,15 +5384,15 @@
         </is>
       </c>
       <c r="K98" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器*</t>
         </is>
       </c>
       <c r="M98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -5407,22 +5407,22 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-7305</v>
+        <v>-7222</v>
       </c>
       <c r="D99" t="n">
-        <v>-13568</v>
+        <v>-15797</v>
       </c>
       <c r="E99" t="n">
-        <v>-70496</v>
+        <v>-74850</v>
       </c>
       <c r="F99" t="n">
-        <v>1592</v>
+        <v>1000</v>
       </c>
       <c r="G99" t="n">
-        <v>1515</v>
+        <v>1612</v>
       </c>
       <c r="H99" t="n">
-        <v>-239</v>
+        <v>-286</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -5449,82 +5449,70 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-11123</v>
+        <v>-6923</v>
       </c>
       <c r="D100" t="n">
-        <v>-14129</v>
+        <v>-16741</v>
       </c>
       <c r="E100" t="n">
-        <v>-14902</v>
+        <v>-20197</v>
       </c>
       <c r="F100" t="n">
-        <v>8526</v>
+        <v>2081</v>
       </c>
       <c r="G100" t="n">
-        <v>7587</v>
+        <v>4180</v>
       </c>
       <c r="H100" t="n">
-        <v>87</v>
+        <v>738</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
           <t>🔴 大賣</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="K100" t="n">
-        <v>66</v>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>🚀 加速器*</t>
-        </is>
-      </c>
-      <c r="M100" t="n">
-        <v>1</v>
-      </c>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>4191</v>
+        <v>-2962</v>
       </c>
       <c r="D101" t="n">
-        <v>-14157</v>
+        <v>-21607</v>
       </c>
       <c r="E101" t="n">
-        <v>-84297</v>
+        <v>47422</v>
       </c>
       <c r="F101" t="n">
-        <v>1331</v>
+        <v>-962</v>
       </c>
       <c r="G101" t="n">
-        <v>-14332</v>
+        <v>-259</v>
       </c>
       <c r="H101" t="n">
-        <v>3728</v>
+        <v>-2600</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -5537,84 +5525,96 @@
         </is>
       </c>
       <c r="K101" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M101" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-7949</v>
+        <v>-11141</v>
       </c>
       <c r="D102" t="n">
-        <v>-14283</v>
+        <v>-24136</v>
       </c>
       <c r="E102" t="n">
-        <v>-17553</v>
+        <v>77621</v>
       </c>
       <c r="F102" t="n">
-        <v>1457</v>
+        <v>-1541</v>
       </c>
       <c r="G102" t="n">
-        <v>3196</v>
+        <v>1460</v>
       </c>
       <c r="H102" t="n">
-        <v>545</v>
+        <v>83</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
           <t>🔴 大賣</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K102" t="n">
+        <v>68</v>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>🐌 龜速</t>
+        </is>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-6953</v>
+        <v>14909</v>
       </c>
       <c r="D103" t="n">
-        <v>-24704</v>
+        <v>-30514</v>
       </c>
       <c r="E103" t="n">
-        <v>82029</v>
+        <v>60936</v>
       </c>
       <c r="F103" t="n">
-        <v>-1546</v>
+        <v>1268</v>
       </c>
       <c r="G103" t="n">
-        <v>1312</v>
+        <v>-8128</v>
       </c>
       <c r="H103" t="n">
-        <v>-206</v>
+        <v>-5716</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -5623,11 +5623,11 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K103" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -5635,37 +5635,37 @@
         </is>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-3203</v>
+        <v>19646</v>
       </c>
       <c r="D104" t="n">
-        <v>-25112</v>
+        <v>-53584</v>
       </c>
       <c r="E104" t="n">
-        <v>47157</v>
+        <v>36384</v>
       </c>
       <c r="F104" t="n">
-        <v>-786</v>
+        <v>-19993</v>
       </c>
       <c r="G104" t="n">
-        <v>2925</v>
+        <v>-52472</v>
       </c>
       <c r="H104" t="n">
-        <v>-2846</v>
+        <v>-4377</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -5678,15 +5678,15 @@
         </is>
       </c>
       <c r="K104" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>📉 減速</t>
         </is>
       </c>
       <c r="M104" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="105">
@@ -5701,22 +5701,22 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-27147</v>
+        <v>-28100</v>
       </c>
       <c r="D105" t="n">
-        <v>-116884</v>
+        <v>-102323</v>
       </c>
       <c r="E105" t="n">
-        <v>142442</v>
+        <v>150315</v>
       </c>
       <c r="F105" t="n">
-        <v>-7233</v>
+        <v>-10188</v>
       </c>
       <c r="G105" t="n">
-        <v>26872</v>
+        <v>26010</v>
       </c>
       <c r="H105" t="n">
-        <v>1012</v>
+        <v>2039</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5794,348 +5794,348 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 153 千股)</t>
+          <t>📈 20d 巨變(加碼 243 千股)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-468514</v>
+        <v>856656</v>
       </c>
       <c r="D2" t="n">
-        <v>-3106913</v>
+        <v>900482</v>
       </c>
       <c r="E2" t="n">
-        <v>-601814</v>
+        <v>1104270</v>
       </c>
       <c r="F2" t="n">
-        <v>-3259604</v>
+        <v>657310</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>台光電</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 643 千股)</t>
+          <t>📈 20d 巨變(加碼 1,149 千股)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-529108</v>
+        <v>205305</v>
       </c>
       <c r="D3" t="n">
-        <v>727667</v>
+        <v>-4294919</v>
       </c>
       <c r="E3" t="n">
-        <v>-750072</v>
+        <v>433621</v>
       </c>
       <c r="F3" t="n">
-        <v>84978</v>
+        <v>-5443885</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>高力</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -135 千股)</t>
+          <t>📉 20d 巨變(減碼 -576 千股)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>255444</v>
+        <v>-451517</v>
       </c>
       <c r="D4" t="n">
-        <v>559575</v>
+        <v>221103</v>
       </c>
       <c r="E4" t="n">
-        <v>318688</v>
+        <v>-73880</v>
       </c>
       <c r="F4" t="n">
-        <v>694714</v>
+        <v>797206</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>健策</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📈 20d 巨變(加碼 353 千股)</t>
+          <t>📈 20d 巨變(加碼 550 千股)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-73880</v>
+        <v>-208489</v>
       </c>
       <c r="D5" t="n">
-        <v>797206</v>
+        <v>1277338</v>
       </c>
       <c r="E5" t="n">
-        <v>58583</v>
+        <v>-529108</v>
       </c>
       <c r="F5" t="n">
-        <v>443937</v>
+        <v>727667</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>奇鋐</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 779 千股)</t>
+          <t>📈 20d 巨變(加碼 960 千股)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>433621</v>
+        <v>-45118</v>
       </c>
       <c r="D6" t="n">
-        <v>-5443885</v>
+        <v>-2146666</v>
       </c>
       <c r="E6" t="n">
-        <v>743155</v>
+        <v>-468514</v>
       </c>
       <c r="F6" t="n">
-        <v>-6222989</v>
+        <v>-3106913</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>亞翔</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -240 千股)</t>
+          <t>📈 20d 巨變(加碼 166 千股)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1104270</v>
+        <v>202665</v>
       </c>
       <c r="D7" t="n">
-        <v>657310</v>
+        <v>725469</v>
       </c>
       <c r="E7" t="n">
-        <v>1359948</v>
+        <v>255444</v>
       </c>
       <c r="F7" t="n">
-        <v>897264</v>
+        <v>559575</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>勤誠</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,919 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 300 千股)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16316905</v>
+        <v>289755</v>
       </c>
       <c r="D8" t="n">
-        <v>-1321263</v>
+        <v>746015</v>
       </c>
       <c r="E8" t="n">
-        <v>449162</v>
+        <v>-289923</v>
       </c>
       <c r="F8" t="n">
-        <v>-3240294</v>
+        <v>445530</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>光聖</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 293 千股)</t>
+          <t>📈 20d 巨變(加碼 499 千股)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-289923</v>
+        <v>1347035</v>
       </c>
       <c r="D9" t="n">
-        <v>445530</v>
+        <v>1782349</v>
       </c>
       <c r="E9" t="n">
-        <v>-247304</v>
+        <v>736713</v>
       </c>
       <c r="F9" t="n">
-        <v>152737</v>
+        <v>1283710</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>致茂</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 490 千股)</t>
+          <t>📉 20d 巨變(減碼 -445 千股)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-95588</v>
+        <v>890115</v>
       </c>
       <c r="D10" t="n">
-        <v>7385846</v>
+        <v>704228</v>
       </c>
       <c r="E10" t="n">
-        <v>-1304926</v>
+        <v>801689</v>
       </c>
       <c r="F10" t="n">
-        <v>6896264</v>
+        <v>1149094</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>旺矽</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -921 千股)</t>
+          <t>📉 20d 巨變(減碼 -790 千股)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-337159</v>
+        <v>-22396</v>
       </c>
       <c r="D11" t="n">
-        <v>-2021120</v>
+        <v>6596116</v>
       </c>
       <c r="E11" t="n">
-        <v>-608</v>
+        <v>-95588</v>
       </c>
       <c r="F11" t="n">
-        <v>-1100592</v>
+        <v>7385846</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>雙鴻</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 560 千股)</t>
+          <t>📉 20d 巨變(減碼 -9,168 千股)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>801689</v>
+        <v>6854883</v>
       </c>
       <c r="D12" t="n">
-        <v>1149094</v>
+        <v>-10489690</v>
       </c>
       <c r="E12" t="n">
-        <v>529626</v>
+        <v>16316905</v>
       </c>
       <c r="F12" t="n">
-        <v>589461</v>
+        <v>-1321263</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>台積電</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2360</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 437 千股)</t>
+          <t>📈 20d 巨變(加碼 111 千股)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>736713</v>
+        <v>-822095</v>
       </c>
       <c r="D13" t="n">
-        <v>1283710</v>
+        <v>-1909927</v>
       </c>
       <c r="E13" t="n">
-        <v>382368</v>
+        <v>-337159</v>
       </c>
       <c r="F13" t="n">
-        <v>846530</v>
+        <v>-2021120</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>致茂</t>
+          <t>智邦</t>
         </is>
       </c>
     </row>
@@ -6147,20 +6147,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -745 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,043 千股)</t>
         </is>
       </c>
       <c r="C14" t="n">
+        <v>3314976</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-10549554</v>
+      </c>
+      <c r="E14" t="n">
         <v>2979169</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>-9506146</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2273935</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-8761282</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -6176,20 +6176,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -31 千股)</t>
+          <t>📈 20d 巨變(加碼 269 千股)</t>
         </is>
       </c>
       <c r="C15" t="n">
+        <v>810296</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3414062</v>
+      </c>
+      <c r="E15" t="n">
         <v>553834</v>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>3144962</v>
-      </c>
-      <c r="E15" t="n">
-        <v>193017</v>
-      </c>
-      <c r="F15" t="n">
-        <v>3175916</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -6205,20 +6205,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -217 千股)</t>
+          <t>📈 20d 巨變(加碼 27 千股)</t>
         </is>
       </c>
       <c r="C16" t="n">
+        <v>-216336</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-1255270</v>
+      </c>
+      <c r="E16" t="n">
         <v>-238998</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
         <v>-1282699</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-26981</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-1065455</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -6234,20 +6234,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -83 千股)</t>
+          <t>📉 20d 巨變(減碼 -239 千股)</t>
         </is>
       </c>
       <c r="C17" t="n">
+        <v>2137431</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1001763</v>
+      </c>
+      <c r="E17" t="n">
         <v>1643862</v>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
         <v>1240800</v>
-      </c>
-      <c r="E17" t="n">
-        <v>916087</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1323860</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -6258,522 +6258,522 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 158 千股)</t>
+          <t>📉 20d 巨變(減碼 -143 千股)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>496352</v>
+        <v>-193762</v>
       </c>
       <c r="D18" t="n">
-        <v>-2186698</v>
+        <v>-1714338</v>
       </c>
       <c r="E18" t="n">
-        <v>616713</v>
+        <v>-80535</v>
       </c>
       <c r="F18" t="n">
-        <v>-2344651</v>
+        <v>-1570983</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>辛耘</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 17 千股)</t>
+          <t>📈 20d 巨變(加碼 148 千股)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-376315</v>
+        <v>465384</v>
       </c>
       <c r="D19" t="n">
-        <v>-81511</v>
+        <v>-2038209</v>
       </c>
       <c r="E19" t="n">
-        <v>-500044</v>
+        <v>496352</v>
       </c>
       <c r="F19" t="n">
-        <v>-98766</v>
+        <v>-2186698</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>佳必琪</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3583</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -614 千股)</t>
+          <t>📈 20d 巨變(加碼 81 千股)</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-80535</v>
+        <v>-142884</v>
       </c>
       <c r="D20" t="n">
-        <v>-1570983</v>
+        <v>-30</v>
       </c>
       <c r="E20" t="n">
-        <v>151076</v>
+        <v>-376315</v>
       </c>
       <c r="F20" t="n">
-        <v>-957026</v>
+        <v>-81511</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>川湖</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1513</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 183 千股)</t>
+          <t>📉 20d 巨變(減碼 -51 千股)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1416939</v>
+        <v>-2026356</v>
       </c>
       <c r="D21" t="n">
-        <v>5959965</v>
+        <v>-1663379</v>
       </c>
       <c r="E21" t="n">
-        <v>1276930</v>
+        <v>-1844828</v>
       </c>
       <c r="F21" t="n">
-        <v>5776498</v>
+        <v>-1612370</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>中興電</t>
+          <t>大立光</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -47 千股)</t>
+          <t>📈 20d 巨變(加碼 8 千股)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>126357</v>
+        <v>-38006</v>
       </c>
       <c r="D22" t="n">
-        <v>386108</v>
+        <v>-14026</v>
       </c>
       <c r="E22" t="n">
-        <v>216131</v>
+        <v>-49006</v>
       </c>
       <c r="F22" t="n">
-        <v>433380</v>
+        <v>-22326</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>華城</t>
+          <t>大車隊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 232 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,794 千股)</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1126562</v>
+        <v>1399322</v>
       </c>
       <c r="D23" t="n">
-        <v>3076704</v>
+        <v>3166403</v>
       </c>
       <c r="E23" t="n">
-        <v>765131</v>
+        <v>1416939</v>
       </c>
       <c r="F23" t="n">
-        <v>2845163</v>
+        <v>5959965</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>中興電</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -195 千股)</t>
+          <t>📈 20d 巨變(加碼 540 千股)</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-1844828</v>
+        <v>1267578</v>
       </c>
       <c r="D24" t="n">
-        <v>-1612370</v>
+        <v>3616333</v>
       </c>
       <c r="E24" t="n">
-        <v>-1551893</v>
+        <v>1126562</v>
       </c>
       <c r="F24" t="n">
-        <v>-1416938</v>
+        <v>3076704</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>中砂</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5340</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -2,211 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -869 千股)</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-510019</v>
+        <v>-27210</v>
       </c>
       <c r="D25" t="n">
-        <v>-4381902</v>
+        <v>-483259</v>
       </c>
       <c r="E25" t="n">
-        <v>-530029</v>
+        <v>126357</v>
       </c>
       <c r="F25" t="n">
-        <v>-2170846</v>
+        <v>386108</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>建榮</t>
+          <t>華城</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -7 千股)</t>
+          <t>📈 20d 巨變(加碼 94 千股)</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-49006</v>
+        <v>-206144</v>
       </c>
       <c r="D26" t="n">
-        <v>-22326</v>
+        <v>-4287585</v>
       </c>
       <c r="E26" t="n">
-        <v>-36006</v>
+        <v>-510019</v>
       </c>
       <c r="F26" t="n">
-        <v>-15286</v>
+        <v>-4381902</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>大車隊</t>
+          <t>建榮</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -894 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -301 千股)</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1048634</v>
+        <v>-279758</v>
       </c>
       <c r="D27" t="n">
-        <v>15569444</v>
+        <v>-935960</v>
       </c>
       <c r="E27" t="n">
-        <v>906409</v>
+        <v>31242</v>
       </c>
       <c r="F27" t="n">
-        <v>16463522</v>
+        <v>-634830</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>隆大</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -145 千股)</t>
+          <t>📈 20d 巨變(加碼 12 千股)</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>31242</v>
+        <v>-43746</v>
       </c>
       <c r="D28" t="n">
-        <v>-634830</v>
+        <v>-62178</v>
       </c>
       <c r="E28" t="n">
-        <v>53687</v>
+        <v>-36083</v>
       </c>
       <c r="F28" t="n">
-        <v>-489862</v>
+        <v>-73785</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>崇友</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -14 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -546 千股)</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2493009</v>
+        <v>25002</v>
       </c>
       <c r="D29" t="n">
-        <v>296409</v>
+        <v>-1036456</v>
       </c>
       <c r="E29" t="n">
-        <v>1485770</v>
+        <v>-41258</v>
       </c>
       <c r="F29" t="n">
-        <v>310438</v>
+        <v>-490741</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>湧德</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -7 千股)</t>
+          <t>📈 20d 巨變(加碼 236 千股)</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-36083</v>
+        <v>2578779</v>
       </c>
       <c r="D30" t="n">
-        <v>-73785</v>
+        <v>532413</v>
       </c>
       <c r="E30" t="n">
-        <v>-17083</v>
+        <v>2493009</v>
       </c>
       <c r="F30" t="n">
-        <v>-66885</v>
+        <v>296409</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>崇友</t>
+          <t>零壹</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -23 千股)</t>
+          <t>📉 20d 巨變(減碼 -4,636 千股)</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-41258</v>
+        <v>1236188</v>
       </c>
       <c r="D31" t="n">
-        <v>-490741</v>
+        <v>10933721</v>
       </c>
       <c r="E31" t="n">
-        <v>-55036</v>
+        <v>1048634</v>
       </c>
       <c r="F31" t="n">
-        <v>-467428</v>
+        <v>15569444</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>建準</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1618</t>
+          <t>2618</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 75 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -8,776 千股)</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>400000</v>
+        <v>-3702664</v>
       </c>
       <c r="D32" t="n">
-        <v>1323793</v>
+        <v>2199194</v>
       </c>
       <c r="E32" t="n">
-        <v>386138</v>
+        <v>12150162</v>
       </c>
       <c r="F32" t="n">
-        <v>1248444</v>
+        <v>10974847</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>合機</t>
+          <t>長榮航</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 810 千股)</t>
+          <t>📉 20d 巨變(減碼 -332 千股)</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-7305075</v>
+        <v>-1788138</v>
       </c>
       <c r="D33" t="n">
-        <v>-13568097</v>
+        <v>-3096045</v>
       </c>
       <c r="E33" t="n">
-        <v>-6843521</v>
+        <v>-1488244</v>
       </c>
       <c r="F33" t="n">
-        <v>-14377743</v>
+        <v>-2763764</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>寶雅*</t>
+          <t>卜蜂</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 2,509 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,229 千股)</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>12150162</v>
+        <v>-7222163</v>
       </c>
       <c r="D34" t="n">
-        <v>10974847</v>
+        <v>-15797300</v>
       </c>
       <c r="E34" t="n">
-        <v>-1955200</v>
+        <v>-7305075</v>
       </c>
       <c r="F34" t="n">
-        <v>8465438</v>
+        <v>-13568097</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>長榮航</t>
+          <t>寶雅*</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -336 千股)</t>
+          <t>📉 20d 巨變(減碼 -8 千股)</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-1488244</v>
+        <v>50366</v>
       </c>
       <c r="D35" t="n">
-        <v>-2763764</v>
+        <v>108329</v>
       </c>
       <c r="E35" t="n">
-        <v>-1309233</v>
+        <v>76235</v>
       </c>
       <c r="F35" t="n">
-        <v>-2427788</v>
+        <v>116039</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>卜蜂</t>
+          <t>大統益</t>
         </is>
       </c>
     </row>
@@ -6785,20 +6785,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 672 千股)</t>
+          <t>📈 20d 巨變(加碼 86 千股)</t>
         </is>
       </c>
       <c r="C36" t="n">
+        <v>983347</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1344021</v>
+      </c>
+      <c r="E36" t="n">
         <v>1152883</v>
       </c>
-      <c r="D36" t="n">
+      <c r="F36" t="n">
         <v>1257988</v>
-      </c>
-      <c r="E36" t="n">
-        <v>656629</v>
-      </c>
-      <c r="F36" t="n">
-        <v>585719</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -6809,203 +6809,203 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1232</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -13 千股)</t>
+          <t>📉 20d 巨變(減碼 -858 千股)</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>76235</v>
+        <v>251989</v>
       </c>
       <c r="D37" t="n">
-        <v>116039</v>
+        <v>466236</v>
       </c>
       <c r="E37" t="n">
-        <v>66854</v>
+        <v>400000</v>
       </c>
       <c r="F37" t="n">
-        <v>129186</v>
+        <v>1323793</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>大統益</t>
+          <t>合機</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2753</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 147 千股)</t>
+          <t>📈 20d 巨變(加碼 22 千股)</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>34848</v>
+        <v>-60410</v>
       </c>
       <c r="D38" t="n">
-        <v>-182662</v>
+        <v>-383756</v>
       </c>
       <c r="E38" t="n">
-        <v>-10980</v>
+        <v>-33026</v>
       </c>
       <c r="F38" t="n">
-        <v>-329240</v>
+        <v>-406120</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>八方雲集</t>
+          <t>智冠</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>4527</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -15 千股)</t>
+          <t>📉 20d 巨變(減碼 -331 千股)</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-3000</v>
+        <v>-429712</v>
       </c>
       <c r="D39" t="n">
-        <v>35000</v>
+        <v>-1615287</v>
       </c>
       <c r="E39" t="n">
-        <v>-1000</v>
+        <v>-391260</v>
       </c>
       <c r="F39" t="n">
-        <v>50000</v>
+        <v>-1284074</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>方土霖</t>
+          <t>穎崴</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 16 千股)</t>
+          <t>📉 20d 巨變(減碼 -797 千股)</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-33026</v>
+        <v>8648199</v>
       </c>
       <c r="D40" t="n">
-        <v>-406120</v>
+        <v>46352453</v>
       </c>
       <c r="E40" t="n">
-        <v>-33026</v>
+        <v>7976018</v>
       </c>
       <c r="F40" t="n">
-        <v>-422120</v>
+        <v>47149677</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>智冠</t>
+          <t>台灣大</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -43 千股)</t>
+          <t>📈 20d 巨變(加碼 48 千股)</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>58454</v>
+        <v>31932</v>
       </c>
       <c r="D41" t="n">
-        <v>-203867</v>
+        <v>-134428</v>
       </c>
       <c r="E41" t="n">
-        <v>71447</v>
+        <v>34848</v>
       </c>
       <c r="F41" t="n">
-        <v>-161161</v>
+        <v>-182662</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>華景電</t>
+          <t>八方雲集</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -3,630 千股)</t>
+          <t>📉 20d 巨變(減碼 -798 千股)</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7976018</v>
+        <v>-2526228</v>
       </c>
       <c r="D42" t="n">
-        <v>47149677</v>
+        <v>-2761658</v>
       </c>
       <c r="E42" t="n">
-        <v>8907643</v>
+        <v>-1691852</v>
       </c>
       <c r="F42" t="n">
-        <v>50779443</v>
+        <v>-1963623</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>統一超</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -101 千股)</t>
+          <t>📈 20d 巨變(加碼 41 千股)</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-391260</v>
+        <v>289823</v>
       </c>
       <c r="D43" t="n">
-        <v>-1284074</v>
+        <v>385914</v>
       </c>
       <c r="E43" t="n">
-        <v>-376558</v>
+        <v>316483</v>
       </c>
       <c r="F43" t="n">
-        <v>-1183475</v>
+        <v>344594</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>漢科</t>
         </is>
       </c>
     </row>
@@ -7017,20 +7017,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -89 千股)</t>
+          <t>📉 20d 巨變(減碼 -921 千股)</t>
         </is>
       </c>
       <c r="C44" t="n">
+        <v>412259</v>
+      </c>
+      <c r="D44" t="n">
+        <v>-953982</v>
+      </c>
+      <c r="E44" t="n">
         <v>1102129</v>
       </c>
-      <c r="D44" t="n">
+      <c r="F44" t="n">
         <v>-33337</v>
-      </c>
-      <c r="E44" t="n">
-        <v>960416</v>
-      </c>
-      <c r="F44" t="n">
-        <v>55313</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -7046,20 +7046,20 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 64 千股)</t>
+          <t>📉 20d 巨變(減碼 -6 千股)</t>
         </is>
       </c>
       <c r="C45" t="n">
+        <v>201355</v>
+      </c>
+      <c r="D45" t="n">
+        <v>299830</v>
+      </c>
+      <c r="E45" t="n">
         <v>280647</v>
       </c>
-      <c r="D45" t="n">
+      <c r="F45" t="n">
         <v>305332</v>
-      </c>
-      <c r="E45" t="n">
-        <v>142188</v>
-      </c>
-      <c r="F45" t="n">
-        <v>241627</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -7070,348 +7070,348 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -284 千股)</t>
+          <t>📉 20d 巨變(減碼 -74 千股)</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-1691852</v>
+        <v>94096</v>
       </c>
       <c r="D46" t="n">
-        <v>-1963623</v>
+        <v>-278078</v>
       </c>
       <c r="E46" t="n">
-        <v>-1962156</v>
+        <v>58454</v>
       </c>
       <c r="F46" t="n">
-        <v>-1679889</v>
+        <v>-203867</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>統一超</t>
+          <t>華景電</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>4129</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -331 千股)</t>
+          <t>📈 20d 巨變(加碼 1,293 千股)</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-149072</v>
+        <v>2394374</v>
       </c>
       <c r="D47" t="n">
-        <v>-1648405</v>
+        <v>10295883</v>
       </c>
       <c r="E47" t="n">
-        <v>-190072</v>
+        <v>4209385</v>
       </c>
       <c r="F47" t="n">
-        <v>-1317405</v>
+        <v>9002612</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>聯合</t>
+          <t>台燿</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 68 千股)</t>
+          <t>📈 20d 巨變(加碼 319 千股)</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>316483</v>
+        <v>-169000</v>
       </c>
       <c r="D48" t="n">
-        <v>344594</v>
+        <v>-1329405</v>
       </c>
       <c r="E48" t="n">
-        <v>284986</v>
+        <v>-149072</v>
       </c>
       <c r="F48" t="n">
-        <v>276413</v>
+        <v>-1648405</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>聯合</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,558 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,163 千股)</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4209385</v>
+        <v>-2780380</v>
       </c>
       <c r="D49" t="n">
-        <v>9002612</v>
+        <v>-3983562</v>
       </c>
       <c r="E49" t="n">
-        <v>4127406</v>
+        <v>-3650944</v>
       </c>
       <c r="F49" t="n">
-        <v>7444867</v>
+        <v>-2820375</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>玉晶光</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 256 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,806 千股)</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>2258443</v>
+        <v>-2168260</v>
       </c>
       <c r="D50" t="n">
-        <v>-355837</v>
+        <v>-14666067</v>
       </c>
       <c r="E50" t="n">
-        <v>1696536</v>
+        <v>-1004107</v>
       </c>
       <c r="F50" t="n">
-        <v>-611597</v>
+        <v>-12860211</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>威剛</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -63 千股)</t>
+          <t>📈 20d 巨變(加碼 77 千股)</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-3650944</v>
+        <v>-343523</v>
       </c>
       <c r="D51" t="n">
-        <v>-2820375</v>
+        <v>3888813</v>
       </c>
       <c r="E51" t="n">
-        <v>-3706772</v>
+        <v>-48825</v>
       </c>
       <c r="F51" t="n">
-        <v>-2757067</v>
+        <v>3811875</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>立隆電</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2472</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -840 千股)</t>
+          <t>📈 20d 巨變(加碼 2,972 千股)</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-48825</v>
+        <v>8376114</v>
       </c>
       <c r="D52" t="n">
-        <v>3811875</v>
+        <v>-11184678</v>
       </c>
       <c r="E52" t="n">
-        <v>1320154</v>
+        <v>4190684</v>
       </c>
       <c r="F52" t="n">
-        <v>4651731</v>
+        <v>-14156943</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>立隆電</t>
+          <t>國巨*</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,023 千股)</t>
+          <t>📉 20d 巨變(減碼 -50,086 千股)</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-1004107</v>
+        <v>14909059</v>
       </c>
       <c r="D53" t="n">
-        <v>-12860211</v>
+        <v>-30513770</v>
       </c>
       <c r="E53" t="n">
-        <v>-705430</v>
+        <v>35170358</v>
       </c>
       <c r="F53" t="n">
-        <v>-14883040</v>
+        <v>19572477</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>南亞科</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 26,038 千股)</t>
+          <t>📈 20d 巨變(加碼 68 千股)</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>35170358</v>
+        <v>2539038</v>
       </c>
       <c r="D54" t="n">
-        <v>19572477</v>
+        <v>-288033</v>
       </c>
       <c r="E54" t="n">
-        <v>12482165</v>
+        <v>2258443</v>
       </c>
       <c r="F54" t="n">
-        <v>-6465908</v>
+        <v>-355837</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>世芯-KY</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -5,256 千股)</t>
+          <t>📈 20d 巨變(加碼 2,707 千股)</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4190684</v>
+        <v>3559484</v>
       </c>
       <c r="D55" t="n">
-        <v>-14156943</v>
+        <v>6434832</v>
       </c>
       <c r="E55" t="n">
-        <v>2999995</v>
+        <v>1469617</v>
       </c>
       <c r="F55" t="n">
-        <v>-8900948</v>
+        <v>3727896</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>鈊象</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 3,069 千股)</t>
+          <t>📉 20d 巨變(減碼 -887 千股)</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>27289613</v>
+        <v>-462160</v>
       </c>
       <c r="D56" t="n">
-        <v>47974306</v>
+        <v>-1317827</v>
       </c>
       <c r="E56" t="n">
-        <v>25887340</v>
+        <v>-346607</v>
       </c>
       <c r="F56" t="n">
-        <v>44905786</v>
+        <v>-431004</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>士電</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -541 千股)</t>
+          <t>📈 20d 巨變(加碼 99 千股)</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-346607</v>
+        <v>26732575</v>
       </c>
       <c r="D57" t="n">
-        <v>-431004</v>
+        <v>48073253</v>
       </c>
       <c r="E57" t="n">
-        <v>-504736</v>
+        <v>27289613</v>
       </c>
       <c r="F57" t="n">
-        <v>109739</v>
+        <v>47974306</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>士電</t>
+          <t>日月光投控</t>
         </is>
       </c>
     </row>
@@ -7423,20 +7423,20 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 118 千股)</t>
+          <t>📉 20d 巨變(減碼 -149 千股)</t>
         </is>
       </c>
       <c r="C58" t="n">
+        <v>153587</v>
+      </c>
+      <c r="D58" t="n">
+        <v>-49145</v>
+      </c>
+      <c r="E58" t="n">
         <v>253964</v>
       </c>
-      <c r="D58" t="n">
+      <c r="F58" t="n">
         <v>99577</v>
-      </c>
-      <c r="E58" t="n">
-        <v>81914</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-18721</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -7447,261 +7447,261 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,231 千股)</t>
+          <t>📉 20d 巨變(減碼 -543 千股)</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1469617</v>
+        <v>622036</v>
       </c>
       <c r="D59" t="n">
-        <v>3727896</v>
+        <v>-1147020</v>
       </c>
       <c r="E59" t="n">
-        <v>1211758</v>
+        <v>547879</v>
       </c>
       <c r="F59" t="n">
-        <v>2496827</v>
+        <v>-604205</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>鈊象</t>
+          <t>鉅祥</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>6263</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -683 千股)</t>
+          <t>📉 20d 巨變(減碼 -14 千股)</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>547879</v>
+        <v>96845</v>
       </c>
       <c r="D60" t="n">
-        <v>-604205</v>
+        <v>290969</v>
       </c>
       <c r="E60" t="n">
-        <v>392762</v>
+        <v>69359</v>
       </c>
       <c r="F60" t="n">
-        <v>78817</v>
+        <v>304918</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>鉅祥</t>
+          <t>普萊德</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>6263</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -29 千股)</t>
+          <t>📉 20d 巨變(減碼 -18 千股)</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>69359</v>
+        <v>-899782</v>
       </c>
       <c r="D61" t="n">
-        <v>304918</v>
+        <v>-1740018</v>
       </c>
       <c r="E61" t="n">
-        <v>57390</v>
+        <v>-1051618</v>
       </c>
       <c r="F61" t="n">
-        <v>333938</v>
+        <v>-1722083</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 2,092 千股)</t>
+          <t>📉 20d 巨變(減碼 -104 千股)</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>49659</v>
+        <v>-396690</v>
       </c>
       <c r="D62" t="n">
-        <v>-331944</v>
+        <v>-1986981</v>
       </c>
       <c r="E62" t="n">
-        <v>471380</v>
+        <v>-113800</v>
       </c>
       <c r="F62" t="n">
-        <v>-2423465</v>
+        <v>-1882640</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>勝一</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 23 千股)</t>
+          <t>📉 20d 巨變(減碼 -278 千股)</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-1051618</v>
+        <v>160580</v>
       </c>
       <c r="D63" t="n">
-        <v>-1722083</v>
+        <v>-1106143</v>
       </c>
       <c r="E63" t="n">
-        <v>-1183696</v>
+        <v>79327</v>
       </c>
       <c r="F63" t="n">
-        <v>-1744641</v>
+        <v>-828279</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>信立</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1773</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -35 千股)</t>
+          <t>📉 20d 巨變(減碼 -134 千股)</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-113800</v>
+        <v>383435</v>
       </c>
       <c r="D64" t="n">
-        <v>-1882640</v>
+        <v>815215</v>
       </c>
       <c r="E64" t="n">
-        <v>-160490</v>
+        <v>640341</v>
       </c>
       <c r="F64" t="n">
-        <v>-1847615</v>
+        <v>949146</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>勝一</t>
+          <t>祥碩</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 155 千股)</t>
+          <t>📈 20d 巨變(加碼 969 千股)</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>79327</v>
+        <v>371735</v>
       </c>
       <c r="D65" t="n">
-        <v>-828279</v>
+        <v>637174</v>
       </c>
       <c r="E65" t="n">
-        <v>79765</v>
+        <v>49659</v>
       </c>
       <c r="F65" t="n">
-        <v>-983742</v>
+        <v>-331944</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>華星光</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>6446</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -126 千股)</t>
+          <t>📉 20d 巨變(減碼 -562 千股)</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>640341</v>
+        <v>-11014340</v>
       </c>
       <c r="D66" t="n">
-        <v>949146</v>
+        <v>-14690337</v>
       </c>
       <c r="E66" t="n">
-        <v>1154356</v>
+        <v>-11122629</v>
       </c>
       <c r="F66" t="n">
-        <v>1075182</v>
+        <v>-14128811</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>藥華藥</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,238 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,439 千股)</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-11122629</v>
+        <v>-1040896</v>
       </c>
       <c r="D67" t="n">
-        <v>-14128811</v>
+        <v>-4556532</v>
       </c>
       <c r="E67" t="n">
-        <v>-10704384</v>
+        <v>-1903465</v>
       </c>
       <c r="F67" t="n">
-        <v>-12891228</v>
+        <v>-3117865</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>宇瞻</t>
         </is>
       </c>
     </row>
@@ -7713,20 +7713,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,179 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,162 千股)</t>
         </is>
       </c>
       <c r="C68" t="n">
+        <v>-5345409</v>
+      </c>
+      <c r="D68" t="n">
+        <v>-9147034</v>
+      </c>
+      <c r="E68" t="n">
         <v>-7718362</v>
       </c>
-      <c r="D68" t="n">
+      <c r="F68" t="n">
         <v>-7985353</v>
-      </c>
-      <c r="E68" t="n">
-        <v>-6264029</v>
-      </c>
-      <c r="F68" t="n">
-        <v>-6806679</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -7737,232 +7737,232 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 418 千股)</t>
+          <t>📉 20d 巨變(減碼 -7,154 千股)</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-2232416</v>
+        <v>-15842819</v>
       </c>
       <c r="D69" t="n">
-        <v>-2181048</v>
+        <v>7589057</v>
       </c>
       <c r="E69" t="n">
-        <v>-3602726</v>
+        <v>-7399669</v>
       </c>
       <c r="F69" t="n">
-        <v>-2598987</v>
+        <v>14742997</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>廣達</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -5,530 千股)</t>
+          <t>📈 20d 巨變(加碼 42 千股)</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-7399669</v>
+        <v>-1325075</v>
       </c>
       <c r="D70" t="n">
-        <v>14742997</v>
+        <v>-2138671</v>
       </c>
       <c r="E70" t="n">
-        <v>-4793575</v>
+        <v>-2232416</v>
       </c>
       <c r="F70" t="n">
-        <v>20272878</v>
+        <v>-2181048</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>聯亞</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -5 千股)</t>
+          <t>📈 20d 巨變(加碼 14,561 千股)</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-1903465</v>
+        <v>-28100187</v>
       </c>
       <c r="D71" t="n">
-        <v>-3117865</v>
+        <v>-102323096</v>
       </c>
       <c r="E71" t="n">
-        <v>-1419346</v>
+        <v>-27146875</v>
       </c>
       <c r="F71" t="n">
-        <v>-3112504</v>
+        <v>-116883701</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>緯創</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -7,435 千股)</t>
+          <t>📉 20d 巨變(減碼 -831 千股)</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-27146875</v>
+        <v>4778830</v>
       </c>
       <c r="D72" t="n">
-        <v>-116883701</v>
+        <v>6612945</v>
       </c>
       <c r="E72" t="n">
-        <v>-32812476</v>
+        <v>7227888</v>
       </c>
       <c r="F72" t="n">
-        <v>-109448520</v>
+        <v>7444172</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>瑞昱</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 949 千股)</t>
+          <t>📈 20d 巨變(加碼 3,505 千股)</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>7227888</v>
+        <v>-2961794</v>
       </c>
       <c r="D73" t="n">
-        <v>7444172</v>
+        <v>-21607041</v>
       </c>
       <c r="E73" t="n">
-        <v>7073108</v>
+        <v>-3202892</v>
       </c>
       <c r="F73" t="n">
-        <v>6494847</v>
+        <v>-25111868</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>光寶科</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -59 千股)</t>
+          <t>📉 20d 巨變(減碼 -163 千股)</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-3202892</v>
+        <v>-243563</v>
       </c>
       <c r="D74" t="n">
-        <v>-25111868</v>
+        <v>-5163387</v>
       </c>
       <c r="E74" t="n">
-        <v>-2519724</v>
+        <v>-93213</v>
       </c>
       <c r="F74" t="n">
-        <v>-25052637</v>
+        <v>-5000266</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>台汽電</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -258 千股)</t>
+          <t>📈 20d 巨變(加碼 22 千股)</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-93213</v>
+        <v>14420</v>
       </c>
       <c r="D75" t="n">
-        <v>-5000266</v>
+        <v>-409360</v>
       </c>
       <c r="E75" t="n">
-        <v>754419</v>
+        <v>20846</v>
       </c>
       <c r="F75" t="n">
-        <v>-4742299</v>
+        <v>-431360</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>德昌</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>1616</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -27 千股)</t>
+          <t>📉 20d 巨變(減碼 -230 千股)</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>20846</v>
+        <v>256691</v>
       </c>
       <c r="D76" t="n">
-        <v>-431360</v>
+        <v>561858</v>
       </c>
       <c r="E76" t="n">
-        <v>18912</v>
+        <v>429350</v>
       </c>
       <c r="F76" t="n">
-        <v>-404344</v>
+        <v>791450</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>德昌</t>
+          <t>億泰</t>
         </is>
       </c>
     </row>
@@ -7974,20 +7974,20 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 11 千股)</t>
+          <t>📈 20d 巨變(加碼 8 千股)</t>
         </is>
       </c>
       <c r="C77" t="n">
+        <v>78929</v>
+      </c>
+      <c r="D77" t="n">
+        <v>36929</v>
+      </c>
+      <c r="E77" t="n">
         <v>95929</v>
       </c>
-      <c r="D77" t="n">
+      <c r="F77" t="n">
         <v>28929</v>
-      </c>
-      <c r="E77" t="n">
-        <v>106929</v>
-      </c>
-      <c r="F77" t="n">
-        <v>17929</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -7998,522 +7998,522 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1616</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -86 千股)</t>
+          <t>📈 20d 巨變(加碼 163 千股)</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>429350</v>
+        <v>-1421985</v>
       </c>
       <c r="D78" t="n">
-        <v>791450</v>
+        <v>-7091035</v>
       </c>
       <c r="E78" t="n">
-        <v>401310</v>
+        <v>-1240915</v>
       </c>
       <c r="F78" t="n">
-        <v>877379</v>
+        <v>-7254082</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>億泰</t>
+          <t>智易</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3596</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 129 千股)</t>
+          <t>📈 20d 巨變(加碼 1,317 千股)</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-1240915</v>
+        <v>1150106</v>
       </c>
       <c r="D79" t="n">
-        <v>-7254082</v>
+        <v>918178</v>
       </c>
       <c r="E79" t="n">
-        <v>-997915</v>
+        <v>875028</v>
       </c>
       <c r="F79" t="n">
-        <v>-7383519</v>
+        <v>-398855</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>啟碁</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>3227</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -601 千股)</t>
+          <t>📉 20d 巨變(減碼 -116 千股)</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>875028</v>
+        <v>-454251</v>
       </c>
       <c r="D80" t="n">
-        <v>-398855</v>
+        <v>-3223792</v>
       </c>
       <c r="E80" t="n">
-        <v>-226133</v>
+        <v>-687251</v>
       </c>
       <c r="F80" t="n">
-        <v>202059</v>
+        <v>-3107789</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>原相</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -60 千股)</t>
+          <t>📈 20d 巨變(加碼 569 千股)</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-766312</v>
+        <v>-11141148</v>
       </c>
       <c r="D81" t="n">
-        <v>-2218710</v>
+        <v>-24135641</v>
       </c>
       <c r="E81" t="n">
-        <v>-712133</v>
+        <v>-6953167</v>
       </c>
       <c r="F81" t="n">
-        <v>-2159097</v>
+        <v>-24704220</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>英業達</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -10,542 千股)</t>
+          <t>📈 20d 巨變(加碼 27 千股)</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-6953167</v>
+        <v>-662474</v>
       </c>
       <c r="D82" t="n">
-        <v>-24704220</v>
+        <v>-2192005</v>
       </c>
       <c r="E82" t="n">
-        <v>-5160953</v>
+        <v>-766312</v>
       </c>
       <c r="F82" t="n">
-        <v>-14162537</v>
+        <v>-2218710</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>精測</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -230 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -42,122 千股)</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-687251</v>
+        <v>-23601689</v>
       </c>
       <c r="D83" t="n">
-        <v>-3107789</v>
+        <v>-12058135</v>
       </c>
       <c r="E83" t="n">
-        <v>-778206</v>
+        <v>9151152</v>
       </c>
       <c r="F83" t="n">
-        <v>-2877543</v>
+        <v>30063426</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>鴻海</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 7,932 千股)</t>
+          <t>📉 20d 巨變(減碼 -350 千股)</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>9151152</v>
+        <v>-411608</v>
       </c>
       <c r="D84" t="n">
-        <v>30063426</v>
+        <v>-1877856</v>
       </c>
       <c r="E84" t="n">
-        <v>1602170</v>
+        <v>-139616</v>
       </c>
       <c r="F84" t="n">
-        <v>22131664</v>
+        <v>-1528106</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>乙盛-KY</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>3188</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -292 千股)</t>
+          <t>📉 20d 巨變(減碼 -109 千股)</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-139616</v>
+        <v>-157000</v>
       </c>
       <c r="D85" t="n">
-        <v>-1528106</v>
+        <v>-109254</v>
       </c>
       <c r="E85" t="n">
-        <v>146096</v>
+        <v>-105000</v>
       </c>
       <c r="F85" t="n">
-        <v>-1236292</v>
+        <v>9</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>乙盛-KY</t>
+          <t>鑫龍騰</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3188</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -82 千股)</t>
+          <t>📉 20d 巨變(減碼 -28 千股)</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-105000</v>
+        <v>202735</v>
       </c>
       <c r="D86" t="n">
-        <v>9</v>
+        <v>673996</v>
       </c>
       <c r="E86" t="n">
-        <v>-42000</v>
+        <v>195735</v>
       </c>
       <c r="F86" t="n">
-        <v>82009</v>
+        <v>702279</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>鑫龍騰</t>
+          <t>東科-KY</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 1,135 千股)</t>
+          <t>📈 20d 巨變(加碼 545 千股)</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-228481</v>
+        <v>4462026</v>
       </c>
       <c r="D87" t="n">
-        <v>-7692023</v>
+        <v>8728469</v>
       </c>
       <c r="E87" t="n">
-        <v>-220549</v>
+        <v>5582976</v>
       </c>
       <c r="F87" t="n">
-        <v>-8827191</v>
+        <v>8183932</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>全友</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2395</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -1,984 千股)</t>
+          <t>📈 20d 巨變(加碼 838 千股)</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>5582976</v>
+        <v>2439047</v>
       </c>
       <c r="D88" t="n">
-        <v>8183932</v>
+        <v>6460637</v>
       </c>
       <c r="E88" t="n">
-        <v>10840094</v>
+        <v>3179412</v>
       </c>
       <c r="F88" t="n">
-        <v>10168356</v>
+        <v>5622742</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>全友</t>
+          <t>研華</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2395</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 339 千股)</t>
+          <t>📈 20d 巨變(加碼 3,230 千股)</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3179412</v>
+        <v>17401231</v>
       </c>
       <c r="D89" t="n">
-        <v>5622742</v>
+        <v>91921249</v>
       </c>
       <c r="E89" t="n">
-        <v>2905425</v>
+        <v>24582760</v>
       </c>
       <c r="F89" t="n">
-        <v>5283617</v>
+        <v>88691137</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>研華</t>
+          <t>中華電</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 5,616 千股)</t>
+          <t>📉 20d 巨變(減碼 -202 千股)</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>24582760</v>
+        <v>98176</v>
       </c>
       <c r="D90" t="n">
-        <v>88691137</v>
+        <v>-802488</v>
       </c>
       <c r="E90" t="n">
-        <v>26808253</v>
+        <v>263622</v>
       </c>
       <c r="F90" t="n">
-        <v>83075410</v>
+        <v>-600356</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>中保科</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -130 千股)</t>
+          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -47 千股)</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>263622</v>
+        <v>-15921</v>
       </c>
       <c r="D91" t="n">
-        <v>-600356</v>
+        <v>-166694</v>
       </c>
       <c r="E91" t="n">
-        <v>176396</v>
+        <v>4915</v>
       </c>
       <c r="F91" t="n">
-        <v>-470669</v>
+        <v>-119759</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>竹陞科技</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 33 千股)</t>
+          <t>📉 20d 巨變(減碼 -299 千股)</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>4915</v>
+        <v>-342589</v>
       </c>
       <c r="D92" t="n">
-        <v>-119759</v>
+        <v>-5397961</v>
       </c>
       <c r="E92" t="n">
-        <v>-145902</v>
+        <v>-120195</v>
       </c>
       <c r="F92" t="n">
-        <v>-152759</v>
+        <v>-5099458</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>長榮航太</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>6690</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -582 千股)</t>
+          <t>📉 20d 巨變(減碼 -27 千股)</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-120195</v>
+        <v>29432</v>
       </c>
       <c r="D93" t="n">
-        <v>-5099458</v>
+        <v>53059</v>
       </c>
       <c r="E93" t="n">
-        <v>311140</v>
+        <v>72442</v>
       </c>
       <c r="F93" t="n">
-        <v>-4517535</v>
+        <v>80059</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>長榮航太</t>
+          <t>安碁資訊</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 27 千股)</t>
+          <t>📉 20d 巨變(減碼 -1,118 千股)</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>72442</v>
+        <v>592109</v>
       </c>
       <c r="D94" t="n">
-        <v>80059</v>
+        <v>13022540</v>
       </c>
       <c r="E94" t="n">
-        <v>50745</v>
+        <v>1132718</v>
       </c>
       <c r="F94" t="n">
-        <v>53039</v>
+        <v>14140399</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>安碁資訊</t>
+          <t>遠傳</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4569</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -9 千股)</t>
+          <t>📉 20d 巨變(減碼 -47,956 千股)</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>57756</v>
+        <v>19645741</v>
       </c>
       <c r="D95" t="n">
-        <v>-25443</v>
+        <v>-53584173</v>
       </c>
       <c r="E95" t="n">
-        <v>49646</v>
+        <v>27224635</v>
       </c>
       <c r="F95" t="n">
-        <v>-16553</v>
+        <v>-5627928</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>六方科-KY</t>
+          <t>華邦電</t>
         </is>
       </c>
     </row>
@@ -8525,20 +8525,20 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -735 千股)</t>
+          <t>📈 20d 巨變(加碼 1,073 千股)</t>
         </is>
       </c>
       <c r="C96" t="n">
+        <v>8907830</v>
+      </c>
+      <c r="D96" t="n">
+        <v>13969997</v>
+      </c>
+      <c r="E96" t="n">
         <v>8381759</v>
       </c>
-      <c r="D96" t="n">
+      <c r="F96" t="n">
         <v>12896722</v>
-      </c>
-      <c r="E96" t="n">
-        <v>8882370</v>
-      </c>
-      <c r="F96" t="n">
-        <v>13632155</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -8549,230 +8549,201 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>8086</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 873 千股)</t>
+          <t>📉 20d 巨變(減碼 -842 千股)</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>1132718</v>
+        <v>-257300</v>
       </c>
       <c r="D97" t="n">
-        <v>14140399</v>
+        <v>-8534257</v>
       </c>
       <c r="E97" t="n">
-        <v>793066</v>
+        <v>-228481</v>
       </c>
       <c r="F97" t="n">
-        <v>13267255</v>
+        <v>-7692023</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>宏捷科</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -4,112 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 27 千股)</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>27224635</v>
+        <v>245622</v>
       </c>
       <c r="D98" t="n">
-        <v>-5627928</v>
+        <v>-442387</v>
       </c>
       <c r="E98" t="n">
-        <v>35574502</v>
+        <v>-281720</v>
       </c>
       <c r="F98" t="n">
-        <v>-1515536</v>
+        <v>-468980</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>創意</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>📈 20d 巨變(加碼 403 千股)</t>
+          <t>📈 20d 巨變(加碼 350 千股)</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-281720</v>
+        <v>1174981</v>
       </c>
       <c r="D99" t="n">
-        <v>-468980</v>
+        <v>-10719826</v>
       </c>
       <c r="E99" t="n">
-        <v>-748492</v>
+        <v>1194409</v>
       </c>
       <c r="F99" t="n">
-        <v>-872160</v>
+        <v>-11069427</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>緯穎</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 768 千股)</t>
+          <t>📈 20d 巨變(加碼 26 千股)</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1194409</v>
+        <v>112229</v>
       </c>
       <c r="D100" t="n">
-        <v>-11069427</v>
+        <v>141950</v>
       </c>
       <c r="E100" t="n">
-        <v>-1882810</v>
+        <v>39242</v>
       </c>
       <c r="F100" t="n">
-        <v>-11837678</v>
+        <v>115909</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>信驊</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 55 千股)</t>
+          <t>📉 20d 巨變(減碼 -2,458 千股)</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>39242</v>
+        <v>-6922947</v>
       </c>
       <c r="D101" t="n">
-        <v>115909</v>
+        <v>-16741073</v>
       </c>
       <c r="E101" t="n">
-        <v>-10083</v>
+        <v>-7948625</v>
       </c>
       <c r="F101" t="n">
-        <v>60739</v>
+        <v>-14282925</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>金像電</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>📉 20d 巨變(減碼 -585 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 133 千股)</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-7948625</v>
+        <v>119778</v>
       </c>
       <c r="D102" t="n">
-        <v>-14282925</v>
+        <v>-2902119</v>
       </c>
       <c r="E102" t="n">
-        <v>-7743511</v>
+        <v>-116755</v>
       </c>
       <c r="F102" t="n">
-        <v>-13697978</v>
+        <v>-3035457</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>高技</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -820 千股)</t>
+          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -393 千股)</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-116755</v>
+        <v>51839</v>
       </c>
       <c r="D103" t="n">
-        <v>-3035457</v>
+        <v>-968889</v>
       </c>
       <c r="E103" t="n">
-        <v>256716</v>
+        <v>-410444</v>
       </c>
       <c r="F103" t="n">
-        <v>-2215619</v>
+        <v>-575692</v>
       </c>
       <c r="G103" t="inlineStr">
-        <is>
-          <t>高技</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 772 千股)</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>-410444</v>
-      </c>
-      <c r="D104" t="n">
-        <v>-575692</v>
-      </c>
-      <c r="E104" t="n">
-        <v>-501867</v>
-      </c>
-      <c r="F104" t="n">
-        <v>-1347865</v>
-      </c>
-      <c r="G104" t="inlineStr">
         <is>
           <t>萬潤</t>
         </is>

--- a/data/台股_外資雷達.xlsx
+++ b/data/台股_外資雷達.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="總覽" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="翻轉警報" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -502,7 +501,7 @@
         <v>91921</v>
       </c>
       <c r="E2" t="n">
-        <v>181265</v>
+        <v>183753</v>
       </c>
       <c r="F2" t="n">
         <v>276</v>
@@ -553,7 +552,7 @@
         <v>48073</v>
       </c>
       <c r="E3" t="n">
-        <v>20120</v>
+        <v>26432</v>
       </c>
       <c r="F3" t="n">
         <v>-3299</v>
@@ -604,7 +603,7 @@
         <v>46352</v>
       </c>
       <c r="E4" t="n">
-        <v>203837</v>
+        <v>186749</v>
       </c>
       <c r="F4" t="n">
         <v>1723</v>
@@ -655,7 +654,7 @@
         <v>13970</v>
       </c>
       <c r="E5" t="n">
-        <v>15712</v>
+        <v>16260</v>
       </c>
       <c r="F5" t="n">
         <v>259</v>
@@ -685,7 +684,7 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -706,7 +705,7 @@
         <v>13023</v>
       </c>
       <c r="E6" t="n">
-        <v>102099</v>
+        <v>99851</v>
       </c>
       <c r="F6" t="n">
         <v>549</v>
@@ -736,7 +735,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -757,7 +756,7 @@
         <v>10934</v>
       </c>
       <c r="E7" t="n">
-        <v>24177</v>
+        <v>25430</v>
       </c>
       <c r="F7" t="n">
         <v>-165</v>
@@ -808,7 +807,7 @@
         <v>10296</v>
       </c>
       <c r="E8" t="n">
-        <v>3135</v>
+        <v>1825</v>
       </c>
       <c r="F8" t="n">
         <v>-4665</v>
@@ -838,7 +837,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -859,7 +858,7 @@
         <v>8728</v>
       </c>
       <c r="E9" t="n">
-        <v>1763</v>
+        <v>1641</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -910,7 +909,7 @@
         <v>7589</v>
       </c>
       <c r="E10" t="n">
-        <v>-13511</v>
+        <v>-7760</v>
       </c>
       <c r="F10" t="n">
         <v>9819</v>
@@ -961,7 +960,7 @@
         <v>6613</v>
       </c>
       <c r="E11" t="n">
-        <v>648</v>
+        <v>3954</v>
       </c>
       <c r="F11" t="n">
         <v>545</v>
@@ -991,7 +990,7 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="12">
@@ -1012,7 +1011,7 @@
         <v>6596</v>
       </c>
       <c r="E12" t="n">
-        <v>12260</v>
+        <v>12377</v>
       </c>
       <c r="F12" t="n">
         <v>906</v>
@@ -1063,7 +1062,7 @@
         <v>6461</v>
       </c>
       <c r="E13" t="n">
-        <v>2904</v>
+        <v>3229</v>
       </c>
       <c r="F13" t="n">
         <v>-456</v>
@@ -1114,7 +1113,7 @@
         <v>6435</v>
       </c>
       <c r="E14" t="n">
-        <v>14559</v>
+        <v>15036</v>
       </c>
       <c r="F14" t="n">
         <v>421</v>
@@ -1165,7 +1164,7 @@
         <v>3889</v>
       </c>
       <c r="E15" t="n">
-        <v>14567</v>
+        <v>10243</v>
       </c>
       <c r="F15" t="n">
         <v>-1324</v>
@@ -1216,7 +1215,7 @@
         <v>3616</v>
       </c>
       <c r="E16" t="n">
-        <v>1913</v>
+        <v>2271</v>
       </c>
       <c r="F16" t="n">
         <v>1028</v>
@@ -1267,7 +1266,7 @@
         <v>3414</v>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>5746</v>
       </c>
       <c r="F17" t="n">
         <v>-62</v>
@@ -1318,7 +1317,7 @@
         <v>3166</v>
       </c>
       <c r="E18" t="n">
-        <v>25577</v>
+        <v>25539</v>
       </c>
       <c r="F18" t="n">
         <v>828</v>
@@ -1369,7 +1368,7 @@
         <v>2199</v>
       </c>
       <c r="E19" t="n">
-        <v>462961</v>
+        <v>359651</v>
       </c>
       <c r="F19" t="n">
         <v>25838</v>
@@ -1420,7 +1419,7 @@
         <v>1782</v>
       </c>
       <c r="E20" t="n">
-        <v>-2624</v>
+        <v>-3198</v>
       </c>
       <c r="F20" t="n">
         <v>-762</v>
@@ -1471,7 +1470,7 @@
         <v>1344</v>
       </c>
       <c r="E21" t="n">
-        <v>3572</v>
+        <v>3628</v>
       </c>
       <c r="F21" t="n">
         <v>-7</v>
@@ -1501,7 +1500,7 @@
         </is>
       </c>
       <c r="M21" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="22">
@@ -1522,7 +1521,7 @@
         <v>1277</v>
       </c>
       <c r="E22" t="n">
-        <v>4963</v>
+        <v>5231</v>
       </c>
       <c r="F22" t="n">
         <v>318</v>
@@ -1573,7 +1572,7 @@
         <v>1002</v>
       </c>
       <c r="E23" t="n">
-        <v>-9345</v>
+        <v>-8981</v>
       </c>
       <c r="F23" t="n">
         <v>58</v>
@@ -1624,7 +1623,7 @@
         <v>918</v>
       </c>
       <c r="E24" t="n">
-        <v>1539</v>
+        <v>1040</v>
       </c>
       <c r="F24" t="n">
         <v>7</v>
@@ -1675,7 +1674,7 @@
         <v>900</v>
       </c>
       <c r="E25" t="n">
-        <v>-132</v>
+        <v>-227</v>
       </c>
       <c r="F25" t="n">
         <v>-2441</v>
@@ -1726,7 +1725,7 @@
         <v>815</v>
       </c>
       <c r="E26" t="n">
-        <v>2891</v>
+        <v>2260</v>
       </c>
       <c r="F26" t="n">
         <v>7</v>
@@ -1777,7 +1776,7 @@
         <v>746</v>
       </c>
       <c r="E27" t="n">
-        <v>-1405</v>
+        <v>-2855</v>
       </c>
       <c r="F27" t="n">
         <v>-1274</v>
@@ -1828,7 +1827,7 @@
         <v>725</v>
       </c>
       <c r="E28" t="n">
-        <v>898</v>
+        <v>178</v>
       </c>
       <c r="F28" t="n">
         <v>-800</v>
@@ -1879,7 +1878,7 @@
         <v>704</v>
       </c>
       <c r="E29" t="n">
-        <v>-1080</v>
+        <v>-653</v>
       </c>
       <c r="F29" t="n">
         <v>-1308</v>
@@ -1930,7 +1929,7 @@
         <v>674</v>
       </c>
       <c r="E30" t="n">
-        <v>-113</v>
+        <v>-28</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1981,7 +1980,7 @@
         <v>637</v>
       </c>
       <c r="E31" t="n">
-        <v>-954</v>
+        <v>-2688</v>
       </c>
       <c r="F31" t="n">
         <v>-2943</v>
@@ -2032,7 +2031,7 @@
         <v>562</v>
       </c>
       <c r="E32" t="n">
-        <v>1172</v>
+        <v>1226</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -2083,7 +2082,7 @@
         <v>532</v>
       </c>
       <c r="E33" t="n">
-        <v>7854</v>
+        <v>7237</v>
       </c>
       <c r="F33" t="n">
         <v>-2</v>
@@ -2134,7 +2133,7 @@
         <v>466</v>
       </c>
       <c r="E34" t="n">
-        <v>2934</v>
+        <v>3515</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -2185,7 +2184,7 @@
         <v>386</v>
       </c>
       <c r="E35" t="n">
-        <v>-1676</v>
+        <v>-1753</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -2236,7 +2235,7 @@
         <v>300</v>
       </c>
       <c r="E36" t="n">
-        <v>610</v>
+        <v>577</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -2287,7 +2286,7 @@
         <v>291</v>
       </c>
       <c r="E37" t="n">
-        <v>1181</v>
+        <v>1171</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -2338,7 +2337,7 @@
         <v>221</v>
       </c>
       <c r="E38" t="n">
-        <v>-888</v>
+        <v>-1317</v>
       </c>
       <c r="F38" t="n">
         <v>347</v>
@@ -2389,7 +2388,7 @@
         <v>142</v>
       </c>
       <c r="E39" t="n">
-        <v>-258</v>
+        <v>-385</v>
       </c>
       <c r="F39" t="n">
         <v>-25</v>
@@ -2428,7 +2427,7 @@
         <v>108</v>
       </c>
       <c r="E40" t="n">
-        <v>788</v>
+        <v>169</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -2479,7 +2478,7 @@
         <v>53</v>
       </c>
       <c r="E41" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -2530,7 +2529,7 @@
         <v>37</v>
       </c>
       <c r="E42" t="n">
-        <v>-59</v>
+        <v>-153</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -2581,7 +2580,7 @@
         <v>35</v>
       </c>
       <c r="E43" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2632,7 +2631,7 @@
         <v>-0</v>
       </c>
       <c r="E44" t="n">
-        <v>-765</v>
+        <v>-781</v>
       </c>
       <c r="F44" t="n">
         <v>-44</v>
@@ -2683,7 +2682,7 @@
         <v>-14</v>
       </c>
       <c r="E45" t="n">
-        <v>-24</v>
+        <v>-13</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2734,7 +2733,7 @@
         <v>-28</v>
       </c>
       <c r="E46" t="n">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2785,7 +2784,7 @@
         <v>-49</v>
       </c>
       <c r="E47" t="n">
-        <v>-170</v>
+        <v>-99</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -2836,7 +2835,7 @@
         <v>-62</v>
       </c>
       <c r="E48" t="n">
-        <v>664</v>
+        <v>586</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -2887,7 +2886,7 @@
         <v>-109</v>
       </c>
       <c r="E49" t="n">
-        <v>642</v>
+        <v>570</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -2938,7 +2937,7 @@
         <v>-134</v>
       </c>
       <c r="E50" t="n">
-        <v>1430</v>
+        <v>1441</v>
       </c>
       <c r="F50" t="n">
         <v>34</v>
@@ -2989,7 +2988,7 @@
         <v>-167</v>
       </c>
       <c r="E51" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -3040,7 +3039,7 @@
         <v>-278</v>
       </c>
       <c r="E52" t="n">
-        <v>490</v>
+        <v>537</v>
       </c>
       <c r="F52" t="n">
         <v>-1</v>
@@ -3091,7 +3090,7 @@
         <v>-288</v>
       </c>
       <c r="E53" t="n">
-        <v>-1305</v>
+        <v>-662</v>
       </c>
       <c r="F53" t="n">
         <v>-2176</v>
@@ -3142,7 +3141,7 @@
         <v>-384</v>
       </c>
       <c r="E54" t="n">
-        <v>-851</v>
+        <v>-741</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -3193,7 +3192,7 @@
         <v>-409</v>
       </c>
       <c r="E55" t="n">
-        <v>-1279</v>
+        <v>-1042</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3244,7 +3243,7 @@
         <v>-442</v>
       </c>
       <c r="E56" t="n">
-        <v>1550</v>
+        <v>953</v>
       </c>
       <c r="F56" t="n">
         <v>-247</v>
@@ -3295,7 +3294,7 @@
         <v>-483</v>
       </c>
       <c r="E57" t="n">
-        <v>-403</v>
+        <v>-622</v>
       </c>
       <c r="F57" t="n">
         <v>12</v>
@@ -3346,7 +3345,7 @@
         <v>-802</v>
       </c>
       <c r="E58" t="n">
-        <v>2401</v>
+        <v>2479</v>
       </c>
       <c r="F58" t="n">
         <v>-86</v>
@@ -3397,7 +3396,7 @@
         <v>-936</v>
       </c>
       <c r="E59" t="n">
-        <v>-1791</v>
+        <v>-989</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -3448,7 +3447,7 @@
         <v>-954</v>
       </c>
       <c r="E60" t="n">
-        <v>-4562</v>
+        <v>-990</v>
       </c>
       <c r="F60" t="n">
         <v>4</v>
@@ -3499,7 +3498,7 @@
         <v>-969</v>
       </c>
       <c r="E61" t="n">
-        <v>799</v>
+        <v>1080</v>
       </c>
       <c r="F61" t="n">
         <v>-864</v>
@@ -3538,7 +3537,7 @@
         <v>-1036</v>
       </c>
       <c r="E62" t="n">
-        <v>-2738</v>
+        <v>-2419</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -3589,7 +3588,7 @@
         <v>-1106</v>
       </c>
       <c r="E63" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -3640,7 +3639,7 @@
         <v>-1147</v>
       </c>
       <c r="E64" t="n">
-        <v>-2748</v>
+        <v>-3094</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -3691,7 +3690,7 @@
         <v>-1255</v>
       </c>
       <c r="E65" t="n">
-        <v>-1525</v>
+        <v>-300</v>
       </c>
       <c r="F65" t="n">
         <v>-170</v>
@@ -3742,7 +3741,7 @@
         <v>-1318</v>
       </c>
       <c r="E66" t="n">
-        <v>-1269</v>
+        <v>-479</v>
       </c>
       <c r="F66" t="n">
         <v>75</v>
@@ -3793,7 +3792,7 @@
         <v>-1329</v>
       </c>
       <c r="E67" t="n">
-        <v>-1928</v>
+        <v>-1897</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -3844,7 +3843,7 @@
         <v>-1615</v>
       </c>
       <c r="E68" t="n">
-        <v>339</v>
+        <v>214</v>
       </c>
       <c r="F68" t="n">
         <v>-848</v>
@@ -3895,7 +3894,7 @@
         <v>-1663</v>
       </c>
       <c r="E69" t="n">
-        <v>-7935</v>
+        <v>-7420</v>
       </c>
       <c r="F69" t="n">
         <v>299</v>
@@ -3946,7 +3945,7 @@
         <v>-1714</v>
       </c>
       <c r="E70" t="n">
-        <v>996</v>
+        <v>1093</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -3976,7 +3975,7 @@
         </is>
       </c>
       <c r="M70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -3997,7 +3996,7 @@
         <v>-1740</v>
       </c>
       <c r="E71" t="n">
-        <v>-969</v>
+        <v>-1237</v>
       </c>
       <c r="F71" t="n">
         <v>8</v>
@@ -4048,7 +4047,7 @@
         <v>-1878</v>
       </c>
       <c r="E72" t="n">
-        <v>1553</v>
+        <v>690</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -4099,7 +4098,7 @@
         <v>-1910</v>
       </c>
       <c r="E73" t="n">
-        <v>-7489</v>
+        <v>-7503</v>
       </c>
       <c r="F73" t="n">
         <v>-2646</v>
@@ -4150,7 +4149,7 @@
         <v>-1987</v>
       </c>
       <c r="E74" t="n">
-        <v>-3689</v>
+        <v>-3715</v>
       </c>
       <c r="F74" t="n">
         <v>2</v>
@@ -4201,7 +4200,7 @@
         <v>-2038</v>
       </c>
       <c r="E75" t="n">
-        <v>-2823</v>
+        <v>-2751</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -4252,7 +4251,7 @@
         <v>-2139</v>
       </c>
       <c r="E76" t="n">
-        <v>-7781</v>
+        <v>-7596</v>
       </c>
       <c r="F76" t="n">
         <v>436</v>
@@ -4303,7 +4302,7 @@
         <v>-2147</v>
       </c>
       <c r="E77" t="n">
-        <v>-16872</v>
+        <v>-15893</v>
       </c>
       <c r="F77" t="n">
         <v>-748</v>
@@ -4354,7 +4353,7 @@
         <v>-2192</v>
       </c>
       <c r="E78" t="n">
-        <v>-2694</v>
+        <v>-3043</v>
       </c>
       <c r="F78" t="n">
         <v>-220</v>
@@ -4405,7 +4404,7 @@
         <v>-2762</v>
       </c>
       <c r="E79" t="n">
-        <v>6366</v>
+        <v>4763</v>
       </c>
       <c r="F79" t="n">
         <v>277</v>
@@ -4435,7 +4434,7 @@
         </is>
       </c>
       <c r="M79" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="80">
@@ -4456,7 +4455,7 @@
         <v>-2902</v>
       </c>
       <c r="E80" t="n">
-        <v>-5288</v>
+        <v>-4867</v>
       </c>
       <c r="F80" t="n">
         <v>204</v>
@@ -4495,7 +4494,7 @@
         <v>-3096</v>
       </c>
       <c r="E81" t="n">
-        <v>-2124</v>
+        <v>-2887</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -4546,7 +4545,7 @@
         <v>-3224</v>
       </c>
       <c r="E82" t="n">
-        <v>-220</v>
+        <v>455</v>
       </c>
       <c r="F82" t="n">
         <v>-274</v>
@@ -4597,7 +4596,7 @@
         <v>-3984</v>
       </c>
       <c r="E83" t="n">
-        <v>-3821</v>
+        <v>-3801</v>
       </c>
       <c r="F83" t="n">
         <v>70</v>
@@ -4648,7 +4647,7 @@
         <v>-4288</v>
       </c>
       <c r="E84" t="n">
-        <v>-2598</v>
+        <v>-3079</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -4699,7 +4698,7 @@
         <v>-4295</v>
       </c>
       <c r="E85" t="n">
-        <v>-16587</v>
+        <v>-16706</v>
       </c>
       <c r="F85" t="n">
         <v>616</v>
@@ -4750,7 +4749,7 @@
         <v>-4557</v>
       </c>
       <c r="E86" t="n">
-        <v>-263</v>
+        <v>143</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -4801,7 +4800,7 @@
         <v>-5163</v>
       </c>
       <c r="E87" t="n">
-        <v>-31610</v>
+        <v>-28874</v>
       </c>
       <c r="F87" t="n">
         <v>185</v>
@@ -4852,7 +4851,7 @@
         <v>-5398</v>
       </c>
       <c r="E88" t="n">
-        <v>-15174</v>
+        <v>-12931</v>
       </c>
       <c r="F88" t="n">
         <v>-1</v>
@@ -4903,7 +4902,7 @@
         <v>-7091</v>
       </c>
       <c r="E89" t="n">
-        <v>-18093</v>
+        <v>-18085</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -4954,7 +4953,7 @@
         <v>-8534</v>
       </c>
       <c r="E90" t="n">
-        <v>-23567</v>
+        <v>-23417</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -5005,7 +5004,7 @@
         <v>-9147</v>
       </c>
       <c r="E91" t="n">
-        <v>-4688</v>
+        <v>-4033</v>
       </c>
       <c r="F91" t="n">
         <v>1286</v>
@@ -5056,7 +5055,7 @@
         <v>-10490</v>
       </c>
       <c r="E92" t="n">
-        <v>-108804</v>
+        <v>-94343</v>
       </c>
       <c r="F92" t="n">
         <v>-1623</v>
@@ -5107,7 +5106,7 @@
         <v>-10550</v>
       </c>
       <c r="E93" t="n">
-        <v>-43020</v>
+        <v>-40878</v>
       </c>
       <c r="F93" t="n">
         <v>5645</v>
@@ -5137,7 +5136,7 @@
         </is>
       </c>
       <c r="M93" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94">
@@ -5158,7 +5157,7 @@
         <v>-10720</v>
       </c>
       <c r="E94" t="n">
-        <v>-11716</v>
+        <v>-11750</v>
       </c>
       <c r="F94" t="n">
         <v>-3873</v>
@@ -5209,7 +5208,7 @@
         <v>-11185</v>
       </c>
       <c r="E95" t="n">
-        <v>-82164</v>
+        <v>-89583</v>
       </c>
       <c r="F95" t="n">
         <v>909</v>
@@ -5260,7 +5259,7 @@
         <v>-12058</v>
       </c>
       <c r="E96" t="n">
-        <v>72883</v>
+        <v>81101</v>
       </c>
       <c r="F96" t="n">
         <v>549</v>
@@ -5311,7 +5310,7 @@
         <v>-14666</v>
       </c>
       <c r="E97" t="n">
-        <v>6584</v>
+        <v>6028</v>
       </c>
       <c r="F97" t="n">
         <v>18</v>
@@ -5362,7 +5361,7 @@
         <v>-14690</v>
       </c>
       <c r="E98" t="n">
-        <v>-15323</v>
+        <v>-15697</v>
       </c>
       <c r="F98" t="n">
         <v>8508</v>
@@ -5413,7 +5412,7 @@
         <v>-15797</v>
       </c>
       <c r="E99" t="n">
-        <v>-74850</v>
+        <v>-74446</v>
       </c>
       <c r="F99" t="n">
         <v>1000</v>
@@ -5464,7 +5463,7 @@
         <v>-16741</v>
       </c>
       <c r="E100" t="n">
-        <v>-20197</v>
+        <v>-22934</v>
       </c>
       <c r="F100" t="n">
         <v>2081</v>
@@ -5503,7 +5502,7 @@
         <v>-21607</v>
       </c>
       <c r="E101" t="n">
-        <v>47422</v>
+        <v>48084</v>
       </c>
       <c r="F101" t="n">
         <v>-962</v>
@@ -5533,7 +5532,7 @@
         </is>
       </c>
       <c r="M101" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -5554,7 +5553,7 @@
         <v>-24136</v>
       </c>
       <c r="E102" t="n">
-        <v>77621</v>
+        <v>108642</v>
       </c>
       <c r="F102" t="n">
         <v>-1541</v>
@@ -5584,7 +5583,7 @@
         </is>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="103">
@@ -5605,7 +5604,7 @@
         <v>-30514</v>
       </c>
       <c r="E103" t="n">
-        <v>60936</v>
+        <v>89984</v>
       </c>
       <c r="F103" t="n">
         <v>1268</v>
@@ -5635,7 +5634,7 @@
         </is>
       </c>
       <c r="M103" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -5656,7 +5655,7 @@
         <v>-53584</v>
       </c>
       <c r="E104" t="n">
-        <v>36384</v>
+        <v>54013</v>
       </c>
       <c r="F104" t="n">
         <v>-19993</v>
@@ -5707,7 +5706,7 @@
         <v>-102323</v>
       </c>
       <c r="E105" t="n">
-        <v>150315</v>
+        <v>150472</v>
       </c>
       <c r="F105" t="n">
         <v>-10188</v>
@@ -5738,3015 +5737,6 @@
       </c>
       <c r="M105" t="n">
         <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G103"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>代號</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>訊號</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>外資5d</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>外資20d</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>外資5d(昨)</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>外資20d(昨)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>名稱</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 243 千股)</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>856656</v>
-      </c>
-      <c r="D2" t="n">
-        <v>900482</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1104270</v>
-      </c>
-      <c r="F2" t="n">
-        <v>657310</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>8996</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 1,149 千股)</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>205305</v>
-      </c>
-      <c r="D3" t="n">
-        <v>-4294919</v>
-      </c>
-      <c r="E3" t="n">
-        <v>433621</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-5443885</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>高力</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3653</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -576 千股)</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>-451517</v>
-      </c>
-      <c r="D4" t="n">
-        <v>221103</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-73880</v>
-      </c>
-      <c r="F4" t="n">
-        <v>797206</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>健策</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 550 千股)</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>-208489</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1277338</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-529108</v>
-      </c>
-      <c r="F5" t="n">
-        <v>727667</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>6139</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 960 千股)</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>-45118</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-2146666</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-468514</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-3106913</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>亞翔</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>8210</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 166 千股)</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>202665</v>
-      </c>
-      <c r="D7" t="n">
-        <v>725469</v>
-      </c>
-      <c r="E7" t="n">
-        <v>255444</v>
-      </c>
-      <c r="F7" t="n">
-        <v>559575</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>勤誠</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>6442</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 300 千股)</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>289755</v>
-      </c>
-      <c r="D8" t="n">
-        <v>746015</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-289923</v>
-      </c>
-      <c r="F8" t="n">
-        <v>445530</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>光聖</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 499 千股)</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>1347035</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1782349</v>
-      </c>
-      <c r="E9" t="n">
-        <v>736713</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1283710</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>6223</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -445 千股)</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>890115</v>
-      </c>
-      <c r="D10" t="n">
-        <v>704228</v>
-      </c>
-      <c r="E10" t="n">
-        <v>801689</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1149094</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>旺矽</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>3324</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -790 千股)</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>-22396</v>
-      </c>
-      <c r="D11" t="n">
-        <v>6596116</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-95588</v>
-      </c>
-      <c r="F11" t="n">
-        <v>7385846</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>雙鴻</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2330</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -9,168 千股)</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>6854883</v>
-      </c>
-      <c r="D12" t="n">
-        <v>-10489690</v>
-      </c>
-      <c r="E12" t="n">
-        <v>16316905</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-1321263</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>台積電</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 111 千股)</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>-822095</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-1909927</v>
-      </c>
-      <c r="E13" t="n">
-        <v>-337159</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-2021120</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -1,043 千股)</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>3314976</v>
-      </c>
-      <c r="D14" t="n">
-        <v>-10549554</v>
-      </c>
-      <c r="E14" t="n">
-        <v>2979169</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-9506146</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>台達電</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>6196</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 269 千股)</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>810296</v>
-      </c>
-      <c r="D15" t="n">
-        <v>3414062</v>
-      </c>
-      <c r="E15" t="n">
-        <v>553834</v>
-      </c>
-      <c r="F15" t="n">
-        <v>3144962</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>帆宣</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>5434</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 27 千股)</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>-216336</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-1255270</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-238998</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-1282699</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>崇越</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>3044</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -239 千股)</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>2137431</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1001763</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1643862</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1240800</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>健鼎</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>3583</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -143 千股)</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>-193762</v>
-      </c>
-      <c r="D18" t="n">
-        <v>-1714338</v>
-      </c>
-      <c r="E18" t="n">
-        <v>-80535</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-1570983</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>辛耘</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>6197</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 148 千股)</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>465384</v>
-      </c>
-      <c r="D19" t="n">
-        <v>-2038209</v>
-      </c>
-      <c r="E19" t="n">
-        <v>496352</v>
-      </c>
-      <c r="F19" t="n">
-        <v>-2186698</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>佳必琪</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2059</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 81 千股)</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>-142884</v>
-      </c>
-      <c r="D20" t="n">
-        <v>-30</v>
-      </c>
-      <c r="E20" t="n">
-        <v>-376315</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-81511</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>川湖</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>3008</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -51 千股)</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>-2026356</v>
-      </c>
-      <c r="D21" t="n">
-        <v>-1663379</v>
-      </c>
-      <c r="E21" t="n">
-        <v>-1844828</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-1612370</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>大立光</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2640</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 8 千股)</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>-38006</v>
-      </c>
-      <c r="D22" t="n">
-        <v>-14026</v>
-      </c>
-      <c r="E22" t="n">
-        <v>-49006</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-22326</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>大車隊</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>1513</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -2,794 千股)</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1399322</v>
-      </c>
-      <c r="D23" t="n">
-        <v>3166403</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1416939</v>
-      </c>
-      <c r="F23" t="n">
-        <v>5959965</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>中興電</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>1560</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 540 千股)</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1267578</v>
-      </c>
-      <c r="D24" t="n">
-        <v>3616333</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1126562</v>
-      </c>
-      <c r="F24" t="n">
-        <v>3076704</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>中砂</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>1519</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -869 千股)</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>-27210</v>
-      </c>
-      <c r="D25" t="n">
-        <v>-483259</v>
-      </c>
-      <c r="E25" t="n">
-        <v>126357</v>
-      </c>
-      <c r="F25" t="n">
-        <v>386108</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>華城</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>5340</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 94 千股)</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>-206144</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-4287585</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-510019</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-4381902</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>建榮</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>5519</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -301 千股)</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>-279758</v>
-      </c>
-      <c r="D27" t="n">
-        <v>-935960</v>
-      </c>
-      <c r="E27" t="n">
-        <v>31242</v>
-      </c>
-      <c r="F27" t="n">
-        <v>-634830</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>隆大</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>4506</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 12 千股)</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>-43746</v>
-      </c>
-      <c r="D28" t="n">
-        <v>-62178</v>
-      </c>
-      <c r="E28" t="n">
-        <v>-36083</v>
-      </c>
-      <c r="F28" t="n">
-        <v>-73785</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>崇友</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>3689</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -546 千股)</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>25002</v>
-      </c>
-      <c r="D29" t="n">
-        <v>-1036456</v>
-      </c>
-      <c r="E29" t="n">
-        <v>-41258</v>
-      </c>
-      <c r="F29" t="n">
-        <v>-490741</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>湧德</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>3029</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 236 千股)</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>2578779</v>
-      </c>
-      <c r="D30" t="n">
-        <v>532413</v>
-      </c>
-      <c r="E30" t="n">
-        <v>2493009</v>
-      </c>
-      <c r="F30" t="n">
-        <v>296409</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>零壹</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2421</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -4,636 千股)</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>1236188</v>
-      </c>
-      <c r="D31" t="n">
-        <v>10933721</v>
-      </c>
-      <c r="E31" t="n">
-        <v>1048634</v>
-      </c>
-      <c r="F31" t="n">
-        <v>15569444</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>建準</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2618</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -8,776 千股)</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>-3702664</v>
-      </c>
-      <c r="D32" t="n">
-        <v>2199194</v>
-      </c>
-      <c r="E32" t="n">
-        <v>12150162</v>
-      </c>
-      <c r="F32" t="n">
-        <v>10974847</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>長榮航</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>1215</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -332 千股)</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>-1788138</v>
-      </c>
-      <c r="D33" t="n">
-        <v>-3096045</v>
-      </c>
-      <c r="E33" t="n">
-        <v>-1488244</v>
-      </c>
-      <c r="F33" t="n">
-        <v>-2763764</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>卜蜂</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>5904</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -2,229 千股)</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>-7222163</v>
-      </c>
-      <c r="D34" t="n">
-        <v>-15797300</v>
-      </c>
-      <c r="E34" t="n">
-        <v>-7305075</v>
-      </c>
-      <c r="F34" t="n">
-        <v>-13568097</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>寶雅*</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>1232</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -8 千股)</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>50366</v>
-      </c>
-      <c r="D35" t="n">
-        <v>108329</v>
-      </c>
-      <c r="E35" t="n">
-        <v>76235</v>
-      </c>
-      <c r="F35" t="n">
-        <v>116039</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>大統益</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>6189</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 86 千股)</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>983347</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1344021</v>
-      </c>
-      <c r="E36" t="n">
-        <v>1152883</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1257988</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>豐藝</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>1618</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -858 千股)</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>251989</v>
-      </c>
-      <c r="D37" t="n">
-        <v>466236</v>
-      </c>
-      <c r="E37" t="n">
-        <v>400000</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1323793</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>合機</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>5478</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 22 千股)</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>-60410</v>
-      </c>
-      <c r="D38" t="n">
-        <v>-383756</v>
-      </c>
-      <c r="E38" t="n">
-        <v>-33026</v>
-      </c>
-      <c r="F38" t="n">
-        <v>-406120</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>智冠</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -331 千股)</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>-429712</v>
-      </c>
-      <c r="D39" t="n">
-        <v>-1615287</v>
-      </c>
-      <c r="E39" t="n">
-        <v>-391260</v>
-      </c>
-      <c r="F39" t="n">
-        <v>-1284074</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>3045</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -797 千股)</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>8648199</v>
-      </c>
-      <c r="D40" t="n">
-        <v>46352453</v>
-      </c>
-      <c r="E40" t="n">
-        <v>7976018</v>
-      </c>
-      <c r="F40" t="n">
-        <v>47149677</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>台灣大</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2753</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 48 千股)</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>31932</v>
-      </c>
-      <c r="D41" t="n">
-        <v>-134428</v>
-      </c>
-      <c r="E41" t="n">
-        <v>34848</v>
-      </c>
-      <c r="F41" t="n">
-        <v>-182662</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>八方雲集</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>2912</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -798 千股)</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>-2526228</v>
-      </c>
-      <c r="D42" t="n">
-        <v>-2761658</v>
-      </c>
-      <c r="E42" t="n">
-        <v>-1691852</v>
-      </c>
-      <c r="F42" t="n">
-        <v>-1963623</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>統一超</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>3402</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 41 千股)</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>289823</v>
-      </c>
-      <c r="D43" t="n">
-        <v>385914</v>
-      </c>
-      <c r="E43" t="n">
-        <v>316483</v>
-      </c>
-      <c r="F43" t="n">
-        <v>344594</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>漢科</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>1514</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -921 千股)</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>412259</v>
-      </c>
-      <c r="D44" t="n">
-        <v>-953982</v>
-      </c>
-      <c r="E44" t="n">
-        <v>1102129</v>
-      </c>
-      <c r="F44" t="n">
-        <v>-33337</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>亞力</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>3147</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -6 千股)</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>201355</v>
-      </c>
-      <c r="D45" t="n">
-        <v>299830</v>
-      </c>
-      <c r="E45" t="n">
-        <v>280647</v>
-      </c>
-      <c r="F45" t="n">
-        <v>305332</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>大綜</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>6788</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -74 千股)</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>94096</v>
-      </c>
-      <c r="D46" t="n">
-        <v>-278078</v>
-      </c>
-      <c r="E46" t="n">
-        <v>58454</v>
-      </c>
-      <c r="F46" t="n">
-        <v>-203867</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>華景電</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 1,293 千股)</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>2394374</v>
-      </c>
-      <c r="D47" t="n">
-        <v>10295883</v>
-      </c>
-      <c r="E47" t="n">
-        <v>4209385</v>
-      </c>
-      <c r="F47" t="n">
-        <v>9002612</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>台燿</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>4129</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 319 千股)</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>-169000</v>
-      </c>
-      <c r="D48" t="n">
-        <v>-1329405</v>
-      </c>
-      <c r="E48" t="n">
-        <v>-149072</v>
-      </c>
-      <c r="F48" t="n">
-        <v>-1648405</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>聯合</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>3406</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -1,163 千股)</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>-2780380</v>
-      </c>
-      <c r="D49" t="n">
-        <v>-3983562</v>
-      </c>
-      <c r="E49" t="n">
-        <v>-3650944</v>
-      </c>
-      <c r="F49" t="n">
-        <v>-2820375</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>玉晶光</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>3260</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -1,806 千股)</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>-2168260</v>
-      </c>
-      <c r="D50" t="n">
-        <v>-14666067</v>
-      </c>
-      <c r="E50" t="n">
-        <v>-1004107</v>
-      </c>
-      <c r="F50" t="n">
-        <v>-12860211</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>威剛</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2472</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 77 千股)</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>-343523</v>
-      </c>
-      <c r="D51" t="n">
-        <v>3888813</v>
-      </c>
-      <c r="E51" t="n">
-        <v>-48825</v>
-      </c>
-      <c r="F51" t="n">
-        <v>3811875</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>立隆電</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 2,972 千股)</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>8376114</v>
-      </c>
-      <c r="D52" t="n">
-        <v>-11184678</v>
-      </c>
-      <c r="E52" t="n">
-        <v>4190684</v>
-      </c>
-      <c r="F52" t="n">
-        <v>-14156943</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>國巨*</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2408</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -50,086 千股)</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>14909059</v>
-      </c>
-      <c r="D53" t="n">
-        <v>-30513770</v>
-      </c>
-      <c r="E53" t="n">
-        <v>35170358</v>
-      </c>
-      <c r="F53" t="n">
-        <v>19572477</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>南亞科</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>3661</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 68 千股)</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>2539038</v>
-      </c>
-      <c r="D54" t="n">
-        <v>-288033</v>
-      </c>
-      <c r="E54" t="n">
-        <v>2258443</v>
-      </c>
-      <c r="F54" t="n">
-        <v>-355837</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>世芯-KY</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>3293</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 2,707 千股)</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>3559484</v>
-      </c>
-      <c r="D55" t="n">
-        <v>6434832</v>
-      </c>
-      <c r="E55" t="n">
-        <v>1469617</v>
-      </c>
-      <c r="F55" t="n">
-        <v>3727896</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>鈊象</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>1503</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -887 千股)</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>-462160</v>
-      </c>
-      <c r="D56" t="n">
-        <v>-1317827</v>
-      </c>
-      <c r="E56" t="n">
-        <v>-346607</v>
-      </c>
-      <c r="F56" t="n">
-        <v>-431004</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>士電</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>3711</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 99 千股)</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>26732575</v>
-      </c>
-      <c r="D57" t="n">
-        <v>48073253</v>
-      </c>
-      <c r="E57" t="n">
-        <v>27289613</v>
-      </c>
-      <c r="F57" t="n">
-        <v>47974306</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2535</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -149 千股)</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>153587</v>
-      </c>
-      <c r="D58" t="n">
-        <v>-49145</v>
-      </c>
-      <c r="E58" t="n">
-        <v>253964</v>
-      </c>
-      <c r="F58" t="n">
-        <v>99577</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>達欣工</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2476</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -543 千股)</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>622036</v>
-      </c>
-      <c r="D59" t="n">
-        <v>-1147020</v>
-      </c>
-      <c r="E59" t="n">
-        <v>547879</v>
-      </c>
-      <c r="F59" t="n">
-        <v>-604205</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>鉅祥</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>6263</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -14 千股)</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>96845</v>
-      </c>
-      <c r="D60" t="n">
-        <v>290969</v>
-      </c>
-      <c r="E60" t="n">
-        <v>69359</v>
-      </c>
-      <c r="F60" t="n">
-        <v>304918</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>普萊德</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>1590</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -18 千股)</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>-899782</v>
-      </c>
-      <c r="D61" t="n">
-        <v>-1740018</v>
-      </c>
-      <c r="E61" t="n">
-        <v>-1051618</v>
-      </c>
-      <c r="F61" t="n">
-        <v>-1722083</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>亞德客-KY</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>1773</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -104 千股)</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>-396690</v>
-      </c>
-      <c r="D62" t="n">
-        <v>-1986981</v>
-      </c>
-      <c r="E62" t="n">
-        <v>-113800</v>
-      </c>
-      <c r="F62" t="n">
-        <v>-1882640</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>勝一</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>4303</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -278 千股)</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>160580</v>
-      </c>
-      <c r="D63" t="n">
-        <v>-1106143</v>
-      </c>
-      <c r="E63" t="n">
-        <v>79327</v>
-      </c>
-      <c r="F63" t="n">
-        <v>-828279</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>信立</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>5269</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -134 千股)</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>383435</v>
-      </c>
-      <c r="D64" t="n">
-        <v>815215</v>
-      </c>
-      <c r="E64" t="n">
-        <v>640341</v>
-      </c>
-      <c r="F64" t="n">
-        <v>949146</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>祥碩</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>4979</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 969 千股)</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>371735</v>
-      </c>
-      <c r="D65" t="n">
-        <v>637174</v>
-      </c>
-      <c r="E65" t="n">
-        <v>49659</v>
-      </c>
-      <c r="F65" t="n">
-        <v>-331944</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>華星光</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>6446</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -562 千股)</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>-11014340</v>
-      </c>
-      <c r="D66" t="n">
-        <v>-14690337</v>
-      </c>
-      <c r="E66" t="n">
-        <v>-11122629</v>
-      </c>
-      <c r="F66" t="n">
-        <v>-14128811</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>藥華藥</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>8271</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -1,439 千股)</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>-1040896</v>
-      </c>
-      <c r="D67" t="n">
-        <v>-4556532</v>
-      </c>
-      <c r="E67" t="n">
-        <v>-1903465</v>
-      </c>
-      <c r="F67" t="n">
-        <v>-3117865</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>宇瞻</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>3450</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -1,162 千股)</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>-5345409</v>
-      </c>
-      <c r="D68" t="n">
-        <v>-9147034</v>
-      </c>
-      <c r="E68" t="n">
-        <v>-7718362</v>
-      </c>
-      <c r="F68" t="n">
-        <v>-7985353</v>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>聯鈞</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2382</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -7,154 千股)</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>-15842819</v>
-      </c>
-      <c r="D69" t="n">
-        <v>7589057</v>
-      </c>
-      <c r="E69" t="n">
-        <v>-7399669</v>
-      </c>
-      <c r="F69" t="n">
-        <v>14742997</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>廣達</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>3081</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 42 千股)</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>-1325075</v>
-      </c>
-      <c r="D70" t="n">
-        <v>-2138671</v>
-      </c>
-      <c r="E70" t="n">
-        <v>-2232416</v>
-      </c>
-      <c r="F70" t="n">
-        <v>-2181048</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>聯亞</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>3231</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 14,561 千股)</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>-28100187</v>
-      </c>
-      <c r="D71" t="n">
-        <v>-102323096</v>
-      </c>
-      <c r="E71" t="n">
-        <v>-27146875</v>
-      </c>
-      <c r="F71" t="n">
-        <v>-116883701</v>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>緯創</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2379</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -831 千股)</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>4778830</v>
-      </c>
-      <c r="D72" t="n">
-        <v>6612945</v>
-      </c>
-      <c r="E72" t="n">
-        <v>7227888</v>
-      </c>
-      <c r="F72" t="n">
-        <v>7444172</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>瑞昱</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2301</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 3,505 千股)</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>-2961794</v>
-      </c>
-      <c r="D73" t="n">
-        <v>-21607041</v>
-      </c>
-      <c r="E73" t="n">
-        <v>-3202892</v>
-      </c>
-      <c r="F73" t="n">
-        <v>-25111868</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>光寶科</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>8926</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -163 千股)</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>-243563</v>
-      </c>
-      <c r="D74" t="n">
-        <v>-5163387</v>
-      </c>
-      <c r="E74" t="n">
-        <v>-93213</v>
-      </c>
-      <c r="F74" t="n">
-        <v>-5000266</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>台汽電</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>5511</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 22 千股)</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>14420</v>
-      </c>
-      <c r="D75" t="n">
-        <v>-409360</v>
-      </c>
-      <c r="E75" t="n">
-        <v>20846</v>
-      </c>
-      <c r="F75" t="n">
-        <v>-431360</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>德昌</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>1616</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -230 千股)</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>256691</v>
-      </c>
-      <c r="D76" t="n">
-        <v>561858</v>
-      </c>
-      <c r="E76" t="n">
-        <v>429350</v>
-      </c>
-      <c r="F76" t="n">
-        <v>791450</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>億泰</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>4933</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 8 千股)</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>78929</v>
-      </c>
-      <c r="D77" t="n">
-        <v>36929</v>
-      </c>
-      <c r="E77" t="n">
-        <v>95929</v>
-      </c>
-      <c r="F77" t="n">
-        <v>28929</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>友輝</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>3596</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 163 千股)</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>-1421985</v>
-      </c>
-      <c r="D78" t="n">
-        <v>-7091035</v>
-      </c>
-      <c r="E78" t="n">
-        <v>-1240915</v>
-      </c>
-      <c r="F78" t="n">
-        <v>-7254082</v>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>智易</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>6285</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 1,317 千股)</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>1150106</v>
-      </c>
-      <c r="D79" t="n">
-        <v>918178</v>
-      </c>
-      <c r="E79" t="n">
-        <v>875028</v>
-      </c>
-      <c r="F79" t="n">
-        <v>-398855</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>啟碁</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>3227</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -116 千股)</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>-454251</v>
-      </c>
-      <c r="D80" t="n">
-        <v>-3223792</v>
-      </c>
-      <c r="E80" t="n">
-        <v>-687251</v>
-      </c>
-      <c r="F80" t="n">
-        <v>-3107789</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>原相</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>2356</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 569 千股)</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>-11141148</v>
-      </c>
-      <c r="D81" t="n">
-        <v>-24135641</v>
-      </c>
-      <c r="E81" t="n">
-        <v>-6953167</v>
-      </c>
-      <c r="F81" t="n">
-        <v>-24704220</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>英業達</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>6510</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 27 千股)</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>-662474</v>
-      </c>
-      <c r="D82" t="n">
-        <v>-2192005</v>
-      </c>
-      <c r="E82" t="n">
-        <v>-766312</v>
-      </c>
-      <c r="F82" t="n">
-        <v>-2218710</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>精測</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>2317</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -42,122 千股)</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>-23601689</v>
-      </c>
-      <c r="D83" t="n">
-        <v>-12058135</v>
-      </c>
-      <c r="E83" t="n">
-        <v>9151152</v>
-      </c>
-      <c r="F83" t="n">
-        <v>30063426</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>鴻海</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>5243</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -350 千股)</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>-411608</v>
-      </c>
-      <c r="D84" t="n">
-        <v>-1877856</v>
-      </c>
-      <c r="E84" t="n">
-        <v>-139616</v>
-      </c>
-      <c r="F84" t="n">
-        <v>-1528106</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>乙盛-KY</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>3188</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -109 千股)</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>-157000</v>
-      </c>
-      <c r="D85" t="n">
-        <v>-109254</v>
-      </c>
-      <c r="E85" t="n">
-        <v>-105000</v>
-      </c>
-      <c r="F85" t="n">
-        <v>9</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>鑫龍騰</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>5225</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -28 千股)</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>202735</v>
-      </c>
-      <c r="D86" t="n">
-        <v>673996</v>
-      </c>
-      <c r="E86" t="n">
-        <v>195735</v>
-      </c>
-      <c r="F86" t="n">
-        <v>702279</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>東科-KY</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>2305</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 545 千股)</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>4462026</v>
-      </c>
-      <c r="D87" t="n">
-        <v>8728469</v>
-      </c>
-      <c r="E87" t="n">
-        <v>5582976</v>
-      </c>
-      <c r="F87" t="n">
-        <v>8183932</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>全友</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>2395</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 838 千股)</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>2439047</v>
-      </c>
-      <c r="D88" t="n">
-        <v>6460637</v>
-      </c>
-      <c r="E88" t="n">
-        <v>3179412</v>
-      </c>
-      <c r="F88" t="n">
-        <v>5622742</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>研華</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>2412</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 3,230 千股)</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>17401231</v>
-      </c>
-      <c r="D89" t="n">
-        <v>91921249</v>
-      </c>
-      <c r="E89" t="n">
-        <v>24582760</v>
-      </c>
-      <c r="F89" t="n">
-        <v>88691137</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>中華電</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>9917</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -202 千股)</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>98176</v>
-      </c>
-      <c r="D90" t="n">
-        <v>-802488</v>
-      </c>
-      <c r="E90" t="n">
-        <v>263622</v>
-      </c>
-      <c r="F90" t="n">
-        <v>-600356</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>中保科</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>6739</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>🔴 外資 5d 翻紅 / 📉 20d 巨變(減碼 -47 千股)</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>-15921</v>
-      </c>
-      <c r="D91" t="n">
-        <v>-166694</v>
-      </c>
-      <c r="E91" t="n">
-        <v>4915</v>
-      </c>
-      <c r="F91" t="n">
-        <v>-119759</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>竹陞科技</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>2645</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -299 千股)</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>-342589</v>
-      </c>
-      <c r="D92" t="n">
-        <v>-5397961</v>
-      </c>
-      <c r="E92" t="n">
-        <v>-120195</v>
-      </c>
-      <c r="F92" t="n">
-        <v>-5099458</v>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>長榮航太</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>6690</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -27 千股)</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>29432</v>
-      </c>
-      <c r="D93" t="n">
-        <v>53059</v>
-      </c>
-      <c r="E93" t="n">
-        <v>72442</v>
-      </c>
-      <c r="F93" t="n">
-        <v>80059</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>安碁資訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>4904</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -1,118 千股)</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>592109</v>
-      </c>
-      <c r="D94" t="n">
-        <v>13022540</v>
-      </c>
-      <c r="E94" t="n">
-        <v>1132718</v>
-      </c>
-      <c r="F94" t="n">
-        <v>14140399</v>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>遠傳</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>2344</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -47,956 千股)</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>19645741</v>
-      </c>
-      <c r="D95" t="n">
-        <v>-53584173</v>
-      </c>
-      <c r="E95" t="n">
-        <v>27224635</v>
-      </c>
-      <c r="F95" t="n">
-        <v>-5627928</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>2454</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 1,073 千股)</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>8907830</v>
-      </c>
-      <c r="D96" t="n">
-        <v>13969997</v>
-      </c>
-      <c r="E96" t="n">
-        <v>8381759</v>
-      </c>
-      <c r="F96" t="n">
-        <v>12896722</v>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>8086</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -842 千股)</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>-257300</v>
-      </c>
-      <c r="D97" t="n">
-        <v>-8534257</v>
-      </c>
-      <c r="E97" t="n">
-        <v>-228481</v>
-      </c>
-      <c r="F97" t="n">
-        <v>-7692023</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>宏捷科</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>3443</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 27 千股)</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>245622</v>
-      </c>
-      <c r="D98" t="n">
-        <v>-442387</v>
-      </c>
-      <c r="E98" t="n">
-        <v>-281720</v>
-      </c>
-      <c r="F98" t="n">
-        <v>-468980</v>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>創意</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 350 千股)</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>1174981</v>
-      </c>
-      <c r="D99" t="n">
-        <v>-10719826</v>
-      </c>
-      <c r="E99" t="n">
-        <v>1194409</v>
-      </c>
-      <c r="F99" t="n">
-        <v>-11069427</v>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>5274</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>📈 20d 巨變(加碼 26 千股)</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>112229</v>
-      </c>
-      <c r="D100" t="n">
-        <v>141950</v>
-      </c>
-      <c r="E100" t="n">
-        <v>39242</v>
-      </c>
-      <c r="F100" t="n">
-        <v>115909</v>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>信驊</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>📉 20d 巨變(減碼 -2,458 千股)</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>-6922947</v>
-      </c>
-      <c r="D101" t="n">
-        <v>-16741073</v>
-      </c>
-      <c r="E101" t="n">
-        <v>-7948625</v>
-      </c>
-      <c r="F101" t="n">
-        <v>-14282925</v>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>金像電</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>5439</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>🟢 外資 5d 翻綠 / 📈 20d 巨變(加碼 133 千股)</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>119778</v>
-      </c>
-      <c r="D102" t="n">
-        <v>-2902119</v>
-      </c>
-      <c r="E102" t="n">
-        <v>-116755</v>
-      </c>
-      <c r="F102" t="n">
-        <v>-3035457</v>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>高技</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>🟢 外資 5d 翻綠 / 📉 20d 巨變(減碼 -393 千股)</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>51839</v>
-      </c>
-      <c r="D103" t="n">
-        <v>-968889</v>
-      </c>
-      <c r="E103" t="n">
-        <v>-410444</v>
-      </c>
-      <c r="F103" t="n">
-        <v>-575692</v>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/data/台股_外資雷達.xlsx
+++ b/data/台股_外資雷達.xlsx
@@ -501,7 +501,7 @@
         <v>91921</v>
       </c>
       <c r="E2" t="n">
-        <v>183753</v>
+        <v>184135</v>
       </c>
       <c r="F2" t="n">
         <v>276</v>
@@ -552,7 +552,7 @@
         <v>48073</v>
       </c>
       <c r="E3" t="n">
-        <v>26432</v>
+        <v>22159</v>
       </c>
       <c r="F3" t="n">
         <v>-3299</v>
@@ -603,7 +603,7 @@
         <v>46352</v>
       </c>
       <c r="E4" t="n">
-        <v>186749</v>
+        <v>184164</v>
       </c>
       <c r="F4" t="n">
         <v>1723</v>
@@ -654,7 +654,7 @@
         <v>13970</v>
       </c>
       <c r="E5" t="n">
-        <v>16260</v>
+        <v>17571</v>
       </c>
       <c r="F5" t="n">
         <v>259</v>
@@ -705,7 +705,7 @@
         <v>13023</v>
       </c>
       <c r="E6" t="n">
-        <v>99851</v>
+        <v>98838</v>
       </c>
       <c r="F6" t="n">
         <v>549</v>
@@ -756,7 +756,7 @@
         <v>10934</v>
       </c>
       <c r="E7" t="n">
-        <v>25430</v>
+        <v>25120</v>
       </c>
       <c r="F7" t="n">
         <v>-165</v>
@@ -807,7 +807,7 @@
         <v>10296</v>
       </c>
       <c r="E8" t="n">
-        <v>1825</v>
+        <v>874</v>
       </c>
       <c r="F8" t="n">
         <v>-4665</v>
@@ -858,7 +858,7 @@
         <v>8728</v>
       </c>
       <c r="E9" t="n">
-        <v>1641</v>
+        <v>3265</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -909,7 +909,7 @@
         <v>7589</v>
       </c>
       <c r="E10" t="n">
-        <v>-7760</v>
+        <v>-3142</v>
       </c>
       <c r="F10" t="n">
         <v>9819</v>
@@ -960,7 +960,7 @@
         <v>6613</v>
       </c>
       <c r="E11" t="n">
-        <v>3954</v>
+        <v>4241</v>
       </c>
       <c r="F11" t="n">
         <v>545</v>
@@ -1011,7 +1011,7 @@
         <v>6596</v>
       </c>
       <c r="E12" t="n">
-        <v>12377</v>
+        <v>12665</v>
       </c>
       <c r="F12" t="n">
         <v>906</v>
@@ -1062,7 +1062,7 @@
         <v>6461</v>
       </c>
       <c r="E13" t="n">
-        <v>3229</v>
+        <v>3182</v>
       </c>
       <c r="F13" t="n">
         <v>-456</v>
@@ -1113,7 +1113,7 @@
         <v>6435</v>
       </c>
       <c r="E14" t="n">
-        <v>15036</v>
+        <v>15695</v>
       </c>
       <c r="F14" t="n">
         <v>421</v>
@@ -1164,7 +1164,7 @@
         <v>3889</v>
       </c>
       <c r="E15" t="n">
-        <v>10243</v>
+        <v>11172</v>
       </c>
       <c r="F15" t="n">
         <v>-1324</v>
@@ -1215,7 +1215,7 @@
         <v>3616</v>
       </c>
       <c r="E16" t="n">
-        <v>2271</v>
+        <v>1426</v>
       </c>
       <c r="F16" t="n">
         <v>1028</v>
@@ -1266,7 +1266,7 @@
         <v>3414</v>
       </c>
       <c r="E17" t="n">
-        <v>5746</v>
+        <v>5398</v>
       </c>
       <c r="F17" t="n">
         <v>-62</v>
@@ -1317,7 +1317,7 @@
         <v>3166</v>
       </c>
       <c r="E18" t="n">
-        <v>25539</v>
+        <v>24795</v>
       </c>
       <c r="F18" t="n">
         <v>828</v>
@@ -1368,7 +1368,7 @@
         <v>2199</v>
       </c>
       <c r="E19" t="n">
-        <v>359651</v>
+        <v>335514</v>
       </c>
       <c r="F19" t="n">
         <v>25838</v>
@@ -1419,7 +1419,7 @@
         <v>1782</v>
       </c>
       <c r="E20" t="n">
-        <v>-3198</v>
+        <v>-3151</v>
       </c>
       <c r="F20" t="n">
         <v>-762</v>
@@ -1470,7 +1470,7 @@
         <v>1344</v>
       </c>
       <c r="E21" t="n">
-        <v>3628</v>
+        <v>3432</v>
       </c>
       <c r="F21" t="n">
         <v>-7</v>
@@ -1521,7 +1521,7 @@
         <v>1277</v>
       </c>
       <c r="E22" t="n">
-        <v>5231</v>
+        <v>5155</v>
       </c>
       <c r="F22" t="n">
         <v>318</v>
@@ -1572,7 +1572,7 @@
         <v>1002</v>
       </c>
       <c r="E23" t="n">
-        <v>-8981</v>
+        <v>-8861</v>
       </c>
       <c r="F23" t="n">
         <v>58</v>
@@ -1623,7 +1623,7 @@
         <v>918</v>
       </c>
       <c r="E24" t="n">
-        <v>1040</v>
+        <v>668</v>
       </c>
       <c r="F24" t="n">
         <v>7</v>
@@ -1674,7 +1674,7 @@
         <v>900</v>
       </c>
       <c r="E25" t="n">
-        <v>-227</v>
+        <v>-172</v>
       </c>
       <c r="F25" t="n">
         <v>-2441</v>
@@ -1725,7 +1725,7 @@
         <v>815</v>
       </c>
       <c r="E26" t="n">
-        <v>2260</v>
+        <v>2267</v>
       </c>
       <c r="F26" t="n">
         <v>7</v>
@@ -1776,7 +1776,7 @@
         <v>746</v>
       </c>
       <c r="E27" t="n">
-        <v>-2855</v>
+        <v>-2620</v>
       </c>
       <c r="F27" t="n">
         <v>-1274</v>
@@ -1827,7 +1827,7 @@
         <v>725</v>
       </c>
       <c r="E28" t="n">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="F28" t="n">
         <v>-800</v>
@@ -1878,7 +1878,7 @@
         <v>704</v>
       </c>
       <c r="E29" t="n">
-        <v>-653</v>
+        <v>-546</v>
       </c>
       <c r="F29" t="n">
         <v>-1308</v>
@@ -1929,7 +1929,7 @@
         <v>674</v>
       </c>
       <c r="E30" t="n">
-        <v>-28</v>
+        <v>-78</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1980,7 +1980,7 @@
         <v>637</v>
       </c>
       <c r="E31" t="n">
-        <v>-2688</v>
+        <v>-2788</v>
       </c>
       <c r="F31" t="n">
         <v>-2943</v>
@@ -2031,7 +2031,7 @@
         <v>562</v>
       </c>
       <c r="E32" t="n">
-        <v>1226</v>
+        <v>1197</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -2082,7 +2082,7 @@
         <v>532</v>
       </c>
       <c r="E33" t="n">
-        <v>7237</v>
+        <v>6905</v>
       </c>
       <c r="F33" t="n">
         <v>-2</v>
@@ -2133,7 +2133,7 @@
         <v>466</v>
       </c>
       <c r="E34" t="n">
-        <v>3515</v>
+        <v>3467</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -2184,7 +2184,7 @@
         <v>386</v>
       </c>
       <c r="E35" t="n">
-        <v>-1753</v>
+        <v>-2201</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -2235,7 +2235,7 @@
         <v>300</v>
       </c>
       <c r="E36" t="n">
-        <v>577</v>
+        <v>531</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -2286,7 +2286,7 @@
         <v>291</v>
       </c>
       <c r="E37" t="n">
-        <v>1171</v>
+        <v>1194</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -2337,7 +2337,7 @@
         <v>221</v>
       </c>
       <c r="E38" t="n">
-        <v>-1317</v>
+        <v>-1264</v>
       </c>
       <c r="F38" t="n">
         <v>347</v>
@@ -2388,7 +2388,7 @@
         <v>142</v>
       </c>
       <c r="E39" t="n">
-        <v>-385</v>
+        <v>-335</v>
       </c>
       <c r="F39" t="n">
         <v>-25</v>
@@ -2427,7 +2427,7 @@
         <v>108</v>
       </c>
       <c r="E40" t="n">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -2478,7 +2478,7 @@
         <v>53</v>
       </c>
       <c r="E41" t="n">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -2529,7 +2529,7 @@
         <v>37</v>
       </c>
       <c r="E42" t="n">
-        <v>-153</v>
+        <v>-158</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>-0</v>
       </c>
       <c r="E44" t="n">
-        <v>-781</v>
+        <v>-672</v>
       </c>
       <c r="F44" t="n">
         <v>-44</v>
@@ -2682,7 +2682,7 @@
         <v>-14</v>
       </c>
       <c r="E45" t="n">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2733,7 +2733,7 @@
         <v>-28</v>
       </c>
       <c r="E46" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2784,7 +2784,7 @@
         <v>-49</v>
       </c>
       <c r="E47" t="n">
-        <v>-99</v>
+        <v>-101</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>-62</v>
       </c>
       <c r="E48" t="n">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="F48" t="n">
         <v>0</v>
@@ -2886,7 +2886,7 @@
         <v>-109</v>
       </c>
       <c r="E49" t="n">
-        <v>570</v>
+        <v>547</v>
       </c>
       <c r="F49" t="n">
         <v>0</v>
@@ -2937,7 +2937,7 @@
         <v>-134</v>
       </c>
       <c r="E50" t="n">
-        <v>1441</v>
+        <v>1393</v>
       </c>
       <c r="F50" t="n">
         <v>34</v>
@@ -2988,7 +2988,7 @@
         <v>-167</v>
       </c>
       <c r="E51" t="n">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="F51" t="n">
         <v>0</v>
@@ -3039,7 +3039,7 @@
         <v>-278</v>
       </c>
       <c r="E52" t="n">
-        <v>537</v>
+        <v>511</v>
       </c>
       <c r="F52" t="n">
         <v>-1</v>
@@ -3090,7 +3090,7 @@
         <v>-288</v>
       </c>
       <c r="E53" t="n">
-        <v>-662</v>
+        <v>-648</v>
       </c>
       <c r="F53" t="n">
         <v>-2176</v>
@@ -3141,7 +3141,7 @@
         <v>-384</v>
       </c>
       <c r="E54" t="n">
-        <v>-741</v>
+        <v>-739</v>
       </c>
       <c r="F54" t="n">
         <v>0</v>
@@ -3192,7 +3192,7 @@
         <v>-409</v>
       </c>
       <c r="E55" t="n">
-        <v>-1042</v>
+        <v>-991</v>
       </c>
       <c r="F55" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>-442</v>
       </c>
       <c r="E56" t="n">
-        <v>953</v>
+        <v>1015</v>
       </c>
       <c r="F56" t="n">
         <v>-247</v>
@@ -3294,7 +3294,7 @@
         <v>-483</v>
       </c>
       <c r="E57" t="n">
-        <v>-622</v>
+        <v>-895</v>
       </c>
       <c r="F57" t="n">
         <v>12</v>
@@ -3345,7 +3345,7 @@
         <v>-802</v>
       </c>
       <c r="E58" t="n">
-        <v>2479</v>
+        <v>2355</v>
       </c>
       <c r="F58" t="n">
         <v>-86</v>
@@ -3396,7 +3396,7 @@
         <v>-936</v>
       </c>
       <c r="E59" t="n">
-        <v>-989</v>
+        <v>-671</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -3447,7 +3447,7 @@
         <v>-954</v>
       </c>
       <c r="E60" t="n">
-        <v>-990</v>
+        <v>-222</v>
       </c>
       <c r="F60" t="n">
         <v>4</v>
@@ -3498,7 +3498,7 @@
         <v>-969</v>
       </c>
       <c r="E61" t="n">
-        <v>1080</v>
+        <v>953</v>
       </c>
       <c r="F61" t="n">
         <v>-864</v>
@@ -3537,7 +3537,7 @@
         <v>-1036</v>
       </c>
       <c r="E62" t="n">
-        <v>-2419</v>
+        <v>-2441</v>
       </c>
       <c r="F62" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>-1106</v>
       </c>
       <c r="E63" t="n">
-        <v>671</v>
+        <v>477</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -3639,7 +3639,7 @@
         <v>-1147</v>
       </c>
       <c r="E64" t="n">
-        <v>-3094</v>
+        <v>-3692</v>
       </c>
       <c r="F64" t="n">
         <v>0</v>
@@ -3690,7 +3690,7 @@
         <v>-1255</v>
       </c>
       <c r="E65" t="n">
-        <v>-300</v>
+        <v>-194</v>
       </c>
       <c r="F65" t="n">
         <v>-170</v>
@@ -3741,7 +3741,7 @@
         <v>-1318</v>
       </c>
       <c r="E66" t="n">
-        <v>-479</v>
+        <v>-177</v>
       </c>
       <c r="F66" t="n">
         <v>75</v>
@@ -3792,7 +3792,7 @@
         <v>-1329</v>
       </c>
       <c r="E67" t="n">
-        <v>-1897</v>
+        <v>-1907</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -3843,7 +3843,7 @@
         <v>-1615</v>
       </c>
       <c r="E68" t="n">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="F68" t="n">
         <v>-848</v>
@@ -3894,7 +3894,7 @@
         <v>-1663</v>
       </c>
       <c r="E69" t="n">
-        <v>-7420</v>
+        <v>-6305</v>
       </c>
       <c r="F69" t="n">
         <v>299</v>
@@ -3945,7 +3945,7 @@
         <v>-1714</v>
       </c>
       <c r="E70" t="n">
-        <v>1093</v>
+        <v>707</v>
       </c>
       <c r="F70" t="n">
         <v>0</v>
@@ -3996,7 +3996,7 @@
         <v>-1740</v>
       </c>
       <c r="E71" t="n">
-        <v>-1237</v>
+        <v>-1370</v>
       </c>
       <c r="F71" t="n">
         <v>8</v>
@@ -4047,7 +4047,7 @@
         <v>-1878</v>
       </c>
       <c r="E72" t="n">
-        <v>690</v>
+        <v>701</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
@@ -4098,7 +4098,7 @@
         <v>-1910</v>
       </c>
       <c r="E73" t="n">
-        <v>-7503</v>
+        <v>-7453</v>
       </c>
       <c r="F73" t="n">
         <v>-2646</v>
@@ -4149,7 +4149,7 @@
         <v>-1987</v>
       </c>
       <c r="E74" t="n">
-        <v>-3715</v>
+        <v>-4095</v>
       </c>
       <c r="F74" t="n">
         <v>2</v>
@@ -4200,7 +4200,7 @@
         <v>-2038</v>
       </c>
       <c r="E75" t="n">
-        <v>-2751</v>
+        <v>-2293</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -4251,7 +4251,7 @@
         <v>-2139</v>
       </c>
       <c r="E76" t="n">
-        <v>-7596</v>
+        <v>-7205</v>
       </c>
       <c r="F76" t="n">
         <v>436</v>
@@ -4302,7 +4302,7 @@
         <v>-2147</v>
       </c>
       <c r="E77" t="n">
-        <v>-15893</v>
+        <v>-15851</v>
       </c>
       <c r="F77" t="n">
         <v>-748</v>
@@ -4353,7 +4353,7 @@
         <v>-2192</v>
       </c>
       <c r="E78" t="n">
-        <v>-3043</v>
+        <v>-3145</v>
       </c>
       <c r="F78" t="n">
         <v>-220</v>
@@ -4404,7 +4404,7 @@
         <v>-2762</v>
       </c>
       <c r="E79" t="n">
-        <v>4763</v>
+        <v>3938</v>
       </c>
       <c r="F79" t="n">
         <v>277</v>
@@ -4455,7 +4455,7 @@
         <v>-2902</v>
       </c>
       <c r="E80" t="n">
-        <v>-4867</v>
+        <v>-4611</v>
       </c>
       <c r="F80" t="n">
         <v>204</v>
@@ -4494,7 +4494,7 @@
         <v>-3096</v>
       </c>
       <c r="E81" t="n">
-        <v>-2887</v>
+        <v>-2917</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>-3224</v>
       </c>
       <c r="E82" t="n">
-        <v>455</v>
+        <v>748</v>
       </c>
       <c r="F82" t="n">
         <v>-274</v>
@@ -4596,7 +4596,7 @@
         <v>-3984</v>
       </c>
       <c r="E83" t="n">
-        <v>-3801</v>
+        <v>-3480</v>
       </c>
       <c r="F83" t="n">
         <v>70</v>
@@ -4647,7 +4647,7 @@
         <v>-4288</v>
       </c>
       <c r="E84" t="n">
-        <v>-3079</v>
+        <v>-3293</v>
       </c>
       <c r="F84" t="n">
         <v>0</v>
@@ -4698,7 +4698,7 @@
         <v>-4295</v>
       </c>
       <c r="E85" t="n">
-        <v>-16706</v>
+        <v>-16536</v>
       </c>
       <c r="F85" t="n">
         <v>616</v>
@@ -4749,7 +4749,7 @@
         <v>-4557</v>
       </c>
       <c r="E86" t="n">
-        <v>143</v>
+        <v>-243</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -4800,7 +4800,7 @@
         <v>-5163</v>
       </c>
       <c r="E87" t="n">
-        <v>-28874</v>
+        <v>-26550</v>
       </c>
       <c r="F87" t="n">
         <v>185</v>
@@ -4851,7 +4851,7 @@
         <v>-5398</v>
       </c>
       <c r="E88" t="n">
-        <v>-12931</v>
+        <v>-13261</v>
       </c>
       <c r="F88" t="n">
         <v>-1</v>
@@ -4902,7 +4902,7 @@
         <v>-7091</v>
       </c>
       <c r="E89" t="n">
-        <v>-18085</v>
+        <v>-18175</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -4953,7 +4953,7 @@
         <v>-8534</v>
       </c>
       <c r="E90" t="n">
-        <v>-23417</v>
+        <v>-23154</v>
       </c>
       <c r="F90" t="n">
         <v>0</v>
@@ -5004,7 +5004,7 @@
         <v>-9147</v>
       </c>
       <c r="E91" t="n">
-        <v>-4033</v>
+        <v>-2610</v>
       </c>
       <c r="F91" t="n">
         <v>1286</v>
@@ -5055,7 +5055,7 @@
         <v>-10490</v>
       </c>
       <c r="E92" t="n">
-        <v>-94343</v>
+        <v>-90916</v>
       </c>
       <c r="F92" t="n">
         <v>-1623</v>
@@ -5106,7 +5106,7 @@
         <v>-10550</v>
       </c>
       <c r="E93" t="n">
-        <v>-40878</v>
+        <v>-41407</v>
       </c>
       <c r="F93" t="n">
         <v>5645</v>
@@ -5157,7 +5157,7 @@
         <v>-10720</v>
       </c>
       <c r="E94" t="n">
-        <v>-11750</v>
+        <v>-11796</v>
       </c>
       <c r="F94" t="n">
         <v>-3873</v>
@@ -5208,7 +5208,7 @@
         <v>-11185</v>
       </c>
       <c r="E95" t="n">
-        <v>-89583</v>
+        <v>-81596</v>
       </c>
       <c r="F95" t="n">
         <v>909</v>
@@ -5259,7 +5259,7 @@
         <v>-12058</v>
       </c>
       <c r="E96" t="n">
-        <v>81101</v>
+        <v>74220</v>
       </c>
       <c r="F96" t="n">
         <v>549</v>
@@ -5310,7 +5310,7 @@
         <v>-14666</v>
       </c>
       <c r="E97" t="n">
-        <v>6028</v>
+        <v>6014</v>
       </c>
       <c r="F97" t="n">
         <v>18</v>
@@ -5361,7 +5361,7 @@
         <v>-14690</v>
       </c>
       <c r="E98" t="n">
-        <v>-15697</v>
+        <v>-15313</v>
       </c>
       <c r="F98" t="n">
         <v>8508</v>
@@ -5412,7 +5412,7 @@
         <v>-15797</v>
       </c>
       <c r="E99" t="n">
-        <v>-74446</v>
+        <v>-74107</v>
       </c>
       <c r="F99" t="n">
         <v>1000</v>
@@ -5463,7 +5463,7 @@
         <v>-16741</v>
       </c>
       <c r="E100" t="n">
-        <v>-22934</v>
+        <v>-23643</v>
       </c>
       <c r="F100" t="n">
         <v>2081</v>
@@ -5502,7 +5502,7 @@
         <v>-21607</v>
       </c>
       <c r="E101" t="n">
-        <v>48084</v>
+        <v>45391</v>
       </c>
       <c r="F101" t="n">
         <v>-962</v>
@@ -5553,7 +5553,7 @@
         <v>-24136</v>
       </c>
       <c r="E102" t="n">
-        <v>108642</v>
+        <v>108522</v>
       </c>
       <c r="F102" t="n">
         <v>-1541</v>
@@ -5604,7 +5604,7 @@
         <v>-30514</v>
       </c>
       <c r="E103" t="n">
-        <v>89984</v>
+        <v>85134</v>
       </c>
       <c r="F103" t="n">
         <v>1268</v>
@@ -5655,7 +5655,7 @@
         <v>-53584</v>
       </c>
       <c r="E104" t="n">
-        <v>54013</v>
+        <v>39067</v>
       </c>
       <c r="F104" t="n">
         <v>-19993</v>
@@ -5706,7 +5706,7 @@
         <v>-102323</v>
       </c>
       <c r="E105" t="n">
-        <v>150472</v>
+        <v>148582</v>
       </c>
       <c r="F105" t="n">
         <v>-10188</v>

--- a/data/台股_外資雷達.xlsx
+++ b/data/台股_外資雷達.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="總覽" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="翻轉警報" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,22 +496,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17401</v>
+        <v>9819</v>
       </c>
       <c r="D2" t="n">
-        <v>91921</v>
+        <v>95713</v>
       </c>
       <c r="E2" t="n">
-        <v>184135</v>
+        <v>170373</v>
       </c>
       <c r="F2" t="n">
-        <v>276</v>
+        <v>1341</v>
       </c>
       <c r="G2" t="n">
-        <v>25</v>
+        <v>-278</v>
       </c>
       <c r="H2" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -546,22 +547,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26733</v>
+        <v>18794</v>
       </c>
       <c r="D3" t="n">
-        <v>48073</v>
+        <v>47916</v>
       </c>
       <c r="E3" t="n">
-        <v>22159</v>
+        <v>22451</v>
       </c>
       <c r="F3" t="n">
-        <v>-3299</v>
+        <v>-3666</v>
       </c>
       <c r="G3" t="n">
-        <v>-11301</v>
+        <v>-12289</v>
       </c>
       <c r="H3" t="n">
-        <v>4351</v>
+        <v>3366</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -597,22 +598,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8648</v>
+        <v>8771</v>
       </c>
       <c r="D4" t="n">
-        <v>46352</v>
+        <v>44876</v>
       </c>
       <c r="E4" t="n">
-        <v>184164</v>
+        <v>171589</v>
       </c>
       <c r="F4" t="n">
-        <v>1723</v>
+        <v>-426</v>
       </c>
       <c r="G4" t="n">
-        <v>5800</v>
+        <v>5806</v>
       </c>
       <c r="H4" t="n">
-        <v>-2092</v>
+        <v>-1822</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -639,31 +640,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8908</v>
+        <v>-1013</v>
       </c>
       <c r="D5" t="n">
-        <v>13970</v>
+        <v>12606</v>
       </c>
       <c r="E5" t="n">
-        <v>17571</v>
+        <v>89560</v>
       </c>
       <c r="F5" t="n">
-        <v>259</v>
+        <v>1431</v>
       </c>
       <c r="G5" t="n">
-        <v>2545</v>
+        <v>1831</v>
       </c>
       <c r="H5" t="n">
-        <v>1871</v>
+        <v>533</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -672,49 +673,49 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>📉 減速</t>
+          <t>🐌 龜速</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>592</v>
+        <v>2835</v>
       </c>
       <c r="D6" t="n">
-        <v>13023</v>
+        <v>10426</v>
       </c>
       <c r="E6" t="n">
-        <v>98838</v>
+        <v>3942</v>
       </c>
       <c r="F6" t="n">
-        <v>549</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>1189</v>
+        <v>-6</v>
       </c>
       <c r="H6" t="n">
-        <v>62</v>
+        <v>690</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -727,7 +728,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -735,92 +736,92 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1236</v>
+        <v>1550</v>
       </c>
       <c r="D7" t="n">
-        <v>10934</v>
+        <v>9881</v>
       </c>
       <c r="E7" t="n">
-        <v>25120</v>
+        <v>-1789</v>
       </c>
       <c r="F7" t="n">
-        <v>-165</v>
+        <v>-4528</v>
       </c>
       <c r="G7" t="n">
-        <v>-112</v>
+        <v>-20150</v>
       </c>
       <c r="H7" t="n">
-        <v>-80</v>
+        <v>1093</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>🚀 大買</t>
+          <t>🟢 加碼</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>🐌 龜速</t>
+          <t>🚀 加速器</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>廣達</t>
         </is>
       </